--- a/AAAGameData/DataTables/ResourceConfigTable.xlsx
+++ b/AAAGameData/DataTables/ResourceConfigTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="14855"/>
+    <workbookView windowWidth="27948" windowHeight="11855"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="27">
   <si>
     <t>#</t>
   </si>
@@ -111,6 +111,96 @@
   </si>
   <si>
     <t>开始游戏界面背景</t>
+  </si>
+  <si>
+    <r>
+      <t>UI/StartMenuUI/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>诸神对决</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>.png</t>
+    </r>
+  </si>
+  <si>
+    <t>游戏名称</t>
+  </si>
+  <si>
+    <r>
+      <t>UI/StartMenuUI/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Clash Of Gods</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>.png</t>
+    </r>
+  </si>
+  <si>
+    <t>游戏名称-英文</t>
+  </si>
+  <si>
+    <r>
+      <t>UI/StartMenuUI/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>存档上云</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>.png</t>
+    </r>
+  </si>
+  <si>
+    <t>存档上云图标</t>
+  </si>
+  <si>
+    <t>UI/CloudInfo/PlayerInfo</t>
+  </si>
+  <si>
+    <t>角色信息预制体</t>
+  </si>
+  <si>
+    <t>UI/CloudInfo/ItemsInfo</t>
+  </si>
+  <si>
+    <t>仓库信息预制体</t>
+  </si>
+  <si>
+    <t>UI/CloudInfo/TimeInfo</t>
+  </si>
+  <si>
+    <t>存档时间预制体</t>
   </si>
 </sst>
 </file>
@@ -1274,8 +1364,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4" outlineLevelCol="5"/>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
     <col min="4" max="4" width="22.2222222222222" customWidth="1"/>
     <col min="5" max="5" width="36.1111111111111" customWidth="1"/>
@@ -1355,6 +1445,90 @@
       </c>
       <c r="F5" s="1" t="s">
         <v>14</v>
+      </c>
+    </row>
+    <row r="6" customFormat="1" spans="1:6">
+      <c r="B6">
+        <v>1002</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" customFormat="1" spans="1:6">
+      <c r="B7">
+        <v>1003</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" customFormat="1" spans="1:6">
+      <c r="B8">
+        <v>1004</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" customFormat="1" spans="1:6">
+      <c r="B9">
+        <v>5001</v>
+      </c>
+      <c r="D9">
+        <v>2</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" customFormat="1" spans="1:6">
+      <c r="B10">
+        <v>5002</v>
+      </c>
+      <c r="D10">
+        <v>2</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" customFormat="1" spans="1:6">
+      <c r="B11">
+        <v>5003</v>
+      </c>
+      <c r="D11">
+        <v>2</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/DataTables/ResourceConfigTable.xlsx
+++ b/AAAGameData/DataTables/ResourceConfigTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="14855"/>
+    <workbookView windowWidth="28800" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -134,7 +134,7 @@
     <t>Card/HolyLight.png</t>
   </si>
   <si>
-    <t>群体圣光-策略卡图标</t>
+    <t>神圣庇护-策略卡图标</t>
   </si>
   <si>
     <t>Chess/后羿/后羿立绘.png</t>
@@ -633,14 +633,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1096,148 +1089,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1593,7 +1586,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F99"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="21" customWidth="1"/>
@@ -1650,7 +1643,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" ht="86.4" spans="1:6">
+    <row r="4" ht="81" spans="1:6">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>

--- a/AAAGameData/DataTables/ResourceConfigTable.xlsx
+++ b/AAAGameData/DataTables/ResourceConfigTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27948" windowHeight="11855"/>
+    <workbookView windowWidth="28800" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="236">
   <si>
     <t>#</t>
   </si>
@@ -729,6 +729,12 @@
   </si>
   <si>
     <t>名字背景-稀有度4</t>
+  </si>
+  <si>
+    <t>Enemy/默认.png</t>
+  </si>
+  <si>
+    <t>敌人图标</t>
   </si>
 </sst>
 </file>
@@ -741,14 +747,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1204,148 +1203,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1700,8 +1699,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F117"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <dimension ref="A1:F118"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="21" customWidth="1"/>
@@ -1758,7 +1757,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" ht="86.4" spans="1:6">
+    <row r="4" ht="81" spans="1:6">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -3584,6 +3583,20 @@
       </c>
       <c r="F117" s="1" t="s">
         <v>233</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6">
+      <c r="B118">
+        <v>11001</v>
+      </c>
+      <c r="D118">
+        <v>1</v>
+      </c>
+      <c r="E118" t="s">
+        <v>234</v>
+      </c>
+      <c r="F118" t="s">
+        <v>235</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/DataTables/ResourceConfigTable.xlsx
+++ b/AAAGameData/DataTables/ResourceConfigTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11925"/>
+    <workbookView windowWidth="29868" windowHeight="14855"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -389,73 +389,73 @@
     <t>月华天倾-嫦娥技能图标</t>
   </si>
   <si>
-    <t>Items/Consumable/Wallet.png</t>
+    <t>Items/1.png</t>
   </si>
   <si>
     <t>钱包图标</t>
   </si>
   <si>
-    <t>Items/Consumable/HPPotion.png</t>
+    <t>Items/2.png</t>
   </si>
   <si>
     <t>生命药水图标</t>
   </si>
   <si>
-    <t>Items/Consumable/MPPotion.png</t>
+    <t>Items/3.png</t>
   </si>
   <si>
     <t>魔法药水图标</t>
   </si>
   <si>
-    <t>Items/Consumable/ExpGem.png</t>
+    <t>Items/4.png</t>
   </si>
   <si>
     <t>经验宝石图标</t>
   </si>
   <si>
-    <t>Items/Quest/MysteryKey.png</t>
+    <t>Items/5.png</t>
   </si>
   <si>
     <t>神秘钥匙图标</t>
   </si>
   <si>
-    <t>Items/Quest/AncientScroll.png</t>
+    <t>Items/6.png</t>
   </si>
   <si>
     <t>古老卷轴图标</t>
   </si>
   <si>
-    <t>Items/Treasure/Magatama.png</t>
+    <t>Items/7.png</t>
   </si>
   <si>
     <t>八尺琼勾玉图标</t>
   </si>
   <si>
-    <t>Items/Treasure/Kusanagi.png</t>
+    <t>Items/8.png</t>
   </si>
   <si>
     <t>天丛云剑图标</t>
   </si>
   <si>
-    <t>Items/Treasure/Yata.png</t>
+    <t>Items/9.png</t>
   </si>
   <si>
     <t>八咫镜图标</t>
   </si>
   <si>
-    <t>Items/Equipment/Excalibur.png</t>
+    <t>Items/10.png</t>
   </si>
   <si>
     <t>石中剑图标</t>
   </si>
   <si>
-    <t>Items/Equipment/DragonArmor.png</t>
+    <t>Items/11.png</t>
   </si>
   <si>
     <t>龙鳞铠甲图标</t>
   </si>
   <si>
-    <t>Items/Equipment/ElvenRing.png</t>
+    <t>Items/12.png</t>
   </si>
   <si>
     <t>精灵之戒图标</t>
@@ -1700,7 +1700,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F118"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="21" customWidth="1"/>
@@ -1757,7 +1757,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" ht="81" spans="1:6">
+    <row r="4" ht="86.4" spans="1:6">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>

--- a/AAAGameData/DataTables/ResourceConfigTable.xlsx
+++ b/AAAGameData/DataTables/ResourceConfigTable.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="264">
   <si>
     <t>#</t>
   </si>
@@ -461,6 +461,78 @@
     <t>精灵之戒图标</t>
   </si>
   <si>
+    <t>Items/13.png</t>
+  </si>
+  <si>
+    <t>月华玉璧图标</t>
+  </si>
+  <si>
+    <t>Items/14.png</t>
+  </si>
+  <si>
+    <t>太阴弦月弓图标</t>
+  </si>
+  <si>
+    <t>Items/15.png</t>
+  </si>
+  <si>
+    <t>月轮镜图标</t>
+  </si>
+  <si>
+    <t>Items/16.png</t>
+  </si>
+  <si>
+    <t>炎魔之心图标</t>
+  </si>
+  <si>
+    <t>Items/17.png</t>
+  </si>
+  <si>
+    <t>炎魔之冠图标</t>
+  </si>
+  <si>
+    <t>Items/18.png</t>
+  </si>
+  <si>
+    <t>炎魔之剑图标</t>
+  </si>
+  <si>
+    <t>Items/19.png</t>
+  </si>
+  <si>
+    <t>古剑·樱花落图标</t>
+  </si>
+  <si>
+    <t>Items/20.png</t>
+  </si>
+  <si>
+    <t>暗影斗篷图标</t>
+  </si>
+  <si>
+    <t>Items/21.png</t>
+  </si>
+  <si>
+    <t>圣光铠甲图标</t>
+  </si>
+  <si>
+    <t>Items/22.png</t>
+  </si>
+  <si>
+    <t>古墓盗贼手套图标</t>
+  </si>
+  <si>
+    <t>Items/23.png</t>
+  </si>
+  <si>
+    <t>冰晶靴图标</t>
+  </si>
+  <si>
+    <t>Items/24.png</t>
+  </si>
+  <si>
+    <t>风暴法杖图标</t>
+  </si>
+  <si>
     <t>UI/CloudInfo/PlayerInfo</t>
   </si>
   <si>
@@ -567,6 +639,18 @@
   </si>
   <si>
     <t>嫦娥普攻子弹</t>
+  </si>
+  <si>
+    <t>SummonChessEffect/Change_Skill1</t>
+  </si>
+  <si>
+    <t>嫦娥技能一子弹</t>
+  </si>
+  <si>
+    <t>SummonChessEffect/Change_Skill2</t>
+  </si>
+  <si>
+    <t>嫦娥大招特效</t>
   </si>
   <si>
     <t>Skills/SkillParamRegistry</t>
@@ -1699,7 +1783,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F118"/>
+  <dimension ref="A1:F132"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -2852,11 +2936,11 @@
     <row r="72" ht="15" customHeight="1" spans="1:6">
       <c r="A72" s="1"/>
       <c r="B72" s="1">
-        <v>2001</v>
+        <v>1913</v>
       </c>
       <c r="C72" s="1"/>
       <c r="D72" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>144</v>
@@ -2868,11 +2952,11 @@
     <row r="73" ht="15" customHeight="1" spans="1:6">
       <c r="A73" s="1"/>
       <c r="B73" s="1">
-        <v>2002</v>
+        <v>1914</v>
       </c>
       <c r="C73" s="1"/>
       <c r="D73" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>146</v>
@@ -2881,14 +2965,14 @@
         <v>147</v>
       </c>
     </row>
-    <row r="74" ht="15" customHeight="1" spans="1:6">
+    <row r="74" customFormat="1" ht="15" customHeight="1" spans="1:6">
       <c r="A74" s="1"/>
       <c r="B74" s="1">
-        <v>2003</v>
+        <v>1915</v>
       </c>
       <c r="C74" s="1"/>
       <c r="D74" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E74" s="1" t="s">
         <v>148</v>
@@ -2900,11 +2984,11 @@
     <row r="75" ht="15" customHeight="1" spans="1:6">
       <c r="A75" s="1"/>
       <c r="B75" s="1">
-        <v>2004</v>
+        <v>1916</v>
       </c>
       <c r="C75" s="1"/>
       <c r="D75" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E75" s="1" t="s">
         <v>150</v>
@@ -2916,11 +3000,11 @@
     <row r="76" ht="15" customHeight="1" spans="1:6">
       <c r="A76" s="1"/>
       <c r="B76" s="1">
-        <v>2101</v>
+        <v>1917</v>
       </c>
       <c r="C76" s="1"/>
       <c r="D76" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>152</v>
@@ -2932,11 +3016,11 @@
     <row r="77" ht="15" customHeight="1" spans="1:6">
       <c r="A77" s="1"/>
       <c r="B77" s="1">
-        <v>2102</v>
+        <v>1918</v>
       </c>
       <c r="C77" s="1"/>
       <c r="D77" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>154</v>
@@ -2948,222 +3032,222 @@
     <row r="78" ht="15" customHeight="1" spans="1:6">
       <c r="A78" s="1"/>
       <c r="B78" s="1">
-        <v>2103</v>
+        <v>1919</v>
       </c>
       <c r="C78" s="1"/>
       <c r="D78" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1" spans="1:6">
       <c r="A79" s="1"/>
       <c r="B79" s="1">
-        <v>2104</v>
+        <v>1920</v>
       </c>
       <c r="C79" s="1"/>
       <c r="D79" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1" spans="1:6">
       <c r="A80" s="1"/>
       <c r="B80" s="1">
-        <v>2201</v>
+        <v>1921</v>
       </c>
       <c r="C80" s="1"/>
       <c r="D80" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1" spans="1:6">
       <c r="A81" s="1"/>
       <c r="B81" s="1">
-        <v>2301</v>
+        <v>1922</v>
       </c>
       <c r="C81" s="1"/>
       <c r="D81" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1" spans="1:6">
       <c r="A82" s="1"/>
       <c r="B82" s="1">
-        <v>2304</v>
+        <v>1923</v>
       </c>
       <c r="C82" s="1"/>
       <c r="D82" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1" spans="1:6">
       <c r="A83" s="1"/>
       <c r="B83" s="1">
-        <v>2309</v>
+        <v>1924</v>
       </c>
       <c r="C83" s="1"/>
       <c r="D83" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="84" ht="15" customHeight="1" spans="1:6">
       <c r="A84" s="1"/>
       <c r="B84" s="1">
-        <v>2399</v>
+        <v>2001</v>
       </c>
       <c r="C84" s="1"/>
       <c r="D84" s="1">
         <v>2</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1" spans="1:6">
       <c r="A85" s="1"/>
       <c r="B85" s="1">
-        <v>2401</v>
+        <v>2002</v>
       </c>
       <c r="C85" s="1"/>
       <c r="D85" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1" spans="1:6">
       <c r="A86" s="1"/>
       <c r="B86" s="1">
-        <v>2901</v>
+        <v>2003</v>
       </c>
       <c r="C86" s="1"/>
       <c r="D86" s="1">
         <v>2</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1" spans="1:6">
       <c r="A87" s="1"/>
       <c r="B87" s="1">
-        <v>3001</v>
+        <v>2004</v>
       </c>
       <c r="C87" s="1"/>
       <c r="D87" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="88" ht="15" customHeight="1" spans="1:6">
       <c r="A88" s="1"/>
       <c r="B88" s="1">
-        <v>3002</v>
+        <v>2101</v>
       </c>
       <c r="C88" s="1"/>
       <c r="D88" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="89" ht="15" customHeight="1" spans="1:6">
       <c r="A89" s="1"/>
       <c r="B89" s="1">
-        <v>3003</v>
+        <v>2102</v>
       </c>
       <c r="C89" s="1"/>
       <c r="D89" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="90" ht="15" customHeight="1" spans="1:6">
       <c r="A90" s="1"/>
       <c r="B90" s="1">
-        <v>3004</v>
+        <v>2103</v>
       </c>
       <c r="C90" s="1"/>
       <c r="D90" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>178</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="91" ht="15" customHeight="1" spans="1:6">
       <c r="A91" s="1"/>
       <c r="B91" s="1">
-        <v>6001</v>
+        <v>2104</v>
       </c>
       <c r="C91" s="1"/>
       <c r="D91" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>181</v>
@@ -3172,11 +3256,11 @@
     <row r="92" ht="15" customHeight="1" spans="1:6">
       <c r="A92" s="1"/>
       <c r="B92" s="1">
-        <v>10001</v>
+        <v>2201</v>
       </c>
       <c r="C92" s="1"/>
       <c r="D92" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E92" s="1" t="s">
         <v>182</v>
@@ -3188,11 +3272,11 @@
     <row r="93" ht="15" customHeight="1" spans="1:6">
       <c r="A93" s="1"/>
       <c r="B93" s="1">
-        <v>10002</v>
+        <v>2301</v>
       </c>
       <c r="C93" s="1"/>
       <c r="D93" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E93" s="1" t="s">
         <v>184</v>
@@ -3204,11 +3288,11 @@
     <row r="94" ht="15" customHeight="1" spans="1:6">
       <c r="A94" s="1"/>
       <c r="B94" s="1">
-        <v>10003</v>
+        <v>2304</v>
       </c>
       <c r="C94" s="1"/>
       <c r="D94" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E94" s="1" t="s">
         <v>186</v>
@@ -3220,11 +3304,11 @@
     <row r="95" ht="15" customHeight="1" spans="1:6">
       <c r="A95" s="1"/>
       <c r="B95" s="1">
-        <v>10004</v>
+        <v>2309</v>
       </c>
       <c r="C95" s="1"/>
       <c r="D95" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E95" s="1" t="s">
         <v>188</v>
@@ -3236,11 +3320,11 @@
     <row r="96" ht="15" customHeight="1" spans="1:6">
       <c r="A96" s="1"/>
       <c r="B96" s="1">
-        <v>10101</v>
+        <v>2399</v>
       </c>
       <c r="C96" s="1"/>
       <c r="D96" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E96" s="1" t="s">
         <v>190</v>
@@ -3252,11 +3336,11 @@
     <row r="97" ht="15" customHeight="1" spans="1:6">
       <c r="A97" s="1"/>
       <c r="B97" s="1">
-        <v>10102</v>
+        <v>2401</v>
       </c>
       <c r="C97" s="1"/>
       <c r="D97" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E97" s="1" t="s">
         <v>192</v>
@@ -3268,11 +3352,11 @@
     <row r="98" ht="15" customHeight="1" spans="1:6">
       <c r="A98" s="1"/>
       <c r="B98" s="1">
-        <v>10103</v>
+        <v>2901</v>
       </c>
       <c r="C98" s="1"/>
       <c r="D98" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E98" s="1" t="s">
         <v>194</v>
@@ -3284,11 +3368,11 @@
     <row r="99" ht="15" customHeight="1" spans="1:6">
       <c r="A99" s="1"/>
       <c r="B99" s="1">
-        <v>10201</v>
+        <v>3001</v>
       </c>
       <c r="C99" s="1"/>
       <c r="D99" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E99" s="1" t="s">
         <v>196</v>
@@ -3300,11 +3384,11 @@
     <row r="100" ht="15" customHeight="1" spans="1:6">
       <c r="A100" s="1"/>
       <c r="B100" s="1">
-        <v>10202</v>
+        <v>3002</v>
       </c>
       <c r="C100" s="1"/>
       <c r="D100" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E100" s="1" t="s">
         <v>198</v>
@@ -3316,11 +3400,11 @@
     <row r="101" ht="15" customHeight="1" spans="1:6">
       <c r="A101" s="1"/>
       <c r="B101" s="1">
-        <v>10203</v>
+        <v>3003</v>
       </c>
       <c r="C101" s="1"/>
       <c r="D101" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>200</v>
@@ -3332,11 +3416,11 @@
     <row r="102" ht="15" customHeight="1" spans="1:6">
       <c r="A102" s="1"/>
       <c r="B102" s="1">
-        <v>15001</v>
+        <v>3004</v>
       </c>
       <c r="C102" s="1"/>
       <c r="D102" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E102" s="1" t="s">
         <v>202</v>
@@ -3348,11 +3432,11 @@
     <row r="103" ht="15" customHeight="1" spans="1:6">
       <c r="A103" s="1"/>
       <c r="B103" s="1">
-        <v>15002</v>
+        <v>3005</v>
       </c>
       <c r="C103" s="1"/>
       <c r="D103" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E103" s="1" t="s">
         <v>204</v>
@@ -3364,11 +3448,11 @@
     <row r="104" ht="15" customHeight="1" spans="1:6">
       <c r="A104" s="1"/>
       <c r="B104" s="1">
-        <v>15003</v>
+        <v>3006</v>
       </c>
       <c r="C104" s="1"/>
       <c r="D104" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E104" s="1" t="s">
         <v>206</v>
@@ -3380,11 +3464,11 @@
     <row r="105" ht="15" customHeight="1" spans="1:6">
       <c r="A105" s="1"/>
       <c r="B105" s="1">
-        <v>15005</v>
+        <v>6001</v>
       </c>
       <c r="C105" s="1"/>
       <c r="D105" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E105" s="1" t="s">
         <v>208</v>
@@ -3396,7 +3480,7 @@
     <row r="106" ht="15" customHeight="1" spans="1:6">
       <c r="A106" s="1"/>
       <c r="B106" s="1">
-        <v>15007</v>
+        <v>10001</v>
       </c>
       <c r="C106" s="1"/>
       <c r="D106" s="1">
@@ -3412,7 +3496,7 @@
     <row r="107" ht="15" customHeight="1" spans="1:6">
       <c r="A107" s="1"/>
       <c r="B107" s="1">
-        <v>15008</v>
+        <v>10002</v>
       </c>
       <c r="C107" s="1"/>
       <c r="D107" s="1">
@@ -3428,7 +3512,7 @@
     <row r="108" ht="15" customHeight="1" spans="1:6">
       <c r="A108" s="1"/>
       <c r="B108" s="1">
-        <v>15009</v>
+        <v>10003</v>
       </c>
       <c r="C108" s="1"/>
       <c r="D108" s="1">
@@ -3444,7 +3528,7 @@
     <row r="109" ht="15" customHeight="1" spans="1:6">
       <c r="A109" s="1"/>
       <c r="B109" s="1">
-        <v>19002</v>
+        <v>10004</v>
       </c>
       <c r="C109" s="1"/>
       <c r="D109" s="1">
@@ -3460,7 +3544,7 @@
     <row r="110" ht="15" customHeight="1" spans="1:6">
       <c r="A110" s="1"/>
       <c r="B110" s="1">
-        <v>19003</v>
+        <v>10101</v>
       </c>
       <c r="C110" s="1"/>
       <c r="D110" s="1">
@@ -3476,7 +3560,7 @@
     <row r="111" ht="15" customHeight="1" spans="1:6">
       <c r="A111" s="1"/>
       <c r="B111" s="1">
-        <v>19004</v>
+        <v>10102</v>
       </c>
       <c r="C111" s="1"/>
       <c r="D111" s="1">
@@ -3492,7 +3576,7 @@
     <row r="112" ht="15" customHeight="1" spans="1:6">
       <c r="A112" s="1"/>
       <c r="B112" s="1">
-        <v>19012</v>
+        <v>10103</v>
       </c>
       <c r="C112" s="1"/>
       <c r="D112" s="1">
@@ -3508,7 +3592,7 @@
     <row r="113" ht="15" customHeight="1" spans="1:6">
       <c r="A113" s="1"/>
       <c r="B113" s="1">
-        <v>19013</v>
+        <v>10201</v>
       </c>
       <c r="C113" s="1"/>
       <c r="D113" s="1">
@@ -3524,7 +3608,7 @@
     <row r="114" ht="15" customHeight="1" spans="1:6">
       <c r="A114" s="1"/>
       <c r="B114" s="1">
-        <v>19014</v>
+        <v>10202</v>
       </c>
       <c r="C114" s="1"/>
       <c r="D114" s="1">
@@ -3540,7 +3624,7 @@
     <row r="115" ht="15" customHeight="1" spans="1:6">
       <c r="A115" s="1"/>
       <c r="B115" s="1">
-        <v>19022</v>
+        <v>10203</v>
       </c>
       <c r="C115" s="1"/>
       <c r="D115" s="1">
@@ -3556,7 +3640,7 @@
     <row r="116" ht="15" customHeight="1" spans="1:6">
       <c r="A116" s="1"/>
       <c r="B116" s="1">
-        <v>19023</v>
+        <v>15001</v>
       </c>
       <c r="C116" s="1"/>
       <c r="D116" s="1">
@@ -3572,7 +3656,7 @@
     <row r="117" ht="15" customHeight="1" spans="1:6">
       <c r="A117" s="1"/>
       <c r="B117" s="1">
-        <v>19024</v>
+        <v>15002</v>
       </c>
       <c r="C117" s="1"/>
       <c r="D117" s="1">
@@ -3585,18 +3669,242 @@
         <v>233</v>
       </c>
     </row>
-    <row r="118" spans="1:6">
-      <c r="B118">
+    <row r="118" ht="15" customHeight="1" spans="1:6">
+      <c r="A118" s="1"/>
+      <c r="B118" s="1">
+        <v>15003</v>
+      </c>
+      <c r="C118" s="1"/>
+      <c r="D118" s="1">
+        <v>1</v>
+      </c>
+      <c r="E118" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="F118" s="1" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="119" ht="15" customHeight="1" spans="1:6">
+      <c r="A119" s="1"/>
+      <c r="B119" s="1">
+        <v>15005</v>
+      </c>
+      <c r="C119" s="1"/>
+      <c r="D119" s="1">
+        <v>1</v>
+      </c>
+      <c r="E119" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="F119" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="120" ht="15" customHeight="1" spans="1:6">
+      <c r="A120" s="1"/>
+      <c r="B120" s="1">
+        <v>15007</v>
+      </c>
+      <c r="C120" s="1"/>
+      <c r="D120" s="1">
+        <v>1</v>
+      </c>
+      <c r="E120" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="F120" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="121" ht="15" customHeight="1" spans="1:6">
+      <c r="A121" s="1"/>
+      <c r="B121" s="1">
+        <v>15008</v>
+      </c>
+      <c r="C121" s="1"/>
+      <c r="D121" s="1">
+        <v>1</v>
+      </c>
+      <c r="E121" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="F121" s="1" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="122" ht="15" customHeight="1" spans="1:6">
+      <c r="A122" s="1"/>
+      <c r="B122" s="1">
+        <v>15009</v>
+      </c>
+      <c r="C122" s="1"/>
+      <c r="D122" s="1">
+        <v>1</v>
+      </c>
+      <c r="E122" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="F122" s="1" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="123" ht="15" customHeight="1" spans="1:6">
+      <c r="A123" s="1"/>
+      <c r="B123" s="1">
+        <v>19002</v>
+      </c>
+      <c r="C123" s="1"/>
+      <c r="D123" s="1">
+        <v>1</v>
+      </c>
+      <c r="E123" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="F123" s="1" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="124" ht="15" customHeight="1" spans="1:6">
+      <c r="A124" s="1"/>
+      <c r="B124" s="1">
+        <v>19003</v>
+      </c>
+      <c r="C124" s="1"/>
+      <c r="D124" s="1">
+        <v>1</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="F124" s="1" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="125" ht="15" customHeight="1" spans="1:6">
+      <c r="A125" s="1"/>
+      <c r="B125" s="1">
+        <v>19004</v>
+      </c>
+      <c r="C125" s="1"/>
+      <c r="D125" s="1">
+        <v>1</v>
+      </c>
+      <c r="E125" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="F125" s="1" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="126" ht="15" customHeight="1" spans="1:6">
+      <c r="A126" s="1"/>
+      <c r="B126" s="1">
+        <v>19012</v>
+      </c>
+      <c r="C126" s="1"/>
+      <c r="D126" s="1">
+        <v>1</v>
+      </c>
+      <c r="E126" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="F126" s="1" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="127" ht="15" customHeight="1" spans="1:6">
+      <c r="A127" s="1"/>
+      <c r="B127" s="1">
+        <v>19013</v>
+      </c>
+      <c r="C127" s="1"/>
+      <c r="D127" s="1">
+        <v>1</v>
+      </c>
+      <c r="E127" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="F127" s="1" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="128" ht="15" customHeight="1" spans="1:6">
+      <c r="A128" s="1"/>
+      <c r="B128" s="1">
+        <v>19014</v>
+      </c>
+      <c r="C128" s="1"/>
+      <c r="D128" s="1">
+        <v>1</v>
+      </c>
+      <c r="E128" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="F128" s="1" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="129" ht="15" customHeight="1" spans="1:6">
+      <c r="A129" s="1"/>
+      <c r="B129" s="1">
+        <v>19022</v>
+      </c>
+      <c r="C129" s="1"/>
+      <c r="D129" s="1">
+        <v>1</v>
+      </c>
+      <c r="E129" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="F129" s="1" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="130" ht="15" customHeight="1" spans="1:6">
+      <c r="A130" s="1"/>
+      <c r="B130" s="1">
+        <v>19023</v>
+      </c>
+      <c r="C130" s="1"/>
+      <c r="D130" s="1">
+        <v>1</v>
+      </c>
+      <c r="E130" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="F130" s="1" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="131" ht="15" customHeight="1" spans="1:6">
+      <c r="A131" s="1"/>
+      <c r="B131" s="1">
+        <v>19024</v>
+      </c>
+      <c r="C131" s="1"/>
+      <c r="D131" s="1">
+        <v>1</v>
+      </c>
+      <c r="E131" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="F131" s="1" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6">
+      <c r="B132">
         <v>11001</v>
       </c>
-      <c r="D118">
-        <v>1</v>
-      </c>
-      <c r="E118" t="s">
-        <v>234</v>
-      </c>
-      <c r="F118" t="s">
-        <v>235</v>
+      <c r="D132">
+        <v>1</v>
+      </c>
+      <c r="E132" t="s">
+        <v>262</v>
+      </c>
+      <c r="F132" t="s">
+        <v>263</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/DataTables/ResourceConfigTable.xlsx
+++ b/AAAGameData/DataTables/ResourceConfigTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="14855"/>
+    <workbookView windowWidth="28800" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="268">
   <si>
     <t>#</t>
   </si>
@@ -56,7 +56,12 @@
     <t>资源ID</t>
   </si>
   <si>
-    <t>1：Assets/AAAGame/Sprites/2：Assets/AAAGame/Prefabs/3：Assets/AAAGame/Entities/4：Assets/AAAGame/Materials/5：Assets/AAAGame/Textures/6：Assets/AAAGame/Config/备注：大型资源和通用资源放这里</t>
+    <t>1：Assets/AAAGame/Sprites/
+2：Assets/AAAGame/Prefabs/
+3：Assets/AAAGame/Prefabs/Entity/
+4：Assets/AAAGame/Materials/
+5：Assets/AAAGame/Textures/
+6：Assets/AAAGame/Config/</t>
   </si>
   <si>
     <t>资源类型：1 = Sprite（图片）2 = Prefab（预制体）3 = Effect（特效）4 = Material（材质）5 = Texture（纹理）6 = ScriptableObject（配置文件）</t>
@@ -611,6 +616,12 @@
     <t>伤害飘字预制体</t>
   </si>
   <si>
+    <t>InteractTip</t>
+  </si>
+  <si>
+    <t>交互提示预制体</t>
+  </si>
+  <si>
     <t>Combat/BattleArena</t>
   </si>
   <si>
@@ -650,7 +661,13 @@
     <t>SummonChessEffect/Change_Skill2</t>
   </si>
   <si>
-    <t>嫦娥大招特效</t>
+    <t>嫦娥大招法阵预制体</t>
+  </si>
+  <si>
+    <t>SummonChessEffect/Change_Skill2_Projectile</t>
+  </si>
+  <si>
+    <t>嫦娥大招法阵生成的投射物</t>
   </si>
   <si>
     <t>Skills/SkillParamRegistry</t>
@@ -1783,8 +1800,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F132"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <dimension ref="A1:F134"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="21" customWidth="1"/>
@@ -1841,7 +1858,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" ht="86.4" spans="1:6">
+    <row r="4" ht="81" spans="1:6">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -3352,11 +3369,11 @@
     <row r="98" ht="15" customHeight="1" spans="1:6">
       <c r="A98" s="1"/>
       <c r="B98" s="1">
-        <v>2901</v>
+        <v>2402</v>
       </c>
       <c r="C98" s="1"/>
       <c r="D98" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E98" s="1" t="s">
         <v>194</v>
@@ -3368,11 +3385,11 @@
     <row r="99" ht="15" customHeight="1" spans="1:6">
       <c r="A99" s="1"/>
       <c r="B99" s="1">
-        <v>3001</v>
+        <v>2901</v>
       </c>
       <c r="C99" s="1"/>
       <c r="D99" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E99" s="1" t="s">
         <v>196</v>
@@ -3384,7 +3401,7 @@
     <row r="100" ht="15" customHeight="1" spans="1:6">
       <c r="A100" s="1"/>
       <c r="B100" s="1">
-        <v>3002</v>
+        <v>3001</v>
       </c>
       <c r="C100" s="1"/>
       <c r="D100" s="1">
@@ -3400,7 +3417,7 @@
     <row r="101" ht="15" customHeight="1" spans="1:6">
       <c r="A101" s="1"/>
       <c r="B101" s="1">
-        <v>3003</v>
+        <v>3002</v>
       </c>
       <c r="C101" s="1"/>
       <c r="D101" s="1">
@@ -3416,7 +3433,7 @@
     <row r="102" ht="15" customHeight="1" spans="1:6">
       <c r="A102" s="1"/>
       <c r="B102" s="1">
-        <v>3004</v>
+        <v>3003</v>
       </c>
       <c r="C102" s="1"/>
       <c r="D102" s="1">
@@ -3432,7 +3449,7 @@
     <row r="103" ht="15" customHeight="1" spans="1:6">
       <c r="A103" s="1"/>
       <c r="B103" s="1">
-        <v>3005</v>
+        <v>3004</v>
       </c>
       <c r="C103" s="1"/>
       <c r="D103" s="1">
@@ -3448,7 +3465,7 @@
     <row r="104" ht="15" customHeight="1" spans="1:6">
       <c r="A104" s="1"/>
       <c r="B104" s="1">
-        <v>3006</v>
+        <v>3005</v>
       </c>
       <c r="C104" s="1"/>
       <c r="D104" s="1">
@@ -3464,11 +3481,11 @@
     <row r="105" ht="15" customHeight="1" spans="1:6">
       <c r="A105" s="1"/>
       <c r="B105" s="1">
-        <v>6001</v>
+        <v>3006</v>
       </c>
       <c r="C105" s="1"/>
       <c r="D105" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E105" s="1" t="s">
         <v>208</v>
@@ -3480,11 +3497,11 @@
     <row r="106" ht="15" customHeight="1" spans="1:6">
       <c r="A106" s="1"/>
       <c r="B106" s="1">
-        <v>10001</v>
+        <v>3007</v>
       </c>
       <c r="C106" s="1"/>
       <c r="D106" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E106" s="1" t="s">
         <v>210</v>
@@ -3496,11 +3513,11 @@
     <row r="107" ht="15" customHeight="1" spans="1:6">
       <c r="A107" s="1"/>
       <c r="B107" s="1">
-        <v>10002</v>
+        <v>6001</v>
       </c>
       <c r="C107" s="1"/>
       <c r="D107" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E107" s="1" t="s">
         <v>212</v>
@@ -3512,7 +3529,7 @@
     <row r="108" ht="15" customHeight="1" spans="1:6">
       <c r="A108" s="1"/>
       <c r="B108" s="1">
-        <v>10003</v>
+        <v>10001</v>
       </c>
       <c r="C108" s="1"/>
       <c r="D108" s="1">
@@ -3528,7 +3545,7 @@
     <row r="109" ht="15" customHeight="1" spans="1:6">
       <c r="A109" s="1"/>
       <c r="B109" s="1">
-        <v>10004</v>
+        <v>10002</v>
       </c>
       <c r="C109" s="1"/>
       <c r="D109" s="1">
@@ -3544,7 +3561,7 @@
     <row r="110" ht="15" customHeight="1" spans="1:6">
       <c r="A110" s="1"/>
       <c r="B110" s="1">
-        <v>10101</v>
+        <v>10003</v>
       </c>
       <c r="C110" s="1"/>
       <c r="D110" s="1">
@@ -3560,7 +3577,7 @@
     <row r="111" ht="15" customHeight="1" spans="1:6">
       <c r="A111" s="1"/>
       <c r="B111" s="1">
-        <v>10102</v>
+        <v>10004</v>
       </c>
       <c r="C111" s="1"/>
       <c r="D111" s="1">
@@ -3576,7 +3593,7 @@
     <row r="112" ht="15" customHeight="1" spans="1:6">
       <c r="A112" s="1"/>
       <c r="B112" s="1">
-        <v>10103</v>
+        <v>10101</v>
       </c>
       <c r="C112" s="1"/>
       <c r="D112" s="1">
@@ -3592,7 +3609,7 @@
     <row r="113" ht="15" customHeight="1" spans="1:6">
       <c r="A113" s="1"/>
       <c r="B113" s="1">
-        <v>10201</v>
+        <v>10102</v>
       </c>
       <c r="C113" s="1"/>
       <c r="D113" s="1">
@@ -3608,7 +3625,7 @@
     <row r="114" ht="15" customHeight="1" spans="1:6">
       <c r="A114" s="1"/>
       <c r="B114" s="1">
-        <v>10202</v>
+        <v>10103</v>
       </c>
       <c r="C114" s="1"/>
       <c r="D114" s="1">
@@ -3624,7 +3641,7 @@
     <row r="115" ht="15" customHeight="1" spans="1:6">
       <c r="A115" s="1"/>
       <c r="B115" s="1">
-        <v>10203</v>
+        <v>10201</v>
       </c>
       <c r="C115" s="1"/>
       <c r="D115" s="1">
@@ -3640,7 +3657,7 @@
     <row r="116" ht="15" customHeight="1" spans="1:6">
       <c r="A116" s="1"/>
       <c r="B116" s="1">
-        <v>15001</v>
+        <v>10202</v>
       </c>
       <c r="C116" s="1"/>
       <c r="D116" s="1">
@@ -3656,7 +3673,7 @@
     <row r="117" ht="15" customHeight="1" spans="1:6">
       <c r="A117" s="1"/>
       <c r="B117" s="1">
-        <v>15002</v>
+        <v>10203</v>
       </c>
       <c r="C117" s="1"/>
       <c r="D117" s="1">
@@ -3672,7 +3689,7 @@
     <row r="118" ht="15" customHeight="1" spans="1:6">
       <c r="A118" s="1"/>
       <c r="B118" s="1">
-        <v>15003</v>
+        <v>15001</v>
       </c>
       <c r="C118" s="1"/>
       <c r="D118" s="1">
@@ -3688,7 +3705,7 @@
     <row r="119" ht="15" customHeight="1" spans="1:6">
       <c r="A119" s="1"/>
       <c r="B119" s="1">
-        <v>15005</v>
+        <v>15002</v>
       </c>
       <c r="C119" s="1"/>
       <c r="D119" s="1">
@@ -3704,7 +3721,7 @@
     <row r="120" ht="15" customHeight="1" spans="1:6">
       <c r="A120" s="1"/>
       <c r="B120" s="1">
-        <v>15007</v>
+        <v>15003</v>
       </c>
       <c r="C120" s="1"/>
       <c r="D120" s="1">
@@ -3720,7 +3737,7 @@
     <row r="121" ht="15" customHeight="1" spans="1:6">
       <c r="A121" s="1"/>
       <c r="B121" s="1">
-        <v>15008</v>
+        <v>15005</v>
       </c>
       <c r="C121" s="1"/>
       <c r="D121" s="1">
@@ -3736,7 +3753,7 @@
     <row r="122" ht="15" customHeight="1" spans="1:6">
       <c r="A122" s="1"/>
       <c r="B122" s="1">
-        <v>15009</v>
+        <v>15007</v>
       </c>
       <c r="C122" s="1"/>
       <c r="D122" s="1">
@@ -3752,7 +3769,7 @@
     <row r="123" ht="15" customHeight="1" spans="1:6">
       <c r="A123" s="1"/>
       <c r="B123" s="1">
-        <v>19002</v>
+        <v>15008</v>
       </c>
       <c r="C123" s="1"/>
       <c r="D123" s="1">
@@ -3768,7 +3785,7 @@
     <row r="124" ht="15" customHeight="1" spans="1:6">
       <c r="A124" s="1"/>
       <c r="B124" s="1">
-        <v>19003</v>
+        <v>15009</v>
       </c>
       <c r="C124" s="1"/>
       <c r="D124" s="1">
@@ -3784,7 +3801,7 @@
     <row r="125" ht="15" customHeight="1" spans="1:6">
       <c r="A125" s="1"/>
       <c r="B125" s="1">
-        <v>19004</v>
+        <v>19002</v>
       </c>
       <c r="C125" s="1"/>
       <c r="D125" s="1">
@@ -3800,7 +3817,7 @@
     <row r="126" ht="15" customHeight="1" spans="1:6">
       <c r="A126" s="1"/>
       <c r="B126" s="1">
-        <v>19012</v>
+        <v>19003</v>
       </c>
       <c r="C126" s="1"/>
       <c r="D126" s="1">
@@ -3816,7 +3833,7 @@
     <row r="127" ht="15" customHeight="1" spans="1:6">
       <c r="A127" s="1"/>
       <c r="B127" s="1">
-        <v>19013</v>
+        <v>19004</v>
       </c>
       <c r="C127" s="1"/>
       <c r="D127" s="1">
@@ -3832,7 +3849,7 @@
     <row r="128" ht="15" customHeight="1" spans="1:6">
       <c r="A128" s="1"/>
       <c r="B128" s="1">
-        <v>19014</v>
+        <v>19012</v>
       </c>
       <c r="C128" s="1"/>
       <c r="D128" s="1">
@@ -3848,7 +3865,7 @@
     <row r="129" ht="15" customHeight="1" spans="1:6">
       <c r="A129" s="1"/>
       <c r="B129" s="1">
-        <v>19022</v>
+        <v>19013</v>
       </c>
       <c r="C129" s="1"/>
       <c r="D129" s="1">
@@ -3864,7 +3881,7 @@
     <row r="130" ht="15" customHeight="1" spans="1:6">
       <c r="A130" s="1"/>
       <c r="B130" s="1">
-        <v>19023</v>
+        <v>19014</v>
       </c>
       <c r="C130" s="1"/>
       <c r="D130" s="1">
@@ -3880,7 +3897,7 @@
     <row r="131" ht="15" customHeight="1" spans="1:6">
       <c r="A131" s="1"/>
       <c r="B131" s="1">
-        <v>19024</v>
+        <v>19022</v>
       </c>
       <c r="C131" s="1"/>
       <c r="D131" s="1">
@@ -3893,18 +3910,50 @@
         <v>261</v>
       </c>
     </row>
-    <row r="132" spans="1:6">
-      <c r="B132">
+    <row r="132" ht="15" customHeight="1" spans="1:6">
+      <c r="A132" s="1"/>
+      <c r="B132" s="1">
+        <v>19023</v>
+      </c>
+      <c r="C132" s="1"/>
+      <c r="D132" s="1">
+        <v>1</v>
+      </c>
+      <c r="E132" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="F132" s="1" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="133" ht="15" customHeight="1" spans="1:6">
+      <c r="A133" s="1"/>
+      <c r="B133" s="1">
+        <v>19024</v>
+      </c>
+      <c r="C133" s="1"/>
+      <c r="D133" s="1">
+        <v>1</v>
+      </c>
+      <c r="E133" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="F133" s="1" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6">
+      <c r="B134">
         <v>11001</v>
       </c>
-      <c r="D132">
-        <v>1</v>
-      </c>
-      <c r="E132" t="s">
-        <v>262</v>
-      </c>
-      <c r="F132" t="s">
-        <v>263</v>
+      <c r="D134">
+        <v>1</v>
+      </c>
+      <c r="E134" t="s">
+        <v>266</v>
+      </c>
+      <c r="F134" t="s">
+        <v>267</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/DataTables/ResourceConfigTable.xlsx
+++ b/AAAGameData/DataTables/ResourceConfigTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11925"/>
+    <workbookView windowWidth="29868" windowHeight="14855"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="320">
   <si>
     <t>#</t>
   </si>
@@ -56,12 +56,7 @@
     <t>资源ID</t>
   </si>
   <si>
-    <t>1：Assets/AAAGame/Sprites/
-2：Assets/AAAGame/Prefabs/
-3：Assets/AAAGame/Prefabs/Entity/
-4：Assets/AAAGame/Materials/
-5：Assets/AAAGame/Textures/
-6：Assets/AAAGame/Config/</t>
+    <t>1：Assets/AAAGame/Sprites/2：Assets/AAAGame/Prefabs/3：Assets/AAAGame/Prefabs/Entity/4：Assets/AAAGame/Materials/5：Assets/AAAGame/Textures/6：Assets/AAAGame/Config/</t>
   </si>
   <si>
     <t>资源类型：1 = Sprite（图片）2 = Prefab（预制体）3 = Effect（特效）4 = Material（材质）5 = Texture（纹理）6 = ScriptableObject（配置文件）</t>
@@ -103,18 +98,18 @@
     <t>金币图标</t>
   </si>
   <si>
+    <t>UI/Items/OriginStone.png</t>
+  </si>
+  <si>
+    <t>起源石图标</t>
+  </si>
+  <si>
     <t>UI/Items/MagicalStone.png</t>
   </si>
   <si>
     <t>灵石图标</t>
   </si>
   <si>
-    <t>UI/Items/HolyWater.png</t>
-  </si>
-  <si>
-    <t>圣水图标</t>
-  </si>
-  <si>
     <t>UI/Items/Circle.png</t>
   </si>
   <si>
@@ -208,6 +203,90 @@
     <t>不屈意志-策略卡图标</t>
   </si>
   <si>
+    <t>Card/策略卡/反伤之盾.png</t>
+  </si>
+  <si>
+    <t>反伤之盾-策略卡图标</t>
+  </si>
+  <si>
+    <t>Card/策略卡/圣域防线.png</t>
+  </si>
+  <si>
+    <t>圣域防线-策略卡图标</t>
+  </si>
+  <si>
+    <t>Card/策略卡/护盾再生.png</t>
+  </si>
+  <si>
+    <t>护盾再生-策略卡图标</t>
+  </si>
+  <si>
+    <t>Card/策略卡/救赎之光.png</t>
+  </si>
+  <si>
+    <t>救赎之光-策略卡图标</t>
+  </si>
+  <si>
+    <t>Card/策略卡/血源强化.png</t>
+  </si>
+  <si>
+    <t>血源强化-策略卡图标</t>
+  </si>
+  <si>
+    <t>Card/策略卡/吸血之刃.png</t>
+  </si>
+  <si>
+    <t>吸血之刃-策略卡图标</t>
+  </si>
+  <si>
+    <t>Card/策略卡/灾厄之雷.png</t>
+  </si>
+  <si>
+    <t>灾厄之雷-策略卡图标</t>
+  </si>
+  <si>
+    <t>Card/策略卡/护甲破碎.png</t>
+  </si>
+  <si>
+    <t>护甲破碎-策略卡图标</t>
+  </si>
+  <si>
+    <t>Card/策略卡/虚弱诅咒.png</t>
+  </si>
+  <si>
+    <t>虚弱诅咒-策略卡图标</t>
+  </si>
+  <si>
+    <t>Card/策略卡/沉默之符.png</t>
+  </si>
+  <si>
+    <t>沉默之符-策略卡图标</t>
+  </si>
+  <si>
+    <t>Card/策略卡/嘲讽之声.png</t>
+  </si>
+  <si>
+    <t>嘲讽之声-策略卡图标</t>
+  </si>
+  <si>
+    <t>Card/策略卡/剧毒之雾.png</t>
+  </si>
+  <si>
+    <t>剧毒之雾-策略卡图标</t>
+  </si>
+  <si>
+    <t>Card/策略卡/伤害转移.png</t>
+  </si>
+  <si>
+    <t>伤害转移-策略卡图标</t>
+  </si>
+  <si>
+    <t>Card/策略卡/绝对零度.png</t>
+  </si>
+  <si>
+    <t>绝对零度-策略卡图标</t>
+  </si>
+  <si>
     <t>Chess/后羿/后羿立绘.png</t>
   </si>
   <si>
@@ -776,6 +855,78 @@
   </si>
   <si>
     <t>混乱诅咒Buff图标</t>
+  </si>
+  <si>
+    <t>Buff/5011.png</t>
+  </si>
+  <si>
+    <t>反伤之盾Buff图标</t>
+  </si>
+  <si>
+    <t>Buff/5012.png</t>
+  </si>
+  <si>
+    <t>圣域防线Buff图标</t>
+  </si>
+  <si>
+    <t>Buff/5013.png</t>
+  </si>
+  <si>
+    <t>护盾再生Buff图标</t>
+  </si>
+  <si>
+    <t>Buff/5014.png</t>
+  </si>
+  <si>
+    <t>血源强化Buff图标</t>
+  </si>
+  <si>
+    <t>Buff/5015.png</t>
+  </si>
+  <si>
+    <t>吸血之刃Buff图标</t>
+  </si>
+  <si>
+    <t>Buff/5017.png</t>
+  </si>
+  <si>
+    <t>护甲破碎Buff图标</t>
+  </si>
+  <si>
+    <t>Buff/5018.png</t>
+  </si>
+  <si>
+    <t>虚弱诅咒Buff图标</t>
+  </si>
+  <si>
+    <t>Buff/5019.png</t>
+  </si>
+  <si>
+    <t>沉默之符Buff图标</t>
+  </si>
+  <si>
+    <t>Buff/5020.png</t>
+  </si>
+  <si>
+    <t>嘲讽之声Buff图标</t>
+  </si>
+  <si>
+    <t>Buff/5021.png</t>
+  </si>
+  <si>
+    <t>剧毒之雾Buff图标</t>
+  </si>
+  <si>
+    <t>Buff/5022.png</t>
+  </si>
+  <si>
+    <t>伤害转移Buff图标</t>
+  </si>
+  <si>
+    <t>Buff/5023.png</t>
+  </si>
+  <si>
+    <t>绝对零度Buff图标</t>
   </si>
   <si>
     <t>Card/Component/2.png</t>
@@ -848,7 +999,14 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1304,148 +1462,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1800,14 +1958,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F134"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <dimension ref="A1:F160"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="21" customWidth="1"/>
     <col min="3" max="4" width="50" customWidth="1"/>
     <col min="5" max="5" width="44" customWidth="1"/>
-    <col min="6" max="6" width="25" customWidth="1"/>
+    <col min="6" max="6" width="26" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1858,7 +2016,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" ht="81" spans="1:6">
+    <row r="4" ht="72" spans="1:6">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -2265,7 +2423,7 @@
     <row r="29" ht="15" customHeight="1" spans="1:6">
       <c r="A29" s="1"/>
       <c r="B29" s="1">
-        <v>1301</v>
+        <v>1213</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="1">
@@ -2281,7 +2439,7 @@
     <row r="30" ht="15" customHeight="1" spans="1:6">
       <c r="A30" s="1"/>
       <c r="B30" s="1">
-        <v>1304</v>
+        <v>1214</v>
       </c>
       <c r="C30" s="1"/>
       <c r="D30" s="1">
@@ -2297,7 +2455,7 @@
     <row r="31" ht="15" customHeight="1" spans="1:6">
       <c r="A31" s="1"/>
       <c r="B31" s="1">
-        <v>1399</v>
+        <v>1215</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="1">
@@ -2313,7 +2471,7 @@
     <row r="32" ht="15" customHeight="1" spans="1:6">
       <c r="A32" s="1"/>
       <c r="B32" s="1">
-        <v>1401</v>
+        <v>1216</v>
       </c>
       <c r="C32" s="1"/>
       <c r="D32" s="1">
@@ -2329,7 +2487,7 @@
     <row r="33" ht="15" customHeight="1" spans="1:6">
       <c r="A33" s="1"/>
       <c r="B33" s="1">
-        <v>1402</v>
+        <v>1217</v>
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="1">
@@ -2345,7 +2503,7 @@
     <row r="34" ht="15" customHeight="1" spans="1:6">
       <c r="A34" s="1"/>
       <c r="B34" s="1">
-        <v>1403</v>
+        <v>1218</v>
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="1">
@@ -2361,7 +2519,7 @@
     <row r="35" ht="15" customHeight="1" spans="1:6">
       <c r="A35" s="1"/>
       <c r="B35" s="1">
-        <v>1404</v>
+        <v>1219</v>
       </c>
       <c r="C35" s="1"/>
       <c r="D35" s="1">
@@ -2377,7 +2535,7 @@
     <row r="36" ht="15" customHeight="1" spans="1:6">
       <c r="A36" s="1"/>
       <c r="B36" s="1">
-        <v>1405</v>
+        <v>1220</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1">
@@ -2393,7 +2551,7 @@
     <row r="37" ht="15" customHeight="1" spans="1:6">
       <c r="A37" s="1"/>
       <c r="B37" s="1">
-        <v>1406</v>
+        <v>1221</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1">
@@ -2409,7 +2567,7 @@
     <row r="38" ht="15" customHeight="1" spans="1:6">
       <c r="A38" s="1"/>
       <c r="B38" s="1">
-        <v>1501</v>
+        <v>1222</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1">
@@ -2425,7 +2583,7 @@
     <row r="39" ht="15" customHeight="1" spans="1:6">
       <c r="A39" s="1"/>
       <c r="B39" s="1">
-        <v>1502</v>
+        <v>1223</v>
       </c>
       <c r="C39" s="1"/>
       <c r="D39" s="1">
@@ -2441,7 +2599,7 @@
     <row r="40" ht="15" customHeight="1" spans="1:6">
       <c r="A40" s="1"/>
       <c r="B40" s="1">
-        <v>1503</v>
+        <v>1224</v>
       </c>
       <c r="C40" s="1"/>
       <c r="D40" s="1">
@@ -2457,7 +2615,7 @@
     <row r="41" ht="15" customHeight="1" spans="1:6">
       <c r="A41" s="1"/>
       <c r="B41" s="1">
-        <v>1601</v>
+        <v>1225</v>
       </c>
       <c r="C41" s="1"/>
       <c r="D41" s="1">
@@ -2473,7 +2631,7 @@
     <row r="42" ht="15" customHeight="1" spans="1:6">
       <c r="A42" s="1"/>
       <c r="B42" s="1">
-        <v>1701</v>
+        <v>1226</v>
       </c>
       <c r="C42" s="1"/>
       <c r="D42" s="1">
@@ -2489,7 +2647,7 @@
     <row r="43" ht="15" customHeight="1" spans="1:6">
       <c r="A43" s="1"/>
       <c r="B43" s="1">
-        <v>1702</v>
+        <v>1301</v>
       </c>
       <c r="C43" s="1"/>
       <c r="D43" s="1">
@@ -2505,7 +2663,7 @@
     <row r="44" ht="15" customHeight="1" spans="1:6">
       <c r="A44" s="1"/>
       <c r="B44" s="1">
-        <v>1703</v>
+        <v>1304</v>
       </c>
       <c r="C44" s="1"/>
       <c r="D44" s="1">
@@ -2521,7 +2679,7 @@
     <row r="45" ht="15" customHeight="1" spans="1:6">
       <c r="A45" s="1"/>
       <c r="B45" s="1">
-        <v>1704</v>
+        <v>1399</v>
       </c>
       <c r="C45" s="1"/>
       <c r="D45" s="1">
@@ -2537,7 +2695,7 @@
     <row r="46" ht="15" customHeight="1" spans="1:6">
       <c r="A46" s="1"/>
       <c r="B46" s="1">
-        <v>1705</v>
+        <v>1401</v>
       </c>
       <c r="C46" s="1"/>
       <c r="D46" s="1">
@@ -2553,7 +2711,7 @@
     <row r="47" ht="15" customHeight="1" spans="1:6">
       <c r="A47" s="1"/>
       <c r="B47" s="1">
-        <v>1706</v>
+        <v>1402</v>
       </c>
       <c r="C47" s="1"/>
       <c r="D47" s="1">
@@ -2569,7 +2727,7 @@
     <row r="48" ht="15" customHeight="1" spans="1:6">
       <c r="A48" s="1"/>
       <c r="B48" s="1">
-        <v>1707</v>
+        <v>1403</v>
       </c>
       <c r="C48" s="1"/>
       <c r="D48" s="1">
@@ -2585,7 +2743,7 @@
     <row r="49" ht="15" customHeight="1" spans="1:6">
       <c r="A49" s="1"/>
       <c r="B49" s="1">
-        <v>1708</v>
+        <v>1404</v>
       </c>
       <c r="C49" s="1"/>
       <c r="D49" s="1">
@@ -2601,7 +2759,7 @@
     <row r="50" ht="15" customHeight="1" spans="1:6">
       <c r="A50" s="1"/>
       <c r="B50" s="1">
-        <v>1711</v>
+        <v>1405</v>
       </c>
       <c r="C50" s="1"/>
       <c r="D50" s="1">
@@ -2617,7 +2775,7 @@
     <row r="51" ht="15" customHeight="1" spans="1:6">
       <c r="A51" s="1"/>
       <c r="B51" s="1">
-        <v>1712</v>
+        <v>1406</v>
       </c>
       <c r="C51" s="1"/>
       <c r="D51" s="1">
@@ -2633,7 +2791,7 @@
     <row r="52" ht="15" customHeight="1" spans="1:6">
       <c r="A52" s="1"/>
       <c r="B52" s="1">
-        <v>1801</v>
+        <v>1501</v>
       </c>
       <c r="C52" s="1"/>
       <c r="D52" s="1">
@@ -2649,7 +2807,7 @@
     <row r="53" ht="15" customHeight="1" spans="1:6">
       <c r="A53" s="1"/>
       <c r="B53" s="1">
-        <v>1802</v>
+        <v>1502</v>
       </c>
       <c r="C53" s="1"/>
       <c r="D53" s="1">
@@ -2665,7 +2823,7 @@
     <row r="54" ht="15" customHeight="1" spans="1:6">
       <c r="A54" s="1"/>
       <c r="B54" s="1">
-        <v>1803</v>
+        <v>1503</v>
       </c>
       <c r="C54" s="1"/>
       <c r="D54" s="1">
@@ -2681,7 +2839,7 @@
     <row r="55" ht="15" customHeight="1" spans="1:6">
       <c r="A55" s="1"/>
       <c r="B55" s="1">
-        <v>1804</v>
+        <v>1601</v>
       </c>
       <c r="C55" s="1"/>
       <c r="D55" s="1">
@@ -2697,7 +2855,7 @@
     <row r="56" ht="15" customHeight="1" spans="1:6">
       <c r="A56" s="1"/>
       <c r="B56" s="1">
-        <v>1805</v>
+        <v>1701</v>
       </c>
       <c r="C56" s="1"/>
       <c r="D56" s="1">
@@ -2713,7 +2871,7 @@
     <row r="57" ht="15" customHeight="1" spans="1:6">
       <c r="A57" s="1"/>
       <c r="B57" s="1">
-        <v>1806</v>
+        <v>1702</v>
       </c>
       <c r="C57" s="1"/>
       <c r="D57" s="1">
@@ -2729,7 +2887,7 @@
     <row r="58" ht="15" customHeight="1" spans="1:6">
       <c r="A58" s="1"/>
       <c r="B58" s="1">
-        <v>1807</v>
+        <v>1703</v>
       </c>
       <c r="C58" s="1"/>
       <c r="D58" s="1">
@@ -2745,7 +2903,7 @@
     <row r="59" ht="15" customHeight="1" spans="1:6">
       <c r="A59" s="1"/>
       <c r="B59" s="1">
-        <v>1808</v>
+        <v>1704</v>
       </c>
       <c r="C59" s="1"/>
       <c r="D59" s="1">
@@ -2761,7 +2919,7 @@
     <row r="60" ht="15" customHeight="1" spans="1:6">
       <c r="A60" s="1"/>
       <c r="B60" s="1">
-        <v>1901</v>
+        <v>1705</v>
       </c>
       <c r="C60" s="1"/>
       <c r="D60" s="1">
@@ -2777,7 +2935,7 @@
     <row r="61" ht="15" customHeight="1" spans="1:6">
       <c r="A61" s="1"/>
       <c r="B61" s="1">
-        <v>1902</v>
+        <v>1706</v>
       </c>
       <c r="C61" s="1"/>
       <c r="D61" s="1">
@@ -2793,7 +2951,7 @@
     <row r="62" ht="15" customHeight="1" spans="1:6">
       <c r="A62" s="1"/>
       <c r="B62" s="1">
-        <v>1903</v>
+        <v>1707</v>
       </c>
       <c r="C62" s="1"/>
       <c r="D62" s="1">
@@ -2809,7 +2967,7 @@
     <row r="63" ht="15" customHeight="1" spans="1:6">
       <c r="A63" s="1"/>
       <c r="B63" s="1">
-        <v>1904</v>
+        <v>1708</v>
       </c>
       <c r="C63" s="1"/>
       <c r="D63" s="1">
@@ -2825,7 +2983,7 @@
     <row r="64" ht="15" customHeight="1" spans="1:6">
       <c r="A64" s="1"/>
       <c r="B64" s="1">
-        <v>1905</v>
+        <v>1711</v>
       </c>
       <c r="C64" s="1"/>
       <c r="D64" s="1">
@@ -2841,7 +2999,7 @@
     <row r="65" ht="15" customHeight="1" spans="1:6">
       <c r="A65" s="1"/>
       <c r="B65" s="1">
-        <v>1906</v>
+        <v>1712</v>
       </c>
       <c r="C65" s="1"/>
       <c r="D65" s="1">
@@ -2857,7 +3015,7 @@
     <row r="66" ht="15" customHeight="1" spans="1:6">
       <c r="A66" s="1"/>
       <c r="B66" s="1">
-        <v>1907</v>
+        <v>1801</v>
       </c>
       <c r="C66" s="1"/>
       <c r="D66" s="1">
@@ -2873,7 +3031,7 @@
     <row r="67" ht="15" customHeight="1" spans="1:6">
       <c r="A67" s="1"/>
       <c r="B67" s="1">
-        <v>1908</v>
+        <v>1802</v>
       </c>
       <c r="C67" s="1"/>
       <c r="D67" s="1">
@@ -2889,7 +3047,7 @@
     <row r="68" ht="15" customHeight="1" spans="1:6">
       <c r="A68" s="1"/>
       <c r="B68" s="1">
-        <v>1909</v>
+        <v>1803</v>
       </c>
       <c r="C68" s="1"/>
       <c r="D68" s="1">
@@ -2905,7 +3063,7 @@
     <row r="69" ht="15" customHeight="1" spans="1:6">
       <c r="A69" s="1"/>
       <c r="B69" s="1">
-        <v>1910</v>
+        <v>1804</v>
       </c>
       <c r="C69" s="1"/>
       <c r="D69" s="1">
@@ -2921,7 +3079,7 @@
     <row r="70" ht="15" customHeight="1" spans="1:6">
       <c r="A70" s="1"/>
       <c r="B70" s="1">
-        <v>1911</v>
+        <v>1805</v>
       </c>
       <c r="C70" s="1"/>
       <c r="D70" s="1">
@@ -2937,7 +3095,7 @@
     <row r="71" ht="15" customHeight="1" spans="1:6">
       <c r="A71" s="1"/>
       <c r="B71" s="1">
-        <v>1912</v>
+        <v>1806</v>
       </c>
       <c r="C71" s="1"/>
       <c r="D71" s="1">
@@ -2953,7 +3111,7 @@
     <row r="72" ht="15" customHeight="1" spans="1:6">
       <c r="A72" s="1"/>
       <c r="B72" s="1">
-        <v>1913</v>
+        <v>1807</v>
       </c>
       <c r="C72" s="1"/>
       <c r="D72" s="1">
@@ -2969,7 +3127,7 @@
     <row r="73" ht="15" customHeight="1" spans="1:6">
       <c r="A73" s="1"/>
       <c r="B73" s="1">
-        <v>1914</v>
+        <v>1808</v>
       </c>
       <c r="C73" s="1"/>
       <c r="D73" s="1">
@@ -2982,10 +3140,10 @@
         <v>147</v>
       </c>
     </row>
-    <row r="74" customFormat="1" ht="15" customHeight="1" spans="1:6">
+    <row r="74" ht="15" customHeight="1" spans="1:6">
       <c r="A74" s="1"/>
       <c r="B74" s="1">
-        <v>1915</v>
+        <v>1901</v>
       </c>
       <c r="C74" s="1"/>
       <c r="D74" s="1">
@@ -3001,7 +3159,7 @@
     <row r="75" ht="15" customHeight="1" spans="1:6">
       <c r="A75" s="1"/>
       <c r="B75" s="1">
-        <v>1916</v>
+        <v>1902</v>
       </c>
       <c r="C75" s="1"/>
       <c r="D75" s="1">
@@ -3017,7 +3175,7 @@
     <row r="76" ht="15" customHeight="1" spans="1:6">
       <c r="A76" s="1"/>
       <c r="B76" s="1">
-        <v>1917</v>
+        <v>1903</v>
       </c>
       <c r="C76" s="1"/>
       <c r="D76" s="1">
@@ -3033,7 +3191,7 @@
     <row r="77" ht="15" customHeight="1" spans="1:6">
       <c r="A77" s="1"/>
       <c r="B77" s="1">
-        <v>1918</v>
+        <v>1904</v>
       </c>
       <c r="C77" s="1"/>
       <c r="D77" s="1">
@@ -3049,7 +3207,7 @@
     <row r="78" ht="15" customHeight="1" spans="1:6">
       <c r="A78" s="1"/>
       <c r="B78" s="1">
-        <v>1919</v>
+        <v>1905</v>
       </c>
       <c r="C78" s="1"/>
       <c r="D78" s="1">
@@ -3065,7 +3223,7 @@
     <row r="79" ht="15" customHeight="1" spans="1:6">
       <c r="A79" s="1"/>
       <c r="B79" s="1">
-        <v>1920</v>
+        <v>1906</v>
       </c>
       <c r="C79" s="1"/>
       <c r="D79" s="1">
@@ -3081,7 +3239,7 @@
     <row r="80" ht="15" customHeight="1" spans="1:6">
       <c r="A80" s="1"/>
       <c r="B80" s="1">
-        <v>1921</v>
+        <v>1907</v>
       </c>
       <c r="C80" s="1"/>
       <c r="D80" s="1">
@@ -3097,7 +3255,7 @@
     <row r="81" ht="15" customHeight="1" spans="1:6">
       <c r="A81" s="1"/>
       <c r="B81" s="1">
-        <v>1922</v>
+        <v>1908</v>
       </c>
       <c r="C81" s="1"/>
       <c r="D81" s="1">
@@ -3113,7 +3271,7 @@
     <row r="82" ht="15" customHeight="1" spans="1:6">
       <c r="A82" s="1"/>
       <c r="B82" s="1">
-        <v>1923</v>
+        <v>1909</v>
       </c>
       <c r="C82" s="1"/>
       <c r="D82" s="1">
@@ -3129,7 +3287,7 @@
     <row r="83" ht="15" customHeight="1" spans="1:6">
       <c r="A83" s="1"/>
       <c r="B83" s="1">
-        <v>1924</v>
+        <v>1910</v>
       </c>
       <c r="C83" s="1"/>
       <c r="D83" s="1">
@@ -3145,11 +3303,11 @@
     <row r="84" ht="15" customHeight="1" spans="1:6">
       <c r="A84" s="1"/>
       <c r="B84" s="1">
-        <v>2001</v>
+        <v>1911</v>
       </c>
       <c r="C84" s="1"/>
       <c r="D84" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E84" s="1" t="s">
         <v>168</v>
@@ -3161,11 +3319,11 @@
     <row r="85" ht="15" customHeight="1" spans="1:6">
       <c r="A85" s="1"/>
       <c r="B85" s="1">
-        <v>2002</v>
+        <v>1912</v>
       </c>
       <c r="C85" s="1"/>
       <c r="D85" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E85" s="1" t="s">
         <v>170</v>
@@ -3177,11 +3335,11 @@
     <row r="86" ht="15" customHeight="1" spans="1:6">
       <c r="A86" s="1"/>
       <c r="B86" s="1">
-        <v>2003</v>
+        <v>1913</v>
       </c>
       <c r="C86" s="1"/>
       <c r="D86" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E86" s="1" t="s">
         <v>172</v>
@@ -3193,11 +3351,11 @@
     <row r="87" ht="15" customHeight="1" spans="1:6">
       <c r="A87" s="1"/>
       <c r="B87" s="1">
-        <v>2004</v>
+        <v>1914</v>
       </c>
       <c r="C87" s="1"/>
       <c r="D87" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E87" s="1" t="s">
         <v>174</v>
@@ -3209,11 +3367,11 @@
     <row r="88" ht="15" customHeight="1" spans="1:6">
       <c r="A88" s="1"/>
       <c r="B88" s="1">
-        <v>2101</v>
+        <v>1915</v>
       </c>
       <c r="C88" s="1"/>
       <c r="D88" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E88" s="1" t="s">
         <v>176</v>
@@ -3225,11 +3383,11 @@
     <row r="89" ht="15" customHeight="1" spans="1:6">
       <c r="A89" s="1"/>
       <c r="B89" s="1">
-        <v>2102</v>
+        <v>1916</v>
       </c>
       <c r="C89" s="1"/>
       <c r="D89" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E89" s="1" t="s">
         <v>178</v>
@@ -3241,254 +3399,254 @@
     <row r="90" ht="15" customHeight="1" spans="1:6">
       <c r="A90" s="1"/>
       <c r="B90" s="1">
-        <v>2103</v>
+        <v>1917</v>
       </c>
       <c r="C90" s="1"/>
       <c r="D90" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="91" ht="15" customHeight="1" spans="1:6">
       <c r="A91" s="1"/>
       <c r="B91" s="1">
-        <v>2104</v>
+        <v>1918</v>
       </c>
       <c r="C91" s="1"/>
       <c r="D91" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="92" ht="15" customHeight="1" spans="1:6">
       <c r="A92" s="1"/>
       <c r="B92" s="1">
-        <v>2201</v>
+        <v>1919</v>
       </c>
       <c r="C92" s="1"/>
       <c r="D92" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="93" ht="15" customHeight="1" spans="1:6">
       <c r="A93" s="1"/>
       <c r="B93" s="1">
-        <v>2301</v>
+        <v>1920</v>
       </c>
       <c r="C93" s="1"/>
       <c r="D93" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="94" ht="15" customHeight="1" spans="1:6">
       <c r="A94" s="1"/>
       <c r="B94" s="1">
-        <v>2304</v>
+        <v>1921</v>
       </c>
       <c r="C94" s="1"/>
       <c r="D94" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="95" ht="15" customHeight="1" spans="1:6">
       <c r="A95" s="1"/>
       <c r="B95" s="1">
-        <v>2309</v>
+        <v>1922</v>
       </c>
       <c r="C95" s="1"/>
       <c r="D95" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="96" ht="15" customHeight="1" spans="1:6">
       <c r="A96" s="1"/>
       <c r="B96" s="1">
-        <v>2399</v>
+        <v>1923</v>
       </c>
       <c r="C96" s="1"/>
       <c r="D96" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="97" ht="15" customHeight="1" spans="1:6">
       <c r="A97" s="1"/>
       <c r="B97" s="1">
-        <v>2401</v>
+        <v>1924</v>
       </c>
       <c r="C97" s="1"/>
       <c r="D97" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="98" ht="15" customHeight="1" spans="1:6">
       <c r="A98" s="1"/>
       <c r="B98" s="1">
-        <v>2402</v>
+        <v>2001</v>
       </c>
       <c r="C98" s="1"/>
       <c r="D98" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="99" ht="15" customHeight="1" spans="1:6">
       <c r="A99" s="1"/>
       <c r="B99" s="1">
-        <v>2901</v>
+        <v>2002</v>
       </c>
       <c r="C99" s="1"/>
       <c r="D99" s="1">
         <v>2</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="100" ht="15" customHeight="1" spans="1:6">
       <c r="A100" s="1"/>
       <c r="B100" s="1">
-        <v>3001</v>
+        <v>2003</v>
       </c>
       <c r="C100" s="1"/>
       <c r="D100" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="101" ht="15" customHeight="1" spans="1:6">
       <c r="A101" s="1"/>
       <c r="B101" s="1">
-        <v>3002</v>
+        <v>2004</v>
       </c>
       <c r="C101" s="1"/>
       <c r="D101" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="102" ht="15" customHeight="1" spans="1:6">
       <c r="A102" s="1"/>
       <c r="B102" s="1">
-        <v>3003</v>
+        <v>2101</v>
       </c>
       <c r="C102" s="1"/>
       <c r="D102" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="103" ht="15" customHeight="1" spans="1:6">
       <c r="A103" s="1"/>
       <c r="B103" s="1">
-        <v>3004</v>
+        <v>2102</v>
       </c>
       <c r="C103" s="1"/>
       <c r="D103" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="104" ht="15" customHeight="1" spans="1:6">
       <c r="A104" s="1"/>
       <c r="B104" s="1">
-        <v>3005</v>
+        <v>2103</v>
       </c>
       <c r="C104" s="1"/>
       <c r="D104" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E104" s="1" t="s">
         <v>206</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="105" ht="15" customHeight="1" spans="1:6">
       <c r="A105" s="1"/>
       <c r="B105" s="1">
-        <v>3006</v>
+        <v>2104</v>
       </c>
       <c r="C105" s="1"/>
       <c r="D105" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>209</v>
@@ -3497,11 +3655,11 @@
     <row r="106" ht="15" customHeight="1" spans="1:6">
       <c r="A106" s="1"/>
       <c r="B106" s="1">
-        <v>3007</v>
+        <v>2201</v>
       </c>
       <c r="C106" s="1"/>
       <c r="D106" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E106" s="1" t="s">
         <v>210</v>
@@ -3513,11 +3671,11 @@
     <row r="107" ht="15" customHeight="1" spans="1:6">
       <c r="A107" s="1"/>
       <c r="B107" s="1">
-        <v>6001</v>
+        <v>2301</v>
       </c>
       <c r="C107" s="1"/>
       <c r="D107" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E107" s="1" t="s">
         <v>212</v>
@@ -3529,11 +3687,11 @@
     <row r="108" ht="15" customHeight="1" spans="1:6">
       <c r="A108" s="1"/>
       <c r="B108" s="1">
-        <v>10001</v>
+        <v>2304</v>
       </c>
       <c r="C108" s="1"/>
       <c r="D108" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E108" s="1" t="s">
         <v>214</v>
@@ -3545,11 +3703,11 @@
     <row r="109" ht="15" customHeight="1" spans="1:6">
       <c r="A109" s="1"/>
       <c r="B109" s="1">
-        <v>10002</v>
+        <v>2309</v>
       </c>
       <c r="C109" s="1"/>
       <c r="D109" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E109" s="1" t="s">
         <v>216</v>
@@ -3561,11 +3719,11 @@
     <row r="110" ht="15" customHeight="1" spans="1:6">
       <c r="A110" s="1"/>
       <c r="B110" s="1">
-        <v>10003</v>
+        <v>2399</v>
       </c>
       <c r="C110" s="1"/>
       <c r="D110" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E110" s="1" t="s">
         <v>218</v>
@@ -3577,11 +3735,11 @@
     <row r="111" ht="15" customHeight="1" spans="1:6">
       <c r="A111" s="1"/>
       <c r="B111" s="1">
-        <v>10004</v>
+        <v>2401</v>
       </c>
       <c r="C111" s="1"/>
       <c r="D111" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E111" s="1" t="s">
         <v>220</v>
@@ -3593,11 +3751,11 @@
     <row r="112" ht="15" customHeight="1" spans="1:6">
       <c r="A112" s="1"/>
       <c r="B112" s="1">
-        <v>10101</v>
+        <v>2402</v>
       </c>
       <c r="C112" s="1"/>
       <c r="D112" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E112" s="1" t="s">
         <v>222</v>
@@ -3609,11 +3767,11 @@
     <row r="113" ht="15" customHeight="1" spans="1:6">
       <c r="A113" s="1"/>
       <c r="B113" s="1">
-        <v>10102</v>
+        <v>2901</v>
       </c>
       <c r="C113" s="1"/>
       <c r="D113" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E113" s="1" t="s">
         <v>224</v>
@@ -3625,11 +3783,11 @@
     <row r="114" ht="15" customHeight="1" spans="1:6">
       <c r="A114" s="1"/>
       <c r="B114" s="1">
-        <v>10103</v>
+        <v>3001</v>
       </c>
       <c r="C114" s="1"/>
       <c r="D114" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E114" s="1" t="s">
         <v>226</v>
@@ -3641,11 +3799,11 @@
     <row r="115" ht="15" customHeight="1" spans="1:6">
       <c r="A115" s="1"/>
       <c r="B115" s="1">
-        <v>10201</v>
+        <v>3002</v>
       </c>
       <c r="C115" s="1"/>
       <c r="D115" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E115" s="1" t="s">
         <v>228</v>
@@ -3657,11 +3815,11 @@
     <row r="116" ht="15" customHeight="1" spans="1:6">
       <c r="A116" s="1"/>
       <c r="B116" s="1">
-        <v>10202</v>
+        <v>3003</v>
       </c>
       <c r="C116" s="1"/>
       <c r="D116" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E116" s="1" t="s">
         <v>230</v>
@@ -3673,11 +3831,11 @@
     <row r="117" ht="15" customHeight="1" spans="1:6">
       <c r="A117" s="1"/>
       <c r="B117" s="1">
-        <v>10203</v>
+        <v>3004</v>
       </c>
       <c r="C117" s="1"/>
       <c r="D117" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E117" s="1" t="s">
         <v>232</v>
@@ -3689,11 +3847,11 @@
     <row r="118" ht="15" customHeight="1" spans="1:6">
       <c r="A118" s="1"/>
       <c r="B118" s="1">
-        <v>15001</v>
+        <v>3005</v>
       </c>
       <c r="C118" s="1"/>
       <c r="D118" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E118" s="1" t="s">
         <v>234</v>
@@ -3705,11 +3863,11 @@
     <row r="119" ht="15" customHeight="1" spans="1:6">
       <c r="A119" s="1"/>
       <c r="B119" s="1">
-        <v>15002</v>
+        <v>3006</v>
       </c>
       <c r="C119" s="1"/>
       <c r="D119" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E119" s="1" t="s">
         <v>236</v>
@@ -3721,11 +3879,11 @@
     <row r="120" ht="15" customHeight="1" spans="1:6">
       <c r="A120" s="1"/>
       <c r="B120" s="1">
-        <v>15003</v>
+        <v>3007</v>
       </c>
       <c r="C120" s="1"/>
       <c r="D120" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E120" s="1" t="s">
         <v>238</v>
@@ -3737,11 +3895,11 @@
     <row r="121" ht="15" customHeight="1" spans="1:6">
       <c r="A121" s="1"/>
       <c r="B121" s="1">
-        <v>15005</v>
+        <v>6001</v>
       </c>
       <c r="C121" s="1"/>
       <c r="D121" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E121" s="1" t="s">
         <v>240</v>
@@ -3753,7 +3911,7 @@
     <row r="122" ht="15" customHeight="1" spans="1:6">
       <c r="A122" s="1"/>
       <c r="B122" s="1">
-        <v>15007</v>
+        <v>10001</v>
       </c>
       <c r="C122" s="1"/>
       <c r="D122" s="1">
@@ -3769,7 +3927,7 @@
     <row r="123" ht="15" customHeight="1" spans="1:6">
       <c r="A123" s="1"/>
       <c r="B123" s="1">
-        <v>15008</v>
+        <v>10002</v>
       </c>
       <c r="C123" s="1"/>
       <c r="D123" s="1">
@@ -3785,7 +3943,7 @@
     <row r="124" ht="15" customHeight="1" spans="1:6">
       <c r="A124" s="1"/>
       <c r="B124" s="1">
-        <v>15009</v>
+        <v>10003</v>
       </c>
       <c r="C124" s="1"/>
       <c r="D124" s="1">
@@ -3801,7 +3959,7 @@
     <row r="125" ht="15" customHeight="1" spans="1:6">
       <c r="A125" s="1"/>
       <c r="B125" s="1">
-        <v>19002</v>
+        <v>10004</v>
       </c>
       <c r="C125" s="1"/>
       <c r="D125" s="1">
@@ -3817,7 +3975,7 @@
     <row r="126" ht="15" customHeight="1" spans="1:6">
       <c r="A126" s="1"/>
       <c r="B126" s="1">
-        <v>19003</v>
+        <v>10101</v>
       </c>
       <c r="C126" s="1"/>
       <c r="D126" s="1">
@@ -3833,7 +3991,7 @@
     <row r="127" ht="15" customHeight="1" spans="1:6">
       <c r="A127" s="1"/>
       <c r="B127" s="1">
-        <v>19004</v>
+        <v>10102</v>
       </c>
       <c r="C127" s="1"/>
       <c r="D127" s="1">
@@ -3849,7 +4007,7 @@
     <row r="128" ht="15" customHeight="1" spans="1:6">
       <c r="A128" s="1"/>
       <c r="B128" s="1">
-        <v>19012</v>
+        <v>10103</v>
       </c>
       <c r="C128" s="1"/>
       <c r="D128" s="1">
@@ -3865,7 +4023,7 @@
     <row r="129" ht="15" customHeight="1" spans="1:6">
       <c r="A129" s="1"/>
       <c r="B129" s="1">
-        <v>19013</v>
+        <v>10201</v>
       </c>
       <c r="C129" s="1"/>
       <c r="D129" s="1">
@@ -3881,7 +4039,7 @@
     <row r="130" ht="15" customHeight="1" spans="1:6">
       <c r="A130" s="1"/>
       <c r="B130" s="1">
-        <v>19014</v>
+        <v>10202</v>
       </c>
       <c r="C130" s="1"/>
       <c r="D130" s="1">
@@ -3897,7 +4055,7 @@
     <row r="131" ht="15" customHeight="1" spans="1:6">
       <c r="A131" s="1"/>
       <c r="B131" s="1">
-        <v>19022</v>
+        <v>10203</v>
       </c>
       <c r="C131" s="1"/>
       <c r="D131" s="1">
@@ -3913,7 +4071,7 @@
     <row r="132" ht="15" customHeight="1" spans="1:6">
       <c r="A132" s="1"/>
       <c r="B132" s="1">
-        <v>19023</v>
+        <v>15001</v>
       </c>
       <c r="C132" s="1"/>
       <c r="D132" s="1">
@@ -3929,7 +4087,7 @@
     <row r="133" ht="15" customHeight="1" spans="1:6">
       <c r="A133" s="1"/>
       <c r="B133" s="1">
-        <v>19024</v>
+        <v>15002</v>
       </c>
       <c r="C133" s="1"/>
       <c r="D133" s="1">
@@ -3942,18 +4100,436 @@
         <v>265</v>
       </c>
     </row>
-    <row r="134" spans="1:6">
-      <c r="B134">
+    <row r="134" ht="15" customHeight="1" spans="1:6">
+      <c r="A134" s="1"/>
+      <c r="B134" s="1">
+        <v>15003</v>
+      </c>
+      <c r="C134" s="1"/>
+      <c r="D134" s="1">
+        <v>1</v>
+      </c>
+      <c r="E134" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="F134" s="1" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="135" ht="15" customHeight="1" spans="1:6">
+      <c r="A135" s="1"/>
+      <c r="B135" s="1">
+        <v>15005</v>
+      </c>
+      <c r="C135" s="1"/>
+      <c r="D135" s="1">
+        <v>1</v>
+      </c>
+      <c r="E135" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="F135" s="1" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="136" ht="15" customHeight="1" spans="1:6">
+      <c r="A136" s="1"/>
+      <c r="B136" s="1">
+        <v>15007</v>
+      </c>
+      <c r="C136" s="1"/>
+      <c r="D136" s="1">
+        <v>1</v>
+      </c>
+      <c r="E136" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="F136" s="1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="137" ht="15" customHeight="1" spans="1:6">
+      <c r="A137" s="1"/>
+      <c r="B137" s="1">
+        <v>15008</v>
+      </c>
+      <c r="C137" s="1"/>
+      <c r="D137" s="1">
+        <v>1</v>
+      </c>
+      <c r="E137" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="F137" s="1" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="138" ht="15" customHeight="1" spans="1:6">
+      <c r="A138" s="1"/>
+      <c r="B138" s="1">
+        <v>15009</v>
+      </c>
+      <c r="C138" s="1"/>
+      <c r="D138" s="1">
+        <v>1</v>
+      </c>
+      <c r="E138" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="F138" s="1" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="139" ht="15" customHeight="1" spans="1:6">
+      <c r="A139" s="1"/>
+      <c r="B139" s="1">
+        <v>15011</v>
+      </c>
+      <c r="C139" s="1"/>
+      <c r="D139" s="1">
+        <v>1</v>
+      </c>
+      <c r="E139" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F139" s="1" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="140" ht="15" customHeight="1" spans="1:6">
+      <c r="A140" s="1"/>
+      <c r="B140" s="1">
+        <v>15012</v>
+      </c>
+      <c r="C140" s="1"/>
+      <c r="D140" s="1">
+        <v>1</v>
+      </c>
+      <c r="E140" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="F140" s="1" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="141" ht="15" customHeight="1" spans="1:6">
+      <c r="A141" s="1"/>
+      <c r="B141" s="1">
+        <v>15013</v>
+      </c>
+      <c r="C141" s="1"/>
+      <c r="D141" s="1">
+        <v>1</v>
+      </c>
+      <c r="E141" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="F141" s="1" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="142" ht="15" customHeight="1" spans="1:6">
+      <c r="A142" s="1"/>
+      <c r="B142" s="1">
+        <v>15014</v>
+      </c>
+      <c r="C142" s="1"/>
+      <c r="D142" s="1">
+        <v>1</v>
+      </c>
+      <c r="E142" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="F142" s="1" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="143" ht="15" customHeight="1" spans="1:6">
+      <c r="A143" s="1"/>
+      <c r="B143" s="1">
+        <v>15015</v>
+      </c>
+      <c r="C143" s="1"/>
+      <c r="D143" s="1">
+        <v>1</v>
+      </c>
+      <c r="E143" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="F143" s="1" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="144" ht="15" customHeight="1" spans="1:6">
+      <c r="A144" s="1"/>
+      <c r="B144" s="1">
+        <v>15017</v>
+      </c>
+      <c r="C144" s="1"/>
+      <c r="D144" s="1">
+        <v>1</v>
+      </c>
+      <c r="E144" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="F144" s="1" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="145" ht="15" customHeight="1" spans="1:6">
+      <c r="A145" s="1"/>
+      <c r="B145" s="1">
+        <v>15018</v>
+      </c>
+      <c r="C145" s="1"/>
+      <c r="D145" s="1">
+        <v>1</v>
+      </c>
+      <c r="E145" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="F145" s="1" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="146" ht="15" customHeight="1" spans="1:6">
+      <c r="A146" s="1"/>
+      <c r="B146" s="1">
+        <v>15019</v>
+      </c>
+      <c r="C146" s="1"/>
+      <c r="D146" s="1">
+        <v>1</v>
+      </c>
+      <c r="E146" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F146" s="1" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="147" ht="15" customHeight="1" spans="1:6">
+      <c r="A147" s="1"/>
+      <c r="B147" s="1">
+        <v>15020</v>
+      </c>
+      <c r="C147" s="1"/>
+      <c r="D147" s="1">
+        <v>1</v>
+      </c>
+      <c r="E147" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="F147" s="1" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="148" ht="15" customHeight="1" spans="1:6">
+      <c r="A148" s="1"/>
+      <c r="B148" s="1">
+        <v>15021</v>
+      </c>
+      <c r="C148" s="1"/>
+      <c r="D148" s="1">
+        <v>1</v>
+      </c>
+      <c r="E148" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="F148" s="1" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="149" ht="15" customHeight="1" spans="1:6">
+      <c r="A149" s="1"/>
+      <c r="B149" s="1">
+        <v>15022</v>
+      </c>
+      <c r="C149" s="1"/>
+      <c r="D149" s="1">
+        <v>1</v>
+      </c>
+      <c r="E149" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="F149" s="1" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="150" ht="15" customHeight="1" spans="1:6">
+      <c r="A150" s="1"/>
+      <c r="B150" s="1">
+        <v>15023</v>
+      </c>
+      <c r="C150" s="1"/>
+      <c r="D150" s="1">
+        <v>1</v>
+      </c>
+      <c r="E150" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="F150" s="1" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="151" ht="15" customHeight="1" spans="1:6">
+      <c r="A151" s="1"/>
+      <c r="B151" s="1">
+        <v>19002</v>
+      </c>
+      <c r="C151" s="1"/>
+      <c r="D151" s="1">
+        <v>1</v>
+      </c>
+      <c r="E151" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="F151" s="1" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="152" ht="15" customHeight="1" spans="1:6">
+      <c r="A152" s="1"/>
+      <c r="B152" s="1">
+        <v>19003</v>
+      </c>
+      <c r="C152" s="1"/>
+      <c r="D152" s="1">
+        <v>1</v>
+      </c>
+      <c r="E152" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="F152" s="1" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="153" ht="15" customHeight="1" spans="1:6">
+      <c r="A153" s="1"/>
+      <c r="B153" s="1">
+        <v>19004</v>
+      </c>
+      <c r="C153" s="1"/>
+      <c r="D153" s="1">
+        <v>1</v>
+      </c>
+      <c r="E153" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="F153" s="1" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="154" ht="15" customHeight="1" spans="1:6">
+      <c r="A154" s="1"/>
+      <c r="B154" s="1">
+        <v>19012</v>
+      </c>
+      <c r="C154" s="1"/>
+      <c r="D154" s="1">
+        <v>1</v>
+      </c>
+      <c r="E154" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="F154" s="1" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="155" ht="15" customHeight="1" spans="1:6">
+      <c r="A155" s="1"/>
+      <c r="B155" s="1">
+        <v>19013</v>
+      </c>
+      <c r="C155" s="1"/>
+      <c r="D155" s="1">
+        <v>1</v>
+      </c>
+      <c r="E155" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="F155" s="1" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="156" ht="15" customHeight="1" spans="1:6">
+      <c r="A156" s="1"/>
+      <c r="B156" s="1">
+        <v>19014</v>
+      </c>
+      <c r="C156" s="1"/>
+      <c r="D156" s="1">
+        <v>1</v>
+      </c>
+      <c r="E156" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="F156" s="1" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="157" ht="15" customHeight="1" spans="1:6">
+      <c r="A157" s="1"/>
+      <c r="B157" s="1">
+        <v>19022</v>
+      </c>
+      <c r="C157" s="1"/>
+      <c r="D157" s="1">
+        <v>1</v>
+      </c>
+      <c r="E157" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="F157" s="1" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="158" ht="15" customHeight="1" spans="1:6">
+      <c r="A158" s="1"/>
+      <c r="B158" s="1">
+        <v>19023</v>
+      </c>
+      <c r="C158" s="1"/>
+      <c r="D158" s="1">
+        <v>1</v>
+      </c>
+      <c r="E158" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="F158" s="1" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="159" ht="15" customHeight="1" spans="1:6">
+      <c r="A159" s="1"/>
+      <c r="B159" s="1">
+        <v>19024</v>
+      </c>
+      <c r="C159" s="1"/>
+      <c r="D159" s="1">
+        <v>1</v>
+      </c>
+      <c r="E159" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="F159" s="1" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="160" ht="15" customHeight="1" spans="1:6">
+      <c r="A160" s="1"/>
+      <c r="B160" s="1">
         <v>11001</v>
       </c>
-      <c r="D134">
-        <v>1</v>
-      </c>
-      <c r="E134" t="s">
-        <v>266</v>
-      </c>
-      <c r="F134" t="s">
-        <v>267</v>
+      <c r="C160" s="1"/>
+      <c r="D160" s="1">
+        <v>1</v>
+      </c>
+      <c r="E160" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="F160" s="1" t="s">
+        <v>319</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/DataTables/ResourceConfigTable.xlsx
+++ b/AAAGameData/DataTables/ResourceConfigTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="14855"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -999,14 +999,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1462,148 +1455,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1959,7 +1952,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F160"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="21" customWidth="1"/>
@@ -2016,7 +2009,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" ht="72" spans="1:6">
+    <row r="4" ht="67.5" spans="1:6">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>

--- a/AAAGameData/DataTables/ResourceConfigTable.xlsx
+++ b/AAAGameData/DataTables/ResourceConfigTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="330">
   <si>
     <t>#</t>
   </si>
@@ -987,6 +987,36 @@
   </si>
   <si>
     <t>敌人图标</t>
+  </si>
+  <si>
+    <t>Game/Interact/破损的宝箱</t>
+  </si>
+  <si>
+    <t>破损的宝箱</t>
+  </si>
+  <si>
+    <t>Game/Interact/精致的宝箱</t>
+  </si>
+  <si>
+    <t>精致的宝箱</t>
+  </si>
+  <si>
+    <t>Game/Interact/华丽的宝箱</t>
+  </si>
+  <si>
+    <t>华丽的宝箱</t>
+  </si>
+  <si>
+    <t>Game/Interact/神秘的宝箱</t>
+  </si>
+  <si>
+    <t>神秘的宝箱</t>
+  </si>
+  <si>
+    <t>Enemy/后羿(敌人测试)</t>
+  </si>
+  <si>
+    <t>敌人测试预制体</t>
   </si>
 </sst>
 </file>
@@ -1951,7 +1981,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F160"/>
+  <dimension ref="A1:F165"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -4525,6 +4555,76 @@
         <v>319</v>
       </c>
     </row>
+    <row r="161" spans="2:6">
+      <c r="B161">
+        <v>2501</v>
+      </c>
+      <c r="D161">
+        <v>2</v>
+      </c>
+      <c r="E161" t="s">
+        <v>320</v>
+      </c>
+      <c r="F161" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="162" spans="2:6">
+      <c r="B162">
+        <v>2502</v>
+      </c>
+      <c r="D162">
+        <v>2</v>
+      </c>
+      <c r="E162" t="s">
+        <v>322</v>
+      </c>
+      <c r="F162" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="163" spans="2:6">
+      <c r="B163">
+        <v>2503</v>
+      </c>
+      <c r="D163">
+        <v>2</v>
+      </c>
+      <c r="E163" t="s">
+        <v>324</v>
+      </c>
+      <c r="F163" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="164" spans="2:6">
+      <c r="B164">
+        <v>2504</v>
+      </c>
+      <c r="D164">
+        <v>2</v>
+      </c>
+      <c r="E164" t="s">
+        <v>326</v>
+      </c>
+      <c r="F164" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="165" spans="2:6">
+      <c r="B165">
+        <v>2601</v>
+      </c>
+      <c r="D165">
+        <v>2</v>
+      </c>
+      <c r="E165" t="s">
+        <v>328</v>
+      </c>
+      <c r="F165" t="s">
+        <v>329</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/AAAGameData/DataTables/ResourceConfigTable.xlsx
+++ b/AAAGameData/DataTables/ResourceConfigTable.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="380">
   <si>
     <t>#</t>
   </si>
@@ -617,6 +617,150 @@
     <t>风暴法杖图标</t>
   </si>
   <si>
+    <t>Items/CardUnlock/100.png</t>
+  </si>
+  <si>
+    <t>卡牌-神圣庇护解锁物图标</t>
+  </si>
+  <si>
+    <t>Items/CardUnlock/101.png</t>
+  </si>
+  <si>
+    <t>卡牌-烈焰风暴解锁物图标</t>
+  </si>
+  <si>
+    <t>Items/CardUnlock/102.png</t>
+  </si>
+  <si>
+    <t>卡牌-时间回溯解锁物图标</t>
+  </si>
+  <si>
+    <t>Items/CardUnlock/103.png</t>
+  </si>
+  <si>
+    <t>卡牌-战争号角解锁物图标</t>
+  </si>
+  <si>
+    <t>Items/CardUnlock/104.png</t>
+  </si>
+  <si>
+    <t>卡牌-暗影突袭解锁物图标</t>
+  </si>
+  <si>
+    <t>Items/CardUnlock/105.png</t>
+  </si>
+  <si>
+    <t>卡牌-生命汲取解锁物图标</t>
+  </si>
+  <si>
+    <t>Items/CardUnlock/106.png</t>
+  </si>
+  <si>
+    <t>卡牌-冰霜新星解锁物图标</t>
+  </si>
+  <si>
+    <t>Items/CardUnlock/107.png</t>
+  </si>
+  <si>
+    <t>卡牌-狂暴解锁物图标</t>
+  </si>
+  <si>
+    <t>Items/CardUnlock/108.png</t>
+  </si>
+  <si>
+    <t>卡牌-群体治疗解锁物图标</t>
+  </si>
+  <si>
+    <t>Items/CardUnlock/109.png</t>
+  </si>
+  <si>
+    <t>卡牌-雷霆一击解锁物图标</t>
+  </si>
+  <si>
+    <t>Items/CardUnlock/110.png</t>
+  </si>
+  <si>
+    <t>卡牌-混乱诅咒解锁物图标</t>
+  </si>
+  <si>
+    <t>Items/CardUnlock/111.png</t>
+  </si>
+  <si>
+    <t>卡牌-不屈意志解锁物图标</t>
+  </si>
+  <si>
+    <t>Items/CardUnlock/112.png</t>
+  </si>
+  <si>
+    <t>卡牌-反伤之盾解锁物图标</t>
+  </si>
+  <si>
+    <t>Items/CardUnlock/113.png</t>
+  </si>
+  <si>
+    <t>卡牌-圣域防线解锁物图标</t>
+  </si>
+  <si>
+    <t>Items/CardUnlock/114.png</t>
+  </si>
+  <si>
+    <t>卡牌-护盾再生解锁物图标</t>
+  </si>
+  <si>
+    <t>Items/CardUnlock/115.png</t>
+  </si>
+  <si>
+    <t>卡牌-救赎之光解锁物图标</t>
+  </si>
+  <si>
+    <t>Items/CardUnlock/116.png</t>
+  </si>
+  <si>
+    <t>卡牌-血源强化解锁物图标</t>
+  </si>
+  <si>
+    <t>Items/CardUnlock/117.png</t>
+  </si>
+  <si>
+    <t>卡牌-吸血之刃解锁物图标</t>
+  </si>
+  <si>
+    <t>Items/CardUnlock/118.png</t>
+  </si>
+  <si>
+    <t>卡牌-灾厄之雷解锁物图标</t>
+  </si>
+  <si>
+    <t>Items/CardUnlock/119.png</t>
+  </si>
+  <si>
+    <t>卡牌-护甲破碎解锁物图标</t>
+  </si>
+  <si>
+    <t>Items/CardUnlock/120.png</t>
+  </si>
+  <si>
+    <t>卡牌-虚弱诅咒解锁物图标</t>
+  </si>
+  <si>
+    <t>Items/CardUnlock/121.png</t>
+  </si>
+  <si>
+    <t>卡牌-沉默之符解锁物图标</t>
+  </si>
+  <si>
+    <t>Items/CardUnlock/122.png</t>
+  </si>
+  <si>
+    <t>卡牌-嘲讽之声解锁物图标</t>
+  </si>
+  <si>
+    <t>Items/CardUnlock/123.png</t>
+  </si>
+  <si>
+    <t>卡牌-剧毒之雾解锁物图标</t>
+  </si>
+  <si>
     <t>UI/CloudInfo/PlayerInfo</t>
   </si>
   <si>
@@ -821,6 +965,9 @@
     <t>神圣庇护Buff图标</t>
   </si>
   <si>
+    <t>(不再使用)</t>
+  </si>
+  <si>
     <t>Buff/5002.png</t>
   </si>
   <si>
@@ -915,6 +1062,9 @@
   </si>
   <si>
     <t>剧毒之雾Buff图标</t>
+  </si>
+  <si>
+    <t>暂未实现</t>
   </si>
   <si>
     <t>Buff/5022.png</t>
@@ -1029,7 +1179,14 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1485,31 +1642,28 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1518,115 +1672,118 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1981,7 +2138,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F165"/>
+  <dimension ref="A1:F189"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -3550,11 +3707,11 @@
     <row r="98" ht="15" customHeight="1" spans="1:6">
       <c r="A98" s="1"/>
       <c r="B98" s="1">
-        <v>2001</v>
+        <v>1925</v>
       </c>
       <c r="C98" s="1"/>
       <c r="D98" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E98" s="1" t="s">
         <v>196</v>
@@ -3566,11 +3723,11 @@
     <row r="99" ht="15" customHeight="1" spans="1:6">
       <c r="A99" s="1"/>
       <c r="B99" s="1">
-        <v>2002</v>
+        <v>1926</v>
       </c>
       <c r="C99" s="1"/>
       <c r="D99" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E99" s="1" t="s">
         <v>198</v>
@@ -3582,11 +3739,11 @@
     <row r="100" ht="15" customHeight="1" spans="1:6">
       <c r="A100" s="1"/>
       <c r="B100" s="1">
-        <v>2003</v>
+        <v>1927</v>
       </c>
       <c r="C100" s="1"/>
       <c r="D100" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E100" s="1" t="s">
         <v>200</v>
@@ -3598,11 +3755,11 @@
     <row r="101" ht="15" customHeight="1" spans="1:6">
       <c r="A101" s="1"/>
       <c r="B101" s="1">
-        <v>2004</v>
+        <v>1928</v>
       </c>
       <c r="C101" s="1"/>
       <c r="D101" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>202</v>
@@ -3614,11 +3771,11 @@
     <row r="102" ht="15" customHeight="1" spans="1:6">
       <c r="A102" s="1"/>
       <c r="B102" s="1">
-        <v>2101</v>
+        <v>1929</v>
       </c>
       <c r="C102" s="1"/>
       <c r="D102" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E102" s="1" t="s">
         <v>204</v>
@@ -3630,11 +3787,11 @@
     <row r="103" ht="15" customHeight="1" spans="1:6">
       <c r="A103" s="1"/>
       <c r="B103" s="1">
-        <v>2102</v>
+        <v>1930</v>
       </c>
       <c r="C103" s="1"/>
       <c r="D103" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E103" s="1" t="s">
         <v>206</v>
@@ -3646,414 +3803,414 @@
     <row r="104" ht="15" customHeight="1" spans="1:6">
       <c r="A104" s="1"/>
       <c r="B104" s="1">
-        <v>2103</v>
+        <v>1931</v>
       </c>
       <c r="C104" s="1"/>
       <c r="D104" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="105" ht="15" customHeight="1" spans="1:6">
       <c r="A105" s="1"/>
       <c r="B105" s="1">
-        <v>2104</v>
+        <v>1932</v>
       </c>
       <c r="C105" s="1"/>
       <c r="D105" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="106" ht="15" customHeight="1" spans="1:6">
       <c r="A106" s="1"/>
       <c r="B106" s="1">
-        <v>2201</v>
+        <v>1933</v>
       </c>
       <c r="C106" s="1"/>
       <c r="D106" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="107" ht="15" customHeight="1" spans="1:6">
       <c r="A107" s="1"/>
       <c r="B107" s="1">
-        <v>2301</v>
+        <v>1934</v>
       </c>
       <c r="C107" s="1"/>
       <c r="D107" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="108" ht="15" customHeight="1" spans="1:6">
       <c r="A108" s="1"/>
       <c r="B108" s="1">
-        <v>2304</v>
+        <v>1935</v>
       </c>
       <c r="C108" s="1"/>
       <c r="D108" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="109" ht="15" customHeight="1" spans="1:6">
       <c r="A109" s="1"/>
       <c r="B109" s="1">
-        <v>2309</v>
+        <v>1936</v>
       </c>
       <c r="C109" s="1"/>
       <c r="D109" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="110" ht="15" customHeight="1" spans="1:6">
       <c r="A110" s="1"/>
       <c r="B110" s="1">
-        <v>2399</v>
+        <v>1937</v>
       </c>
       <c r="C110" s="1"/>
       <c r="D110" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="111" ht="15" customHeight="1" spans="1:6">
       <c r="A111" s="1"/>
       <c r="B111" s="1">
-        <v>2401</v>
+        <v>1938</v>
       </c>
       <c r="C111" s="1"/>
       <c r="D111" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="112" ht="15" customHeight="1" spans="1:6">
       <c r="A112" s="1"/>
       <c r="B112" s="1">
-        <v>2402</v>
+        <v>1939</v>
       </c>
       <c r="C112" s="1"/>
       <c r="D112" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="113" ht="15" customHeight="1" spans="1:6">
       <c r="A113" s="1"/>
       <c r="B113" s="1">
-        <v>2901</v>
+        <v>1940</v>
       </c>
       <c r="C113" s="1"/>
       <c r="D113" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="114" ht="15" customHeight="1" spans="1:6">
       <c r="A114" s="1"/>
       <c r="B114" s="1">
-        <v>3001</v>
+        <v>1941</v>
       </c>
       <c r="C114" s="1"/>
       <c r="D114" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="115" ht="15" customHeight="1" spans="1:6">
       <c r="A115" s="1"/>
       <c r="B115" s="1">
-        <v>3002</v>
+        <v>1942</v>
       </c>
       <c r="C115" s="1"/>
       <c r="D115" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="116" ht="15" customHeight="1" spans="1:6">
       <c r="A116" s="1"/>
       <c r="B116" s="1">
-        <v>3003</v>
+        <v>1943</v>
       </c>
       <c r="C116" s="1"/>
       <c r="D116" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="117" ht="15" customHeight="1" spans="1:6">
       <c r="A117" s="1"/>
       <c r="B117" s="1">
-        <v>3004</v>
+        <v>1944</v>
       </c>
       <c r="C117" s="1"/>
       <c r="D117" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="118" ht="15" customHeight="1" spans="1:6">
       <c r="A118" s="1"/>
       <c r="B118" s="1">
-        <v>3005</v>
+        <v>1945</v>
       </c>
       <c r="C118" s="1"/>
       <c r="D118" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="119" ht="15" customHeight="1" spans="1:6">
       <c r="A119" s="1"/>
       <c r="B119" s="1">
-        <v>3006</v>
+        <v>1946</v>
       </c>
       <c r="C119" s="1"/>
       <c r="D119" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="120" ht="15" customHeight="1" spans="1:6">
       <c r="A120" s="1"/>
       <c r="B120" s="1">
-        <v>3007</v>
+        <v>1947</v>
       </c>
       <c r="C120" s="1"/>
       <c r="D120" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="121" ht="15" customHeight="1" spans="1:6">
       <c r="A121" s="1"/>
       <c r="B121" s="1">
-        <v>6001</v>
+        <v>1948</v>
       </c>
       <c r="C121" s="1"/>
       <c r="D121" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="122" ht="15" customHeight="1" spans="1:6">
       <c r="A122" s="1"/>
       <c r="B122" s="1">
-        <v>10001</v>
+        <v>2001</v>
       </c>
       <c r="C122" s="1"/>
       <c r="D122" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="123" ht="15" customHeight="1" spans="1:6">
       <c r="A123" s="1"/>
       <c r="B123" s="1">
-        <v>10002</v>
+        <v>2002</v>
       </c>
       <c r="C123" s="1"/>
       <c r="D123" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="124" ht="15" customHeight="1" spans="1:6">
       <c r="A124" s="1"/>
       <c r="B124" s="1">
-        <v>10003</v>
+        <v>2003</v>
       </c>
       <c r="C124" s="1"/>
       <c r="D124" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="125" ht="15" customHeight="1" spans="1:6">
       <c r="A125" s="1"/>
       <c r="B125" s="1">
-        <v>10004</v>
+        <v>2004</v>
       </c>
       <c r="C125" s="1"/>
       <c r="D125" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="126" ht="15" customHeight="1" spans="1:6">
       <c r="A126" s="1"/>
       <c r="B126" s="1">
-        <v>10101</v>
+        <v>2101</v>
       </c>
       <c r="C126" s="1"/>
       <c r="D126" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="127" ht="15" customHeight="1" spans="1:6">
       <c r="A127" s="1"/>
       <c r="B127" s="1">
-        <v>10102</v>
+        <v>2102</v>
       </c>
       <c r="C127" s="1"/>
       <c r="D127" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="128" ht="15" customHeight="1" spans="1:6">
       <c r="A128" s="1"/>
       <c r="B128" s="1">
-        <v>10103</v>
+        <v>2103</v>
       </c>
       <c r="C128" s="1"/>
       <c r="D128" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E128" s="1" t="s">
         <v>254</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="129" ht="15" customHeight="1" spans="1:6">
       <c r="A129" s="1"/>
       <c r="B129" s="1">
-        <v>10201</v>
+        <v>2104</v>
       </c>
       <c r="C129" s="1"/>
       <c r="D129" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>257</v>
@@ -4062,11 +4219,11 @@
     <row r="130" ht="15" customHeight="1" spans="1:6">
       <c r="A130" s="1"/>
       <c r="B130" s="1">
-        <v>10202</v>
+        <v>2201</v>
       </c>
       <c r="C130" s="1"/>
       <c r="D130" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E130" s="1" t="s">
         <v>258</v>
@@ -4078,11 +4235,11 @@
     <row r="131" ht="15" customHeight="1" spans="1:6">
       <c r="A131" s="1"/>
       <c r="B131" s="1">
-        <v>10203</v>
+        <v>2301</v>
       </c>
       <c r="C131" s="1"/>
       <c r="D131" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E131" s="1" t="s">
         <v>260</v>
@@ -4094,11 +4251,11 @@
     <row r="132" ht="15" customHeight="1" spans="1:6">
       <c r="A132" s="1"/>
       <c r="B132" s="1">
-        <v>15001</v>
+        <v>2304</v>
       </c>
       <c r="C132" s="1"/>
       <c r="D132" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E132" s="1" t="s">
         <v>262</v>
@@ -4110,11 +4267,11 @@
     <row r="133" ht="15" customHeight="1" spans="1:6">
       <c r="A133" s="1"/>
       <c r="B133" s="1">
-        <v>15002</v>
+        <v>2309</v>
       </c>
       <c r="C133" s="1"/>
       <c r="D133" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E133" s="1" t="s">
         <v>264</v>
@@ -4126,11 +4283,11 @@
     <row r="134" ht="15" customHeight="1" spans="1:6">
       <c r="A134" s="1"/>
       <c r="B134" s="1">
-        <v>15003</v>
+        <v>2399</v>
       </c>
       <c r="C134" s="1"/>
       <c r="D134" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E134" s="1" t="s">
         <v>266</v>
@@ -4142,11 +4299,11 @@
     <row r="135" ht="15" customHeight="1" spans="1:6">
       <c r="A135" s="1"/>
       <c r="B135" s="1">
-        <v>15005</v>
+        <v>2401</v>
       </c>
       <c r="C135" s="1"/>
       <c r="D135" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E135" s="1" t="s">
         <v>268</v>
@@ -4158,11 +4315,11 @@
     <row r="136" ht="15" customHeight="1" spans="1:6">
       <c r="A136" s="1"/>
       <c r="B136" s="1">
-        <v>15007</v>
+        <v>2402</v>
       </c>
       <c r="C136" s="1"/>
       <c r="D136" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E136" s="1" t="s">
         <v>270</v>
@@ -4174,11 +4331,11 @@
     <row r="137" ht="15" customHeight="1" spans="1:6">
       <c r="A137" s="1"/>
       <c r="B137" s="1">
-        <v>15008</v>
+        <v>2901</v>
       </c>
       <c r="C137" s="1"/>
       <c r="D137" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E137" s="1" t="s">
         <v>272</v>
@@ -4190,11 +4347,11 @@
     <row r="138" ht="15" customHeight="1" spans="1:6">
       <c r="A138" s="1"/>
       <c r="B138" s="1">
-        <v>15009</v>
+        <v>3001</v>
       </c>
       <c r="C138" s="1"/>
       <c r="D138" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E138" s="1" t="s">
         <v>274</v>
@@ -4206,11 +4363,11 @@
     <row r="139" ht="15" customHeight="1" spans="1:6">
       <c r="A139" s="1"/>
       <c r="B139" s="1">
-        <v>15011</v>
+        <v>3002</v>
       </c>
       <c r="C139" s="1"/>
       <c r="D139" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E139" s="1" t="s">
         <v>276</v>
@@ -4222,11 +4379,11 @@
     <row r="140" ht="15" customHeight="1" spans="1:6">
       <c r="A140" s="1"/>
       <c r="B140" s="1">
-        <v>15012</v>
+        <v>3003</v>
       </c>
       <c r="C140" s="1"/>
       <c r="D140" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E140" s="1" t="s">
         <v>278</v>
@@ -4238,11 +4395,11 @@
     <row r="141" ht="15" customHeight="1" spans="1:6">
       <c r="A141" s="1"/>
       <c r="B141" s="1">
-        <v>15013</v>
+        <v>3004</v>
       </c>
       <c r="C141" s="1"/>
       <c r="D141" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E141" s="1" t="s">
         <v>280</v>
@@ -4254,11 +4411,11 @@
     <row r="142" ht="15" customHeight="1" spans="1:6">
       <c r="A142" s="1"/>
       <c r="B142" s="1">
-        <v>15014</v>
+        <v>3005</v>
       </c>
       <c r="C142" s="1"/>
       <c r="D142" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E142" s="1" t="s">
         <v>282</v>
@@ -4270,11 +4427,11 @@
     <row r="143" ht="15" customHeight="1" spans="1:6">
       <c r="A143" s="1"/>
       <c r="B143" s="1">
-        <v>15015</v>
+        <v>3006</v>
       </c>
       <c r="C143" s="1"/>
       <c r="D143" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E143" s="1" t="s">
         <v>284</v>
@@ -4286,11 +4443,11 @@
     <row r="144" ht="15" customHeight="1" spans="1:6">
       <c r="A144" s="1"/>
       <c r="B144" s="1">
-        <v>15017</v>
+        <v>3007</v>
       </c>
       <c r="C144" s="1"/>
       <c r="D144" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E144" s="1" t="s">
         <v>286</v>
@@ -4302,11 +4459,11 @@
     <row r="145" ht="15" customHeight="1" spans="1:6">
       <c r="A145" s="1"/>
       <c r="B145" s="1">
-        <v>15018</v>
+        <v>6001</v>
       </c>
       <c r="C145" s="1"/>
       <c r="D145" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E145" s="1" t="s">
         <v>288</v>
@@ -4318,7 +4475,7 @@
     <row r="146" ht="15" customHeight="1" spans="1:6">
       <c r="A146" s="1"/>
       <c r="B146" s="1">
-        <v>15019</v>
+        <v>10001</v>
       </c>
       <c r="C146" s="1"/>
       <c r="D146" s="1">
@@ -4334,7 +4491,7 @@
     <row r="147" ht="15" customHeight="1" spans="1:6">
       <c r="A147" s="1"/>
       <c r="B147" s="1">
-        <v>15020</v>
+        <v>10002</v>
       </c>
       <c r="C147" s="1"/>
       <c r="D147" s="1">
@@ -4350,7 +4507,7 @@
     <row r="148" ht="15" customHeight="1" spans="1:6">
       <c r="A148" s="1"/>
       <c r="B148" s="1">
-        <v>15021</v>
+        <v>10003</v>
       </c>
       <c r="C148" s="1"/>
       <c r="D148" s="1">
@@ -4366,7 +4523,7 @@
     <row r="149" ht="15" customHeight="1" spans="1:6">
       <c r="A149" s="1"/>
       <c r="B149" s="1">
-        <v>15022</v>
+        <v>10004</v>
       </c>
       <c r="C149" s="1"/>
       <c r="D149" s="1">
@@ -4382,7 +4539,7 @@
     <row r="150" ht="15" customHeight="1" spans="1:6">
       <c r="A150" s="1"/>
       <c r="B150" s="1">
-        <v>15023</v>
+        <v>10101</v>
       </c>
       <c r="C150" s="1"/>
       <c r="D150" s="1">
@@ -4398,7 +4555,7 @@
     <row r="151" ht="15" customHeight="1" spans="1:6">
       <c r="A151" s="1"/>
       <c r="B151" s="1">
-        <v>19002</v>
+        <v>10102</v>
       </c>
       <c r="C151" s="1"/>
       <c r="D151" s="1">
@@ -4414,7 +4571,7 @@
     <row r="152" ht="15" customHeight="1" spans="1:6">
       <c r="A152" s="1"/>
       <c r="B152" s="1">
-        <v>19003</v>
+        <v>10103</v>
       </c>
       <c r="C152" s="1"/>
       <c r="D152" s="1">
@@ -4430,7 +4587,7 @@
     <row r="153" ht="15" customHeight="1" spans="1:6">
       <c r="A153" s="1"/>
       <c r="B153" s="1">
-        <v>19004</v>
+        <v>10201</v>
       </c>
       <c r="C153" s="1"/>
       <c r="D153" s="1">
@@ -4446,7 +4603,7 @@
     <row r="154" ht="15" customHeight="1" spans="1:6">
       <c r="A154" s="1"/>
       <c r="B154" s="1">
-        <v>19012</v>
+        <v>10202</v>
       </c>
       <c r="C154" s="1"/>
       <c r="D154" s="1">
@@ -4462,7 +4619,7 @@
     <row r="155" ht="15" customHeight="1" spans="1:6">
       <c r="A155" s="1"/>
       <c r="B155" s="1">
-        <v>19013</v>
+        <v>10203</v>
       </c>
       <c r="C155" s="1"/>
       <c r="D155" s="1">
@@ -4478,7 +4635,7 @@
     <row r="156" ht="15" customHeight="1" spans="1:6">
       <c r="A156" s="1"/>
       <c r="B156" s="1">
-        <v>19014</v>
+        <v>15001</v>
       </c>
       <c r="C156" s="1"/>
       <c r="D156" s="1">
@@ -4494,135 +4651,535 @@
     <row r="157" ht="15" customHeight="1" spans="1:6">
       <c r="A157" s="1"/>
       <c r="B157" s="1">
-        <v>19022</v>
-      </c>
-      <c r="C157" s="1"/>
+        <v>15002</v>
+      </c>
+      <c r="C157" s="1" t="s">
+        <v>312</v>
+      </c>
       <c r="D157" s="1">
         <v>1</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="158" ht="15" customHeight="1" spans="1:6">
       <c r="A158" s="1"/>
       <c r="B158" s="1">
-        <v>19023</v>
+        <v>15003</v>
       </c>
       <c r="C158" s="1"/>
       <c r="D158" s="1">
         <v>1</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="159" ht="15" customHeight="1" spans="1:6">
       <c r="A159" s="1"/>
       <c r="B159" s="1">
-        <v>19024</v>
+        <v>15005</v>
       </c>
       <c r="C159" s="1"/>
       <c r="D159" s="1">
         <v>1</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="160" ht="15" customHeight="1" spans="1:6">
       <c r="A160" s="1"/>
       <c r="B160" s="1">
-        <v>11001</v>
+        <v>15007</v>
       </c>
       <c r="C160" s="1"/>
       <c r="D160" s="1">
         <v>1</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="161" spans="2:6">
-      <c r="B161">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="161" ht="15" customHeight="1" spans="1:6">
+      <c r="A161" s="1"/>
+      <c r="B161" s="1">
+        <v>15008</v>
+      </c>
+      <c r="C161" s="1"/>
+      <c r="D161" s="1">
+        <v>1</v>
+      </c>
+      <c r="E161" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="F161" s="1" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="162" ht="15" customHeight="1" spans="1:6">
+      <c r="A162" s="1"/>
+      <c r="B162" s="1">
+        <v>15009</v>
+      </c>
+      <c r="C162" s="1"/>
+      <c r="D162" s="1">
+        <v>1</v>
+      </c>
+      <c r="E162" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="F162" s="1" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="163" ht="15" customHeight="1" spans="1:6">
+      <c r="A163" s="1"/>
+      <c r="B163" s="1">
+        <v>15011</v>
+      </c>
+      <c r="C163" s="1"/>
+      <c r="D163" s="1">
+        <v>1</v>
+      </c>
+      <c r="E163" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="F163" s="1" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="164" ht="15" customHeight="1" spans="1:6">
+      <c r="A164" s="1"/>
+      <c r="B164" s="1">
+        <v>15012</v>
+      </c>
+      <c r="C164" s="1"/>
+      <c r="D164" s="1">
+        <v>1</v>
+      </c>
+      <c r="E164" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="F164" s="1" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="165" ht="15" customHeight="1" spans="1:6">
+      <c r="A165" s="1"/>
+      <c r="B165" s="1">
+        <v>15013</v>
+      </c>
+      <c r="C165" s="1"/>
+      <c r="D165" s="1">
+        <v>1</v>
+      </c>
+      <c r="E165" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="F165" s="1" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="166" ht="15" customHeight="1" spans="1:6">
+      <c r="A166" s="1"/>
+      <c r="B166" s="1">
+        <v>15014</v>
+      </c>
+      <c r="C166" s="1"/>
+      <c r="D166" s="1">
+        <v>1</v>
+      </c>
+      <c r="E166" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="F166" s="1" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="167" ht="15" customHeight="1" spans="1:6">
+      <c r="A167" s="1"/>
+      <c r="B167" s="1">
+        <v>15015</v>
+      </c>
+      <c r="C167" s="1"/>
+      <c r="D167" s="1">
+        <v>1</v>
+      </c>
+      <c r="E167" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="F167" s="1" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="168" ht="15" customHeight="1" spans="1:6">
+      <c r="A168" s="1"/>
+      <c r="B168" s="1">
+        <v>15017</v>
+      </c>
+      <c r="C168" s="1"/>
+      <c r="D168" s="1">
+        <v>1</v>
+      </c>
+      <c r="E168" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="F168" s="1" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="169" ht="15" customHeight="1" spans="1:6">
+      <c r="A169" s="1"/>
+      <c r="B169" s="1">
+        <v>15018</v>
+      </c>
+      <c r="C169" s="1"/>
+      <c r="D169" s="1">
+        <v>1</v>
+      </c>
+      <c r="E169" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="F169" s="1" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="170" ht="15" customHeight="1" spans="1:6">
+      <c r="A170" s="1"/>
+      <c r="B170" s="1">
+        <v>15019</v>
+      </c>
+      <c r="C170" s="1"/>
+      <c r="D170" s="1">
+        <v>1</v>
+      </c>
+      <c r="E170" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="F170" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="171" ht="15" customHeight="1" spans="1:6">
+      <c r="A171" s="1"/>
+      <c r="B171" s="1">
+        <v>15020</v>
+      </c>
+      <c r="C171" s="1"/>
+      <c r="D171" s="1">
+        <v>1</v>
+      </c>
+      <c r="E171" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="F171" s="1" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="172" ht="15" customHeight="1" spans="1:6">
+      <c r="A172" s="1"/>
+      <c r="B172" s="1">
+        <v>15021</v>
+      </c>
+      <c r="C172" s="1"/>
+      <c r="D172" s="1">
+        <v>1</v>
+      </c>
+      <c r="E172" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="F172" s="1" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="173" ht="15" customHeight="1" spans="1:6">
+      <c r="A173" s="1"/>
+      <c r="B173" s="1">
+        <v>15022</v>
+      </c>
+      <c r="C173" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="D173" s="1">
+        <v>1</v>
+      </c>
+      <c r="E173" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="F173" s="1" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="174" ht="15" customHeight="1" spans="1:6">
+      <c r="A174" s="1"/>
+      <c r="B174" s="1">
+        <v>15023</v>
+      </c>
+      <c r="C174" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="D174" s="1">
+        <v>1</v>
+      </c>
+      <c r="E174" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="F174" s="1" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="175" ht="15" customHeight="1" spans="1:6">
+      <c r="A175" s="1"/>
+      <c r="B175" s="1">
+        <v>19002</v>
+      </c>
+      <c r="C175" s="1"/>
+      <c r="D175" s="1">
+        <v>1</v>
+      </c>
+      <c r="E175" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="F175" s="1" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="176" ht="15" customHeight="1" spans="1:6">
+      <c r="A176" s="1"/>
+      <c r="B176" s="1">
+        <v>19003</v>
+      </c>
+      <c r="C176" s="1"/>
+      <c r="D176" s="1">
+        <v>1</v>
+      </c>
+      <c r="E176" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="F176" s="1" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="177" ht="15" customHeight="1" spans="1:6">
+      <c r="A177" s="1"/>
+      <c r="B177" s="1">
+        <v>19004</v>
+      </c>
+      <c r="C177" s="1"/>
+      <c r="D177" s="1">
+        <v>1</v>
+      </c>
+      <c r="E177" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="F177" s="1" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="178" ht="15" customHeight="1" spans="1:6">
+      <c r="A178" s="1"/>
+      <c r="B178" s="1">
+        <v>19012</v>
+      </c>
+      <c r="C178" s="1"/>
+      <c r="D178" s="1">
+        <v>1</v>
+      </c>
+      <c r="E178" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="F178" s="1" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="179" ht="15" customHeight="1" spans="1:6">
+      <c r="A179" s="1"/>
+      <c r="B179" s="1">
+        <v>19013</v>
+      </c>
+      <c r="C179" s="1"/>
+      <c r="D179" s="1">
+        <v>1</v>
+      </c>
+      <c r="E179" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="F179" s="1" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="180" ht="15" customHeight="1" spans="1:6">
+      <c r="A180" s="1"/>
+      <c r="B180" s="1">
+        <v>19014</v>
+      </c>
+      <c r="C180" s="1"/>
+      <c r="D180" s="1">
+        <v>1</v>
+      </c>
+      <c r="E180" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="F180" s="1" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="181" ht="15" customHeight="1" spans="1:6">
+      <c r="A181" s="1"/>
+      <c r="B181" s="1">
+        <v>19022</v>
+      </c>
+      <c r="C181" s="1"/>
+      <c r="D181" s="1">
+        <v>1</v>
+      </c>
+      <c r="E181" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="F181" s="1" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="182" ht="15" customHeight="1" spans="1:6">
+      <c r="A182" s="1"/>
+      <c r="B182" s="1">
+        <v>19023</v>
+      </c>
+      <c r="C182" s="1"/>
+      <c r="D182" s="1">
+        <v>1</v>
+      </c>
+      <c r="E182" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="F182" s="1" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="183" ht="15" customHeight="1" spans="1:6">
+      <c r="A183" s="1"/>
+      <c r="B183" s="1">
+        <v>19024</v>
+      </c>
+      <c r="C183" s="1"/>
+      <c r="D183" s="1">
+        <v>1</v>
+      </c>
+      <c r="E183" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="F183" s="1" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="184" ht="15" customHeight="1" spans="1:6">
+      <c r="A184" s="1"/>
+      <c r="B184" s="1">
+        <v>11001</v>
+      </c>
+      <c r="C184" s="1"/>
+      <c r="D184" s="1">
+        <v>1</v>
+      </c>
+      <c r="E184" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="F184" s="1" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="185" ht="15" customHeight="1" spans="1:6">
+      <c r="A185" s="1"/>
+      <c r="B185" s="1">
         <v>2501</v>
       </c>
-      <c r="D161">
+      <c r="C185" s="1"/>
+      <c r="D185" s="1">
         <v>2</v>
       </c>
-      <c r="E161" t="s">
-        <v>320</v>
-      </c>
-      <c r="F161" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="162" spans="2:6">
-      <c r="B162">
+      <c r="E185" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="F185" s="1" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="186" ht="15" customHeight="1" spans="1:6">
+      <c r="A186" s="1"/>
+      <c r="B186" s="1">
         <v>2502</v>
       </c>
-      <c r="D162">
+      <c r="C186" s="1"/>
+      <c r="D186" s="1">
         <v>2</v>
       </c>
-      <c r="E162" t="s">
-        <v>322</v>
-      </c>
-      <c r="F162" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="163" spans="2:6">
-      <c r="B163">
+      <c r="E186" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="F186" s="1" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="187" ht="15" customHeight="1" spans="1:6">
+      <c r="A187" s="1"/>
+      <c r="B187" s="1">
         <v>2503</v>
       </c>
-      <c r="D163">
+      <c r="C187" s="1"/>
+      <c r="D187" s="1">
         <v>2</v>
       </c>
-      <c r="E163" t="s">
-        <v>324</v>
-      </c>
-      <c r="F163" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="164" spans="2:6">
-      <c r="B164">
+      <c r="E187" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="F187" s="1" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="188" ht="15" customHeight="1" spans="1:6">
+      <c r="A188" s="1"/>
+      <c r="B188" s="1">
         <v>2504</v>
       </c>
-      <c r="D164">
+      <c r="C188" s="1"/>
+      <c r="D188" s="1">
         <v>2</v>
       </c>
-      <c r="E164" t="s">
-        <v>326</v>
-      </c>
-      <c r="F164" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="165" spans="2:6">
-      <c r="B165">
+      <c r="E188" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="F188" s="1" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="189" ht="15" customHeight="1" spans="1:6">
+      <c r="A189" s="1"/>
+      <c r="B189" s="1">
         <v>2601</v>
       </c>
-      <c r="D165">
+      <c r="C189" s="1"/>
+      <c r="D189" s="1">
         <v>2</v>
       </c>
-      <c r="E165" t="s">
-        <v>328</v>
-      </c>
-      <c r="F165" t="s">
-        <v>329</v>
+      <c r="E189" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="F189" s="1" t="s">
+        <v>379</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/DataTables/ResourceConfigTable.xlsx
+++ b/AAAGameData/DataTables/ResourceConfigTable.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="388">
   <si>
     <t>#</t>
   </si>
@@ -1167,6 +1167,30 @@
   </si>
   <si>
     <t>敌人测试预制体</t>
+  </si>
+  <si>
+    <t>Summoner/召唤师头像/狂战士.png</t>
+  </si>
+  <si>
+    <t>狂战士头像</t>
+  </si>
+  <si>
+    <t>Summoner/召唤师头像/术士.png</t>
+  </si>
+  <si>
+    <t>术士头像</t>
+  </si>
+  <si>
+    <t>Summoner/召唤师头像/混沌.png</t>
+  </si>
+  <si>
+    <t>混沌头像</t>
+  </si>
+  <si>
+    <t>Summoner/召唤师头像/德鲁伊.png</t>
+  </si>
+  <si>
+    <t>德鲁伊头像</t>
   </si>
 </sst>
 </file>
@@ -2138,7 +2162,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F189"/>
+  <dimension ref="A1:F193"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -5182,6 +5206,62 @@
         <v>379</v>
       </c>
     </row>
+    <row r="190" spans="1:6">
+      <c r="B190">
+        <v>1155</v>
+      </c>
+      <c r="D190">
+        <v>1</v>
+      </c>
+      <c r="E190" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F190" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6">
+      <c r="B191">
+        <v>1156</v>
+      </c>
+      <c r="D191">
+        <v>1</v>
+      </c>
+      <c r="E191" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="F191" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6">
+      <c r="B192">
+        <v>1157</v>
+      </c>
+      <c r="D192">
+        <v>1</v>
+      </c>
+      <c r="E192" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="F192" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="193" spans="2:6">
+      <c r="B193">
+        <v>1158</v>
+      </c>
+      <c r="D193">
+        <v>1</v>
+      </c>
+      <c r="E193" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="F193" t="s">
+        <v>387</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/AAAGameData/DataTables/ResourceConfigTable.xlsx
+++ b/AAAGameData/DataTables/ResourceConfigTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11925"/>
+    <workbookView windowWidth="29868" windowHeight="14855"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="390">
   <si>
     <t>#</t>
   </si>
@@ -1166,7 +1166,13 @@
     <t>Enemy/后羿(敌人测试)</t>
   </si>
   <si>
-    <t>敌人测试预制体</t>
+    <t>敌人-测试预制体</t>
+  </si>
+  <si>
+    <t>Enemy/邪灵</t>
+  </si>
+  <si>
+    <t>敌人-邪灵预制体</t>
   </si>
   <si>
     <t>Summoner/召唤师头像/狂战士.png</t>
@@ -1203,14 +1209,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1666,28 +1665,31 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1696,118 +1698,115 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2162,8 +2161,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F193"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <dimension ref="A1:F194"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="21" customWidth="1"/>
@@ -2220,7 +2219,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" ht="67.5" spans="1:6">
+    <row r="4" ht="72" spans="1:6">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -5193,7 +5192,7 @@
     <row r="189" ht="15" customHeight="1" spans="1:6">
       <c r="A189" s="1"/>
       <c r="B189" s="1">
-        <v>2601</v>
+        <v>2600</v>
       </c>
       <c r="C189" s="1"/>
       <c r="D189" s="1">
@@ -5206,23 +5205,25 @@
         <v>379</v>
       </c>
     </row>
-    <row r="190" spans="1:6">
-      <c r="B190">
-        <v>1155</v>
-      </c>
-      <c r="D190">
-        <v>1</v>
+    <row r="190" ht="15" customHeight="1" spans="1:6">
+      <c r="A190" s="1"/>
+      <c r="B190" s="1">
+        <v>2601</v>
+      </c>
+      <c r="C190" s="1"/>
+      <c r="D190" s="1">
+        <v>2</v>
       </c>
       <c r="E190" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="F190" t="s">
+      <c r="F190" s="1" t="s">
         <v>381</v>
       </c>
     </row>
     <row r="191" spans="1:6">
       <c r="B191">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="D191">
         <v>1</v>
@@ -5236,7 +5237,7 @@
     </row>
     <row r="192" spans="1:6">
       <c r="B192">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="D192">
         <v>1</v>
@@ -5250,7 +5251,7 @@
     </row>
     <row r="193" spans="2:6">
       <c r="B193">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="D193">
         <v>1</v>
@@ -5260,6 +5261,20 @@
       </c>
       <c r="F193" t="s">
         <v>387</v>
+      </c>
+    </row>
+    <row r="194" spans="2:6">
+      <c r="B194">
+        <v>1158</v>
+      </c>
+      <c r="D194">
+        <v>1</v>
+      </c>
+      <c r="E194" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="F194" t="s">
+        <v>389</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/DataTables/ResourceConfigTable.xlsx
+++ b/AAAGameData/DataTables/ResourceConfigTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="14855"/>
+    <workbookView windowWidth="28800" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -617,145 +617,145 @@
     <t>风暴法杖图标</t>
   </si>
   <si>
-    <t>Items/CardUnlock/100.png</t>
+    <t>Items/100.png</t>
   </si>
   <si>
     <t>卡牌-神圣庇护解锁物图标</t>
   </si>
   <si>
-    <t>Items/CardUnlock/101.png</t>
+    <t>Items/101.png</t>
   </si>
   <si>
     <t>卡牌-烈焰风暴解锁物图标</t>
   </si>
   <si>
-    <t>Items/CardUnlock/102.png</t>
+    <t>Items/102.png</t>
   </si>
   <si>
     <t>卡牌-时间回溯解锁物图标</t>
   </si>
   <si>
-    <t>Items/CardUnlock/103.png</t>
+    <t>Items/103.png</t>
   </si>
   <si>
     <t>卡牌-战争号角解锁物图标</t>
   </si>
   <si>
-    <t>Items/CardUnlock/104.png</t>
+    <t>Items/104.png</t>
   </si>
   <si>
     <t>卡牌-暗影突袭解锁物图标</t>
   </si>
   <si>
-    <t>Items/CardUnlock/105.png</t>
+    <t>Items/105.png</t>
   </si>
   <si>
     <t>卡牌-生命汲取解锁物图标</t>
   </si>
   <si>
-    <t>Items/CardUnlock/106.png</t>
+    <t>Items/106.png</t>
   </si>
   <si>
     <t>卡牌-冰霜新星解锁物图标</t>
   </si>
   <si>
-    <t>Items/CardUnlock/107.png</t>
+    <t>Items/107.png</t>
   </si>
   <si>
     <t>卡牌-狂暴解锁物图标</t>
   </si>
   <si>
-    <t>Items/CardUnlock/108.png</t>
+    <t>Items/108.png</t>
   </si>
   <si>
     <t>卡牌-群体治疗解锁物图标</t>
   </si>
   <si>
-    <t>Items/CardUnlock/109.png</t>
+    <t>Items/109.png</t>
   </si>
   <si>
     <t>卡牌-雷霆一击解锁物图标</t>
   </si>
   <si>
-    <t>Items/CardUnlock/110.png</t>
+    <t>Items/110.png</t>
   </si>
   <si>
     <t>卡牌-混乱诅咒解锁物图标</t>
   </si>
   <si>
-    <t>Items/CardUnlock/111.png</t>
+    <t>Items/111.png</t>
   </si>
   <si>
     <t>卡牌-不屈意志解锁物图标</t>
   </si>
   <si>
-    <t>Items/CardUnlock/112.png</t>
+    <t>Items/112.png</t>
   </si>
   <si>
     <t>卡牌-反伤之盾解锁物图标</t>
   </si>
   <si>
-    <t>Items/CardUnlock/113.png</t>
+    <t>Items/113.png</t>
   </si>
   <si>
     <t>卡牌-圣域防线解锁物图标</t>
   </si>
   <si>
-    <t>Items/CardUnlock/114.png</t>
+    <t>Items/114.png</t>
   </si>
   <si>
     <t>卡牌-护盾再生解锁物图标</t>
   </si>
   <si>
-    <t>Items/CardUnlock/115.png</t>
+    <t>Items/115.png</t>
   </si>
   <si>
     <t>卡牌-救赎之光解锁物图标</t>
   </si>
   <si>
-    <t>Items/CardUnlock/116.png</t>
+    <t>Items/116.png</t>
   </si>
   <si>
     <t>卡牌-血源强化解锁物图标</t>
   </si>
   <si>
-    <t>Items/CardUnlock/117.png</t>
+    <t>Items/117.png</t>
   </si>
   <si>
     <t>卡牌-吸血之刃解锁物图标</t>
   </si>
   <si>
-    <t>Items/CardUnlock/118.png</t>
+    <t>Items/118.png</t>
   </si>
   <si>
     <t>卡牌-灾厄之雷解锁物图标</t>
   </si>
   <si>
-    <t>Items/CardUnlock/119.png</t>
+    <t>Items/119.png</t>
   </si>
   <si>
     <t>卡牌-护甲破碎解锁物图标</t>
   </si>
   <si>
-    <t>Items/CardUnlock/120.png</t>
+    <t>Items/120.png</t>
   </si>
   <si>
     <t>卡牌-虚弱诅咒解锁物图标</t>
   </si>
   <si>
-    <t>Items/CardUnlock/121.png</t>
+    <t>Items/121.png</t>
   </si>
   <si>
     <t>卡牌-沉默之符解锁物图标</t>
   </si>
   <si>
-    <t>Items/CardUnlock/122.png</t>
+    <t>Items/122.png</t>
   </si>
   <si>
     <t>卡牌-嘲讽之声解锁物图标</t>
   </si>
   <si>
-    <t>Items/CardUnlock/123.png</t>
+    <t>Items/123.png</t>
   </si>
   <si>
     <t>卡牌-剧毒之雾解锁物图标</t>
@@ -2162,7 +2162,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F194"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="21" customWidth="1"/>
@@ -2219,7 +2219,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" ht="72" spans="1:6">
+    <row r="4" ht="67.5" spans="1:6">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>

--- a/AAAGameData/DataTables/ResourceConfigTable.xlsx
+++ b/AAAGameData/DataTables/ResourceConfigTable.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="556">
   <si>
     <t>#</t>
   </si>
@@ -56,10 +56,10 @@
     <t>资源ID</t>
   </si>
   <si>
-    <t>1：Assets/AAAGame/Sprites/2：Assets/AAAGame/Prefabs/3：Assets/AAAGame/Prefabs/Entity/4：Assets/AAAGame/Materials/5：Assets/AAAGame/Textures/6：Assets/AAAGame/Config/</t>
-  </si>
-  <si>
-    <t>资源类型：1 = Sprite（图片）2 = Prefab（预制体）3 = Effect（特效）4 = Material（材质）5 = Texture（纹理）6 = ScriptableObject（配置文件）</t>
+    <t>1：Assets/AAAGame/Sprites/2：Assets/AAAGame/Prefabs/3：Assets/AAAGame/Prefabs/Entity/4：Assets/AAAGame/Materials/5：Assets/AAAGame/Textures/6：Assets/AAAGame/Config/7：Assets/AAAGame/Audio/</t>
+  </si>
+  <si>
+    <t>资源类型：1 = Sprite（图片）2 = Prefab（预制体）3 = Effect（特效）4 = Material（材质）5 = Texture（纹理）6 = ScriptableObject（配置文件）7 = Audio（音频）</t>
   </si>
   <si>
     <t>资源路径</t>
@@ -1197,6 +1197,504 @@
   </si>
   <si>
     <t>德鲁伊头像</t>
+  </si>
+  <si>
+    <t>BGM/游戏启动主菜单BGM</t>
+  </si>
+  <si>
+    <t>游戏启动/主菜单</t>
+  </si>
+  <si>
+    <t>BGM/基地场景BGM</t>
+  </si>
+  <si>
+    <t>基地场景</t>
+  </si>
+  <si>
+    <t>BGM/大世界探索BGM</t>
+  </si>
+  <si>
+    <t>大世界探索</t>
+  </si>
+  <si>
+    <t>BGM/教程场景BGM</t>
+  </si>
+  <si>
+    <t>教程场景</t>
+  </si>
+  <si>
+    <t>BGM/天宫副本BGM</t>
+  </si>
+  <si>
+    <t>天宫副本</t>
+  </si>
+  <si>
+    <t>BGM/赫尔海姆副本BGM</t>
+  </si>
+  <si>
+    <t>赫尔海姆副本</t>
+  </si>
+  <si>
+    <t>BGM/高天原副本BGM</t>
+  </si>
+  <si>
+    <t>高天原副本</t>
+  </si>
+  <si>
+    <t>BGM/奥林匹斯副本BGM</t>
+  </si>
+  <si>
+    <t>奥林匹斯副本</t>
+  </si>
+  <si>
+    <t>BGM/巴比伦副本BGM</t>
+  </si>
+  <si>
+    <t>巴比伦副本</t>
+  </si>
+  <si>
+    <t>BGM/阿瓦隆副本BGM</t>
+  </si>
+  <si>
+    <t>阿瓦隆副本</t>
+  </si>
+  <si>
+    <t>BGM/深渊副本BGM</t>
+  </si>
+  <si>
+    <t>深渊副本</t>
+  </si>
+  <si>
+    <t>BGM/普通敌人战斗BGM</t>
+  </si>
+  <si>
+    <t>普通敌人战斗</t>
+  </si>
+  <si>
+    <t>BGM/精英敌人战斗BGM</t>
+  </si>
+  <si>
+    <t>精英敌人战斗</t>
+  </si>
+  <si>
+    <t>BGM/Boss战斗BGM</t>
+  </si>
+  <si>
+    <t>Boss战斗</t>
+  </si>
+  <si>
+    <t>BGM/战斗结算BGM</t>
+  </si>
+  <si>
+    <t>战斗结算</t>
+  </si>
+  <si>
+    <t>BGM/出战预设BGM</t>
+  </si>
+  <si>
+    <t>出战预设</t>
+  </si>
+  <si>
+    <t>BGM/背包界面BGM</t>
+  </si>
+  <si>
+    <t>背包界面</t>
+  </si>
+  <si>
+    <t>BGM/商城界面BGM</t>
+  </si>
+  <si>
+    <t>商城界面</t>
+  </si>
+  <si>
+    <t>BGM/升级界面BGM</t>
+  </si>
+  <si>
+    <t>升级界面</t>
+  </si>
+  <si>
+    <t>SFX/UI/按钮点击音效</t>
+  </si>
+  <si>
+    <t>按钮点击</t>
+  </si>
+  <si>
+    <t>SFX/UI/界面打开音效</t>
+  </si>
+  <si>
+    <t>界面打开</t>
+  </si>
+  <si>
+    <t>SFX/UI/界面关闭音效</t>
+  </si>
+  <si>
+    <t>界面关闭</t>
+  </si>
+  <si>
+    <t>SFX/UI/按钮悬停音效</t>
+  </si>
+  <si>
+    <t>按钮悬停</t>
+  </si>
+  <si>
+    <t>SFX/UI/标签页切换音效</t>
+  </si>
+  <si>
+    <t>标签页切换</t>
+  </si>
+  <si>
+    <t>SFX/UI/确认按钮音效</t>
+  </si>
+  <si>
+    <t>确认按钮</t>
+  </si>
+  <si>
+    <t>SFX/UI/取消按钮音效</t>
+  </si>
+  <si>
+    <t>取消按钮</t>
+  </si>
+  <si>
+    <t>SFX/UI/错误音效</t>
+  </si>
+  <si>
+    <t>错误音效</t>
+  </si>
+  <si>
+    <t>SFX/UI/成功音效</t>
+  </si>
+  <si>
+    <t>成功音效</t>
+  </si>
+  <si>
+    <t>SFX/UI/解锁音效</t>
+  </si>
+  <si>
+    <t>解锁音效</t>
+  </si>
+  <si>
+    <t>SFX/UI/通知提示音音效</t>
+  </si>
+  <si>
+    <t>通知提示音</t>
+  </si>
+  <si>
+    <t>SFX/UI/货币获得音效</t>
+  </si>
+  <si>
+    <t>货币获得</t>
+  </si>
+  <si>
+    <t>SFX/Combat/棋子选中音效</t>
+  </si>
+  <si>
+    <t>棋子选中</t>
+  </si>
+  <si>
+    <t>SFX/Combat/移动开始音效</t>
+  </si>
+  <si>
+    <t>移动开始</t>
+  </si>
+  <si>
+    <t>SFX/Combat/移动停止音效</t>
+  </si>
+  <si>
+    <t>移动停止</t>
+  </si>
+  <si>
+    <t>SFX/Combat/攻击蓄力音效</t>
+  </si>
+  <si>
+    <t>攻击蓄力</t>
+  </si>
+  <si>
+    <t>SFX/Combat/攻击释放音效</t>
+  </si>
+  <si>
+    <t>攻击释放</t>
+  </si>
+  <si>
+    <t>SFX/Combat/攻击破风音效</t>
+  </si>
+  <si>
+    <t>攻击破风</t>
+  </si>
+  <si>
+    <t>SFX/Combat/技能施放音效</t>
+  </si>
+  <si>
+    <t>技能施放</t>
+  </si>
+  <si>
+    <t>SFX/Combat/Buff应用音效</t>
+  </si>
+  <si>
+    <t>Buff应用</t>
+  </si>
+  <si>
+    <t>SFX/Combat/Debuff应用音效</t>
+  </si>
+  <si>
+    <t>Debuff应用</t>
+  </si>
+  <si>
+    <t>SFX/Combat/轻度伤害音效</t>
+  </si>
+  <si>
+    <t>轻度伤害</t>
+  </si>
+  <si>
+    <t>SFX/Combat/普通伤害音效</t>
+  </si>
+  <si>
+    <t>普通伤害</t>
+  </si>
+  <si>
+    <t>SFX/Combat/重度伤害音效</t>
+  </si>
+  <si>
+    <t>重度伤害</t>
+  </si>
+  <si>
+    <t>SFX/Combat/暴击伤害音效</t>
+  </si>
+  <si>
+    <t>暴击伤害</t>
+  </si>
+  <si>
+    <t>SFX/Combat/闪避格挡音效</t>
+  </si>
+  <si>
+    <t>闪避/格挡</t>
+  </si>
+  <si>
+    <t>SFX/Combat/治疗音效</t>
+  </si>
+  <si>
+    <t>治疗</t>
+  </si>
+  <si>
+    <t>SFX/Combat/护盾获得音效</t>
+  </si>
+  <si>
+    <t>护盾获得</t>
+  </si>
+  <si>
+    <t>SFX/Combat/死亡音效</t>
+  </si>
+  <si>
+    <t>死亡</t>
+  </si>
+  <si>
+    <t>SFX/Combat/回合开始音效</t>
+  </si>
+  <si>
+    <t>回合开始</t>
+  </si>
+  <si>
+    <t>SFX/Combat/回合结束音效</t>
+  </si>
+  <si>
+    <t>回合结束</t>
+  </si>
+  <si>
+    <t>SFX/Combat/战斗开始音效</t>
+  </si>
+  <si>
+    <t>战斗开始</t>
+  </si>
+  <si>
+    <t>SFX/Combat/Boss出现音效</t>
+  </si>
+  <si>
+    <t>Boss出现</t>
+  </si>
+  <si>
+    <t>SFX/Combat/Boss技能警告音效</t>
+  </si>
+  <si>
+    <t>Boss技能警告</t>
+  </si>
+  <si>
+    <t>SFX/Combat/战斗胜利音效</t>
+  </si>
+  <si>
+    <t>战斗胜利</t>
+  </si>
+  <si>
+    <t>SFX/Combat/战斗失败音效</t>
+  </si>
+  <si>
+    <t>战斗失败</t>
+  </si>
+  <si>
+    <t>SFX/Explore/脚步声音效</t>
+  </si>
+  <si>
+    <t>脚步声</t>
+  </si>
+  <si>
+    <t>SFX/Explore/物品捡起音效</t>
+  </si>
+  <si>
+    <t>物品捡起</t>
+  </si>
+  <si>
+    <t>SFX/Explore/宝箱打开音效</t>
+  </si>
+  <si>
+    <t>宝箱打开</t>
+  </si>
+  <si>
+    <t>SFX/Explore/门打开音效</t>
+  </si>
+  <si>
+    <t>门打开</t>
+  </si>
+  <si>
+    <t>SFX/Explore/门关闭音效</t>
+  </si>
+  <si>
+    <t>门关闭</t>
+  </si>
+  <si>
+    <t>SFX/Explore/NPC对话音效</t>
+  </si>
+  <si>
+    <t>NPC对话</t>
+  </si>
+  <si>
+    <t>SFX/Explore/任务接受音效</t>
+  </si>
+  <si>
+    <t>任务接受</t>
+  </si>
+  <si>
+    <t>SFX/Explore/任务完成音效</t>
+  </si>
+  <si>
+    <t>任务完成</t>
+  </si>
+  <si>
+    <t>SFX/Ambient/风声音效</t>
+  </si>
+  <si>
+    <t>风声</t>
+  </si>
+  <si>
+    <t>SFX/Ambient/雷声音效</t>
+  </si>
+  <si>
+    <t>雷声</t>
+  </si>
+  <si>
+    <t>SFX/Ambient/流水声音效</t>
+  </si>
+  <si>
+    <t>流水声</t>
+  </si>
+  <si>
+    <t>SFX/Ambient/火焰声音效</t>
+  </si>
+  <si>
+    <t>火焰声</t>
+  </si>
+  <si>
+    <t>SFX/Ambient/阴冷氛围音效</t>
+  </si>
+  <si>
+    <t>阴冷氛围</t>
+  </si>
+  <si>
+    <t>SFX/Ambient/诡异低语音效</t>
+  </si>
+  <si>
+    <t>诡异低语</t>
+  </si>
+  <si>
+    <t>SFX/Explore/传送进入音效</t>
+  </si>
+  <si>
+    <t>传送进入</t>
+  </si>
+  <si>
+    <t>SFX/Explore/传送离开音效</t>
+  </si>
+  <si>
+    <t>传送离开</t>
+  </si>
+  <si>
+    <t>SFX/UI/场景加载音效</t>
+  </si>
+  <si>
+    <t>场景加载</t>
+  </si>
+  <si>
+    <t>SFX/Explore/传送准备音效</t>
+  </si>
+  <si>
+    <t>传送准备</t>
+  </si>
+  <si>
+    <t>SFX/Reward/成就解锁音效</t>
+  </si>
+  <si>
+    <t>成就解锁</t>
+  </si>
+  <si>
+    <t>SFX/Reward/等级提升音效</t>
+  </si>
+  <si>
+    <t>等级提升</t>
+  </si>
+  <si>
+    <t>SFX/Reward/品质提升音效</t>
+  </si>
+  <si>
+    <t>品质提升</t>
+  </si>
+  <si>
+    <t>SFX/Reward/额外奖励音效</t>
+  </si>
+  <si>
+    <t>额外奖励</t>
+  </si>
+  <si>
+    <t>SFX/Reward/传说物品音效</t>
+  </si>
+  <si>
+    <t>传说物品</t>
+  </si>
+  <si>
+    <t>SFX/UI/金币捡起音效</t>
+  </si>
+  <si>
+    <t>金币捡起</t>
+  </si>
+  <si>
+    <t>SFX/UI/宝石捡起音效</t>
+  </si>
+  <si>
+    <t>宝石捡起</t>
+  </si>
+  <si>
+    <t>SFX/UI/金币消耗音效</t>
+  </si>
+  <si>
+    <t>金币消耗</t>
+  </si>
+  <si>
+    <t>SFX/UI/宝石消耗音效</t>
+  </si>
+  <si>
+    <t>宝石消耗</t>
+  </si>
+  <si>
+    <t>SFX/UI/交易音效</t>
+  </si>
+  <si>
+    <t>交易音效</t>
   </si>
 </sst>
 </file>
@@ -1209,7 +1707,14 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1665,31 +2170,28 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1698,115 +2200,118 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2161,7 +2666,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F194"/>
+  <dimension ref="A1:F277"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -2219,7 +2724,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" ht="67.5" spans="1:6">
+    <row r="4" ht="81" spans="1:6">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -5221,60 +5726,1396 @@
         <v>381</v>
       </c>
     </row>
-    <row r="191" spans="1:6">
-      <c r="B191">
+    <row r="191" ht="15" customHeight="1" spans="1:6">
+      <c r="A191" s="1"/>
+      <c r="B191" s="1">
         <v>1155</v>
       </c>
-      <c r="D191">
+      <c r="C191" s="1"/>
+      <c r="D191" s="1">
         <v>1</v>
       </c>
       <c r="E191" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="F191" t="s">
+      <c r="F191" s="1" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="192" spans="1:6">
-      <c r="B192">
+    <row r="192" ht="15" customHeight="1" spans="1:6">
+      <c r="A192" s="1"/>
+      <c r="B192" s="1">
         <v>1156</v>
       </c>
-      <c r="D192">
+      <c r="C192" s="1"/>
+      <c r="D192" s="1">
         <v>1</v>
       </c>
       <c r="E192" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="F192" t="s">
+      <c r="F192" s="1" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="193" spans="2:6">
-      <c r="B193">
+    <row r="193" ht="15" customHeight="1" spans="1:6">
+      <c r="A193" s="1"/>
+      <c r="B193" s="1">
         <v>1157</v>
       </c>
-      <c r="D193">
+      <c r="C193" s="1"/>
+      <c r="D193" s="1">
         <v>1</v>
       </c>
       <c r="E193" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="F193" t="s">
+      <c r="F193" s="1" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="194" spans="2:6">
-      <c r="B194">
+    <row r="194" ht="15" customHeight="1" spans="1:6">
+      <c r="A194" s="1"/>
+      <c r="B194" s="1">
         <v>1158</v>
       </c>
-      <c r="D194">
+      <c r="C194" s="1"/>
+      <c r="D194" s="1">
         <v>1</v>
       </c>
       <c r="E194" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="F194" t="s">
+      <c r="F194" s="1" t="s">
         <v>389</v>
+      </c>
+    </row>
+    <row r="195" ht="15" customHeight="1" spans="1:6">
+      <c r="A195" s="1"/>
+      <c r="B195" s="1">
+        <v>60001</v>
+      </c>
+      <c r="C195" s="1"/>
+      <c r="D195" s="1">
+        <v>7</v>
+      </c>
+      <c r="E195" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="F195" s="1" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="196" ht="15" customHeight="1" spans="1:6">
+      <c r="A196" s="1"/>
+      <c r="B196" s="1">
+        <v>60002</v>
+      </c>
+      <c r="C196" s="1"/>
+      <c r="D196" s="1">
+        <v>7</v>
+      </c>
+      <c r="E196" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="F196" s="1" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="197" ht="15" customHeight="1" spans="1:6">
+      <c r="A197" s="1"/>
+      <c r="B197" s="1">
+        <v>60003</v>
+      </c>
+      <c r="C197" s="1"/>
+      <c r="D197" s="1">
+        <v>7</v>
+      </c>
+      <c r="E197" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="F197" s="1" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="198" ht="15" customHeight="1" spans="1:6">
+      <c r="A198" s="1"/>
+      <c r="B198" s="1">
+        <v>60004</v>
+      </c>
+      <c r="C198" s="1"/>
+      <c r="D198" s="1">
+        <v>7</v>
+      </c>
+      <c r="E198" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="F198" s="1" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="199" ht="15" customHeight="1" spans="1:6">
+      <c r="A199" s="1"/>
+      <c r="B199" s="1">
+        <v>60005</v>
+      </c>
+      <c r="C199" s="1"/>
+      <c r="D199" s="1">
+        <v>7</v>
+      </c>
+      <c r="E199" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="F199" s="1" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="200" ht="15" customHeight="1" spans="1:6">
+      <c r="A200" s="1"/>
+      <c r="B200" s="1">
+        <v>60006</v>
+      </c>
+      <c r="C200" s="1"/>
+      <c r="D200" s="1">
+        <v>7</v>
+      </c>
+      <c r="E200" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="F200" s="1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="201" ht="15" customHeight="1" spans="1:6">
+      <c r="A201" s="1"/>
+      <c r="B201" s="1">
+        <v>60007</v>
+      </c>
+      <c r="C201" s="1"/>
+      <c r="D201" s="1">
+        <v>7</v>
+      </c>
+      <c r="E201" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="F201" s="1" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="202" ht="15" customHeight="1" spans="1:6">
+      <c r="A202" s="1"/>
+      <c r="B202" s="1">
+        <v>60008</v>
+      </c>
+      <c r="C202" s="1"/>
+      <c r="D202" s="1">
+        <v>7</v>
+      </c>
+      <c r="E202" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="F202" s="1" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="203" ht="15" customHeight="1" spans="1:6">
+      <c r="A203" s="1"/>
+      <c r="B203" s="1">
+        <v>60009</v>
+      </c>
+      <c r="C203" s="1"/>
+      <c r="D203" s="1">
+        <v>7</v>
+      </c>
+      <c r="E203" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="F203" s="1" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="204" ht="15" customHeight="1" spans="1:6">
+      <c r="A204" s="1"/>
+      <c r="B204" s="1">
+        <v>60010</v>
+      </c>
+      <c r="C204" s="1"/>
+      <c r="D204" s="1">
+        <v>7</v>
+      </c>
+      <c r="E204" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="F204" s="1" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="205" ht="15" customHeight="1" spans="1:6">
+      <c r="A205" s="1"/>
+      <c r="B205" s="1">
+        <v>60011</v>
+      </c>
+      <c r="C205" s="1"/>
+      <c r="D205" s="1">
+        <v>7</v>
+      </c>
+      <c r="E205" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="F205" s="1" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="206" ht="15" customHeight="1" spans="1:6">
+      <c r="A206" s="1"/>
+      <c r="B206" s="1">
+        <v>60012</v>
+      </c>
+      <c r="C206" s="1"/>
+      <c r="D206" s="1">
+        <v>7</v>
+      </c>
+      <c r="E206" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="F206" s="1" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="207" ht="15" customHeight="1" spans="1:6">
+      <c r="A207" s="1"/>
+      <c r="B207" s="1">
+        <v>60013</v>
+      </c>
+      <c r="C207" s="1"/>
+      <c r="D207" s="1">
+        <v>7</v>
+      </c>
+      <c r="E207" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="F207" s="1" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="208" ht="15" customHeight="1" spans="1:6">
+      <c r="A208" s="1"/>
+      <c r="B208" s="1">
+        <v>60014</v>
+      </c>
+      <c r="C208" s="1"/>
+      <c r="D208" s="1">
+        <v>7</v>
+      </c>
+      <c r="E208" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="F208" s="1" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="209" ht="15" customHeight="1" spans="1:6">
+      <c r="A209" s="1"/>
+      <c r="B209" s="1">
+        <v>60015</v>
+      </c>
+      <c r="C209" s="1"/>
+      <c r="D209" s="1">
+        <v>7</v>
+      </c>
+      <c r="E209" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="F209" s="1" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="210" ht="15" customHeight="1" spans="1:6">
+      <c r="A210" s="1"/>
+      <c r="B210" s="1">
+        <v>60016</v>
+      </c>
+      <c r="C210" s="1"/>
+      <c r="D210" s="1">
+        <v>7</v>
+      </c>
+      <c r="E210" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="F210" s="1" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="211" ht="15" customHeight="1" spans="1:6">
+      <c r="A211" s="1"/>
+      <c r="B211" s="1">
+        <v>60017</v>
+      </c>
+      <c r="C211" s="1"/>
+      <c r="D211" s="1">
+        <v>7</v>
+      </c>
+      <c r="E211" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="F211" s="1" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="212" ht="15" customHeight="1" spans="1:6">
+      <c r="A212" s="1"/>
+      <c r="B212" s="1">
+        <v>60018</v>
+      </c>
+      <c r="C212" s="1"/>
+      <c r="D212" s="1">
+        <v>7</v>
+      </c>
+      <c r="E212" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="F212" s="1" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="213" ht="15" customHeight="1" spans="1:6">
+      <c r="A213" s="1"/>
+      <c r="B213" s="1">
+        <v>60019</v>
+      </c>
+      <c r="C213" s="1"/>
+      <c r="D213" s="1">
+        <v>7</v>
+      </c>
+      <c r="E213" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="F213" s="1" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="214" ht="15" customHeight="1" spans="1:6">
+      <c r="A214" s="1"/>
+      <c r="B214" s="1">
+        <v>60020</v>
+      </c>
+      <c r="C214" s="1"/>
+      <c r="D214" s="1">
+        <v>7</v>
+      </c>
+      <c r="E214" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="F214" s="1" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="215" ht="15" customHeight="1" spans="1:6">
+      <c r="A215" s="1"/>
+      <c r="B215" s="1">
+        <v>60021</v>
+      </c>
+      <c r="C215" s="1"/>
+      <c r="D215" s="1">
+        <v>7</v>
+      </c>
+      <c r="E215" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="F215" s="1" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="216" ht="15" customHeight="1" spans="1:6">
+      <c r="A216" s="1"/>
+      <c r="B216" s="1">
+        <v>60022</v>
+      </c>
+      <c r="C216" s="1"/>
+      <c r="D216" s="1">
+        <v>7</v>
+      </c>
+      <c r="E216" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="F216" s="1" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="217" ht="15" customHeight="1" spans="1:6">
+      <c r="A217" s="1"/>
+      <c r="B217" s="1">
+        <v>60023</v>
+      </c>
+      <c r="C217" s="1"/>
+      <c r="D217" s="1">
+        <v>7</v>
+      </c>
+      <c r="E217" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="F217" s="1" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="218" ht="15" customHeight="1" spans="1:6">
+      <c r="A218" s="1"/>
+      <c r="B218" s="1">
+        <v>60024</v>
+      </c>
+      <c r="C218" s="1"/>
+      <c r="D218" s="1">
+        <v>7</v>
+      </c>
+      <c r="E218" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="F218" s="1" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="219" ht="15" customHeight="1" spans="1:6">
+      <c r="A219" s="1"/>
+      <c r="B219" s="1">
+        <v>60025</v>
+      </c>
+      <c r="C219" s="1"/>
+      <c r="D219" s="1">
+        <v>7</v>
+      </c>
+      <c r="E219" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="F219" s="1" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="220" ht="15" customHeight="1" spans="1:6">
+      <c r="A220" s="1"/>
+      <c r="B220" s="1">
+        <v>60026</v>
+      </c>
+      <c r="C220" s="1"/>
+      <c r="D220" s="1">
+        <v>7</v>
+      </c>
+      <c r="E220" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="F220" s="1" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="221" ht="15" customHeight="1" spans="1:6">
+      <c r="A221" s="1"/>
+      <c r="B221" s="1">
+        <v>60027</v>
+      </c>
+      <c r="C221" s="1"/>
+      <c r="D221" s="1">
+        <v>7</v>
+      </c>
+      <c r="E221" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="F221" s="1" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="222" ht="15" customHeight="1" spans="1:6">
+      <c r="A222" s="1"/>
+      <c r="B222" s="1">
+        <v>60028</v>
+      </c>
+      <c r="C222" s="1"/>
+      <c r="D222" s="1">
+        <v>7</v>
+      </c>
+      <c r="E222" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="F222" s="1" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="223" ht="15" customHeight="1" spans="1:6">
+      <c r="A223" s="1"/>
+      <c r="B223" s="1">
+        <v>60029</v>
+      </c>
+      <c r="C223" s="1"/>
+      <c r="D223" s="1">
+        <v>7</v>
+      </c>
+      <c r="E223" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="F223" s="1" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="224" ht="15" customHeight="1" spans="1:6">
+      <c r="A224" s="1"/>
+      <c r="B224" s="1">
+        <v>60030</v>
+      </c>
+      <c r="C224" s="1"/>
+      <c r="D224" s="1">
+        <v>7</v>
+      </c>
+      <c r="E224" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="F224" s="1" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="225" ht="15" customHeight="1" spans="1:6">
+      <c r="A225" s="1"/>
+      <c r="B225" s="1">
+        <v>60031</v>
+      </c>
+      <c r="C225" s="1"/>
+      <c r="D225" s="1">
+        <v>7</v>
+      </c>
+      <c r="E225" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="F225" s="1" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="226" ht="15" customHeight="1" spans="1:6">
+      <c r="A226" s="1"/>
+      <c r="B226" s="1">
+        <v>60032</v>
+      </c>
+      <c r="C226" s="1"/>
+      <c r="D226" s="1">
+        <v>7</v>
+      </c>
+      <c r="E226" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="F226" s="1" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="227" ht="15" customHeight="1" spans="1:6">
+      <c r="A227" s="1"/>
+      <c r="B227" s="1">
+        <v>60033</v>
+      </c>
+      <c r="C227" s="1"/>
+      <c r="D227" s="1">
+        <v>7</v>
+      </c>
+      <c r="E227" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="F227" s="1" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="228" ht="15" customHeight="1" spans="1:6">
+      <c r="A228" s="1"/>
+      <c r="B228" s="1">
+        <v>60034</v>
+      </c>
+      <c r="C228" s="1"/>
+      <c r="D228" s="1">
+        <v>7</v>
+      </c>
+      <c r="E228" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="F228" s="1" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="229" ht="15" customHeight="1" spans="1:6">
+      <c r="A229" s="1"/>
+      <c r="B229" s="1">
+        <v>60035</v>
+      </c>
+      <c r="C229" s="1"/>
+      <c r="D229" s="1">
+        <v>7</v>
+      </c>
+      <c r="E229" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="F229" s="1" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="230" ht="15" customHeight="1" spans="1:6">
+      <c r="A230" s="1"/>
+      <c r="B230" s="1">
+        <v>60036</v>
+      </c>
+      <c r="C230" s="1"/>
+      <c r="D230" s="1">
+        <v>7</v>
+      </c>
+      <c r="E230" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="F230" s="1" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="231" ht="15" customHeight="1" spans="1:6">
+      <c r="A231" s="1"/>
+      <c r="B231" s="1">
+        <v>60037</v>
+      </c>
+      <c r="C231" s="1"/>
+      <c r="D231" s="1">
+        <v>7</v>
+      </c>
+      <c r="E231" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="F231" s="1" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="232" ht="15" customHeight="1" spans="1:6">
+      <c r="A232" s="1"/>
+      <c r="B232" s="1">
+        <v>60038</v>
+      </c>
+      <c r="C232" s="1"/>
+      <c r="D232" s="1">
+        <v>7</v>
+      </c>
+      <c r="E232" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="F232" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="233" ht="15" customHeight="1" spans="1:6">
+      <c r="A233" s="1"/>
+      <c r="B233" s="1">
+        <v>60039</v>
+      </c>
+      <c r="C233" s="1"/>
+      <c r="D233" s="1">
+        <v>7</v>
+      </c>
+      <c r="E233" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="F233" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="234" ht="15" customHeight="1" spans="1:6">
+      <c r="A234" s="1"/>
+      <c r="B234" s="1">
+        <v>60040</v>
+      </c>
+      <c r="C234" s="1"/>
+      <c r="D234" s="1">
+        <v>7</v>
+      </c>
+      <c r="E234" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="F234" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="235" ht="15" customHeight="1" spans="1:6">
+      <c r="A235" s="1"/>
+      <c r="B235" s="1">
+        <v>60041</v>
+      </c>
+      <c r="C235" s="1"/>
+      <c r="D235" s="1">
+        <v>7</v>
+      </c>
+      <c r="E235" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="F235" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="236" ht="15" customHeight="1" spans="1:6">
+      <c r="A236" s="1"/>
+      <c r="B236" s="1">
+        <v>60042</v>
+      </c>
+      <c r="C236" s="1"/>
+      <c r="D236" s="1">
+        <v>7</v>
+      </c>
+      <c r="E236" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="F236" s="1" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="237" ht="15" customHeight="1" spans="1:6">
+      <c r="A237" s="1"/>
+      <c r="B237" s="1">
+        <v>60043</v>
+      </c>
+      <c r="C237" s="1"/>
+      <c r="D237" s="1">
+        <v>7</v>
+      </c>
+      <c r="E237" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="F237" s="1" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="238" ht="15" customHeight="1" spans="1:6">
+      <c r="A238" s="1"/>
+      <c r="B238" s="1">
+        <v>60044</v>
+      </c>
+      <c r="C238" s="1"/>
+      <c r="D238" s="1">
+        <v>7</v>
+      </c>
+      <c r="E238" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="F238" s="1" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="239" ht="15" customHeight="1" spans="1:6">
+      <c r="A239" s="1"/>
+      <c r="B239" s="1">
+        <v>60045</v>
+      </c>
+      <c r="C239" s="1"/>
+      <c r="D239" s="1">
+        <v>7</v>
+      </c>
+      <c r="E239" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="F239" s="1" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="240" ht="15" customHeight="1" spans="1:6">
+      <c r="A240" s="1"/>
+      <c r="B240" s="1">
+        <v>60046</v>
+      </c>
+      <c r="C240" s="1"/>
+      <c r="D240" s="1">
+        <v>7</v>
+      </c>
+      <c r="E240" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="F240" s="1" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="241" ht="15" customHeight="1" spans="1:6">
+      <c r="A241" s="1"/>
+      <c r="B241" s="1">
+        <v>60047</v>
+      </c>
+      <c r="C241" s="1"/>
+      <c r="D241" s="1">
+        <v>7</v>
+      </c>
+      <c r="E241" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="F241" s="1" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="242" ht="15" customHeight="1" spans="1:6">
+      <c r="A242" s="1"/>
+      <c r="B242" s="1">
+        <v>60048</v>
+      </c>
+      <c r="C242" s="1"/>
+      <c r="D242" s="1">
+        <v>7</v>
+      </c>
+      <c r="E242" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="F242" s="1" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="243" ht="15" customHeight="1" spans="1:6">
+      <c r="A243" s="1"/>
+      <c r="B243" s="1">
+        <v>60049</v>
+      </c>
+      <c r="C243" s="1"/>
+      <c r="D243" s="1">
+        <v>7</v>
+      </c>
+      <c r="E243" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="F243" s="1" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="244" ht="15" customHeight="1" spans="1:6">
+      <c r="A244" s="1"/>
+      <c r="B244" s="1">
+        <v>60050</v>
+      </c>
+      <c r="C244" s="1"/>
+      <c r="D244" s="1">
+        <v>7</v>
+      </c>
+      <c r="E244" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="F244" s="1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="245" ht="15" customHeight="1" spans="1:6">
+      <c r="A245" s="1"/>
+      <c r="B245" s="1">
+        <v>60051</v>
+      </c>
+      <c r="C245" s="1"/>
+      <c r="D245" s="1">
+        <v>7</v>
+      </c>
+      <c r="E245" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="F245" s="1" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="246" ht="15" customHeight="1" spans="1:6">
+      <c r="A246" s="1"/>
+      <c r="B246" s="1">
+        <v>60052</v>
+      </c>
+      <c r="C246" s="1"/>
+      <c r="D246" s="1">
+        <v>7</v>
+      </c>
+      <c r="E246" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="F246" s="1" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="247" ht="15" customHeight="1" spans="1:6">
+      <c r="A247" s="1"/>
+      <c r="B247" s="1">
+        <v>60053</v>
+      </c>
+      <c r="C247" s="1"/>
+      <c r="D247" s="1">
+        <v>7</v>
+      </c>
+      <c r="E247" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="F247" s="1" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="248" ht="15" customHeight="1" spans="1:6">
+      <c r="A248" s="1"/>
+      <c r="B248" s="1">
+        <v>60054</v>
+      </c>
+      <c r="C248" s="1"/>
+      <c r="D248" s="1">
+        <v>7</v>
+      </c>
+      <c r="E248" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="F248" s="1" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="249" ht="15" customHeight="1" spans="1:6">
+      <c r="A249" s="1"/>
+      <c r="B249" s="1">
+        <v>60055</v>
+      </c>
+      <c r="C249" s="1"/>
+      <c r="D249" s="1">
+        <v>7</v>
+      </c>
+      <c r="E249" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="F249" s="1" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="250" ht="15" customHeight="1" spans="1:6">
+      <c r="A250" s="1"/>
+      <c r="B250" s="1">
+        <v>60056</v>
+      </c>
+      <c r="C250" s="1"/>
+      <c r="D250" s="1">
+        <v>7</v>
+      </c>
+      <c r="E250" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="F250" s="1" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="251" ht="15" customHeight="1" spans="1:6">
+      <c r="A251" s="1"/>
+      <c r="B251" s="1">
+        <v>60057</v>
+      </c>
+      <c r="C251" s="1"/>
+      <c r="D251" s="1">
+        <v>7</v>
+      </c>
+      <c r="E251" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="F251" s="1" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="252" ht="15" customHeight="1" spans="1:6">
+      <c r="A252" s="1"/>
+      <c r="B252" s="1">
+        <v>60058</v>
+      </c>
+      <c r="C252" s="1"/>
+      <c r="D252" s="1">
+        <v>7</v>
+      </c>
+      <c r="E252" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="F252" s="1" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="253" ht="15" customHeight="1" spans="1:6">
+      <c r="A253" s="1"/>
+      <c r="B253" s="1">
+        <v>60059</v>
+      </c>
+      <c r="C253" s="1"/>
+      <c r="D253" s="1">
+        <v>7</v>
+      </c>
+      <c r="E253" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="F253" s="1" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="254" ht="15" customHeight="1" spans="1:6">
+      <c r="A254" s="1"/>
+      <c r="B254" s="1">
+        <v>60060</v>
+      </c>
+      <c r="C254" s="1"/>
+      <c r="D254" s="1">
+        <v>7</v>
+      </c>
+      <c r="E254" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="F254" s="1" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="255" ht="15" customHeight="1" spans="1:6">
+      <c r="A255" s="1"/>
+      <c r="B255" s="1">
+        <v>60061</v>
+      </c>
+      <c r="C255" s="1"/>
+      <c r="D255" s="1">
+        <v>7</v>
+      </c>
+      <c r="E255" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="F255" s="1" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="256" ht="15" customHeight="1" spans="1:6">
+      <c r="A256" s="1"/>
+      <c r="B256" s="1">
+        <v>60062</v>
+      </c>
+      <c r="C256" s="1"/>
+      <c r="D256" s="1">
+        <v>7</v>
+      </c>
+      <c r="E256" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="F256" s="1" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="257" ht="15" customHeight="1" spans="1:6">
+      <c r="A257" s="1"/>
+      <c r="B257" s="1">
+        <v>60063</v>
+      </c>
+      <c r="C257" s="1"/>
+      <c r="D257" s="1">
+        <v>7</v>
+      </c>
+      <c r="E257" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="F257" s="1" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="258" ht="15" customHeight="1" spans="1:6">
+      <c r="A258" s="1"/>
+      <c r="B258" s="1">
+        <v>60064</v>
+      </c>
+      <c r="C258" s="1"/>
+      <c r="D258" s="1">
+        <v>7</v>
+      </c>
+      <c r="E258" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="F258" s="1" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="259" ht="15" customHeight="1" spans="1:6">
+      <c r="A259" s="1"/>
+      <c r="B259" s="1">
+        <v>60065</v>
+      </c>
+      <c r="C259" s="1"/>
+      <c r="D259" s="1">
+        <v>7</v>
+      </c>
+      <c r="E259" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="F259" s="1" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="260" ht="15" customHeight="1" spans="1:6">
+      <c r="A260" s="1"/>
+      <c r="B260" s="1">
+        <v>60066</v>
+      </c>
+      <c r="C260" s="1"/>
+      <c r="D260" s="1">
+        <v>7</v>
+      </c>
+      <c r="E260" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="F260" s="1" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="261" ht="15" customHeight="1" spans="1:6">
+      <c r="A261" s="1"/>
+      <c r="B261" s="1">
+        <v>60067</v>
+      </c>
+      <c r="C261" s="1"/>
+      <c r="D261" s="1">
+        <v>7</v>
+      </c>
+      <c r="E261" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="F261" s="1" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="262" ht="15" customHeight="1" spans="1:6">
+      <c r="A262" s="1"/>
+      <c r="B262" s="1">
+        <v>60068</v>
+      </c>
+      <c r="C262" s="1"/>
+      <c r="D262" s="1">
+        <v>7</v>
+      </c>
+      <c r="E262" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="F262" s="1" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="263" ht="15" customHeight="1" spans="1:6">
+      <c r="A263" s="1"/>
+      <c r="B263" s="1">
+        <v>60069</v>
+      </c>
+      <c r="C263" s="1"/>
+      <c r="D263" s="1">
+        <v>7</v>
+      </c>
+      <c r="E263" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="F263" s="1" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="264" ht="15" customHeight="1" spans="1:6">
+      <c r="A264" s="1"/>
+      <c r="B264" s="1">
+        <v>60070</v>
+      </c>
+      <c r="C264" s="1"/>
+      <c r="D264" s="1">
+        <v>7</v>
+      </c>
+      <c r="E264" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="F264" s="1" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="265" ht="15" customHeight="1" spans="1:6">
+      <c r="A265" s="1"/>
+      <c r="B265" s="1">
+        <v>60071</v>
+      </c>
+      <c r="C265" s="1"/>
+      <c r="D265" s="1">
+        <v>7</v>
+      </c>
+      <c r="E265" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="F265" s="1" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="266" ht="15" customHeight="1" spans="1:6">
+      <c r="A266" s="1"/>
+      <c r="B266" s="1">
+        <v>60072</v>
+      </c>
+      <c r="C266" s="1"/>
+      <c r="D266" s="1">
+        <v>7</v>
+      </c>
+      <c r="E266" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="F266" s="1" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="267" ht="15" customHeight="1" spans="1:6">
+      <c r="A267" s="1"/>
+      <c r="B267" s="1">
+        <v>60073</v>
+      </c>
+      <c r="C267" s="1"/>
+      <c r="D267" s="1">
+        <v>7</v>
+      </c>
+      <c r="E267" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="F267" s="1" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="268" ht="15" customHeight="1" spans="1:6">
+      <c r="A268" s="1"/>
+      <c r="B268" s="1">
+        <v>60074</v>
+      </c>
+      <c r="C268" s="1"/>
+      <c r="D268" s="1">
+        <v>7</v>
+      </c>
+      <c r="E268" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="F268" s="1" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="269" ht="15" customHeight="1" spans="1:6">
+      <c r="A269" s="1"/>
+      <c r="B269" s="1">
+        <v>60075</v>
+      </c>
+      <c r="C269" s="1"/>
+      <c r="D269" s="1">
+        <v>7</v>
+      </c>
+      <c r="E269" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="F269" s="1" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="270" ht="15" customHeight="1" spans="1:6">
+      <c r="A270" s="1"/>
+      <c r="B270" s="1">
+        <v>60076</v>
+      </c>
+      <c r="C270" s="1"/>
+      <c r="D270" s="1">
+        <v>7</v>
+      </c>
+      <c r="E270" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="F270" s="1" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="271" ht="15" customHeight="1" spans="1:6">
+      <c r="A271" s="1"/>
+      <c r="B271" s="1">
+        <v>60077</v>
+      </c>
+      <c r="C271" s="1"/>
+      <c r="D271" s="1">
+        <v>7</v>
+      </c>
+      <c r="E271" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="F271" s="1" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="272" ht="15" customHeight="1" spans="1:6">
+      <c r="A272" s="1"/>
+      <c r="B272" s="1">
+        <v>60078</v>
+      </c>
+      <c r="C272" s="1"/>
+      <c r="D272" s="1">
+        <v>7</v>
+      </c>
+      <c r="E272" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="F272" s="1" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="273" ht="15" customHeight="1" spans="1:6">
+      <c r="A273" s="1"/>
+      <c r="B273" s="1">
+        <v>60079</v>
+      </c>
+      <c r="C273" s="1"/>
+      <c r="D273" s="1">
+        <v>7</v>
+      </c>
+      <c r="E273" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="F273" s="1" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="274" ht="15" customHeight="1" spans="1:6">
+      <c r="A274" s="1"/>
+      <c r="B274" s="1">
+        <v>60080</v>
+      </c>
+      <c r="C274" s="1"/>
+      <c r="D274" s="1">
+        <v>7</v>
+      </c>
+      <c r="E274" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="F274" s="1" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="275" ht="15" customHeight="1" spans="1:6">
+      <c r="A275" s="1"/>
+      <c r="B275" s="1">
+        <v>60081</v>
+      </c>
+      <c r="C275" s="1"/>
+      <c r="D275" s="1">
+        <v>7</v>
+      </c>
+      <c r="E275" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="F275" s="1" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="276" ht="15" customHeight="1" spans="1:6">
+      <c r="A276" s="1"/>
+      <c r="B276" s="1">
+        <v>60082</v>
+      </c>
+      <c r="C276" s="1"/>
+      <c r="D276" s="1">
+        <v>7</v>
+      </c>
+      <c r="E276" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="F276" s="1" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="277" ht="15" customHeight="1" spans="1:6">
+      <c r="A277" s="1"/>
+      <c r="B277" s="1">
+        <v>60083</v>
+      </c>
+      <c r="C277" s="1"/>
+      <c r="D277" s="1">
+        <v>7</v>
+      </c>
+      <c r="E277" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="F277" s="1" t="s">
+        <v>555</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/DataTables/ResourceConfigTable.xlsx
+++ b/AAAGameData/DataTables/ResourceConfigTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11925"/>
+    <workbookView windowWidth="29868" windowHeight="14855"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="556">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="563">
   <si>
     <t>#</t>
   </si>
@@ -122,15 +122,48 @@
     <t>召唤师-狂战士立绘</t>
   </si>
   <si>
+    <t>Summoner/术士.png</t>
+  </si>
+  <si>
     <t>召唤师-术士立绘</t>
   </si>
   <si>
+    <t>Summoner/混沌.png</t>
+  </si>
+  <si>
     <t>召唤师-混沌立绘</t>
   </si>
   <si>
+    <t>Summoner/德鲁伊.png</t>
+  </si>
+  <si>
     <t>召唤师-德鲁伊立绘</t>
   </si>
   <si>
+    <t>Summoner/召唤师头像/狂战士.png</t>
+  </si>
+  <si>
+    <t>狂战士头像</t>
+  </si>
+  <si>
+    <t>Summoner/召唤师头像/术士.png</t>
+  </si>
+  <si>
+    <t>术士头像</t>
+  </si>
+  <si>
+    <t>Summoner/召唤师头像/混沌.png</t>
+  </si>
+  <si>
+    <t>混沌头像</t>
+  </si>
+  <si>
+    <t>Summoner/召唤师头像/德鲁伊.png</t>
+  </si>
+  <si>
+    <t>德鲁伊头像</t>
+  </si>
+  <si>
     <t>Card/策略卡/神圣庇护.png</t>
   </si>
   <si>
@@ -845,6 +878,42 @@
     <t>交互提示预制体</t>
   </si>
   <si>
+    <t>Game/Interact/破损的宝箱</t>
+  </si>
+  <si>
+    <t>破损的宝箱</t>
+  </si>
+  <si>
+    <t>Game/Interact/精致的宝箱</t>
+  </si>
+  <si>
+    <t>精致的宝箱</t>
+  </si>
+  <si>
+    <t>Game/Interact/华丽的宝箱</t>
+  </si>
+  <si>
+    <t>华丽的宝箱</t>
+  </si>
+  <si>
+    <t>Game/Interact/神秘的宝箱</t>
+  </si>
+  <si>
+    <t>神秘的宝箱</t>
+  </si>
+  <si>
+    <t>Enemy/后羿(敌人测试)</t>
+  </si>
+  <si>
+    <t>敌人-测试预制体</t>
+  </si>
+  <si>
+    <t>Enemy/邪灵</t>
+  </si>
+  <si>
+    <t>敌人-邪灵预制体</t>
+  </si>
+  <si>
     <t>Combat/BattleArena</t>
   </si>
   <si>
@@ -959,6 +1028,12 @@
     <t>暗影咒体Buff图标</t>
   </si>
   <si>
+    <t>Enemy/默认.png</t>
+  </si>
+  <si>
+    <t>敌人图标</t>
+  </si>
+  <si>
     <t>Buff/5001.png</t>
   </si>
   <si>
@@ -1133,72 +1208,6 @@
     <t>名字背景-稀有度4</t>
   </si>
   <si>
-    <t>Enemy/默认.png</t>
-  </si>
-  <si>
-    <t>敌人图标</t>
-  </si>
-  <si>
-    <t>Game/Interact/破损的宝箱</t>
-  </si>
-  <si>
-    <t>破损的宝箱</t>
-  </si>
-  <si>
-    <t>Game/Interact/精致的宝箱</t>
-  </si>
-  <si>
-    <t>精致的宝箱</t>
-  </si>
-  <si>
-    <t>Game/Interact/华丽的宝箱</t>
-  </si>
-  <si>
-    <t>华丽的宝箱</t>
-  </si>
-  <si>
-    <t>Game/Interact/神秘的宝箱</t>
-  </si>
-  <si>
-    <t>神秘的宝箱</t>
-  </si>
-  <si>
-    <t>Enemy/后羿(敌人测试)</t>
-  </si>
-  <si>
-    <t>敌人-测试预制体</t>
-  </si>
-  <si>
-    <t>Enemy/邪灵</t>
-  </si>
-  <si>
-    <t>敌人-邪灵预制体</t>
-  </si>
-  <si>
-    <t>Summoner/召唤师头像/狂战士.png</t>
-  </si>
-  <si>
-    <t>狂战士头像</t>
-  </si>
-  <si>
-    <t>Summoner/召唤师头像/术士.png</t>
-  </si>
-  <si>
-    <t>术士头像</t>
-  </si>
-  <si>
-    <t>Summoner/召唤师头像/混沌.png</t>
-  </si>
-  <si>
-    <t>混沌头像</t>
-  </si>
-  <si>
-    <t>Summoner/召唤师头像/德鲁伊.png</t>
-  </si>
-  <si>
-    <t>德鲁伊头像</t>
-  </si>
-  <si>
     <t>BGM/游戏启动主菜单BGM</t>
   </si>
   <si>
@@ -1695,6 +1704,18 @@
   </si>
   <si>
     <t>交易音效</t>
+  </si>
+  <si>
+    <t>Chess/后羿/后羿头像.png</t>
+  </si>
+  <si>
+    <t>棋子后羿头像</t>
+  </si>
+  <si>
+    <t>Chess/嫦娥/嫦娥头像.png</t>
+  </si>
+  <si>
+    <t>棋子嫦娥头像</t>
   </si>
 </sst>
 </file>
@@ -1707,14 +1728,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2170,28 +2184,31 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2200,118 +2217,115 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2666,8 +2680,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F277"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <dimension ref="A1:F279"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="21" customWidth="1"/>
@@ -2724,7 +2738,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" ht="81" spans="1:6">
+    <row r="4" ht="86.4" spans="1:6">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -2898,10 +2912,10 @@
         <v>1</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" spans="1:6">
@@ -2914,10 +2928,10 @@
         <v>1</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" spans="1:6">
@@ -2930,2864 +2944,2864 @@
         <v>1</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1" spans="1:6">
       <c r="A17" s="1"/>
       <c r="B17" s="1">
-        <v>1201</v>
+        <v>1155</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="1">
         <v>1</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" spans="1:6">
       <c r="A18" s="1"/>
       <c r="B18" s="1">
-        <v>1202</v>
+        <v>1156</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="1">
         <v>1</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1" spans="1:6">
       <c r="A19" s="1"/>
       <c r="B19" s="1">
-        <v>1203</v>
+        <v>1157</v>
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="1">
         <v>1</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" spans="1:6">
       <c r="A20" s="1"/>
       <c r="B20" s="1">
-        <v>1204</v>
+        <v>1158</v>
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="1">
         <v>1</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1" spans="1:6">
       <c r="A21" s="1"/>
       <c r="B21" s="1">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="1">
         <v>1</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" spans="1:6">
       <c r="A22" s="1"/>
       <c r="B22" s="1">
-        <v>1206</v>
+        <v>1202</v>
       </c>
       <c r="C22" s="1"/>
       <c r="D22" s="1">
         <v>1</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" spans="1:6">
       <c r="A23" s="1"/>
       <c r="B23" s="1">
-        <v>1207</v>
+        <v>1203</v>
       </c>
       <c r="C23" s="1"/>
       <c r="D23" s="1">
         <v>1</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" spans="1:6">
       <c r="A24" s="1"/>
       <c r="B24" s="1">
-        <v>1208</v>
+        <v>1204</v>
       </c>
       <c r="C24" s="1"/>
       <c r="D24" s="1">
         <v>1</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" spans="1:6">
       <c r="A25" s="1"/>
       <c r="B25" s="1">
-        <v>1209</v>
+        <v>1205</v>
       </c>
       <c r="C25" s="1"/>
       <c r="D25" s="1">
         <v>1</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1" spans="1:6">
       <c r="A26" s="1"/>
       <c r="B26" s="1">
-        <v>1210</v>
+        <v>1206</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="1">
         <v>1</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" spans="1:6">
       <c r="A27" s="1"/>
       <c r="B27" s="1">
-        <v>1211</v>
+        <v>1207</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="1">
         <v>1</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1" spans="1:6">
       <c r="A28" s="1"/>
       <c r="B28" s="1">
-        <v>1212</v>
+        <v>1208</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="1">
         <v>1</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" spans="1:6">
       <c r="A29" s="1"/>
       <c r="B29" s="1">
-        <v>1213</v>
+        <v>1209</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="1">
         <v>1</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1" spans="1:6">
       <c r="A30" s="1"/>
       <c r="B30" s="1">
-        <v>1214</v>
+        <v>1210</v>
       </c>
       <c r="C30" s="1"/>
       <c r="D30" s="1">
         <v>1</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1" spans="1:6">
       <c r="A31" s="1"/>
       <c r="B31" s="1">
-        <v>1215</v>
+        <v>1211</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="1">
         <v>1</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1" spans="1:6">
       <c r="A32" s="1"/>
       <c r="B32" s="1">
-        <v>1216</v>
+        <v>1212</v>
       </c>
       <c r="C32" s="1"/>
       <c r="D32" s="1">
         <v>1</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1" spans="1:6">
       <c r="A33" s="1"/>
       <c r="B33" s="1">
-        <v>1217</v>
+        <v>1213</v>
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="1">
         <v>1</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1" spans="1:6">
       <c r="A34" s="1"/>
       <c r="B34" s="1">
-        <v>1218</v>
+        <v>1214</v>
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="1">
         <v>1</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1" spans="1:6">
       <c r="A35" s="1"/>
       <c r="B35" s="1">
-        <v>1219</v>
+        <v>1215</v>
       </c>
       <c r="C35" s="1"/>
       <c r="D35" s="1">
         <v>1</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" spans="1:6">
       <c r="A36" s="1"/>
       <c r="B36" s="1">
-        <v>1220</v>
+        <v>1216</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1">
         <v>1</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" spans="1:6">
       <c r="A37" s="1"/>
       <c r="B37" s="1">
-        <v>1221</v>
+        <v>1217</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1">
         <v>1</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" spans="1:6">
       <c r="A38" s="1"/>
       <c r="B38" s="1">
-        <v>1222</v>
+        <v>1218</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1">
         <v>1</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" spans="1:6">
       <c r="A39" s="1"/>
       <c r="B39" s="1">
-        <v>1223</v>
+        <v>1219</v>
       </c>
       <c r="C39" s="1"/>
       <c r="D39" s="1">
         <v>1</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" spans="1:6">
       <c r="A40" s="1"/>
       <c r="B40" s="1">
-        <v>1224</v>
+        <v>1220</v>
       </c>
       <c r="C40" s="1"/>
       <c r="D40" s="1">
         <v>1</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1" spans="1:6">
       <c r="A41" s="1"/>
       <c r="B41" s="1">
-        <v>1225</v>
+        <v>1221</v>
       </c>
       <c r="C41" s="1"/>
       <c r="D41" s="1">
         <v>1</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" spans="1:6">
       <c r="A42" s="1"/>
       <c r="B42" s="1">
-        <v>1226</v>
+        <v>1222</v>
       </c>
       <c r="C42" s="1"/>
       <c r="D42" s="1">
         <v>1</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1" spans="1:6">
       <c r="A43" s="1"/>
       <c r="B43" s="1">
-        <v>1301</v>
+        <v>1223</v>
       </c>
       <c r="C43" s="1"/>
       <c r="D43" s="1">
         <v>1</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1" spans="1:6">
       <c r="A44" s="1"/>
       <c r="B44" s="1">
-        <v>1304</v>
+        <v>1224</v>
       </c>
       <c r="C44" s="1"/>
       <c r="D44" s="1">
         <v>1</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1" spans="1:6">
       <c r="A45" s="1"/>
       <c r="B45" s="1">
-        <v>1399</v>
+        <v>1225</v>
       </c>
       <c r="C45" s="1"/>
       <c r="D45" s="1">
         <v>1</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" spans="1:6">
       <c r="A46" s="1"/>
       <c r="B46" s="1">
-        <v>1401</v>
+        <v>1226</v>
       </c>
       <c r="C46" s="1"/>
       <c r="D46" s="1">
         <v>1</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1" spans="1:6">
       <c r="A47" s="1"/>
       <c r="B47" s="1">
-        <v>1402</v>
+        <v>1301</v>
       </c>
       <c r="C47" s="1"/>
       <c r="D47" s="1">
         <v>1</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1" spans="1:6">
       <c r="A48" s="1"/>
       <c r="B48" s="1">
-        <v>1403</v>
+        <v>1304</v>
       </c>
       <c r="C48" s="1"/>
       <c r="D48" s="1">
         <v>1</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1" spans="1:6">
       <c r="A49" s="1"/>
       <c r="B49" s="1">
-        <v>1404</v>
+        <v>1399</v>
       </c>
       <c r="C49" s="1"/>
       <c r="D49" s="1">
         <v>1</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1" spans="1:6">
       <c r="A50" s="1"/>
       <c r="B50" s="1">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="C50" s="1"/>
       <c r="D50" s="1">
         <v>1</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1" spans="1:6">
       <c r="A51" s="1"/>
       <c r="B51" s="1">
-        <v>1406</v>
+        <v>1402</v>
       </c>
       <c r="C51" s="1"/>
       <c r="D51" s="1">
         <v>1</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1" spans="1:6">
       <c r="A52" s="1"/>
       <c r="B52" s="1">
-        <v>1501</v>
+        <v>1403</v>
       </c>
       <c r="C52" s="1"/>
       <c r="D52" s="1">
         <v>1</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="53" ht="15" customHeight="1" spans="1:6">
       <c r="A53" s="1"/>
       <c r="B53" s="1">
-        <v>1502</v>
+        <v>1404</v>
       </c>
       <c r="C53" s="1"/>
       <c r="D53" s="1">
         <v>1</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="54" ht="15" customHeight="1" spans="1:6">
       <c r="A54" s="1"/>
       <c r="B54" s="1">
-        <v>1503</v>
+        <v>1405</v>
       </c>
       <c r="C54" s="1"/>
       <c r="D54" s="1">
         <v>1</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="55" ht="15" customHeight="1" spans="1:6">
       <c r="A55" s="1"/>
       <c r="B55" s="1">
-        <v>1601</v>
+        <v>1406</v>
       </c>
       <c r="C55" s="1"/>
       <c r="D55" s="1">
         <v>1</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="56" ht="15" customHeight="1" spans="1:6">
       <c r="A56" s="1"/>
       <c r="B56" s="1">
-        <v>1701</v>
+        <v>1501</v>
       </c>
       <c r="C56" s="1"/>
       <c r="D56" s="1">
         <v>1</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="57" ht="15" customHeight="1" spans="1:6">
       <c r="A57" s="1"/>
       <c r="B57" s="1">
-        <v>1702</v>
+        <v>1502</v>
       </c>
       <c r="C57" s="1"/>
       <c r="D57" s="1">
         <v>1</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="58" ht="15" customHeight="1" spans="1:6">
       <c r="A58" s="1"/>
       <c r="B58" s="1">
-        <v>1703</v>
+        <v>1503</v>
       </c>
       <c r="C58" s="1"/>
       <c r="D58" s="1">
         <v>1</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="59" ht="15" customHeight="1" spans="1:6">
       <c r="A59" s="1"/>
       <c r="B59" s="1">
-        <v>1704</v>
+        <v>1601</v>
       </c>
       <c r="C59" s="1"/>
       <c r="D59" s="1">
         <v>1</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="60" ht="15" customHeight="1" spans="1:6">
       <c r="A60" s="1"/>
       <c r="B60" s="1">
-        <v>1705</v>
+        <v>1701</v>
       </c>
       <c r="C60" s="1"/>
       <c r="D60" s="1">
         <v>1</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="61" ht="15" customHeight="1" spans="1:6">
       <c r="A61" s="1"/>
       <c r="B61" s="1">
-        <v>1706</v>
+        <v>1702</v>
       </c>
       <c r="C61" s="1"/>
       <c r="D61" s="1">
         <v>1</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="62" ht="15" customHeight="1" spans="1:6">
       <c r="A62" s="1"/>
       <c r="B62" s="1">
-        <v>1707</v>
+        <v>1703</v>
       </c>
       <c r="C62" s="1"/>
       <c r="D62" s="1">
         <v>1</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="63" ht="15" customHeight="1" spans="1:6">
       <c r="A63" s="1"/>
       <c r="B63" s="1">
-        <v>1708</v>
+        <v>1704</v>
       </c>
       <c r="C63" s="1"/>
       <c r="D63" s="1">
         <v>1</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="64" ht="15" customHeight="1" spans="1:6">
       <c r="A64" s="1"/>
       <c r="B64" s="1">
-        <v>1711</v>
+        <v>1705</v>
       </c>
       <c r="C64" s="1"/>
       <c r="D64" s="1">
         <v>1</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="65" ht="15" customHeight="1" spans="1:6">
       <c r="A65" s="1"/>
       <c r="B65" s="1">
-        <v>1712</v>
+        <v>1706</v>
       </c>
       <c r="C65" s="1"/>
       <c r="D65" s="1">
         <v>1</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="66" ht="15" customHeight="1" spans="1:6">
       <c r="A66" s="1"/>
       <c r="B66" s="1">
-        <v>1801</v>
+        <v>1707</v>
       </c>
       <c r="C66" s="1"/>
       <c r="D66" s="1">
         <v>1</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1" spans="1:6">
       <c r="A67" s="1"/>
       <c r="B67" s="1">
-        <v>1802</v>
+        <v>1708</v>
       </c>
       <c r="C67" s="1"/>
       <c r="D67" s="1">
         <v>1</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="68" ht="15" customHeight="1" spans="1:6">
       <c r="A68" s="1"/>
       <c r="B68" s="1">
-        <v>1803</v>
+        <v>1711</v>
       </c>
       <c r="C68" s="1"/>
       <c r="D68" s="1">
         <v>1</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" spans="1:6">
       <c r="A69" s="1"/>
       <c r="B69" s="1">
-        <v>1804</v>
+        <v>1712</v>
       </c>
       <c r="C69" s="1"/>
       <c r="D69" s="1">
         <v>1</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1" spans="1:6">
       <c r="A70" s="1"/>
       <c r="B70" s="1">
-        <v>1805</v>
+        <v>1801</v>
       </c>
       <c r="C70" s="1"/>
       <c r="D70" s="1">
         <v>1</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1" spans="1:6">
       <c r="A71" s="1"/>
       <c r="B71" s="1">
-        <v>1806</v>
+        <v>1802</v>
       </c>
       <c r="C71" s="1"/>
       <c r="D71" s="1">
         <v>1</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1" spans="1:6">
       <c r="A72" s="1"/>
       <c r="B72" s="1">
-        <v>1807</v>
+        <v>1803</v>
       </c>
       <c r="C72" s="1"/>
       <c r="D72" s="1">
         <v>1</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1" spans="1:6">
       <c r="A73" s="1"/>
       <c r="B73" s="1">
-        <v>1808</v>
+        <v>1804</v>
       </c>
       <c r="C73" s="1"/>
       <c r="D73" s="1">
         <v>1</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="74" ht="15" customHeight="1" spans="1:6">
       <c r="A74" s="1"/>
       <c r="B74" s="1">
-        <v>1901</v>
+        <v>1805</v>
       </c>
       <c r="C74" s="1"/>
       <c r="D74" s="1">
         <v>1</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1" spans="1:6">
       <c r="A75" s="1"/>
       <c r="B75" s="1">
-        <v>1902</v>
+        <v>1806</v>
       </c>
       <c r="C75" s="1"/>
       <c r="D75" s="1">
         <v>1</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="76" ht="15" customHeight="1" spans="1:6">
       <c r="A76" s="1"/>
       <c r="B76" s="1">
-        <v>1903</v>
+        <v>1807</v>
       </c>
       <c r="C76" s="1"/>
       <c r="D76" s="1">
         <v>1</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="77" ht="15" customHeight="1" spans="1:6">
       <c r="A77" s="1"/>
       <c r="B77" s="1">
-        <v>1904</v>
+        <v>1808</v>
       </c>
       <c r="C77" s="1"/>
       <c r="D77" s="1">
         <v>1</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="78" ht="15" customHeight="1" spans="1:6">
       <c r="A78" s="1"/>
       <c r="B78" s="1">
-        <v>1905</v>
+        <v>1901</v>
       </c>
       <c r="C78" s="1"/>
       <c r="D78" s="1">
         <v>1</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1" spans="1:6">
       <c r="A79" s="1"/>
       <c r="B79" s="1">
-        <v>1906</v>
+        <v>1902</v>
       </c>
       <c r="C79" s="1"/>
       <c r="D79" s="1">
         <v>1</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1" spans="1:6">
       <c r="A80" s="1"/>
       <c r="B80" s="1">
-        <v>1907</v>
+        <v>1903</v>
       </c>
       <c r="C80" s="1"/>
       <c r="D80" s="1">
         <v>1</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1" spans="1:6">
       <c r="A81" s="1"/>
       <c r="B81" s="1">
-        <v>1908</v>
+        <v>1904</v>
       </c>
       <c r="C81" s="1"/>
       <c r="D81" s="1">
         <v>1</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1" spans="1:6">
       <c r="A82" s="1"/>
       <c r="B82" s="1">
-        <v>1909</v>
+        <v>1905</v>
       </c>
       <c r="C82" s="1"/>
       <c r="D82" s="1">
         <v>1</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1" spans="1:6">
       <c r="A83" s="1"/>
       <c r="B83" s="1">
-        <v>1910</v>
+        <v>1906</v>
       </c>
       <c r="C83" s="1"/>
       <c r="D83" s="1">
         <v>1</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
     </row>
     <row r="84" ht="15" customHeight="1" spans="1:6">
       <c r="A84" s="1"/>
       <c r="B84" s="1">
-        <v>1911</v>
+        <v>1907</v>
       </c>
       <c r="C84" s="1"/>
       <c r="D84" s="1">
         <v>1</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1" spans="1:6">
       <c r="A85" s="1"/>
       <c r="B85" s="1">
-        <v>1912</v>
+        <v>1908</v>
       </c>
       <c r="C85" s="1"/>
       <c r="D85" s="1">
         <v>1</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1" spans="1:6">
       <c r="A86" s="1"/>
       <c r="B86" s="1">
-        <v>1913</v>
+        <v>1909</v>
       </c>
       <c r="C86" s="1"/>
       <c r="D86" s="1">
         <v>1</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1" spans="1:6">
       <c r="A87" s="1"/>
       <c r="B87" s="1">
-        <v>1914</v>
+        <v>1910</v>
       </c>
       <c r="C87" s="1"/>
       <c r="D87" s="1">
         <v>1</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="88" ht="15" customHeight="1" spans="1:6">
       <c r="A88" s="1"/>
       <c r="B88" s="1">
-        <v>1915</v>
+        <v>1911</v>
       </c>
       <c r="C88" s="1"/>
       <c r="D88" s="1">
         <v>1</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
     </row>
     <row r="89" ht="15" customHeight="1" spans="1:6">
       <c r="A89" s="1"/>
       <c r="B89" s="1">
-        <v>1916</v>
+        <v>1912</v>
       </c>
       <c r="C89" s="1"/>
       <c r="D89" s="1">
         <v>1</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="90" ht="15" customHeight="1" spans="1:6">
       <c r="A90" s="1"/>
       <c r="B90" s="1">
-        <v>1917</v>
+        <v>1913</v>
       </c>
       <c r="C90" s="1"/>
       <c r="D90" s="1">
         <v>1</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="91" ht="15" customHeight="1" spans="1:6">
       <c r="A91" s="1"/>
       <c r="B91" s="1">
-        <v>1918</v>
+        <v>1914</v>
       </c>
       <c r="C91" s="1"/>
       <c r="D91" s="1">
         <v>1</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
     </row>
     <row r="92" ht="15" customHeight="1" spans="1:6">
       <c r="A92" s="1"/>
       <c r="B92" s="1">
-        <v>1919</v>
+        <v>1915</v>
       </c>
       <c r="C92" s="1"/>
       <c r="D92" s="1">
         <v>1</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
     </row>
     <row r="93" ht="15" customHeight="1" spans="1:6">
       <c r="A93" s="1"/>
       <c r="B93" s="1">
-        <v>1920</v>
+        <v>1916</v>
       </c>
       <c r="C93" s="1"/>
       <c r="D93" s="1">
         <v>1</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="94" ht="15" customHeight="1" spans="1:6">
       <c r="A94" s="1"/>
       <c r="B94" s="1">
-        <v>1921</v>
+        <v>1917</v>
       </c>
       <c r="C94" s="1"/>
       <c r="D94" s="1">
         <v>1</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
     </row>
     <row r="95" ht="15" customHeight="1" spans="1:6">
       <c r="A95" s="1"/>
       <c r="B95" s="1">
-        <v>1922</v>
+        <v>1918</v>
       </c>
       <c r="C95" s="1"/>
       <c r="D95" s="1">
         <v>1</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
     </row>
     <row r="96" ht="15" customHeight="1" spans="1:6">
       <c r="A96" s="1"/>
       <c r="B96" s="1">
-        <v>1923</v>
+        <v>1919</v>
       </c>
       <c r="C96" s="1"/>
       <c r="D96" s="1">
         <v>1</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="97" ht="15" customHeight="1" spans="1:6">
       <c r="A97" s="1"/>
       <c r="B97" s="1">
-        <v>1924</v>
+        <v>1920</v>
       </c>
       <c r="C97" s="1"/>
       <c r="D97" s="1">
         <v>1</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="98" ht="15" customHeight="1" spans="1:6">
       <c r="A98" s="1"/>
       <c r="B98" s="1">
-        <v>1925</v>
+        <v>1921</v>
       </c>
       <c r="C98" s="1"/>
       <c r="D98" s="1">
         <v>1</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
     </row>
     <row r="99" ht="15" customHeight="1" spans="1:6">
       <c r="A99" s="1"/>
       <c r="B99" s="1">
-        <v>1926</v>
+        <v>1922</v>
       </c>
       <c r="C99" s="1"/>
       <c r="D99" s="1">
         <v>1</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="100" ht="15" customHeight="1" spans="1:6">
       <c r="A100" s="1"/>
       <c r="B100" s="1">
-        <v>1927</v>
+        <v>1923</v>
       </c>
       <c r="C100" s="1"/>
       <c r="D100" s="1">
         <v>1</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
     </row>
     <row r="101" ht="15" customHeight="1" spans="1:6">
       <c r="A101" s="1"/>
       <c r="B101" s="1">
-        <v>1928</v>
+        <v>1924</v>
       </c>
       <c r="C101" s="1"/>
       <c r="D101" s="1">
         <v>1</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="102" ht="15" customHeight="1" spans="1:6">
       <c r="A102" s="1"/>
       <c r="B102" s="1">
-        <v>1929</v>
+        <v>1925</v>
       </c>
       <c r="C102" s="1"/>
       <c r="D102" s="1">
         <v>1</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
     </row>
     <row r="103" ht="15" customHeight="1" spans="1:6">
       <c r="A103" s="1"/>
       <c r="B103" s="1">
-        <v>1930</v>
+        <v>1926</v>
       </c>
       <c r="C103" s="1"/>
       <c r="D103" s="1">
         <v>1</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="104" ht="15" customHeight="1" spans="1:6">
       <c r="A104" s="1"/>
       <c r="B104" s="1">
-        <v>1931</v>
+        <v>1927</v>
       </c>
       <c r="C104" s="1"/>
       <c r="D104" s="1">
         <v>1</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
     </row>
     <row r="105" ht="15" customHeight="1" spans="1:6">
       <c r="A105" s="1"/>
       <c r="B105" s="1">
-        <v>1932</v>
+        <v>1928</v>
       </c>
       <c r="C105" s="1"/>
       <c r="D105" s="1">
         <v>1</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
     </row>
     <row r="106" ht="15" customHeight="1" spans="1:6">
       <c r="A106" s="1"/>
       <c r="B106" s="1">
-        <v>1933</v>
+        <v>1929</v>
       </c>
       <c r="C106" s="1"/>
       <c r="D106" s="1">
         <v>1</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
     </row>
     <row r="107" ht="15" customHeight="1" spans="1:6">
       <c r="A107" s="1"/>
       <c r="B107" s="1">
-        <v>1934</v>
+        <v>1930</v>
       </c>
       <c r="C107" s="1"/>
       <c r="D107" s="1">
         <v>1</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
     </row>
     <row r="108" ht="15" customHeight="1" spans="1:6">
       <c r="A108" s="1"/>
       <c r="B108" s="1">
-        <v>1935</v>
+        <v>1931</v>
       </c>
       <c r="C108" s="1"/>
       <c r="D108" s="1">
         <v>1</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
     </row>
     <row r="109" ht="15" customHeight="1" spans="1:6">
       <c r="A109" s="1"/>
       <c r="B109" s="1">
-        <v>1936</v>
+        <v>1932</v>
       </c>
       <c r="C109" s="1"/>
       <c r="D109" s="1">
         <v>1</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
     </row>
     <row r="110" ht="15" customHeight="1" spans="1:6">
       <c r="A110" s="1"/>
       <c r="B110" s="1">
-        <v>1937</v>
+        <v>1933</v>
       </c>
       <c r="C110" s="1"/>
       <c r="D110" s="1">
         <v>1</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="111" ht="15" customHeight="1" spans="1:6">
       <c r="A111" s="1"/>
       <c r="B111" s="1">
-        <v>1938</v>
+        <v>1934</v>
       </c>
       <c r="C111" s="1"/>
       <c r="D111" s="1">
         <v>1</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="112" ht="15" customHeight="1" spans="1:6">
       <c r="A112" s="1"/>
       <c r="B112" s="1">
-        <v>1939</v>
+        <v>1935</v>
       </c>
       <c r="C112" s="1"/>
       <c r="D112" s="1">
         <v>1</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="113" ht="15" customHeight="1" spans="1:6">
       <c r="A113" s="1"/>
       <c r="B113" s="1">
-        <v>1940</v>
+        <v>1936</v>
       </c>
       <c r="C113" s="1"/>
       <c r="D113" s="1">
         <v>1</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="114" ht="15" customHeight="1" spans="1:6">
       <c r="A114" s="1"/>
       <c r="B114" s="1">
-        <v>1941</v>
+        <v>1937</v>
       </c>
       <c r="C114" s="1"/>
       <c r="D114" s="1">
         <v>1</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="115" ht="15" customHeight="1" spans="1:6">
       <c r="A115" s="1"/>
       <c r="B115" s="1">
-        <v>1942</v>
+        <v>1938</v>
       </c>
       <c r="C115" s="1"/>
       <c r="D115" s="1">
         <v>1</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
     <row r="116" ht="15" customHeight="1" spans="1:6">
       <c r="A116" s="1"/>
       <c r="B116" s="1">
-        <v>1943</v>
+        <v>1939</v>
       </c>
       <c r="C116" s="1"/>
       <c r="D116" s="1">
         <v>1</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
     <row r="117" ht="15" customHeight="1" spans="1:6">
       <c r="A117" s="1"/>
       <c r="B117" s="1">
-        <v>1944</v>
+        <v>1940</v>
       </c>
       <c r="C117" s="1"/>
       <c r="D117" s="1">
         <v>1</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
     </row>
     <row r="118" ht="15" customHeight="1" spans="1:6">
       <c r="A118" s="1"/>
       <c r="B118" s="1">
-        <v>1945</v>
+        <v>1941</v>
       </c>
       <c r="C118" s="1"/>
       <c r="D118" s="1">
         <v>1</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="119" ht="15" customHeight="1" spans="1:6">
       <c r="A119" s="1"/>
       <c r="B119" s="1">
-        <v>1946</v>
+        <v>1942</v>
       </c>
       <c r="C119" s="1"/>
       <c r="D119" s="1">
         <v>1</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
     </row>
     <row r="120" ht="15" customHeight="1" spans="1:6">
       <c r="A120" s="1"/>
       <c r="B120" s="1">
-        <v>1947</v>
+        <v>1943</v>
       </c>
       <c r="C120" s="1"/>
       <c r="D120" s="1">
         <v>1</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="121" ht="15" customHeight="1" spans="1:6">
       <c r="A121" s="1"/>
       <c r="B121" s="1">
-        <v>1948</v>
+        <v>1944</v>
       </c>
       <c r="C121" s="1"/>
       <c r="D121" s="1">
         <v>1</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="122" ht="15" customHeight="1" spans="1:6">
       <c r="A122" s="1"/>
       <c r="B122" s="1">
-        <v>2001</v>
+        <v>1945</v>
       </c>
       <c r="C122" s="1"/>
       <c r="D122" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
     </row>
     <row r="123" ht="15" customHeight="1" spans="1:6">
       <c r="A123" s="1"/>
       <c r="B123" s="1">
-        <v>2002</v>
+        <v>1946</v>
       </c>
       <c r="C123" s="1"/>
       <c r="D123" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="124" ht="15" customHeight="1" spans="1:6">
       <c r="A124" s="1"/>
       <c r="B124" s="1">
-        <v>2003</v>
+        <v>1947</v>
       </c>
       <c r="C124" s="1"/>
       <c r="D124" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
     </row>
     <row r="125" ht="15" customHeight="1" spans="1:6">
       <c r="A125" s="1"/>
       <c r="B125" s="1">
-        <v>2004</v>
+        <v>1948</v>
       </c>
       <c r="C125" s="1"/>
       <c r="D125" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="126" ht="15" customHeight="1" spans="1:6">
       <c r="A126" s="1"/>
       <c r="B126" s="1">
-        <v>2101</v>
+        <v>2001</v>
       </c>
       <c r="C126" s="1"/>
       <c r="D126" s="1">
         <v>2</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
     </row>
     <row r="127" ht="15" customHeight="1" spans="1:6">
       <c r="A127" s="1"/>
       <c r="B127" s="1">
-        <v>2102</v>
+        <v>2002</v>
       </c>
       <c r="C127" s="1"/>
       <c r="D127" s="1">
         <v>2</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
     </row>
     <row r="128" ht="15" customHeight="1" spans="1:6">
       <c r="A128" s="1"/>
       <c r="B128" s="1">
-        <v>2103</v>
+        <v>2003</v>
       </c>
       <c r="C128" s="1"/>
       <c r="D128" s="1">
         <v>2</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
     </row>
     <row r="129" ht="15" customHeight="1" spans="1:6">
       <c r="A129" s="1"/>
       <c r="B129" s="1">
-        <v>2104</v>
+        <v>2004</v>
       </c>
       <c r="C129" s="1"/>
       <c r="D129" s="1">
         <v>2</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
     </row>
     <row r="130" ht="15" customHeight="1" spans="1:6">
       <c r="A130" s="1"/>
       <c r="B130" s="1">
-        <v>2201</v>
+        <v>2101</v>
       </c>
       <c r="C130" s="1"/>
       <c r="D130" s="1">
         <v>2</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
     </row>
     <row r="131" ht="15" customHeight="1" spans="1:6">
       <c r="A131" s="1"/>
       <c r="B131" s="1">
-        <v>2301</v>
+        <v>2102</v>
       </c>
       <c r="C131" s="1"/>
       <c r="D131" s="1">
         <v>2</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
     </row>
     <row r="132" ht="15" customHeight="1" spans="1:6">
       <c r="A132" s="1"/>
       <c r="B132" s="1">
-        <v>2304</v>
+        <v>2103</v>
       </c>
       <c r="C132" s="1"/>
       <c r="D132" s="1">
         <v>2</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
     </row>
     <row r="133" ht="15" customHeight="1" spans="1:6">
       <c r="A133" s="1"/>
       <c r="B133" s="1">
-        <v>2309</v>
+        <v>2104</v>
       </c>
       <c r="C133" s="1"/>
       <c r="D133" s="1">
         <v>2</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="134" ht="15" customHeight="1" spans="1:6">
       <c r="A134" s="1"/>
       <c r="B134" s="1">
-        <v>2399</v>
+        <v>2201</v>
       </c>
       <c r="C134" s="1"/>
       <c r="D134" s="1">
         <v>2</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="135" ht="15" customHeight="1" spans="1:6">
       <c r="A135" s="1"/>
       <c r="B135" s="1">
-        <v>2401</v>
+        <v>2301</v>
       </c>
       <c r="C135" s="1"/>
       <c r="D135" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="136" ht="15" customHeight="1" spans="1:6">
       <c r="A136" s="1"/>
       <c r="B136" s="1">
-        <v>2402</v>
+        <v>2304</v>
       </c>
       <c r="C136" s="1"/>
       <c r="D136" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="137" ht="15" customHeight="1" spans="1:6">
       <c r="A137" s="1"/>
       <c r="B137" s="1">
-        <v>2901</v>
+        <v>2309</v>
       </c>
       <c r="C137" s="1"/>
       <c r="D137" s="1">
         <v>2</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="138" ht="15" customHeight="1" spans="1:6">
       <c r="A138" s="1"/>
       <c r="B138" s="1">
-        <v>3001</v>
+        <v>2399</v>
       </c>
       <c r="C138" s="1"/>
       <c r="D138" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="139" ht="15" customHeight="1" spans="1:6">
       <c r="A139" s="1"/>
       <c r="B139" s="1">
-        <v>3002</v>
+        <v>2401</v>
       </c>
       <c r="C139" s="1"/>
       <c r="D139" s="1">
         <v>3</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="140" ht="15" customHeight="1" spans="1:6">
       <c r="A140" s="1"/>
       <c r="B140" s="1">
-        <v>3003</v>
+        <v>2402</v>
       </c>
       <c r="C140" s="1"/>
       <c r="D140" s="1">
         <v>3</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="141" ht="15" customHeight="1" spans="1:6">
       <c r="A141" s="1"/>
       <c r="B141" s="1">
-        <v>3004</v>
+        <v>2501</v>
       </c>
       <c r="C141" s="1"/>
       <c r="D141" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="142" ht="15" customHeight="1" spans="1:6">
       <c r="A142" s="1"/>
       <c r="B142" s="1">
-        <v>3005</v>
+        <v>2502</v>
       </c>
       <c r="C142" s="1"/>
       <c r="D142" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="143" ht="15" customHeight="1" spans="1:6">
       <c r="A143" s="1"/>
       <c r="B143" s="1">
-        <v>3006</v>
+        <v>2503</v>
       </c>
       <c r="C143" s="1"/>
       <c r="D143" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="144" ht="15" customHeight="1" spans="1:6">
       <c r="A144" s="1"/>
       <c r="B144" s="1">
-        <v>3007</v>
+        <v>2504</v>
       </c>
       <c r="C144" s="1"/>
       <c r="D144" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="145" ht="15" customHeight="1" spans="1:6">
       <c r="A145" s="1"/>
       <c r="B145" s="1">
-        <v>6001</v>
+        <v>2600</v>
       </c>
       <c r="C145" s="1"/>
       <c r="D145" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="146" ht="15" customHeight="1" spans="1:6">
       <c r="A146" s="1"/>
       <c r="B146" s="1">
-        <v>10001</v>
+        <v>2601</v>
       </c>
       <c r="C146" s="1"/>
       <c r="D146" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="147" ht="15" customHeight="1" spans="1:6">
       <c r="A147" s="1"/>
       <c r="B147" s="1">
-        <v>10002</v>
+        <v>2901</v>
       </c>
       <c r="C147" s="1"/>
       <c r="D147" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="148" ht="15" customHeight="1" spans="1:6">
       <c r="A148" s="1"/>
       <c r="B148" s="1">
-        <v>10003</v>
+        <v>3001</v>
       </c>
       <c r="C148" s="1"/>
       <c r="D148" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="149" ht="15" customHeight="1" spans="1:6">
       <c r="A149" s="1"/>
       <c r="B149" s="1">
-        <v>10004</v>
+        <v>3002</v>
       </c>
       <c r="C149" s="1"/>
       <c r="D149" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="150" ht="15" customHeight="1" spans="1:6">
       <c r="A150" s="1"/>
       <c r="B150" s="1">
-        <v>10101</v>
+        <v>3003</v>
       </c>
       <c r="C150" s="1"/>
       <c r="D150" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="151" ht="15" customHeight="1" spans="1:6">
       <c r="A151" s="1"/>
       <c r="B151" s="1">
-        <v>10102</v>
+        <v>3004</v>
       </c>
       <c r="C151" s="1"/>
       <c r="D151" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="152" ht="15" customHeight="1" spans="1:6">
       <c r="A152" s="1"/>
       <c r="B152" s="1">
-        <v>10103</v>
+        <v>3005</v>
       </c>
       <c r="C152" s="1"/>
       <c r="D152" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="153" ht="15" customHeight="1" spans="1:6">
       <c r="A153" s="1"/>
       <c r="B153" s="1">
-        <v>10201</v>
+        <v>3006</v>
       </c>
       <c r="C153" s="1"/>
       <c r="D153" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="154" ht="15" customHeight="1" spans="1:6">
       <c r="A154" s="1"/>
       <c r="B154" s="1">
-        <v>10202</v>
+        <v>3007</v>
       </c>
       <c r="C154" s="1"/>
       <c r="D154" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="155" ht="15" customHeight="1" spans="1:6">
       <c r="A155" s="1"/>
       <c r="B155" s="1">
-        <v>10203</v>
+        <v>6001</v>
       </c>
       <c r="C155" s="1"/>
       <c r="D155" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="156" ht="15" customHeight="1" spans="1:6">
       <c r="A156" s="1"/>
       <c r="B156" s="1">
-        <v>15001</v>
+        <v>10001</v>
       </c>
       <c r="C156" s="1"/>
       <c r="D156" s="1">
         <v>1</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="157" ht="15" customHeight="1" spans="1:6">
       <c r="A157" s="1"/>
       <c r="B157" s="1">
-        <v>15002</v>
-      </c>
-      <c r="C157" s="1" t="s">
-        <v>312</v>
-      </c>
+        <v>10002</v>
+      </c>
+      <c r="C157" s="1"/>
       <c r="D157" s="1">
         <v>1</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="158" ht="15" customHeight="1" spans="1:6">
       <c r="A158" s="1"/>
       <c r="B158" s="1">
-        <v>15003</v>
+        <v>10003</v>
       </c>
       <c r="C158" s="1"/>
       <c r="D158" s="1">
         <v>1</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="159" ht="15" customHeight="1" spans="1:6">
       <c r="A159" s="1"/>
       <c r="B159" s="1">
-        <v>15005</v>
+        <v>10004</v>
       </c>
       <c r="C159" s="1"/>
       <c r="D159" s="1">
         <v>1</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="160" ht="15" customHeight="1" spans="1:6">
       <c r="A160" s="1"/>
       <c r="B160" s="1">
-        <v>15007</v>
+        <v>10101</v>
       </c>
       <c r="C160" s="1"/>
       <c r="D160" s="1">
         <v>1</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="161" ht="15" customHeight="1" spans="1:6">
       <c r="A161" s="1"/>
       <c r="B161" s="1">
-        <v>15008</v>
+        <v>10102</v>
       </c>
       <c r="C161" s="1"/>
       <c r="D161" s="1">
         <v>1</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="162" ht="15" customHeight="1" spans="1:6">
       <c r="A162" s="1"/>
       <c r="B162" s="1">
-        <v>15009</v>
+        <v>10103</v>
       </c>
       <c r="C162" s="1"/>
       <c r="D162" s="1">
         <v>1</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="163" ht="15" customHeight="1" spans="1:6">
       <c r="A163" s="1"/>
       <c r="B163" s="1">
-        <v>15011</v>
+        <v>10201</v>
       </c>
       <c r="C163" s="1"/>
       <c r="D163" s="1">
         <v>1</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="164" ht="15" customHeight="1" spans="1:6">
       <c r="A164" s="1"/>
       <c r="B164" s="1">
-        <v>15012</v>
+        <v>10202</v>
       </c>
       <c r="C164" s="1"/>
       <c r="D164" s="1">
         <v>1</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="165" ht="15" customHeight="1" spans="1:6">
       <c r="A165" s="1"/>
       <c r="B165" s="1">
-        <v>15013</v>
+        <v>10203</v>
       </c>
       <c r="C165" s="1"/>
       <c r="D165" s="1">
         <v>1</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="166" ht="15" customHeight="1" spans="1:6">
       <c r="A166" s="1"/>
       <c r="B166" s="1">
-        <v>15014</v>
+        <v>11001</v>
       </c>
       <c r="C166" s="1"/>
       <c r="D166" s="1">
         <v>1</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="167" ht="15" customHeight="1" spans="1:6">
       <c r="A167" s="1"/>
       <c r="B167" s="1">
-        <v>15015</v>
+        <v>15001</v>
       </c>
       <c r="C167" s="1"/>
       <c r="D167" s="1">
         <v>1</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="168" ht="15" customHeight="1" spans="1:6">
       <c r="A168" s="1"/>
       <c r="B168" s="1">
-        <v>15017</v>
-      </c>
-      <c r="C168" s="1"/>
+        <v>15002</v>
+      </c>
+      <c r="C168" s="1" t="s">
+        <v>337</v>
+      </c>
       <c r="D168" s="1">
         <v>1</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="169" ht="15" customHeight="1" spans="1:6">
       <c r="A169" s="1"/>
       <c r="B169" s="1">
-        <v>15018</v>
+        <v>15003</v>
       </c>
       <c r="C169" s="1"/>
       <c r="D169" s="1">
         <v>1</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="170" ht="15" customHeight="1" spans="1:6">
       <c r="A170" s="1"/>
       <c r="B170" s="1">
-        <v>15019</v>
+        <v>15005</v>
       </c>
       <c r="C170" s="1"/>
       <c r="D170" s="1">
         <v>1</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="171" ht="15" customHeight="1" spans="1:6">
       <c r="A171" s="1"/>
       <c r="B171" s="1">
-        <v>15020</v>
+        <v>15007</v>
       </c>
       <c r="C171" s="1"/>
       <c r="D171" s="1">
         <v>1</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="172" ht="15" customHeight="1" spans="1:6">
       <c r="A172" s="1"/>
       <c r="B172" s="1">
-        <v>15021</v>
+        <v>15008</v>
       </c>
       <c r="C172" s="1"/>
       <c r="D172" s="1">
         <v>1</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="173" ht="15" customHeight="1" spans="1:6">
       <c r="A173" s="1"/>
       <c r="B173" s="1">
-        <v>15022</v>
-      </c>
-      <c r="C173" s="1" t="s">
-        <v>345</v>
-      </c>
+        <v>15009</v>
+      </c>
+      <c r="C173" s="1"/>
       <c r="D173" s="1">
         <v>1</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="174" ht="15" customHeight="1" spans="1:6">
       <c r="A174" s="1"/>
       <c r="B174" s="1">
-        <v>15023</v>
-      </c>
-      <c r="C174" s="1" t="s">
-        <v>345</v>
-      </c>
+        <v>15011</v>
+      </c>
+      <c r="C174" s="1"/>
       <c r="D174" s="1">
         <v>1</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="175" ht="15" customHeight="1" spans="1:6">
       <c r="A175" s="1"/>
       <c r="B175" s="1">
-        <v>19002</v>
+        <v>15012</v>
       </c>
       <c r="C175" s="1"/>
       <c r="D175" s="1">
         <v>1</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="176" ht="15" customHeight="1" spans="1:6">
       <c r="A176" s="1"/>
       <c r="B176" s="1">
-        <v>19003</v>
+        <v>15013</v>
       </c>
       <c r="C176" s="1"/>
       <c r="D176" s="1">
         <v>1</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="177" ht="15" customHeight="1" spans="1:6">
       <c r="A177" s="1"/>
       <c r="B177" s="1">
-        <v>19004</v>
+        <v>15014</v>
       </c>
       <c r="C177" s="1"/>
       <c r="D177" s="1">
         <v>1</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="178" ht="15" customHeight="1" spans="1:6">
       <c r="A178" s="1"/>
       <c r="B178" s="1">
-        <v>19012</v>
+        <v>15015</v>
       </c>
       <c r="C178" s="1"/>
       <c r="D178" s="1">
         <v>1</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="179" ht="15" customHeight="1" spans="1:6">
       <c r="A179" s="1"/>
       <c r="B179" s="1">
-        <v>19013</v>
+        <v>15017</v>
       </c>
       <c r="C179" s="1"/>
       <c r="D179" s="1">
         <v>1</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="180" ht="15" customHeight="1" spans="1:6">
       <c r="A180" s="1"/>
       <c r="B180" s="1">
-        <v>19014</v>
+        <v>15018</v>
       </c>
       <c r="C180" s="1"/>
       <c r="D180" s="1">
         <v>1</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="181" ht="15" customHeight="1" spans="1:6">
       <c r="A181" s="1"/>
       <c r="B181" s="1">
-        <v>19022</v>
+        <v>15019</v>
       </c>
       <c r="C181" s="1"/>
       <c r="D181" s="1">
         <v>1</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="182" ht="15" customHeight="1" spans="1:6">
       <c r="A182" s="1"/>
       <c r="B182" s="1">
-        <v>19023</v>
+        <v>15020</v>
       </c>
       <c r="C182" s="1"/>
       <c r="D182" s="1">
         <v>1</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="183" ht="15" customHeight="1" spans="1:6">
       <c r="A183" s="1"/>
       <c r="B183" s="1">
-        <v>19024</v>
+        <v>15021</v>
       </c>
       <c r="C183" s="1"/>
       <c r="D183" s="1">
         <v>1</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="184" ht="15" customHeight="1" spans="1:6">
       <c r="A184" s="1"/>
       <c r="B184" s="1">
-        <v>11001</v>
-      </c>
-      <c r="C184" s="1"/>
+        <v>15022</v>
+      </c>
+      <c r="C184" s="1" t="s">
+        <v>370</v>
+      </c>
       <c r="D184" s="1">
         <v>1</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="185" ht="15" customHeight="1" spans="1:6">
       <c r="A185" s="1"/>
       <c r="B185" s="1">
-        <v>2501</v>
-      </c>
-      <c r="C185" s="1"/>
+        <v>15023</v>
+      </c>
+      <c r="C185" s="1" t="s">
+        <v>370</v>
+      </c>
       <c r="D185" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="186" ht="15" customHeight="1" spans="1:6">
       <c r="A186" s="1"/>
       <c r="B186" s="1">
-        <v>2502</v>
+        <v>19002</v>
       </c>
       <c r="C186" s="1"/>
       <c r="D186" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="187" ht="15" customHeight="1" spans="1:6">
       <c r="A187" s="1"/>
       <c r="B187" s="1">
-        <v>2503</v>
+        <v>19003</v>
       </c>
       <c r="C187" s="1"/>
       <c r="D187" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="188" ht="15" customHeight="1" spans="1:6">
       <c r="A188" s="1"/>
       <c r="B188" s="1">
-        <v>2504</v>
+        <v>19004</v>
       </c>
       <c r="C188" s="1"/>
       <c r="D188" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="189" ht="15" customHeight="1" spans="1:6">
       <c r="A189" s="1"/>
       <c r="B189" s="1">
-        <v>2600</v>
+        <v>19012</v>
       </c>
       <c r="C189" s="1"/>
       <c r="D189" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="190" ht="15" customHeight="1" spans="1:6">
       <c r="A190" s="1"/>
       <c r="B190" s="1">
-        <v>2601</v>
+        <v>19013</v>
       </c>
       <c r="C190" s="1"/>
       <c r="D190" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="191" ht="15" customHeight="1" spans="1:6">
       <c r="A191" s="1"/>
       <c r="B191" s="1">
-        <v>1155</v>
+        <v>19014</v>
       </c>
       <c r="C191" s="1"/>
       <c r="D191" s="1">
         <v>1</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="192" ht="15" customHeight="1" spans="1:6">
       <c r="A192" s="1"/>
       <c r="B192" s="1">
-        <v>1156</v>
+        <v>19022</v>
       </c>
       <c r="C192" s="1"/>
       <c r="D192" s="1">
         <v>1</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="193" ht="15" customHeight="1" spans="1:6">
       <c r="A193" s="1"/>
       <c r="B193" s="1">
-        <v>1157</v>
+        <v>19023</v>
       </c>
       <c r="C193" s="1"/>
       <c r="D193" s="1">
         <v>1</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="194" ht="15" customHeight="1" spans="1:6">
       <c r="A194" s="1"/>
       <c r="B194" s="1">
-        <v>1158</v>
+        <v>19024</v>
       </c>
       <c r="C194" s="1"/>
       <c r="D194" s="1">
         <v>1</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="F194" s="1" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="195" ht="15" customHeight="1" spans="1:6">
@@ -5800,10 +5814,10 @@
         <v>7</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="F195" s="1" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="196" ht="15" customHeight="1" spans="1:6">
@@ -5816,10 +5830,10 @@
         <v>7</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="F196" s="1" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="197" ht="15" customHeight="1" spans="1:6">
@@ -5832,10 +5846,10 @@
         <v>7</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="198" ht="15" customHeight="1" spans="1:6">
@@ -5848,10 +5862,10 @@
         <v>7</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="F198" s="1" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="199" ht="15" customHeight="1" spans="1:6">
@@ -5864,10 +5878,10 @@
         <v>7</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="F199" s="1" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="200" ht="15" customHeight="1" spans="1:6">
@@ -5880,10 +5894,10 @@
         <v>7</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="F200" s="1" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="201" ht="15" customHeight="1" spans="1:6">
@@ -5896,10 +5910,10 @@
         <v>7</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="202" ht="15" customHeight="1" spans="1:6">
@@ -5912,10 +5926,10 @@
         <v>7</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="F202" s="1" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="203" ht="15" customHeight="1" spans="1:6">
@@ -5928,10 +5942,10 @@
         <v>7</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="F203" s="1" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="204" ht="15" customHeight="1" spans="1:6">
@@ -5944,10 +5958,10 @@
         <v>7</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="F204" s="1" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="205" ht="15" customHeight="1" spans="1:6">
@@ -5960,10 +5974,10 @@
         <v>7</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="F205" s="1" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="206" ht="15" customHeight="1" spans="1:6">
@@ -5976,10 +5990,10 @@
         <v>7</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="F206" s="1" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="207" ht="15" customHeight="1" spans="1:6">
@@ -5992,10 +6006,10 @@
         <v>7</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F207" s="1" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="208" ht="15" customHeight="1" spans="1:6">
@@ -6008,10 +6022,10 @@
         <v>7</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F208" s="1" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="209" ht="15" customHeight="1" spans="1:6">
@@ -6024,10 +6038,10 @@
         <v>7</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="F209" s="1" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="210" ht="15" customHeight="1" spans="1:6">
@@ -6040,10 +6054,10 @@
         <v>7</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="F210" s="1" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="211" ht="15" customHeight="1" spans="1:6">
@@ -6056,10 +6070,10 @@
         <v>7</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="F211" s="1" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="212" ht="15" customHeight="1" spans="1:6">
@@ -6072,10 +6086,10 @@
         <v>7</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="F212" s="1" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="213" ht="15" customHeight="1" spans="1:6">
@@ -6088,10 +6102,10 @@
         <v>7</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="214" ht="15" customHeight="1" spans="1:6">
@@ -6104,10 +6118,10 @@
         <v>7</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="F214" s="1" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="215" ht="15" customHeight="1" spans="1:6">
@@ -6120,10 +6134,10 @@
         <v>7</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="F215" s="1" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="216" ht="15" customHeight="1" spans="1:6">
@@ -6136,10 +6150,10 @@
         <v>7</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="F216" s="1" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="217" ht="15" customHeight="1" spans="1:6">
@@ -6152,10 +6166,10 @@
         <v>7</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="F217" s="1" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="218" ht="15" customHeight="1" spans="1:6">
@@ -6168,10 +6182,10 @@
         <v>7</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="F218" s="1" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="219" ht="15" customHeight="1" spans="1:6">
@@ -6184,10 +6198,10 @@
         <v>7</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="F219" s="1" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="220" ht="15" customHeight="1" spans="1:6">
@@ -6200,10 +6214,10 @@
         <v>7</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="221" ht="15" customHeight="1" spans="1:6">
@@ -6216,10 +6230,10 @@
         <v>7</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="F221" s="1" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="222" ht="15" customHeight="1" spans="1:6">
@@ -6232,10 +6246,10 @@
         <v>7</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="F222" s="1" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="223" ht="15" customHeight="1" spans="1:6">
@@ -6248,10 +6262,10 @@
         <v>7</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="F223" s="1" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="224" ht="15" customHeight="1" spans="1:6">
@@ -6264,10 +6278,10 @@
         <v>7</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="F224" s="1" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="225" ht="15" customHeight="1" spans="1:6">
@@ -6280,10 +6294,10 @@
         <v>7</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="F225" s="1" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="226" ht="15" customHeight="1" spans="1:6">
@@ -6296,10 +6310,10 @@
         <v>7</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="F226" s="1" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="227" ht="15" customHeight="1" spans="1:6">
@@ -6312,10 +6326,10 @@
         <v>7</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="228" ht="15" customHeight="1" spans="1:6">
@@ -6328,10 +6342,10 @@
         <v>7</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="F228" s="1" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="229" ht="15" customHeight="1" spans="1:6">
@@ -6344,10 +6358,10 @@
         <v>7</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="F229" s="1" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="230" ht="15" customHeight="1" spans="1:6">
@@ -6360,10 +6374,10 @@
         <v>7</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="F230" s="1" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="231" ht="15" customHeight="1" spans="1:6">
@@ -6376,10 +6390,10 @@
         <v>7</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="F231" s="1" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="232" ht="15" customHeight="1" spans="1:6">
@@ -6392,10 +6406,10 @@
         <v>7</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="F232" s="1" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="233" ht="15" customHeight="1" spans="1:6">
@@ -6408,10 +6422,10 @@
         <v>7</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="F233" s="1" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="234" ht="15" customHeight="1" spans="1:6">
@@ -6424,10 +6438,10 @@
         <v>7</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="F234" s="1" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="235" ht="15" customHeight="1" spans="1:6">
@@ -6440,10 +6454,10 @@
         <v>7</v>
       </c>
       <c r="E235" s="1" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="F235" s="1" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="236" ht="15" customHeight="1" spans="1:6">
@@ -6456,10 +6470,10 @@
         <v>7</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="F236" s="1" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="237" ht="15" customHeight="1" spans="1:6">
@@ -6472,10 +6486,10 @@
         <v>7</v>
       </c>
       <c r="E237" s="1" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="F237" s="1" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="238" ht="15" customHeight="1" spans="1:6">
@@ -6488,10 +6502,10 @@
         <v>7</v>
       </c>
       <c r="E238" s="1" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="F238" s="1" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="239" ht="15" customHeight="1" spans="1:6">
@@ -6504,10 +6518,10 @@
         <v>7</v>
       </c>
       <c r="E239" s="1" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="F239" s="1" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="240" ht="15" customHeight="1" spans="1:6">
@@ -6520,10 +6534,10 @@
         <v>7</v>
       </c>
       <c r="E240" s="1" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="F240" s="1" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="241" ht="15" customHeight="1" spans="1:6">
@@ -6536,10 +6550,10 @@
         <v>7</v>
       </c>
       <c r="E241" s="1" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="F241" s="1" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="242" ht="15" customHeight="1" spans="1:6">
@@ -6552,10 +6566,10 @@
         <v>7</v>
       </c>
       <c r="E242" s="1" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="F242" s="1" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="243" ht="15" customHeight="1" spans="1:6">
@@ -6568,10 +6582,10 @@
         <v>7</v>
       </c>
       <c r="E243" s="1" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="F243" s="1" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="244" ht="15" customHeight="1" spans="1:6">
@@ -6584,10 +6598,10 @@
         <v>7</v>
       </c>
       <c r="E244" s="1" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="F244" s="1" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="245" ht="15" customHeight="1" spans="1:6">
@@ -6600,10 +6614,10 @@
         <v>7</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="F245" s="1" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="246" ht="15" customHeight="1" spans="1:6">
@@ -6616,10 +6630,10 @@
         <v>7</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="F246" s="1" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
     </row>
     <row r="247" ht="15" customHeight="1" spans="1:6">
@@ -6632,10 +6646,10 @@
         <v>7</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="F247" s="1" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="248" ht="15" customHeight="1" spans="1:6">
@@ -6648,10 +6662,10 @@
         <v>7</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="F248" s="1" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
     </row>
     <row r="249" ht="15" customHeight="1" spans="1:6">
@@ -6664,10 +6678,10 @@
         <v>7</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="F249" s="1" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="250" ht="15" customHeight="1" spans="1:6">
@@ -6680,10 +6694,10 @@
         <v>7</v>
       </c>
       <c r="E250" s="1" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="F250" s="1" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="251" ht="15" customHeight="1" spans="1:6">
@@ -6696,10 +6710,10 @@
         <v>7</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="F251" s="1" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
     </row>
     <row r="252" ht="15" customHeight="1" spans="1:6">
@@ -6712,10 +6726,10 @@
         <v>7</v>
       </c>
       <c r="E252" s="1" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="F252" s="1" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
     </row>
     <row r="253" ht="15" customHeight="1" spans="1:6">
@@ -6728,10 +6742,10 @@
         <v>7</v>
       </c>
       <c r="E253" s="1" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="F253" s="1" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="254" ht="15" customHeight="1" spans="1:6">
@@ -6744,10 +6758,10 @@
         <v>7</v>
       </c>
       <c r="E254" s="1" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="F254" s="1" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="255" ht="15" customHeight="1" spans="1:6">
@@ -6760,10 +6774,10 @@
         <v>7</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="F255" s="1" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="256" ht="15" customHeight="1" spans="1:6">
@@ -6776,10 +6790,10 @@
         <v>7</v>
       </c>
       <c r="E256" s="1" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="F256" s="1" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
     </row>
     <row r="257" ht="15" customHeight="1" spans="1:6">
@@ -6792,10 +6806,10 @@
         <v>7</v>
       </c>
       <c r="E257" s="1" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="F257" s="1" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
     </row>
     <row r="258" ht="15" customHeight="1" spans="1:6">
@@ -6808,10 +6822,10 @@
         <v>7</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="F258" s="1" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="259" ht="15" customHeight="1" spans="1:6">
@@ -6824,10 +6838,10 @@
         <v>7</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="F259" s="1" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
     </row>
     <row r="260" ht="15" customHeight="1" spans="1:6">
@@ -6840,10 +6854,10 @@
         <v>7</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="F260" s="1" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
     </row>
     <row r="261" ht="15" customHeight="1" spans="1:6">
@@ -6856,10 +6870,10 @@
         <v>7</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="F261" s="1" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
     </row>
     <row r="262" ht="15" customHeight="1" spans="1:6">
@@ -6872,10 +6886,10 @@
         <v>7</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="F262" s="1" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
     </row>
     <row r="263" ht="15" customHeight="1" spans="1:6">
@@ -6888,10 +6902,10 @@
         <v>7</v>
       </c>
       <c r="E263" s="1" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="F263" s="1" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
     </row>
     <row r="264" ht="15" customHeight="1" spans="1:6">
@@ -6904,10 +6918,10 @@
         <v>7</v>
       </c>
       <c r="E264" s="1" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="F264" s="1" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
     </row>
     <row r="265" ht="15" customHeight="1" spans="1:6">
@@ -6920,10 +6934,10 @@
         <v>7</v>
       </c>
       <c r="E265" s="1" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="F265" s="1" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
     </row>
     <row r="266" ht="15" customHeight="1" spans="1:6">
@@ -6936,10 +6950,10 @@
         <v>7</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="F266" s="1" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
     </row>
     <row r="267" ht="15" customHeight="1" spans="1:6">
@@ -6952,10 +6966,10 @@
         <v>7</v>
       </c>
       <c r="E267" s="1" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="F267" s="1" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
     </row>
     <row r="268" ht="15" customHeight="1" spans="1:6">
@@ -6968,10 +6982,10 @@
         <v>7</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="F268" s="1" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="269" ht="15" customHeight="1" spans="1:6">
@@ -6984,10 +6998,10 @@
         <v>7</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="F269" s="1" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
     </row>
     <row r="270" ht="15" customHeight="1" spans="1:6">
@@ -7000,10 +7014,10 @@
         <v>7</v>
       </c>
       <c r="E270" s="1" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="F270" s="1" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
     </row>
     <row r="271" ht="15" customHeight="1" spans="1:6">
@@ -7016,10 +7030,10 @@
         <v>7</v>
       </c>
       <c r="E271" s="1" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="F271" s="1" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
     </row>
     <row r="272" ht="15" customHeight="1" spans="1:6">
@@ -7032,10 +7046,10 @@
         <v>7</v>
       </c>
       <c r="E272" s="1" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="F272" s="1" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
     </row>
     <row r="273" ht="15" customHeight="1" spans="1:6">
@@ -7048,10 +7062,10 @@
         <v>7</v>
       </c>
       <c r="E273" s="1" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="F273" s="1" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
     </row>
     <row r="274" ht="15" customHeight="1" spans="1:6">
@@ -7064,10 +7078,10 @@
         <v>7</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="F274" s="1" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
     </row>
     <row r="275" ht="15" customHeight="1" spans="1:6">
@@ -7080,10 +7094,10 @@
         <v>7</v>
       </c>
       <c r="E275" s="1" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="F275" s="1" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
     </row>
     <row r="276" ht="15" customHeight="1" spans="1:6">
@@ -7096,10 +7110,10 @@
         <v>7</v>
       </c>
       <c r="E276" s="1" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="F276" s="1" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
     </row>
     <row r="277" ht="15" customHeight="1" spans="1:6">
@@ -7112,13 +7126,44 @@
         <v>7</v>
       </c>
       <c r="E277" s="1" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="F277" s="1" t="s">
-        <v>555</v>
+        <v>558</v>
+      </c>
+    </row>
+    <row r="278" spans="1:6">
+      <c r="B278">
+        <v>13001</v>
+      </c>
+      <c r="D278">
+        <v>1</v>
+      </c>
+      <c r="E278" t="s">
+        <v>559</v>
+      </c>
+      <c r="F278" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="279" spans="1:6">
+      <c r="B279">
+        <v>13004</v>
+      </c>
+      <c r="D279">
+        <v>1</v>
+      </c>
+      <c r="E279" t="s">
+        <v>561</v>
+      </c>
+      <c r="F279" t="s">
+        <v>562</v>
       </c>
     </row>
   </sheetData>
+  <sortState ref="A5:F277">
+    <sortCondition ref="B5:B277"/>
+  </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>

--- a/AAAGameData/DataTables/ResourceConfigTable.xlsx
+++ b/AAAGameData/DataTables/ResourceConfigTable.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F281"/>
+  <dimension ref="A1:F291"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1414,7 +1414,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" s="1" t="n"/>
       <c r="B49" s="1" t="n">
-        <v>1399</v>
+        <v>1310</v>
       </c>
       <c r="C49" s="1" t="n"/>
       <c r="D49" s="1" t="n">
@@ -1422,19 +1422,19 @@
       </c>
       <c r="E49" s="1" t="inlineStr">
         <is>
-          <t>Chess/靶子.png</t>
+          <t>Chess/邪灵/邪灵立绘.png</t>
         </is>
       </c>
       <c r="F49" s="1" t="inlineStr">
         <is>
-          <t>棋子-靶子图标</t>
+          <t>棋子-邪灵图标</t>
         </is>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1">
       <c r="A50" s="1" t="n"/>
       <c r="B50" s="1" t="n">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="C50" s="1" t="n"/>
       <c r="D50" s="1" t="n">
@@ -1442,19 +1442,19 @@
       </c>
       <c r="E50" s="1" t="inlineStr">
         <is>
-          <t>Buff/1.png</t>
+          <t>Chess/靶子.png</t>
         </is>
       </c>
       <c r="F50" s="1" t="inlineStr">
         <is>
-          <t>灼烧Buff图标</t>
+          <t>棋子-靶子图标</t>
         </is>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1">
       <c r="A51" s="1" t="n"/>
       <c r="B51" s="1" t="n">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="C51" s="1" t="n"/>
       <c r="D51" s="1" t="n">
@@ -1462,19 +1462,19 @@
       </c>
       <c r="E51" s="1" t="inlineStr">
         <is>
-          <t>Buff/2.png</t>
+          <t>Buff/1.png</t>
         </is>
       </c>
       <c r="F51" s="1" t="inlineStr">
         <is>
-          <t>寒霜Buff图标</t>
+          <t>灼烧Buff图标</t>
         </is>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1">
       <c r="A52" s="1" t="n"/>
       <c r="B52" s="1" t="n">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="C52" s="1" t="n"/>
       <c r="D52" s="1" t="n">
@@ -1482,19 +1482,19 @@
       </c>
       <c r="E52" s="1" t="inlineStr">
         <is>
-          <t>Buff/3.png</t>
+          <t>Buff/2.png</t>
         </is>
       </c>
       <c r="F52" s="1" t="inlineStr">
         <is>
-          <t>融化Buff图标</t>
+          <t>寒霜Buff图标</t>
         </is>
       </c>
     </row>
     <row r="53" ht="15" customHeight="1">
       <c r="A53" s="1" t="n"/>
       <c r="B53" s="1" t="n">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="C53" s="1" t="n"/>
       <c r="D53" s="1" t="n">
@@ -1502,19 +1502,19 @@
       </c>
       <c r="E53" s="1" t="inlineStr">
         <is>
-          <t>Buff/4.png</t>
+          <t>Buff/3.png</t>
         </is>
       </c>
       <c r="F53" s="1" t="inlineStr">
         <is>
-          <t>神力增益Buff图标</t>
+          <t>融化Buff图标</t>
         </is>
       </c>
     </row>
     <row r="54" ht="15" customHeight="1">
       <c r="A54" s="1" t="n"/>
       <c r="B54" s="1" t="n">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="C54" s="1" t="n"/>
       <c r="D54" s="1" t="n">
@@ -1522,19 +1522,19 @@
       </c>
       <c r="E54" s="1" t="inlineStr">
         <is>
-          <t>Buff/5.png</t>
+          <t>Buff/4.png</t>
         </is>
       </c>
       <c r="F54" s="1" t="inlineStr">
         <is>
-          <t>日落长弓Buff图标</t>
+          <t>神力增益Buff图标</t>
         </is>
       </c>
     </row>
     <row r="55" ht="15" customHeight="1">
       <c r="A55" s="1" t="n"/>
       <c r="B55" s="1" t="n">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="C55" s="1" t="n"/>
       <c r="D55" s="1" t="n">
@@ -1542,19 +1542,19 @@
       </c>
       <c r="E55" s="1" t="inlineStr">
         <is>
-          <t>Buff/6.png</t>
+          <t>Buff/5.png</t>
         </is>
       </c>
       <c r="F55" s="1" t="inlineStr">
         <is>
-          <t>九天玄冰Buff图标</t>
+          <t>日落长弓Buff图标</t>
         </is>
       </c>
     </row>
     <row r="56" ht="15" customHeight="1">
       <c r="A56" s="1" t="n"/>
       <c r="B56" s="1" t="n">
-        <v>1501</v>
+        <v>1406</v>
       </c>
       <c r="C56" s="1" t="n"/>
       <c r="D56" s="1" t="n">
@@ -1562,19 +1562,19 @@
       </c>
       <c r="E56" s="1" t="inlineStr">
         <is>
-          <t>UI/Icons/Skill_Dash.png</t>
+          <t>Buff/6.png</t>
         </is>
       </c>
       <c r="F56" s="1" t="inlineStr">
         <is>
-          <t>飞雷神-角色技能图标</t>
+          <t>九天玄冰Buff图标</t>
         </is>
       </c>
     </row>
     <row r="57" ht="15" customHeight="1">
       <c r="A57" s="1" t="n"/>
       <c r="B57" s="1" t="n">
-        <v>1502</v>
+        <v>1407</v>
       </c>
       <c r="C57" s="1" t="n"/>
       <c r="D57" s="1" t="n">
@@ -1582,19 +1582,19 @@
       </c>
       <c r="E57" s="1" t="inlineStr">
         <is>
-          <t>UI/Icons/Skill_Heal.png</t>
+          <t>Buff/7.png</t>
         </is>
       </c>
       <c r="F57" s="1" t="inlineStr">
         <is>
-          <t>治疗术-角色技能图标</t>
+          <t>腐蚀Buff图标</t>
         </is>
       </c>
     </row>
     <row r="58" ht="15" customHeight="1">
       <c r="A58" s="1" t="n"/>
       <c r="B58" s="1" t="n">
-        <v>1503</v>
+        <v>1408</v>
       </c>
       <c r="C58" s="1" t="n"/>
       <c r="D58" s="1" t="n">
@@ -1602,19 +1602,19 @@
       </c>
       <c r="E58" s="1" t="inlineStr">
         <is>
-          <t>UI/Icons/Skill_Bomb.png</t>
+          <t>Buff/8.png</t>
         </is>
       </c>
       <c r="F58" s="1" t="inlineStr">
         <is>
-          <t>爆裂弹-角色技能图标</t>
+          <t>黑暗狂暴Buff图标</t>
         </is>
       </c>
     </row>
     <row r="59" ht="15" customHeight="1">
       <c r="A59" s="1" t="n"/>
       <c r="B59" s="1" t="n">
-        <v>1601</v>
+        <v>1409</v>
       </c>
       <c r="C59" s="1" t="n"/>
       <c r="D59" s="1" t="n">
@@ -1622,19 +1622,19 @@
       </c>
       <c r="E59" s="1" t="inlineStr">
         <is>
-          <t>Equipment/SunsetBow.png</t>
+          <t>Buff/9.png</t>
         </is>
       </c>
       <c r="F59" s="1" t="inlineStr">
         <is>
-          <t>落日弓-棋子装备图标</t>
+          <t>恐惧Buff图标</t>
         </is>
       </c>
     </row>
     <row r="60" ht="15" customHeight="1">
       <c r="A60" s="1" t="n"/>
       <c r="B60" s="1" t="n">
-        <v>1701</v>
+        <v>1501</v>
       </c>
       <c r="C60" s="1" t="n"/>
       <c r="D60" s="1" t="n">
@@ -1642,19 +1642,19 @@
       </c>
       <c r="E60" s="1" t="inlineStr">
         <is>
-          <t>Summoner/Skill/狂怒之心技能.png</t>
+          <t>UI/Icons/Skill_Dash.png</t>
         </is>
       </c>
       <c r="F60" s="1" t="inlineStr">
         <is>
-          <t>狂怒之心-召唤师技能图标</t>
+          <t>飞雷神-角色技能图标</t>
         </is>
       </c>
     </row>
     <row r="61" ht="15" customHeight="1">
       <c r="A61" s="1" t="n"/>
       <c r="B61" s="1" t="n">
-        <v>1702</v>
+        <v>1502</v>
       </c>
       <c r="C61" s="1" t="n"/>
       <c r="D61" s="1" t="n">
@@ -1662,19 +1662,19 @@
       </c>
       <c r="E61" s="1" t="inlineStr">
         <is>
-          <t>Summoner/Skill/战意激昂技能.png</t>
+          <t>UI/Icons/Skill_Heal.png</t>
         </is>
       </c>
       <c r="F61" s="1" t="inlineStr">
         <is>
-          <t>战意激昂-召唤师技能图标</t>
+          <t>治疗术-角色技能图标</t>
         </is>
       </c>
     </row>
     <row r="62" ht="15" customHeight="1">
       <c r="A62" s="1" t="n"/>
       <c r="B62" s="1" t="n">
-        <v>1703</v>
+        <v>1503</v>
       </c>
       <c r="C62" s="1" t="n"/>
       <c r="D62" s="1" t="n">
@@ -1682,19 +1682,19 @@
       </c>
       <c r="E62" s="1" t="inlineStr">
         <is>
-          <t>Summoner/Skill/王者号令技能.png</t>
+          <t>UI/Icons/Skill_Bomb.png</t>
         </is>
       </c>
       <c r="F62" s="1" t="inlineStr">
         <is>
-          <t>王者号令-召唤师技能图标</t>
+          <t>爆裂弹-角色技能图标</t>
         </is>
       </c>
     </row>
     <row r="63" ht="15" customHeight="1">
       <c r="A63" s="1" t="n"/>
       <c r="B63" s="1" t="n">
-        <v>1704</v>
+        <v>1601</v>
       </c>
       <c r="C63" s="1" t="n"/>
       <c r="D63" s="1" t="n">
@@ -1702,19 +1702,19 @@
       </c>
       <c r="E63" s="1" t="inlineStr">
         <is>
-          <t>Summoner/Skill/钢铁洪流技能.png</t>
+          <t>Equipment/SunsetBow.png</t>
         </is>
       </c>
       <c r="F63" s="1" t="inlineStr">
         <is>
-          <t>钢铁洪流-召唤师技能图标</t>
+          <t>落日弓-棋子装备图标</t>
         </is>
       </c>
     </row>
     <row r="64" ht="15" customHeight="1">
       <c r="A64" s="1" t="n"/>
       <c r="B64" s="1" t="n">
-        <v>1705</v>
+        <v>1701</v>
       </c>
       <c r="C64" s="1" t="n"/>
       <c r="D64" s="1" t="n">
@@ -1722,19 +1722,19 @@
       </c>
       <c r="E64" s="1" t="inlineStr">
         <is>
-          <t>Summoner/Skill/天灾降临技能.png</t>
+          <t>Summoner/Skill/狂怒之心技能.png</t>
         </is>
       </c>
       <c r="F64" s="1" t="inlineStr">
         <is>
-          <t>天灾降临-召唤师技能图标</t>
+          <t>狂怒之心-召唤师技能图标</t>
         </is>
       </c>
     </row>
     <row r="65" ht="15" customHeight="1">
       <c r="A65" s="1" t="n"/>
       <c r="B65" s="1" t="n">
-        <v>1706</v>
+        <v>1702</v>
       </c>
       <c r="C65" s="1" t="n"/>
       <c r="D65" s="1" t="n">
@@ -1742,19 +1742,19 @@
       </c>
       <c r="E65" s="1" t="inlineStr">
         <is>
-          <t>Summoner/Skill/寂灭斩技能.png</t>
+          <t>Summoner/Skill/战意激昂技能.png</t>
         </is>
       </c>
       <c r="F65" s="1" t="inlineStr">
         <is>
-          <t>寂灭斩-召唤师技能图标</t>
+          <t>战意激昂-召唤师技能图标</t>
         </is>
       </c>
     </row>
     <row r="66" ht="15" customHeight="1">
       <c r="A66" s="1" t="n"/>
       <c r="B66" s="1" t="n">
-        <v>1707</v>
+        <v>1703</v>
       </c>
       <c r="C66" s="1" t="n"/>
       <c r="D66" s="1" t="n">
@@ -1762,19 +1762,19 @@
       </c>
       <c r="E66" s="1" t="inlineStr">
         <is>
-          <t>Summoner/Skill/孤影技能.png</t>
+          <t>Summoner/Skill/王者号令技能.png</t>
         </is>
       </c>
       <c r="F66" s="1" t="inlineStr">
         <is>
-          <t>孤影-召唤师技能图标</t>
+          <t>王者号令-召唤师技能图标</t>
         </is>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1">
       <c r="A67" s="1" t="n"/>
       <c r="B67" s="1" t="n">
-        <v>1708</v>
+        <v>1704</v>
       </c>
       <c r="C67" s="1" t="n"/>
       <c r="D67" s="1" t="n">
@@ -1782,19 +1782,19 @@
       </c>
       <c r="E67" s="1" t="inlineStr">
         <is>
-          <t>Summoner/Skill/裁决之刻技能.png</t>
+          <t>Summoner/Skill/钢铁洪流技能.png</t>
         </is>
       </c>
       <c r="F67" s="1" t="inlineStr">
         <is>
-          <t>裁决之刻-召唤师技能图标</t>
+          <t>钢铁洪流-召唤师技能图标</t>
         </is>
       </c>
     </row>
     <row r="68" ht="15" customHeight="1">
       <c r="A68" s="1" t="n"/>
       <c r="B68" s="1" t="n">
-        <v>1711</v>
+        <v>1705</v>
       </c>
       <c r="C68" s="1" t="n"/>
       <c r="D68" s="1" t="n">
@@ -1802,19 +1802,19 @@
       </c>
       <c r="E68" s="1" t="inlineStr">
         <is>
-          <t>Summoner/Skill/暗影咒体技能.png</t>
+          <t>Summoner/Skill/天灾降临技能.png</t>
         </is>
       </c>
       <c r="F68" s="1" t="inlineStr">
         <is>
-          <t>暗影咒体-召唤师技能图标</t>
+          <t>天灾降临-召唤师技能图标</t>
         </is>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1">
       <c r="A69" s="1" t="n"/>
       <c r="B69" s="1" t="n">
-        <v>1712</v>
+        <v>1706</v>
       </c>
       <c r="C69" s="1" t="n"/>
       <c r="D69" s="1" t="n">
@@ -1822,19 +1822,19 @@
       </c>
       <c r="E69" s="1" t="inlineStr">
         <is>
-          <t>Summoner/Skill/生命虹吸技能.png</t>
+          <t>Summoner/Skill/寂灭斩技能.png</t>
         </is>
       </c>
       <c r="F69" s="1" t="inlineStr">
         <is>
-          <t>生命虹吸-召唤师技能图标</t>
+          <t>寂灭斩-召唤师技能图标</t>
         </is>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1">
       <c r="A70" s="1" t="n"/>
       <c r="B70" s="1" t="n">
-        <v>1801</v>
+        <v>1707</v>
       </c>
       <c r="C70" s="1" t="n"/>
       <c r="D70" s="1" t="n">
@@ -1842,19 +1842,19 @@
       </c>
       <c r="E70" s="1" t="inlineStr">
         <is>
-          <t>Skill/1.png</t>
+          <t>Summoner/Skill/孤影技能.png</t>
         </is>
       </c>
       <c r="F70" s="1" t="inlineStr">
         <is>
-          <t>日落长弓-后羿技能图标</t>
+          <t>孤影-召唤师技能图标</t>
         </is>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1">
       <c r="A71" s="1" t="n"/>
       <c r="B71" s="1" t="n">
-        <v>1802</v>
+        <v>1708</v>
       </c>
       <c r="C71" s="1" t="n"/>
       <c r="D71" s="1" t="n">
@@ -1862,19 +1862,19 @@
       </c>
       <c r="E71" s="1" t="inlineStr">
         <is>
-          <t>Skill/2.png</t>
+          <t>Summoner/Skill/裁决之刻技能.png</t>
         </is>
       </c>
       <c r="F71" s="1" t="inlineStr">
         <is>
-          <t>后羿普攻-后羿技能图标</t>
+          <t>裁决之刻-召唤师技能图标</t>
         </is>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1">
       <c r="A72" s="1" t="n"/>
       <c r="B72" s="1" t="n">
-        <v>1803</v>
+        <v>1711</v>
       </c>
       <c r="C72" s="1" t="n"/>
       <c r="D72" s="1" t="n">
@@ -1882,19 +1882,19 @@
       </c>
       <c r="E72" s="1" t="inlineStr">
         <is>
-          <t>Skill/3.png</t>
+          <t>Summoner/Skill/暗影咒体技能.png</t>
         </is>
       </c>
       <c r="F72" s="1" t="inlineStr">
         <is>
-          <t>神力-后羿技能图标</t>
+          <t>暗影咒体-召唤师技能图标</t>
         </is>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1">
       <c r="A73" s="1" t="n"/>
       <c r="B73" s="1" t="n">
-        <v>1804</v>
+        <v>1712</v>
       </c>
       <c r="C73" s="1" t="n"/>
       <c r="D73" s="1" t="n">
@@ -1902,19 +1902,19 @@
       </c>
       <c r="E73" s="1" t="inlineStr">
         <is>
-          <t>Skill/4.png</t>
+          <t>Summoner/Skill/生命虹吸技能.png</t>
         </is>
       </c>
       <c r="F73" s="1" t="inlineStr">
         <is>
-          <t>日陨-后羿技能图标</t>
+          <t>生命虹吸-召唤师技能图标</t>
         </is>
       </c>
     </row>
     <row r="74" ht="15" customHeight="1">
       <c r="A74" s="1" t="n"/>
       <c r="B74" s="1" t="n">
-        <v>1805</v>
+        <v>1801</v>
       </c>
       <c r="C74" s="1" t="n"/>
       <c r="D74" s="1" t="n">
@@ -1922,19 +1922,19 @@
       </c>
       <c r="E74" s="1" t="inlineStr">
         <is>
-          <t>Skill/5.png</t>
+          <t>Skill/1.png</t>
         </is>
       </c>
       <c r="F74" s="1" t="inlineStr">
         <is>
-          <t>九天玄冰-嫦娥技能图标</t>
+          <t>日落长弓-后羿技能图标</t>
         </is>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1">
       <c r="A75" s="1" t="n"/>
       <c r="B75" s="1" t="n">
-        <v>1806</v>
+        <v>1802</v>
       </c>
       <c r="C75" s="1" t="n"/>
       <c r="D75" s="1" t="n">
@@ -1942,19 +1942,19 @@
       </c>
       <c r="E75" s="1" t="inlineStr">
         <is>
-          <t>Skill/6.png</t>
+          <t>Skill/2.png</t>
         </is>
       </c>
       <c r="F75" s="1" t="inlineStr">
         <is>
-          <t>嫦娥普攻-嫦娥技能图标</t>
+          <t>后羿普攻-后羿技能图标</t>
         </is>
       </c>
     </row>
     <row r="76" ht="15" customHeight="1">
       <c r="A76" s="1" t="n"/>
       <c r="B76" s="1" t="n">
-        <v>1807</v>
+        <v>1803</v>
       </c>
       <c r="C76" s="1" t="n"/>
       <c r="D76" s="1" t="n">
@@ -1962,19 +1962,19 @@
       </c>
       <c r="E76" s="1" t="inlineStr">
         <is>
-          <t>Skill/7.png</t>
+          <t>Skill/3.png</t>
         </is>
       </c>
       <c r="F76" s="1" t="inlineStr">
         <is>
-          <t>朔月飞轮-嫦娥技能图标</t>
+          <t>神力-后羿技能图标</t>
         </is>
       </c>
     </row>
     <row r="77" ht="15" customHeight="1">
       <c r="A77" s="1" t="n"/>
       <c r="B77" s="1" t="n">
-        <v>1808</v>
+        <v>1804</v>
       </c>
       <c r="C77" s="1" t="n"/>
       <c r="D77" s="1" t="n">
@@ -1982,19 +1982,19 @@
       </c>
       <c r="E77" s="1" t="inlineStr">
         <is>
-          <t>Skill/8.png</t>
+          <t>Skill/4.png</t>
         </is>
       </c>
       <c r="F77" s="1" t="inlineStr">
         <is>
-          <t>月华天倾-嫦娥技能图标</t>
+          <t>日陨-后羿技能图标</t>
         </is>
       </c>
     </row>
     <row r="78" ht="15" customHeight="1">
       <c r="A78" s="1" t="n"/>
       <c r="B78" s="1" t="n">
-        <v>1901</v>
+        <v>1805</v>
       </c>
       <c r="C78" s="1" t="n"/>
       <c r="D78" s="1" t="n">
@@ -2002,19 +2002,19 @@
       </c>
       <c r="E78" s="1" t="inlineStr">
         <is>
-          <t>Items/1.png</t>
+          <t>Skill/5.png</t>
         </is>
       </c>
       <c r="F78" s="1" t="inlineStr">
         <is>
-          <t>钱包图标</t>
+          <t>九天玄冰-嫦娥技能图标</t>
         </is>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1">
       <c r="A79" s="1" t="n"/>
       <c r="B79" s="1" t="n">
-        <v>1902</v>
+        <v>1806</v>
       </c>
       <c r="C79" s="1" t="n"/>
       <c r="D79" s="1" t="n">
@@ -2022,19 +2022,19 @@
       </c>
       <c r="E79" s="1" t="inlineStr">
         <is>
-          <t>Items/2.png</t>
+          <t>Skill/6.png</t>
         </is>
       </c>
       <c r="F79" s="1" t="inlineStr">
         <is>
-          <t>生命药水图标</t>
+          <t>嫦娥普攻-嫦娥技能图标</t>
         </is>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1">
       <c r="A80" s="1" t="n"/>
       <c r="B80" s="1" t="n">
-        <v>1903</v>
+        <v>1807</v>
       </c>
       <c r="C80" s="1" t="n"/>
       <c r="D80" s="1" t="n">
@@ -2042,19 +2042,19 @@
       </c>
       <c r="E80" s="1" t="inlineStr">
         <is>
-          <t>Items/3.png</t>
+          <t>Skill/7.png</t>
         </is>
       </c>
       <c r="F80" s="1" t="inlineStr">
         <is>
-          <t>魔法药水图标</t>
+          <t>朔月飞轮-嫦娥技能图标</t>
         </is>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1">
       <c r="A81" s="1" t="n"/>
       <c r="B81" s="1" t="n">
-        <v>1904</v>
+        <v>1808</v>
       </c>
       <c r="C81" s="1" t="n"/>
       <c r="D81" s="1" t="n">
@@ -2062,19 +2062,19 @@
       </c>
       <c r="E81" s="1" t="inlineStr">
         <is>
-          <t>Items/4.png</t>
+          <t>Skill/8.png</t>
         </is>
       </c>
       <c r="F81" s="1" t="inlineStr">
         <is>
-          <t>经验宝石图标</t>
+          <t>月华天倾-嫦娥技能图标</t>
         </is>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1">
       <c r="A82" s="1" t="n"/>
       <c r="B82" s="1" t="n">
-        <v>1905</v>
+        <v>1831</v>
       </c>
       <c r="C82" s="1" t="n"/>
       <c r="D82" s="1" t="n">
@@ -2082,19 +2082,19 @@
       </c>
       <c r="E82" s="1" t="inlineStr">
         <is>
-          <t>Items/5.png</t>
+          <t>Skill/31.png</t>
         </is>
       </c>
       <c r="F82" s="1" t="inlineStr">
         <is>
-          <t>神秘钥匙图标</t>
+          <t>黑暗侵染-邪灵技能图标</t>
         </is>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1">
       <c r="A83" s="1" t="n"/>
       <c r="B83" s="1" t="n">
-        <v>1906</v>
+        <v>1832</v>
       </c>
       <c r="C83" s="1" t="n"/>
       <c r="D83" s="1" t="n">
@@ -2102,19 +2102,19 @@
       </c>
       <c r="E83" s="1" t="inlineStr">
         <is>
-          <t>Items/6.png</t>
+          <t>Skill/32.png</t>
         </is>
       </c>
       <c r="F83" s="1" t="inlineStr">
         <is>
-          <t>古老卷轴图标</t>
+          <t>邪灵爪击-邪灵技能图标</t>
         </is>
       </c>
     </row>
     <row r="84" ht="15" customHeight="1">
       <c r="A84" s="1" t="n"/>
       <c r="B84" s="1" t="n">
-        <v>1907</v>
+        <v>1833</v>
       </c>
       <c r="C84" s="1" t="n"/>
       <c r="D84" s="1" t="n">
@@ -2122,19 +2122,19 @@
       </c>
       <c r="E84" s="1" t="inlineStr">
         <is>
-          <t>Items/7.png</t>
+          <t>Skill/33.png</t>
         </is>
       </c>
       <c r="F84" s="1" t="inlineStr">
         <is>
-          <t>八尺琼勾玉图标</t>
+          <t>污染斩击-邪灵技能图标</t>
         </is>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1">
       <c r="A85" s="1" t="n"/>
       <c r="B85" s="1" t="n">
-        <v>1908</v>
+        <v>1834</v>
       </c>
       <c r="C85" s="1" t="n"/>
       <c r="D85" s="1" t="n">
@@ -2142,19 +2142,19 @@
       </c>
       <c r="E85" s="1" t="inlineStr">
         <is>
-          <t>Items/8.png</t>
+          <t>Skill/34.png</t>
         </is>
       </c>
       <c r="F85" s="1" t="inlineStr">
         <is>
-          <t>天丛云剑图标</t>
+          <t>腐蚀法阵-邪灵技能图标</t>
         </is>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1">
       <c r="A86" s="1" t="n"/>
       <c r="B86" s="1" t="n">
-        <v>1909</v>
+        <v>1901</v>
       </c>
       <c r="C86" s="1" t="n"/>
       <c r="D86" s="1" t="n">
@@ -2162,19 +2162,19 @@
       </c>
       <c r="E86" s="1" t="inlineStr">
         <is>
-          <t>Items/9.png</t>
+          <t>Items/1.png</t>
         </is>
       </c>
       <c r="F86" s="1" t="inlineStr">
         <is>
-          <t>八咫镜图标</t>
+          <t>钱包图标</t>
         </is>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1">
       <c r="A87" s="1" t="n"/>
       <c r="B87" s="1" t="n">
-        <v>1910</v>
+        <v>1902</v>
       </c>
       <c r="C87" s="1" t="n"/>
       <c r="D87" s="1" t="n">
@@ -2182,19 +2182,19 @@
       </c>
       <c r="E87" s="1" t="inlineStr">
         <is>
-          <t>Items/10.png</t>
+          <t>Items/2.png</t>
         </is>
       </c>
       <c r="F87" s="1" t="inlineStr">
         <is>
-          <t>石中剑图标</t>
+          <t>生命药水图标</t>
         </is>
       </c>
     </row>
     <row r="88" ht="15" customHeight="1">
       <c r="A88" s="1" t="n"/>
       <c r="B88" s="1" t="n">
-        <v>1911</v>
+        <v>1903</v>
       </c>
       <c r="C88" s="1" t="n"/>
       <c r="D88" s="1" t="n">
@@ -2202,19 +2202,19 @@
       </c>
       <c r="E88" s="1" t="inlineStr">
         <is>
-          <t>Items/11.png</t>
+          <t>Items/3.png</t>
         </is>
       </c>
       <c r="F88" s="1" t="inlineStr">
         <is>
-          <t>龙鳞铠甲图标</t>
+          <t>魔法药水图标</t>
         </is>
       </c>
     </row>
     <row r="89" ht="15" customHeight="1">
       <c r="A89" s="1" t="n"/>
       <c r="B89" s="1" t="n">
-        <v>1912</v>
+        <v>1904</v>
       </c>
       <c r="C89" s="1" t="n"/>
       <c r="D89" s="1" t="n">
@@ -2222,19 +2222,19 @@
       </c>
       <c r="E89" s="1" t="inlineStr">
         <is>
-          <t>Items/12.png</t>
+          <t>Items/4.png</t>
         </is>
       </c>
       <c r="F89" s="1" t="inlineStr">
         <is>
-          <t>精灵之戒图标</t>
+          <t>经验宝石图标</t>
         </is>
       </c>
     </row>
     <row r="90" ht="15" customHeight="1">
       <c r="A90" s="1" t="n"/>
       <c r="B90" s="1" t="n">
-        <v>1913</v>
+        <v>1905</v>
       </c>
       <c r="C90" s="1" t="n"/>
       <c r="D90" s="1" t="n">
@@ -2242,19 +2242,19 @@
       </c>
       <c r="E90" s="1" t="inlineStr">
         <is>
-          <t>Items/13.png</t>
+          <t>Items/5.png</t>
         </is>
       </c>
       <c r="F90" s="1" t="inlineStr">
         <is>
-          <t>月华玉璧图标</t>
+          <t>神秘钥匙图标</t>
         </is>
       </c>
     </row>
     <row r="91" ht="15" customHeight="1">
       <c r="A91" s="1" t="n"/>
       <c r="B91" s="1" t="n">
-        <v>1914</v>
+        <v>1906</v>
       </c>
       <c r="C91" s="1" t="n"/>
       <c r="D91" s="1" t="n">
@@ -2262,19 +2262,19 @@
       </c>
       <c r="E91" s="1" t="inlineStr">
         <is>
-          <t>Items/14.png</t>
+          <t>Items/6.png</t>
         </is>
       </c>
       <c r="F91" s="1" t="inlineStr">
         <is>
-          <t>太阴弦月弓图标</t>
+          <t>古老卷轴图标</t>
         </is>
       </c>
     </row>
     <row r="92" ht="15" customHeight="1">
       <c r="A92" s="1" t="n"/>
       <c r="B92" s="1" t="n">
-        <v>1915</v>
+        <v>1907</v>
       </c>
       <c r="C92" s="1" t="n"/>
       <c r="D92" s="1" t="n">
@@ -2282,19 +2282,19 @@
       </c>
       <c r="E92" s="1" t="inlineStr">
         <is>
-          <t>Items/15.png</t>
+          <t>Items/7.png</t>
         </is>
       </c>
       <c r="F92" s="1" t="inlineStr">
         <is>
-          <t>月轮镜图标</t>
+          <t>八尺琼勾玉图标</t>
         </is>
       </c>
     </row>
     <row r="93" ht="15" customHeight="1">
       <c r="A93" s="1" t="n"/>
       <c r="B93" s="1" t="n">
-        <v>1916</v>
+        <v>1908</v>
       </c>
       <c r="C93" s="1" t="n"/>
       <c r="D93" s="1" t="n">
@@ -2302,19 +2302,19 @@
       </c>
       <c r="E93" s="1" t="inlineStr">
         <is>
-          <t>Items/16.png</t>
+          <t>Items/8.png</t>
         </is>
       </c>
       <c r="F93" s="1" t="inlineStr">
         <is>
-          <t>炎魔之心图标</t>
+          <t>天丛云剑图标</t>
         </is>
       </c>
     </row>
     <row r="94" ht="15" customHeight="1">
       <c r="A94" s="1" t="n"/>
       <c r="B94" s="1" t="n">
-        <v>1917</v>
+        <v>1909</v>
       </c>
       <c r="C94" s="1" t="n"/>
       <c r="D94" s="1" t="n">
@@ -2322,19 +2322,19 @@
       </c>
       <c r="E94" s="1" t="inlineStr">
         <is>
-          <t>Items/17.png</t>
+          <t>Items/9.png</t>
         </is>
       </c>
       <c r="F94" s="1" t="inlineStr">
         <is>
-          <t>炎魔之冠图标</t>
+          <t>八咫镜图标</t>
         </is>
       </c>
     </row>
     <row r="95" ht="15" customHeight="1">
       <c r="A95" s="1" t="n"/>
       <c r="B95" s="1" t="n">
-        <v>1918</v>
+        <v>1910</v>
       </c>
       <c r="C95" s="1" t="n"/>
       <c r="D95" s="1" t="n">
@@ -2342,19 +2342,19 @@
       </c>
       <c r="E95" s="1" t="inlineStr">
         <is>
-          <t>Items/18.png</t>
+          <t>Items/10.png</t>
         </is>
       </c>
       <c r="F95" s="1" t="inlineStr">
         <is>
-          <t>炎魔之剑图标</t>
+          <t>石中剑图标</t>
         </is>
       </c>
     </row>
     <row r="96" ht="15" customHeight="1">
       <c r="A96" s="1" t="n"/>
       <c r="B96" s="1" t="n">
-        <v>1919</v>
+        <v>1911</v>
       </c>
       <c r="C96" s="1" t="n"/>
       <c r="D96" s="1" t="n">
@@ -2362,19 +2362,19 @@
       </c>
       <c r="E96" s="1" t="inlineStr">
         <is>
-          <t>Items/19.png</t>
+          <t>Items/11.png</t>
         </is>
       </c>
       <c r="F96" s="1" t="inlineStr">
         <is>
-          <t>古剑·樱花落图标</t>
+          <t>龙鳞铠甲图标</t>
         </is>
       </c>
     </row>
     <row r="97" ht="15" customHeight="1">
       <c r="A97" s="1" t="n"/>
       <c r="B97" s="1" t="n">
-        <v>1920</v>
+        <v>1912</v>
       </c>
       <c r="C97" s="1" t="n"/>
       <c r="D97" s="1" t="n">
@@ -2382,19 +2382,19 @@
       </c>
       <c r="E97" s="1" t="inlineStr">
         <is>
-          <t>Items/20.png</t>
+          <t>Items/12.png</t>
         </is>
       </c>
       <c r="F97" s="1" t="inlineStr">
         <is>
-          <t>暗影斗篷图标</t>
+          <t>精灵之戒图标</t>
         </is>
       </c>
     </row>
     <row r="98" ht="15" customHeight="1">
       <c r="A98" s="1" t="n"/>
       <c r="B98" s="1" t="n">
-        <v>1921</v>
+        <v>1913</v>
       </c>
       <c r="C98" s="1" t="n"/>
       <c r="D98" s="1" t="n">
@@ -2402,19 +2402,19 @@
       </c>
       <c r="E98" s="1" t="inlineStr">
         <is>
-          <t>Items/21.png</t>
+          <t>Items/13.png</t>
         </is>
       </c>
       <c r="F98" s="1" t="inlineStr">
         <is>
-          <t>圣光铠甲图标</t>
+          <t>月华玉璧图标</t>
         </is>
       </c>
     </row>
     <row r="99" ht="15" customHeight="1">
       <c r="A99" s="1" t="n"/>
       <c r="B99" s="1" t="n">
-        <v>1922</v>
+        <v>1914</v>
       </c>
       <c r="C99" s="1" t="n"/>
       <c r="D99" s="1" t="n">
@@ -2422,19 +2422,19 @@
       </c>
       <c r="E99" s="1" t="inlineStr">
         <is>
-          <t>Items/22.png</t>
+          <t>Items/14.png</t>
         </is>
       </c>
       <c r="F99" s="1" t="inlineStr">
         <is>
-          <t>古墓盗贼手套图标</t>
+          <t>太阴弦月弓图标</t>
         </is>
       </c>
     </row>
     <row r="100" ht="15" customHeight="1">
       <c r="A100" s="1" t="n"/>
       <c r="B100" s="1" t="n">
-        <v>1923</v>
+        <v>1915</v>
       </c>
       <c r="C100" s="1" t="n"/>
       <c r="D100" s="1" t="n">
@@ -2442,19 +2442,19 @@
       </c>
       <c r="E100" s="1" t="inlineStr">
         <is>
-          <t>Items/23.png</t>
+          <t>Items/15.png</t>
         </is>
       </c>
       <c r="F100" s="1" t="inlineStr">
         <is>
-          <t>冰晶靴图标</t>
+          <t>月轮镜图标</t>
         </is>
       </c>
     </row>
     <row r="101" ht="15" customHeight="1">
       <c r="A101" s="1" t="n"/>
       <c r="B101" s="1" t="n">
-        <v>1924</v>
+        <v>1916</v>
       </c>
       <c r="C101" s="1" t="n"/>
       <c r="D101" s="1" t="n">
@@ -2462,19 +2462,19 @@
       </c>
       <c r="E101" s="1" t="inlineStr">
         <is>
-          <t>Items/24.png</t>
+          <t>Items/16.png</t>
         </is>
       </c>
       <c r="F101" s="1" t="inlineStr">
         <is>
-          <t>风暴法杖图标</t>
+          <t>炎魔之心图标</t>
         </is>
       </c>
     </row>
     <row r="102" ht="15" customHeight="1">
       <c r="A102" s="1" t="n"/>
       <c r="B102" s="1" t="n">
-        <v>1925</v>
+        <v>1917</v>
       </c>
       <c r="C102" s="1" t="n"/>
       <c r="D102" s="1" t="n">
@@ -2482,19 +2482,19 @@
       </c>
       <c r="E102" s="1" t="inlineStr">
         <is>
-          <t>Items/100.png</t>
+          <t>Items/17.png</t>
         </is>
       </c>
       <c r="F102" s="1" t="inlineStr">
         <is>
-          <t>卡牌-神圣庇护解锁物图标</t>
+          <t>炎魔之冠图标</t>
         </is>
       </c>
     </row>
     <row r="103" ht="15" customHeight="1">
       <c r="A103" s="1" t="n"/>
       <c r="B103" s="1" t="n">
-        <v>1926</v>
+        <v>1918</v>
       </c>
       <c r="C103" s="1" t="n"/>
       <c r="D103" s="1" t="n">
@@ -2502,19 +2502,19 @@
       </c>
       <c r="E103" s="1" t="inlineStr">
         <is>
-          <t>Items/101.png</t>
+          <t>Items/18.png</t>
         </is>
       </c>
       <c r="F103" s="1" t="inlineStr">
         <is>
-          <t>卡牌-烈焰风暴解锁物图标</t>
+          <t>炎魔之剑图标</t>
         </is>
       </c>
     </row>
     <row r="104" ht="15" customHeight="1">
       <c r="A104" s="1" t="n"/>
       <c r="B104" s="1" t="n">
-        <v>1927</v>
+        <v>1919</v>
       </c>
       <c r="C104" s="1" t="n"/>
       <c r="D104" s="1" t="n">
@@ -2522,19 +2522,19 @@
       </c>
       <c r="E104" s="1" t="inlineStr">
         <is>
-          <t>Items/102.png</t>
+          <t>Items/19.png</t>
         </is>
       </c>
       <c r="F104" s="1" t="inlineStr">
         <is>
-          <t>卡牌-时间回溯解锁物图标</t>
+          <t>古剑·樱花落图标</t>
         </is>
       </c>
     </row>
     <row r="105" ht="15" customHeight="1">
       <c r="A105" s="1" t="n"/>
       <c r="B105" s="1" t="n">
-        <v>1928</v>
+        <v>1920</v>
       </c>
       <c r="C105" s="1" t="n"/>
       <c r="D105" s="1" t="n">
@@ -2542,19 +2542,19 @@
       </c>
       <c r="E105" s="1" t="inlineStr">
         <is>
-          <t>Items/103.png</t>
+          <t>Items/20.png</t>
         </is>
       </c>
       <c r="F105" s="1" t="inlineStr">
         <is>
-          <t>卡牌-战争号角解锁物图标</t>
+          <t>暗影斗篷图标</t>
         </is>
       </c>
     </row>
     <row r="106" ht="15" customHeight="1">
       <c r="A106" s="1" t="n"/>
       <c r="B106" s="1" t="n">
-        <v>1929</v>
+        <v>1921</v>
       </c>
       <c r="C106" s="1" t="n"/>
       <c r="D106" s="1" t="n">
@@ -2562,19 +2562,19 @@
       </c>
       <c r="E106" s="1" t="inlineStr">
         <is>
-          <t>Items/104.png</t>
+          <t>Items/21.png</t>
         </is>
       </c>
       <c r="F106" s="1" t="inlineStr">
         <is>
-          <t>卡牌-暗影突袭解锁物图标</t>
+          <t>圣光铠甲图标</t>
         </is>
       </c>
     </row>
     <row r="107" ht="15" customHeight="1">
       <c r="A107" s="1" t="n"/>
       <c r="B107" s="1" t="n">
-        <v>1930</v>
+        <v>1922</v>
       </c>
       <c r="C107" s="1" t="n"/>
       <c r="D107" s="1" t="n">
@@ -2582,19 +2582,19 @@
       </c>
       <c r="E107" s="1" t="inlineStr">
         <is>
-          <t>Items/105.png</t>
+          <t>Items/22.png</t>
         </is>
       </c>
       <c r="F107" s="1" t="inlineStr">
         <is>
-          <t>卡牌-生命汲取解锁物图标</t>
+          <t>古墓盗贼手套图标</t>
         </is>
       </c>
     </row>
     <row r="108" ht="15" customHeight="1">
       <c r="A108" s="1" t="n"/>
       <c r="B108" s="1" t="n">
-        <v>1931</v>
+        <v>1923</v>
       </c>
       <c r="C108" s="1" t="n"/>
       <c r="D108" s="1" t="n">
@@ -2602,19 +2602,19 @@
       </c>
       <c r="E108" s="1" t="inlineStr">
         <is>
-          <t>Items/106.png</t>
+          <t>Items/23.png</t>
         </is>
       </c>
       <c r="F108" s="1" t="inlineStr">
         <is>
-          <t>卡牌-冰霜新星解锁物图标</t>
+          <t>冰晶靴图标</t>
         </is>
       </c>
     </row>
     <row r="109" ht="15" customHeight="1">
       <c r="A109" s="1" t="n"/>
       <c r="B109" s="1" t="n">
-        <v>1932</v>
+        <v>1924</v>
       </c>
       <c r="C109" s="1" t="n"/>
       <c r="D109" s="1" t="n">
@@ -2622,19 +2622,19 @@
       </c>
       <c r="E109" s="1" t="inlineStr">
         <is>
-          <t>Items/107.png</t>
+          <t>Items/24.png</t>
         </is>
       </c>
       <c r="F109" s="1" t="inlineStr">
         <is>
-          <t>卡牌-狂暴解锁物图标</t>
+          <t>风暴法杖图标</t>
         </is>
       </c>
     </row>
     <row r="110" ht="15" customHeight="1">
       <c r="A110" s="1" t="n"/>
       <c r="B110" s="1" t="n">
-        <v>1933</v>
+        <v>1925</v>
       </c>
       <c r="C110" s="1" t="n"/>
       <c r="D110" s="1" t="n">
@@ -2642,19 +2642,19 @@
       </c>
       <c r="E110" s="1" t="inlineStr">
         <is>
-          <t>Items/108.png</t>
+          <t>Items/100.png</t>
         </is>
       </c>
       <c r="F110" s="1" t="inlineStr">
         <is>
-          <t>卡牌-群体治疗解锁物图标</t>
+          <t>卡牌-神圣庇护解锁物图标</t>
         </is>
       </c>
     </row>
     <row r="111" ht="15" customHeight="1">
       <c r="A111" s="1" t="n"/>
       <c r="B111" s="1" t="n">
-        <v>1934</v>
+        <v>1926</v>
       </c>
       <c r="C111" s="1" t="n"/>
       <c r="D111" s="1" t="n">
@@ -2662,19 +2662,19 @@
       </c>
       <c r="E111" s="1" t="inlineStr">
         <is>
-          <t>Items/109.png</t>
+          <t>Items/101.png</t>
         </is>
       </c>
       <c r="F111" s="1" t="inlineStr">
         <is>
-          <t>卡牌-雷霆一击解锁物图标</t>
+          <t>卡牌-烈焰风暴解锁物图标</t>
         </is>
       </c>
     </row>
     <row r="112" ht="15" customHeight="1">
       <c r="A112" s="1" t="n"/>
       <c r="B112" s="1" t="n">
-        <v>1935</v>
+        <v>1927</v>
       </c>
       <c r="C112" s="1" t="n"/>
       <c r="D112" s="1" t="n">
@@ -2682,19 +2682,19 @@
       </c>
       <c r="E112" s="1" t="inlineStr">
         <is>
-          <t>Items/110.png</t>
+          <t>Items/102.png</t>
         </is>
       </c>
       <c r="F112" s="1" t="inlineStr">
         <is>
-          <t>卡牌-混乱诅咒解锁物图标</t>
+          <t>卡牌-时间回溯解锁物图标</t>
         </is>
       </c>
     </row>
     <row r="113" ht="15" customHeight="1">
       <c r="A113" s="1" t="n"/>
       <c r="B113" s="1" t="n">
-        <v>1936</v>
+        <v>1928</v>
       </c>
       <c r="C113" s="1" t="n"/>
       <c r="D113" s="1" t="n">
@@ -2702,19 +2702,19 @@
       </c>
       <c r="E113" s="1" t="inlineStr">
         <is>
-          <t>Items/111.png</t>
+          <t>Items/103.png</t>
         </is>
       </c>
       <c r="F113" s="1" t="inlineStr">
         <is>
-          <t>卡牌-不屈意志解锁物图标</t>
+          <t>卡牌-战争号角解锁物图标</t>
         </is>
       </c>
     </row>
     <row r="114" ht="15" customHeight="1">
       <c r="A114" s="1" t="n"/>
       <c r="B114" s="1" t="n">
-        <v>1937</v>
+        <v>1929</v>
       </c>
       <c r="C114" s="1" t="n"/>
       <c r="D114" s="1" t="n">
@@ -2722,19 +2722,19 @@
       </c>
       <c r="E114" s="1" t="inlineStr">
         <is>
-          <t>Items/112.png</t>
+          <t>Items/104.png</t>
         </is>
       </c>
       <c r="F114" s="1" t="inlineStr">
         <is>
-          <t>卡牌-反伤之盾解锁物图标</t>
+          <t>卡牌-暗影突袭解锁物图标</t>
         </is>
       </c>
     </row>
     <row r="115" ht="15" customHeight="1">
       <c r="A115" s="1" t="n"/>
       <c r="B115" s="1" t="n">
-        <v>1938</v>
+        <v>1930</v>
       </c>
       <c r="C115" s="1" t="n"/>
       <c r="D115" s="1" t="n">
@@ -2742,19 +2742,19 @@
       </c>
       <c r="E115" s="1" t="inlineStr">
         <is>
-          <t>Items/113.png</t>
+          <t>Items/105.png</t>
         </is>
       </c>
       <c r="F115" s="1" t="inlineStr">
         <is>
-          <t>卡牌-圣域防线解锁物图标</t>
+          <t>卡牌-生命汲取解锁物图标</t>
         </is>
       </c>
     </row>
     <row r="116" ht="15" customHeight="1">
       <c r="A116" s="1" t="n"/>
       <c r="B116" s="1" t="n">
-        <v>1939</v>
+        <v>1931</v>
       </c>
       <c r="C116" s="1" t="n"/>
       <c r="D116" s="1" t="n">
@@ -2762,19 +2762,19 @@
       </c>
       <c r="E116" s="1" t="inlineStr">
         <is>
-          <t>Items/114.png</t>
+          <t>Items/106.png</t>
         </is>
       </c>
       <c r="F116" s="1" t="inlineStr">
         <is>
-          <t>卡牌-护盾再生解锁物图标</t>
+          <t>卡牌-冰霜新星解锁物图标</t>
         </is>
       </c>
     </row>
     <row r="117" ht="15" customHeight="1">
       <c r="A117" s="1" t="n"/>
       <c r="B117" s="1" t="n">
-        <v>1940</v>
+        <v>1932</v>
       </c>
       <c r="C117" s="1" t="n"/>
       <c r="D117" s="1" t="n">
@@ -2782,19 +2782,19 @@
       </c>
       <c r="E117" s="1" t="inlineStr">
         <is>
-          <t>Items/115.png</t>
+          <t>Items/107.png</t>
         </is>
       </c>
       <c r="F117" s="1" t="inlineStr">
         <is>
-          <t>卡牌-救赎之光解锁物图标</t>
+          <t>卡牌-狂暴解锁物图标</t>
         </is>
       </c>
     </row>
     <row r="118" ht="15" customHeight="1">
       <c r="A118" s="1" t="n"/>
       <c r="B118" s="1" t="n">
-        <v>1941</v>
+        <v>1933</v>
       </c>
       <c r="C118" s="1" t="n"/>
       <c r="D118" s="1" t="n">
@@ -2802,19 +2802,19 @@
       </c>
       <c r="E118" s="1" t="inlineStr">
         <is>
-          <t>Items/116.png</t>
+          <t>Items/108.png</t>
         </is>
       </c>
       <c r="F118" s="1" t="inlineStr">
         <is>
-          <t>卡牌-血源强化解锁物图标</t>
+          <t>卡牌-群体治疗解锁物图标</t>
         </is>
       </c>
     </row>
     <row r="119" ht="15" customHeight="1">
       <c r="A119" s="1" t="n"/>
       <c r="B119" s="1" t="n">
-        <v>1942</v>
+        <v>1934</v>
       </c>
       <c r="C119" s="1" t="n"/>
       <c r="D119" s="1" t="n">
@@ -2822,19 +2822,19 @@
       </c>
       <c r="E119" s="1" t="inlineStr">
         <is>
-          <t>Items/117.png</t>
+          <t>Items/109.png</t>
         </is>
       </c>
       <c r="F119" s="1" t="inlineStr">
         <is>
-          <t>卡牌-吸血之刃解锁物图标</t>
+          <t>卡牌-雷霆一击解锁物图标</t>
         </is>
       </c>
     </row>
     <row r="120" ht="15" customHeight="1">
       <c r="A120" s="1" t="n"/>
       <c r="B120" s="1" t="n">
-        <v>1943</v>
+        <v>1935</v>
       </c>
       <c r="C120" s="1" t="n"/>
       <c r="D120" s="1" t="n">
@@ -2842,19 +2842,19 @@
       </c>
       <c r="E120" s="1" t="inlineStr">
         <is>
-          <t>Items/118.png</t>
+          <t>Items/110.png</t>
         </is>
       </c>
       <c r="F120" s="1" t="inlineStr">
         <is>
-          <t>卡牌-灾厄之雷解锁物图标</t>
+          <t>卡牌-混乱诅咒解锁物图标</t>
         </is>
       </c>
     </row>
     <row r="121" ht="15" customHeight="1">
       <c r="A121" s="1" t="n"/>
       <c r="B121" s="1" t="n">
-        <v>1944</v>
+        <v>1936</v>
       </c>
       <c r="C121" s="1" t="n"/>
       <c r="D121" s="1" t="n">
@@ -2862,19 +2862,19 @@
       </c>
       <c r="E121" s="1" t="inlineStr">
         <is>
-          <t>Items/119.png</t>
+          <t>Items/111.png</t>
         </is>
       </c>
       <c r="F121" s="1" t="inlineStr">
         <is>
-          <t>卡牌-护甲破碎解锁物图标</t>
+          <t>卡牌-不屈意志解锁物图标</t>
         </is>
       </c>
     </row>
     <row r="122" ht="15" customHeight="1">
       <c r="A122" s="1" t="n"/>
       <c r="B122" s="1" t="n">
-        <v>1945</v>
+        <v>1937</v>
       </c>
       <c r="C122" s="1" t="n"/>
       <c r="D122" s="1" t="n">
@@ -2882,19 +2882,19 @@
       </c>
       <c r="E122" s="1" t="inlineStr">
         <is>
-          <t>Items/120.png</t>
+          <t>Items/112.png</t>
         </is>
       </c>
       <c r="F122" s="1" t="inlineStr">
         <is>
-          <t>卡牌-虚弱诅咒解锁物图标</t>
+          <t>卡牌-反伤之盾解锁物图标</t>
         </is>
       </c>
     </row>
     <row r="123" ht="15" customHeight="1">
       <c r="A123" s="1" t="n"/>
       <c r="B123" s="1" t="n">
-        <v>1946</v>
+        <v>1938</v>
       </c>
       <c r="C123" s="1" t="n"/>
       <c r="D123" s="1" t="n">
@@ -2902,19 +2902,19 @@
       </c>
       <c r="E123" s="1" t="inlineStr">
         <is>
-          <t>Items/121.png</t>
+          <t>Items/113.png</t>
         </is>
       </c>
       <c r="F123" s="1" t="inlineStr">
         <is>
-          <t>卡牌-沉默之符解锁物图标</t>
+          <t>卡牌-圣域防线解锁物图标</t>
         </is>
       </c>
     </row>
     <row r="124" ht="15" customHeight="1">
       <c r="A124" s="1" t="n"/>
       <c r="B124" s="1" t="n">
-        <v>1947</v>
+        <v>1939</v>
       </c>
       <c r="C124" s="1" t="n"/>
       <c r="D124" s="1" t="n">
@@ -2922,19 +2922,19 @@
       </c>
       <c r="E124" s="1" t="inlineStr">
         <is>
-          <t>Items/122.png</t>
+          <t>Items/114.png</t>
         </is>
       </c>
       <c r="F124" s="1" t="inlineStr">
         <is>
-          <t>卡牌-嘲讽之声解锁物图标</t>
+          <t>卡牌-护盾再生解锁物图标</t>
         </is>
       </c>
     </row>
     <row r="125" ht="15" customHeight="1">
       <c r="A125" s="1" t="n"/>
       <c r="B125" s="1" t="n">
-        <v>1948</v>
+        <v>1940</v>
       </c>
       <c r="C125" s="1" t="n"/>
       <c r="D125" s="1" t="n">
@@ -2942,179 +2942,179 @@
       </c>
       <c r="E125" s="1" t="inlineStr">
         <is>
-          <t>Items/123.png</t>
+          <t>Items/115.png</t>
         </is>
       </c>
       <c r="F125" s="1" t="inlineStr">
         <is>
-          <t>卡牌-剧毒之雾解锁物图标</t>
+          <t>卡牌-救赎之光解锁物图标</t>
         </is>
       </c>
     </row>
     <row r="126" ht="15" customHeight="1">
       <c r="A126" s="1" t="n"/>
       <c r="B126" s="1" t="n">
-        <v>2001</v>
+        <v>1941</v>
       </c>
       <c r="C126" s="1" t="n"/>
       <c r="D126" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E126" s="1" t="inlineStr">
         <is>
-          <t>UI/CloudInfo/PlayerInfo</t>
+          <t>Items/116.png</t>
         </is>
       </c>
       <c r="F126" s="1" t="inlineStr">
         <is>
-          <t>角色信息预制体</t>
+          <t>卡牌-血源强化解锁物图标</t>
         </is>
       </c>
     </row>
     <row r="127" ht="15" customHeight="1">
       <c r="A127" s="1" t="n"/>
       <c r="B127" s="1" t="n">
-        <v>2002</v>
+        <v>1942</v>
       </c>
       <c r="C127" s="1" t="n"/>
       <c r="D127" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E127" s="1" t="inlineStr">
         <is>
-          <t>UI/CloudInfo/ItemsInfo</t>
+          <t>Items/117.png</t>
         </is>
       </c>
       <c r="F127" s="1" t="inlineStr">
         <is>
-          <t>仓库信息预制体</t>
+          <t>卡牌-吸血之刃解锁物图标</t>
         </is>
       </c>
     </row>
     <row r="128" ht="15" customHeight="1">
       <c r="A128" s="1" t="n"/>
       <c r="B128" s="1" t="n">
-        <v>2003</v>
+        <v>1943</v>
       </c>
       <c r="C128" s="1" t="n"/>
       <c r="D128" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E128" s="1" t="inlineStr">
         <is>
-          <t>UI/CloudInfo/TimeInfo</t>
+          <t>Items/118.png</t>
         </is>
       </c>
       <c r="F128" s="1" t="inlineStr">
         <is>
-          <t>存档时间预制体</t>
+          <t>卡牌-灾厄之雷解锁物图标</t>
         </is>
       </c>
     </row>
     <row r="129" ht="15" customHeight="1">
       <c r="A129" s="1" t="n"/>
       <c r="B129" s="1" t="n">
-        <v>2004</v>
+        <v>1944</v>
       </c>
       <c r="C129" s="1" t="n"/>
       <c r="D129" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E129" s="1" t="inlineStr">
         <is>
-          <t>UI/Items/SummonChessStateUI</t>
+          <t>Items/119.png</t>
         </is>
       </c>
       <c r="F129" s="1" t="inlineStr">
         <is>
-          <t>棋子状态UI预制体</t>
+          <t>卡牌-护甲破碎解锁物图标</t>
         </is>
       </c>
     </row>
     <row r="130" ht="15" customHeight="1">
       <c r="A130" s="1" t="n"/>
       <c r="B130" s="1" t="n">
-        <v>2101</v>
+        <v>1945</v>
       </c>
       <c r="C130" s="1" t="n"/>
       <c r="D130" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E130" s="1" t="inlineStr">
         <is>
-          <t>角色/召唤师/狂战士/狂战士_End</t>
+          <t>Items/120.png</t>
         </is>
       </c>
       <c r="F130" s="1" t="inlineStr">
         <is>
-          <t>狂战士</t>
+          <t>卡牌-虚弱诅咒解锁物图标</t>
         </is>
       </c>
     </row>
     <row r="131" ht="15" customHeight="1">
       <c r="A131" s="1" t="n"/>
       <c r="B131" s="1" t="n">
-        <v>2102</v>
+        <v>1946</v>
       </c>
       <c r="C131" s="1" t="n"/>
       <c r="D131" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E131" s="1" t="inlineStr">
         <is>
-          <t>角色/NPC/勇士End</t>
+          <t>Items/121.png</t>
         </is>
       </c>
       <c r="F131" s="1" t="inlineStr">
         <is>
-          <t>术士</t>
+          <t>卡牌-沉默之符解锁物图标</t>
         </is>
       </c>
     </row>
     <row r="132" ht="15" customHeight="1">
       <c r="A132" s="1" t="n"/>
       <c r="B132" s="1" t="n">
-        <v>2103</v>
+        <v>1947</v>
       </c>
       <c r="C132" s="1" t="n"/>
       <c r="D132" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E132" s="1" t="inlineStr">
         <is>
-          <t>角色/NPC/勇士End</t>
+          <t>Items/122.png</t>
         </is>
       </c>
       <c r="F132" s="1" t="inlineStr">
         <is>
-          <t>混沌</t>
+          <t>卡牌-嘲讽之声解锁物图标</t>
         </is>
       </c>
     </row>
     <row r="133" ht="15" customHeight="1">
       <c r="A133" s="1" t="n"/>
       <c r="B133" s="1" t="n">
-        <v>2104</v>
+        <v>1948</v>
       </c>
       <c r="C133" s="1" t="n"/>
       <c r="D133" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E133" s="1" t="inlineStr">
         <is>
-          <t>角色/NPC/勇士End</t>
+          <t>Items/123.png</t>
         </is>
       </c>
       <c r="F133" s="1" t="inlineStr">
         <is>
-          <t>德鲁伊</t>
+          <t>卡牌-剧毒之雾解锁物图标</t>
         </is>
       </c>
     </row>
     <row r="134" ht="15" customHeight="1">
       <c r="A134" s="1" t="n"/>
       <c r="B134" s="1" t="n">
-        <v>2201</v>
+        <v>2001</v>
       </c>
       <c r="C134" s="1" t="n"/>
       <c r="D134" s="1" t="n">
@@ -3122,19 +3122,19 @@
       </c>
       <c r="E134" s="1" t="inlineStr">
         <is>
-          <t>Items/DashItem</t>
+          <t>UI/CloudInfo/PlayerInfo</t>
         </is>
       </c>
       <c r="F134" s="1" t="inlineStr">
         <is>
-          <t>飞雷神道具预制体</t>
+          <t>角色信息预制体</t>
         </is>
       </c>
     </row>
     <row r="135" ht="15" customHeight="1">
       <c r="A135" s="1" t="n"/>
       <c r="B135" s="1" t="n">
-        <v>2301</v>
+        <v>2002</v>
       </c>
       <c r="C135" s="1" t="n"/>
       <c r="D135" s="1" t="n">
@@ -3142,19 +3142,19 @@
       </c>
       <c r="E135" s="1" t="inlineStr">
         <is>
-          <t>角色/友方神话角色/后羿</t>
+          <t>UI/CloudInfo/ItemsInfo</t>
         </is>
       </c>
       <c r="F135" s="1" t="inlineStr">
         <is>
-          <t>棋子-后羿预制体</t>
+          <t>仓库信息预制体</t>
         </is>
       </c>
     </row>
     <row r="136" ht="15" customHeight="1">
       <c r="A136" s="1" t="n"/>
       <c r="B136" s="1" t="n">
-        <v>2304</v>
+        <v>2003</v>
       </c>
       <c r="C136" s="1" t="n"/>
       <c r="D136" s="1" t="n">
@@ -3162,19 +3162,19 @@
       </c>
       <c r="E136" s="1" t="inlineStr">
         <is>
-          <t>角色/友方神话角色/嫦娥</t>
+          <t>UI/CloudInfo/TimeInfo</t>
         </is>
       </c>
       <c r="F136" s="1" t="inlineStr">
         <is>
-          <t>棋子-嫦娥预制体</t>
+          <t>存档时间预制体</t>
         </is>
       </c>
     </row>
     <row r="137" ht="15" customHeight="1">
       <c r="A137" s="1" t="n"/>
       <c r="B137" s="1" t="n">
-        <v>2309</v>
+        <v>2004</v>
       </c>
       <c r="C137" s="1" t="n"/>
       <c r="D137" s="1" t="n">
@@ -3182,19 +3182,19 @@
       </c>
       <c r="E137" s="1" t="inlineStr">
         <is>
-          <t>角色/友方神话角色/敌人测试</t>
+          <t>UI/Items/SummonChessStateUI</t>
         </is>
       </c>
       <c r="F137" s="1" t="inlineStr">
         <is>
-          <t>棋子-敌人测试预制体</t>
+          <t>棋子状态UI预制体</t>
         </is>
       </c>
     </row>
     <row r="138" ht="15" customHeight="1">
       <c r="A138" s="1" t="n"/>
       <c r="B138" s="1" t="n">
-        <v>2399</v>
+        <v>2101</v>
       </c>
       <c r="C138" s="1" t="n"/>
       <c r="D138" s="1" t="n">
@@ -3202,59 +3202,59 @@
       </c>
       <c r="E138" s="1" t="inlineStr">
         <is>
-          <t>角色/测试/靶子</t>
+          <t>角色/召唤师/狂战士/狂战士_End</t>
         </is>
       </c>
       <c r="F138" s="1" t="inlineStr">
         <is>
-          <t>棋子-靶子预制体</t>
+          <t>狂战士</t>
         </is>
       </c>
     </row>
     <row r="139" ht="15" customHeight="1">
       <c r="A139" s="1" t="n"/>
       <c r="B139" s="1" t="n">
-        <v>2401</v>
+        <v>2102</v>
       </c>
       <c r="C139" s="1" t="n"/>
       <c r="D139" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E139" s="1" t="inlineStr">
         <is>
-          <t>DamagePopup</t>
+          <t>角色/NPC/勇士End</t>
         </is>
       </c>
       <c r="F139" s="1" t="inlineStr">
         <is>
-          <t>伤害飘字预制体</t>
+          <t>术士</t>
         </is>
       </c>
     </row>
     <row r="140" ht="15" customHeight="1">
       <c r="A140" s="1" t="n"/>
       <c r="B140" s="1" t="n">
-        <v>2402</v>
+        <v>2103</v>
       </c>
       <c r="C140" s="1" t="n"/>
       <c r="D140" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E140" s="1" t="inlineStr">
         <is>
-          <t>InteractTip</t>
+          <t>角色/NPC/勇士End</t>
         </is>
       </c>
       <c r="F140" s="1" t="inlineStr">
         <is>
-          <t>交互提示预制体</t>
+          <t>混沌</t>
         </is>
       </c>
     </row>
     <row r="141" ht="15" customHeight="1">
       <c r="A141" s="1" t="n"/>
       <c r="B141" s="1" t="n">
-        <v>2501</v>
+        <v>2104</v>
       </c>
       <c r="C141" s="1" t="n"/>
       <c r="D141" s="1" t="n">
@@ -3262,19 +3262,19 @@
       </c>
       <c r="E141" s="1" t="inlineStr">
         <is>
-          <t>Game/Interact/破损的宝箱</t>
+          <t>角色/NPC/勇士End</t>
         </is>
       </c>
       <c r="F141" s="1" t="inlineStr">
         <is>
-          <t>破损的宝箱</t>
+          <t>德鲁伊</t>
         </is>
       </c>
     </row>
     <row r="142" ht="15" customHeight="1">
       <c r="A142" s="1" t="n"/>
       <c r="B142" s="1" t="n">
-        <v>2502</v>
+        <v>2201</v>
       </c>
       <c r="C142" s="1" t="n"/>
       <c r="D142" s="1" t="n">
@@ -3282,19 +3282,19 @@
       </c>
       <c r="E142" s="1" t="inlineStr">
         <is>
-          <t>Game/Interact/精致的宝箱</t>
+          <t>Items/DashItem</t>
         </is>
       </c>
       <c r="F142" s="1" t="inlineStr">
         <is>
-          <t>精致的宝箱</t>
+          <t>飞雷神道具预制体</t>
         </is>
       </c>
     </row>
     <row r="143" ht="15" customHeight="1">
       <c r="A143" s="1" t="n"/>
       <c r="B143" s="1" t="n">
-        <v>2503</v>
+        <v>2301</v>
       </c>
       <c r="C143" s="1" t="n"/>
       <c r="D143" s="1" t="n">
@@ -3302,19 +3302,19 @@
       </c>
       <c r="E143" s="1" t="inlineStr">
         <is>
-          <t>Game/Interact/华丽的宝箱</t>
+          <t>角色/友方神话角色/后羿</t>
         </is>
       </c>
       <c r="F143" s="1" t="inlineStr">
         <is>
-          <t>华丽的宝箱</t>
+          <t>棋子-后羿预制体</t>
         </is>
       </c>
     </row>
     <row r="144" ht="15" customHeight="1">
       <c r="A144" s="1" t="n"/>
       <c r="B144" s="1" t="n">
-        <v>2504</v>
+        <v>2304</v>
       </c>
       <c r="C144" s="1" t="n"/>
       <c r="D144" s="1" t="n">
@@ -3322,19 +3322,19 @@
       </c>
       <c r="E144" s="1" t="inlineStr">
         <is>
-          <t>Game/Interact/神秘的宝箱</t>
+          <t>角色/友方神话角色/嫦娥</t>
         </is>
       </c>
       <c r="F144" s="1" t="inlineStr">
         <is>
-          <t>神秘的宝箱</t>
+          <t>棋子-嫦娥预制体</t>
         </is>
       </c>
     </row>
     <row r="145" ht="15" customHeight="1">
       <c r="A145" s="1" t="n"/>
       <c r="B145" s="1" t="n">
-        <v>2600</v>
+        <v>2309</v>
       </c>
       <c r="C145" s="1" t="n"/>
       <c r="D145" s="1" t="n">
@@ -3342,19 +3342,19 @@
       </c>
       <c r="E145" s="1" t="inlineStr">
         <is>
-          <t>Enemy/后羿(敌人测试)</t>
+          <t>角色/友方神话角色/敌人测试</t>
         </is>
       </c>
       <c r="F145" s="1" t="inlineStr">
         <is>
-          <t>敌人-测试预制体</t>
+          <t>棋子-敌人测试预制体</t>
         </is>
       </c>
     </row>
     <row r="146" ht="15" customHeight="1">
       <c r="A146" s="1" t="n"/>
       <c r="B146" s="1" t="n">
-        <v>2601</v>
+        <v>2310</v>
       </c>
       <c r="C146" s="1" t="n"/>
       <c r="D146" s="1" t="n">
@@ -3362,19 +3362,19 @@
       </c>
       <c r="E146" s="1" t="inlineStr">
         <is>
-          <t>Enemy/邪灵</t>
+          <t>角色/敌方神话生物/邪灵</t>
         </is>
       </c>
       <c r="F146" s="1" t="inlineStr">
         <is>
-          <t>敌人-邪灵预制体</t>
+          <t>棋子-邪灵预制体</t>
         </is>
       </c>
     </row>
     <row r="147" ht="15" customHeight="1">
       <c r="A147" s="1" t="n"/>
       <c r="B147" s="1" t="n">
-        <v>2901</v>
+        <v>2399</v>
       </c>
       <c r="C147" s="1" t="n"/>
       <c r="D147" s="1" t="n">
@@ -3382,19 +3382,19 @@
       </c>
       <c r="E147" s="1" t="inlineStr">
         <is>
-          <t>Combat/BattleArena</t>
+          <t>角色/测试/靶子</t>
         </is>
       </c>
       <c r="F147" s="1" t="inlineStr">
         <is>
-          <t>战斗场景预制体</t>
+          <t>棋子-靶子预制体</t>
         </is>
       </c>
     </row>
     <row r="148" ht="15" customHeight="1">
       <c r="A148" s="1" t="n"/>
       <c r="B148" s="1" t="n">
-        <v>3001</v>
+        <v>2401</v>
       </c>
       <c r="C148" s="1" t="n"/>
       <c r="D148" s="1" t="n">
@@ -3402,19 +3402,19 @@
       </c>
       <c r="E148" s="1" t="inlineStr">
         <is>
-          <t>SummonChessEffect/HouYi_Skill1</t>
+          <t>DamagePopup</t>
         </is>
       </c>
       <c r="F148" s="1" t="inlineStr">
         <is>
-          <t>后羿技能1特效</t>
+          <t>伤害飘字预制体</t>
         </is>
       </c>
     </row>
     <row r="149" ht="15" customHeight="1">
       <c r="A149" s="1" t="n"/>
       <c r="B149" s="1" t="n">
-        <v>3002</v>
+        <v>2402</v>
       </c>
       <c r="C149" s="1" t="n"/>
       <c r="D149" s="1" t="n">
@@ -3422,359 +3422,359 @@
       </c>
       <c r="E149" s="1" t="inlineStr">
         <is>
-          <t>SummonChessEffect/Projectile_HouYi_Attack</t>
+          <t>InteractTip</t>
         </is>
       </c>
       <c r="F149" s="1" t="inlineStr">
         <is>
-          <t>后羿普攻子弹</t>
+          <t>交互提示预制体</t>
         </is>
       </c>
     </row>
     <row r="150" ht="15" customHeight="1">
       <c r="A150" s="1" t="n"/>
       <c r="B150" s="1" t="n">
-        <v>3003</v>
+        <v>2501</v>
       </c>
       <c r="C150" s="1" t="n"/>
       <c r="D150" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E150" s="1" t="inlineStr">
         <is>
-          <t>SummonChessEffect/Projectile_HouYi_Skill2</t>
+          <t>Game/Interact/破损的宝箱</t>
         </is>
       </c>
       <c r="F150" s="1" t="inlineStr">
         <is>
-          <t>后羿大招子弹</t>
+          <t>破损的宝箱</t>
         </is>
       </c>
     </row>
     <row r="151" ht="15" customHeight="1">
       <c r="A151" s="1" t="n"/>
       <c r="B151" s="1" t="n">
-        <v>3004</v>
+        <v>2502</v>
       </c>
       <c r="C151" s="1" t="n"/>
       <c r="D151" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E151" s="1" t="inlineStr">
         <is>
-          <t>SummonChessEffect/Projectile_ChangE_Attack</t>
+          <t>Game/Interact/精致的宝箱</t>
         </is>
       </c>
       <c r="F151" s="1" t="inlineStr">
         <is>
-          <t>嫦娥普攻子弹</t>
+          <t>精致的宝箱</t>
         </is>
       </c>
     </row>
     <row r="152" ht="15" customHeight="1">
       <c r="A152" s="1" t="n"/>
       <c r="B152" s="1" t="n">
-        <v>3005</v>
+        <v>2503</v>
       </c>
       <c r="C152" s="1" t="n"/>
       <c r="D152" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E152" s="1" t="inlineStr">
         <is>
-          <t>SummonChessEffect/Change_Skill1</t>
+          <t>Game/Interact/华丽的宝箱</t>
         </is>
       </c>
       <c r="F152" s="1" t="inlineStr">
         <is>
-          <t>嫦娥技能一子弹</t>
+          <t>华丽的宝箱</t>
         </is>
       </c>
     </row>
     <row r="153" ht="15" customHeight="1">
       <c r="A153" s="1" t="n"/>
       <c r="B153" s="1" t="n">
-        <v>3006</v>
+        <v>2504</v>
       </c>
       <c r="C153" s="1" t="n"/>
       <c r="D153" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E153" s="1" t="inlineStr">
         <is>
-          <t>SummonChessEffect/Change_Skill2</t>
+          <t>Game/Interact/神秘的宝箱</t>
         </is>
       </c>
       <c r="F153" s="1" t="inlineStr">
         <is>
-          <t>嫦娥大招法阵预制体</t>
+          <t>神秘的宝箱</t>
         </is>
       </c>
     </row>
     <row r="154" ht="15" customHeight="1">
       <c r="A154" s="1" t="n"/>
       <c r="B154" s="1" t="n">
-        <v>3007</v>
+        <v>2600</v>
       </c>
       <c r="C154" s="1" t="n"/>
       <c r="D154" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E154" s="1" t="inlineStr">
         <is>
-          <t>SummonChessEffect/Change_Skill2_Projectile</t>
+          <t>Enemy/后羿(敌人测试)</t>
         </is>
       </c>
       <c r="F154" s="1" t="inlineStr">
         <is>
-          <t>嫦娥大招法阵生成的投射物</t>
+          <t>敌人-测试预制体</t>
         </is>
       </c>
     </row>
     <row r="155" ht="15" customHeight="1">
       <c r="A155" s="1" t="n"/>
       <c r="B155" s="1" t="n">
-        <v>3008</v>
+        <v>2601</v>
       </c>
       <c r="C155" s="1" t="n"/>
       <c r="D155" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E155" s="1" t="inlineStr">
         <is>
-          <t>SummonChessEffect/XieLing_Skill1_Effect</t>
+          <t>Enemy/邪灵</t>
         </is>
       </c>
       <c r="F155" s="1" t="inlineStr">
         <is>
-          <t>邪灵技能1特效</t>
+          <t>敌人-邪灵预制体</t>
         </is>
       </c>
     </row>
     <row r="156" ht="15" customHeight="1">
       <c r="A156" s="1" t="n"/>
       <c r="B156" s="1" t="n">
-        <v>3009</v>
+        <v>2901</v>
       </c>
       <c r="C156" s="1" t="n"/>
       <c r="D156" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E156" s="1" t="inlineStr">
         <is>
-          <t>SummonChessEffect/XieLing_Skill2</t>
+          <t>Combat/BattleArena</t>
         </is>
       </c>
       <c r="F156" s="1" t="inlineStr">
         <is>
-          <t>邪灵技能2法阵预制体</t>
+          <t>战斗场景预制体</t>
         </is>
       </c>
     </row>
     <row r="157" ht="15" customHeight="1">
       <c r="A157" s="1" t="n"/>
       <c r="B157" s="1" t="n">
-        <v>6001</v>
+        <v>3001</v>
       </c>
       <c r="C157" s="1" t="n"/>
       <c r="D157" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E157" s="1" t="inlineStr">
         <is>
-          <t>Skills/SkillParamRegistry</t>
+          <t>SummonChessEffect/HouYi_Skill1</t>
         </is>
       </c>
       <c r="F157" s="1" t="inlineStr">
         <is>
-          <t>技能参数注册表</t>
+          <t>后羿技能1特效</t>
         </is>
       </c>
     </row>
     <row r="158" ht="15" customHeight="1">
       <c r="A158" s="1" t="n"/>
       <c r="B158" s="1" t="n">
-        <v>10001</v>
+        <v>3002</v>
       </c>
       <c r="C158" s="1" t="n"/>
       <c r="D158" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E158" s="1" t="inlineStr">
         <is>
-          <t>Buff/2001.png</t>
+          <t>SummonChessEffect/Projectile_HouYi_Attack</t>
         </is>
       </c>
       <c r="F158" s="1" t="inlineStr">
         <is>
-          <t>先手·速度爆发图标</t>
+          <t>后羿普攻子弹</t>
         </is>
       </c>
     </row>
     <row r="159" ht="15" customHeight="1">
       <c r="A159" s="1" t="n"/>
       <c r="B159" s="1" t="n">
-        <v>10002</v>
+        <v>3003</v>
       </c>
       <c r="C159" s="1" t="n"/>
       <c r="D159" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E159" s="1" t="inlineStr">
         <is>
-          <t>Buff/2002.png</t>
+          <t>SummonChessEffect/Projectile_HouYi_Skill2</t>
         </is>
       </c>
       <c r="F159" s="1" t="inlineStr">
         <is>
-          <t>先手·攻击强化图标</t>
+          <t>后羿大招子弹</t>
         </is>
       </c>
     </row>
     <row r="160" ht="15" customHeight="1">
       <c r="A160" s="1" t="n"/>
       <c r="B160" s="1" t="n">
-        <v>10003</v>
+        <v>3004</v>
       </c>
       <c r="C160" s="1" t="n"/>
       <c r="D160" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E160" s="1" t="inlineStr">
         <is>
-          <t>Buff/2003.png</t>
+          <t>SummonChessEffect/Projectile_ChangE_Attack</t>
         </is>
       </c>
       <c r="F160" s="1" t="inlineStr">
         <is>
-          <t>先手·伤害减免图标</t>
+          <t>嫦娥普攻子弹</t>
         </is>
       </c>
     </row>
     <row r="161" ht="15" customHeight="1">
       <c r="A161" s="1" t="n"/>
       <c r="B161" s="1" t="n">
-        <v>10004</v>
+        <v>3005</v>
       </c>
       <c r="C161" s="1" t="n"/>
       <c r="D161" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E161" s="1" t="inlineStr">
         <is>
-          <t>Buff/2004.png</t>
+          <t>SummonChessEffect/Change_Skill1</t>
         </is>
       </c>
       <c r="F161" s="1" t="inlineStr">
         <is>
-          <t>先手·防御加强图标</t>
+          <t>嫦娥技能一子弹</t>
         </is>
       </c>
     </row>
     <row r="162" ht="15" customHeight="1">
       <c r="A162" s="1" t="n"/>
       <c r="B162" s="1" t="n">
-        <v>10101</v>
+        <v>3006</v>
       </c>
       <c r="C162" s="1" t="n"/>
       <c r="D162" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E162" s="1" t="inlineStr">
         <is>
-          <t>Buff/3001.png</t>
+          <t>SummonChessEffect/Change_Skill2</t>
         </is>
       </c>
       <c r="F162" s="1" t="inlineStr">
         <is>
-          <t>偷袭·防御破阵图标</t>
+          <t>嫦娥大招法阵预制体</t>
         </is>
       </c>
     </row>
     <row r="163" ht="15" customHeight="1">
       <c r="A163" s="1" t="n"/>
       <c r="B163" s="1" t="n">
-        <v>10102</v>
+        <v>3007</v>
       </c>
       <c r="C163" s="1" t="n"/>
       <c r="D163" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E163" s="1" t="inlineStr">
         <is>
-          <t>Buff/3002.png</t>
+          <t>SummonChessEffect/Change_Skill2_Projectile</t>
         </is>
       </c>
       <c r="F163" s="1" t="inlineStr">
         <is>
-          <t>偷袭·致命眩晕图标</t>
+          <t>嫦娥大招法阵生成的投射物</t>
         </is>
       </c>
     </row>
     <row r="164" ht="15" customHeight="1">
       <c r="A164" s="1" t="n"/>
       <c r="B164" s="1" t="n">
-        <v>10103</v>
+        <v>3008</v>
       </c>
       <c r="C164" s="1" t="n"/>
       <c r="D164" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E164" s="1" t="inlineStr">
         <is>
-          <t>Buff/3003.png</t>
+          <t>SummonChessEffect/XieLing_Skill1_Effect</t>
         </is>
       </c>
       <c r="F164" s="1" t="inlineStr">
         <is>
-          <t>偷袭·致命流血图标</t>
+          <t>邪灵技能1特效</t>
         </is>
       </c>
     </row>
     <row r="165" ht="15" customHeight="1">
       <c r="A165" s="1" t="n"/>
       <c r="B165" s="1" t="n">
-        <v>10201</v>
+        <v>3009</v>
       </c>
       <c r="C165" s="1" t="n"/>
       <c r="D165" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E165" s="1" t="inlineStr">
         <is>
-          <t>Buff/4001.png</t>
+          <t>SummonChessEffect/XieLing_Skill2</t>
         </is>
       </c>
       <c r="F165" s="1" t="inlineStr">
         <is>
-          <t>战意激昂Buff图标</t>
+          <t>邪灵技能2法阵预制体</t>
         </is>
       </c>
     </row>
     <row r="166" ht="15" customHeight="1">
       <c r="A166" s="1" t="n"/>
       <c r="B166" s="1" t="n">
-        <v>10202</v>
+        <v>6001</v>
       </c>
       <c r="C166" s="1" t="n"/>
       <c r="D166" s="1" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E166" s="1" t="inlineStr">
         <is>
-          <t>Buff/4002.png</t>
+          <t>Skills/SkillParamRegistry</t>
         </is>
       </c>
       <c r="F166" s="1" t="inlineStr">
         <is>
-          <t>狂怒之心Buff图标</t>
+          <t>技能参数注册表</t>
         </is>
       </c>
     </row>
     <row r="167" ht="15" customHeight="1">
       <c r="A167" s="1" t="n"/>
       <c r="B167" s="1" t="n">
-        <v>10203</v>
+        <v>10001</v>
       </c>
       <c r="C167" s="1" t="n"/>
       <c r="D167" s="1" t="n">
@@ -3782,19 +3782,19 @@
       </c>
       <c r="E167" s="1" t="inlineStr">
         <is>
-          <t>Buff/4003.png</t>
+          <t>Buff/2001.png</t>
         </is>
       </c>
       <c r="F167" s="1" t="inlineStr">
         <is>
-          <t>暗影咒体Buff图标</t>
+          <t>先手·速度爆发图标</t>
         </is>
       </c>
     </row>
     <row r="168" ht="15" customHeight="1">
       <c r="A168" s="1" t="n"/>
       <c r="B168" s="1" t="n">
-        <v>11001</v>
+        <v>10002</v>
       </c>
       <c r="C168" s="1" t="n"/>
       <c r="D168" s="1" t="n">
@@ -3802,19 +3802,19 @@
       </c>
       <c r="E168" s="1" t="inlineStr">
         <is>
-          <t>Enemy/默认.png</t>
+          <t>Buff/2002.png</t>
         </is>
       </c>
       <c r="F168" s="1" t="inlineStr">
         <is>
-          <t>敌人图标</t>
+          <t>先手·攻击强化图标</t>
         </is>
       </c>
     </row>
     <row r="169" ht="15" customHeight="1">
       <c r="A169" s="1" t="n"/>
       <c r="B169" s="1" t="n">
-        <v>15001</v>
+        <v>10003</v>
       </c>
       <c r="C169" s="1" t="n"/>
       <c r="D169" s="1" t="n">
@@ -3822,43 +3822,39 @@
       </c>
       <c r="E169" s="1" t="inlineStr">
         <is>
-          <t>Buff/5001.png</t>
+          <t>Buff/2003.png</t>
         </is>
       </c>
       <c r="F169" s="1" t="inlineStr">
         <is>
-          <t>神圣庇护Buff图标</t>
+          <t>先手·伤害减免图标</t>
         </is>
       </c>
     </row>
     <row r="170" ht="15" customHeight="1">
       <c r="A170" s="1" t="n"/>
       <c r="B170" s="1" t="n">
-        <v>15002</v>
-      </c>
-      <c r="C170" s="1" t="inlineStr">
-        <is>
-          <t>(不再使用)</t>
-        </is>
-      </c>
+        <v>10004</v>
+      </c>
+      <c r="C170" s="1" t="n"/>
       <c r="D170" s="1" t="n">
         <v>1</v>
       </c>
       <c r="E170" s="1" t="inlineStr">
         <is>
-          <t>Buff/5002.png</t>
+          <t>Buff/2004.png</t>
         </is>
       </c>
       <c r="F170" s="1" t="inlineStr">
         <is>
-          <t>烈焰风暴·灼烧Buff图标</t>
+          <t>先手·防御加强图标</t>
         </is>
       </c>
     </row>
     <row r="171" ht="15" customHeight="1">
       <c r="A171" s="1" t="n"/>
       <c r="B171" s="1" t="n">
-        <v>15003</v>
+        <v>10101</v>
       </c>
       <c r="C171" s="1" t="n"/>
       <c r="D171" s="1" t="n">
@@ -3866,19 +3862,19 @@
       </c>
       <c r="E171" s="1" t="inlineStr">
         <is>
-          <t>Buff/5003.png</t>
+          <t>Buff/3001.png</t>
         </is>
       </c>
       <c r="F171" s="1" t="inlineStr">
         <is>
-          <t>战争号角Buff图标</t>
+          <t>偷袭·防御破阵图标</t>
         </is>
       </c>
     </row>
     <row r="172" ht="15" customHeight="1">
       <c r="A172" s="1" t="n"/>
       <c r="B172" s="1" t="n">
-        <v>15005</v>
+        <v>10102</v>
       </c>
       <c r="C172" s="1" t="n"/>
       <c r="D172" s="1" t="n">
@@ -3886,19 +3882,19 @@
       </c>
       <c r="E172" s="1" t="inlineStr">
         <is>
-          <t>Buff/5005.png</t>
+          <t>Buff/3002.png</t>
         </is>
       </c>
       <c r="F172" s="1" t="inlineStr">
         <is>
-          <t>暗影突袭·眩晕Buff图标</t>
+          <t>偷袭·致命眩晕图标</t>
         </is>
       </c>
     </row>
     <row r="173" ht="15" customHeight="1">
       <c r="A173" s="1" t="n"/>
       <c r="B173" s="1" t="n">
-        <v>15007</v>
+        <v>10103</v>
       </c>
       <c r="C173" s="1" t="n"/>
       <c r="D173" s="1" t="n">
@@ -3906,19 +3902,19 @@
       </c>
       <c r="E173" s="1" t="inlineStr">
         <is>
-          <t>Buff/5007.png</t>
+          <t>Buff/3003.png</t>
         </is>
       </c>
       <c r="F173" s="1" t="inlineStr">
         <is>
-          <t>冰霜新星Buff图标</t>
+          <t>偷袭·致命流血图标</t>
         </is>
       </c>
     </row>
     <row r="174" ht="15" customHeight="1">
       <c r="A174" s="1" t="n"/>
       <c r="B174" s="1" t="n">
-        <v>15008</v>
+        <v>10201</v>
       </c>
       <c r="C174" s="1" t="n"/>
       <c r="D174" s="1" t="n">
@@ -3926,19 +3922,19 @@
       </c>
       <c r="E174" s="1" t="inlineStr">
         <is>
-          <t>Buff/5008.png</t>
+          <t>Buff/4001.png</t>
         </is>
       </c>
       <c r="F174" s="1" t="inlineStr">
         <is>
-          <t>狂暴Buff图标</t>
+          <t>战意激昂Buff图标</t>
         </is>
       </c>
     </row>
     <row r="175" ht="15" customHeight="1">
       <c r="A175" s="1" t="n"/>
       <c r="B175" s="1" t="n">
-        <v>15009</v>
+        <v>10202</v>
       </c>
       <c r="C175" s="1" t="n"/>
       <c r="D175" s="1" t="n">
@@ -3946,19 +3942,19 @@
       </c>
       <c r="E175" s="1" t="inlineStr">
         <is>
-          <t>Buff/5009.png</t>
+          <t>Buff/4002.png</t>
         </is>
       </c>
       <c r="F175" s="1" t="inlineStr">
         <is>
-          <t>混乱诅咒Buff图标</t>
+          <t>狂怒之心Buff图标</t>
         </is>
       </c>
     </row>
     <row r="176" ht="15" customHeight="1">
       <c r="A176" s="1" t="n"/>
       <c r="B176" s="1" t="n">
-        <v>15011</v>
+        <v>10203</v>
       </c>
       <c r="C176" s="1" t="n"/>
       <c r="D176" s="1" t="n">
@@ -3966,19 +3962,19 @@
       </c>
       <c r="E176" s="1" t="inlineStr">
         <is>
-          <t>Buff/5011.png</t>
+          <t>Buff/4003.png</t>
         </is>
       </c>
       <c r="F176" s="1" t="inlineStr">
         <is>
-          <t>反伤之盾Buff图标</t>
+          <t>暗影咒体Buff图标</t>
         </is>
       </c>
     </row>
     <row r="177" ht="15" customHeight="1">
       <c r="A177" s="1" t="n"/>
       <c r="B177" s="1" t="n">
-        <v>15012</v>
+        <v>11001</v>
       </c>
       <c r="C177" s="1" t="n"/>
       <c r="D177" s="1" t="n">
@@ -3986,19 +3982,19 @@
       </c>
       <c r="E177" s="1" t="inlineStr">
         <is>
-          <t>Buff/5012.png</t>
+          <t>Enemy/默认.png</t>
         </is>
       </c>
       <c r="F177" s="1" t="inlineStr">
         <is>
-          <t>圣域防线Buff图标</t>
+          <t>敌人图标</t>
         </is>
       </c>
     </row>
     <row r="178" ht="15" customHeight="1">
       <c r="A178" s="1" t="n"/>
       <c r="B178" s="1" t="n">
-        <v>15013</v>
+        <v>15001</v>
       </c>
       <c r="C178" s="1" t="n"/>
       <c r="D178" s="1" t="n">
@@ -4006,39 +4002,43 @@
       </c>
       <c r="E178" s="1" t="inlineStr">
         <is>
-          <t>Buff/5013.png</t>
+          <t>Buff/5001.png</t>
         </is>
       </c>
       <c r="F178" s="1" t="inlineStr">
         <is>
-          <t>护盾再生Buff图标</t>
+          <t>神圣庇护Buff图标</t>
         </is>
       </c>
     </row>
     <row r="179" ht="15" customHeight="1">
       <c r="A179" s="1" t="n"/>
       <c r="B179" s="1" t="n">
-        <v>15014</v>
-      </c>
-      <c r="C179" s="1" t="n"/>
+        <v>15002</v>
+      </c>
+      <c r="C179" s="1" t="inlineStr">
+        <is>
+          <t>(不再使用)</t>
+        </is>
+      </c>
       <c r="D179" s="1" t="n">
         <v>1</v>
       </c>
       <c r="E179" s="1" t="inlineStr">
         <is>
-          <t>Buff/5014.png</t>
+          <t>Buff/5002.png</t>
         </is>
       </c>
       <c r="F179" s="1" t="inlineStr">
         <is>
-          <t>血源强化Buff图标</t>
+          <t>烈焰风暴·灼烧Buff图标</t>
         </is>
       </c>
     </row>
     <row r="180" ht="15" customHeight="1">
       <c r="A180" s="1" t="n"/>
       <c r="B180" s="1" t="n">
-        <v>15015</v>
+        <v>15003</v>
       </c>
       <c r="C180" s="1" t="n"/>
       <c r="D180" s="1" t="n">
@@ -4046,19 +4046,19 @@
       </c>
       <c r="E180" s="1" t="inlineStr">
         <is>
-          <t>Buff/5015.png</t>
+          <t>Buff/5003.png</t>
         </is>
       </c>
       <c r="F180" s="1" t="inlineStr">
         <is>
-          <t>吸血之刃Buff图标</t>
+          <t>战争号角Buff图标</t>
         </is>
       </c>
     </row>
     <row r="181" ht="15" customHeight="1">
       <c r="A181" s="1" t="n"/>
       <c r="B181" s="1" t="n">
-        <v>15017</v>
+        <v>15005</v>
       </c>
       <c r="C181" s="1" t="n"/>
       <c r="D181" s="1" t="n">
@@ -4066,19 +4066,19 @@
       </c>
       <c r="E181" s="1" t="inlineStr">
         <is>
-          <t>Buff/5017.png</t>
+          <t>Buff/5005.png</t>
         </is>
       </c>
       <c r="F181" s="1" t="inlineStr">
         <is>
-          <t>护甲破碎Buff图标</t>
+          <t>暗影突袭·眩晕Buff图标</t>
         </is>
       </c>
     </row>
     <row r="182" ht="15" customHeight="1">
       <c r="A182" s="1" t="n"/>
       <c r="B182" s="1" t="n">
-        <v>15018</v>
+        <v>15007</v>
       </c>
       <c r="C182" s="1" t="n"/>
       <c r="D182" s="1" t="n">
@@ -4086,19 +4086,19 @@
       </c>
       <c r="E182" s="1" t="inlineStr">
         <is>
-          <t>Buff/5018.png</t>
+          <t>Buff/5007.png</t>
         </is>
       </c>
       <c r="F182" s="1" t="inlineStr">
         <is>
-          <t>虚弱诅咒Buff图标</t>
+          <t>冰霜新星Buff图标</t>
         </is>
       </c>
     </row>
     <row r="183" ht="15" customHeight="1">
       <c r="A183" s="1" t="n"/>
       <c r="B183" s="1" t="n">
-        <v>15019</v>
+        <v>15008</v>
       </c>
       <c r="C183" s="1" t="n"/>
       <c r="D183" s="1" t="n">
@@ -4106,19 +4106,19 @@
       </c>
       <c r="E183" s="1" t="inlineStr">
         <is>
-          <t>Buff/5019.png</t>
+          <t>Buff/5008.png</t>
         </is>
       </c>
       <c r="F183" s="1" t="inlineStr">
         <is>
-          <t>沉默之符Buff图标</t>
+          <t>狂暴Buff图标</t>
         </is>
       </c>
     </row>
     <row r="184" ht="15" customHeight="1">
       <c r="A184" s="1" t="n"/>
       <c r="B184" s="1" t="n">
-        <v>15020</v>
+        <v>15009</v>
       </c>
       <c r="C184" s="1" t="n"/>
       <c r="D184" s="1" t="n">
@@ -4126,19 +4126,19 @@
       </c>
       <c r="E184" s="1" t="inlineStr">
         <is>
-          <t>Buff/5020.png</t>
+          <t>Buff/5009.png</t>
         </is>
       </c>
       <c r="F184" s="1" t="inlineStr">
         <is>
-          <t>嘲讽之声Buff图标</t>
+          <t>混乱诅咒Buff图标</t>
         </is>
       </c>
     </row>
     <row r="185" ht="15" customHeight="1">
       <c r="A185" s="1" t="n"/>
       <c r="B185" s="1" t="n">
-        <v>15021</v>
+        <v>15011</v>
       </c>
       <c r="C185" s="1" t="n"/>
       <c r="D185" s="1" t="n">
@@ -4146,67 +4146,59 @@
       </c>
       <c r="E185" s="1" t="inlineStr">
         <is>
-          <t>Buff/5021.png</t>
+          <t>Buff/5011.png</t>
         </is>
       </c>
       <c r="F185" s="1" t="inlineStr">
         <is>
-          <t>剧毒之雾Buff图标</t>
+          <t>反伤之盾Buff图标</t>
         </is>
       </c>
     </row>
     <row r="186" ht="15" customHeight="1">
       <c r="A186" s="1" t="n"/>
       <c r="B186" s="1" t="n">
-        <v>15022</v>
-      </c>
-      <c r="C186" s="1" t="inlineStr">
-        <is>
-          <t>暂未实现</t>
-        </is>
-      </c>
+        <v>15012</v>
+      </c>
+      <c r="C186" s="1" t="n"/>
       <c r="D186" s="1" t="n">
         <v>1</v>
       </c>
       <c r="E186" s="1" t="inlineStr">
         <is>
-          <t>Buff/5022.png</t>
+          <t>Buff/5012.png</t>
         </is>
       </c>
       <c r="F186" s="1" t="inlineStr">
         <is>
-          <t>伤害转移Buff图标</t>
+          <t>圣域防线Buff图标</t>
         </is>
       </c>
     </row>
     <row r="187" ht="15" customHeight="1">
       <c r="A187" s="1" t="n"/>
       <c r="B187" s="1" t="n">
-        <v>15023</v>
-      </c>
-      <c r="C187" s="1" t="inlineStr">
-        <is>
-          <t>暂未实现</t>
-        </is>
-      </c>
+        <v>15013</v>
+      </c>
+      <c r="C187" s="1" t="n"/>
       <c r="D187" s="1" t="n">
         <v>1</v>
       </c>
       <c r="E187" s="1" t="inlineStr">
         <is>
-          <t>Buff/5023.png</t>
+          <t>Buff/5013.png</t>
         </is>
       </c>
       <c r="F187" s="1" t="inlineStr">
         <is>
-          <t>绝对零度Buff图标</t>
+          <t>护盾再生Buff图标</t>
         </is>
       </c>
     </row>
     <row r="188" ht="15" customHeight="1">
       <c r="A188" s="1" t="n"/>
       <c r="B188" s="1" t="n">
-        <v>19002</v>
+        <v>15014</v>
       </c>
       <c r="C188" s="1" t="n"/>
       <c r="D188" s="1" t="n">
@@ -4214,19 +4206,19 @@
       </c>
       <c r="E188" s="1" t="inlineStr">
         <is>
-          <t>Card/Component/2.png</t>
+          <t>Buff/5014.png</t>
         </is>
       </c>
       <c r="F188" s="1" t="inlineStr">
         <is>
-          <t>卡牌框-稀有度2</t>
+          <t>血源强化Buff图标</t>
         </is>
       </c>
     </row>
     <row r="189" ht="15" customHeight="1">
       <c r="A189" s="1" t="n"/>
       <c r="B189" s="1" t="n">
-        <v>19003</v>
+        <v>15015</v>
       </c>
       <c r="C189" s="1" t="n"/>
       <c r="D189" s="1" t="n">
@@ -4234,19 +4226,19 @@
       </c>
       <c r="E189" s="1" t="inlineStr">
         <is>
-          <t>Card/Component/3.png</t>
+          <t>Buff/5015.png</t>
         </is>
       </c>
       <c r="F189" s="1" t="inlineStr">
         <is>
-          <t>卡牌框-稀有度3</t>
+          <t>吸血之刃Buff图标</t>
         </is>
       </c>
     </row>
     <row r="190" ht="15" customHeight="1">
       <c r="A190" s="1" t="n"/>
       <c r="B190" s="1" t="n">
-        <v>19004</v>
+        <v>15017</v>
       </c>
       <c r="C190" s="1" t="n"/>
       <c r="D190" s="1" t="n">
@@ -4254,19 +4246,19 @@
       </c>
       <c r="E190" s="1" t="inlineStr">
         <is>
-          <t>Card/Component/4.png</t>
+          <t>Buff/5017.png</t>
         </is>
       </c>
       <c r="F190" s="1" t="inlineStr">
         <is>
-          <t>卡牌框-稀有度4</t>
+          <t>护甲破碎Buff图标</t>
         </is>
       </c>
     </row>
     <row r="191" ht="15" customHeight="1">
       <c r="A191" s="1" t="n"/>
       <c r="B191" s="1" t="n">
-        <v>19012</v>
+        <v>15018</v>
       </c>
       <c r="C191" s="1" t="n"/>
       <c r="D191" s="1" t="n">
@@ -4274,19 +4266,19 @@
       </c>
       <c r="E191" s="1" t="inlineStr">
         <is>
-          <t>Card/Component/Bg-2.png</t>
+          <t>Buff/5018.png</t>
         </is>
       </c>
       <c r="F191" s="1" t="inlineStr">
         <is>
-          <t>卡片背景-稀有度2</t>
+          <t>虚弱诅咒Buff图标</t>
         </is>
       </c>
     </row>
     <row r="192" ht="15" customHeight="1">
       <c r="A192" s="1" t="n"/>
       <c r="B192" s="1" t="n">
-        <v>19013</v>
+        <v>15019</v>
       </c>
       <c r="C192" s="1" t="n"/>
       <c r="D192" s="1" t="n">
@@ -4294,19 +4286,19 @@
       </c>
       <c r="E192" s="1" t="inlineStr">
         <is>
-          <t>Card/Component/Bg-3.png</t>
+          <t>Buff/5019.png</t>
         </is>
       </c>
       <c r="F192" s="1" t="inlineStr">
         <is>
-          <t>卡片背景-稀有度3</t>
+          <t>沉默之符Buff图标</t>
         </is>
       </c>
     </row>
     <row r="193" ht="15" customHeight="1">
       <c r="A193" s="1" t="n"/>
       <c r="B193" s="1" t="n">
-        <v>19014</v>
+        <v>15020</v>
       </c>
       <c r="C193" s="1" t="n"/>
       <c r="D193" s="1" t="n">
@@ -4314,19 +4306,19 @@
       </c>
       <c r="E193" s="1" t="inlineStr">
         <is>
-          <t>Card/Component/Bg-4.png</t>
+          <t>Buff/5020.png</t>
         </is>
       </c>
       <c r="F193" s="1" t="inlineStr">
         <is>
-          <t>卡片背景-稀有度4</t>
+          <t>嘲讽之声Buff图标</t>
         </is>
       </c>
     </row>
     <row r="194" ht="15" customHeight="1">
       <c r="A194" s="1" t="n"/>
       <c r="B194" s="1" t="n">
-        <v>19022</v>
+        <v>15021</v>
       </c>
       <c r="C194" s="1" t="n"/>
       <c r="D194" s="1" t="n">
@@ -4334,239 +4326,247 @@
       </c>
       <c r="E194" s="1" t="inlineStr">
         <is>
-          <t>Card/Component/Mask/Mask2.png</t>
+          <t>Buff/5021.png</t>
         </is>
       </c>
       <c r="F194" s="1" t="inlineStr">
         <is>
-          <t>名字背景-稀有度2</t>
+          <t>剧毒之雾Buff图标</t>
         </is>
       </c>
     </row>
     <row r="195" ht="15" customHeight="1">
       <c r="A195" s="1" t="n"/>
       <c r="B195" s="1" t="n">
-        <v>19023</v>
-      </c>
-      <c r="C195" s="1" t="n"/>
+        <v>15022</v>
+      </c>
+      <c r="C195" s="1" t="inlineStr">
+        <is>
+          <t>暂未实现</t>
+        </is>
+      </c>
       <c r="D195" s="1" t="n">
         <v>1</v>
       </c>
       <c r="E195" s="1" t="inlineStr">
         <is>
-          <t>Card/Component/Mask/Mask3.png</t>
+          <t>Buff/5022.png</t>
         </is>
       </c>
       <c r="F195" s="1" t="inlineStr">
         <is>
-          <t>名字背景-稀有度3</t>
+          <t>伤害转移Buff图标</t>
         </is>
       </c>
     </row>
     <row r="196" ht="15" customHeight="1">
       <c r="A196" s="1" t="n"/>
       <c r="B196" s="1" t="n">
-        <v>19024</v>
-      </c>
-      <c r="C196" s="1" t="n"/>
+        <v>15023</v>
+      </c>
+      <c r="C196" s="1" t="inlineStr">
+        <is>
+          <t>暂未实现</t>
+        </is>
+      </c>
       <c r="D196" s="1" t="n">
         <v>1</v>
       </c>
       <c r="E196" s="1" t="inlineStr">
         <is>
-          <t>Card/Component/Mask/Mask4.png</t>
+          <t>Buff/5023.png</t>
         </is>
       </c>
       <c r="F196" s="1" t="inlineStr">
         <is>
-          <t>名字背景-稀有度4</t>
+          <t>绝对零度Buff图标</t>
         </is>
       </c>
     </row>
     <row r="197" ht="15" customHeight="1">
       <c r="A197" s="1" t="n"/>
       <c r="B197" s="1" t="n">
-        <v>60001</v>
+        <v>19002</v>
       </c>
       <c r="C197" s="1" t="n"/>
       <c r="D197" s="1" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E197" s="1" t="inlineStr">
         <is>
-          <t>BGM/游戏启动主菜单BGM</t>
+          <t>Card/Component/2.png</t>
         </is>
       </c>
       <c r="F197" s="1" t="inlineStr">
         <is>
-          <t>游戏启动/主菜单</t>
+          <t>卡牌框-稀有度2</t>
         </is>
       </c>
     </row>
     <row r="198" ht="15" customHeight="1">
       <c r="A198" s="1" t="n"/>
       <c r="B198" s="1" t="n">
-        <v>60002</v>
+        <v>19003</v>
       </c>
       <c r="C198" s="1" t="n"/>
       <c r="D198" s="1" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E198" s="1" t="inlineStr">
         <is>
-          <t>BGM/基地场景BGM</t>
+          <t>Card/Component/3.png</t>
         </is>
       </c>
       <c r="F198" s="1" t="inlineStr">
         <is>
-          <t>基地场景</t>
+          <t>卡牌框-稀有度3</t>
         </is>
       </c>
     </row>
     <row r="199" ht="15" customHeight="1">
       <c r="A199" s="1" t="n"/>
       <c r="B199" s="1" t="n">
-        <v>60003</v>
+        <v>19004</v>
       </c>
       <c r="C199" s="1" t="n"/>
       <c r="D199" s="1" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E199" s="1" t="inlineStr">
         <is>
-          <t>BGM/大世界探索BGM</t>
+          <t>Card/Component/4.png</t>
         </is>
       </c>
       <c r="F199" s="1" t="inlineStr">
         <is>
-          <t>大世界探索</t>
+          <t>卡牌框-稀有度4</t>
         </is>
       </c>
     </row>
     <row r="200" ht="15" customHeight="1">
       <c r="A200" s="1" t="n"/>
       <c r="B200" s="1" t="n">
-        <v>60004</v>
+        <v>19012</v>
       </c>
       <c r="C200" s="1" t="n"/>
       <c r="D200" s="1" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E200" s="1" t="inlineStr">
         <is>
-          <t>BGM/教程场景BGM</t>
+          <t>Card/Component/Bg-2.png</t>
         </is>
       </c>
       <c r="F200" s="1" t="inlineStr">
         <is>
-          <t>教程场景</t>
+          <t>卡片背景-稀有度2</t>
         </is>
       </c>
     </row>
     <row r="201" ht="15" customHeight="1">
       <c r="A201" s="1" t="n"/>
       <c r="B201" s="1" t="n">
-        <v>60005</v>
+        <v>19013</v>
       </c>
       <c r="C201" s="1" t="n"/>
       <c r="D201" s="1" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E201" s="1" t="inlineStr">
         <is>
-          <t>BGM/天宫副本BGM</t>
+          <t>Card/Component/Bg-3.png</t>
         </is>
       </c>
       <c r="F201" s="1" t="inlineStr">
         <is>
-          <t>天宫副本</t>
+          <t>卡片背景-稀有度3</t>
         </is>
       </c>
     </row>
     <row r="202" ht="15" customHeight="1">
       <c r="A202" s="1" t="n"/>
       <c r="B202" s="1" t="n">
-        <v>60006</v>
+        <v>19014</v>
       </c>
       <c r="C202" s="1" t="n"/>
       <c r="D202" s="1" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E202" s="1" t="inlineStr">
         <is>
-          <t>BGM/赫尔海姆副本BGM</t>
+          <t>Card/Component/Bg-4.png</t>
         </is>
       </c>
       <c r="F202" s="1" t="inlineStr">
         <is>
-          <t>赫尔海姆副本</t>
+          <t>卡片背景-稀有度4</t>
         </is>
       </c>
     </row>
     <row r="203" ht="15" customHeight="1">
       <c r="A203" s="1" t="n"/>
       <c r="B203" s="1" t="n">
-        <v>60007</v>
+        <v>19022</v>
       </c>
       <c r="C203" s="1" t="n"/>
       <c r="D203" s="1" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E203" s="1" t="inlineStr">
         <is>
-          <t>BGM/高天原副本BGM</t>
+          <t>Card/Component/Mask/Mask2.png</t>
         </is>
       </c>
       <c r="F203" s="1" t="inlineStr">
         <is>
-          <t>高天原副本</t>
+          <t>名字背景-稀有度2</t>
         </is>
       </c>
     </row>
     <row r="204" ht="15" customHeight="1">
       <c r="A204" s="1" t="n"/>
       <c r="B204" s="1" t="n">
-        <v>60008</v>
+        <v>19023</v>
       </c>
       <c r="C204" s="1" t="n"/>
       <c r="D204" s="1" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E204" s="1" t="inlineStr">
         <is>
-          <t>BGM/奥林匹斯副本BGM</t>
+          <t>Card/Component/Mask/Mask3.png</t>
         </is>
       </c>
       <c r="F204" s="1" t="inlineStr">
         <is>
-          <t>奥林匹斯副本</t>
+          <t>名字背景-稀有度3</t>
         </is>
       </c>
     </row>
     <row r="205" ht="15" customHeight="1">
       <c r="A205" s="1" t="n"/>
       <c r="B205" s="1" t="n">
-        <v>60009</v>
+        <v>19024</v>
       </c>
       <c r="C205" s="1" t="n"/>
       <c r="D205" s="1" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E205" s="1" t="inlineStr">
         <is>
-          <t>BGM/巴比伦副本BGM</t>
+          <t>Card/Component/Mask/Mask4.png</t>
         </is>
       </c>
       <c r="F205" s="1" t="inlineStr">
         <is>
-          <t>巴比伦副本</t>
+          <t>名字背景-稀有度4</t>
         </is>
       </c>
     </row>
     <row r="206" ht="15" customHeight="1">
       <c r="A206" s="1" t="n"/>
       <c r="B206" s="1" t="n">
-        <v>60010</v>
+        <v>60001</v>
       </c>
       <c r="C206" s="1" t="n"/>
       <c r="D206" s="1" t="n">
@@ -4574,19 +4574,19 @@
       </c>
       <c r="E206" s="1" t="inlineStr">
         <is>
-          <t>BGM/阿瓦隆副本BGM</t>
+          <t>BGM/游戏启动主菜单BGM</t>
         </is>
       </c>
       <c r="F206" s="1" t="inlineStr">
         <is>
-          <t>阿瓦隆副本</t>
+          <t>游戏启动/主菜单</t>
         </is>
       </c>
     </row>
     <row r="207" ht="15" customHeight="1">
       <c r="A207" s="1" t="n"/>
       <c r="B207" s="1" t="n">
-        <v>60011</v>
+        <v>60002</v>
       </c>
       <c r="C207" s="1" t="n"/>
       <c r="D207" s="1" t="n">
@@ -4594,19 +4594,19 @@
       </c>
       <c r="E207" s="1" t="inlineStr">
         <is>
-          <t>BGM/深渊副本BGM</t>
+          <t>BGM/基地场景BGM</t>
         </is>
       </c>
       <c r="F207" s="1" t="inlineStr">
         <is>
-          <t>深渊副本</t>
+          <t>基地场景</t>
         </is>
       </c>
     </row>
     <row r="208" ht="15" customHeight="1">
       <c r="A208" s="1" t="n"/>
       <c r="B208" s="1" t="n">
-        <v>60012</v>
+        <v>60003</v>
       </c>
       <c r="C208" s="1" t="n"/>
       <c r="D208" s="1" t="n">
@@ -4614,19 +4614,19 @@
       </c>
       <c r="E208" s="1" t="inlineStr">
         <is>
-          <t>BGM/普通敌人战斗BGM</t>
+          <t>BGM/大世界探索BGM</t>
         </is>
       </c>
       <c r="F208" s="1" t="inlineStr">
         <is>
-          <t>普通敌人战斗</t>
+          <t>大世界探索</t>
         </is>
       </c>
     </row>
     <row r="209" ht="15" customHeight="1">
       <c r="A209" s="1" t="n"/>
       <c r="B209" s="1" t="n">
-        <v>60013</v>
+        <v>60004</v>
       </c>
       <c r="C209" s="1" t="n"/>
       <c r="D209" s="1" t="n">
@@ -4634,19 +4634,19 @@
       </c>
       <c r="E209" s="1" t="inlineStr">
         <is>
-          <t>BGM/精英敌人战斗BGM</t>
+          <t>BGM/教程场景BGM</t>
         </is>
       </c>
       <c r="F209" s="1" t="inlineStr">
         <is>
-          <t>精英敌人战斗</t>
+          <t>教程场景</t>
         </is>
       </c>
     </row>
     <row r="210" ht="15" customHeight="1">
       <c r="A210" s="1" t="n"/>
       <c r="B210" s="1" t="n">
-        <v>60014</v>
+        <v>60005</v>
       </c>
       <c r="C210" s="1" t="n"/>
       <c r="D210" s="1" t="n">
@@ -4654,19 +4654,19 @@
       </c>
       <c r="E210" s="1" t="inlineStr">
         <is>
-          <t>BGM/Boss战斗BGM</t>
+          <t>BGM/天宫副本BGM</t>
         </is>
       </c>
       <c r="F210" s="1" t="inlineStr">
         <is>
-          <t>Boss战斗</t>
+          <t>天宫副本</t>
         </is>
       </c>
     </row>
     <row r="211" ht="15" customHeight="1">
       <c r="A211" s="1" t="n"/>
       <c r="B211" s="1" t="n">
-        <v>60015</v>
+        <v>60006</v>
       </c>
       <c r="C211" s="1" t="n"/>
       <c r="D211" s="1" t="n">
@@ -4674,19 +4674,19 @@
       </c>
       <c r="E211" s="1" t="inlineStr">
         <is>
-          <t>BGM/战斗结算BGM</t>
+          <t>BGM/赫尔海姆副本BGM</t>
         </is>
       </c>
       <c r="F211" s="1" t="inlineStr">
         <is>
-          <t>战斗结算</t>
+          <t>赫尔海姆副本</t>
         </is>
       </c>
     </row>
     <row r="212" ht="15" customHeight="1">
       <c r="A212" s="1" t="n"/>
       <c r="B212" s="1" t="n">
-        <v>60016</v>
+        <v>60007</v>
       </c>
       <c r="C212" s="1" t="n"/>
       <c r="D212" s="1" t="n">
@@ -4694,19 +4694,19 @@
       </c>
       <c r="E212" s="1" t="inlineStr">
         <is>
-          <t>BGM/出战预设BGM</t>
+          <t>BGM/高天原副本BGM</t>
         </is>
       </c>
       <c r="F212" s="1" t="inlineStr">
         <is>
-          <t>出战预设</t>
+          <t>高天原副本</t>
         </is>
       </c>
     </row>
     <row r="213" ht="15" customHeight="1">
       <c r="A213" s="1" t="n"/>
       <c r="B213" s="1" t="n">
-        <v>60017</v>
+        <v>60008</v>
       </c>
       <c r="C213" s="1" t="n"/>
       <c r="D213" s="1" t="n">
@@ -4714,19 +4714,19 @@
       </c>
       <c r="E213" s="1" t="inlineStr">
         <is>
-          <t>BGM/背包界面BGM</t>
+          <t>BGM/奥林匹斯副本BGM</t>
         </is>
       </c>
       <c r="F213" s="1" t="inlineStr">
         <is>
-          <t>背包界面</t>
+          <t>奥林匹斯副本</t>
         </is>
       </c>
     </row>
     <row r="214" ht="15" customHeight="1">
       <c r="A214" s="1" t="n"/>
       <c r="B214" s="1" t="n">
-        <v>60018</v>
+        <v>60009</v>
       </c>
       <c r="C214" s="1" t="n"/>
       <c r="D214" s="1" t="n">
@@ -4734,19 +4734,19 @@
       </c>
       <c r="E214" s="1" t="inlineStr">
         <is>
-          <t>BGM/商城界面BGM</t>
+          <t>BGM/巴比伦副本BGM</t>
         </is>
       </c>
       <c r="F214" s="1" t="inlineStr">
         <is>
-          <t>商城界面</t>
+          <t>巴比伦副本</t>
         </is>
       </c>
     </row>
     <row r="215" ht="15" customHeight="1">
       <c r="A215" s="1" t="n"/>
       <c r="B215" s="1" t="n">
-        <v>60019</v>
+        <v>60010</v>
       </c>
       <c r="C215" s="1" t="n"/>
       <c r="D215" s="1" t="n">
@@ -4754,19 +4754,19 @@
       </c>
       <c r="E215" s="1" t="inlineStr">
         <is>
-          <t>BGM/升级界面BGM</t>
+          <t>BGM/阿瓦隆副本BGM</t>
         </is>
       </c>
       <c r="F215" s="1" t="inlineStr">
         <is>
-          <t>升级界面</t>
+          <t>阿瓦隆副本</t>
         </is>
       </c>
     </row>
     <row r="216" ht="15" customHeight="1">
       <c r="A216" s="1" t="n"/>
       <c r="B216" s="1" t="n">
-        <v>60020</v>
+        <v>60011</v>
       </c>
       <c r="C216" s="1" t="n"/>
       <c r="D216" s="1" t="n">
@@ -4774,19 +4774,19 @@
       </c>
       <c r="E216" s="1" t="inlineStr">
         <is>
-          <t>SFX/UI/按钮点击音效</t>
+          <t>BGM/深渊副本BGM</t>
         </is>
       </c>
       <c r="F216" s="1" t="inlineStr">
         <is>
-          <t>按钮点击</t>
+          <t>深渊副本</t>
         </is>
       </c>
     </row>
     <row r="217" ht="15" customHeight="1">
       <c r="A217" s="1" t="n"/>
       <c r="B217" s="1" t="n">
-        <v>60021</v>
+        <v>60012</v>
       </c>
       <c r="C217" s="1" t="n"/>
       <c r="D217" s="1" t="n">
@@ -4794,19 +4794,19 @@
       </c>
       <c r="E217" s="1" t="inlineStr">
         <is>
-          <t>SFX/UI/界面打开音效</t>
+          <t>BGM/普通敌人战斗BGM</t>
         </is>
       </c>
       <c r="F217" s="1" t="inlineStr">
         <is>
-          <t>界面打开</t>
+          <t>普通敌人战斗</t>
         </is>
       </c>
     </row>
     <row r="218" ht="15" customHeight="1">
       <c r="A218" s="1" t="n"/>
       <c r="B218" s="1" t="n">
-        <v>60022</v>
+        <v>60013</v>
       </c>
       <c r="C218" s="1" t="n"/>
       <c r="D218" s="1" t="n">
@@ -4814,19 +4814,19 @@
       </c>
       <c r="E218" s="1" t="inlineStr">
         <is>
-          <t>SFX/UI/界面关闭音效</t>
+          <t>BGM/精英敌人战斗BGM</t>
         </is>
       </c>
       <c r="F218" s="1" t="inlineStr">
         <is>
-          <t>界面关闭</t>
+          <t>精英敌人战斗</t>
         </is>
       </c>
     </row>
     <row r="219" ht="15" customHeight="1">
       <c r="A219" s="1" t="n"/>
       <c r="B219" s="1" t="n">
-        <v>60023</v>
+        <v>60014</v>
       </c>
       <c r="C219" s="1" t="n"/>
       <c r="D219" s="1" t="n">
@@ -4834,19 +4834,19 @@
       </c>
       <c r="E219" s="1" t="inlineStr">
         <is>
-          <t>SFX/UI/按钮悬停音效</t>
+          <t>BGM/Boss战斗BGM</t>
         </is>
       </c>
       <c r="F219" s="1" t="inlineStr">
         <is>
-          <t>按钮悬停</t>
+          <t>Boss战斗</t>
         </is>
       </c>
     </row>
     <row r="220" ht="15" customHeight="1">
       <c r="A220" s="1" t="n"/>
       <c r="B220" s="1" t="n">
-        <v>60024</v>
+        <v>60015</v>
       </c>
       <c r="C220" s="1" t="n"/>
       <c r="D220" s="1" t="n">
@@ -4854,19 +4854,19 @@
       </c>
       <c r="E220" s="1" t="inlineStr">
         <is>
-          <t>SFX/UI/标签页切换音效</t>
+          <t>BGM/战斗结算BGM</t>
         </is>
       </c>
       <c r="F220" s="1" t="inlineStr">
         <is>
-          <t>标签页切换</t>
+          <t>战斗结算</t>
         </is>
       </c>
     </row>
     <row r="221" ht="15" customHeight="1">
       <c r="A221" s="1" t="n"/>
       <c r="B221" s="1" t="n">
-        <v>60025</v>
+        <v>60016</v>
       </c>
       <c r="C221" s="1" t="n"/>
       <c r="D221" s="1" t="n">
@@ -4874,19 +4874,19 @@
       </c>
       <c r="E221" s="1" t="inlineStr">
         <is>
-          <t>SFX/UI/确认按钮音效</t>
+          <t>BGM/出战预设BGM</t>
         </is>
       </c>
       <c r="F221" s="1" t="inlineStr">
         <is>
-          <t>确认按钮</t>
+          <t>出战预设</t>
         </is>
       </c>
     </row>
     <row r="222" ht="15" customHeight="1">
       <c r="A222" s="1" t="n"/>
       <c r="B222" s="1" t="n">
-        <v>60026</v>
+        <v>60017</v>
       </c>
       <c r="C222" s="1" t="n"/>
       <c r="D222" s="1" t="n">
@@ -4894,19 +4894,19 @@
       </c>
       <c r="E222" s="1" t="inlineStr">
         <is>
-          <t>SFX/UI/取消按钮音效</t>
+          <t>BGM/背包界面BGM</t>
         </is>
       </c>
       <c r="F222" s="1" t="inlineStr">
         <is>
-          <t>取消按钮</t>
+          <t>背包界面</t>
         </is>
       </c>
     </row>
     <row r="223" ht="15" customHeight="1">
       <c r="A223" s="1" t="n"/>
       <c r="B223" s="1" t="n">
-        <v>60027</v>
+        <v>60018</v>
       </c>
       <c r="C223" s="1" t="n"/>
       <c r="D223" s="1" t="n">
@@ -4914,19 +4914,19 @@
       </c>
       <c r="E223" s="1" t="inlineStr">
         <is>
-          <t>SFX/UI/错误音效</t>
+          <t>BGM/商城界面BGM</t>
         </is>
       </c>
       <c r="F223" s="1" t="inlineStr">
         <is>
-          <t>错误音效</t>
+          <t>商城界面</t>
         </is>
       </c>
     </row>
     <row r="224" ht="15" customHeight="1">
       <c r="A224" s="1" t="n"/>
       <c r="B224" s="1" t="n">
-        <v>60028</v>
+        <v>60019</v>
       </c>
       <c r="C224" s="1" t="n"/>
       <c r="D224" s="1" t="n">
@@ -4934,19 +4934,19 @@
       </c>
       <c r="E224" s="1" t="inlineStr">
         <is>
-          <t>SFX/UI/成功音效</t>
+          <t>BGM/升级界面BGM</t>
         </is>
       </c>
       <c r="F224" s="1" t="inlineStr">
         <is>
-          <t>成功音效</t>
+          <t>升级界面</t>
         </is>
       </c>
     </row>
     <row r="225" ht="15" customHeight="1">
       <c r="A225" s="1" t="n"/>
       <c r="B225" s="1" t="n">
-        <v>60029</v>
+        <v>60020</v>
       </c>
       <c r="C225" s="1" t="n"/>
       <c r="D225" s="1" t="n">
@@ -4954,19 +4954,19 @@
       </c>
       <c r="E225" s="1" t="inlineStr">
         <is>
-          <t>SFX/UI/解锁音效</t>
+          <t>SFX/UI/按钮点击音效</t>
         </is>
       </c>
       <c r="F225" s="1" t="inlineStr">
         <is>
-          <t>解锁音效</t>
+          <t>按钮点击</t>
         </is>
       </c>
     </row>
     <row r="226" ht="15" customHeight="1">
       <c r="A226" s="1" t="n"/>
       <c r="B226" s="1" t="n">
-        <v>60030</v>
+        <v>60021</v>
       </c>
       <c r="C226" s="1" t="n"/>
       <c r="D226" s="1" t="n">
@@ -4974,19 +4974,19 @@
       </c>
       <c r="E226" s="1" t="inlineStr">
         <is>
-          <t>SFX/UI/通知提示音音效</t>
+          <t>SFX/UI/界面打开音效</t>
         </is>
       </c>
       <c r="F226" s="1" t="inlineStr">
         <is>
-          <t>通知提示音</t>
+          <t>界面打开</t>
         </is>
       </c>
     </row>
     <row r="227" ht="15" customHeight="1">
       <c r="A227" s="1" t="n"/>
       <c r="B227" s="1" t="n">
-        <v>60031</v>
+        <v>60022</v>
       </c>
       <c r="C227" s="1" t="n"/>
       <c r="D227" s="1" t="n">
@@ -4994,19 +4994,19 @@
       </c>
       <c r="E227" s="1" t="inlineStr">
         <is>
-          <t>SFX/UI/货币获得音效</t>
+          <t>SFX/UI/界面关闭音效</t>
         </is>
       </c>
       <c r="F227" s="1" t="inlineStr">
         <is>
-          <t>货币获得</t>
+          <t>界面关闭</t>
         </is>
       </c>
     </row>
     <row r="228" ht="15" customHeight="1">
       <c r="A228" s="1" t="n"/>
       <c r="B228" s="1" t="n">
-        <v>60032</v>
+        <v>60023</v>
       </c>
       <c r="C228" s="1" t="n"/>
       <c r="D228" s="1" t="n">
@@ -5014,19 +5014,19 @@
       </c>
       <c r="E228" s="1" t="inlineStr">
         <is>
-          <t>SFX/Combat/棋子选中音效</t>
+          <t>SFX/UI/按钮悬停音效</t>
         </is>
       </c>
       <c r="F228" s="1" t="inlineStr">
         <is>
-          <t>棋子选中</t>
+          <t>按钮悬停</t>
         </is>
       </c>
     </row>
     <row r="229" ht="15" customHeight="1">
       <c r="A229" s="1" t="n"/>
       <c r="B229" s="1" t="n">
-        <v>60033</v>
+        <v>60024</v>
       </c>
       <c r="C229" s="1" t="n"/>
       <c r="D229" s="1" t="n">
@@ -5034,19 +5034,19 @@
       </c>
       <c r="E229" s="1" t="inlineStr">
         <is>
-          <t>SFX/Combat/移动开始音效</t>
+          <t>SFX/UI/标签页切换音效</t>
         </is>
       </c>
       <c r="F229" s="1" t="inlineStr">
         <is>
-          <t>移动开始</t>
+          <t>标签页切换</t>
         </is>
       </c>
     </row>
     <row r="230" ht="15" customHeight="1">
       <c r="A230" s="1" t="n"/>
       <c r="B230" s="1" t="n">
-        <v>60034</v>
+        <v>60025</v>
       </c>
       <c r="C230" s="1" t="n"/>
       <c r="D230" s="1" t="n">
@@ -5054,19 +5054,19 @@
       </c>
       <c r="E230" s="1" t="inlineStr">
         <is>
-          <t>SFX/Combat/移动停止音效</t>
+          <t>SFX/UI/确认按钮音效</t>
         </is>
       </c>
       <c r="F230" s="1" t="inlineStr">
         <is>
-          <t>移动停止</t>
+          <t>确认按钮</t>
         </is>
       </c>
     </row>
     <row r="231" ht="15" customHeight="1">
       <c r="A231" s="1" t="n"/>
       <c r="B231" s="1" t="n">
-        <v>60035</v>
+        <v>60026</v>
       </c>
       <c r="C231" s="1" t="n"/>
       <c r="D231" s="1" t="n">
@@ -5074,19 +5074,19 @@
       </c>
       <c r="E231" s="1" t="inlineStr">
         <is>
-          <t>SFX/Combat/攻击蓄力音效</t>
+          <t>SFX/UI/取消按钮音效</t>
         </is>
       </c>
       <c r="F231" s="1" t="inlineStr">
         <is>
-          <t>攻击蓄力</t>
+          <t>取消按钮</t>
         </is>
       </c>
     </row>
     <row r="232" ht="15" customHeight="1">
       <c r="A232" s="1" t="n"/>
       <c r="B232" s="1" t="n">
-        <v>60036</v>
+        <v>60027</v>
       </c>
       <c r="C232" s="1" t="n"/>
       <c r="D232" s="1" t="n">
@@ -5094,19 +5094,19 @@
       </c>
       <c r="E232" s="1" t="inlineStr">
         <is>
-          <t>SFX/Combat/攻击释放音效</t>
+          <t>SFX/UI/错误音效</t>
         </is>
       </c>
       <c r="F232" s="1" t="inlineStr">
         <is>
-          <t>攻击释放</t>
+          <t>错误音效</t>
         </is>
       </c>
     </row>
     <row r="233" ht="15" customHeight="1">
       <c r="A233" s="1" t="n"/>
       <c r="B233" s="1" t="n">
-        <v>60037</v>
+        <v>60028</v>
       </c>
       <c r="C233" s="1" t="n"/>
       <c r="D233" s="1" t="n">
@@ -5114,19 +5114,19 @@
       </c>
       <c r="E233" s="1" t="inlineStr">
         <is>
-          <t>SFX/Combat/攻击破风音效</t>
+          <t>SFX/UI/成功音效</t>
         </is>
       </c>
       <c r="F233" s="1" t="inlineStr">
         <is>
-          <t>攻击破风</t>
+          <t>成功音效</t>
         </is>
       </c>
     </row>
     <row r="234" ht="15" customHeight="1">
       <c r="A234" s="1" t="n"/>
       <c r="B234" s="1" t="n">
-        <v>60038</v>
+        <v>60029</v>
       </c>
       <c r="C234" s="1" t="n"/>
       <c r="D234" s="1" t="n">
@@ -5134,19 +5134,19 @@
       </c>
       <c r="E234" s="1" t="inlineStr">
         <is>
-          <t>SFX/Combat/技能施放音效</t>
+          <t>SFX/UI/解锁音效</t>
         </is>
       </c>
       <c r="F234" s="1" t="inlineStr">
         <is>
-          <t>技能施放</t>
+          <t>解锁音效</t>
         </is>
       </c>
     </row>
     <row r="235" ht="15" customHeight="1">
       <c r="A235" s="1" t="n"/>
       <c r="B235" s="1" t="n">
-        <v>60039</v>
+        <v>60030</v>
       </c>
       <c r="C235" s="1" t="n"/>
       <c r="D235" s="1" t="n">
@@ -5154,19 +5154,19 @@
       </c>
       <c r="E235" s="1" t="inlineStr">
         <is>
-          <t>SFX/Combat/Buff应用音效</t>
+          <t>SFX/UI/通知提示音音效</t>
         </is>
       </c>
       <c r="F235" s="1" t="inlineStr">
         <is>
-          <t>Buff应用</t>
+          <t>通知提示音</t>
         </is>
       </c>
     </row>
     <row r="236" ht="15" customHeight="1">
       <c r="A236" s="1" t="n"/>
       <c r="B236" s="1" t="n">
-        <v>60040</v>
+        <v>60031</v>
       </c>
       <c r="C236" s="1" t="n"/>
       <c r="D236" s="1" t="n">
@@ -5174,19 +5174,19 @@
       </c>
       <c r="E236" s="1" t="inlineStr">
         <is>
-          <t>SFX/Combat/Debuff应用音效</t>
+          <t>SFX/UI/货币获得音效</t>
         </is>
       </c>
       <c r="F236" s="1" t="inlineStr">
         <is>
-          <t>Debuff应用</t>
+          <t>货币获得</t>
         </is>
       </c>
     </row>
     <row r="237" ht="15" customHeight="1">
       <c r="A237" s="1" t="n"/>
       <c r="B237" s="1" t="n">
-        <v>60041</v>
+        <v>60032</v>
       </c>
       <c r="C237" s="1" t="n"/>
       <c r="D237" s="1" t="n">
@@ -5194,19 +5194,19 @@
       </c>
       <c r="E237" s="1" t="inlineStr">
         <is>
-          <t>SFX/Combat/轻度伤害音效</t>
+          <t>SFX/Combat/棋子选中音效</t>
         </is>
       </c>
       <c r="F237" s="1" t="inlineStr">
         <is>
-          <t>轻度伤害</t>
+          <t>棋子选中</t>
         </is>
       </c>
     </row>
     <row r="238" ht="15" customHeight="1">
       <c r="A238" s="1" t="n"/>
       <c r="B238" s="1" t="n">
-        <v>60042</v>
+        <v>60033</v>
       </c>
       <c r="C238" s="1" t="n"/>
       <c r="D238" s="1" t="n">
@@ -5214,19 +5214,19 @@
       </c>
       <c r="E238" s="1" t="inlineStr">
         <is>
-          <t>SFX/Combat/普通伤害音效</t>
+          <t>SFX/Combat/移动开始音效</t>
         </is>
       </c>
       <c r="F238" s="1" t="inlineStr">
         <is>
-          <t>普通伤害</t>
+          <t>移动开始</t>
         </is>
       </c>
     </row>
     <row r="239" ht="15" customHeight="1">
       <c r="A239" s="1" t="n"/>
       <c r="B239" s="1" t="n">
-        <v>60043</v>
+        <v>60034</v>
       </c>
       <c r="C239" s="1" t="n"/>
       <c r="D239" s="1" t="n">
@@ -5234,19 +5234,19 @@
       </c>
       <c r="E239" s="1" t="inlineStr">
         <is>
-          <t>SFX/Combat/重度伤害音效</t>
+          <t>SFX/Combat/移动停止音效</t>
         </is>
       </c>
       <c r="F239" s="1" t="inlineStr">
         <is>
-          <t>重度伤害</t>
+          <t>移动停止</t>
         </is>
       </c>
     </row>
     <row r="240" ht="15" customHeight="1">
       <c r="A240" s="1" t="n"/>
       <c r="B240" s="1" t="n">
-        <v>60044</v>
+        <v>60035</v>
       </c>
       <c r="C240" s="1" t="n"/>
       <c r="D240" s="1" t="n">
@@ -5254,19 +5254,19 @@
       </c>
       <c r="E240" s="1" t="inlineStr">
         <is>
-          <t>SFX/Combat/暴击伤害音效</t>
+          <t>SFX/Combat/攻击蓄力音效</t>
         </is>
       </c>
       <c r="F240" s="1" t="inlineStr">
         <is>
-          <t>暴击伤害</t>
+          <t>攻击蓄力</t>
         </is>
       </c>
     </row>
     <row r="241" ht="15" customHeight="1">
       <c r="A241" s="1" t="n"/>
       <c r="B241" s="1" t="n">
-        <v>60045</v>
+        <v>60036</v>
       </c>
       <c r="C241" s="1" t="n"/>
       <c r="D241" s="1" t="n">
@@ -5274,19 +5274,19 @@
       </c>
       <c r="E241" s="1" t="inlineStr">
         <is>
-          <t>SFX/Combat/闪避格挡音效</t>
+          <t>SFX/Combat/攻击释放音效</t>
         </is>
       </c>
       <c r="F241" s="1" t="inlineStr">
         <is>
-          <t>闪避/格挡</t>
+          <t>攻击释放</t>
         </is>
       </c>
     </row>
     <row r="242" ht="15" customHeight="1">
       <c r="A242" s="1" t="n"/>
       <c r="B242" s="1" t="n">
-        <v>60046</v>
+        <v>60037</v>
       </c>
       <c r="C242" s="1" t="n"/>
       <c r="D242" s="1" t="n">
@@ -5294,19 +5294,19 @@
       </c>
       <c r="E242" s="1" t="inlineStr">
         <is>
-          <t>SFX/Combat/治疗音效</t>
+          <t>SFX/Combat/攻击破风音效</t>
         </is>
       </c>
       <c r="F242" s="1" t="inlineStr">
         <is>
-          <t>治疗</t>
+          <t>攻击破风</t>
         </is>
       </c>
     </row>
     <row r="243" ht="15" customHeight="1">
       <c r="A243" s="1" t="n"/>
       <c r="B243" s="1" t="n">
-        <v>60047</v>
+        <v>60038</v>
       </c>
       <c r="C243" s="1" t="n"/>
       <c r="D243" s="1" t="n">
@@ -5314,19 +5314,19 @@
       </c>
       <c r="E243" s="1" t="inlineStr">
         <is>
-          <t>SFX/Combat/护盾获得音效</t>
+          <t>SFX/Combat/技能施放音效</t>
         </is>
       </c>
       <c r="F243" s="1" t="inlineStr">
         <is>
-          <t>护盾获得</t>
+          <t>技能施放</t>
         </is>
       </c>
     </row>
     <row r="244" ht="15" customHeight="1">
       <c r="A244" s="1" t="n"/>
       <c r="B244" s="1" t="n">
-        <v>60048</v>
+        <v>60039</v>
       </c>
       <c r="C244" s="1" t="n"/>
       <c r="D244" s="1" t="n">
@@ -5334,19 +5334,19 @@
       </c>
       <c r="E244" s="1" t="inlineStr">
         <is>
-          <t>SFX/Combat/死亡音效</t>
+          <t>SFX/Combat/Buff应用音效</t>
         </is>
       </c>
       <c r="F244" s="1" t="inlineStr">
         <is>
-          <t>死亡</t>
+          <t>Buff应用</t>
         </is>
       </c>
     </row>
     <row r="245" ht="15" customHeight="1">
       <c r="A245" s="1" t="n"/>
       <c r="B245" s="1" t="n">
-        <v>60049</v>
+        <v>60040</v>
       </c>
       <c r="C245" s="1" t="n"/>
       <c r="D245" s="1" t="n">
@@ -5354,19 +5354,19 @@
       </c>
       <c r="E245" s="1" t="inlineStr">
         <is>
-          <t>SFX/Combat/回合开始音效</t>
+          <t>SFX/Combat/Debuff应用音效</t>
         </is>
       </c>
       <c r="F245" s="1" t="inlineStr">
         <is>
-          <t>回合开始</t>
+          <t>Debuff应用</t>
         </is>
       </c>
     </row>
     <row r="246" ht="15" customHeight="1">
       <c r="A246" s="1" t="n"/>
       <c r="B246" s="1" t="n">
-        <v>60050</v>
+        <v>60041</v>
       </c>
       <c r="C246" s="1" t="n"/>
       <c r="D246" s="1" t="n">
@@ -5374,19 +5374,19 @@
       </c>
       <c r="E246" s="1" t="inlineStr">
         <is>
-          <t>SFX/Combat/回合结束音效</t>
+          <t>SFX/Combat/轻度伤害音效</t>
         </is>
       </c>
       <c r="F246" s="1" t="inlineStr">
         <is>
-          <t>回合结束</t>
+          <t>轻度伤害</t>
         </is>
       </c>
     </row>
     <row r="247" ht="15" customHeight="1">
       <c r="A247" s="1" t="n"/>
       <c r="B247" s="1" t="n">
-        <v>60051</v>
+        <v>60042</v>
       </c>
       <c r="C247" s="1" t="n"/>
       <c r="D247" s="1" t="n">
@@ -5394,19 +5394,19 @@
       </c>
       <c r="E247" s="1" t="inlineStr">
         <is>
-          <t>SFX/Combat/战斗开始音效</t>
+          <t>SFX/Combat/普通伤害音效</t>
         </is>
       </c>
       <c r="F247" s="1" t="inlineStr">
         <is>
-          <t>战斗开始</t>
+          <t>普通伤害</t>
         </is>
       </c>
     </row>
     <row r="248" ht="15" customHeight="1">
       <c r="A248" s="1" t="n"/>
       <c r="B248" s="1" t="n">
-        <v>60052</v>
+        <v>60043</v>
       </c>
       <c r="C248" s="1" t="n"/>
       <c r="D248" s="1" t="n">
@@ -5414,19 +5414,19 @@
       </c>
       <c r="E248" s="1" t="inlineStr">
         <is>
-          <t>SFX/Combat/Boss出现音效</t>
+          <t>SFX/Combat/重度伤害音效</t>
         </is>
       </c>
       <c r="F248" s="1" t="inlineStr">
         <is>
-          <t>Boss出现</t>
+          <t>重度伤害</t>
         </is>
       </c>
     </row>
     <row r="249" ht="15" customHeight="1">
       <c r="A249" s="1" t="n"/>
       <c r="B249" s="1" t="n">
-        <v>60053</v>
+        <v>60044</v>
       </c>
       <c r="C249" s="1" t="n"/>
       <c r="D249" s="1" t="n">
@@ -5434,19 +5434,19 @@
       </c>
       <c r="E249" s="1" t="inlineStr">
         <is>
-          <t>SFX/Combat/Boss技能警告音效</t>
+          <t>SFX/Combat/暴击伤害音效</t>
         </is>
       </c>
       <c r="F249" s="1" t="inlineStr">
         <is>
-          <t>Boss技能警告</t>
+          <t>暴击伤害</t>
         </is>
       </c>
     </row>
     <row r="250" ht="15" customHeight="1">
       <c r="A250" s="1" t="n"/>
       <c r="B250" s="1" t="n">
-        <v>60054</v>
+        <v>60045</v>
       </c>
       <c r="C250" s="1" t="n"/>
       <c r="D250" s="1" t="n">
@@ -5454,19 +5454,19 @@
       </c>
       <c r="E250" s="1" t="inlineStr">
         <is>
-          <t>SFX/Combat/战斗胜利音效</t>
+          <t>SFX/Combat/闪避格挡音效</t>
         </is>
       </c>
       <c r="F250" s="1" t="inlineStr">
         <is>
-          <t>战斗胜利</t>
+          <t>闪避/格挡</t>
         </is>
       </c>
     </row>
     <row r="251" ht="15" customHeight="1">
       <c r="A251" s="1" t="n"/>
       <c r="B251" s="1" t="n">
-        <v>60055</v>
+        <v>60046</v>
       </c>
       <c r="C251" s="1" t="n"/>
       <c r="D251" s="1" t="n">
@@ -5474,19 +5474,19 @@
       </c>
       <c r="E251" s="1" t="inlineStr">
         <is>
-          <t>SFX/Combat/战斗失败音效</t>
+          <t>SFX/Combat/治疗音效</t>
         </is>
       </c>
       <c r="F251" s="1" t="inlineStr">
         <is>
-          <t>战斗失败</t>
+          <t>治疗</t>
         </is>
       </c>
     </row>
     <row r="252" ht="15" customHeight="1">
       <c r="A252" s="1" t="n"/>
       <c r="B252" s="1" t="n">
-        <v>60056</v>
+        <v>60047</v>
       </c>
       <c r="C252" s="1" t="n"/>
       <c r="D252" s="1" t="n">
@@ -5494,19 +5494,19 @@
       </c>
       <c r="E252" s="1" t="inlineStr">
         <is>
-          <t>SFX/Explore/脚步声音效</t>
+          <t>SFX/Combat/护盾获得音效</t>
         </is>
       </c>
       <c r="F252" s="1" t="inlineStr">
         <is>
-          <t>脚步声</t>
+          <t>护盾获得</t>
         </is>
       </c>
     </row>
     <row r="253" ht="15" customHeight="1">
       <c r="A253" s="1" t="n"/>
       <c r="B253" s="1" t="n">
-        <v>60057</v>
+        <v>60048</v>
       </c>
       <c r="C253" s="1" t="n"/>
       <c r="D253" s="1" t="n">
@@ -5514,19 +5514,19 @@
       </c>
       <c r="E253" s="1" t="inlineStr">
         <is>
-          <t>SFX/Explore/物品捡起音效</t>
+          <t>SFX/Combat/死亡音效</t>
         </is>
       </c>
       <c r="F253" s="1" t="inlineStr">
         <is>
-          <t>物品捡起</t>
+          <t>死亡</t>
         </is>
       </c>
     </row>
     <row r="254" ht="15" customHeight="1">
       <c r="A254" s="1" t="n"/>
       <c r="B254" s="1" t="n">
-        <v>60058</v>
+        <v>60049</v>
       </c>
       <c r="C254" s="1" t="n"/>
       <c r="D254" s="1" t="n">
@@ -5534,19 +5534,19 @@
       </c>
       <c r="E254" s="1" t="inlineStr">
         <is>
-          <t>SFX/Explore/宝箱打开音效</t>
+          <t>SFX/Combat/回合开始音效</t>
         </is>
       </c>
       <c r="F254" s="1" t="inlineStr">
         <is>
-          <t>宝箱打开</t>
+          <t>回合开始</t>
         </is>
       </c>
     </row>
     <row r="255" ht="15" customHeight="1">
       <c r="A255" s="1" t="n"/>
       <c r="B255" s="1" t="n">
-        <v>60059</v>
+        <v>60050</v>
       </c>
       <c r="C255" s="1" t="n"/>
       <c r="D255" s="1" t="n">
@@ -5554,19 +5554,19 @@
       </c>
       <c r="E255" s="1" t="inlineStr">
         <is>
-          <t>SFX/Explore/门打开音效</t>
+          <t>SFX/Combat/回合结束音效</t>
         </is>
       </c>
       <c r="F255" s="1" t="inlineStr">
         <is>
-          <t>门打开</t>
+          <t>回合结束</t>
         </is>
       </c>
     </row>
     <row r="256" ht="15" customHeight="1">
       <c r="A256" s="1" t="n"/>
       <c r="B256" s="1" t="n">
-        <v>60060</v>
+        <v>60051</v>
       </c>
       <c r="C256" s="1" t="n"/>
       <c r="D256" s="1" t="n">
@@ -5574,19 +5574,19 @@
       </c>
       <c r="E256" s="1" t="inlineStr">
         <is>
-          <t>SFX/Explore/门关闭音效</t>
+          <t>SFX/Combat/战斗开始音效</t>
         </is>
       </c>
       <c r="F256" s="1" t="inlineStr">
         <is>
-          <t>门关闭</t>
+          <t>战斗开始</t>
         </is>
       </c>
     </row>
     <row r="257" ht="15" customHeight="1">
       <c r="A257" s="1" t="n"/>
       <c r="B257" s="1" t="n">
-        <v>60061</v>
+        <v>60052</v>
       </c>
       <c r="C257" s="1" t="n"/>
       <c r="D257" s="1" t="n">
@@ -5594,19 +5594,19 @@
       </c>
       <c r="E257" s="1" t="inlineStr">
         <is>
-          <t>SFX/Explore/NPC对话音效</t>
+          <t>SFX/Combat/Boss出现音效</t>
         </is>
       </c>
       <c r="F257" s="1" t="inlineStr">
         <is>
-          <t>NPC对话</t>
+          <t>Boss出现</t>
         </is>
       </c>
     </row>
     <row r="258" ht="15" customHeight="1">
       <c r="A258" s="1" t="n"/>
       <c r="B258" s="1" t="n">
-        <v>60062</v>
+        <v>60053</v>
       </c>
       <c r="C258" s="1" t="n"/>
       <c r="D258" s="1" t="n">
@@ -5614,19 +5614,19 @@
       </c>
       <c r="E258" s="1" t="inlineStr">
         <is>
-          <t>SFX/Explore/任务接受音效</t>
+          <t>SFX/Combat/Boss技能警告音效</t>
         </is>
       </c>
       <c r="F258" s="1" t="inlineStr">
         <is>
-          <t>任务接受</t>
+          <t>Boss技能警告</t>
         </is>
       </c>
     </row>
     <row r="259" ht="15" customHeight="1">
       <c r="A259" s="1" t="n"/>
       <c r="B259" s="1" t="n">
-        <v>60063</v>
+        <v>60054</v>
       </c>
       <c r="C259" s="1" t="n"/>
       <c r="D259" s="1" t="n">
@@ -5634,19 +5634,19 @@
       </c>
       <c r="E259" s="1" t="inlineStr">
         <is>
-          <t>SFX/Explore/任务完成音效</t>
+          <t>SFX/Combat/战斗胜利音效</t>
         </is>
       </c>
       <c r="F259" s="1" t="inlineStr">
         <is>
-          <t>任务完成</t>
+          <t>战斗胜利</t>
         </is>
       </c>
     </row>
     <row r="260" ht="15" customHeight="1">
       <c r="A260" s="1" t="n"/>
       <c r="B260" s="1" t="n">
-        <v>60064</v>
+        <v>60055</v>
       </c>
       <c r="C260" s="1" t="n"/>
       <c r="D260" s="1" t="n">
@@ -5654,19 +5654,19 @@
       </c>
       <c r="E260" s="1" t="inlineStr">
         <is>
-          <t>SFX/Ambient/风声音效</t>
+          <t>SFX/Combat/战斗失败音效</t>
         </is>
       </c>
       <c r="F260" s="1" t="inlineStr">
         <is>
-          <t>风声</t>
+          <t>战斗失败</t>
         </is>
       </c>
     </row>
     <row r="261" ht="15" customHeight="1">
       <c r="A261" s="1" t="n"/>
       <c r="B261" s="1" t="n">
-        <v>60065</v>
+        <v>60056</v>
       </c>
       <c r="C261" s="1" t="n"/>
       <c r="D261" s="1" t="n">
@@ -5674,19 +5674,19 @@
       </c>
       <c r="E261" s="1" t="inlineStr">
         <is>
-          <t>SFX/Ambient/雷声音效</t>
+          <t>SFX/Explore/脚步声音效</t>
         </is>
       </c>
       <c r="F261" s="1" t="inlineStr">
         <is>
-          <t>雷声</t>
+          <t>脚步声</t>
         </is>
       </c>
     </row>
     <row r="262" ht="15" customHeight="1">
       <c r="A262" s="1" t="n"/>
       <c r="B262" s="1" t="n">
-        <v>60066</v>
+        <v>60057</v>
       </c>
       <c r="C262" s="1" t="n"/>
       <c r="D262" s="1" t="n">
@@ -5694,19 +5694,19 @@
       </c>
       <c r="E262" s="1" t="inlineStr">
         <is>
-          <t>SFX/Ambient/流水声音效</t>
+          <t>SFX/Explore/物品捡起音效</t>
         </is>
       </c>
       <c r="F262" s="1" t="inlineStr">
         <is>
-          <t>流水声</t>
+          <t>物品捡起</t>
         </is>
       </c>
     </row>
     <row r="263" ht="15" customHeight="1">
       <c r="A263" s="1" t="n"/>
       <c r="B263" s="1" t="n">
-        <v>60067</v>
+        <v>60058</v>
       </c>
       <c r="C263" s="1" t="n"/>
       <c r="D263" s="1" t="n">
@@ -5714,19 +5714,19 @@
       </c>
       <c r="E263" s="1" t="inlineStr">
         <is>
-          <t>SFX/Ambient/火焰声音效</t>
+          <t>SFX/Explore/宝箱打开音效</t>
         </is>
       </c>
       <c r="F263" s="1" t="inlineStr">
         <is>
-          <t>火焰声</t>
+          <t>宝箱打开</t>
         </is>
       </c>
     </row>
     <row r="264" ht="15" customHeight="1">
       <c r="A264" s="1" t="n"/>
       <c r="B264" s="1" t="n">
-        <v>60068</v>
+        <v>60059</v>
       </c>
       <c r="C264" s="1" t="n"/>
       <c r="D264" s="1" t="n">
@@ -5734,19 +5734,19 @@
       </c>
       <c r="E264" s="1" t="inlineStr">
         <is>
-          <t>SFX/Ambient/阴冷氛围音效</t>
+          <t>SFX/Explore/门打开音效</t>
         </is>
       </c>
       <c r="F264" s="1" t="inlineStr">
         <is>
-          <t>阴冷氛围</t>
+          <t>门打开</t>
         </is>
       </c>
     </row>
     <row r="265" ht="15" customHeight="1">
       <c r="A265" s="1" t="n"/>
       <c r="B265" s="1" t="n">
-        <v>60069</v>
+        <v>60060</v>
       </c>
       <c r="C265" s="1" t="n"/>
       <c r="D265" s="1" t="n">
@@ -5754,19 +5754,19 @@
       </c>
       <c r="E265" s="1" t="inlineStr">
         <is>
-          <t>SFX/Ambient/诡异低语音效</t>
+          <t>SFX/Explore/门关闭音效</t>
         </is>
       </c>
       <c r="F265" s="1" t="inlineStr">
         <is>
-          <t>诡异低语</t>
+          <t>门关闭</t>
         </is>
       </c>
     </row>
     <row r="266" ht="15" customHeight="1">
       <c r="A266" s="1" t="n"/>
       <c r="B266" s="1" t="n">
-        <v>60070</v>
+        <v>60061</v>
       </c>
       <c r="C266" s="1" t="n"/>
       <c r="D266" s="1" t="n">
@@ -5774,19 +5774,19 @@
       </c>
       <c r="E266" s="1" t="inlineStr">
         <is>
-          <t>SFX/Explore/传送进入音效</t>
+          <t>SFX/Explore/NPC对话音效</t>
         </is>
       </c>
       <c r="F266" s="1" t="inlineStr">
         <is>
-          <t>传送进入</t>
+          <t>NPC对话</t>
         </is>
       </c>
     </row>
     <row r="267" ht="15" customHeight="1">
       <c r="A267" s="1" t="n"/>
       <c r="B267" s="1" t="n">
-        <v>60071</v>
+        <v>60062</v>
       </c>
       <c r="C267" s="1" t="n"/>
       <c r="D267" s="1" t="n">
@@ -5794,19 +5794,19 @@
       </c>
       <c r="E267" s="1" t="inlineStr">
         <is>
-          <t>SFX/Explore/传送离开音效</t>
+          <t>SFX/Explore/任务接受音效</t>
         </is>
       </c>
       <c r="F267" s="1" t="inlineStr">
         <is>
-          <t>传送离开</t>
+          <t>任务接受</t>
         </is>
       </c>
     </row>
     <row r="268" ht="15" customHeight="1">
       <c r="A268" s="1" t="n"/>
       <c r="B268" s="1" t="n">
-        <v>60072</v>
+        <v>60063</v>
       </c>
       <c r="C268" s="1" t="n"/>
       <c r="D268" s="1" t="n">
@@ -5814,19 +5814,19 @@
       </c>
       <c r="E268" s="1" t="inlineStr">
         <is>
-          <t>SFX/UI/场景加载音效</t>
+          <t>SFX/Explore/任务完成音效</t>
         </is>
       </c>
       <c r="F268" s="1" t="inlineStr">
         <is>
-          <t>场景加载</t>
+          <t>任务完成</t>
         </is>
       </c>
     </row>
     <row r="269" ht="15" customHeight="1">
       <c r="A269" s="1" t="n"/>
       <c r="B269" s="1" t="n">
-        <v>60073</v>
+        <v>60064</v>
       </c>
       <c r="C269" s="1" t="n"/>
       <c r="D269" s="1" t="n">
@@ -5834,19 +5834,19 @@
       </c>
       <c r="E269" s="1" t="inlineStr">
         <is>
-          <t>SFX/Explore/传送准备音效</t>
+          <t>SFX/Ambient/风声音效</t>
         </is>
       </c>
       <c r="F269" s="1" t="inlineStr">
         <is>
-          <t>传送准备</t>
+          <t>风声</t>
         </is>
       </c>
     </row>
     <row r="270" ht="15" customHeight="1">
       <c r="A270" s="1" t="n"/>
       <c r="B270" s="1" t="n">
-        <v>60074</v>
+        <v>60065</v>
       </c>
       <c r="C270" s="1" t="n"/>
       <c r="D270" s="1" t="n">
@@ -5854,19 +5854,19 @@
       </c>
       <c r="E270" s="1" t="inlineStr">
         <is>
-          <t>SFX/Reward/成就解锁音效</t>
+          <t>SFX/Ambient/雷声音效</t>
         </is>
       </c>
       <c r="F270" s="1" t="inlineStr">
         <is>
-          <t>成就解锁</t>
+          <t>雷声</t>
         </is>
       </c>
     </row>
     <row r="271" ht="15" customHeight="1">
       <c r="A271" s="1" t="n"/>
       <c r="B271" s="1" t="n">
-        <v>60075</v>
+        <v>60066</v>
       </c>
       <c r="C271" s="1" t="n"/>
       <c r="D271" s="1" t="n">
@@ -5874,19 +5874,19 @@
       </c>
       <c r="E271" s="1" t="inlineStr">
         <is>
-          <t>SFX/Reward/等级提升音效</t>
+          <t>SFX/Ambient/流水声音效</t>
         </is>
       </c>
       <c r="F271" s="1" t="inlineStr">
         <is>
-          <t>等级提升</t>
+          <t>流水声</t>
         </is>
       </c>
     </row>
     <row r="272" ht="15" customHeight="1">
       <c r="A272" s="1" t="n"/>
       <c r="B272" s="1" t="n">
-        <v>60076</v>
+        <v>60067</v>
       </c>
       <c r="C272" s="1" t="n"/>
       <c r="D272" s="1" t="n">
@@ -5894,19 +5894,19 @@
       </c>
       <c r="E272" s="1" t="inlineStr">
         <is>
-          <t>SFX/Reward/品质提升音效</t>
+          <t>SFX/Ambient/火焰声音效</t>
         </is>
       </c>
       <c r="F272" s="1" t="inlineStr">
         <is>
-          <t>品质提升</t>
+          <t>火焰声</t>
         </is>
       </c>
     </row>
     <row r="273" ht="15" customHeight="1">
       <c r="A273" s="1" t="n"/>
       <c r="B273" s="1" t="n">
-        <v>60077</v>
+        <v>60068</v>
       </c>
       <c r="C273" s="1" t="n"/>
       <c r="D273" s="1" t="n">
@@ -5914,19 +5914,19 @@
       </c>
       <c r="E273" s="1" t="inlineStr">
         <is>
-          <t>SFX/Reward/额外奖励音效</t>
+          <t>SFX/Ambient/阴冷氛围音效</t>
         </is>
       </c>
       <c r="F273" s="1" t="inlineStr">
         <is>
-          <t>额外奖励</t>
+          <t>阴冷氛围</t>
         </is>
       </c>
     </row>
     <row r="274" ht="15" customHeight="1">
       <c r="A274" s="1" t="n"/>
       <c r="B274" s="1" t="n">
-        <v>60078</v>
+        <v>60069</v>
       </c>
       <c r="C274" s="1" t="n"/>
       <c r="D274" s="1" t="n">
@@ -5934,19 +5934,19 @@
       </c>
       <c r="E274" s="1" t="inlineStr">
         <is>
-          <t>SFX/Reward/传说物品音效</t>
+          <t>SFX/Ambient/诡异低语音效</t>
         </is>
       </c>
       <c r="F274" s="1" t="inlineStr">
         <is>
-          <t>传说物品</t>
+          <t>诡异低语</t>
         </is>
       </c>
     </row>
     <row r="275" ht="15" customHeight="1">
       <c r="A275" s="1" t="n"/>
       <c r="B275" s="1" t="n">
-        <v>60079</v>
+        <v>60070</v>
       </c>
       <c r="C275" s="1" t="n"/>
       <c r="D275" s="1" t="n">
@@ -5954,19 +5954,19 @@
       </c>
       <c r="E275" s="1" t="inlineStr">
         <is>
-          <t>SFX/UI/金币捡起音效</t>
+          <t>SFX/Explore/传送进入音效</t>
         </is>
       </c>
       <c r="F275" s="1" t="inlineStr">
         <is>
-          <t>金币捡起</t>
+          <t>传送进入</t>
         </is>
       </c>
     </row>
     <row r="276" ht="15" customHeight="1">
       <c r="A276" s="1" t="n"/>
       <c r="B276" s="1" t="n">
-        <v>60080</v>
+        <v>60071</v>
       </c>
       <c r="C276" s="1" t="n"/>
       <c r="D276" s="1" t="n">
@@ -5974,19 +5974,19 @@
       </c>
       <c r="E276" s="1" t="inlineStr">
         <is>
-          <t>SFX/UI/宝石捡起音效</t>
+          <t>SFX/Explore/传送离开音效</t>
         </is>
       </c>
       <c r="F276" s="1" t="inlineStr">
         <is>
-          <t>宝石捡起</t>
+          <t>传送离开</t>
         </is>
       </c>
     </row>
     <row r="277" ht="15" customHeight="1">
       <c r="A277" s="1" t="n"/>
       <c r="B277" s="1" t="n">
-        <v>60081</v>
+        <v>60072</v>
       </c>
       <c r="C277" s="1" t="n"/>
       <c r="D277" s="1" t="n">
@@ -5994,19 +5994,19 @@
       </c>
       <c r="E277" s="1" t="inlineStr">
         <is>
-          <t>SFX/UI/金币消耗音效</t>
+          <t>SFX/UI/场景加载音效</t>
         </is>
       </c>
       <c r="F277" s="1" t="inlineStr">
         <is>
-          <t>金币消耗</t>
+          <t>场景加载</t>
         </is>
       </c>
     </row>
     <row r="278" ht="15" customHeight="1">
       <c r="A278" s="1" t="n"/>
       <c r="B278" s="1" t="n">
-        <v>60082</v>
+        <v>60073</v>
       </c>
       <c r="C278" s="1" t="n"/>
       <c r="D278" s="1" t="n">
@@ -6014,19 +6014,19 @@
       </c>
       <c r="E278" s="1" t="inlineStr">
         <is>
-          <t>SFX/UI/宝石消耗音效</t>
+          <t>SFX/Explore/传送准备音效</t>
         </is>
       </c>
       <c r="F278" s="1" t="inlineStr">
         <is>
-          <t>宝石消耗</t>
+          <t>传送准备</t>
         </is>
       </c>
     </row>
     <row r="279" ht="15" customHeight="1">
       <c r="A279" s="1" t="n"/>
       <c r="B279" s="1" t="n">
-        <v>60083</v>
+        <v>60074</v>
       </c>
       <c r="C279" s="1" t="n"/>
       <c r="D279" s="1" t="n">
@@ -6034,50 +6034,250 @@
       </c>
       <c r="E279" s="1" t="inlineStr">
         <is>
-          <t>SFX/UI/交易音效</t>
+          <t>SFX/Reward/成就解锁音效</t>
         </is>
       </c>
       <c r="F279" s="1" t="inlineStr">
         <is>
-          <t>交易音效</t>
+          <t>成就解锁</t>
         </is>
       </c>
     </row>
     <row r="280" ht="15" customHeight="1">
       <c r="A280" s="1" t="n"/>
       <c r="B280" s="1" t="n">
-        <v>13001</v>
+        <v>60075</v>
       </c>
       <c r="C280" s="1" t="n"/>
       <c r="D280" s="1" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E280" s="1" t="inlineStr">
         <is>
-          <t>Chess/后羿/后羿头像.png</t>
+          <t>SFX/Reward/等级提升音效</t>
         </is>
       </c>
       <c r="F280" s="1" t="inlineStr">
         <is>
-          <t>棋子后羿头像</t>
+          <t>等级提升</t>
         </is>
       </c>
     </row>
     <row r="281" ht="15" customHeight="1">
       <c r="A281" s="1" t="n"/>
       <c r="B281" s="1" t="n">
-        <v>13004</v>
+        <v>60076</v>
       </c>
       <c r="C281" s="1" t="n"/>
       <c r="D281" s="1" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E281" s="1" t="inlineStr">
         <is>
+          <t>SFX/Reward/品质提升音效</t>
+        </is>
+      </c>
+      <c r="F281" s="1" t="inlineStr">
+        <is>
+          <t>品质提升</t>
+        </is>
+      </c>
+    </row>
+    <row r="282" ht="15" customHeight="1">
+      <c r="A282" s="1" t="n"/>
+      <c r="B282" s="1" t="n">
+        <v>60077</v>
+      </c>
+      <c r="C282" s="1" t="n"/>
+      <c r="D282" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="E282" s="1" t="inlineStr">
+        <is>
+          <t>SFX/Reward/额外奖励音效</t>
+        </is>
+      </c>
+      <c r="F282" s="1" t="inlineStr">
+        <is>
+          <t>额外奖励</t>
+        </is>
+      </c>
+    </row>
+    <row r="283" ht="15" customHeight="1">
+      <c r="A283" s="1" t="n"/>
+      <c r="B283" s="1" t="n">
+        <v>60078</v>
+      </c>
+      <c r="C283" s="1" t="n"/>
+      <c r="D283" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="E283" s="1" t="inlineStr">
+        <is>
+          <t>SFX/Reward/传说物品音效</t>
+        </is>
+      </c>
+      <c r="F283" s="1" t="inlineStr">
+        <is>
+          <t>传说物品</t>
+        </is>
+      </c>
+    </row>
+    <row r="284" ht="15" customHeight="1">
+      <c r="A284" s="1" t="n"/>
+      <c r="B284" s="1" t="n">
+        <v>60079</v>
+      </c>
+      <c r="C284" s="1" t="n"/>
+      <c r="D284" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="E284" s="1" t="inlineStr">
+        <is>
+          <t>SFX/UI/金币捡起音效</t>
+        </is>
+      </c>
+      <c r="F284" s="1" t="inlineStr">
+        <is>
+          <t>金币捡起</t>
+        </is>
+      </c>
+    </row>
+    <row r="285" ht="15" customHeight="1">
+      <c r="A285" s="1" t="n"/>
+      <c r="B285" s="1" t="n">
+        <v>60080</v>
+      </c>
+      <c r="C285" s="1" t="n"/>
+      <c r="D285" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="E285" s="1" t="inlineStr">
+        <is>
+          <t>SFX/UI/宝石捡起音效</t>
+        </is>
+      </c>
+      <c r="F285" s="1" t="inlineStr">
+        <is>
+          <t>宝石捡起</t>
+        </is>
+      </c>
+    </row>
+    <row r="286" ht="15" customHeight="1">
+      <c r="A286" s="1" t="n"/>
+      <c r="B286" s="1" t="n">
+        <v>60081</v>
+      </c>
+      <c r="C286" s="1" t="n"/>
+      <c r="D286" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="E286" s="1" t="inlineStr">
+        <is>
+          <t>SFX/UI/金币消耗音效</t>
+        </is>
+      </c>
+      <c r="F286" s="1" t="inlineStr">
+        <is>
+          <t>金币消耗</t>
+        </is>
+      </c>
+    </row>
+    <row r="287" ht="15" customHeight="1">
+      <c r="A287" s="1" t="n"/>
+      <c r="B287" s="1" t="n">
+        <v>60082</v>
+      </c>
+      <c r="C287" s="1" t="n"/>
+      <c r="D287" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="E287" s="1" t="inlineStr">
+        <is>
+          <t>SFX/UI/宝石消耗音效</t>
+        </is>
+      </c>
+      <c r="F287" s="1" t="inlineStr">
+        <is>
+          <t>宝石消耗</t>
+        </is>
+      </c>
+    </row>
+    <row r="288" ht="15" customHeight="1">
+      <c r="A288" s="1" t="n"/>
+      <c r="B288" s="1" t="n">
+        <v>60083</v>
+      </c>
+      <c r="C288" s="1" t="n"/>
+      <c r="D288" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="E288" s="1" t="inlineStr">
+        <is>
+          <t>SFX/UI/交易音效</t>
+        </is>
+      </c>
+      <c r="F288" s="1" t="inlineStr">
+        <is>
+          <t>交易音效</t>
+        </is>
+      </c>
+    </row>
+    <row r="289" ht="15" customHeight="1">
+      <c r="A289" s="1" t="n"/>
+      <c r="B289" s="1" t="n">
+        <v>13010</v>
+      </c>
+      <c r="C289" s="1" t="n"/>
+      <c r="D289" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E289" s="1" t="inlineStr">
+        <is>
+          <t>Chess/邪灵/邪灵头像.png</t>
+        </is>
+      </c>
+      <c r="F289" s="1" t="inlineStr">
+        <is>
+          <t>棋子邪灵头像</t>
+        </is>
+      </c>
+    </row>
+    <row r="290" ht="15" customHeight="1">
+      <c r="A290" s="1" t="n"/>
+      <c r="B290" s="1" t="n">
+        <v>13001</v>
+      </c>
+      <c r="C290" s="1" t="n"/>
+      <c r="D290" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E290" s="1" t="inlineStr">
+        <is>
+          <t>Chess/后羿/后羿头像.png</t>
+        </is>
+      </c>
+      <c r="F290" s="1" t="inlineStr">
+        <is>
+          <t>棋子后羿头像</t>
+        </is>
+      </c>
+    </row>
+    <row r="291" ht="15" customHeight="1">
+      <c r="A291" s="1" t="n"/>
+      <c r="B291" s="1" t="n">
+        <v>13004</v>
+      </c>
+      <c r="C291" s="1" t="n"/>
+      <c r="D291" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E291" s="1" t="inlineStr">
+        <is>
           <t>Chess/嫦娥/嫦娥头像.png</t>
         </is>
       </c>
-      <c r="F281" s="1" t="inlineStr">
+      <c r="F291" s="1" t="inlineStr">
         <is>
           <t>棋子嫦娥头像</t>
         </is>

--- a/AAAGameData/DataTables/ResourceConfigTable.xlsx
+++ b/AAAGameData/DataTables/ResourceConfigTable.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="630">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1001" uniqueCount="797">
   <si>
     <t>#</t>
   </si>
@@ -308,6 +308,9 @@
     <t>剧毒之雾-策略卡图标</t>
   </si>
   <si>
+    <t>CardTable使用|资源暂不存在</t>
+  </si>
+  <si>
     <t>Card/策略卡/伤害转移.png</t>
   </si>
   <si>
@@ -332,6 +335,9 @@
     <t>棋子-嫦娥图标</t>
   </si>
   <si>
+    <t>SummonChessTable使用|资源暂不存在</t>
+  </si>
+  <si>
     <t>Chess/邪灵/邪灵立绘.png</t>
   </si>
   <si>
@@ -383,7 +389,10 @@
     <t>Buff/6.png</t>
   </si>
   <si>
-    <t>九天玄冰Buff图标</t>
+    <t>九天玄冰（对敌）Buff图标</t>
+  </si>
+  <si>
+    <t>BuffTable使用|资源暂不存在</t>
   </si>
   <si>
     <t>Buff/7.png</t>
@@ -413,6 +422,9 @@
     <t>Buff/28.png</t>
   </si>
   <si>
+    <t>九天玄冰（自身）Buff图标</t>
+  </si>
+  <si>
     <t>UI/Icons/Skill_Dash.png</t>
   </si>
   <si>
@@ -431,6 +443,9 @@
     <t>爆裂弹-角色技能图标</t>
   </si>
   <si>
+    <t>ResourceConfigTable使用|资源暂不存在</t>
+  </si>
+  <si>
     <t>Equipment/SunsetBow.png</t>
   </si>
   <si>
@@ -497,6 +512,9 @@
     <t>生命虹吸-召唤师技能图标</t>
   </si>
   <si>
+    <t>SummonChessSkillTable使用|资源暂不存在</t>
+  </si>
+  <si>
     <t>Skill/1.png</t>
   </si>
   <si>
@@ -947,6 +965,9 @@
     <t>狂战士</t>
   </si>
   <si>
+    <t>SummonerTable使用|资源暂不存在</t>
+  </si>
+  <si>
     <t>角色/NPC/勇士End</t>
   </si>
   <si>
@@ -1127,6 +1148,9 @@
     <t>恶魂普攻子弹</t>
   </si>
   <si>
+    <t>DamageFloatingTextTable使用|资源暂不存在</t>
+  </si>
+  <si>
     <t>SummonChessEffect/EvilSpirit_Skill1</t>
   </si>
   <si>
@@ -1139,6 +1163,51 @@
     <t>恶魂大招特效</t>
   </si>
   <si>
+    <t>Effect/DamageText/技能伤害</t>
+  </si>
+  <si>
+    <t>技能伤害-飘字音效</t>
+  </si>
+  <si>
+    <t>Effect/DamageText/连击伤害</t>
+  </si>
+  <si>
+    <t>连击伤害-飘字音效</t>
+  </si>
+  <si>
+    <t>Effect/DamageText/反弹伤害</t>
+  </si>
+  <si>
+    <t>反弹伤害-飘字音效</t>
+  </si>
+  <si>
+    <t>Effect/DamageText/吸血效果</t>
+  </si>
+  <si>
+    <t>吸血效果-飘字音效</t>
+  </si>
+  <si>
+    <t>Effect/DamageText/法力消耗</t>
+  </si>
+  <si>
+    <t>法力消耗-飘字音效</t>
+  </si>
+  <si>
+    <t>Effect/DamageText/法力恢复</t>
+  </si>
+  <si>
+    <t>法力恢复-飘字音效</t>
+  </si>
+  <si>
+    <t>Effect/DamageText/免疫提示</t>
+  </si>
+  <si>
+    <t>免疫提示-飘字音效</t>
+  </si>
+  <si>
+    <t>EquipmentTable使用|资源暂不存在</t>
+  </si>
+  <si>
     <t>Skills/SkillParamRegistry</t>
   </si>
   <si>
@@ -1205,6 +1274,9 @@
     <t>暗影咒体Buff图标</t>
   </si>
   <si>
+    <t>EnemyEntityTable使用|资源暂不存在</t>
+  </si>
+  <si>
     <t>Enemy/默认.png</t>
   </si>
   <si>
@@ -1247,6 +1319,12 @@
     <t>棋子黑暗哮天犬头像</t>
   </si>
   <si>
+    <t>Chess/稻草人/稻草人头像.png</t>
+  </si>
+  <si>
+    <t>稻草人头像</t>
+  </si>
+  <si>
     <t>Buff/5001.png</t>
   </si>
   <si>
@@ -1352,9 +1430,6 @@
     <t>剧毒之雾Buff图标</t>
   </si>
   <si>
-    <t>暂未实现</t>
-  </si>
-  <si>
     <t>Buff/5022.png</t>
   </si>
   <si>
@@ -1367,6 +1442,21 @@
     <t>绝对零度Buff图标</t>
   </si>
   <si>
+    <t>SynergyTable使用|资源暂不存在</t>
+  </si>
+  <si>
+    <t>Synergy/日月.png</t>
+  </si>
+  <si>
+    <t>日月-种族羁绊图标</t>
+  </si>
+  <si>
+    <t>Synergy/法师.png</t>
+  </si>
+  <si>
+    <t>法师-职业羁绊图标</t>
+  </si>
+  <si>
     <t>Card/Component/2.png</t>
   </si>
   <si>
@@ -1419,6 +1509,417 @@
   </si>
   <si>
     <t>名字背景-稀有度4</t>
+  </si>
+  <si>
+    <t>Entity/Card/神圣庇护_Effect</t>
+  </si>
+  <si>
+    <t>神圣庇护-施法预制体</t>
+  </si>
+  <si>
+    <t>Entity/Card/烈焰风暴_Effect</t>
+  </si>
+  <si>
+    <t>烈焰风暴-施法预制体</t>
+  </si>
+  <si>
+    <t>Entity/Card/时间回溯_Effect</t>
+  </si>
+  <si>
+    <t>时间回溯-施法预制体</t>
+  </si>
+  <si>
+    <t>Entity/Card/战争号角_Effect</t>
+  </si>
+  <si>
+    <t>战争号角-施法预制体</t>
+  </si>
+  <si>
+    <t>Entity/Card/暗影突袭_Effect</t>
+  </si>
+  <si>
+    <t>暗影突袭-施法预制体</t>
+  </si>
+  <si>
+    <t>Entity/Card/暗影突袭_Projectile</t>
+  </si>
+  <si>
+    <t>暗影突袭-投射物预制体</t>
+  </si>
+  <si>
+    <t>Entity/Card/生命汲取_Effect</t>
+  </si>
+  <si>
+    <t>生命汲取-施法预制体</t>
+  </si>
+  <si>
+    <t>Entity/Card/冰霜新星_Effect</t>
+  </si>
+  <si>
+    <t>冰霜新星-施法预制体</t>
+  </si>
+  <si>
+    <t>Entity/Card/狂暴_Effect</t>
+  </si>
+  <si>
+    <t>狂暴-施法预制体</t>
+  </si>
+  <si>
+    <t>Entity/Card/群体治疗_Effect</t>
+  </si>
+  <si>
+    <t>群体治疗-施法预制体</t>
+  </si>
+  <si>
+    <t>Entity/Card/雷霆一击_Effect</t>
+  </si>
+  <si>
+    <t>雷霆一击-施法预制体</t>
+  </si>
+  <si>
+    <t>Entity/Card/混乱诅咒_Effect</t>
+  </si>
+  <si>
+    <t>混乱诅咒-施法预制体</t>
+  </si>
+  <si>
+    <t>Entity/Card/不屈意志_Effect</t>
+  </si>
+  <si>
+    <t>不屈意志-施法预制体</t>
+  </si>
+  <si>
+    <t>Entity/Card/反伤之盾_Effect</t>
+  </si>
+  <si>
+    <t>反伤之盾-施法预制体</t>
+  </si>
+  <si>
+    <t>Entity/Card/圣域防线_Effect</t>
+  </si>
+  <si>
+    <t>圣域防线-施法预制体</t>
+  </si>
+  <si>
+    <t>Entity/Card/护盾再生_Effect</t>
+  </si>
+  <si>
+    <t>护盾再生-施法预制体</t>
+  </si>
+  <si>
+    <t>Entity/Card/救赎之光_Effect</t>
+  </si>
+  <si>
+    <t>救赎之光-施法预制体</t>
+  </si>
+  <si>
+    <t>Entity/Card/血源强化_Effect</t>
+  </si>
+  <si>
+    <t>血源强化-施法预制体</t>
+  </si>
+  <si>
+    <t>Entity/Card/吸血之刃_Effect</t>
+  </si>
+  <si>
+    <t>吸血之刃-施法预制体</t>
+  </si>
+  <si>
+    <t>Entity/Card/吸血之刃_Projectile</t>
+  </si>
+  <si>
+    <t>吸血之刃-投射物预制体</t>
+  </si>
+  <si>
+    <t>Entity/Card/灾厄之雷_Effect</t>
+  </si>
+  <si>
+    <t>灾厄之雷-施法预制体</t>
+  </si>
+  <si>
+    <t>Entity/Card/护甲破碎_Effect</t>
+  </si>
+  <si>
+    <t>护甲破碎-施法预制体</t>
+  </si>
+  <si>
+    <t>Entity/Card/虚弱诅咒_Effect</t>
+  </si>
+  <si>
+    <t>虚弱诅咒-施法预制体</t>
+  </si>
+  <si>
+    <t>Entity/Card/沉默之符_Effect</t>
+  </si>
+  <si>
+    <t>沉默之符-施法预制体</t>
+  </si>
+  <si>
+    <t>Entity/Card/嘲讽之声_Effect</t>
+  </si>
+  <si>
+    <t>嘲讽之声-施法预制体</t>
+  </si>
+  <si>
+    <t>Entity/Card/剧毒之雾_Effect</t>
+  </si>
+  <si>
+    <t>剧毒之雾-施法预制体</t>
+  </si>
+  <si>
+    <t>Entity/Card/伤害转移_Effect</t>
+  </si>
+  <si>
+    <t>伤害转移-施法预制体</t>
+  </si>
+  <si>
+    <t>Entity/Card/绝对零度_Effect</t>
+  </si>
+  <si>
+    <t>绝对零度-施法预制体</t>
+  </si>
+  <si>
+    <t>Effect/Card/神圣庇护</t>
+  </si>
+  <si>
+    <t>神圣庇护-施法特效</t>
+  </si>
+  <si>
+    <t>Effect/Card/烈焰风暴</t>
+  </si>
+  <si>
+    <t>烈焰风暴-施法特效</t>
+  </si>
+  <si>
+    <t>Effect/Card/时间回溯</t>
+  </si>
+  <si>
+    <t>时间回溯-施法特效</t>
+  </si>
+  <si>
+    <t>Effect/Card/战争号角</t>
+  </si>
+  <si>
+    <t>战争号角-施法特效</t>
+  </si>
+  <si>
+    <t>Effect/Card/暗影突袭</t>
+  </si>
+  <si>
+    <t>暗影突袭-施法特效</t>
+  </si>
+  <si>
+    <t>Effect/Card/生命汲取</t>
+  </si>
+  <si>
+    <t>生命汲取-施法特效</t>
+  </si>
+  <si>
+    <t>Effect/Card/冰霜新星</t>
+  </si>
+  <si>
+    <t>冰霜新星-施法特效</t>
+  </si>
+  <si>
+    <t>Effect/Card/狂暴</t>
+  </si>
+  <si>
+    <t>狂暴-施法特效</t>
+  </si>
+  <si>
+    <t>Effect/Card/群体治疗</t>
+  </si>
+  <si>
+    <t>群体治疗-施法特效</t>
+  </si>
+  <si>
+    <t>Effect/Card/雷霆一击</t>
+  </si>
+  <si>
+    <t>雷霆一击-施法特效</t>
+  </si>
+  <si>
+    <t>Effect/Card/混乱诅咒</t>
+  </si>
+  <si>
+    <t>混乱诅咒-施法特效</t>
+  </si>
+  <si>
+    <t>Effect/Card/不屈意志</t>
+  </si>
+  <si>
+    <t>不屈意志-施法特效</t>
+  </si>
+  <si>
+    <t>Effect/Card/反伤之盾</t>
+  </si>
+  <si>
+    <t>反伤之盾-施法特效</t>
+  </si>
+  <si>
+    <t>Effect/Card/圣域防线</t>
+  </si>
+  <si>
+    <t>圣域防线-施法特效</t>
+  </si>
+  <si>
+    <t>Effect/Card/护盾再生</t>
+  </si>
+  <si>
+    <t>护盾再生-施法特效</t>
+  </si>
+  <si>
+    <t>Effect/Card/救赎之光</t>
+  </si>
+  <si>
+    <t>救赎之光-施法特效</t>
+  </si>
+  <si>
+    <t>Effect/Card/血源强化</t>
+  </si>
+  <si>
+    <t>血源强化-施法特效</t>
+  </si>
+  <si>
+    <t>Effect/Card/吸血之刃</t>
+  </si>
+  <si>
+    <t>吸血之刃-施法特效</t>
+  </si>
+  <si>
+    <t>Effect/Card/灾厄之雷</t>
+  </si>
+  <si>
+    <t>灾厄之雷-施法特效</t>
+  </si>
+  <si>
+    <t>Effect/Card/护甲破碎</t>
+  </si>
+  <si>
+    <t>护甲破碎-施法特效</t>
+  </si>
+  <si>
+    <t>Effect/Card/虚弱诅咒</t>
+  </si>
+  <si>
+    <t>虚弱诅咒-施法特效</t>
+  </si>
+  <si>
+    <t>Effect/Card/沉默之符</t>
+  </si>
+  <si>
+    <t>沉默之符-施法特效</t>
+  </si>
+  <si>
+    <t>Effect/Card/嘲讽之声</t>
+  </si>
+  <si>
+    <t>嘲讽之声-施法特效</t>
+  </si>
+  <si>
+    <t>Effect/Card/剧毒之雾</t>
+  </si>
+  <si>
+    <t>剧毒之雾-施法特效</t>
+  </si>
+  <si>
+    <t>Effect/Card/伤害转移</t>
+  </si>
+  <si>
+    <t>伤害转移-施法特效</t>
+  </si>
+  <si>
+    <t>Effect/Card/绝对零度</t>
+  </si>
+  <si>
+    <t>绝对零度-施法特效</t>
+  </si>
+  <si>
+    <t>Effect/Card/烈焰风暴_Hit</t>
+  </si>
+  <si>
+    <t>烈焰风暴-受击特效</t>
+  </si>
+  <si>
+    <t>Effect/Card/暗影突袭_Hit</t>
+  </si>
+  <si>
+    <t>暗影突袭-受击特效</t>
+  </si>
+  <si>
+    <t>Effect/Card/生命汲取_Hit</t>
+  </si>
+  <si>
+    <t>生命汲取-受击特效</t>
+  </si>
+  <si>
+    <t>Effect/Card/冰霜新星_Hit</t>
+  </si>
+  <si>
+    <t>冰霜新星-受击特效</t>
+  </si>
+  <si>
+    <t>Effect/Card/雷霆一击_Hit</t>
+  </si>
+  <si>
+    <t>雷霆一击-受击特效</t>
+  </si>
+  <si>
+    <t>Effect/Card/混乱诅咒_Hit</t>
+  </si>
+  <si>
+    <t>混乱诅咒-受击特效</t>
+  </si>
+  <si>
+    <t>Effect/Card/吸血之刃_Hit</t>
+  </si>
+  <si>
+    <t>吸血之刃-受击特效</t>
+  </si>
+  <si>
+    <t>Effect/Card/灾厄之雷_Hit</t>
+  </si>
+  <si>
+    <t>灾厄之雷-受击特效</t>
+  </si>
+  <si>
+    <t>Effect/Card/护甲破碎_Hit</t>
+  </si>
+  <si>
+    <t>护甲破碎-受击特效</t>
+  </si>
+  <si>
+    <t>Effect/Card/虚弱诅咒_Hit</t>
+  </si>
+  <si>
+    <t>虚弱诅咒-受击特效</t>
+  </si>
+  <si>
+    <t>Effect/Card/沉默之符_Hit</t>
+  </si>
+  <si>
+    <t>沉默之符-受击特效</t>
+  </si>
+  <si>
+    <t>Effect/Card/嘲讽之声_Hit</t>
+  </si>
+  <si>
+    <t>嘲讽之声-受击特效</t>
+  </si>
+  <si>
+    <t>Effect/Card/剧毒之雾_Hit</t>
+  </si>
+  <si>
+    <t>剧毒之雾-受击特效</t>
+  </si>
+  <si>
+    <t>Effect/Card/绝对零度_Hit</t>
+  </si>
+  <si>
+    <t>绝对零度-受击特效</t>
+  </si>
+  <si>
+    <t>AudioClipTable使用|资源暂不存在</t>
   </si>
   <si>
     <t>BGM/游戏启动主菜单BGM</t>
@@ -2888,14 +3389,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F313"/>
+  <dimension ref="A1:F391"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="21" customWidth="1"/>
     <col min="3" max="4" width="50" customWidth="1"/>
     <col min="5" max="5" width="48" customWidth="1"/>
-    <col min="6" max="6" width="26" customWidth="1"/>
+    <col min="6" max="6" width="33" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -3611,15 +4112,17 @@
       <c r="B45" s="1">
         <v>1225</v>
       </c>
-      <c r="C45" s="1"/>
+      <c r="C45" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="D45" s="1">
         <v>1</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" spans="1:6">
@@ -3627,15 +4130,17 @@
       <c r="B46" s="1">
         <v>1226</v>
       </c>
-      <c r="C46" s="1"/>
+      <c r="C46" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="D46" s="1">
         <v>1</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1" spans="1:6">
@@ -3648,10 +4153,10 @@
         <v>1</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1" spans="1:6">
@@ -3664,10 +4169,10 @@
         <v>1</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1" spans="1:6">
@@ -3675,15 +4180,17 @@
       <c r="B49" s="1">
         <v>1310</v>
       </c>
-      <c r="C49" s="1"/>
+      <c r="C49" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="D49" s="1">
         <v>1</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1" spans="1:6">
@@ -3691,15 +4198,17 @@
       <c r="B50" s="1">
         <v>1311</v>
       </c>
-      <c r="C50" s="1"/>
+      <c r="C50" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="D50" s="1">
         <v>1</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1" spans="1:6">
@@ -3712,10 +4221,10 @@
         <v>1</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1" spans="1:6">
@@ -3728,10 +4237,10 @@
         <v>1</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="53" ht="15" customHeight="1" spans="1:6">
@@ -3744,10 +4253,10 @@
         <v>1</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="54" ht="15" customHeight="1" spans="1:6">
@@ -3760,10 +4269,10 @@
         <v>1</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="55" ht="15" customHeight="1" spans="1:6">
@@ -3776,10 +4285,10 @@
         <v>1</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="56" ht="15" customHeight="1" spans="1:6">
@@ -3792,10 +4301,10 @@
         <v>1</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="57" ht="15" customHeight="1" spans="1:6">
@@ -3808,10 +4317,10 @@
         <v>1</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="58" ht="15" customHeight="1" spans="1:6">
@@ -3819,15 +4328,17 @@
       <c r="B58" s="1">
         <v>1407</v>
       </c>
-      <c r="C58" s="1"/>
+      <c r="C58" s="1" t="s">
+        <v>121</v>
+      </c>
       <c r="D58" s="1">
         <v>1</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="59" ht="15" customHeight="1" spans="1:6">
@@ -3835,15 +4346,17 @@
       <c r="B59" s="1">
         <v>1408</v>
       </c>
-      <c r="C59" s="1"/>
+      <c r="C59" s="1" t="s">
+        <v>121</v>
+      </c>
       <c r="D59" s="1">
         <v>1</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="60" ht="15" customHeight="1" spans="1:6">
@@ -3851,15 +4364,17 @@
       <c r="B60" s="1">
         <v>1409</v>
       </c>
-      <c r="C60" s="1"/>
+      <c r="C60" s="1" t="s">
+        <v>121</v>
+      </c>
       <c r="D60" s="1">
         <v>1</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="61" ht="15" customHeight="1" spans="1:6">
@@ -3867,15 +4382,17 @@
       <c r="B61" s="1">
         <v>1410</v>
       </c>
-      <c r="C61" s="1"/>
+      <c r="C61" s="1" t="s">
+        <v>121</v>
+      </c>
       <c r="D61" s="1">
         <v>1</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="62" ht="15" customHeight="1" spans="1:6">
@@ -3883,15 +4400,17 @@
       <c r="B62" s="1">
         <v>1411</v>
       </c>
-      <c r="C62" s="1"/>
+      <c r="C62" s="1" t="s">
+        <v>121</v>
+      </c>
       <c r="D62" s="1">
         <v>1</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
     </row>
     <row r="63" ht="15" customHeight="1" spans="1:6">
@@ -3904,10 +4423,10 @@
         <v>1</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
     </row>
     <row r="64" ht="15" customHeight="1" spans="1:6">
@@ -3920,10 +4439,10 @@
         <v>1</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="65" ht="15" customHeight="1" spans="1:6">
@@ -3936,10 +4455,10 @@
         <v>1</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="66" ht="15" customHeight="1" spans="1:6">
@@ -3947,15 +4466,17 @@
       <c r="B66" s="1">
         <v>1601</v>
       </c>
-      <c r="C66" s="1"/>
+      <c r="C66" s="1" t="s">
+        <v>138</v>
+      </c>
       <c r="D66" s="1">
         <v>1</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1" spans="1:6">
@@ -3968,10 +4489,10 @@
         <v>1</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
     </row>
     <row r="68" ht="15" customHeight="1" spans="1:6">
@@ -3984,10 +4505,10 @@
         <v>1</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" spans="1:6">
@@ -4000,10 +4521,10 @@
         <v>1</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1" spans="1:6">
@@ -4016,10 +4537,10 @@
         <v>1</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1" spans="1:6">
@@ -4032,10 +4553,10 @@
         <v>1</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1" spans="1:6">
@@ -4048,10 +4569,10 @@
         <v>1</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1" spans="1:6">
@@ -4064,10 +4585,10 @@
         <v>1</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
     <row r="74" ht="15" customHeight="1" spans="1:6">
@@ -4080,10 +4601,10 @@
         <v>1</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1" spans="1:6">
@@ -4096,10 +4617,10 @@
         <v>1</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
     </row>
     <row r="76" ht="15" customHeight="1" spans="1:6">
@@ -4112,10 +4633,10 @@
         <v>1</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
     </row>
     <row r="77" ht="15" customHeight="1" spans="1:6">
@@ -4123,15 +4644,17 @@
       <c r="B77" s="1">
         <v>1801</v>
       </c>
-      <c r="C77" s="1"/>
+      <c r="C77" s="1" t="s">
+        <v>161</v>
+      </c>
       <c r="D77" s="1">
         <v>1</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="78" ht="15" customHeight="1" spans="1:6">
@@ -4139,15 +4662,17 @@
       <c r="B78" s="1">
         <v>1802</v>
       </c>
-      <c r="C78" s="1"/>
+      <c r="C78" s="1" t="s">
+        <v>161</v>
+      </c>
       <c r="D78" s="1">
         <v>1</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1" spans="1:6">
@@ -4155,15 +4680,17 @@
       <c r="B79" s="1">
         <v>1803</v>
       </c>
-      <c r="C79" s="1"/>
+      <c r="C79" s="1" t="s">
+        <v>161</v>
+      </c>
       <c r="D79" s="1">
         <v>1</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1" spans="1:6">
@@ -4171,15 +4698,17 @@
       <c r="B80" s="1">
         <v>1804</v>
       </c>
-      <c r="C80" s="1"/>
+      <c r="C80" s="1" t="s">
+        <v>161</v>
+      </c>
       <c r="D80" s="1">
         <v>1</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1" spans="1:6">
@@ -4187,15 +4716,17 @@
       <c r="B81" s="1">
         <v>1805</v>
       </c>
-      <c r="C81" s="1"/>
+      <c r="C81" s="1" t="s">
+        <v>161</v>
+      </c>
       <c r="D81" s="1">
         <v>1</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1" spans="1:6">
@@ -4203,15 +4734,17 @@
       <c r="B82" s="1">
         <v>1806</v>
       </c>
-      <c r="C82" s="1"/>
+      <c r="C82" s="1" t="s">
+        <v>161</v>
+      </c>
       <c r="D82" s="1">
         <v>1</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1" spans="1:6">
@@ -4219,15 +4752,17 @@
       <c r="B83" s="1">
         <v>1807</v>
       </c>
-      <c r="C83" s="1"/>
+      <c r="C83" s="1" t="s">
+        <v>161</v>
+      </c>
       <c r="D83" s="1">
         <v>1</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
     </row>
     <row r="84" ht="15" customHeight="1" spans="1:6">
@@ -4235,15 +4770,17 @@
       <c r="B84" s="1">
         <v>1808</v>
       </c>
-      <c r="C84" s="1"/>
+      <c r="C84" s="1" t="s">
+        <v>161</v>
+      </c>
       <c r="D84" s="1">
         <v>1</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1" spans="1:6">
@@ -4251,15 +4788,17 @@
       <c r="B85" s="1">
         <v>1831</v>
       </c>
-      <c r="C85" s="1"/>
+      <c r="C85" s="1" t="s">
+        <v>161</v>
+      </c>
       <c r="D85" s="1">
         <v>1</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1" spans="1:6">
@@ -4267,15 +4806,17 @@
       <c r="B86" s="1">
         <v>1832</v>
       </c>
-      <c r="C86" s="1"/>
+      <c r="C86" s="1" t="s">
+        <v>161</v>
+      </c>
       <c r="D86" s="1">
         <v>1</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1" spans="1:6">
@@ -4283,15 +4824,17 @@
       <c r="B87" s="1">
         <v>1833</v>
       </c>
-      <c r="C87" s="1"/>
+      <c r="C87" s="1" t="s">
+        <v>161</v>
+      </c>
       <c r="D87" s="1">
         <v>1</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
     </row>
     <row r="88" ht="15" customHeight="1" spans="1:6">
@@ -4299,15 +4842,17 @@
       <c r="B88" s="1">
         <v>1834</v>
       </c>
-      <c r="C88" s="1"/>
+      <c r="C88" s="1" t="s">
+        <v>161</v>
+      </c>
       <c r="D88" s="1">
         <v>1</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
     </row>
     <row r="89" ht="15" customHeight="1" spans="1:6">
@@ -4315,15 +4860,17 @@
       <c r="B89" s="1">
         <v>1841</v>
       </c>
-      <c r="C89" s="1"/>
+      <c r="C89" s="1" t="s">
+        <v>161</v>
+      </c>
       <c r="D89" s="1">
         <v>1</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
     </row>
     <row r="90" ht="15" customHeight="1" spans="1:6">
@@ -4331,15 +4878,17 @@
       <c r="B90" s="1">
         <v>1842</v>
       </c>
-      <c r="C90" s="1"/>
+      <c r="C90" s="1" t="s">
+        <v>161</v>
+      </c>
       <c r="D90" s="1">
         <v>1</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
     </row>
     <row r="91" ht="15" customHeight="1" spans="1:6">
@@ -4347,15 +4896,17 @@
       <c r="B91" s="1">
         <v>1843</v>
       </c>
-      <c r="C91" s="1"/>
+      <c r="C91" s="1" t="s">
+        <v>161</v>
+      </c>
       <c r="D91" s="1">
         <v>1</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="92" ht="15" customHeight="1" spans="1:6">
@@ -4363,15 +4914,17 @@
       <c r="B92" s="1">
         <v>1844</v>
       </c>
-      <c r="C92" s="1"/>
+      <c r="C92" s="1" t="s">
+        <v>161</v>
+      </c>
       <c r="D92" s="1">
         <v>1</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
     </row>
     <row r="93" ht="15" customHeight="1" spans="1:6">
@@ -4379,15 +4932,17 @@
       <c r="B93" s="1">
         <v>1845</v>
       </c>
-      <c r="C93" s="1"/>
+      <c r="C93" s="1" t="s">
+        <v>161</v>
+      </c>
       <c r="D93" s="1">
         <v>1</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
     </row>
     <row r="94" ht="15" customHeight="1" spans="1:6">
@@ -4395,15 +4950,17 @@
       <c r="B94" s="1">
         <v>1846</v>
       </c>
-      <c r="C94" s="1"/>
+      <c r="C94" s="1" t="s">
+        <v>161</v>
+      </c>
       <c r="D94" s="1">
         <v>1</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
     </row>
     <row r="95" ht="15" customHeight="1" spans="1:6">
@@ -4411,15 +4968,17 @@
       <c r="B95" s="1">
         <v>1847</v>
       </c>
-      <c r="C95" s="1"/>
+      <c r="C95" s="1" t="s">
+        <v>161</v>
+      </c>
       <c r="D95" s="1">
         <v>1</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
     </row>
     <row r="96" ht="15" customHeight="1" spans="1:6">
@@ -4427,15 +4986,17 @@
       <c r="B96" s="1">
         <v>1848</v>
       </c>
-      <c r="C96" s="1"/>
+      <c r="C96" s="1" t="s">
+        <v>161</v>
+      </c>
       <c r="D96" s="1">
         <v>1</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
     </row>
     <row r="97" ht="15" customHeight="1" spans="1:6">
@@ -4443,15 +5004,17 @@
       <c r="B97" s="1">
         <v>1849</v>
       </c>
-      <c r="C97" s="1"/>
+      <c r="C97" s="1" t="s">
+        <v>161</v>
+      </c>
       <c r="D97" s="1">
         <v>1</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
     </row>
     <row r="98" ht="15" customHeight="1" spans="1:6">
@@ -4459,15 +5022,17 @@
       <c r="B98" s="1">
         <v>1850</v>
       </c>
-      <c r="C98" s="1"/>
+      <c r="C98" s="1" t="s">
+        <v>161</v>
+      </c>
       <c r="D98" s="1">
         <v>1</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
     </row>
     <row r="99" ht="15" customHeight="1" spans="1:6">
@@ -4480,10 +5045,10 @@
         <v>1</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
     </row>
     <row r="100" ht="15" customHeight="1" spans="1:6">
@@ -4496,10 +5061,10 @@
         <v>1</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
     </row>
     <row r="101" ht="15" customHeight="1" spans="1:6">
@@ -4512,10 +5077,10 @@
         <v>1</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
     </row>
     <row r="102" ht="15" customHeight="1" spans="1:6">
@@ -4528,10 +5093,10 @@
         <v>1</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
     </row>
     <row r="103" ht="15" customHeight="1" spans="1:6">
@@ -4544,10 +5109,10 @@
         <v>1</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="104" ht="15" customHeight="1" spans="1:6">
@@ -4560,10 +5125,10 @@
         <v>1</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
     </row>
     <row r="105" ht="15" customHeight="1" spans="1:6">
@@ -4576,10 +5141,10 @@
         <v>1</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
     </row>
     <row r="106" ht="15" customHeight="1" spans="1:6">
@@ -4592,10 +5157,10 @@
         <v>1</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="107" ht="15" customHeight="1" spans="1:6">
@@ -4608,10 +5173,10 @@
         <v>1</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="108" ht="15" customHeight="1" spans="1:6">
@@ -4624,10 +5189,10 @@
         <v>1</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
     </row>
     <row r="109" ht="15" customHeight="1" spans="1:6">
@@ -4640,10 +5205,10 @@
         <v>1</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
     </row>
     <row r="110" ht="15" customHeight="1" spans="1:6">
@@ -4656,10 +5221,10 @@
         <v>1</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
     </row>
     <row r="111" ht="15" customHeight="1" spans="1:6">
@@ -4672,10 +5237,10 @@
         <v>1</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
     </row>
     <row r="112" ht="15" customHeight="1" spans="1:6">
@@ -4688,10 +5253,10 @@
         <v>1</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
     </row>
     <row r="113" ht="15" customHeight="1" spans="1:6">
@@ -4704,10 +5269,10 @@
         <v>1</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
     </row>
     <row r="114" ht="15" customHeight="1" spans="1:6">
@@ -4720,10 +5285,10 @@
         <v>1</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
     </row>
     <row r="115" ht="15" customHeight="1" spans="1:6">
@@ -4736,10 +5301,10 @@
         <v>1</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
     </row>
     <row r="116" ht="15" customHeight="1" spans="1:6">
@@ -4752,10 +5317,10 @@
         <v>1</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
     </row>
     <row r="117" ht="15" customHeight="1" spans="1:6">
@@ -4768,10 +5333,10 @@
         <v>1</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
     </row>
     <row r="118" ht="15" customHeight="1" spans="1:6">
@@ -4784,10 +5349,10 @@
         <v>1</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
     </row>
     <row r="119" ht="15" customHeight="1" spans="1:6">
@@ -4800,10 +5365,10 @@
         <v>1</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
     </row>
     <row r="120" ht="15" customHeight="1" spans="1:6">
@@ -4816,10 +5381,10 @@
         <v>1</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
     </row>
     <row r="121" ht="15" customHeight="1" spans="1:6">
@@ -4832,10 +5397,10 @@
         <v>1</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
     </row>
     <row r="122" ht="15" customHeight="1" spans="1:6">
@@ -4848,10 +5413,10 @@
         <v>1</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
     </row>
     <row r="123" ht="15" customHeight="1" spans="1:6">
@@ -4864,10 +5429,10 @@
         <v>1</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
     </row>
     <row r="124" ht="15" customHeight="1" spans="1:6">
@@ -4880,10 +5445,10 @@
         <v>1</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
     </row>
     <row r="125" ht="15" customHeight="1" spans="1:6">
@@ -4896,10 +5461,10 @@
         <v>1</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
     </row>
     <row r="126" ht="15" customHeight="1" spans="1:6">
@@ -4912,10 +5477,10 @@
         <v>1</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
     </row>
     <row r="127" ht="15" customHeight="1" spans="1:6">
@@ -4928,10 +5493,10 @@
         <v>1</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
     </row>
     <row r="128" ht="15" customHeight="1" spans="1:6">
@@ -4944,10 +5509,10 @@
         <v>1</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
     </row>
     <row r="129" ht="15" customHeight="1" spans="1:6">
@@ -4960,10 +5525,10 @@
         <v>1</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="130" ht="15" customHeight="1" spans="1:6">
@@ -4976,10 +5541,10 @@
         <v>1</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
     </row>
     <row r="131" ht="15" customHeight="1" spans="1:6">
@@ -4992,10 +5557,10 @@
         <v>1</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
     </row>
     <row r="132" ht="15" customHeight="1" spans="1:6">
@@ -5008,10 +5573,10 @@
         <v>1</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
     </row>
     <row r="133" ht="15" customHeight="1" spans="1:6">
@@ -5024,10 +5589,10 @@
         <v>1</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
     </row>
     <row r="134" ht="15" customHeight="1" spans="1:6">
@@ -5040,10 +5605,10 @@
         <v>1</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
     </row>
     <row r="135" ht="15" customHeight="1" spans="1:6">
@@ -5056,10 +5621,10 @@
         <v>1</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
     </row>
     <row r="136" ht="15" customHeight="1" spans="1:6">
@@ -5072,10 +5637,10 @@
         <v>1</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
     </row>
     <row r="137" ht="15" customHeight="1" spans="1:6">
@@ -5088,10 +5653,10 @@
         <v>1</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
     </row>
     <row r="138" ht="15" customHeight="1" spans="1:6">
@@ -5104,10 +5669,10 @@
         <v>1</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
     </row>
     <row r="139" ht="15" customHeight="1" spans="1:6">
@@ -5120,10 +5685,10 @@
         <v>1</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
     </row>
     <row r="140" ht="15" customHeight="1" spans="1:6">
@@ -5136,10 +5701,10 @@
         <v>1</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
     </row>
     <row r="141" ht="15" customHeight="1" spans="1:6">
@@ -5152,10 +5717,10 @@
         <v>1</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
     </row>
     <row r="142" ht="15" customHeight="1" spans="1:6">
@@ -5168,10 +5733,10 @@
         <v>1</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
     </row>
     <row r="143" ht="15" customHeight="1" spans="1:6">
@@ -5184,10 +5749,10 @@
         <v>1</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
     </row>
     <row r="144" ht="15" customHeight="1" spans="1:6">
@@ -5200,10 +5765,10 @@
         <v>1</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
     </row>
     <row r="145" ht="15" customHeight="1" spans="1:6">
@@ -5216,10 +5781,10 @@
         <v>1</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="146" ht="15" customHeight="1" spans="1:6">
@@ -5232,10 +5797,10 @@
         <v>1</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
     </row>
     <row r="147" ht="15" customHeight="1" spans="1:6">
@@ -5248,10 +5813,10 @@
         <v>2</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
     </row>
     <row r="148" ht="15" customHeight="1" spans="1:6">
@@ -5264,10 +5829,10 @@
         <v>2</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
     </row>
     <row r="149" ht="15" customHeight="1" spans="1:6">
@@ -5280,10 +5845,10 @@
         <v>2</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
     </row>
     <row r="150" ht="15" customHeight="1" spans="1:6">
@@ -5296,10 +5861,10 @@
         <v>2</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
     </row>
     <row r="151" ht="15" customHeight="1" spans="1:6">
@@ -5312,10 +5877,10 @@
         <v>2</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
     </row>
     <row r="152" ht="15" customHeight="1" spans="1:6">
@@ -5323,15 +5888,17 @@
       <c r="B152" s="1">
         <v>2102</v>
       </c>
-      <c r="C152" s="1"/>
+      <c r="C152" s="1" t="s">
+        <v>312</v>
+      </c>
       <c r="D152" s="1">
         <v>2</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
     </row>
     <row r="153" ht="15" customHeight="1" spans="1:6">
@@ -5339,15 +5906,17 @@
       <c r="B153" s="1">
         <v>2103</v>
       </c>
-      <c r="C153" s="1"/>
+      <c r="C153" s="1" t="s">
+        <v>312</v>
+      </c>
       <c r="D153" s="1">
         <v>2</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
     </row>
     <row r="154" ht="15" customHeight="1" spans="1:6">
@@ -5355,15 +5924,17 @@
       <c r="B154" s="1">
         <v>2104</v>
       </c>
-      <c r="C154" s="1"/>
+      <c r="C154" s="1" t="s">
+        <v>312</v>
+      </c>
       <c r="D154" s="1">
         <v>2</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
     </row>
     <row r="155" ht="15" customHeight="1" spans="1:6">
@@ -5376,10 +5947,10 @@
         <v>2</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
     </row>
     <row r="156" ht="15" customHeight="1" spans="1:6">
@@ -5392,10 +5963,10 @@
         <v>2</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
     </row>
     <row r="157" ht="15" customHeight="1" spans="1:6">
@@ -5408,10 +5979,10 @@
         <v>2</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
     </row>
     <row r="158" ht="15" customHeight="1" spans="1:6">
@@ -5424,10 +5995,10 @@
         <v>2</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
     </row>
     <row r="159" ht="15" customHeight="1" spans="1:6">
@@ -5440,10 +6011,10 @@
         <v>2</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
     </row>
     <row r="160" ht="15" customHeight="1" spans="1:6">
@@ -5456,10 +6027,10 @@
         <v>2</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
     </row>
     <row r="161" ht="15" customHeight="1" spans="1:6">
@@ -5472,10 +6043,10 @@
         <v>2</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
     </row>
     <row r="162" ht="15" customHeight="1" spans="1:6">
@@ -5483,15 +6054,17 @@
       <c r="B162" s="1">
         <v>2313</v>
       </c>
-      <c r="C162" s="1"/>
+      <c r="C162" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="D162" s="1">
         <v>2</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
     </row>
     <row r="163" ht="15" customHeight="1" spans="1:6">
@@ -5504,10 +6077,10 @@
         <v>2</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
     </row>
     <row r="164" ht="15" customHeight="1" spans="1:6">
@@ -5520,10 +6093,10 @@
         <v>3</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
     </row>
     <row r="165" ht="15" customHeight="1" spans="1:6">
@@ -5536,10 +6109,10 @@
         <v>3</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
     </row>
     <row r="166" ht="15" customHeight="1" spans="1:6">
@@ -5552,10 +6125,10 @@
         <v>2</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
     </row>
     <row r="167" ht="15" customHeight="1" spans="1:6">
@@ -5568,10 +6141,10 @@
         <v>2</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
     </row>
     <row r="168" ht="15" customHeight="1" spans="1:6">
@@ -5584,10 +6157,10 @@
         <v>2</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
     </row>
     <row r="169" ht="15" customHeight="1" spans="1:6">
@@ -5600,10 +6173,10 @@
         <v>2</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
     </row>
     <row r="170" ht="15" customHeight="1" spans="1:6">
@@ -5616,10 +6189,10 @@
         <v>2</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
     </row>
     <row r="171" ht="15" customHeight="1" spans="1:6">
@@ -5632,10 +6205,10 @@
         <v>2</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>343</v>
+        <v>350</v>
       </c>
     </row>
     <row r="172" ht="15" customHeight="1" spans="1:6">
@@ -5648,10 +6221,10 @@
         <v>2</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
     </row>
     <row r="173" ht="15" customHeight="1" spans="1:6">
@@ -5664,10 +6237,10 @@
         <v>3</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
     </row>
     <row r="174" ht="15" customHeight="1" spans="1:6">
@@ -5680,10 +6253,10 @@
         <v>3</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
     </row>
     <row r="175" ht="15" customHeight="1" spans="1:6">
@@ -5696,10 +6269,10 @@
         <v>3</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
     </row>
     <row r="176" ht="15" customHeight="1" spans="1:6">
@@ -5712,10 +6285,10 @@
         <v>3</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>353</v>
+        <v>360</v>
       </c>
     </row>
     <row r="177" ht="15" customHeight="1" spans="1:6">
@@ -5728,10 +6301,10 @@
         <v>3</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
     </row>
     <row r="178" ht="15" customHeight="1" spans="1:6">
@@ -5744,10 +6317,10 @@
         <v>3</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
     </row>
     <row r="179" ht="15" customHeight="1" spans="1:6">
@@ -5760,10 +6333,10 @@
         <v>3</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
     </row>
     <row r="180" ht="15" customHeight="1" spans="1:6">
@@ -5776,10 +6349,10 @@
         <v>3</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
     </row>
     <row r="181" ht="15" customHeight="1" spans="1:6">
@@ -5792,10 +6365,10 @@
         <v>3</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
     </row>
     <row r="182" ht="15" customHeight="1" spans="1:6">
@@ -5803,15 +6376,17 @@
       <c r="B182" s="1">
         <v>3010</v>
       </c>
-      <c r="C182" s="1"/>
+      <c r="C182" s="1" t="s">
+        <v>161</v>
+      </c>
       <c r="D182" s="1">
         <v>3</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>365</v>
+        <v>372</v>
       </c>
     </row>
     <row r="183" ht="15" customHeight="1" spans="1:6">
@@ -5819,15 +6394,17 @@
       <c r="B183" s="1">
         <v>3011</v>
       </c>
-      <c r="C183" s="1"/>
+      <c r="C183" s="1" t="s">
+        <v>373</v>
+      </c>
       <c r="D183" s="1">
         <v>3</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
     </row>
     <row r="184" ht="15" customHeight="1" spans="1:6">
@@ -5835,2090 +6412,3674 @@
       <c r="B184" s="1">
         <v>3012</v>
       </c>
-      <c r="C184" s="1"/>
+      <c r="C184" s="1" t="s">
+        <v>373</v>
+      </c>
       <c r="D184" s="1">
         <v>3</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>369</v>
+        <v>377</v>
       </c>
     </row>
     <row r="185" ht="15" customHeight="1" spans="1:6">
       <c r="A185" s="1"/>
       <c r="B185" s="1">
-        <v>6001</v>
-      </c>
-      <c r="C185" s="1"/>
+        <v>3013</v>
+      </c>
+      <c r="C185" s="1" t="s">
+        <v>373</v>
+      </c>
       <c r="D185" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>371</v>
+        <v>379</v>
       </c>
     </row>
     <row r="186" ht="15" customHeight="1" spans="1:6">
       <c r="A186" s="1"/>
       <c r="B186" s="1">
-        <v>10001</v>
-      </c>
-      <c r="C186" s="1"/>
+        <v>3014</v>
+      </c>
+      <c r="C186" s="1" t="s">
+        <v>373</v>
+      </c>
       <c r="D186" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>373</v>
+        <v>381</v>
       </c>
     </row>
     <row r="187" ht="15" customHeight="1" spans="1:6">
       <c r="A187" s="1"/>
       <c r="B187" s="1">
-        <v>10002</v>
-      </c>
-      <c r="C187" s="1"/>
+        <v>3015</v>
+      </c>
+      <c r="C187" s="1" t="s">
+        <v>373</v>
+      </c>
       <c r="D187" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>375</v>
+        <v>383</v>
       </c>
     </row>
     <row r="188" ht="15" customHeight="1" spans="1:6">
       <c r="A188" s="1"/>
       <c r="B188" s="1">
-        <v>10003</v>
-      </c>
-      <c r="C188" s="1"/>
+        <v>3016</v>
+      </c>
+      <c r="C188" s="1" t="s">
+        <v>373</v>
+      </c>
       <c r="D188" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>377</v>
+        <v>385</v>
       </c>
     </row>
     <row r="189" ht="15" customHeight="1" spans="1:6">
       <c r="A189" s="1"/>
       <c r="B189" s="1">
-        <v>10004</v>
-      </c>
-      <c r="C189" s="1"/>
+        <v>3017</v>
+      </c>
+      <c r="C189" s="1" t="s">
+        <v>373</v>
+      </c>
       <c r="D189" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>379</v>
+        <v>387</v>
       </c>
     </row>
     <row r="190" ht="15" customHeight="1" spans="1:6">
       <c r="A190" s="1"/>
       <c r="B190" s="1">
-        <v>10101</v>
-      </c>
-      <c r="C190" s="1"/>
+        <v>3018</v>
+      </c>
+      <c r="C190" s="1" t="s">
+        <v>373</v>
+      </c>
       <c r="D190" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>381</v>
+        <v>389</v>
       </c>
     </row>
     <row r="191" ht="15" customHeight="1" spans="1:6">
       <c r="A191" s="1"/>
       <c r="B191" s="1">
-        <v>10102</v>
-      </c>
-      <c r="C191" s="1"/>
+        <v>3019</v>
+      </c>
+      <c r="C191" s="1" t="s">
+        <v>373</v>
+      </c>
       <c r="D191" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
     </row>
     <row r="192" ht="15" customHeight="1" spans="1:6">
       <c r="A192" s="1"/>
       <c r="B192" s="1">
-        <v>10103</v>
-      </c>
-      <c r="C192" s="1"/>
+        <v>6001</v>
+      </c>
+      <c r="C192" s="1" t="s">
+        <v>392</v>
+      </c>
       <c r="D192" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>384</v>
+        <v>393</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>385</v>
+        <v>394</v>
       </c>
     </row>
     <row r="193" ht="15" customHeight="1" spans="1:6">
       <c r="A193" s="1"/>
       <c r="B193" s="1">
-        <v>10201</v>
+        <v>10001</v>
       </c>
       <c r="C193" s="1"/>
       <c r="D193" s="1">
         <v>1</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>387</v>
+        <v>396</v>
       </c>
     </row>
     <row r="194" ht="15" customHeight="1" spans="1:6">
       <c r="A194" s="1"/>
       <c r="B194" s="1">
-        <v>10202</v>
+        <v>10002</v>
       </c>
       <c r="C194" s="1"/>
       <c r="D194" s="1">
         <v>1</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c r="F194" s="1" t="s">
-        <v>389</v>
+        <v>398</v>
       </c>
     </row>
     <row r="195" ht="15" customHeight="1" spans="1:6">
       <c r="A195" s="1"/>
       <c r="B195" s="1">
-        <v>10203</v>
+        <v>10003</v>
       </c>
       <c r="C195" s="1"/>
       <c r="D195" s="1">
         <v>1</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="F195" s="1" t="s">
-        <v>391</v>
+        <v>400</v>
       </c>
     </row>
     <row r="196" ht="15" customHeight="1" spans="1:6">
       <c r="A196" s="1"/>
       <c r="B196" s="1">
-        <v>11001</v>
+        <v>10004</v>
       </c>
       <c r="C196" s="1"/>
       <c r="D196" s="1">
         <v>1</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="F196" s="1" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
     </row>
     <row r="197" ht="15" customHeight="1" spans="1:6">
       <c r="A197" s="1"/>
       <c r="B197" s="1">
-        <v>13001</v>
+        <v>10101</v>
       </c>
       <c r="C197" s="1"/>
       <c r="D197" s="1">
         <v>1</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>395</v>
+        <v>404</v>
       </c>
     </row>
     <row r="198" ht="15" customHeight="1" spans="1:6">
       <c r="A198" s="1"/>
       <c r="B198" s="1">
-        <v>13004</v>
+        <v>10102</v>
       </c>
       <c r="C198" s="1"/>
       <c r="D198" s="1">
         <v>1</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="F198" s="1" t="s">
-        <v>397</v>
+        <v>406</v>
       </c>
     </row>
     <row r="199" ht="15" customHeight="1" spans="1:6">
       <c r="A199" s="1"/>
       <c r="B199" s="1">
-        <v>13010</v>
+        <v>10103</v>
       </c>
       <c r="C199" s="1"/>
       <c r="D199" s="1">
         <v>1</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>398</v>
+        <v>407</v>
       </c>
       <c r="F199" s="1" t="s">
-        <v>399</v>
+        <v>408</v>
       </c>
     </row>
     <row r="200" ht="15" customHeight="1" spans="1:6">
       <c r="A200" s="1"/>
       <c r="B200" s="1">
-        <v>13011</v>
+        <v>10201</v>
       </c>
       <c r="C200" s="1"/>
       <c r="D200" s="1">
         <v>1</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>400</v>
+        <v>409</v>
       </c>
       <c r="F200" s="1" t="s">
-        <v>401</v>
+        <v>410</v>
       </c>
     </row>
     <row r="201" ht="15" customHeight="1" spans="1:6">
       <c r="A201" s="1"/>
       <c r="B201" s="1">
-        <v>13012</v>
+        <v>10202</v>
       </c>
       <c r="C201" s="1"/>
       <c r="D201" s="1">
         <v>1</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>402</v>
+        <v>411</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>403</v>
+        <v>412</v>
       </c>
     </row>
     <row r="202" ht="15" customHeight="1" spans="1:6">
       <c r="A202" s="1"/>
       <c r="B202" s="1">
-        <v>13013</v>
+        <v>10203</v>
       </c>
       <c r="C202" s="1"/>
       <c r="D202" s="1">
         <v>1</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>404</v>
+        <v>413</v>
       </c>
       <c r="F202" s="1" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
     </row>
     <row r="203" ht="15" customHeight="1" spans="1:6">
       <c r="A203" s="1"/>
       <c r="B203" s="1">
-        <v>15001</v>
-      </c>
-      <c r="C203" s="1"/>
+        <v>11001</v>
+      </c>
+      <c r="C203" s="1" t="s">
+        <v>415</v>
+      </c>
       <c r="D203" s="1">
         <v>1</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c r="F203" s="1" t="s">
-        <v>407</v>
+        <v>417</v>
       </c>
     </row>
     <row r="204" ht="15" customHeight="1" spans="1:6">
       <c r="A204" s="1"/>
       <c r="B204" s="1">
-        <v>15002</v>
-      </c>
-      <c r="C204" s="1" t="s">
-        <v>408</v>
-      </c>
+        <v>13001</v>
+      </c>
+      <c r="C204" s="1"/>
       <c r="D204" s="1">
         <v>1</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>409</v>
+        <v>418</v>
       </c>
       <c r="F204" s="1" t="s">
-        <v>410</v>
+        <v>419</v>
       </c>
     </row>
     <row r="205" ht="15" customHeight="1" spans="1:6">
       <c r="A205" s="1"/>
       <c r="B205" s="1">
-        <v>15003</v>
+        <v>13004</v>
       </c>
       <c r="C205" s="1"/>
       <c r="D205" s="1">
         <v>1</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="F205" s="1" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
     </row>
     <row r="206" ht="15" customHeight="1" spans="1:6">
       <c r="A206" s="1"/>
       <c r="B206" s="1">
-        <v>15005</v>
-      </c>
-      <c r="C206" s="1"/>
+        <v>13010</v>
+      </c>
+      <c r="C206" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="D206" s="1">
         <v>1</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>413</v>
+        <v>422</v>
       </c>
       <c r="F206" s="1" t="s">
-        <v>414</v>
+        <v>423</v>
       </c>
     </row>
     <row r="207" ht="15" customHeight="1" spans="1:6">
       <c r="A207" s="1"/>
       <c r="B207" s="1">
-        <v>15007</v>
-      </c>
-      <c r="C207" s="1"/>
+        <v>13011</v>
+      </c>
+      <c r="C207" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="D207" s="1">
         <v>1</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="F207" s="1" t="s">
-        <v>416</v>
+        <v>425</v>
       </c>
     </row>
     <row r="208" ht="15" customHeight="1" spans="1:6">
       <c r="A208" s="1"/>
       <c r="B208" s="1">
-        <v>15008</v>
-      </c>
-      <c r="C208" s="1"/>
+        <v>13012</v>
+      </c>
+      <c r="C208" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="D208" s="1">
         <v>1</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="F208" s="1" t="s">
-        <v>418</v>
+        <v>427</v>
       </c>
     </row>
     <row r="209" ht="15" customHeight="1" spans="1:6">
       <c r="A209" s="1"/>
       <c r="B209" s="1">
-        <v>15009</v>
-      </c>
-      <c r="C209" s="1"/>
+        <v>13013</v>
+      </c>
+      <c r="C209" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="D209" s="1">
         <v>1</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>419</v>
+        <v>428</v>
       </c>
       <c r="F209" s="1" t="s">
-        <v>420</v>
+        <v>429</v>
       </c>
     </row>
     <row r="210" ht="15" customHeight="1" spans="1:6">
       <c r="A210" s="1"/>
       <c r="B210" s="1">
-        <v>15011</v>
-      </c>
-      <c r="C210" s="1"/>
+        <v>13999</v>
+      </c>
+      <c r="C210" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="D210" s="1">
         <v>1</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="F210" s="1" t="s">
-        <v>422</v>
+        <v>431</v>
       </c>
     </row>
     <row r="211" ht="15" customHeight="1" spans="1:6">
       <c r="A211" s="1"/>
       <c r="B211" s="1">
-        <v>15012</v>
+        <v>15001</v>
       </c>
       <c r="C211" s="1"/>
       <c r="D211" s="1">
         <v>1</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>423</v>
+        <v>432</v>
       </c>
       <c r="F211" s="1" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
     </row>
     <row r="212" ht="15" customHeight="1" spans="1:6">
       <c r="A212" s="1"/>
       <c r="B212" s="1">
-        <v>15013</v>
-      </c>
-      <c r="C212" s="1"/>
+        <v>15002</v>
+      </c>
+      <c r="C212" s="1" t="s">
+        <v>434</v>
+      </c>
       <c r="D212" s="1">
         <v>1</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>425</v>
+        <v>435</v>
       </c>
       <c r="F212" s="1" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
     </row>
     <row r="213" ht="15" customHeight="1" spans="1:6">
       <c r="A213" s="1"/>
       <c r="B213" s="1">
-        <v>15014</v>
+        <v>15003</v>
       </c>
       <c r="C213" s="1"/>
       <c r="D213" s="1">
         <v>1</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>427</v>
+        <v>437</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>428</v>
+        <v>438</v>
       </c>
     </row>
     <row r="214" ht="15" customHeight="1" spans="1:6">
       <c r="A214" s="1"/>
       <c r="B214" s="1">
-        <v>15015</v>
+        <v>15005</v>
       </c>
       <c r="C214" s="1"/>
       <c r="D214" s="1">
         <v>1</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>429</v>
+        <v>439</v>
       </c>
       <c r="F214" s="1" t="s">
-        <v>430</v>
+        <v>440</v>
       </c>
     </row>
     <row r="215" ht="15" customHeight="1" spans="1:6">
       <c r="A215" s="1"/>
       <c r="B215" s="1">
-        <v>15017</v>
+        <v>15007</v>
       </c>
       <c r="C215" s="1"/>
       <c r="D215" s="1">
         <v>1</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>431</v>
+        <v>441</v>
       </c>
       <c r="F215" s="1" t="s">
-        <v>432</v>
+        <v>442</v>
       </c>
     </row>
     <row r="216" ht="15" customHeight="1" spans="1:6">
       <c r="A216" s="1"/>
       <c r="B216" s="1">
-        <v>15018</v>
+        <v>15008</v>
       </c>
       <c r="C216" s="1"/>
       <c r="D216" s="1">
         <v>1</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>433</v>
+        <v>443</v>
       </c>
       <c r="F216" s="1" t="s">
-        <v>434</v>
+        <v>444</v>
       </c>
     </row>
     <row r="217" ht="15" customHeight="1" spans="1:6">
       <c r="A217" s="1"/>
       <c r="B217" s="1">
-        <v>15019</v>
+        <v>15009</v>
       </c>
       <c r="C217" s="1"/>
       <c r="D217" s="1">
         <v>1</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>435</v>
+        <v>445</v>
       </c>
       <c r="F217" s="1" t="s">
-        <v>436</v>
+        <v>446</v>
       </c>
     </row>
     <row r="218" ht="15" customHeight="1" spans="1:6">
       <c r="A218" s="1"/>
       <c r="B218" s="1">
-        <v>15020</v>
+        <v>15011</v>
       </c>
       <c r="C218" s="1"/>
       <c r="D218" s="1">
         <v>1</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>437</v>
+        <v>447</v>
       </c>
       <c r="F218" s="1" t="s">
-        <v>438</v>
+        <v>448</v>
       </c>
     </row>
     <row r="219" ht="15" customHeight="1" spans="1:6">
       <c r="A219" s="1"/>
       <c r="B219" s="1">
-        <v>15021</v>
+        <v>15012</v>
       </c>
       <c r="C219" s="1"/>
       <c r="D219" s="1">
         <v>1</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>439</v>
+        <v>449</v>
       </c>
       <c r="F219" s="1" t="s">
-        <v>440</v>
+        <v>450</v>
       </c>
     </row>
     <row r="220" ht="15" customHeight="1" spans="1:6">
       <c r="A220" s="1"/>
       <c r="B220" s="1">
-        <v>15022</v>
-      </c>
-      <c r="C220" s="1" t="s">
-        <v>441</v>
-      </c>
+        <v>15013</v>
+      </c>
+      <c r="C220" s="1"/>
       <c r="D220" s="1">
         <v>1</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>442</v>
+        <v>451</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>443</v>
+        <v>452</v>
       </c>
     </row>
     <row r="221" ht="15" customHeight="1" spans="1:6">
       <c r="A221" s="1"/>
       <c r="B221" s="1">
-        <v>15023</v>
-      </c>
-      <c r="C221" s="1" t="s">
-        <v>441</v>
-      </c>
+        <v>15014</v>
+      </c>
+      <c r="C221" s="1"/>
       <c r="D221" s="1">
         <v>1</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>444</v>
+        <v>453</v>
       </c>
       <c r="F221" s="1" t="s">
-        <v>445</v>
+        <v>454</v>
       </c>
     </row>
     <row r="222" ht="15" customHeight="1" spans="1:6">
       <c r="A222" s="1"/>
       <c r="B222" s="1">
-        <v>19002</v>
+        <v>15015</v>
       </c>
       <c r="C222" s="1"/>
       <c r="D222" s="1">
         <v>1</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>446</v>
+        <v>455</v>
       </c>
       <c r="F222" s="1" t="s">
-        <v>447</v>
+        <v>456</v>
       </c>
     </row>
     <row r="223" ht="15" customHeight="1" spans="1:6">
       <c r="A223" s="1"/>
       <c r="B223" s="1">
-        <v>19003</v>
+        <v>15017</v>
       </c>
       <c r="C223" s="1"/>
       <c r="D223" s="1">
         <v>1</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>448</v>
+        <v>457</v>
       </c>
       <c r="F223" s="1" t="s">
-        <v>449</v>
+        <v>458</v>
       </c>
     </row>
     <row r="224" ht="15" customHeight="1" spans="1:6">
       <c r="A224" s="1"/>
       <c r="B224" s="1">
-        <v>19004</v>
+        <v>15018</v>
       </c>
       <c r="C224" s="1"/>
       <c r="D224" s="1">
         <v>1</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>450</v>
+        <v>459</v>
       </c>
       <c r="F224" s="1" t="s">
-        <v>451</v>
+        <v>460</v>
       </c>
     </row>
     <row r="225" ht="15" customHeight="1" spans="1:6">
       <c r="A225" s="1"/>
       <c r="B225" s="1">
-        <v>19012</v>
+        <v>15019</v>
       </c>
       <c r="C225" s="1"/>
       <c r="D225" s="1">
         <v>1</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>452</v>
+        <v>461</v>
       </c>
       <c r="F225" s="1" t="s">
-        <v>453</v>
+        <v>462</v>
       </c>
     </row>
     <row r="226" ht="15" customHeight="1" spans="1:6">
       <c r="A226" s="1"/>
       <c r="B226" s="1">
-        <v>19013</v>
+        <v>15020</v>
       </c>
       <c r="C226" s="1"/>
       <c r="D226" s="1">
         <v>1</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>454</v>
+        <v>463</v>
       </c>
       <c r="F226" s="1" t="s">
-        <v>455</v>
+        <v>464</v>
       </c>
     </row>
     <row r="227" ht="15" customHeight="1" spans="1:6">
       <c r="A227" s="1"/>
       <c r="B227" s="1">
-        <v>19014</v>
+        <v>15021</v>
       </c>
       <c r="C227" s="1"/>
       <c r="D227" s="1">
         <v>1</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>456</v>
+        <v>465</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
     </row>
     <row r="228" ht="15" customHeight="1" spans="1:6">
       <c r="A228" s="1"/>
       <c r="B228" s="1">
-        <v>19022</v>
-      </c>
-      <c r="C228" s="1"/>
+        <v>15022</v>
+      </c>
+      <c r="C228" s="1" t="s">
+        <v>138</v>
+      </c>
       <c r="D228" s="1">
         <v>1</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
       <c r="F228" s="1" t="s">
-        <v>459</v>
+        <v>468</v>
       </c>
     </row>
     <row r="229" ht="15" customHeight="1" spans="1:6">
       <c r="A229" s="1"/>
       <c r="B229" s="1">
-        <v>19023</v>
-      </c>
-      <c r="C229" s="1"/>
+        <v>15023</v>
+      </c>
+      <c r="C229" s="1" t="s">
+        <v>138</v>
+      </c>
       <c r="D229" s="1">
         <v>1</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="F229" s="1" t="s">
-        <v>461</v>
+        <v>470</v>
       </c>
     </row>
     <row r="230" ht="15" customHeight="1" spans="1:6">
       <c r="A230" s="1"/>
       <c r="B230" s="1">
-        <v>19024</v>
-      </c>
-      <c r="C230" s="1"/>
+        <v>16001</v>
+      </c>
+      <c r="C230" s="1" t="s">
+        <v>471</v>
+      </c>
       <c r="D230" s="1">
         <v>1</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>462</v>
+        <v>472</v>
       </c>
       <c r="F230" s="1" t="s">
-        <v>463</v>
+        <v>473</v>
       </c>
     </row>
     <row r="231" ht="15" customHeight="1" spans="1:6">
       <c r="A231" s="1"/>
       <c r="B231" s="1">
-        <v>60001</v>
-      </c>
-      <c r="C231" s="1"/>
+        <v>16002</v>
+      </c>
+      <c r="C231" s="1" t="s">
+        <v>471</v>
+      </c>
       <c r="D231" s="1">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>464</v>
+        <v>474</v>
       </c>
       <c r="F231" s="1" t="s">
-        <v>465</v>
+        <v>475</v>
       </c>
     </row>
     <row r="232" ht="15" customHeight="1" spans="1:6">
       <c r="A232" s="1"/>
       <c r="B232" s="1">
-        <v>60002</v>
+        <v>19002</v>
       </c>
       <c r="C232" s="1"/>
       <c r="D232" s="1">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>466</v>
+        <v>476</v>
       </c>
       <c r="F232" s="1" t="s">
-        <v>467</v>
+        <v>477</v>
       </c>
     </row>
     <row r="233" ht="15" customHeight="1" spans="1:6">
       <c r="A233" s="1"/>
       <c r="B233" s="1">
-        <v>60003</v>
+        <v>19003</v>
       </c>
       <c r="C233" s="1"/>
       <c r="D233" s="1">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>468</v>
+        <v>478</v>
       </c>
       <c r="F233" s="1" t="s">
-        <v>469</v>
+        <v>479</v>
       </c>
     </row>
     <row r="234" ht="15" customHeight="1" spans="1:6">
       <c r="A234" s="1"/>
       <c r="B234" s="1">
-        <v>60004</v>
+        <v>19004</v>
       </c>
       <c r="C234" s="1"/>
       <c r="D234" s="1">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>470</v>
+        <v>480</v>
       </c>
       <c r="F234" s="1" t="s">
-        <v>471</v>
+        <v>481</v>
       </c>
     </row>
     <row r="235" ht="15" customHeight="1" spans="1:6">
       <c r="A235" s="1"/>
       <c r="B235" s="1">
-        <v>60005</v>
+        <v>19012</v>
       </c>
       <c r="C235" s="1"/>
       <c r="D235" s="1">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E235" s="1" t="s">
-        <v>472</v>
+        <v>482</v>
       </c>
       <c r="F235" s="1" t="s">
-        <v>473</v>
+        <v>483</v>
       </c>
     </row>
     <row r="236" ht="15" customHeight="1" spans="1:6">
       <c r="A236" s="1"/>
       <c r="B236" s="1">
-        <v>60006</v>
+        <v>19013</v>
       </c>
       <c r="C236" s="1"/>
       <c r="D236" s="1">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>474</v>
+        <v>484</v>
       </c>
       <c r="F236" s="1" t="s">
-        <v>475</v>
+        <v>485</v>
       </c>
     </row>
     <row r="237" ht="15" customHeight="1" spans="1:6">
       <c r="A237" s="1"/>
       <c r="B237" s="1">
-        <v>60007</v>
+        <v>19014</v>
       </c>
       <c r="C237" s="1"/>
       <c r="D237" s="1">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E237" s="1" t="s">
-        <v>476</v>
+        <v>486</v>
       </c>
       <c r="F237" s="1" t="s">
-        <v>477</v>
+        <v>487</v>
       </c>
     </row>
     <row r="238" ht="15" customHeight="1" spans="1:6">
       <c r="A238" s="1"/>
       <c r="B238" s="1">
-        <v>60008</v>
+        <v>19022</v>
       </c>
       <c r="C238" s="1"/>
       <c r="D238" s="1">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E238" s="1" t="s">
-        <v>478</v>
+        <v>488</v>
       </c>
       <c r="F238" s="1" t="s">
-        <v>479</v>
+        <v>489</v>
       </c>
     </row>
     <row r="239" ht="15" customHeight="1" spans="1:6">
       <c r="A239" s="1"/>
       <c r="B239" s="1">
-        <v>60009</v>
+        <v>19023</v>
       </c>
       <c r="C239" s="1"/>
       <c r="D239" s="1">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E239" s="1" t="s">
-        <v>480</v>
+        <v>490</v>
       </c>
       <c r="F239" s="1" t="s">
-        <v>481</v>
+        <v>491</v>
       </c>
     </row>
     <row r="240" ht="15" customHeight="1" spans="1:6">
       <c r="A240" s="1"/>
       <c r="B240" s="1">
-        <v>60010</v>
+        <v>19024</v>
       </c>
       <c r="C240" s="1"/>
       <c r="D240" s="1">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E240" s="1" t="s">
-        <v>482</v>
+        <v>492</v>
       </c>
       <c r="F240" s="1" t="s">
-        <v>483</v>
+        <v>493</v>
       </c>
     </row>
     <row r="241" ht="15" customHeight="1" spans="1:6">
       <c r="A241" s="1"/>
       <c r="B241" s="1">
-        <v>60011</v>
-      </c>
-      <c r="C241" s="1"/>
+        <v>20101</v>
+      </c>
+      <c r="C241" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="D241" s="1">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E241" s="1" t="s">
-        <v>484</v>
+        <v>494</v>
       </c>
       <c r="F241" s="1" t="s">
-        <v>485</v>
+        <v>495</v>
       </c>
     </row>
     <row r="242" ht="15" customHeight="1" spans="1:6">
       <c r="A242" s="1"/>
       <c r="B242" s="1">
-        <v>60012</v>
-      </c>
-      <c r="C242" s="1"/>
+        <v>20102</v>
+      </c>
+      <c r="C242" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="D242" s="1">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E242" s="1" t="s">
-        <v>486</v>
+        <v>496</v>
       </c>
       <c r="F242" s="1" t="s">
-        <v>487</v>
+        <v>497</v>
       </c>
     </row>
     <row r="243" ht="15" customHeight="1" spans="1:6">
       <c r="A243" s="1"/>
       <c r="B243" s="1">
-        <v>60013</v>
-      </c>
-      <c r="C243" s="1"/>
+        <v>20103</v>
+      </c>
+      <c r="C243" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="D243" s="1">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E243" s="1" t="s">
-        <v>488</v>
+        <v>498</v>
       </c>
       <c r="F243" s="1" t="s">
-        <v>489</v>
+        <v>499</v>
       </c>
     </row>
     <row r="244" ht="15" customHeight="1" spans="1:6">
       <c r="A244" s="1"/>
       <c r="B244" s="1">
-        <v>60014</v>
-      </c>
-      <c r="C244" s="1"/>
+        <v>20104</v>
+      </c>
+      <c r="C244" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="D244" s="1">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E244" s="1" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="F244" s="1" t="s">
-        <v>491</v>
+        <v>501</v>
       </c>
     </row>
     <row r="245" ht="15" customHeight="1" spans="1:6">
       <c r="A245" s="1"/>
       <c r="B245" s="1">
-        <v>60015</v>
-      </c>
-      <c r="C245" s="1"/>
+        <v>20105</v>
+      </c>
+      <c r="C245" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="D245" s="1">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>492</v>
+        <v>502</v>
       </c>
       <c r="F245" s="1" t="s">
-        <v>493</v>
+        <v>503</v>
       </c>
     </row>
     <row r="246" ht="15" customHeight="1" spans="1:6">
       <c r="A246" s="1"/>
       <c r="B246" s="1">
-        <v>60016</v>
-      </c>
-      <c r="C246" s="1"/>
+        <v>20106</v>
+      </c>
+      <c r="C246" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="D246" s="1">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>494</v>
+        <v>504</v>
       </c>
       <c r="F246" s="1" t="s">
-        <v>495</v>
+        <v>505</v>
       </c>
     </row>
     <row r="247" ht="15" customHeight="1" spans="1:6">
       <c r="A247" s="1"/>
       <c r="B247" s="1">
-        <v>60017</v>
-      </c>
-      <c r="C247" s="1"/>
+        <v>20107</v>
+      </c>
+      <c r="C247" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="D247" s="1">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>496</v>
+        <v>506</v>
       </c>
       <c r="F247" s="1" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
     </row>
     <row r="248" ht="15" customHeight="1" spans="1:6">
       <c r="A248" s="1"/>
       <c r="B248" s="1">
-        <v>60018</v>
-      </c>
-      <c r="C248" s="1"/>
+        <v>20108</v>
+      </c>
+      <c r="C248" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="D248" s="1">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>498</v>
+        <v>508</v>
       </c>
       <c r="F248" s="1" t="s">
-        <v>499</v>
+        <v>509</v>
       </c>
     </row>
     <row r="249" ht="15" customHeight="1" spans="1:6">
       <c r="A249" s="1"/>
       <c r="B249" s="1">
-        <v>60019</v>
-      </c>
-      <c r="C249" s="1"/>
+        <v>20109</v>
+      </c>
+      <c r="C249" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="D249" s="1">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>500</v>
+        <v>510</v>
       </c>
       <c r="F249" s="1" t="s">
-        <v>501</v>
+        <v>511</v>
       </c>
     </row>
     <row r="250" ht="15" customHeight="1" spans="1:6">
       <c r="A250" s="1"/>
       <c r="B250" s="1">
-        <v>60020</v>
-      </c>
-      <c r="C250" s="1"/>
+        <v>20110</v>
+      </c>
+      <c r="C250" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="D250" s="1">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E250" s="1" t="s">
-        <v>502</v>
+        <v>512</v>
       </c>
       <c r="F250" s="1" t="s">
-        <v>503</v>
+        <v>513</v>
       </c>
     </row>
     <row r="251" ht="15" customHeight="1" spans="1:6">
       <c r="A251" s="1"/>
       <c r="B251" s="1">
-        <v>60021</v>
-      </c>
-      <c r="C251" s="1"/>
+        <v>20111</v>
+      </c>
+      <c r="C251" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="D251" s="1">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>504</v>
+        <v>514</v>
       </c>
       <c r="F251" s="1" t="s">
-        <v>505</v>
+        <v>515</v>
       </c>
     </row>
     <row r="252" ht="15" customHeight="1" spans="1:6">
       <c r="A252" s="1"/>
       <c r="B252" s="1">
-        <v>60022</v>
-      </c>
-      <c r="C252" s="1"/>
+        <v>20112</v>
+      </c>
+      <c r="C252" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="D252" s="1">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E252" s="1" t="s">
-        <v>506</v>
+        <v>516</v>
       </c>
       <c r="F252" s="1" t="s">
-        <v>507</v>
+        <v>517</v>
       </c>
     </row>
     <row r="253" ht="15" customHeight="1" spans="1:6">
       <c r="A253" s="1"/>
       <c r="B253" s="1">
-        <v>60023</v>
-      </c>
-      <c r="C253" s="1"/>
+        <v>20113</v>
+      </c>
+      <c r="C253" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="D253" s="1">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E253" s="1" t="s">
-        <v>508</v>
+        <v>518</v>
       </c>
       <c r="F253" s="1" t="s">
-        <v>509</v>
+        <v>519</v>
       </c>
     </row>
     <row r="254" ht="15" customHeight="1" spans="1:6">
       <c r="A254" s="1"/>
       <c r="B254" s="1">
-        <v>60024</v>
-      </c>
-      <c r="C254" s="1"/>
+        <v>20114</v>
+      </c>
+      <c r="C254" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="D254" s="1">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E254" s="1" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="F254" s="1" t="s">
-        <v>511</v>
+        <v>521</v>
       </c>
     </row>
     <row r="255" ht="15" customHeight="1" spans="1:6">
       <c r="A255" s="1"/>
       <c r="B255" s="1">
-        <v>60025</v>
-      </c>
-      <c r="C255" s="1"/>
+        <v>20115</v>
+      </c>
+      <c r="C255" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="D255" s="1">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>512</v>
+        <v>522</v>
       </c>
       <c r="F255" s="1" t="s">
-        <v>513</v>
+        <v>523</v>
       </c>
     </row>
     <row r="256" ht="15" customHeight="1" spans="1:6">
       <c r="A256" s="1"/>
       <c r="B256" s="1">
-        <v>60026</v>
-      </c>
-      <c r="C256" s="1"/>
+        <v>20116</v>
+      </c>
+      <c r="C256" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="D256" s="1">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E256" s="1" t="s">
-        <v>514</v>
+        <v>524</v>
       </c>
       <c r="F256" s="1" t="s">
-        <v>515</v>
+        <v>525</v>
       </c>
     </row>
     <row r="257" ht="15" customHeight="1" spans="1:6">
       <c r="A257" s="1"/>
       <c r="B257" s="1">
-        <v>60027</v>
-      </c>
-      <c r="C257" s="1"/>
+        <v>20117</v>
+      </c>
+      <c r="C257" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="D257" s="1">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E257" s="1" t="s">
-        <v>516</v>
+        <v>526</v>
       </c>
       <c r="F257" s="1" t="s">
-        <v>517</v>
+        <v>527</v>
       </c>
     </row>
     <row r="258" ht="15" customHeight="1" spans="1:6">
       <c r="A258" s="1"/>
       <c r="B258" s="1">
-        <v>60028</v>
-      </c>
-      <c r="C258" s="1"/>
+        <v>20118</v>
+      </c>
+      <c r="C258" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="D258" s="1">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="F258" s="1" t="s">
-        <v>519</v>
+        <v>529</v>
       </c>
     </row>
     <row r="259" ht="15" customHeight="1" spans="1:6">
       <c r="A259" s="1"/>
       <c r="B259" s="1">
-        <v>60029</v>
-      </c>
-      <c r="C259" s="1"/>
+        <v>20119</v>
+      </c>
+      <c r="C259" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="D259" s="1">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>520</v>
+        <v>530</v>
       </c>
       <c r="F259" s="1" t="s">
-        <v>521</v>
+        <v>531</v>
       </c>
     </row>
     <row r="260" ht="15" customHeight="1" spans="1:6">
       <c r="A260" s="1"/>
       <c r="B260" s="1">
-        <v>60030</v>
-      </c>
-      <c r="C260" s="1"/>
+        <v>20120</v>
+      </c>
+      <c r="C260" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="D260" s="1">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="F260" s="1" t="s">
-        <v>523</v>
+        <v>533</v>
       </c>
     </row>
     <row r="261" ht="15" customHeight="1" spans="1:6">
       <c r="A261" s="1"/>
       <c r="B261" s="1">
-        <v>60031</v>
-      </c>
-      <c r="C261" s="1"/>
+        <v>20121</v>
+      </c>
+      <c r="C261" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="D261" s="1">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>524</v>
+        <v>534</v>
       </c>
       <c r="F261" s="1" t="s">
-        <v>525</v>
+        <v>535</v>
       </c>
     </row>
     <row r="262" ht="15" customHeight="1" spans="1:6">
       <c r="A262" s="1"/>
       <c r="B262" s="1">
-        <v>60032</v>
-      </c>
-      <c r="C262" s="1"/>
+        <v>20122</v>
+      </c>
+      <c r="C262" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="D262" s="1">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="F262" s="1" t="s">
-        <v>527</v>
+        <v>537</v>
       </c>
     </row>
     <row r="263" ht="15" customHeight="1" spans="1:6">
       <c r="A263" s="1"/>
       <c r="B263" s="1">
-        <v>60033</v>
-      </c>
-      <c r="C263" s="1"/>
+        <v>20123</v>
+      </c>
+      <c r="C263" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="D263" s="1">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E263" s="1" t="s">
-        <v>528</v>
+        <v>538</v>
       </c>
       <c r="F263" s="1" t="s">
-        <v>529</v>
+        <v>539</v>
       </c>
     </row>
     <row r="264" ht="15" customHeight="1" spans="1:6">
       <c r="A264" s="1"/>
       <c r="B264" s="1">
-        <v>60034</v>
-      </c>
-      <c r="C264" s="1"/>
+        <v>20124</v>
+      </c>
+      <c r="C264" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="D264" s="1">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E264" s="1" t="s">
-        <v>530</v>
+        <v>540</v>
       </c>
       <c r="F264" s="1" t="s">
-        <v>531</v>
+        <v>541</v>
       </c>
     </row>
     <row r="265" ht="15" customHeight="1" spans="1:6">
       <c r="A265" s="1"/>
       <c r="B265" s="1">
-        <v>60035</v>
-      </c>
-      <c r="C265" s="1"/>
+        <v>20125</v>
+      </c>
+      <c r="C265" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="D265" s="1">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E265" s="1" t="s">
-        <v>532</v>
+        <v>542</v>
       </c>
       <c r="F265" s="1" t="s">
-        <v>533</v>
+        <v>543</v>
       </c>
     </row>
     <row r="266" ht="15" customHeight="1" spans="1:6">
       <c r="A266" s="1"/>
       <c r="B266" s="1">
-        <v>60036</v>
-      </c>
-      <c r="C266" s="1"/>
+        <v>20126</v>
+      </c>
+      <c r="C266" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="D266" s="1">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>534</v>
+        <v>544</v>
       </c>
       <c r="F266" s="1" t="s">
-        <v>535</v>
+        <v>545</v>
       </c>
     </row>
     <row r="267" ht="15" customHeight="1" spans="1:6">
       <c r="A267" s="1"/>
       <c r="B267" s="1">
-        <v>60037</v>
-      </c>
-      <c r="C267" s="1"/>
+        <v>20127</v>
+      </c>
+      <c r="C267" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="D267" s="1">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E267" s="1" t="s">
-        <v>536</v>
+        <v>546</v>
       </c>
       <c r="F267" s="1" t="s">
-        <v>537</v>
+        <v>547</v>
       </c>
     </row>
     <row r="268" ht="15" customHeight="1" spans="1:6">
       <c r="A268" s="1"/>
       <c r="B268" s="1">
-        <v>60038</v>
-      </c>
-      <c r="C268" s="1"/>
+        <v>20128</v>
+      </c>
+      <c r="C268" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="D268" s="1">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>538</v>
+        <v>548</v>
       </c>
       <c r="F268" s="1" t="s">
-        <v>539</v>
+        <v>549</v>
       </c>
     </row>
     <row r="269" ht="15" customHeight="1" spans="1:6">
       <c r="A269" s="1"/>
       <c r="B269" s="1">
-        <v>60039</v>
-      </c>
-      <c r="C269" s="1"/>
+        <v>30101</v>
+      </c>
+      <c r="C269" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="D269" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>540</v>
+        <v>550</v>
       </c>
       <c r="F269" s="1" t="s">
-        <v>541</v>
+        <v>551</v>
       </c>
     </row>
     <row r="270" ht="15" customHeight="1" spans="1:6">
       <c r="A270" s="1"/>
       <c r="B270" s="1">
-        <v>60040</v>
-      </c>
-      <c r="C270" s="1"/>
+        <v>30102</v>
+      </c>
+      <c r="C270" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="D270" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E270" s="1" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="F270" s="1" t="s">
-        <v>543</v>
+        <v>553</v>
       </c>
     </row>
     <row r="271" ht="15" customHeight="1" spans="1:6">
       <c r="A271" s="1"/>
       <c r="B271" s="1">
-        <v>60041</v>
-      </c>
-      <c r="C271" s="1"/>
+        <v>30103</v>
+      </c>
+      <c r="C271" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="D271" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E271" s="1" t="s">
-        <v>544</v>
+        <v>554</v>
       </c>
       <c r="F271" s="1" t="s">
-        <v>545</v>
+        <v>555</v>
       </c>
     </row>
     <row r="272" ht="15" customHeight="1" spans="1:6">
       <c r="A272" s="1"/>
       <c r="B272" s="1">
-        <v>60042</v>
-      </c>
-      <c r="C272" s="1"/>
+        <v>30104</v>
+      </c>
+      <c r="C272" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="D272" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E272" s="1" t="s">
-        <v>546</v>
+        <v>556</v>
       </c>
       <c r="F272" s="1" t="s">
-        <v>547</v>
+        <v>557</v>
       </c>
     </row>
     <row r="273" ht="15" customHeight="1" spans="1:6">
       <c r="A273" s="1"/>
       <c r="B273" s="1">
-        <v>60043</v>
-      </c>
-      <c r="C273" s="1"/>
+        <v>30105</v>
+      </c>
+      <c r="C273" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="D273" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E273" s="1" t="s">
-        <v>548</v>
+        <v>558</v>
       </c>
       <c r="F273" s="1" t="s">
-        <v>549</v>
+        <v>559</v>
       </c>
     </row>
     <row r="274" ht="15" customHeight="1" spans="1:6">
       <c r="A274" s="1"/>
       <c r="B274" s="1">
-        <v>60044</v>
-      </c>
-      <c r="C274" s="1"/>
+        <v>30106</v>
+      </c>
+      <c r="C274" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="D274" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>550</v>
+        <v>560</v>
       </c>
       <c r="F274" s="1" t="s">
-        <v>551</v>
+        <v>561</v>
       </c>
     </row>
     <row r="275" ht="15" customHeight="1" spans="1:6">
       <c r="A275" s="1"/>
       <c r="B275" s="1">
-        <v>60045</v>
-      </c>
-      <c r="C275" s="1"/>
+        <v>30107</v>
+      </c>
+      <c r="C275" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="D275" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E275" s="1" t="s">
-        <v>552</v>
+        <v>562</v>
       </c>
       <c r="F275" s="1" t="s">
-        <v>553</v>
+        <v>563</v>
       </c>
     </row>
     <row r="276" ht="15" customHeight="1" spans="1:6">
       <c r="A276" s="1"/>
       <c r="B276" s="1">
-        <v>60046</v>
-      </c>
-      <c r="C276" s="1"/>
+        <v>30108</v>
+      </c>
+      <c r="C276" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="D276" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E276" s="1" t="s">
-        <v>554</v>
+        <v>564</v>
       </c>
       <c r="F276" s="1" t="s">
-        <v>555</v>
+        <v>565</v>
       </c>
     </row>
     <row r="277" ht="15" customHeight="1" spans="1:6">
       <c r="A277" s="1"/>
       <c r="B277" s="1">
-        <v>60047</v>
-      </c>
-      <c r="C277" s="1"/>
+        <v>30109</v>
+      </c>
+      <c r="C277" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="D277" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E277" s="1" t="s">
-        <v>556</v>
+        <v>566</v>
       </c>
       <c r="F277" s="1" t="s">
-        <v>557</v>
+        <v>567</v>
       </c>
     </row>
     <row r="278" ht="15" customHeight="1" spans="1:6">
       <c r="A278" s="1"/>
       <c r="B278" s="1">
-        <v>60048</v>
-      </c>
-      <c r="C278" s="1"/>
+        <v>30110</v>
+      </c>
+      <c r="C278" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="D278" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E278" s="1" t="s">
-        <v>558</v>
+        <v>568</v>
       </c>
       <c r="F278" s="1" t="s">
-        <v>559</v>
+        <v>569</v>
       </c>
     </row>
     <row r="279" ht="15" customHeight="1" spans="1:6">
       <c r="A279" s="1"/>
       <c r="B279" s="1">
-        <v>60049</v>
-      </c>
-      <c r="C279" s="1"/>
+        <v>30111</v>
+      </c>
+      <c r="C279" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="D279" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E279" s="1" t="s">
-        <v>560</v>
+        <v>570</v>
       </c>
       <c r="F279" s="1" t="s">
-        <v>561</v>
+        <v>571</v>
       </c>
     </row>
     <row r="280" ht="15" customHeight="1" spans="1:6">
       <c r="A280" s="1"/>
       <c r="B280" s="1">
-        <v>60050</v>
-      </c>
-      <c r="C280" s="1"/>
+        <v>30112</v>
+      </c>
+      <c r="C280" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="D280" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E280" s="1" t="s">
-        <v>562</v>
+        <v>572</v>
       </c>
       <c r="F280" s="1" t="s">
-        <v>563</v>
+        <v>573</v>
       </c>
     </row>
     <row r="281" ht="15" customHeight="1" spans="1:6">
       <c r="A281" s="1"/>
       <c r="B281" s="1">
-        <v>60051</v>
-      </c>
-      <c r="C281" s="1"/>
+        <v>30113</v>
+      </c>
+      <c r="C281" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="D281" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E281" s="1" t="s">
-        <v>564</v>
+        <v>574</v>
       </c>
       <c r="F281" s="1" t="s">
-        <v>565</v>
+        <v>575</v>
       </c>
     </row>
     <row r="282" ht="15" customHeight="1" spans="1:6">
       <c r="A282" s="1"/>
       <c r="B282" s="1">
-        <v>60052</v>
-      </c>
-      <c r="C282" s="1"/>
+        <v>30114</v>
+      </c>
+      <c r="C282" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="D282" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E282" s="1" t="s">
-        <v>566</v>
+        <v>576</v>
       </c>
       <c r="F282" s="1" t="s">
-        <v>567</v>
+        <v>577</v>
       </c>
     </row>
     <row r="283" ht="15" customHeight="1" spans="1:6">
       <c r="A283" s="1"/>
       <c r="B283" s="1">
-        <v>60053</v>
-      </c>
-      <c r="C283" s="1"/>
+        <v>30115</v>
+      </c>
+      <c r="C283" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="D283" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E283" s="1" t="s">
-        <v>568</v>
+        <v>578</v>
       </c>
       <c r="F283" s="1" t="s">
-        <v>569</v>
+        <v>579</v>
       </c>
     </row>
     <row r="284" ht="15" customHeight="1" spans="1:6">
       <c r="A284" s="1"/>
       <c r="B284" s="1">
-        <v>60054</v>
-      </c>
-      <c r="C284" s="1"/>
+        <v>30116</v>
+      </c>
+      <c r="C284" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="D284" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E284" s="1" t="s">
-        <v>570</v>
+        <v>580</v>
       </c>
       <c r="F284" s="1" t="s">
-        <v>571</v>
+        <v>581</v>
       </c>
     </row>
     <row r="285" ht="15" customHeight="1" spans="1:6">
       <c r="A285" s="1"/>
       <c r="B285" s="1">
-        <v>60055</v>
-      </c>
-      <c r="C285" s="1"/>
+        <v>30117</v>
+      </c>
+      <c r="C285" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="D285" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E285" s="1" t="s">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F285" s="1" t="s">
-        <v>573</v>
+        <v>583</v>
       </c>
     </row>
     <row r="286" ht="15" customHeight="1" spans="1:6">
       <c r="A286" s="1"/>
       <c r="B286" s="1">
-        <v>60056</v>
-      </c>
-      <c r="C286" s="1"/>
+        <v>30118</v>
+      </c>
+      <c r="C286" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="D286" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>574</v>
+        <v>584</v>
       </c>
       <c r="F286" s="1" t="s">
-        <v>575</v>
+        <v>585</v>
       </c>
     </row>
     <row r="287" ht="15" customHeight="1" spans="1:6">
       <c r="A287" s="1"/>
       <c r="B287" s="1">
-        <v>60057</v>
-      </c>
-      <c r="C287" s="1"/>
+        <v>30119</v>
+      </c>
+      <c r="C287" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="D287" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>576</v>
+        <v>586</v>
       </c>
       <c r="F287" s="1" t="s">
-        <v>577</v>
+        <v>587</v>
       </c>
     </row>
     <row r="288" ht="15" customHeight="1" spans="1:6">
       <c r="A288" s="1"/>
       <c r="B288" s="1">
-        <v>60058</v>
-      </c>
-      <c r="C288" s="1"/>
+        <v>30120</v>
+      </c>
+      <c r="C288" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="D288" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>578</v>
+        <v>588</v>
       </c>
       <c r="F288" s="1" t="s">
-        <v>579</v>
+        <v>589</v>
       </c>
     </row>
     <row r="289" ht="15" customHeight="1" spans="1:6">
       <c r="A289" s="1"/>
       <c r="B289" s="1">
-        <v>60059</v>
-      </c>
-      <c r="C289" s="1"/>
+        <v>30121</v>
+      </c>
+      <c r="C289" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="D289" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E289" s="1" t="s">
-        <v>580</v>
+        <v>590</v>
       </c>
       <c r="F289" s="1" t="s">
-        <v>581</v>
+        <v>591</v>
       </c>
     </row>
     <row r="290" ht="15" customHeight="1" spans="1:6">
       <c r="A290" s="1"/>
       <c r="B290" s="1">
-        <v>60060</v>
-      </c>
-      <c r="C290" s="1"/>
+        <v>30122</v>
+      </c>
+      <c r="C290" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="D290" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E290" s="1" t="s">
-        <v>582</v>
+        <v>592</v>
       </c>
       <c r="F290" s="1" t="s">
-        <v>583</v>
+        <v>593</v>
       </c>
     </row>
     <row r="291" ht="15" customHeight="1" spans="1:6">
       <c r="A291" s="1"/>
       <c r="B291" s="1">
-        <v>60061</v>
-      </c>
-      <c r="C291" s="1"/>
+        <v>30123</v>
+      </c>
+      <c r="C291" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="D291" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>584</v>
+        <v>594</v>
       </c>
       <c r="F291" s="1" t="s">
-        <v>585</v>
+        <v>595</v>
       </c>
     </row>
     <row r="292" ht="15" customHeight="1" spans="1:6">
       <c r="A292" s="1"/>
       <c r="B292" s="1">
-        <v>60062</v>
-      </c>
-      <c r="C292" s="1"/>
+        <v>30124</v>
+      </c>
+      <c r="C292" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="D292" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E292" s="1" t="s">
-        <v>586</v>
+        <v>596</v>
       </c>
       <c r="F292" s="1" t="s">
-        <v>587</v>
+        <v>597</v>
       </c>
     </row>
     <row r="293" ht="15" customHeight="1" spans="1:6">
       <c r="A293" s="1"/>
       <c r="B293" s="1">
-        <v>60063</v>
-      </c>
-      <c r="C293" s="1"/>
+        <v>30125</v>
+      </c>
+      <c r="C293" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="D293" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E293" s="1" t="s">
-        <v>588</v>
+        <v>598</v>
       </c>
       <c r="F293" s="1" t="s">
-        <v>589</v>
+        <v>599</v>
       </c>
     </row>
     <row r="294" ht="15" customHeight="1" spans="1:6">
       <c r="A294" s="1"/>
       <c r="B294" s="1">
-        <v>60064</v>
-      </c>
-      <c r="C294" s="1"/>
+        <v>30126</v>
+      </c>
+      <c r="C294" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="D294" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E294" s="1" t="s">
-        <v>590</v>
+        <v>600</v>
       </c>
       <c r="F294" s="1" t="s">
-        <v>591</v>
+        <v>601</v>
       </c>
     </row>
     <row r="295" ht="15" customHeight="1" spans="1:6">
       <c r="A295" s="1"/>
       <c r="B295" s="1">
-        <v>60065</v>
-      </c>
-      <c r="C295" s="1"/>
+        <v>30201</v>
+      </c>
+      <c r="C295" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="D295" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E295" s="1" t="s">
-        <v>592</v>
+        <v>602</v>
       </c>
       <c r="F295" s="1" t="s">
-        <v>593</v>
+        <v>603</v>
       </c>
     </row>
     <row r="296" ht="15" customHeight="1" spans="1:6">
       <c r="A296" s="1"/>
       <c r="B296" s="1">
-        <v>60066</v>
-      </c>
-      <c r="C296" s="1"/>
+        <v>30202</v>
+      </c>
+      <c r="C296" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="D296" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E296" s="1" t="s">
-        <v>594</v>
+        <v>604</v>
       </c>
       <c r="F296" s="1" t="s">
-        <v>595</v>
+        <v>605</v>
       </c>
     </row>
     <row r="297" ht="15" customHeight="1" spans="1:6">
       <c r="A297" s="1"/>
       <c r="B297" s="1">
-        <v>60067</v>
-      </c>
-      <c r="C297" s="1"/>
+        <v>30203</v>
+      </c>
+      <c r="C297" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="D297" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E297" s="1" t="s">
-        <v>596</v>
+        <v>606</v>
       </c>
       <c r="F297" s="1" t="s">
-        <v>597</v>
+        <v>607</v>
       </c>
     </row>
     <row r="298" ht="15" customHeight="1" spans="1:6">
       <c r="A298" s="1"/>
       <c r="B298" s="1">
-        <v>60068</v>
-      </c>
-      <c r="C298" s="1"/>
+        <v>30204</v>
+      </c>
+      <c r="C298" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="D298" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>598</v>
+        <v>608</v>
       </c>
       <c r="F298" s="1" t="s">
-        <v>599</v>
+        <v>609</v>
       </c>
     </row>
     <row r="299" ht="15" customHeight="1" spans="1:6">
       <c r="A299" s="1"/>
       <c r="B299" s="1">
-        <v>60069</v>
-      </c>
-      <c r="C299" s="1"/>
+        <v>30205</v>
+      </c>
+      <c r="C299" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="D299" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>600</v>
+        <v>610</v>
       </c>
       <c r="F299" s="1" t="s">
-        <v>601</v>
+        <v>611</v>
       </c>
     </row>
     <row r="300" ht="15" customHeight="1" spans="1:6">
       <c r="A300" s="1"/>
       <c r="B300" s="1">
-        <v>60070</v>
-      </c>
-      <c r="C300" s="1"/>
+        <v>30206</v>
+      </c>
+      <c r="C300" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="D300" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>602</v>
+        <v>612</v>
       </c>
       <c r="F300" s="1" t="s">
-        <v>603</v>
+        <v>613</v>
       </c>
     </row>
     <row r="301" ht="15" customHeight="1" spans="1:6">
       <c r="A301" s="1"/>
       <c r="B301" s="1">
-        <v>60071</v>
-      </c>
-      <c r="C301" s="1"/>
+        <v>30301</v>
+      </c>
+      <c r="C301" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="D301" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E301" s="1" t="s">
-        <v>604</v>
+        <v>614</v>
       </c>
       <c r="F301" s="1" t="s">
-        <v>605</v>
+        <v>615</v>
       </c>
     </row>
     <row r="302" ht="15" customHeight="1" spans="1:6">
       <c r="A302" s="1"/>
       <c r="B302" s="1">
-        <v>60072</v>
-      </c>
-      <c r="C302" s="1"/>
+        <v>30302</v>
+      </c>
+      <c r="C302" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="D302" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E302" s="1" t="s">
-        <v>606</v>
+        <v>616</v>
       </c>
       <c r="F302" s="1" t="s">
-        <v>607</v>
+        <v>617</v>
       </c>
     </row>
     <row r="303" ht="15" customHeight="1" spans="1:6">
       <c r="A303" s="1"/>
       <c r="B303" s="1">
-        <v>60073</v>
-      </c>
-      <c r="C303" s="1"/>
+        <v>30303</v>
+      </c>
+      <c r="C303" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="D303" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E303" s="1" t="s">
-        <v>608</v>
+        <v>618</v>
       </c>
       <c r="F303" s="1" t="s">
-        <v>609</v>
+        <v>619</v>
       </c>
     </row>
     <row r="304" ht="15" customHeight="1" spans="1:6">
       <c r="A304" s="1"/>
       <c r="B304" s="1">
-        <v>60074</v>
-      </c>
-      <c r="C304" s="1"/>
+        <v>30304</v>
+      </c>
+      <c r="C304" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="D304" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E304" s="1" t="s">
-        <v>610</v>
+        <v>620</v>
       </c>
       <c r="F304" s="1" t="s">
-        <v>611</v>
+        <v>621</v>
       </c>
     </row>
     <row r="305" ht="15" customHeight="1" spans="1:6">
       <c r="A305" s="1"/>
       <c r="B305" s="1">
-        <v>60075</v>
-      </c>
-      <c r="C305" s="1"/>
+        <v>30305</v>
+      </c>
+      <c r="C305" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="D305" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E305" s="1" t="s">
-        <v>612</v>
+        <v>622</v>
       </c>
       <c r="F305" s="1" t="s">
-        <v>613</v>
+        <v>623</v>
       </c>
     </row>
     <row r="306" ht="15" customHeight="1" spans="1:6">
       <c r="A306" s="1"/>
       <c r="B306" s="1">
-        <v>60076</v>
-      </c>
-      <c r="C306" s="1"/>
+        <v>30306</v>
+      </c>
+      <c r="C306" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="D306" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E306" s="1" t="s">
-        <v>614</v>
+        <v>624</v>
       </c>
       <c r="F306" s="1" t="s">
-        <v>615</v>
+        <v>625</v>
       </c>
     </row>
     <row r="307" ht="15" customHeight="1" spans="1:6">
       <c r="A307" s="1"/>
       <c r="B307" s="1">
-        <v>60077</v>
-      </c>
-      <c r="C307" s="1"/>
+        <v>30307</v>
+      </c>
+      <c r="C307" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="D307" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E307" s="1" t="s">
-        <v>616</v>
+        <v>626</v>
       </c>
       <c r="F307" s="1" t="s">
-        <v>617</v>
+        <v>627</v>
       </c>
     </row>
     <row r="308" ht="15" customHeight="1" spans="1:6">
       <c r="A308" s="1"/>
       <c r="B308" s="1">
-        <v>60078</v>
-      </c>
-      <c r="C308" s="1"/>
+        <v>30308</v>
+      </c>
+      <c r="C308" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="D308" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E308" s="1" t="s">
-        <v>618</v>
+        <v>628</v>
       </c>
       <c r="F308" s="1" t="s">
-        <v>619</v>
+        <v>629</v>
       </c>
     </row>
     <row r="309" ht="15" customHeight="1" spans="1:6">
       <c r="A309" s="1"/>
       <c r="B309" s="1">
-        <v>60079</v>
-      </c>
-      <c r="C309" s="1"/>
+        <v>60001</v>
+      </c>
+      <c r="C309" s="1" t="s">
+        <v>630</v>
+      </c>
       <c r="D309" s="1">
         <v>7</v>
       </c>
       <c r="E309" s="1" t="s">
-        <v>620</v>
+        <v>631</v>
       </c>
       <c r="F309" s="1" t="s">
-        <v>621</v>
+        <v>632</v>
       </c>
     </row>
     <row r="310" ht="15" customHeight="1" spans="1:6">
       <c r="A310" s="1"/>
       <c r="B310" s="1">
-        <v>60080</v>
-      </c>
-      <c r="C310" s="1"/>
+        <v>60002</v>
+      </c>
+      <c r="C310" s="1" t="s">
+        <v>630</v>
+      </c>
       <c r="D310" s="1">
         <v>7</v>
       </c>
       <c r="E310" s="1" t="s">
-        <v>622</v>
+        <v>633</v>
       </c>
       <c r="F310" s="1" t="s">
-        <v>623</v>
+        <v>634</v>
       </c>
     </row>
     <row r="311" ht="15" customHeight="1" spans="1:6">
       <c r="A311" s="1"/>
       <c r="B311" s="1">
-        <v>60081</v>
-      </c>
-      <c r="C311" s="1"/>
+        <v>60003</v>
+      </c>
+      <c r="C311" s="1" t="s">
+        <v>630</v>
+      </c>
       <c r="D311" s="1">
         <v>7</v>
       </c>
       <c r="E311" s="1" t="s">
-        <v>624</v>
+        <v>635</v>
       </c>
       <c r="F311" s="1" t="s">
-        <v>625</v>
+        <v>636</v>
       </c>
     </row>
     <row r="312" ht="15" customHeight="1" spans="1:6">
       <c r="A312" s="1"/>
       <c r="B312" s="1">
-        <v>60082</v>
-      </c>
-      <c r="C312" s="1"/>
+        <v>60004</v>
+      </c>
+      <c r="C312" s="1" t="s">
+        <v>630</v>
+      </c>
       <c r="D312" s="1">
         <v>7</v>
       </c>
       <c r="E312" s="1" t="s">
-        <v>626</v>
+        <v>637</v>
       </c>
       <c r="F312" s="1" t="s">
-        <v>627</v>
+        <v>638</v>
       </c>
     </row>
     <row r="313" ht="15" customHeight="1" spans="1:6">
       <c r="A313" s="1"/>
       <c r="B313" s="1">
-        <v>60083</v>
-      </c>
-      <c r="C313" s="1"/>
+        <v>60005</v>
+      </c>
+      <c r="C313" s="1" t="s">
+        <v>630</v>
+      </c>
       <c r="D313" s="1">
         <v>7</v>
       </c>
       <c r="E313" s="1" t="s">
-        <v>628</v>
+        <v>639</v>
       </c>
       <c r="F313" s="1" t="s">
-        <v>629</v>
+        <v>640</v>
+      </c>
+    </row>
+    <row r="314" ht="15" customHeight="1" spans="1:6">
+      <c r="A314" s="1"/>
+      <c r="B314" s="1">
+        <v>60006</v>
+      </c>
+      <c r="C314" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D314" s="1">
+        <v>7</v>
+      </c>
+      <c r="E314" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="F314" s="1" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="315" ht="15" customHeight="1" spans="1:6">
+      <c r="A315" s="1"/>
+      <c r="B315" s="1">
+        <v>60007</v>
+      </c>
+      <c r="C315" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D315" s="1">
+        <v>7</v>
+      </c>
+      <c r="E315" s="1" t="s">
+        <v>643</v>
+      </c>
+      <c r="F315" s="1" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="316" ht="15" customHeight="1" spans="1:6">
+      <c r="A316" s="1"/>
+      <c r="B316" s="1">
+        <v>60008</v>
+      </c>
+      <c r="C316" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D316" s="1">
+        <v>7</v>
+      </c>
+      <c r="E316" s="1" t="s">
+        <v>645</v>
+      </c>
+      <c r="F316" s="1" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="317" ht="15" customHeight="1" spans="1:6">
+      <c r="A317" s="1"/>
+      <c r="B317" s="1">
+        <v>60009</v>
+      </c>
+      <c r="C317" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D317" s="1">
+        <v>7</v>
+      </c>
+      <c r="E317" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="F317" s="1" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="318" ht="15" customHeight="1" spans="1:6">
+      <c r="A318" s="1"/>
+      <c r="B318" s="1">
+        <v>60010</v>
+      </c>
+      <c r="C318" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D318" s="1">
+        <v>7</v>
+      </c>
+      <c r="E318" s="1" t="s">
+        <v>649</v>
+      </c>
+      <c r="F318" s="1" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="319" ht="15" customHeight="1" spans="1:6">
+      <c r="A319" s="1"/>
+      <c r="B319" s="1">
+        <v>60011</v>
+      </c>
+      <c r="C319" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D319" s="1">
+        <v>7</v>
+      </c>
+      <c r="E319" s="1" t="s">
+        <v>651</v>
+      </c>
+      <c r="F319" s="1" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="320" ht="15" customHeight="1" spans="1:6">
+      <c r="A320" s="1"/>
+      <c r="B320" s="1">
+        <v>60012</v>
+      </c>
+      <c r="C320" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D320" s="1">
+        <v>7</v>
+      </c>
+      <c r="E320" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="F320" s="1" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="321" ht="15" customHeight="1" spans="1:6">
+      <c r="A321" s="1"/>
+      <c r="B321" s="1">
+        <v>60013</v>
+      </c>
+      <c r="C321" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D321" s="1">
+        <v>7</v>
+      </c>
+      <c r="E321" s="1" t="s">
+        <v>655</v>
+      </c>
+      <c r="F321" s="1" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="322" ht="15" customHeight="1" spans="1:6">
+      <c r="A322" s="1"/>
+      <c r="B322" s="1">
+        <v>60014</v>
+      </c>
+      <c r="C322" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D322" s="1">
+        <v>7</v>
+      </c>
+      <c r="E322" s="1" t="s">
+        <v>657</v>
+      </c>
+      <c r="F322" s="1" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="323" ht="15" customHeight="1" spans="1:6">
+      <c r="A323" s="1"/>
+      <c r="B323" s="1">
+        <v>60015</v>
+      </c>
+      <c r="C323" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D323" s="1">
+        <v>7</v>
+      </c>
+      <c r="E323" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="F323" s="1" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="324" ht="15" customHeight="1" spans="1:6">
+      <c r="A324" s="1"/>
+      <c r="B324" s="1">
+        <v>60016</v>
+      </c>
+      <c r="C324" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D324" s="1">
+        <v>7</v>
+      </c>
+      <c r="E324" s="1" t="s">
+        <v>661</v>
+      </c>
+      <c r="F324" s="1" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="325" ht="15" customHeight="1" spans="1:6">
+      <c r="A325" s="1"/>
+      <c r="B325" s="1">
+        <v>60017</v>
+      </c>
+      <c r="C325" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D325" s="1">
+        <v>7</v>
+      </c>
+      <c r="E325" s="1" t="s">
+        <v>663</v>
+      </c>
+      <c r="F325" s="1" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="326" ht="15" customHeight="1" spans="1:6">
+      <c r="A326" s="1"/>
+      <c r="B326" s="1">
+        <v>60018</v>
+      </c>
+      <c r="C326" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D326" s="1">
+        <v>7</v>
+      </c>
+      <c r="E326" s="1" t="s">
+        <v>665</v>
+      </c>
+      <c r="F326" s="1" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="327" ht="15" customHeight="1" spans="1:6">
+      <c r="A327" s="1"/>
+      <c r="B327" s="1">
+        <v>60019</v>
+      </c>
+      <c r="C327" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D327" s="1">
+        <v>7</v>
+      </c>
+      <c r="E327" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="F327" s="1" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="328" ht="15" customHeight="1" spans="1:6">
+      <c r="A328" s="1"/>
+      <c r="B328" s="1">
+        <v>60020</v>
+      </c>
+      <c r="C328" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D328" s="1">
+        <v>7</v>
+      </c>
+      <c r="E328" s="1" t="s">
+        <v>669</v>
+      </c>
+      <c r="F328" s="1" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="329" ht="15" customHeight="1" spans="1:6">
+      <c r="A329" s="1"/>
+      <c r="B329" s="1">
+        <v>60021</v>
+      </c>
+      <c r="C329" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D329" s="1">
+        <v>7</v>
+      </c>
+      <c r="E329" s="1" t="s">
+        <v>671</v>
+      </c>
+      <c r="F329" s="1" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="330" ht="15" customHeight="1" spans="1:6">
+      <c r="A330" s="1"/>
+      <c r="B330" s="1">
+        <v>60022</v>
+      </c>
+      <c r="C330" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D330" s="1">
+        <v>7</v>
+      </c>
+      <c r="E330" s="1" t="s">
+        <v>673</v>
+      </c>
+      <c r="F330" s="1" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="331" ht="15" customHeight="1" spans="1:6">
+      <c r="A331" s="1"/>
+      <c r="B331" s="1">
+        <v>60023</v>
+      </c>
+      <c r="C331" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D331" s="1">
+        <v>7</v>
+      </c>
+      <c r="E331" s="1" t="s">
+        <v>675</v>
+      </c>
+      <c r="F331" s="1" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="332" ht="15" customHeight="1" spans="1:6">
+      <c r="A332" s="1"/>
+      <c r="B332" s="1">
+        <v>60024</v>
+      </c>
+      <c r="C332" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D332" s="1">
+        <v>7</v>
+      </c>
+      <c r="E332" s="1" t="s">
+        <v>677</v>
+      </c>
+      <c r="F332" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="333" ht="15" customHeight="1" spans="1:6">
+      <c r="A333" s="1"/>
+      <c r="B333" s="1">
+        <v>60025</v>
+      </c>
+      <c r="C333" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D333" s="1">
+        <v>7</v>
+      </c>
+      <c r="E333" s="1" t="s">
+        <v>679</v>
+      </c>
+      <c r="F333" s="1" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="334" ht="15" customHeight="1" spans="1:6">
+      <c r="A334" s="1"/>
+      <c r="B334" s="1">
+        <v>60026</v>
+      </c>
+      <c r="C334" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D334" s="1">
+        <v>7</v>
+      </c>
+      <c r="E334" s="1" t="s">
+        <v>681</v>
+      </c>
+      <c r="F334" s="1" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="335" ht="15" customHeight="1" spans="1:6">
+      <c r="A335" s="1"/>
+      <c r="B335" s="1">
+        <v>60027</v>
+      </c>
+      <c r="C335" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D335" s="1">
+        <v>7</v>
+      </c>
+      <c r="E335" s="1" t="s">
+        <v>683</v>
+      </c>
+      <c r="F335" s="1" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="336" ht="15" customHeight="1" spans="1:6">
+      <c r="A336" s="1"/>
+      <c r="B336" s="1">
+        <v>60028</v>
+      </c>
+      <c r="C336" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D336" s="1">
+        <v>7</v>
+      </c>
+      <c r="E336" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="F336" s="1" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="337" ht="15" customHeight="1" spans="1:6">
+      <c r="A337" s="1"/>
+      <c r="B337" s="1">
+        <v>60029</v>
+      </c>
+      <c r="C337" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D337" s="1">
+        <v>7</v>
+      </c>
+      <c r="E337" s="1" t="s">
+        <v>687</v>
+      </c>
+      <c r="F337" s="1" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="338" ht="15" customHeight="1" spans="1:6">
+      <c r="A338" s="1"/>
+      <c r="B338" s="1">
+        <v>60030</v>
+      </c>
+      <c r="C338" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D338" s="1">
+        <v>7</v>
+      </c>
+      <c r="E338" s="1" t="s">
+        <v>689</v>
+      </c>
+      <c r="F338" s="1" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="339" ht="15" customHeight="1" spans="1:6">
+      <c r="A339" s="1"/>
+      <c r="B339" s="1">
+        <v>60031</v>
+      </c>
+      <c r="C339" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D339" s="1">
+        <v>7</v>
+      </c>
+      <c r="E339" s="1" t="s">
+        <v>691</v>
+      </c>
+      <c r="F339" s="1" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="340" ht="15" customHeight="1" spans="1:6">
+      <c r="A340" s="1"/>
+      <c r="B340" s="1">
+        <v>60032</v>
+      </c>
+      <c r="C340" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D340" s="1">
+        <v>7</v>
+      </c>
+      <c r="E340" s="1" t="s">
+        <v>693</v>
+      </c>
+      <c r="F340" s="1" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="341" ht="15" customHeight="1" spans="1:6">
+      <c r="A341" s="1"/>
+      <c r="B341" s="1">
+        <v>60033</v>
+      </c>
+      <c r="C341" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D341" s="1">
+        <v>7</v>
+      </c>
+      <c r="E341" s="1" t="s">
+        <v>695</v>
+      </c>
+      <c r="F341" s="1" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="342" ht="15" customHeight="1" spans="1:6">
+      <c r="A342" s="1"/>
+      <c r="B342" s="1">
+        <v>60034</v>
+      </c>
+      <c r="C342" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D342" s="1">
+        <v>7</v>
+      </c>
+      <c r="E342" s="1" t="s">
+        <v>697</v>
+      </c>
+      <c r="F342" s="1" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="343" ht="15" customHeight="1" spans="1:6">
+      <c r="A343" s="1"/>
+      <c r="B343" s="1">
+        <v>60035</v>
+      </c>
+      <c r="C343" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D343" s="1">
+        <v>7</v>
+      </c>
+      <c r="E343" s="1" t="s">
+        <v>699</v>
+      </c>
+      <c r="F343" s="1" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="344" ht="15" customHeight="1" spans="1:6">
+      <c r="A344" s="1"/>
+      <c r="B344" s="1">
+        <v>60036</v>
+      </c>
+      <c r="C344" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D344" s="1">
+        <v>7</v>
+      </c>
+      <c r="E344" s="1" t="s">
+        <v>701</v>
+      </c>
+      <c r="F344" s="1" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="345" ht="15" customHeight="1" spans="1:6">
+      <c r="A345" s="1"/>
+      <c r="B345" s="1">
+        <v>60037</v>
+      </c>
+      <c r="C345" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D345" s="1">
+        <v>7</v>
+      </c>
+      <c r="E345" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="F345" s="1" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="346" ht="15" customHeight="1" spans="1:6">
+      <c r="A346" s="1"/>
+      <c r="B346" s="1">
+        <v>60038</v>
+      </c>
+      <c r="C346" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D346" s="1">
+        <v>7</v>
+      </c>
+      <c r="E346" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="F346" s="1" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="347" ht="15" customHeight="1" spans="1:6">
+      <c r="A347" s="1"/>
+      <c r="B347" s="1">
+        <v>60039</v>
+      </c>
+      <c r="C347" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D347" s="1">
+        <v>7</v>
+      </c>
+      <c r="E347" s="1" t="s">
+        <v>707</v>
+      </c>
+      <c r="F347" s="1" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="348" ht="15" customHeight="1" spans="1:6">
+      <c r="A348" s="1"/>
+      <c r="B348" s="1">
+        <v>60040</v>
+      </c>
+      <c r="C348" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D348" s="1">
+        <v>7</v>
+      </c>
+      <c r="E348" s="1" t="s">
+        <v>709</v>
+      </c>
+      <c r="F348" s="1" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="349" ht="15" customHeight="1" spans="1:6">
+      <c r="A349" s="1"/>
+      <c r="B349" s="1">
+        <v>60041</v>
+      </c>
+      <c r="C349" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D349" s="1">
+        <v>7</v>
+      </c>
+      <c r="E349" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="F349" s="1" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="350" ht="15" customHeight="1" spans="1:6">
+      <c r="A350" s="1"/>
+      <c r="B350" s="1">
+        <v>60042</v>
+      </c>
+      <c r="C350" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D350" s="1">
+        <v>7</v>
+      </c>
+      <c r="E350" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="F350" s="1" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="351" ht="15" customHeight="1" spans="1:6">
+      <c r="A351" s="1"/>
+      <c r="B351" s="1">
+        <v>60043</v>
+      </c>
+      <c r="C351" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D351" s="1">
+        <v>7</v>
+      </c>
+      <c r="E351" s="1" t="s">
+        <v>715</v>
+      </c>
+      <c r="F351" s="1" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="352" ht="15" customHeight="1" spans="1:6">
+      <c r="A352" s="1"/>
+      <c r="B352" s="1">
+        <v>60044</v>
+      </c>
+      <c r="C352" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D352" s="1">
+        <v>7</v>
+      </c>
+      <c r="E352" s="1" t="s">
+        <v>717</v>
+      </c>
+      <c r="F352" s="1" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="353" ht="15" customHeight="1" spans="1:6">
+      <c r="A353" s="1"/>
+      <c r="B353" s="1">
+        <v>60045</v>
+      </c>
+      <c r="C353" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D353" s="1">
+        <v>7</v>
+      </c>
+      <c r="E353" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="F353" s="1" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="354" ht="15" customHeight="1" spans="1:6">
+      <c r="A354" s="1"/>
+      <c r="B354" s="1">
+        <v>60046</v>
+      </c>
+      <c r="C354" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D354" s="1">
+        <v>7</v>
+      </c>
+      <c r="E354" s="1" t="s">
+        <v>721</v>
+      </c>
+      <c r="F354" s="1" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="355" ht="15" customHeight="1" spans="1:6">
+      <c r="A355" s="1"/>
+      <c r="B355" s="1">
+        <v>60047</v>
+      </c>
+      <c r="C355" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D355" s="1">
+        <v>7</v>
+      </c>
+      <c r="E355" s="1" t="s">
+        <v>723</v>
+      </c>
+      <c r="F355" s="1" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="356" ht="15" customHeight="1" spans="1:6">
+      <c r="A356" s="1"/>
+      <c r="B356" s="1">
+        <v>60048</v>
+      </c>
+      <c r="C356" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D356" s="1">
+        <v>7</v>
+      </c>
+      <c r="E356" s="1" t="s">
+        <v>725</v>
+      </c>
+      <c r="F356" s="1" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="357" ht="15" customHeight="1" spans="1:6">
+      <c r="A357" s="1"/>
+      <c r="B357" s="1">
+        <v>60049</v>
+      </c>
+      <c r="C357" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D357" s="1">
+        <v>7</v>
+      </c>
+      <c r="E357" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="F357" s="1" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="358" ht="15" customHeight="1" spans="1:6">
+      <c r="A358" s="1"/>
+      <c r="B358" s="1">
+        <v>60050</v>
+      </c>
+      <c r="C358" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D358" s="1">
+        <v>7</v>
+      </c>
+      <c r="E358" s="1" t="s">
+        <v>729</v>
+      </c>
+      <c r="F358" s="1" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="359" ht="15" customHeight="1" spans="1:6">
+      <c r="A359" s="1"/>
+      <c r="B359" s="1">
+        <v>60051</v>
+      </c>
+      <c r="C359" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D359" s="1">
+        <v>7</v>
+      </c>
+      <c r="E359" s="1" t="s">
+        <v>731</v>
+      </c>
+      <c r="F359" s="1" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="360" ht="15" customHeight="1" spans="1:6">
+      <c r="A360" s="1"/>
+      <c r="B360" s="1">
+        <v>60052</v>
+      </c>
+      <c r="C360" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D360" s="1">
+        <v>7</v>
+      </c>
+      <c r="E360" s="1" t="s">
+        <v>733</v>
+      </c>
+      <c r="F360" s="1" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="361" ht="15" customHeight="1" spans="1:6">
+      <c r="A361" s="1"/>
+      <c r="B361" s="1">
+        <v>60053</v>
+      </c>
+      <c r="C361" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D361" s="1">
+        <v>7</v>
+      </c>
+      <c r="E361" s="1" t="s">
+        <v>735</v>
+      </c>
+      <c r="F361" s="1" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="362" ht="15" customHeight="1" spans="1:6">
+      <c r="A362" s="1"/>
+      <c r="B362" s="1">
+        <v>60054</v>
+      </c>
+      <c r="C362" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D362" s="1">
+        <v>7</v>
+      </c>
+      <c r="E362" s="1" t="s">
+        <v>737</v>
+      </c>
+      <c r="F362" s="1" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="363" ht="15" customHeight="1" spans="1:6">
+      <c r="A363" s="1"/>
+      <c r="B363" s="1">
+        <v>60055</v>
+      </c>
+      <c r="C363" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D363" s="1">
+        <v>7</v>
+      </c>
+      <c r="E363" s="1" t="s">
+        <v>739</v>
+      </c>
+      <c r="F363" s="1" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="364" ht="15" customHeight="1" spans="1:6">
+      <c r="A364" s="1"/>
+      <c r="B364" s="1">
+        <v>60056</v>
+      </c>
+      <c r="C364" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D364" s="1">
+        <v>7</v>
+      </c>
+      <c r="E364" s="1" t="s">
+        <v>741</v>
+      </c>
+      <c r="F364" s="1" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="365" ht="15" customHeight="1" spans="1:6">
+      <c r="A365" s="1"/>
+      <c r="B365" s="1">
+        <v>60057</v>
+      </c>
+      <c r="C365" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D365" s="1">
+        <v>7</v>
+      </c>
+      <c r="E365" s="1" t="s">
+        <v>743</v>
+      </c>
+      <c r="F365" s="1" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="366" ht="15" customHeight="1" spans="1:6">
+      <c r="A366" s="1"/>
+      <c r="B366" s="1">
+        <v>60058</v>
+      </c>
+      <c r="C366" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D366" s="1">
+        <v>7</v>
+      </c>
+      <c r="E366" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="F366" s="1" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="367" ht="15" customHeight="1" spans="1:6">
+      <c r="A367" s="1"/>
+      <c r="B367" s="1">
+        <v>60059</v>
+      </c>
+      <c r="C367" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D367" s="1">
+        <v>7</v>
+      </c>
+      <c r="E367" s="1" t="s">
+        <v>747</v>
+      </c>
+      <c r="F367" s="1" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="368" ht="15" customHeight="1" spans="1:6">
+      <c r="A368" s="1"/>
+      <c r="B368" s="1">
+        <v>60060</v>
+      </c>
+      <c r="C368" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D368" s="1">
+        <v>7</v>
+      </c>
+      <c r="E368" s="1" t="s">
+        <v>749</v>
+      </c>
+      <c r="F368" s="1" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="369" ht="15" customHeight="1" spans="1:6">
+      <c r="A369" s="1"/>
+      <c r="B369" s="1">
+        <v>60061</v>
+      </c>
+      <c r="C369" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D369" s="1">
+        <v>7</v>
+      </c>
+      <c r="E369" s="1" t="s">
+        <v>751</v>
+      </c>
+      <c r="F369" s="1" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="370" ht="15" customHeight="1" spans="1:6">
+      <c r="A370" s="1"/>
+      <c r="B370" s="1">
+        <v>60062</v>
+      </c>
+      <c r="C370" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D370" s="1">
+        <v>7</v>
+      </c>
+      <c r="E370" s="1" t="s">
+        <v>753</v>
+      </c>
+      <c r="F370" s="1" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="371" ht="15" customHeight="1" spans="1:6">
+      <c r="A371" s="1"/>
+      <c r="B371" s="1">
+        <v>60063</v>
+      </c>
+      <c r="C371" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D371" s="1">
+        <v>7</v>
+      </c>
+      <c r="E371" s="1" t="s">
+        <v>755</v>
+      </c>
+      <c r="F371" s="1" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="372" ht="15" customHeight="1" spans="1:6">
+      <c r="A372" s="1"/>
+      <c r="B372" s="1">
+        <v>60064</v>
+      </c>
+      <c r="C372" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D372" s="1">
+        <v>7</v>
+      </c>
+      <c r="E372" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="F372" s="1" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="373" ht="15" customHeight="1" spans="1:6">
+      <c r="A373" s="1"/>
+      <c r="B373" s="1">
+        <v>60065</v>
+      </c>
+      <c r="C373" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D373" s="1">
+        <v>7</v>
+      </c>
+      <c r="E373" s="1" t="s">
+        <v>759</v>
+      </c>
+      <c r="F373" s="1" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="374" ht="15" customHeight="1" spans="1:6">
+      <c r="A374" s="1"/>
+      <c r="B374" s="1">
+        <v>60066</v>
+      </c>
+      <c r="C374" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D374" s="1">
+        <v>7</v>
+      </c>
+      <c r="E374" s="1" t="s">
+        <v>761</v>
+      </c>
+      <c r="F374" s="1" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="375" ht="15" customHeight="1" spans="1:6">
+      <c r="A375" s="1"/>
+      <c r="B375" s="1">
+        <v>60067</v>
+      </c>
+      <c r="C375" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D375" s="1">
+        <v>7</v>
+      </c>
+      <c r="E375" s="1" t="s">
+        <v>763</v>
+      </c>
+      <c r="F375" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="376" ht="15" customHeight="1" spans="1:6">
+      <c r="A376" s="1"/>
+      <c r="B376" s="1">
+        <v>60068</v>
+      </c>
+      <c r="C376" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D376" s="1">
+        <v>7</v>
+      </c>
+      <c r="E376" s="1" t="s">
+        <v>765</v>
+      </c>
+      <c r="F376" s="1" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="377" ht="15" customHeight="1" spans="1:6">
+      <c r="A377" s="1"/>
+      <c r="B377" s="1">
+        <v>60069</v>
+      </c>
+      <c r="C377" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D377" s="1">
+        <v>7</v>
+      </c>
+      <c r="E377" s="1" t="s">
+        <v>767</v>
+      </c>
+      <c r="F377" s="1" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="378" ht="15" customHeight="1" spans="1:6">
+      <c r="A378" s="1"/>
+      <c r="B378" s="1">
+        <v>60070</v>
+      </c>
+      <c r="C378" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D378" s="1">
+        <v>7</v>
+      </c>
+      <c r="E378" s="1" t="s">
+        <v>769</v>
+      </c>
+      <c r="F378" s="1" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="379" ht="15" customHeight="1" spans="1:6">
+      <c r="A379" s="1"/>
+      <c r="B379" s="1">
+        <v>60071</v>
+      </c>
+      <c r="C379" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D379" s="1">
+        <v>7</v>
+      </c>
+      <c r="E379" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="F379" s="1" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="380" ht="15" customHeight="1" spans="1:6">
+      <c r="A380" s="1"/>
+      <c r="B380" s="1">
+        <v>60072</v>
+      </c>
+      <c r="C380" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D380" s="1">
+        <v>7</v>
+      </c>
+      <c r="E380" s="1" t="s">
+        <v>773</v>
+      </c>
+      <c r="F380" s="1" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="381" ht="15" customHeight="1" spans="1:6">
+      <c r="A381" s="1"/>
+      <c r="B381" s="1">
+        <v>60073</v>
+      </c>
+      <c r="C381" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D381" s="1">
+        <v>7</v>
+      </c>
+      <c r="E381" s="1" t="s">
+        <v>775</v>
+      </c>
+      <c r="F381" s="1" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="382" ht="15" customHeight="1" spans="1:6">
+      <c r="A382" s="1"/>
+      <c r="B382" s="1">
+        <v>60074</v>
+      </c>
+      <c r="C382" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D382" s="1">
+        <v>7</v>
+      </c>
+      <c r="E382" s="1" t="s">
+        <v>777</v>
+      </c>
+      <c r="F382" s="1" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="383" ht="15" customHeight="1" spans="1:6">
+      <c r="A383" s="1"/>
+      <c r="B383" s="1">
+        <v>60075</v>
+      </c>
+      <c r="C383" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D383" s="1">
+        <v>7</v>
+      </c>
+      <c r="E383" s="1" t="s">
+        <v>779</v>
+      </c>
+      <c r="F383" s="1" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="384" ht="15" customHeight="1" spans="1:6">
+      <c r="A384" s="1"/>
+      <c r="B384" s="1">
+        <v>60076</v>
+      </c>
+      <c r="C384" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D384" s="1">
+        <v>7</v>
+      </c>
+      <c r="E384" s="1" t="s">
+        <v>781</v>
+      </c>
+      <c r="F384" s="1" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="385" ht="15" customHeight="1" spans="1:6">
+      <c r="A385" s="1"/>
+      <c r="B385" s="1">
+        <v>60077</v>
+      </c>
+      <c r="C385" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D385" s="1">
+        <v>7</v>
+      </c>
+      <c r="E385" s="1" t="s">
+        <v>783</v>
+      </c>
+      <c r="F385" s="1" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="386" ht="15" customHeight="1" spans="1:6">
+      <c r="A386" s="1"/>
+      <c r="B386" s="1">
+        <v>60078</v>
+      </c>
+      <c r="C386" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D386" s="1">
+        <v>7</v>
+      </c>
+      <c r="E386" s="1" t="s">
+        <v>785</v>
+      </c>
+      <c r="F386" s="1" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="387" ht="15" customHeight="1" spans="1:6">
+      <c r="A387" s="1"/>
+      <c r="B387" s="1">
+        <v>60079</v>
+      </c>
+      <c r="C387" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D387" s="1">
+        <v>7</v>
+      </c>
+      <c r="E387" s="1" t="s">
+        <v>787</v>
+      </c>
+      <c r="F387" s="1" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="388" ht="15" customHeight="1" spans="1:6">
+      <c r="A388" s="1"/>
+      <c r="B388" s="1">
+        <v>60080</v>
+      </c>
+      <c r="C388" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D388" s="1">
+        <v>7</v>
+      </c>
+      <c r="E388" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="F388" s="1" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="389" ht="15" customHeight="1" spans="1:6">
+      <c r="A389" s="1"/>
+      <c r="B389" s="1">
+        <v>60081</v>
+      </c>
+      <c r="C389" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D389" s="1">
+        <v>7</v>
+      </c>
+      <c r="E389" s="1" t="s">
+        <v>791</v>
+      </c>
+      <c r="F389" s="1" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="390" ht="15" customHeight="1" spans="1:6">
+      <c r="A390" s="1"/>
+      <c r="B390" s="1">
+        <v>60082</v>
+      </c>
+      <c r="C390" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D390" s="1">
+        <v>7</v>
+      </c>
+      <c r="E390" s="1" t="s">
+        <v>793</v>
+      </c>
+      <c r="F390" s="1" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="391" ht="15" customHeight="1" spans="1:6">
+      <c r="A391" s="1"/>
+      <c r="B391" s="1">
+        <v>60083</v>
+      </c>
+      <c r="C391" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="D391" s="1">
+        <v>7</v>
+      </c>
+      <c r="E391" s="1" t="s">
+        <v>795</v>
+      </c>
+      <c r="F391" s="1" t="s">
+        <v>796</v>
       </c>
     </row>
   </sheetData>
-  <sortState ref="B5:F312">
-    <sortCondition ref="B5:B312"/>
+  <sortState ref="B5:F391">
+    <sortCondition ref="B5:B391"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/AAAGameData/DataTables/ResourceConfigTable.xlsx
+++ b/AAAGameData/DataTables/ResourceConfigTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="14855"/>
+    <workbookView windowWidth="28800" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1006" uniqueCount="804">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1013" uniqueCount="808">
   <si>
     <t>#</t>
   </si>
@@ -110,6 +110,18 @@
     <t>战斗预设界面，新增预设</t>
   </si>
   <si>
+    <t>UI/Combat/SneakAttack.png</t>
+  </si>
+  <si>
+    <t>探索阶段-偷袭图标</t>
+  </si>
+  <si>
+    <t>UI/Combat/Encounter.png</t>
+  </si>
+  <si>
+    <t>探索阶段-遭遇战图标</t>
+  </si>
+  <si>
     <t>UI/Items/Gold.png</t>
   </si>
   <si>
@@ -452,13 +464,22 @@
     <t>爆裂弹-角色技能图标</t>
   </si>
   <si>
-    <t>ResourceConfigTable使用|资源暂不存在</t>
-  </si>
-  <si>
-    <t>Equipment/SunsetBow.png</t>
-  </si>
-  <si>
-    <t>落日弓-棋子装备图标</t>
+    <t>Chess/邪灵/邪灵头像.png</t>
+  </si>
+  <si>
+    <t>邪灵-敌人头像</t>
+  </si>
+  <si>
+    <t>Chess/恶魂/恶魂头像.png</t>
+  </si>
+  <si>
+    <t>恶魂-敌人头像</t>
+  </si>
+  <si>
+    <t>Chess/黑暗杨戬/黑暗杨戬头像.png</t>
+  </si>
+  <si>
+    <t>黑暗杨戬-敌人头像</t>
   </si>
   <si>
     <t>Summoner/Skill/狂怒之心技能.png</t>
@@ -1304,19 +1325,10 @@
     <t>棋子嫦娥头像</t>
   </si>
   <si>
-    <t>Chess/邪灵/邪灵头像.png</t>
-  </si>
-  <si>
     <t>棋子邪灵头像</t>
   </si>
   <si>
-    <t>Chess/恶魂/恶魂头像.png</t>
-  </si>
-  <si>
     <t>棋子恶魂头像</t>
-  </si>
-  <si>
-    <t>Chess/黑暗杨戬/黑暗杨戬头像.png</t>
   </si>
   <si>
     <t>棋子黑暗杨戬头像</t>
@@ -3403,8 +3415,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F394"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <dimension ref="A1:F398"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="21" customWidth="1"/>
@@ -3461,7 +3473,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" ht="86.4" spans="1:6">
+    <row r="4" ht="81" spans="1:6">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -3596,7 +3608,7 @@
     <row r="12" ht="15" customHeight="1" spans="1:6">
       <c r="A12" s="1"/>
       <c r="B12" s="1">
-        <v>1101</v>
+        <v>1008</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1">
@@ -3612,7 +3624,7 @@
     <row r="13" ht="15" customHeight="1" spans="1:6">
       <c r="A13" s="1"/>
       <c r="B13" s="1">
-        <v>1102</v>
+        <v>1009</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1">
@@ -3628,7 +3640,7 @@
     <row r="14" ht="15" customHeight="1" spans="1:6">
       <c r="A14" s="1"/>
       <c r="B14" s="1">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1">
@@ -3644,7 +3656,7 @@
     <row r="15" ht="15" customHeight="1" spans="1:6">
       <c r="A15" s="1"/>
       <c r="B15" s="1">
-        <v>1104</v>
+        <v>1102</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1">
@@ -3660,7 +3672,7 @@
     <row r="16" ht="15" customHeight="1" spans="1:6">
       <c r="A16" s="1"/>
       <c r="B16" s="1">
-        <v>1105</v>
+        <v>1103</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1">
@@ -3676,7 +3688,7 @@
     <row r="17" ht="15" customHeight="1" spans="1:6">
       <c r="A17" s="1"/>
       <c r="B17" s="1">
-        <v>1106</v>
+        <v>1104</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="1">
@@ -3692,7 +3704,7 @@
     <row r="18" ht="15" customHeight="1" spans="1:6">
       <c r="A18" s="1"/>
       <c r="B18" s="1">
-        <v>1107</v>
+        <v>1105</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="1">
@@ -3708,7 +3720,7 @@
     <row r="19" ht="15" customHeight="1" spans="1:6">
       <c r="A19" s="1"/>
       <c r="B19" s="1">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="1">
@@ -3724,7 +3736,7 @@
     <row r="20" ht="15" customHeight="1" spans="1:6">
       <c r="A20" s="1"/>
       <c r="B20" s="1">
-        <v>1155</v>
+        <v>1107</v>
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="1">
@@ -3740,7 +3752,7 @@
     <row r="21" ht="15" customHeight="1" spans="1:6">
       <c r="A21" s="1"/>
       <c r="B21" s="1">
-        <v>1156</v>
+        <v>1108</v>
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="1">
@@ -3756,7 +3768,7 @@
     <row r="22" ht="15" customHeight="1" spans="1:6">
       <c r="A22" s="1"/>
       <c r="B22" s="1">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="C22" s="1"/>
       <c r="D22" s="1">
@@ -3772,7 +3784,7 @@
     <row r="23" ht="15" customHeight="1" spans="1:6">
       <c r="A23" s="1"/>
       <c r="B23" s="1">
-        <v>1158</v>
+        <v>1156</v>
       </c>
       <c r="C23" s="1"/>
       <c r="D23" s="1">
@@ -3788,7 +3800,7 @@
     <row r="24" ht="15" customHeight="1" spans="1:6">
       <c r="A24" s="1"/>
       <c r="B24" s="1">
-        <v>1201</v>
+        <v>1157</v>
       </c>
       <c r="C24" s="1"/>
       <c r="D24" s="1">
@@ -3804,7 +3816,7 @@
     <row r="25" ht="15" customHeight="1" spans="1:6">
       <c r="A25" s="1"/>
       <c r="B25" s="1">
-        <v>1202</v>
+        <v>1158</v>
       </c>
       <c r="C25" s="1"/>
       <c r="D25" s="1">
@@ -3820,7 +3832,7 @@
     <row r="26" ht="15" customHeight="1" spans="1:6">
       <c r="A26" s="1"/>
       <c r="B26" s="1">
-        <v>1203</v>
+        <v>1201</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="1">
@@ -3836,7 +3848,7 @@
     <row r="27" ht="15" customHeight="1" spans="1:6">
       <c r="A27" s="1"/>
       <c r="B27" s="1">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="1">
@@ -3852,7 +3864,7 @@
     <row r="28" ht="15" customHeight="1" spans="1:6">
       <c r="A28" s="1"/>
       <c r="B28" s="1">
-        <v>1205</v>
+        <v>1203</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="1">
@@ -3868,7 +3880,7 @@
     <row r="29" ht="15" customHeight="1" spans="1:6">
       <c r="A29" s="1"/>
       <c r="B29" s="1">
-        <v>1206</v>
+        <v>1204</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="1">
@@ -3884,7 +3896,7 @@
     <row r="30" ht="15" customHeight="1" spans="1:6">
       <c r="A30" s="1"/>
       <c r="B30" s="1">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="C30" s="1"/>
       <c r="D30" s="1">
@@ -3900,7 +3912,7 @@
     <row r="31" ht="15" customHeight="1" spans="1:6">
       <c r="A31" s="1"/>
       <c r="B31" s="1">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="1">
@@ -3916,7 +3928,7 @@
     <row r="32" ht="15" customHeight="1" spans="1:6">
       <c r="A32" s="1"/>
       <c r="B32" s="1">
-        <v>1209</v>
+        <v>1207</v>
       </c>
       <c r="C32" s="1"/>
       <c r="D32" s="1">
@@ -3932,7 +3944,7 @@
     <row r="33" ht="15" customHeight="1" spans="1:6">
       <c r="A33" s="1"/>
       <c r="B33" s="1">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="1">
@@ -3948,7 +3960,7 @@
     <row r="34" ht="15" customHeight="1" spans="1:6">
       <c r="A34" s="1"/>
       <c r="B34" s="1">
-        <v>1211</v>
+        <v>1209</v>
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="1">
@@ -3964,7 +3976,7 @@
     <row r="35" ht="15" customHeight="1" spans="1:6">
       <c r="A35" s="1"/>
       <c r="B35" s="1">
-        <v>1212</v>
+        <v>1210</v>
       </c>
       <c r="C35" s="1"/>
       <c r="D35" s="1">
@@ -3980,7 +3992,7 @@
     <row r="36" ht="15" customHeight="1" spans="1:6">
       <c r="A36" s="1"/>
       <c r="B36" s="1">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1">
@@ -3996,7 +4008,7 @@
     <row r="37" ht="15" customHeight="1" spans="1:6">
       <c r="A37" s="1"/>
       <c r="B37" s="1">
-        <v>1214</v>
+        <v>1212</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1">
@@ -4012,7 +4024,7 @@
     <row r="38" ht="15" customHeight="1" spans="1:6">
       <c r="A38" s="1"/>
       <c r="B38" s="1">
-        <v>1215</v>
+        <v>1213</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1">
@@ -4028,7 +4040,7 @@
     <row r="39" ht="15" customHeight="1" spans="1:6">
       <c r="A39" s="1"/>
       <c r="B39" s="1">
-        <v>1216</v>
+        <v>1214</v>
       </c>
       <c r="C39" s="1"/>
       <c r="D39" s="1">
@@ -4044,7 +4056,7 @@
     <row r="40" ht="15" customHeight="1" spans="1:6">
       <c r="A40" s="1"/>
       <c r="B40" s="1">
-        <v>1217</v>
+        <v>1215</v>
       </c>
       <c r="C40" s="1"/>
       <c r="D40" s="1">
@@ -4060,7 +4072,7 @@
     <row r="41" ht="15" customHeight="1" spans="1:6">
       <c r="A41" s="1"/>
       <c r="B41" s="1">
-        <v>1218</v>
+        <v>1216</v>
       </c>
       <c r="C41" s="1"/>
       <c r="D41" s="1">
@@ -4076,7 +4088,7 @@
     <row r="42" ht="15" customHeight="1" spans="1:6">
       <c r="A42" s="1"/>
       <c r="B42" s="1">
-        <v>1219</v>
+        <v>1217</v>
       </c>
       <c r="C42" s="1"/>
       <c r="D42" s="1">
@@ -4092,7 +4104,7 @@
     <row r="43" ht="15" customHeight="1" spans="1:6">
       <c r="A43" s="1"/>
       <c r="B43" s="1">
-        <v>1220</v>
+        <v>1218</v>
       </c>
       <c r="C43" s="1"/>
       <c r="D43" s="1">
@@ -4108,7 +4120,7 @@
     <row r="44" ht="15" customHeight="1" spans="1:6">
       <c r="A44" s="1"/>
       <c r="B44" s="1">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="C44" s="1"/>
       <c r="D44" s="1">
@@ -4124,7 +4136,7 @@
     <row r="45" ht="15" customHeight="1" spans="1:6">
       <c r="A45" s="1"/>
       <c r="B45" s="1">
-        <v>1222</v>
+        <v>1220</v>
       </c>
       <c r="C45" s="1"/>
       <c r="D45" s="1">
@@ -4140,7 +4152,7 @@
     <row r="46" ht="15" customHeight="1" spans="1:6">
       <c r="A46" s="1"/>
       <c r="B46" s="1">
-        <v>1223</v>
+        <v>1221</v>
       </c>
       <c r="C46" s="1"/>
       <c r="D46" s="1">
@@ -4156,7 +4168,7 @@
     <row r="47" ht="15" customHeight="1" spans="1:6">
       <c r="A47" s="1"/>
       <c r="B47" s="1">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="C47" s="1"/>
       <c r="D47" s="1">
@@ -4172,7 +4184,7 @@
     <row r="48" ht="15" customHeight="1" spans="1:6">
       <c r="A48" s="1"/>
       <c r="B48" s="1">
-        <v>1225</v>
+        <v>1223</v>
       </c>
       <c r="C48" s="1"/>
       <c r="D48" s="1">
@@ -4188,7 +4200,7 @@
     <row r="49" ht="15" customHeight="1" spans="1:6">
       <c r="A49" s="1"/>
       <c r="B49" s="1">
-        <v>1301</v>
+        <v>1224</v>
       </c>
       <c r="C49" s="1"/>
       <c r="D49" s="1">
@@ -4204,7 +4216,7 @@
     <row r="50" ht="15" customHeight="1" spans="1:6">
       <c r="A50" s="1"/>
       <c r="B50" s="1">
-        <v>1304</v>
+        <v>1225</v>
       </c>
       <c r="C50" s="1"/>
       <c r="D50" s="1">
@@ -4220,45 +4232,43 @@
     <row r="51" ht="15" customHeight="1" spans="1:6">
       <c r="A51" s="1"/>
       <c r="B51" s="1">
-        <v>1310</v>
-      </c>
-      <c r="C51" s="1" t="s">
+        <v>1301</v>
+      </c>
+      <c r="C51" s="1"/>
+      <c r="D51" s="1">
+        <v>1</v>
+      </c>
+      <c r="E51" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="D51" s="1">
-        <v>1</v>
-      </c>
-      <c r="E51" s="1" t="s">
+      <c r="F51" s="1" t="s">
         <v>106</v>
-      </c>
-      <c r="F51" s="1" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1" spans="1:6">
       <c r="A52" s="1"/>
       <c r="B52" s="1">
-        <v>1311</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>105</v>
-      </c>
+        <v>1304</v>
+      </c>
+      <c r="C52" s="1"/>
       <c r="D52" s="1">
         <v>1</v>
       </c>
       <c r="E52" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F52" s="1" t="s">
         <v>108</v>
-      </c>
-      <c r="F52" s="1" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="53" ht="15" customHeight="1" spans="1:6">
       <c r="A53" s="1"/>
       <c r="B53" s="1">
-        <v>1399</v>
-      </c>
-      <c r="C53" s="1"/>
+        <v>1310</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>109</v>
+      </c>
       <c r="D53" s="1">
         <v>1</v>
       </c>
@@ -4272,9 +4282,11 @@
     <row r="54" ht="15" customHeight="1" spans="1:6">
       <c r="A54" s="1"/>
       <c r="B54" s="1">
-        <v>1401</v>
-      </c>
-      <c r="C54" s="1"/>
+        <v>1311</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>109</v>
+      </c>
       <c r="D54" s="1">
         <v>1</v>
       </c>
@@ -4288,7 +4300,7 @@
     <row r="55" ht="15" customHeight="1" spans="1:6">
       <c r="A55" s="1"/>
       <c r="B55" s="1">
-        <v>1402</v>
+        <v>1399</v>
       </c>
       <c r="C55" s="1"/>
       <c r="D55" s="1">
@@ -4304,7 +4316,7 @@
     <row r="56" ht="15" customHeight="1" spans="1:6">
       <c r="A56" s="1"/>
       <c r="B56" s="1">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="C56" s="1"/>
       <c r="D56" s="1">
@@ -4320,7 +4332,7 @@
     <row r="57" ht="15" customHeight="1" spans="1:6">
       <c r="A57" s="1"/>
       <c r="B57" s="1">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="C57" s="1"/>
       <c r="D57" s="1">
@@ -4336,7 +4348,7 @@
     <row r="58" ht="15" customHeight="1" spans="1:6">
       <c r="A58" s="1"/>
       <c r="B58" s="1">
-        <v>1405</v>
+        <v>1403</v>
       </c>
       <c r="C58" s="1"/>
       <c r="D58" s="1">
@@ -4352,7 +4364,7 @@
     <row r="59" ht="15" customHeight="1" spans="1:6">
       <c r="A59" s="1"/>
       <c r="B59" s="1">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="C59" s="1"/>
       <c r="D59" s="1">
@@ -4368,46 +4380,42 @@
     <row r="60" ht="15" customHeight="1" spans="1:6">
       <c r="A60" s="1"/>
       <c r="B60" s="1">
-        <v>1407</v>
-      </c>
-      <c r="C60" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="C60" s="1"/>
+      <c r="D60" s="1">
+        <v>1</v>
+      </c>
+      <c r="E60" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="D60" s="1">
-        <v>1</v>
-      </c>
-      <c r="E60" s="1" t="s">
+      <c r="F60" s="1" t="s">
         <v>125</v>
-      </c>
-      <c r="F60" s="1" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="61" ht="15" customHeight="1" spans="1:6">
       <c r="A61" s="1"/>
       <c r="B61" s="1">
-        <v>1408</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>124</v>
-      </c>
+        <v>1406</v>
+      </c>
+      <c r="C61" s="1"/>
       <c r="D61" s="1">
         <v>1</v>
       </c>
       <c r="E61" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="F61" s="1" t="s">
         <v>127</v>
-      </c>
-      <c r="F61" s="1" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="62" ht="15" customHeight="1" spans="1:6">
       <c r="A62" s="1"/>
       <c r="B62" s="1">
-        <v>1409</v>
+        <v>1407</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D62" s="1">
         <v>1</v>
@@ -4422,10 +4430,10 @@
     <row r="63" ht="15" customHeight="1" spans="1:6">
       <c r="A63" s="1"/>
       <c r="B63" s="1">
-        <v>1410</v>
+        <v>1408</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D63" s="1">
         <v>1</v>
@@ -4440,10 +4448,10 @@
     <row r="64" ht="15" customHeight="1" spans="1:6">
       <c r="A64" s="1"/>
       <c r="B64" s="1">
-        <v>1411</v>
+        <v>1409</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D64" s="1">
         <v>1</v>
@@ -4458,9 +4466,11 @@
     <row r="65" ht="15" customHeight="1" spans="1:6">
       <c r="A65" s="1"/>
       <c r="B65" s="1">
-        <v>1501</v>
-      </c>
-      <c r="C65" s="1"/>
+        <v>1410</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="D65" s="1">
         <v>1</v>
       </c>
@@ -4474,9 +4484,11 @@
     <row r="66" ht="15" customHeight="1" spans="1:6">
       <c r="A66" s="1"/>
       <c r="B66" s="1">
-        <v>1502</v>
-      </c>
-      <c r="C66" s="1"/>
+        <v>1411</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="D66" s="1">
         <v>1</v>
       </c>
@@ -4490,7 +4502,7 @@
     <row r="67" ht="15" customHeight="1" spans="1:6">
       <c r="A67" s="1"/>
       <c r="B67" s="1">
-        <v>1503</v>
+        <v>1501</v>
       </c>
       <c r="C67" s="1"/>
       <c r="D67" s="1">
@@ -4506,1451 +4518,1445 @@
     <row r="68" ht="15" customHeight="1" spans="1:6">
       <c r="A68" s="1"/>
       <c r="B68" s="1">
-        <v>1601</v>
-      </c>
-      <c r="C68" s="1" t="s">
+        <v>1502</v>
+      </c>
+      <c r="C68" s="1"/>
+      <c r="D68" s="1">
+        <v>1</v>
+      </c>
+      <c r="E68" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="D68" s="1">
-        <v>1</v>
-      </c>
-      <c r="E68" s="1" t="s">
+      <c r="F68" s="1" t="s">
         <v>142</v>
-      </c>
-      <c r="F68" s="1" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" spans="1:6">
       <c r="A69" s="1"/>
       <c r="B69" s="1">
-        <v>1701</v>
+        <v>1503</v>
       </c>
       <c r="C69" s="1"/>
       <c r="D69" s="1">
         <v>1</v>
       </c>
       <c r="E69" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="F69" s="1" t="s">
         <v>144</v>
-      </c>
-      <c r="F69" s="1" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1" spans="1:6">
       <c r="A70" s="1"/>
       <c r="B70" s="1">
-        <v>1702</v>
+        <v>1601</v>
       </c>
       <c r="C70" s="1"/>
       <c r="D70" s="1">
         <v>1</v>
       </c>
       <c r="E70" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="F70" s="1" t="s">
         <v>146</v>
-      </c>
-      <c r="F70" s="1" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1" spans="1:6">
       <c r="A71" s="1"/>
       <c r="B71" s="1">
-        <v>1703</v>
+        <v>1602</v>
       </c>
       <c r="C71" s="1"/>
       <c r="D71" s="1">
         <v>1</v>
       </c>
       <c r="E71" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="F71" s="1" t="s">
         <v>148</v>
-      </c>
-      <c r="F71" s="1" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1" spans="1:6">
       <c r="A72" s="1"/>
       <c r="B72" s="1">
-        <v>1704</v>
+        <v>1603</v>
       </c>
       <c r="C72" s="1"/>
       <c r="D72" s="1">
         <v>1</v>
       </c>
       <c r="E72" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="F72" s="1" t="s">
         <v>150</v>
-      </c>
-      <c r="F72" s="1" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1" spans="1:6">
       <c r="A73" s="1"/>
       <c r="B73" s="1">
-        <v>1705</v>
+        <v>1701</v>
       </c>
       <c r="C73" s="1"/>
       <c r="D73" s="1">
         <v>1</v>
       </c>
       <c r="E73" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="F73" s="1" t="s">
         <v>152</v>
-      </c>
-      <c r="F73" s="1" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="74" ht="15" customHeight="1" spans="1:6">
       <c r="A74" s="1"/>
       <c r="B74" s="1">
-        <v>1706</v>
+        <v>1702</v>
       </c>
       <c r="C74" s="1"/>
       <c r="D74" s="1">
         <v>1</v>
       </c>
       <c r="E74" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F74" s="1" t="s">
         <v>154</v>
-      </c>
-      <c r="F74" s="1" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1" spans="1:6">
       <c r="A75" s="1"/>
       <c r="B75" s="1">
-        <v>1707</v>
+        <v>1703</v>
       </c>
       <c r="C75" s="1"/>
       <c r="D75" s="1">
         <v>1</v>
       </c>
       <c r="E75" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="F75" s="1" t="s">
         <v>156</v>
-      </c>
-      <c r="F75" s="1" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="76" ht="15" customHeight="1" spans="1:6">
       <c r="A76" s="1"/>
       <c r="B76" s="1">
-        <v>1708</v>
+        <v>1704</v>
       </c>
       <c r="C76" s="1"/>
       <c r="D76" s="1">
         <v>1</v>
       </c>
       <c r="E76" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="F76" s="1" t="s">
         <v>158</v>
-      </c>
-      <c r="F76" s="1" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="77" ht="15" customHeight="1" spans="1:6">
       <c r="A77" s="1"/>
       <c r="B77" s="1">
-        <v>1711</v>
+        <v>1705</v>
       </c>
       <c r="C77" s="1"/>
       <c r="D77" s="1">
         <v>1</v>
       </c>
       <c r="E77" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F77" s="1" t="s">
         <v>160</v>
-      </c>
-      <c r="F77" s="1" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="78" ht="15" customHeight="1" spans="1:6">
       <c r="A78" s="1"/>
       <c r="B78" s="1">
-        <v>1712</v>
+        <v>1706</v>
       </c>
       <c r="C78" s="1"/>
       <c r="D78" s="1">
         <v>1</v>
       </c>
       <c r="E78" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="F78" s="1" t="s">
         <v>162</v>
-      </c>
-      <c r="F78" s="1" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1" spans="1:6">
       <c r="A79" s="1"/>
       <c r="B79" s="1">
-        <v>1801</v>
-      </c>
-      <c r="C79" s="1" t="s">
+        <v>1707</v>
+      </c>
+      <c r="C79" s="1"/>
+      <c r="D79" s="1">
+        <v>1</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="F79" s="1" t="s">
         <v>164</v>
-      </c>
-      <c r="D79" s="1">
-        <v>1</v>
-      </c>
-      <c r="E79" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="F79" s="1" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1" spans="1:6">
       <c r="A80" s="1"/>
       <c r="B80" s="1">
-        <v>1802</v>
-      </c>
-      <c r="C80" s="1" t="s">
-        <v>164</v>
-      </c>
+        <v>1708</v>
+      </c>
+      <c r="C80" s="1"/>
       <c r="D80" s="1">
         <v>1</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1" spans="1:6">
       <c r="A81" s="1"/>
       <c r="B81" s="1">
-        <v>1803</v>
-      </c>
-      <c r="C81" s="1" t="s">
-        <v>164</v>
-      </c>
+        <v>1711</v>
+      </c>
+      <c r="C81" s="1"/>
       <c r="D81" s="1">
         <v>1</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1" spans="1:6">
       <c r="A82" s="1"/>
       <c r="B82" s="1">
-        <v>1804</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>164</v>
-      </c>
+        <v>1712</v>
+      </c>
+      <c r="C82" s="1"/>
       <c r="D82" s="1">
         <v>1</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1" spans="1:6">
       <c r="A83" s="1"/>
       <c r="B83" s="1">
-        <v>1805</v>
+        <v>1801</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="D83" s="1">
         <v>1</v>
       </c>
       <c r="E83" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="F83" s="1" t="s">
         <v>173</v>
-      </c>
-      <c r="F83" s="1" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="84" ht="15" customHeight="1" spans="1:6">
       <c r="A84" s="1"/>
       <c r="B84" s="1">
-        <v>1806</v>
+        <v>1802</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="D84" s="1">
         <v>1</v>
       </c>
       <c r="E84" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="F84" s="1" t="s">
         <v>175</v>
-      </c>
-      <c r="F84" s="1" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1" spans="1:6">
       <c r="A85" s="1"/>
       <c r="B85" s="1">
-        <v>1807</v>
+        <v>1803</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="D85" s="1">
         <v>1</v>
       </c>
       <c r="E85" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="F85" s="1" t="s">
         <v>177</v>
-      </c>
-      <c r="F85" s="1" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1" spans="1:6">
       <c r="A86" s="1"/>
       <c r="B86" s="1">
-        <v>1808</v>
+        <v>1804</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="D86" s="1">
         <v>1</v>
       </c>
       <c r="E86" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="F86" s="1" t="s">
         <v>179</v>
-      </c>
-      <c r="F86" s="1" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1" spans="1:6">
       <c r="A87" s="1"/>
       <c r="B87" s="1">
-        <v>1831</v>
+        <v>1805</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="D87" s="1">
         <v>1</v>
       </c>
       <c r="E87" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="F87" s="1" t="s">
         <v>181</v>
-      </c>
-      <c r="F87" s="1" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="88" ht="15" customHeight="1" spans="1:6">
       <c r="A88" s="1"/>
       <c r="B88" s="1">
-        <v>1832</v>
+        <v>1806</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="D88" s="1">
         <v>1</v>
       </c>
       <c r="E88" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="F88" s="1" t="s">
         <v>183</v>
-      </c>
-      <c r="F88" s="1" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="89" ht="15" customHeight="1" spans="1:6">
       <c r="A89" s="1"/>
       <c r="B89" s="1">
-        <v>1833</v>
+        <v>1807</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="D89" s="1">
         <v>1</v>
       </c>
       <c r="E89" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="F89" s="1" t="s">
         <v>185</v>
-      </c>
-      <c r="F89" s="1" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="90" ht="15" customHeight="1" spans="1:6">
       <c r="A90" s="1"/>
       <c r="B90" s="1">
-        <v>1834</v>
+        <v>1808</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="D90" s="1">
         <v>1</v>
       </c>
       <c r="E90" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="F90" s="1" t="s">
         <v>187</v>
-      </c>
-      <c r="F90" s="1" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="91" ht="15" customHeight="1" spans="1:6">
       <c r="A91" s="1"/>
       <c r="B91" s="1">
-        <v>1841</v>
+        <v>1831</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="D91" s="1">
         <v>1</v>
       </c>
       <c r="E91" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="F91" s="1" t="s">
         <v>189</v>
-      </c>
-      <c r="F91" s="1" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="92" ht="15" customHeight="1" spans="1:6">
       <c r="A92" s="1"/>
       <c r="B92" s="1">
-        <v>1842</v>
+        <v>1832</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="D92" s="1">
         <v>1</v>
       </c>
       <c r="E92" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F92" s="1" t="s">
         <v>191</v>
-      </c>
-      <c r="F92" s="1" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="93" ht="15" customHeight="1" spans="1:6">
       <c r="A93" s="1"/>
       <c r="B93" s="1">
-        <v>1843</v>
+        <v>1833</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="D93" s="1">
         <v>1</v>
       </c>
       <c r="E93" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="F93" s="1" t="s">
         <v>193</v>
-      </c>
-      <c r="F93" s="1" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="94" ht="15" customHeight="1" spans="1:6">
       <c r="A94" s="1"/>
       <c r="B94" s="1">
-        <v>1844</v>
+        <v>1834</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="D94" s="1">
         <v>1</v>
       </c>
       <c r="E94" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="F94" s="1" t="s">
         <v>195</v>
-      </c>
-      <c r="F94" s="1" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="95" ht="15" customHeight="1" spans="1:6">
       <c r="A95" s="1"/>
       <c r="B95" s="1">
-        <v>1845</v>
+        <v>1841</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="D95" s="1">
         <v>1</v>
       </c>
       <c r="E95" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="F95" s="1" t="s">
         <v>197</v>
-      </c>
-      <c r="F95" s="1" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="96" ht="15" customHeight="1" spans="1:6">
       <c r="A96" s="1"/>
       <c r="B96" s="1">
-        <v>1846</v>
+        <v>1842</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="D96" s="1">
         <v>1</v>
       </c>
       <c r="E96" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="F96" s="1" t="s">
         <v>199</v>
-      </c>
-      <c r="F96" s="1" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="97" ht="15" customHeight="1" spans="1:6">
       <c r="A97" s="1"/>
       <c r="B97" s="1">
-        <v>1847</v>
+        <v>1843</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="D97" s="1">
         <v>1</v>
       </c>
       <c r="E97" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="F97" s="1" t="s">
         <v>201</v>
-      </c>
-      <c r="F97" s="1" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="98" ht="15" customHeight="1" spans="1:6">
       <c r="A98" s="1"/>
       <c r="B98" s="1">
-        <v>1848</v>
+        <v>1844</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="D98" s="1">
         <v>1</v>
       </c>
       <c r="E98" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="F98" s="1" t="s">
         <v>203</v>
-      </c>
-      <c r="F98" s="1" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="99" ht="15" customHeight="1" spans="1:6">
       <c r="A99" s="1"/>
       <c r="B99" s="1">
-        <v>1849</v>
+        <v>1845</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="D99" s="1">
         <v>1</v>
       </c>
       <c r="E99" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="F99" s="1" t="s">
         <v>205</v>
-      </c>
-      <c r="F99" s="1" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="100" ht="15" customHeight="1" spans="1:6">
       <c r="A100" s="1"/>
       <c r="B100" s="1">
-        <v>1850</v>
+        <v>1846</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="D100" s="1">
         <v>1</v>
       </c>
       <c r="E100" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="F100" s="1" t="s">
         <v>207</v>
-      </c>
-      <c r="F100" s="1" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="101" ht="15" customHeight="1" spans="1:6">
       <c r="A101" s="1"/>
       <c r="B101" s="1">
-        <v>1901</v>
-      </c>
-      <c r="C101" s="1"/>
+        <v>1847</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>171</v>
+      </c>
       <c r="D101" s="1">
         <v>1</v>
       </c>
       <c r="E101" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="F101" s="1" t="s">
         <v>209</v>
-      </c>
-      <c r="F101" s="1" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="102" ht="15" customHeight="1" spans="1:6">
       <c r="A102" s="1"/>
       <c r="B102" s="1">
-        <v>1902</v>
-      </c>
-      <c r="C102" s="1"/>
+        <v>1848</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>171</v>
+      </c>
       <c r="D102" s="1">
         <v>1</v>
       </c>
       <c r="E102" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="F102" s="1" t="s">
         <v>211</v>
-      </c>
-      <c r="F102" s="1" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="103" ht="15" customHeight="1" spans="1:6">
       <c r="A103" s="1"/>
       <c r="B103" s="1">
-        <v>1903</v>
-      </c>
-      <c r="C103" s="1"/>
+        <v>1849</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>171</v>
+      </c>
       <c r="D103" s="1">
         <v>1</v>
       </c>
       <c r="E103" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="F103" s="1" t="s">
         <v>213</v>
-      </c>
-      <c r="F103" s="1" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="104" ht="15" customHeight="1" spans="1:6">
       <c r="A104" s="1"/>
       <c r="B104" s="1">
-        <v>1904</v>
-      </c>
-      <c r="C104" s="1"/>
+        <v>1850</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>171</v>
+      </c>
       <c r="D104" s="1">
         <v>1</v>
       </c>
       <c r="E104" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="F104" s="1" t="s">
         <v>215</v>
-      </c>
-      <c r="F104" s="1" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="105" ht="15" customHeight="1" spans="1:6">
       <c r="A105" s="1"/>
       <c r="B105" s="1">
-        <v>1905</v>
+        <v>1901</v>
       </c>
       <c r="C105" s="1"/>
       <c r="D105" s="1">
         <v>1</v>
       </c>
       <c r="E105" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="F105" s="1" t="s">
         <v>217</v>
-      </c>
-      <c r="F105" s="1" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="106" ht="15" customHeight="1" spans="1:6">
       <c r="A106" s="1"/>
       <c r="B106" s="1">
-        <v>1906</v>
+        <v>1902</v>
       </c>
       <c r="C106" s="1"/>
       <c r="D106" s="1">
         <v>1</v>
       </c>
       <c r="E106" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="F106" s="1" t="s">
         <v>219</v>
-      </c>
-      <c r="F106" s="1" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="107" ht="15" customHeight="1" spans="1:6">
       <c r="A107" s="1"/>
       <c r="B107" s="1">
-        <v>1907</v>
+        <v>1903</v>
       </c>
       <c r="C107" s="1"/>
       <c r="D107" s="1">
         <v>1</v>
       </c>
       <c r="E107" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="F107" s="1" t="s">
         <v>221</v>
-      </c>
-      <c r="F107" s="1" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="108" ht="15" customHeight="1" spans="1:6">
       <c r="A108" s="1"/>
       <c r="B108" s="1">
-        <v>1908</v>
+        <v>1904</v>
       </c>
       <c r="C108" s="1"/>
       <c r="D108" s="1">
         <v>1</v>
       </c>
       <c r="E108" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="F108" s="1" t="s">
         <v>223</v>
-      </c>
-      <c r="F108" s="1" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="109" ht="15" customHeight="1" spans="1:6">
       <c r="A109" s="1"/>
       <c r="B109" s="1">
-        <v>1909</v>
+        <v>1905</v>
       </c>
       <c r="C109" s="1"/>
       <c r="D109" s="1">
         <v>1</v>
       </c>
       <c r="E109" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="F109" s="1" t="s">
         <v>225</v>
-      </c>
-      <c r="F109" s="1" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="110" ht="15" customHeight="1" spans="1:6">
       <c r="A110" s="1"/>
       <c r="B110" s="1">
-        <v>1910</v>
+        <v>1906</v>
       </c>
       <c r="C110" s="1"/>
       <c r="D110" s="1">
         <v>1</v>
       </c>
       <c r="E110" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="F110" s="1" t="s">
         <v>227</v>
-      </c>
-      <c r="F110" s="1" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="111" ht="15" customHeight="1" spans="1:6">
       <c r="A111" s="1"/>
       <c r="B111" s="1">
-        <v>1911</v>
+        <v>1907</v>
       </c>
       <c r="C111" s="1"/>
       <c r="D111" s="1">
         <v>1</v>
       </c>
       <c r="E111" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="F111" s="1" t="s">
         <v>229</v>
-      </c>
-      <c r="F111" s="1" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="112" ht="15" customHeight="1" spans="1:6">
       <c r="A112" s="1"/>
       <c r="B112" s="1">
-        <v>1912</v>
+        <v>1908</v>
       </c>
       <c r="C112" s="1"/>
       <c r="D112" s="1">
         <v>1</v>
       </c>
       <c r="E112" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="F112" s="1" t="s">
         <v>231</v>
-      </c>
-      <c r="F112" s="1" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="113" ht="15" customHeight="1" spans="1:6">
       <c r="A113" s="1"/>
       <c r="B113" s="1">
-        <v>1913</v>
+        <v>1909</v>
       </c>
       <c r="C113" s="1"/>
       <c r="D113" s="1">
         <v>1</v>
       </c>
       <c r="E113" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="F113" s="1" t="s">
         <v>233</v>
-      </c>
-      <c r="F113" s="1" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="114" ht="15" customHeight="1" spans="1:6">
       <c r="A114" s="1"/>
       <c r="B114" s="1">
-        <v>1914</v>
+        <v>1910</v>
       </c>
       <c r="C114" s="1"/>
       <c r="D114" s="1">
         <v>1</v>
       </c>
       <c r="E114" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="F114" s="1" t="s">
         <v>235</v>
-      </c>
-      <c r="F114" s="1" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="115" ht="15" customHeight="1" spans="1:6">
       <c r="A115" s="1"/>
       <c r="B115" s="1">
-        <v>1915</v>
+        <v>1911</v>
       </c>
       <c r="C115" s="1"/>
       <c r="D115" s="1">
         <v>1</v>
       </c>
       <c r="E115" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="F115" s="1" t="s">
         <v>237</v>
-      </c>
-      <c r="F115" s="1" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="116" ht="15" customHeight="1" spans="1:6">
       <c r="A116" s="1"/>
       <c r="B116" s="1">
-        <v>1916</v>
+        <v>1912</v>
       </c>
       <c r="C116" s="1"/>
       <c r="D116" s="1">
         <v>1</v>
       </c>
       <c r="E116" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="F116" s="1" t="s">
         <v>239</v>
-      </c>
-      <c r="F116" s="1" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="117" ht="15" customHeight="1" spans="1:6">
       <c r="A117" s="1"/>
       <c r="B117" s="1">
-        <v>1917</v>
+        <v>1913</v>
       </c>
       <c r="C117" s="1"/>
       <c r="D117" s="1">
         <v>1</v>
       </c>
       <c r="E117" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="F117" s="1" t="s">
         <v>241</v>
-      </c>
-      <c r="F117" s="1" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="118" ht="15" customHeight="1" spans="1:6">
       <c r="A118" s="1"/>
       <c r="B118" s="1">
-        <v>1918</v>
+        <v>1914</v>
       </c>
       <c r="C118" s="1"/>
       <c r="D118" s="1">
         <v>1</v>
       </c>
       <c r="E118" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="F118" s="1" t="s">
         <v>243</v>
-      </c>
-      <c r="F118" s="1" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="119" ht="15" customHeight="1" spans="1:6">
       <c r="A119" s="1"/>
       <c r="B119" s="1">
-        <v>1919</v>
+        <v>1915</v>
       </c>
       <c r="C119" s="1"/>
       <c r="D119" s="1">
         <v>1</v>
       </c>
       <c r="E119" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="F119" s="1" t="s">
         <v>245</v>
-      </c>
-      <c r="F119" s="1" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="120" ht="15" customHeight="1" spans="1:6">
       <c r="A120" s="1"/>
       <c r="B120" s="1">
-        <v>1920</v>
+        <v>1916</v>
       </c>
       <c r="C120" s="1"/>
       <c r="D120" s="1">
         <v>1</v>
       </c>
       <c r="E120" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="F120" s="1" t="s">
         <v>247</v>
-      </c>
-      <c r="F120" s="1" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="121" ht="15" customHeight="1" spans="1:6">
       <c r="A121" s="1"/>
       <c r="B121" s="1">
-        <v>1921</v>
+        <v>1917</v>
       </c>
       <c r="C121" s="1"/>
       <c r="D121" s="1">
         <v>1</v>
       </c>
       <c r="E121" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="F121" s="1" t="s">
         <v>249</v>
-      </c>
-      <c r="F121" s="1" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="122" ht="15" customHeight="1" spans="1:6">
       <c r="A122" s="1"/>
       <c r="B122" s="1">
-        <v>1922</v>
+        <v>1918</v>
       </c>
       <c r="C122" s="1"/>
       <c r="D122" s="1">
         <v>1</v>
       </c>
       <c r="E122" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="F122" s="1" t="s">
         <v>251</v>
-      </c>
-      <c r="F122" s="1" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="123" ht="15" customHeight="1" spans="1:6">
       <c r="A123" s="1"/>
       <c r="B123" s="1">
-        <v>1923</v>
+        <v>1919</v>
       </c>
       <c r="C123" s="1"/>
       <c r="D123" s="1">
         <v>1</v>
       </c>
       <c r="E123" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="F123" s="1" t="s">
         <v>253</v>
-      </c>
-      <c r="F123" s="1" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="124" ht="15" customHeight="1" spans="1:6">
       <c r="A124" s="1"/>
       <c r="B124" s="1">
-        <v>1924</v>
+        <v>1920</v>
       </c>
       <c r="C124" s="1"/>
       <c r="D124" s="1">
         <v>1</v>
       </c>
       <c r="E124" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="F124" s="1" t="s">
         <v>255</v>
-      </c>
-      <c r="F124" s="1" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="125" ht="15" customHeight="1" spans="1:6">
       <c r="A125" s="1"/>
       <c r="B125" s="1">
-        <v>1925</v>
+        <v>1921</v>
       </c>
       <c r="C125" s="1"/>
       <c r="D125" s="1">
         <v>1</v>
       </c>
       <c r="E125" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="F125" s="1" t="s">
         <v>257</v>
-      </c>
-      <c r="F125" s="1" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="126" ht="15" customHeight="1" spans="1:6">
       <c r="A126" s="1"/>
       <c r="B126" s="1">
-        <v>1926</v>
+        <v>1922</v>
       </c>
       <c r="C126" s="1"/>
       <c r="D126" s="1">
         <v>1</v>
       </c>
       <c r="E126" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="F126" s="1" t="s">
         <v>259</v>
-      </c>
-      <c r="F126" s="1" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="127" ht="15" customHeight="1" spans="1:6">
       <c r="A127" s="1"/>
       <c r="B127" s="1">
-        <v>1927</v>
+        <v>1923</v>
       </c>
       <c r="C127" s="1"/>
       <c r="D127" s="1">
         <v>1</v>
       </c>
       <c r="E127" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="F127" s="1" t="s">
         <v>261</v>
-      </c>
-      <c r="F127" s="1" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="128" ht="15" customHeight="1" spans="1:6">
       <c r="A128" s="1"/>
       <c r="B128" s="1">
-        <v>1928</v>
+        <v>1924</v>
       </c>
       <c r="C128" s="1"/>
       <c r="D128" s="1">
         <v>1</v>
       </c>
       <c r="E128" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="F128" s="1" t="s">
         <v>263</v>
-      </c>
-      <c r="F128" s="1" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="129" ht="15" customHeight="1" spans="1:6">
       <c r="A129" s="1"/>
       <c r="B129" s="1">
-        <v>1929</v>
+        <v>1925</v>
       </c>
       <c r="C129" s="1"/>
       <c r="D129" s="1">
         <v>1</v>
       </c>
       <c r="E129" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="F129" s="1" t="s">
         <v>265</v>
-      </c>
-      <c r="F129" s="1" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="130" ht="15" customHeight="1" spans="1:6">
       <c r="A130" s="1"/>
       <c r="B130" s="1">
-        <v>1930</v>
+        <v>1926</v>
       </c>
       <c r="C130" s="1"/>
       <c r="D130" s="1">
         <v>1</v>
       </c>
       <c r="E130" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="F130" s="1" t="s">
         <v>267</v>
-      </c>
-      <c r="F130" s="1" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="131" ht="15" customHeight="1" spans="1:6">
       <c r="A131" s="1"/>
       <c r="B131" s="1">
-        <v>1931</v>
+        <v>1927</v>
       </c>
       <c r="C131" s="1"/>
       <c r="D131" s="1">
         <v>1</v>
       </c>
       <c r="E131" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="F131" s="1" t="s">
         <v>269</v>
-      </c>
-      <c r="F131" s="1" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="132" ht="15" customHeight="1" spans="1:6">
       <c r="A132" s="1"/>
       <c r="B132" s="1">
-        <v>1932</v>
+        <v>1928</v>
       </c>
       <c r="C132" s="1"/>
       <c r="D132" s="1">
         <v>1</v>
       </c>
       <c r="E132" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="F132" s="1" t="s">
         <v>271</v>
-      </c>
-      <c r="F132" s="1" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="133" ht="15" customHeight="1" spans="1:6">
       <c r="A133" s="1"/>
       <c r="B133" s="1">
-        <v>1933</v>
+        <v>1929</v>
       </c>
       <c r="C133" s="1"/>
       <c r="D133" s="1">
         <v>1</v>
       </c>
       <c r="E133" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="F133" s="1" t="s">
         <v>273</v>
-      </c>
-      <c r="F133" s="1" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="134" ht="15" customHeight="1" spans="1:6">
       <c r="A134" s="1"/>
       <c r="B134" s="1">
-        <v>1934</v>
+        <v>1930</v>
       </c>
       <c r="C134" s="1"/>
       <c r="D134" s="1">
         <v>1</v>
       </c>
       <c r="E134" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="F134" s="1" t="s">
         <v>275</v>
-      </c>
-      <c r="F134" s="1" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="135" ht="15" customHeight="1" spans="1:6">
       <c r="A135" s="1"/>
       <c r="B135" s="1">
-        <v>1935</v>
+        <v>1931</v>
       </c>
       <c r="C135" s="1"/>
       <c r="D135" s="1">
         <v>1</v>
       </c>
       <c r="E135" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F135" s="1" t="s">
         <v>277</v>
-      </c>
-      <c r="F135" s="1" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="136" ht="15" customHeight="1" spans="1:6">
       <c r="A136" s="1"/>
       <c r="B136" s="1">
-        <v>1936</v>
+        <v>1932</v>
       </c>
       <c r="C136" s="1"/>
       <c r="D136" s="1">
         <v>1</v>
       </c>
       <c r="E136" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="F136" s="1" t="s">
         <v>279</v>
-      </c>
-      <c r="F136" s="1" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="137" ht="15" customHeight="1" spans="1:6">
       <c r="A137" s="1"/>
       <c r="B137" s="1">
-        <v>1937</v>
+        <v>1933</v>
       </c>
       <c r="C137" s="1"/>
       <c r="D137" s="1">
         <v>1</v>
       </c>
       <c r="E137" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="F137" s="1" t="s">
         <v>281</v>
-      </c>
-      <c r="F137" s="1" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="138" ht="15" customHeight="1" spans="1:6">
       <c r="A138" s="1"/>
       <c r="B138" s="1">
-        <v>1938</v>
+        <v>1934</v>
       </c>
       <c r="C138" s="1"/>
       <c r="D138" s="1">
         <v>1</v>
       </c>
       <c r="E138" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="F138" s="1" t="s">
         <v>283</v>
-      </c>
-      <c r="F138" s="1" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="139" ht="15" customHeight="1" spans="1:6">
       <c r="A139" s="1"/>
       <c r="B139" s="1">
-        <v>1939</v>
+        <v>1935</v>
       </c>
       <c r="C139" s="1"/>
       <c r="D139" s="1">
         <v>1</v>
       </c>
       <c r="E139" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="F139" s="1" t="s">
         <v>285</v>
-      </c>
-      <c r="F139" s="1" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="140" ht="15" customHeight="1" spans="1:6">
       <c r="A140" s="1"/>
       <c r="B140" s="1">
-        <v>1940</v>
+        <v>1936</v>
       </c>
       <c r="C140" s="1"/>
       <c r="D140" s="1">
         <v>1</v>
       </c>
       <c r="E140" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="F140" s="1" t="s">
         <v>287</v>
-      </c>
-      <c r="F140" s="1" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="141" ht="15" customHeight="1" spans="1:6">
       <c r="A141" s="1"/>
       <c r="B141" s="1">
-        <v>1941</v>
+        <v>1937</v>
       </c>
       <c r="C141" s="1"/>
       <c r="D141" s="1">
         <v>1</v>
       </c>
       <c r="E141" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="F141" s="1" t="s">
         <v>289</v>
-      </c>
-      <c r="F141" s="1" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="142" ht="15" customHeight="1" spans="1:6">
       <c r="A142" s="1"/>
       <c r="B142" s="1">
-        <v>1942</v>
+        <v>1938</v>
       </c>
       <c r="C142" s="1"/>
       <c r="D142" s="1">
         <v>1</v>
       </c>
       <c r="E142" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F142" s="1" t="s">
         <v>291</v>
-      </c>
-      <c r="F142" s="1" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="143" ht="15" customHeight="1" spans="1:6">
       <c r="A143" s="1"/>
       <c r="B143" s="1">
-        <v>1943</v>
+        <v>1939</v>
       </c>
       <c r="C143" s="1"/>
       <c r="D143" s="1">
         <v>1</v>
       </c>
       <c r="E143" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="F143" s="1" t="s">
         <v>293</v>
-      </c>
-      <c r="F143" s="1" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="144" ht="15" customHeight="1" spans="1:6">
       <c r="A144" s="1"/>
       <c r="B144" s="1">
-        <v>1944</v>
+        <v>1940</v>
       </c>
       <c r="C144" s="1"/>
       <c r="D144" s="1">
         <v>1</v>
       </c>
       <c r="E144" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="F144" s="1" t="s">
         <v>295</v>
-      </c>
-      <c r="F144" s="1" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="145" ht="15" customHeight="1" spans="1:6">
       <c r="A145" s="1"/>
       <c r="B145" s="1">
-        <v>1945</v>
+        <v>1941</v>
       </c>
       <c r="C145" s="1"/>
       <c r="D145" s="1">
         <v>1</v>
       </c>
       <c r="E145" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="F145" s="1" t="s">
         <v>297</v>
-      </c>
-      <c r="F145" s="1" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="146" ht="15" customHeight="1" spans="1:6">
       <c r="A146" s="1"/>
       <c r="B146" s="1">
-        <v>1946</v>
+        <v>1942</v>
       </c>
       <c r="C146" s="1"/>
       <c r="D146" s="1">
         <v>1</v>
       </c>
       <c r="E146" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="F146" s="1" t="s">
         <v>299</v>
-      </c>
-      <c r="F146" s="1" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="147" ht="15" customHeight="1" spans="1:6">
       <c r="A147" s="1"/>
       <c r="B147" s="1">
-        <v>1947</v>
+        <v>1943</v>
       </c>
       <c r="C147" s="1"/>
       <c r="D147" s="1">
         <v>1</v>
       </c>
       <c r="E147" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="F147" s="1" t="s">
         <v>301</v>
-      </c>
-      <c r="F147" s="1" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="148" ht="15" customHeight="1" spans="1:6">
       <c r="A148" s="1"/>
       <c r="B148" s="1">
-        <v>1948</v>
+        <v>1944</v>
       </c>
       <c r="C148" s="1"/>
       <c r="D148" s="1">
         <v>1</v>
       </c>
       <c r="E148" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="F148" s="1" t="s">
         <v>303</v>
-      </c>
-      <c r="F148" s="1" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="149" ht="15" customHeight="1" spans="1:6">
       <c r="A149" s="1"/>
       <c r="B149" s="1">
-        <v>2001</v>
+        <v>1945</v>
       </c>
       <c r="C149" s="1"/>
       <c r="D149" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E149" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="F149" s="1" t="s">
         <v>305</v>
-      </c>
-      <c r="F149" s="1" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="150" ht="15" customHeight="1" spans="1:6">
       <c r="A150" s="1"/>
       <c r="B150" s="1">
-        <v>2002</v>
+        <v>1946</v>
       </c>
       <c r="C150" s="1"/>
       <c r="D150" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E150" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="F150" s="1" t="s">
         <v>307</v>
-      </c>
-      <c r="F150" s="1" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="151" ht="15" customHeight="1" spans="1:6">
       <c r="A151" s="1"/>
       <c r="B151" s="1">
-        <v>2003</v>
+        <v>1947</v>
       </c>
       <c r="C151" s="1"/>
       <c r="D151" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E151" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="F151" s="1" t="s">
         <v>309</v>
-      </c>
-      <c r="F151" s="1" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="152" ht="15" customHeight="1" spans="1:6">
       <c r="A152" s="1"/>
       <c r="B152" s="1">
-        <v>2004</v>
+        <v>1948</v>
       </c>
       <c r="C152" s="1"/>
       <c r="D152" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E152" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="F152" s="1" t="s">
         <v>311</v>
-      </c>
-      <c r="F152" s="1" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="153" ht="15" customHeight="1" spans="1:6">
       <c r="A153" s="1"/>
       <c r="B153" s="1">
-        <v>2101</v>
+        <v>2001</v>
       </c>
       <c r="C153" s="1"/>
       <c r="D153" s="1">
         <v>2</v>
       </c>
       <c r="E153" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="F153" s="1" t="s">
         <v>313</v>
-      </c>
-      <c r="F153" s="1" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="154" ht="15" customHeight="1" spans="1:6">
       <c r="A154" s="1"/>
       <c r="B154" s="1">
-        <v>2102</v>
-      </c>
-      <c r="C154" s="1" t="s">
-        <v>315</v>
-      </c>
+        <v>2002</v>
+      </c>
+      <c r="C154" s="1"/>
       <c r="D154" s="1">
         <v>2</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="155" ht="15" customHeight="1" spans="1:6">
       <c r="A155" s="1"/>
       <c r="B155" s="1">
-        <v>2103</v>
-      </c>
-      <c r="C155" s="1" t="s">
-        <v>315</v>
-      </c>
+        <v>2003</v>
+      </c>
+      <c r="C155" s="1"/>
       <c r="D155" s="1">
         <v>2</v>
       </c>
@@ -5958,22 +5964,20 @@
         <v>316</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="156" ht="15" customHeight="1" spans="1:6">
       <c r="A156" s="1"/>
       <c r="B156" s="1">
-        <v>2104</v>
-      </c>
-      <c r="C156" s="1" t="s">
-        <v>315</v>
-      </c>
+        <v>2004</v>
+      </c>
+      <c r="C156" s="1"/>
       <c r="D156" s="1">
         <v>2</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>319</v>
@@ -5982,7 +5986,7 @@
     <row r="157" ht="15" customHeight="1" spans="1:6">
       <c r="A157" s="1"/>
       <c r="B157" s="1">
-        <v>2201</v>
+        <v>2101</v>
       </c>
       <c r="C157" s="1"/>
       <c r="D157" s="1">
@@ -5998,30 +6002,34 @@
     <row r="158" ht="15" customHeight="1" spans="1:6">
       <c r="A158" s="1"/>
       <c r="B158" s="1">
-        <v>2301</v>
-      </c>
-      <c r="C158" s="1"/>
+        <v>2102</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>322</v>
+      </c>
       <c r="D158" s="1">
         <v>2</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="159" ht="15" customHeight="1" spans="1:6">
       <c r="A159" s="1"/>
       <c r="B159" s="1">
-        <v>2304</v>
-      </c>
-      <c r="C159" s="1"/>
+        <v>2103</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>322</v>
+      </c>
       <c r="D159" s="1">
         <v>2</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>325</v>
@@ -6030,4111 +6038,4177 @@
     <row r="160" ht="15" customHeight="1" spans="1:6">
       <c r="A160" s="1"/>
       <c r="B160" s="1">
-        <v>2309</v>
-      </c>
-      <c r="C160" s="1"/>
+        <v>2104</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>322</v>
+      </c>
       <c r="D160" s="1">
         <v>2</v>
       </c>
       <c r="E160" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="F160" s="1" t="s">
         <v>326</v>
-      </c>
-      <c r="F160" s="1" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="161" ht="15" customHeight="1" spans="1:6">
       <c r="A161" s="1"/>
       <c r="B161" s="1">
-        <v>2310</v>
+        <v>2201</v>
       </c>
       <c r="C161" s="1"/>
       <c r="D161" s="1">
         <v>2</v>
       </c>
       <c r="E161" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="F161" s="1" t="s">
         <v>328</v>
-      </c>
-      <c r="F161" s="1" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="162" ht="15" customHeight="1" spans="1:6">
       <c r="A162" s="1"/>
       <c r="B162" s="1">
-        <v>2311</v>
+        <v>2301</v>
       </c>
       <c r="C162" s="1"/>
       <c r="D162" s="1">
         <v>2</v>
       </c>
       <c r="E162" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="F162" s="1" t="s">
         <v>330</v>
-      </c>
-      <c r="F162" s="1" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="163" ht="15" customHeight="1" spans="1:6">
       <c r="A163" s="1"/>
       <c r="B163" s="1">
-        <v>2312</v>
+        <v>2304</v>
       </c>
       <c r="C163" s="1"/>
       <c r="D163" s="1">
         <v>2</v>
       </c>
       <c r="E163" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="F163" s="1" t="s">
         <v>332</v>
-      </c>
-      <c r="F163" s="1" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="164" ht="15" customHeight="1" spans="1:6">
       <c r="A164" s="1"/>
       <c r="B164" s="1">
-        <v>2313</v>
-      </c>
-      <c r="C164" s="1" t="s">
-        <v>105</v>
-      </c>
+        <v>2309</v>
+      </c>
+      <c r="C164" s="1"/>
       <c r="D164" s="1">
         <v>2</v>
       </c>
       <c r="E164" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="F164" s="1" t="s">
         <v>334</v>
-      </c>
-      <c r="F164" s="1" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="165" ht="15" customHeight="1" spans="1:6">
       <c r="A165" s="1"/>
       <c r="B165" s="1">
-        <v>2399</v>
+        <v>2310</v>
       </c>
       <c r="C165" s="1"/>
       <c r="D165" s="1">
         <v>2</v>
       </c>
       <c r="E165" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="F165" s="1" t="s">
         <v>336</v>
-      </c>
-      <c r="F165" s="1" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="166" ht="15" customHeight="1" spans="1:6">
       <c r="A166" s="1"/>
       <c r="B166" s="1">
-        <v>2401</v>
+        <v>2311</v>
       </c>
       <c r="C166" s="1"/>
       <c r="D166" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E166" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="F166" s="1" t="s">
         <v>338</v>
-      </c>
-      <c r="F166" s="1" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="167" ht="15" customHeight="1" spans="1:6">
       <c r="A167" s="1"/>
       <c r="B167" s="1">
-        <v>2402</v>
+        <v>2312</v>
       </c>
       <c r="C167" s="1"/>
       <c r="D167" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E167" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="F167" s="1" t="s">
         <v>340</v>
-      </c>
-      <c r="F167" s="1" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="168" ht="15" customHeight="1" spans="1:6">
       <c r="A168" s="1"/>
       <c r="B168" s="1">
-        <v>2501</v>
-      </c>
-      <c r="C168" s="1"/>
+        <v>2313</v>
+      </c>
+      <c r="C168" s="1" t="s">
+        <v>109</v>
+      </c>
       <c r="D168" s="1">
         <v>2</v>
       </c>
       <c r="E168" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="F168" s="1" t="s">
         <v>342</v>
-      </c>
-      <c r="F168" s="1" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="169" ht="15" customHeight="1" spans="1:6">
       <c r="A169" s="1"/>
       <c r="B169" s="1">
-        <v>2502</v>
+        <v>2399</v>
       </c>
       <c r="C169" s="1"/>
       <c r="D169" s="1">
         <v>2</v>
       </c>
       <c r="E169" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="F169" s="1" t="s">
         <v>344</v>
-      </c>
-      <c r="F169" s="1" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="170" ht="15" customHeight="1" spans="1:6">
       <c r="A170" s="1"/>
       <c r="B170" s="1">
-        <v>2503</v>
+        <v>2401</v>
       </c>
       <c r="C170" s="1"/>
       <c r="D170" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E170" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="F170" s="1" t="s">
         <v>346</v>
-      </c>
-      <c r="F170" s="1" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="171" ht="15" customHeight="1" spans="1:6">
       <c r="A171" s="1"/>
       <c r="B171" s="1">
-        <v>2504</v>
+        <v>2402</v>
       </c>
       <c r="C171" s="1"/>
       <c r="D171" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E171" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="F171" s="1" t="s">
         <v>348</v>
-      </c>
-      <c r="F171" s="1" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="172" ht="15" customHeight="1" spans="1:6">
       <c r="A172" s="1"/>
       <c r="B172" s="1">
-        <v>2600</v>
+        <v>2501</v>
       </c>
       <c r="C172" s="1"/>
       <c r="D172" s="1">
         <v>2</v>
       </c>
       <c r="E172" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="F172" s="1" t="s">
         <v>350</v>
-      </c>
-      <c r="F172" s="1" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="173" ht="15" customHeight="1" spans="1:6">
       <c r="A173" s="1"/>
       <c r="B173" s="1">
-        <v>2601</v>
+        <v>2502</v>
       </c>
       <c r="C173" s="1"/>
       <c r="D173" s="1">
         <v>2</v>
       </c>
       <c r="E173" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="F173" s="1" t="s">
         <v>352</v>
-      </c>
-      <c r="F173" s="1" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="174" ht="15" customHeight="1" spans="1:6">
       <c r="A174" s="1"/>
       <c r="B174" s="1">
-        <v>2901</v>
+        <v>2503</v>
       </c>
       <c r="C174" s="1"/>
       <c r="D174" s="1">
         <v>2</v>
       </c>
       <c r="E174" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="F174" s="1" t="s">
         <v>354</v>
-      </c>
-      <c r="F174" s="1" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="175" ht="15" customHeight="1" spans="1:6">
       <c r="A175" s="1"/>
       <c r="B175" s="1">
-        <v>3001</v>
+        <v>2504</v>
       </c>
       <c r="C175" s="1"/>
       <c r="D175" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E175" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="F175" s="1" t="s">
         <v>356</v>
-      </c>
-      <c r="F175" s="1" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="176" ht="15" customHeight="1" spans="1:6">
       <c r="A176" s="1"/>
       <c r="B176" s="1">
-        <v>3002</v>
+        <v>2600</v>
       </c>
       <c r="C176" s="1"/>
       <c r="D176" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E176" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="F176" s="1" t="s">
         <v>358</v>
-      </c>
-      <c r="F176" s="1" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="177" ht="15" customHeight="1" spans="1:6">
       <c r="A177" s="1"/>
       <c r="B177" s="1">
-        <v>3003</v>
+        <v>2601</v>
       </c>
       <c r="C177" s="1"/>
       <c r="D177" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E177" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="F177" s="1" t="s">
         <v>360</v>
-      </c>
-      <c r="F177" s="1" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="178" ht="15" customHeight="1" spans="1:6">
       <c r="A178" s="1"/>
       <c r="B178" s="1">
-        <v>3004</v>
+        <v>2901</v>
       </c>
       <c r="C178" s="1"/>
       <c r="D178" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E178" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="F178" s="1" t="s">
         <v>362</v>
-      </c>
-      <c r="F178" s="1" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="179" ht="15" customHeight="1" spans="1:6">
       <c r="A179" s="1"/>
       <c r="B179" s="1">
-        <v>3005</v>
+        <v>3001</v>
       </c>
       <c r="C179" s="1"/>
       <c r="D179" s="1">
         <v>3</v>
       </c>
       <c r="E179" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="F179" s="1" t="s">
         <v>364</v>
-      </c>
-      <c r="F179" s="1" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="180" ht="15" customHeight="1" spans="1:6">
       <c r="A180" s="1"/>
       <c r="B180" s="1">
-        <v>3006</v>
+        <v>3002</v>
       </c>
       <c r="C180" s="1"/>
       <c r="D180" s="1">
         <v>3</v>
       </c>
       <c r="E180" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="F180" s="1" t="s">
         <v>366</v>
-      </c>
-      <c r="F180" s="1" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="181" ht="15" customHeight="1" spans="1:6">
       <c r="A181" s="1"/>
       <c r="B181" s="1">
-        <v>3007</v>
+        <v>3003</v>
       </c>
       <c r="C181" s="1"/>
       <c r="D181" s="1">
         <v>3</v>
       </c>
       <c r="E181" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="F181" s="1" t="s">
         <v>368</v>
-      </c>
-      <c r="F181" s="1" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="182" ht="15" customHeight="1" spans="1:6">
       <c r="A182" s="1"/>
       <c r="B182" s="1">
-        <v>3008</v>
+        <v>3004</v>
       </c>
       <c r="C182" s="1"/>
       <c r="D182" s="1">
         <v>3</v>
       </c>
       <c r="E182" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="F182" s="1" t="s">
         <v>370</v>
-      </c>
-      <c r="F182" s="1" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="183" ht="15" customHeight="1" spans="1:6">
       <c r="A183" s="1"/>
       <c r="B183" s="1">
-        <v>3009</v>
+        <v>3005</v>
       </c>
       <c r="C183" s="1"/>
       <c r="D183" s="1">
         <v>3</v>
       </c>
       <c r="E183" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="F183" s="1" t="s">
         <v>372</v>
-      </c>
-      <c r="F183" s="1" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="184" ht="15" customHeight="1" spans="1:6">
       <c r="A184" s="1"/>
       <c r="B184" s="1">
-        <v>3010</v>
-      </c>
-      <c r="C184" s="1" t="s">
-        <v>164</v>
-      </c>
+        <v>3006</v>
+      </c>
+      <c r="C184" s="1"/>
       <c r="D184" s="1">
         <v>3</v>
       </c>
       <c r="E184" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="F184" s="1" t="s">
         <v>374</v>
-      </c>
-      <c r="F184" s="1" t="s">
-        <v>375</v>
       </c>
     </row>
     <row r="185" ht="15" customHeight="1" spans="1:6">
       <c r="A185" s="1"/>
       <c r="B185" s="1">
-        <v>3011</v>
-      </c>
-      <c r="C185" s="1" t="s">
-        <v>376</v>
-      </c>
+        <v>3007</v>
+      </c>
+      <c r="C185" s="1"/>
       <c r="D185" s="1">
         <v>3</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="186" ht="15" customHeight="1" spans="1:6">
       <c r="A186" s="1"/>
       <c r="B186" s="1">
-        <v>3012</v>
-      </c>
-      <c r="C186" s="1" t="s">
-        <v>376</v>
-      </c>
+        <v>3008</v>
+      </c>
+      <c r="C186" s="1"/>
       <c r="D186" s="1">
         <v>3</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="187" ht="15" customHeight="1" spans="1:6">
       <c r="A187" s="1"/>
       <c r="B187" s="1">
-        <v>3013</v>
-      </c>
-      <c r="C187" s="1" t="s">
-        <v>376</v>
-      </c>
+        <v>3009</v>
+      </c>
+      <c r="C187" s="1"/>
       <c r="D187" s="1">
         <v>3</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="188" ht="15" customHeight="1" spans="1:6">
       <c r="A188" s="1"/>
       <c r="B188" s="1">
-        <v>3014</v>
+        <v>3010</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>376</v>
+        <v>171</v>
       </c>
       <c r="D188" s="1">
         <v>3</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="189" ht="15" customHeight="1" spans="1:6">
       <c r="A189" s="1"/>
       <c r="B189" s="1">
-        <v>3015</v>
+        <v>3011</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="D189" s="1">
         <v>3</v>
       </c>
       <c r="E189" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="F189" s="1" t="s">
         <v>385</v>
-      </c>
-      <c r="F189" s="1" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="190" ht="15" customHeight="1" spans="1:6">
       <c r="A190" s="1"/>
       <c r="B190" s="1">
-        <v>3016</v>
+        <v>3012</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="D190" s="1">
         <v>3</v>
       </c>
       <c r="E190" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="F190" s="1" t="s">
         <v>387</v>
-      </c>
-      <c r="F190" s="1" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="191" ht="15" customHeight="1" spans="1:6">
       <c r="A191" s="1"/>
       <c r="B191" s="1">
-        <v>3017</v>
+        <v>3013</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="D191" s="1">
         <v>3</v>
       </c>
       <c r="E191" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="F191" s="1" t="s">
         <v>389</v>
-      </c>
-      <c r="F191" s="1" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="192" ht="15" customHeight="1" spans="1:6">
       <c r="A192" s="1"/>
       <c r="B192" s="1">
-        <v>3018</v>
+        <v>3014</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="D192" s="1">
         <v>3</v>
       </c>
       <c r="E192" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="F192" s="1" t="s">
         <v>391</v>
-      </c>
-      <c r="F192" s="1" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="193" ht="15" customHeight="1" spans="1:6">
       <c r="A193" s="1"/>
       <c r="B193" s="1">
-        <v>3019</v>
+        <v>3015</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="D193" s="1">
         <v>3</v>
       </c>
       <c r="E193" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="F193" s="1" t="s">
         <v>393</v>
-      </c>
-      <c r="F193" s="1" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="194" ht="15" customHeight="1" spans="1:6">
       <c r="A194" s="1"/>
       <c r="B194" s="1">
-        <v>6001</v>
+        <v>3016</v>
       </c>
       <c r="C194" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="D194" s="1">
+        <v>3</v>
+      </c>
+      <c r="E194" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="F194" s="1" t="s">
         <v>395</v>
-      </c>
-      <c r="D194" s="1">
-        <v>6</v>
-      </c>
-      <c r="E194" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="F194" s="1" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="195" ht="15" customHeight="1" spans="1:6">
       <c r="A195" s="1"/>
       <c r="B195" s="1">
-        <v>10001</v>
-      </c>
-      <c r="C195" s="1"/>
+        <v>3017</v>
+      </c>
+      <c r="C195" s="1" t="s">
+        <v>383</v>
+      </c>
       <c r="D195" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F195" s="1" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="196" ht="15" customHeight="1" spans="1:6">
       <c r="A196" s="1"/>
       <c r="B196" s="1">
-        <v>10002</v>
-      </c>
-      <c r="C196" s="1"/>
+        <v>3018</v>
+      </c>
+      <c r="C196" s="1" t="s">
+        <v>383</v>
+      </c>
       <c r="D196" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="F196" s="1" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="197" ht="15" customHeight="1" spans="1:6">
       <c r="A197" s="1"/>
       <c r="B197" s="1">
-        <v>10003</v>
-      </c>
-      <c r="C197" s="1"/>
+        <v>3019</v>
+      </c>
+      <c r="C197" s="1" t="s">
+        <v>383</v>
+      </c>
       <c r="D197" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="198" ht="15" customHeight="1" spans="1:6">
       <c r="A198" s="1"/>
       <c r="B198" s="1">
-        <v>10004</v>
-      </c>
-      <c r="C198" s="1"/>
+        <v>6001</v>
+      </c>
+      <c r="C198" s="1" t="s">
+        <v>402</v>
+      </c>
       <c r="D198" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E198" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="F198" s="1" t="s">
         <v>404</v>
-      </c>
-      <c r="F198" s="1" t="s">
-        <v>405</v>
       </c>
     </row>
     <row r="199" ht="15" customHeight="1" spans="1:6">
       <c r="A199" s="1"/>
       <c r="B199" s="1">
-        <v>10101</v>
+        <v>10001</v>
       </c>
       <c r="C199" s="1"/>
       <c r="D199" s="1">
         <v>1</v>
       </c>
       <c r="E199" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="F199" s="1" t="s">
         <v>406</v>
-      </c>
-      <c r="F199" s="1" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="200" ht="15" customHeight="1" spans="1:6">
       <c r="A200" s="1"/>
       <c r="B200" s="1">
-        <v>10102</v>
+        <v>10002</v>
       </c>
       <c r="C200" s="1"/>
       <c r="D200" s="1">
         <v>1</v>
       </c>
       <c r="E200" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="F200" s="1" t="s">
         <v>408</v>
-      </c>
-      <c r="F200" s="1" t="s">
-        <v>409</v>
       </c>
     </row>
     <row r="201" ht="15" customHeight="1" spans="1:6">
       <c r="A201" s="1"/>
       <c r="B201" s="1">
-        <v>10103</v>
+        <v>10003</v>
       </c>
       <c r="C201" s="1"/>
       <c r="D201" s="1">
         <v>1</v>
       </c>
       <c r="E201" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="F201" s="1" t="s">
         <v>410</v>
-      </c>
-      <c r="F201" s="1" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="202" ht="15" customHeight="1" spans="1:6">
       <c r="A202" s="1"/>
       <c r="B202" s="1">
-        <v>10201</v>
+        <v>10004</v>
       </c>
       <c r="C202" s="1"/>
       <c r="D202" s="1">
         <v>1</v>
       </c>
       <c r="E202" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="F202" s="1" t="s">
         <v>412</v>
-      </c>
-      <c r="F202" s="1" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="203" ht="15" customHeight="1" spans="1:6">
       <c r="A203" s="1"/>
       <c r="B203" s="1">
-        <v>10202</v>
+        <v>10101</v>
       </c>
       <c r="C203" s="1"/>
       <c r="D203" s="1">
         <v>1</v>
       </c>
       <c r="E203" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="F203" s="1" t="s">
         <v>414</v>
-      </c>
-      <c r="F203" s="1" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="204" ht="15" customHeight="1" spans="1:6">
       <c r="A204" s="1"/>
       <c r="B204" s="1">
-        <v>10203</v>
+        <v>10102</v>
       </c>
       <c r="C204" s="1"/>
       <c r="D204" s="1">
         <v>1</v>
       </c>
       <c r="E204" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="F204" s="1" t="s">
         <v>416</v>
-      </c>
-      <c r="F204" s="1" t="s">
-        <v>417</v>
       </c>
     </row>
     <row r="205" ht="15" customHeight="1" spans="1:6">
       <c r="A205" s="1"/>
       <c r="B205" s="1">
-        <v>11001</v>
-      </c>
-      <c r="C205" s="1" t="s">
+        <v>10103</v>
+      </c>
+      <c r="C205" s="1"/>
+      <c r="D205" s="1">
+        <v>1</v>
+      </c>
+      <c r="E205" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="F205" s="1" t="s">
         <v>418</v>
-      </c>
-      <c r="D205" s="1">
-        <v>1</v>
-      </c>
-      <c r="E205" s="1" t="s">
-        <v>419</v>
-      </c>
-      <c r="F205" s="1" t="s">
-        <v>420</v>
       </c>
     </row>
     <row r="206" ht="15" customHeight="1" spans="1:6">
       <c r="A206" s="1"/>
       <c r="B206" s="1">
-        <v>13001</v>
+        <v>10201</v>
       </c>
       <c r="C206" s="1"/>
       <c r="D206" s="1">
         <v>1</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="F206" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="207" ht="15" customHeight="1" spans="1:6">
       <c r="A207" s="1"/>
       <c r="B207" s="1">
-        <v>13004</v>
+        <v>10202</v>
       </c>
       <c r="C207" s="1"/>
       <c r="D207" s="1">
         <v>1</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="F207" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="208" ht="15" customHeight="1" spans="1:6">
       <c r="A208" s="1"/>
       <c r="B208" s="1">
-        <v>13010</v>
-      </c>
-      <c r="C208" s="1" t="s">
-        <v>105</v>
-      </c>
+        <v>10203</v>
+      </c>
+      <c r="C208" s="1"/>
       <c r="D208" s="1">
         <v>1</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="F208" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="209" ht="15" customHeight="1" spans="1:6">
       <c r="A209" s="1"/>
       <c r="B209" s="1">
-        <v>13011</v>
+        <v>11001</v>
       </c>
       <c r="C209" s="1" t="s">
-        <v>105</v>
+        <v>425</v>
       </c>
       <c r="D209" s="1">
         <v>1</v>
       </c>
       <c r="E209" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="F209" s="1" t="s">
         <v>427</v>
-      </c>
-      <c r="F209" s="1" t="s">
-        <v>428</v>
       </c>
     </row>
     <row r="210" ht="15" customHeight="1" spans="1:6">
       <c r="A210" s="1"/>
       <c r="B210" s="1">
-        <v>13012</v>
-      </c>
-      <c r="C210" s="1" t="s">
-        <v>105</v>
-      </c>
+        <v>13001</v>
+      </c>
+      <c r="C210" s="1"/>
       <c r="D210" s="1">
         <v>1</v>
       </c>
       <c r="E210" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="F210" s="1" t="s">
         <v>429</v>
-      </c>
-      <c r="F210" s="1" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="211" ht="15" customHeight="1" spans="1:6">
       <c r="A211" s="1"/>
       <c r="B211" s="1">
-        <v>13013</v>
-      </c>
-      <c r="C211" s="1" t="s">
-        <v>105</v>
-      </c>
+        <v>13004</v>
+      </c>
+      <c r="C211" s="1"/>
       <c r="D211" s="1">
         <v>1</v>
       </c>
       <c r="E211" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="F211" s="1" t="s">
         <v>431</v>
-      </c>
-      <c r="F211" s="1" t="s">
-        <v>432</v>
       </c>
     </row>
     <row r="212" ht="15" customHeight="1" spans="1:6">
       <c r="A212" s="1"/>
       <c r="B212" s="1">
-        <v>13999</v>
+        <v>13010</v>
       </c>
       <c r="C212" s="1" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D212" s="1">
         <v>1</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>433</v>
+        <v>145</v>
       </c>
       <c r="F212" s="1" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="213" ht="15" customHeight="1" spans="1:6">
       <c r="A213" s="1"/>
       <c r="B213" s="1">
-        <v>15001</v>
-      </c>
-      <c r="C213" s="1"/>
+        <v>13011</v>
+      </c>
+      <c r="C213" s="1" t="s">
+        <v>109</v>
+      </c>
       <c r="D213" s="1">
         <v>1</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>435</v>
+        <v>147</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
     </row>
     <row r="214" ht="15" customHeight="1" spans="1:6">
       <c r="A214" s="1"/>
       <c r="B214" s="1">
-        <v>15002</v>
+        <v>13012</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>437</v>
+        <v>109</v>
       </c>
       <c r="D214" s="1">
         <v>1</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>438</v>
+        <v>149</v>
       </c>
       <c r="F214" s="1" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
     </row>
     <row r="215" ht="15" customHeight="1" spans="1:6">
       <c r="A215" s="1"/>
       <c r="B215" s="1">
-        <v>15003</v>
-      </c>
-      <c r="C215" s="1"/>
+        <v>13013</v>
+      </c>
+      <c r="C215" s="1" t="s">
+        <v>109</v>
+      </c>
       <c r="D215" s="1">
         <v>1</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="F215" s="1" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
     </row>
     <row r="216" ht="15" customHeight="1" spans="1:6">
       <c r="A216" s="1"/>
       <c r="B216" s="1">
-        <v>15005</v>
-      </c>
-      <c r="C216" s="1"/>
+        <v>13999</v>
+      </c>
+      <c r="C216" s="1" t="s">
+        <v>109</v>
+      </c>
       <c r="D216" s="1">
         <v>1</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="F216" s="1" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
     </row>
     <row r="217" ht="15" customHeight="1" spans="1:6">
       <c r="A217" s="1"/>
       <c r="B217" s="1">
-        <v>15007</v>
+        <v>15001</v>
       </c>
       <c r="C217" s="1"/>
       <c r="D217" s="1">
         <v>1</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="F217" s="1" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
     </row>
     <row r="218" ht="15" customHeight="1" spans="1:6">
       <c r="A218" s="1"/>
       <c r="B218" s="1">
-        <v>15008</v>
-      </c>
-      <c r="C218" s="1"/>
+        <v>15002</v>
+      </c>
+      <c r="C218" s="1" t="s">
+        <v>441</v>
+      </c>
       <c r="D218" s="1">
         <v>1</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="F218" s="1" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
     </row>
     <row r="219" ht="15" customHeight="1" spans="1:6">
       <c r="A219" s="1"/>
       <c r="B219" s="1">
-        <v>15009</v>
+        <v>15003</v>
       </c>
       <c r="C219" s="1"/>
       <c r="D219" s="1">
         <v>1</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="F219" s="1" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
     </row>
     <row r="220" ht="15" customHeight="1" spans="1:6">
       <c r="A220" s="1"/>
       <c r="B220" s="1">
-        <v>15011</v>
+        <v>15005</v>
       </c>
       <c r="C220" s="1"/>
       <c r="D220" s="1">
         <v>1</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
     </row>
     <row r="221" ht="15" customHeight="1" spans="1:6">
       <c r="A221" s="1"/>
       <c r="B221" s="1">
-        <v>15012</v>
+        <v>15007</v>
       </c>
       <c r="C221" s="1"/>
       <c r="D221" s="1">
         <v>1</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="F221" s="1" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
     </row>
     <row r="222" ht="15" customHeight="1" spans="1:6">
       <c r="A222" s="1"/>
       <c r="B222" s="1">
-        <v>15013</v>
+        <v>15008</v>
       </c>
       <c r="C222" s="1"/>
       <c r="D222" s="1">
         <v>1</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="F222" s="1" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
     </row>
     <row r="223" ht="15" customHeight="1" spans="1:6">
       <c r="A223" s="1"/>
       <c r="B223" s="1">
-        <v>15014</v>
+        <v>15009</v>
       </c>
       <c r="C223" s="1"/>
       <c r="D223" s="1">
         <v>1</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="F223" s="1" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
     </row>
     <row r="224" ht="15" customHeight="1" spans="1:6">
       <c r="A224" s="1"/>
       <c r="B224" s="1">
-        <v>15015</v>
+        <v>15011</v>
       </c>
       <c r="C224" s="1"/>
       <c r="D224" s="1">
         <v>1</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="F224" s="1" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
     </row>
     <row r="225" ht="15" customHeight="1" spans="1:6">
       <c r="A225" s="1"/>
       <c r="B225" s="1">
-        <v>15017</v>
+        <v>15012</v>
       </c>
       <c r="C225" s="1"/>
       <c r="D225" s="1">
         <v>1</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="F225" s="1" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
     </row>
     <row r="226" ht="15" customHeight="1" spans="1:6">
       <c r="A226" s="1"/>
       <c r="B226" s="1">
-        <v>15018</v>
+        <v>15013</v>
       </c>
       <c r="C226" s="1"/>
       <c r="D226" s="1">
         <v>1</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="F226" s="1" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
     </row>
     <row r="227" ht="15" customHeight="1" spans="1:6">
       <c r="A227" s="1"/>
       <c r="B227" s="1">
-        <v>15019</v>
+        <v>15014</v>
       </c>
       <c r="C227" s="1"/>
       <c r="D227" s="1">
         <v>1</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
     </row>
     <row r="228" ht="15" customHeight="1" spans="1:6">
       <c r="A228" s="1"/>
       <c r="B228" s="1">
-        <v>15020</v>
+        <v>15015</v>
       </c>
       <c r="C228" s="1"/>
       <c r="D228" s="1">
         <v>1</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="F228" s="1" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
     </row>
     <row r="229" ht="15" customHeight="1" spans="1:6">
       <c r="A229" s="1"/>
       <c r="B229" s="1">
-        <v>15021</v>
+        <v>15017</v>
       </c>
       <c r="C229" s="1"/>
       <c r="D229" s="1">
         <v>1</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="F229" s="1" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
     </row>
     <row r="230" ht="15" customHeight="1" spans="1:6">
       <c r="A230" s="1"/>
       <c r="B230" s="1">
-        <v>15022</v>
-      </c>
-      <c r="C230" s="1" t="s">
-        <v>470</v>
-      </c>
+        <v>15018</v>
+      </c>
+      <c r="C230" s="1"/>
       <c r="D230" s="1">
         <v>1</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="F230" s="1" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
     </row>
     <row r="231" ht="15" customHeight="1" spans="1:6">
       <c r="A231" s="1"/>
       <c r="B231" s="1">
-        <v>16001</v>
-      </c>
-      <c r="C231" s="1" t="s">
-        <v>473</v>
-      </c>
+        <v>15019</v>
+      </c>
+      <c r="C231" s="1"/>
       <c r="D231" s="1">
         <v>1</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="F231" s="1" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
     </row>
     <row r="232" ht="15" customHeight="1" spans="1:6">
       <c r="A232" s="1"/>
       <c r="B232" s="1">
-        <v>16002</v>
-      </c>
-      <c r="C232" s="1" t="s">
-        <v>473</v>
-      </c>
+        <v>15020</v>
+      </c>
+      <c r="C232" s="1"/>
       <c r="D232" s="1">
         <v>1</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="F232" s="1" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
     </row>
     <row r="233" ht="15" customHeight="1" spans="1:6">
       <c r="A233" s="1"/>
       <c r="B233" s="1">
-        <v>16003</v>
-      </c>
-      <c r="C233" s="1" t="s">
+        <v>15021</v>
+      </c>
+      <c r="C233" s="1"/>
+      <c r="D233" s="1">
+        <v>1</v>
+      </c>
+      <c r="E233" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="F233" s="1" t="s">
         <v>473</v>
-      </c>
-      <c r="D233" s="1">
-        <v>1</v>
-      </c>
-      <c r="E233" s="1" t="s">
-        <v>478</v>
-      </c>
-      <c r="F233" s="1" t="s">
-        <v>479</v>
       </c>
     </row>
     <row r="234" ht="15" customHeight="1" spans="1:6">
       <c r="A234" s="1"/>
       <c r="B234" s="1">
-        <v>16004</v>
+        <v>15022</v>
       </c>
       <c r="C234" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D234" s="1">
         <v>1</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="F234" s="1" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
     </row>
     <row r="235" ht="15" customHeight="1" spans="1:6">
       <c r="A235" s="1"/>
       <c r="B235" s="1">
-        <v>16005</v>
+        <v>16001</v>
       </c>
       <c r="C235" s="1" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="D235" s="1">
         <v>1</v>
       </c>
       <c r="E235" s="1" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="F235" s="1" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
     </row>
     <row r="236" ht="15" customHeight="1" spans="1:6">
       <c r="A236" s="1"/>
       <c r="B236" s="1">
-        <v>16006</v>
+        <v>16002</v>
       </c>
       <c r="C236" s="1" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="D236" s="1">
         <v>1</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="F236" s="1" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
     </row>
     <row r="237" ht="15" customHeight="1" spans="1:6">
       <c r="A237" s="1"/>
       <c r="B237" s="1">
-        <v>19002</v>
-      </c>
-      <c r="C237" s="1"/>
+        <v>16003</v>
+      </c>
+      <c r="C237" s="1" t="s">
+        <v>477</v>
+      </c>
       <c r="D237" s="1">
         <v>1</v>
       </c>
       <c r="E237" s="1" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="F237" s="1" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
     </row>
     <row r="238" ht="15" customHeight="1" spans="1:6">
       <c r="A238" s="1"/>
       <c r="B238" s="1">
-        <v>19003</v>
-      </c>
-      <c r="C238" s="1"/>
+        <v>16004</v>
+      </c>
+      <c r="C238" s="1" t="s">
+        <v>477</v>
+      </c>
       <c r="D238" s="1">
         <v>1</v>
       </c>
       <c r="E238" s="1" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="F238" s="1" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
     </row>
     <row r="239" ht="15" customHeight="1" spans="1:6">
       <c r="A239" s="1"/>
       <c r="B239" s="1">
-        <v>19004</v>
-      </c>
-      <c r="C239" s="1"/>
+        <v>16005</v>
+      </c>
+      <c r="C239" s="1" t="s">
+        <v>477</v>
+      </c>
       <c r="D239" s="1">
         <v>1</v>
       </c>
       <c r="E239" s="1" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="F239" s="1" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
     </row>
     <row r="240" ht="15" customHeight="1" spans="1:6">
       <c r="A240" s="1"/>
       <c r="B240" s="1">
-        <v>19012</v>
-      </c>
-      <c r="C240" s="1"/>
+        <v>16006</v>
+      </c>
+      <c r="C240" s="1" t="s">
+        <v>477</v>
+      </c>
       <c r="D240" s="1">
         <v>1</v>
       </c>
       <c r="E240" s="1" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="F240" s="1" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
     </row>
     <row r="241" ht="15" customHeight="1" spans="1:6">
       <c r="A241" s="1"/>
       <c r="B241" s="1">
-        <v>19013</v>
+        <v>19002</v>
       </c>
       <c r="C241" s="1"/>
       <c r="D241" s="1">
         <v>1</v>
       </c>
       <c r="E241" s="1" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="F241" s="1" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
     </row>
     <row r="242" ht="15" customHeight="1" spans="1:6">
       <c r="A242" s="1"/>
       <c r="B242" s="1">
-        <v>19014</v>
+        <v>19003</v>
       </c>
       <c r="C242" s="1"/>
       <c r="D242" s="1">
         <v>1</v>
       </c>
       <c r="E242" s="1" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="F242" s="1" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
     </row>
     <row r="243" ht="15" customHeight="1" spans="1:6">
       <c r="A243" s="1"/>
       <c r="B243" s="1">
-        <v>19022</v>
+        <v>19004</v>
       </c>
       <c r="C243" s="1"/>
       <c r="D243" s="1">
         <v>1</v>
       </c>
       <c r="E243" s="1" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="F243" s="1" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
     </row>
     <row r="244" ht="15" customHeight="1" spans="1:6">
       <c r="A244" s="1"/>
       <c r="B244" s="1">
-        <v>19023</v>
+        <v>19012</v>
       </c>
       <c r="C244" s="1"/>
       <c r="D244" s="1">
         <v>1</v>
       </c>
       <c r="E244" s="1" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="F244" s="1" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
     </row>
     <row r="245" ht="15" customHeight="1" spans="1:6">
       <c r="A245" s="1"/>
       <c r="B245" s="1">
-        <v>19024</v>
+        <v>19013</v>
       </c>
       <c r="C245" s="1"/>
       <c r="D245" s="1">
         <v>1</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="F245" s="1" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
     </row>
     <row r="246" ht="15" customHeight="1" spans="1:6">
       <c r="A246" s="1"/>
       <c r="B246" s="1">
-        <v>20101</v>
-      </c>
-      <c r="C246" s="1" t="s">
-        <v>504</v>
-      </c>
+        <v>19014</v>
+      </c>
+      <c r="C246" s="1"/>
       <c r="D246" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="F246" s="1" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
     </row>
     <row r="247" ht="15" customHeight="1" spans="1:6">
       <c r="A247" s="1"/>
       <c r="B247" s="1">
-        <v>20102</v>
-      </c>
-      <c r="C247" s="1" t="s">
-        <v>504</v>
-      </c>
+        <v>19022</v>
+      </c>
+      <c r="C247" s="1"/>
       <c r="D247" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="F247" s="1" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
     </row>
     <row r="248" ht="15" customHeight="1" spans="1:6">
       <c r="A248" s="1"/>
       <c r="B248" s="1">
-        <v>20103</v>
-      </c>
-      <c r="C248" s="1" t="s">
+        <v>19023</v>
+      </c>
+      <c r="C248" s="1"/>
+      <c r="D248" s="1">
+        <v>1</v>
+      </c>
+      <c r="E248" s="1" t="s">
         <v>504</v>
       </c>
-      <c r="D248" s="1">
-        <v>2</v>
-      </c>
-      <c r="E248" s="1" t="s">
-        <v>509</v>
-      </c>
       <c r="F248" s="1" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
     </row>
     <row r="249" ht="15" customHeight="1" spans="1:6">
       <c r="A249" s="1"/>
       <c r="B249" s="1">
-        <v>20104</v>
-      </c>
-      <c r="C249" s="1" t="s">
-        <v>504</v>
-      </c>
+        <v>19024</v>
+      </c>
+      <c r="C249" s="1"/>
       <c r="D249" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="F249" s="1" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
     </row>
     <row r="250" ht="15" customHeight="1" spans="1:6">
       <c r="A250" s="1"/>
       <c r="B250" s="1">
-        <v>20105</v>
+        <v>20101</v>
       </c>
       <c r="C250" s="1" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="D250" s="1">
         <v>2</v>
       </c>
       <c r="E250" s="1" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="F250" s="1" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
     </row>
     <row r="251" ht="15" customHeight="1" spans="1:6">
       <c r="A251" s="1"/>
       <c r="B251" s="1">
-        <v>20106</v>
+        <v>20102</v>
       </c>
       <c r="C251" s="1" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="D251" s="1">
         <v>2</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="F251" s="1" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
     </row>
     <row r="252" ht="15" customHeight="1" spans="1:6">
       <c r="A252" s="1"/>
       <c r="B252" s="1">
-        <v>20107</v>
+        <v>20103</v>
       </c>
       <c r="C252" s="1" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="D252" s="1">
         <v>2</v>
       </c>
       <c r="E252" s="1" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="F252" s="1" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
     </row>
     <row r="253" ht="15" customHeight="1" spans="1:6">
       <c r="A253" s="1"/>
       <c r="B253" s="1">
-        <v>20108</v>
+        <v>20104</v>
       </c>
       <c r="C253" s="1" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="D253" s="1">
         <v>2</v>
       </c>
       <c r="E253" s="1" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="F253" s="1" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
     </row>
     <row r="254" ht="15" customHeight="1" spans="1:6">
       <c r="A254" s="1"/>
       <c r="B254" s="1">
-        <v>20109</v>
+        <v>20105</v>
       </c>
       <c r="C254" s="1" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="D254" s="1">
         <v>2</v>
       </c>
       <c r="E254" s="1" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="F254" s="1" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
     </row>
     <row r="255" ht="15" customHeight="1" spans="1:6">
       <c r="A255" s="1"/>
       <c r="B255" s="1">
-        <v>20110</v>
+        <v>20106</v>
       </c>
       <c r="C255" s="1" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="D255" s="1">
         <v>2</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="F255" s="1" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
     </row>
     <row r="256" ht="15" customHeight="1" spans="1:6">
       <c r="A256" s="1"/>
       <c r="B256" s="1">
-        <v>20111</v>
+        <v>20107</v>
       </c>
       <c r="C256" s="1" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="D256" s="1">
         <v>2</v>
       </c>
       <c r="E256" s="1" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="F256" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
     </row>
     <row r="257" ht="15" customHeight="1" spans="1:6">
       <c r="A257" s="1"/>
       <c r="B257" s="1">
-        <v>20112</v>
+        <v>20108</v>
       </c>
       <c r="C257" s="1" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="D257" s="1">
         <v>2</v>
       </c>
       <c r="E257" s="1" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="F257" s="1" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
     </row>
     <row r="258" ht="15" customHeight="1" spans="1:6">
       <c r="A258" s="1"/>
       <c r="B258" s="1">
-        <v>20113</v>
+        <v>20109</v>
       </c>
       <c r="C258" s="1" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="D258" s="1">
         <v>2</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="F258" s="1" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
     </row>
     <row r="259" ht="15" customHeight="1" spans="1:6">
       <c r="A259" s="1"/>
       <c r="B259" s="1">
-        <v>20114</v>
+        <v>20110</v>
       </c>
       <c r="C259" s="1" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="D259" s="1">
         <v>2</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="F259" s="1" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
     </row>
     <row r="260" ht="15" customHeight="1" spans="1:6">
       <c r="A260" s="1"/>
       <c r="B260" s="1">
-        <v>20115</v>
+        <v>20111</v>
       </c>
       <c r="C260" s="1" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="D260" s="1">
         <v>2</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="F260" s="1" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
     </row>
     <row r="261" ht="15" customHeight="1" spans="1:6">
       <c r="A261" s="1"/>
       <c r="B261" s="1">
-        <v>20116</v>
+        <v>20112</v>
       </c>
       <c r="C261" s="1" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="D261" s="1">
         <v>2</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="F261" s="1" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
     </row>
     <row r="262" ht="15" customHeight="1" spans="1:6">
       <c r="A262" s="1"/>
       <c r="B262" s="1">
-        <v>20117</v>
+        <v>20113</v>
       </c>
       <c r="C262" s="1" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="D262" s="1">
         <v>2</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="F262" s="1" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
     </row>
     <row r="263" ht="15" customHeight="1" spans="1:6">
       <c r="A263" s="1"/>
       <c r="B263" s="1">
-        <v>20118</v>
+        <v>20114</v>
       </c>
       <c r="C263" s="1" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="D263" s="1">
         <v>2</v>
       </c>
       <c r="E263" s="1" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="F263" s="1" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
     </row>
     <row r="264" ht="15" customHeight="1" spans="1:6">
       <c r="A264" s="1"/>
       <c r="B264" s="1">
-        <v>20119</v>
+        <v>20115</v>
       </c>
       <c r="C264" s="1" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="D264" s="1">
         <v>2</v>
       </c>
       <c r="E264" s="1" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="F264" s="1" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
     </row>
     <row r="265" ht="15" customHeight="1" spans="1:6">
       <c r="A265" s="1"/>
       <c r="B265" s="1">
-        <v>20120</v>
+        <v>20116</v>
       </c>
       <c r="C265" s="1" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="D265" s="1">
         <v>2</v>
       </c>
       <c r="E265" s="1" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="F265" s="1" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
     </row>
     <row r="266" ht="15" customHeight="1" spans="1:6">
       <c r="A266" s="1"/>
       <c r="B266" s="1">
-        <v>20121</v>
+        <v>20117</v>
       </c>
       <c r="C266" s="1" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="D266" s="1">
         <v>2</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="F266" s="1" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
     </row>
     <row r="267" ht="15" customHeight="1" spans="1:6">
       <c r="A267" s="1"/>
       <c r="B267" s="1">
-        <v>20122</v>
+        <v>20118</v>
       </c>
       <c r="C267" s="1" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="D267" s="1">
         <v>2</v>
       </c>
       <c r="E267" s="1" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="F267" s="1" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
     </row>
     <row r="268" ht="15" customHeight="1" spans="1:6">
       <c r="A268" s="1"/>
       <c r="B268" s="1">
-        <v>20123</v>
+        <v>20119</v>
       </c>
       <c r="C268" s="1" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="D268" s="1">
         <v>2</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="F268" s="1" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
     </row>
     <row r="269" ht="15" customHeight="1" spans="1:6">
       <c r="A269" s="1"/>
       <c r="B269" s="1">
-        <v>20124</v>
+        <v>20120</v>
       </c>
       <c r="C269" s="1" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="D269" s="1">
         <v>2</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="F269" s="1" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="270" ht="15" customHeight="1" spans="1:6">
       <c r="A270" s="1"/>
       <c r="B270" s="1">
-        <v>20125</v>
+        <v>20121</v>
       </c>
       <c r="C270" s="1" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="D270" s="1">
         <v>2</v>
       </c>
       <c r="E270" s="1" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="F270" s="1" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
     </row>
     <row r="271" ht="15" customHeight="1" spans="1:6">
       <c r="A271" s="1"/>
       <c r="B271" s="1">
-        <v>20126</v>
+        <v>20122</v>
       </c>
       <c r="C271" s="1" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="D271" s="1">
         <v>2</v>
       </c>
       <c r="E271" s="1" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="F271" s="1" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
     </row>
     <row r="272" ht="15" customHeight="1" spans="1:6">
       <c r="A272" s="1"/>
       <c r="B272" s="1">
-        <v>20127</v>
+        <v>20123</v>
       </c>
       <c r="C272" s="1" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="D272" s="1">
         <v>2</v>
       </c>
       <c r="E272" s="1" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="F272" s="1" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
     </row>
     <row r="273" ht="15" customHeight="1" spans="1:6">
       <c r="A273" s="1"/>
       <c r="B273" s="1">
-        <v>30101</v>
+        <v>20124</v>
       </c>
       <c r="C273" s="1" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="D273" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E273" s="1" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="F273" s="1" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
     </row>
     <row r="274" ht="15" customHeight="1" spans="1:6">
       <c r="A274" s="1"/>
       <c r="B274" s="1">
-        <v>30102</v>
+        <v>20125</v>
       </c>
       <c r="C274" s="1" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="D274" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="F274" s="1" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
     </row>
     <row r="275" ht="15" customHeight="1" spans="1:6">
       <c r="A275" s="1"/>
       <c r="B275" s="1">
-        <v>30103</v>
+        <v>20126</v>
       </c>
       <c r="C275" s="1" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="D275" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E275" s="1" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="F275" s="1" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
     </row>
     <row r="276" ht="15" customHeight="1" spans="1:6">
       <c r="A276" s="1"/>
       <c r="B276" s="1">
-        <v>30104</v>
+        <v>20127</v>
       </c>
       <c r="C276" s="1" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="D276" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E276" s="1" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="F276" s="1" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
     </row>
     <row r="277" ht="15" customHeight="1" spans="1:6">
       <c r="A277" s="1"/>
       <c r="B277" s="1">
-        <v>30105</v>
+        <v>30101</v>
       </c>
       <c r="C277" s="1" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="D277" s="1">
         <v>3</v>
       </c>
       <c r="E277" s="1" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="F277" s="1" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
     </row>
     <row r="278" ht="15" customHeight="1" spans="1:6">
       <c r="A278" s="1"/>
       <c r="B278" s="1">
-        <v>30106</v>
+        <v>30102</v>
       </c>
       <c r="C278" s="1" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="D278" s="1">
         <v>3</v>
       </c>
       <c r="E278" s="1" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="F278" s="1" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
     </row>
     <row r="279" ht="15" customHeight="1" spans="1:6">
       <c r="A279" s="1"/>
       <c r="B279" s="1">
-        <v>30107</v>
+        <v>30103</v>
       </c>
       <c r="C279" s="1" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="D279" s="1">
         <v>3</v>
       </c>
       <c r="E279" s="1" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="F279" s="1" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
     </row>
     <row r="280" ht="15" customHeight="1" spans="1:6">
       <c r="A280" s="1"/>
       <c r="B280" s="1">
-        <v>30108</v>
+        <v>30104</v>
       </c>
       <c r="C280" s="1" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="D280" s="1">
         <v>3</v>
       </c>
       <c r="E280" s="1" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="F280" s="1" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
     </row>
     <row r="281" ht="15" customHeight="1" spans="1:6">
       <c r="A281" s="1"/>
       <c r="B281" s="1">
-        <v>30109</v>
+        <v>30105</v>
       </c>
       <c r="C281" s="1" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="D281" s="1">
         <v>3</v>
       </c>
       <c r="E281" s="1" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="F281" s="1" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
     </row>
     <row r="282" ht="15" customHeight="1" spans="1:6">
       <c r="A282" s="1"/>
       <c r="B282" s="1">
-        <v>30110</v>
+        <v>30106</v>
       </c>
       <c r="C282" s="1" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="D282" s="1">
         <v>3</v>
       </c>
       <c r="E282" s="1" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="F282" s="1" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
     </row>
     <row r="283" ht="15" customHeight="1" spans="1:6">
       <c r="A283" s="1"/>
       <c r="B283" s="1">
-        <v>30111</v>
+        <v>30107</v>
       </c>
       <c r="C283" s="1" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="D283" s="1">
         <v>3</v>
       </c>
       <c r="E283" s="1" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="F283" s="1" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
     </row>
     <row r="284" ht="15" customHeight="1" spans="1:6">
       <c r="A284" s="1"/>
       <c r="B284" s="1">
-        <v>30112</v>
+        <v>30108</v>
       </c>
       <c r="C284" s="1" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="D284" s="1">
         <v>3</v>
       </c>
       <c r="E284" s="1" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="F284" s="1" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
     </row>
     <row r="285" ht="15" customHeight="1" spans="1:6">
       <c r="A285" s="1"/>
       <c r="B285" s="1">
-        <v>30113</v>
+        <v>30109</v>
       </c>
       <c r="C285" s="1" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="D285" s="1">
         <v>3</v>
       </c>
       <c r="E285" s="1" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="F285" s="1" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
     </row>
     <row r="286" ht="15" customHeight="1" spans="1:6">
       <c r="A286" s="1"/>
       <c r="B286" s="1">
-        <v>30114</v>
+        <v>30110</v>
       </c>
       <c r="C286" s="1" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="D286" s="1">
         <v>3</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="F286" s="1" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
     </row>
     <row r="287" ht="15" customHeight="1" spans="1:6">
       <c r="A287" s="1"/>
       <c r="B287" s="1">
-        <v>30115</v>
+        <v>30111</v>
       </c>
       <c r="C287" s="1" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="D287" s="1">
         <v>3</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="F287" s="1" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
     </row>
     <row r="288" ht="15" customHeight="1" spans="1:6">
       <c r="A288" s="1"/>
       <c r="B288" s="1">
-        <v>30116</v>
+        <v>30112</v>
       </c>
       <c r="C288" s="1" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="D288" s="1">
         <v>3</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="F288" s="1" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
     </row>
     <row r="289" ht="15" customHeight="1" spans="1:6">
       <c r="A289" s="1"/>
       <c r="B289" s="1">
-        <v>30117</v>
+        <v>30113</v>
       </c>
       <c r="C289" s="1" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="D289" s="1">
         <v>3</v>
       </c>
       <c r="E289" s="1" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="F289" s="1" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
     </row>
     <row r="290" ht="15" customHeight="1" spans="1:6">
       <c r="A290" s="1"/>
       <c r="B290" s="1">
-        <v>30118</v>
+        <v>30114</v>
       </c>
       <c r="C290" s="1" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="D290" s="1">
         <v>3</v>
       </c>
       <c r="E290" s="1" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="F290" s="1" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
     </row>
     <row r="291" ht="15" customHeight="1" spans="1:6">
       <c r="A291" s="1"/>
       <c r="B291" s="1">
-        <v>30119</v>
+        <v>30115</v>
       </c>
       <c r="C291" s="1" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="D291" s="1">
         <v>3</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="F291" s="1" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
     </row>
     <row r="292" ht="15" customHeight="1" spans="1:6">
       <c r="A292" s="1"/>
       <c r="B292" s="1">
-        <v>30120</v>
+        <v>30116</v>
       </c>
       <c r="C292" s="1" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="D292" s="1">
         <v>3</v>
       </c>
       <c r="E292" s="1" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="F292" s="1" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
     </row>
     <row r="293" ht="15" customHeight="1" spans="1:6">
       <c r="A293" s="1"/>
       <c r="B293" s="1">
-        <v>30121</v>
+        <v>30117</v>
       </c>
       <c r="C293" s="1" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="D293" s="1">
         <v>3</v>
       </c>
       <c r="E293" s="1" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="F293" s="1" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
     </row>
     <row r="294" ht="15" customHeight="1" spans="1:6">
       <c r="A294" s="1"/>
       <c r="B294" s="1">
-        <v>30122</v>
+        <v>30118</v>
       </c>
       <c r="C294" s="1" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="D294" s="1">
         <v>3</v>
       </c>
       <c r="E294" s="1" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="F294" s="1" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
     </row>
     <row r="295" ht="15" customHeight="1" spans="1:6">
       <c r="A295" s="1"/>
       <c r="B295" s="1">
-        <v>30123</v>
+        <v>30119</v>
       </c>
       <c r="C295" s="1" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="D295" s="1">
         <v>3</v>
       </c>
       <c r="E295" s="1" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="F295" s="1" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="296" ht="15" customHeight="1" spans="1:6">
       <c r="A296" s="1"/>
       <c r="B296" s="1">
-        <v>30124</v>
+        <v>30120</v>
       </c>
       <c r="C296" s="1" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="D296" s="1">
         <v>3</v>
       </c>
       <c r="E296" s="1" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="F296" s="1" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
     </row>
     <row r="297" ht="15" customHeight="1" spans="1:6">
       <c r="A297" s="1"/>
       <c r="B297" s="1">
-        <v>30125</v>
+        <v>30121</v>
       </c>
       <c r="C297" s="1" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="D297" s="1">
         <v>3</v>
       </c>
       <c r="E297" s="1" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="F297" s="1" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
     </row>
     <row r="298" ht="15" customHeight="1" spans="1:6">
       <c r="A298" s="1"/>
       <c r="B298" s="1">
-        <v>30201</v>
+        <v>30122</v>
       </c>
       <c r="C298" s="1" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="D298" s="1">
         <v>3</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="F298" s="1" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
     </row>
     <row r="299" ht="15" customHeight="1" spans="1:6">
       <c r="A299" s="1"/>
       <c r="B299" s="1">
-        <v>30202</v>
+        <v>30123</v>
       </c>
       <c r="C299" s="1" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="D299" s="1">
         <v>3</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="F299" s="1" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
     </row>
     <row r="300" ht="15" customHeight="1" spans="1:6">
       <c r="A300" s="1"/>
       <c r="B300" s="1">
-        <v>30203</v>
+        <v>30124</v>
       </c>
       <c r="C300" s="1" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="D300" s="1">
         <v>3</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="F300" s="1" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
     </row>
     <row r="301" ht="15" customHeight="1" spans="1:6">
       <c r="A301" s="1"/>
       <c r="B301" s="1">
-        <v>30204</v>
+        <v>30125</v>
       </c>
       <c r="C301" s="1" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="D301" s="1">
         <v>3</v>
       </c>
       <c r="E301" s="1" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="F301" s="1" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
     </row>
     <row r="302" ht="15" customHeight="1" spans="1:6">
       <c r="A302" s="1"/>
       <c r="B302" s="1">
-        <v>30205</v>
+        <v>30201</v>
       </c>
       <c r="C302" s="1" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="D302" s="1">
         <v>3</v>
       </c>
       <c r="E302" s="1" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="F302" s="1" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="303" ht="15" customHeight="1" spans="1:6">
       <c r="A303" s="1"/>
       <c r="B303" s="1">
-        <v>30206</v>
+        <v>30202</v>
       </c>
       <c r="C303" s="1" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="D303" s="1">
         <v>3</v>
       </c>
       <c r="E303" s="1" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="F303" s="1" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
     </row>
     <row r="304" ht="15" customHeight="1" spans="1:6">
       <c r="A304" s="1"/>
       <c r="B304" s="1">
-        <v>30301</v>
+        <v>30203</v>
       </c>
       <c r="C304" s="1" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="D304" s="1">
         <v>3</v>
       </c>
       <c r="E304" s="1" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="F304" s="1" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
     </row>
     <row r="305" ht="15" customHeight="1" spans="1:6">
       <c r="A305" s="1"/>
       <c r="B305" s="1">
-        <v>30302</v>
+        <v>30204</v>
       </c>
       <c r="C305" s="1" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="D305" s="1">
         <v>3</v>
       </c>
       <c r="E305" s="1" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="F305" s="1" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
     </row>
     <row r="306" ht="15" customHeight="1" spans="1:6">
       <c r="A306" s="1"/>
       <c r="B306" s="1">
-        <v>30303</v>
+        <v>30205</v>
       </c>
       <c r="C306" s="1" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="D306" s="1">
         <v>3</v>
       </c>
       <c r="E306" s="1" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="F306" s="1" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
     </row>
     <row r="307" ht="15" customHeight="1" spans="1:6">
       <c r="A307" s="1"/>
       <c r="B307" s="1">
-        <v>30304</v>
+        <v>30206</v>
       </c>
       <c r="C307" s="1" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="D307" s="1">
         <v>3</v>
       </c>
       <c r="E307" s="1" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="F307" s="1" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
     </row>
     <row r="308" ht="15" customHeight="1" spans="1:6">
       <c r="A308" s="1"/>
       <c r="B308" s="1">
-        <v>30305</v>
+        <v>30301</v>
       </c>
       <c r="C308" s="1" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="D308" s="1">
         <v>3</v>
       </c>
       <c r="E308" s="1" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="F308" s="1" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
     </row>
     <row r="309" ht="15" customHeight="1" spans="1:6">
       <c r="A309" s="1"/>
       <c r="B309" s="1">
-        <v>30306</v>
+        <v>30302</v>
       </c>
       <c r="C309" s="1" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="D309" s="1">
         <v>3</v>
       </c>
       <c r="E309" s="1" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="F309" s="1" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
     </row>
     <row r="310" ht="15" customHeight="1" spans="1:6">
       <c r="A310" s="1"/>
       <c r="B310" s="1">
-        <v>30307</v>
+        <v>30303</v>
       </c>
       <c r="C310" s="1" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="D310" s="1">
         <v>3</v>
       </c>
       <c r="E310" s="1" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="F310" s="1" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
     </row>
     <row r="311" ht="15" customHeight="1" spans="1:6">
       <c r="A311" s="1"/>
       <c r="B311" s="1">
-        <v>30308</v>
+        <v>30304</v>
       </c>
       <c r="C311" s="1" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="D311" s="1">
         <v>3</v>
       </c>
       <c r="E311" s="1" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="F311" s="1" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
     </row>
     <row r="312" ht="15" customHeight="1" spans="1:6">
       <c r="A312" s="1"/>
       <c r="B312" s="1">
-        <v>60001</v>
+        <v>30305</v>
       </c>
       <c r="C312" s="1" t="s">
-        <v>637</v>
+        <v>508</v>
       </c>
       <c r="D312" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E312" s="1" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="F312" s="1" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
     </row>
     <row r="313" ht="15" customHeight="1" spans="1:6">
       <c r="A313" s="1"/>
       <c r="B313" s="1">
-        <v>60002</v>
+        <v>30306</v>
       </c>
       <c r="C313" s="1" t="s">
-        <v>637</v>
+        <v>508</v>
       </c>
       <c r="D313" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E313" s="1" t="s">
-        <v>640</v>
+        <v>635</v>
       </c>
       <c r="F313" s="1" t="s">
-        <v>641</v>
+        <v>636</v>
       </c>
     </row>
     <row r="314" ht="15" customHeight="1" spans="1:6">
       <c r="A314" s="1"/>
       <c r="B314" s="1">
-        <v>60003</v>
+        <v>30307</v>
       </c>
       <c r="C314" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="D314" s="1">
+        <v>3</v>
+      </c>
+      <c r="E314" s="1" t="s">
         <v>637</v>
       </c>
-      <c r="D314" s="1">
-        <v>7</v>
-      </c>
-      <c r="E314" s="1" t="s">
-        <v>642</v>
-      </c>
       <c r="F314" s="1" t="s">
-        <v>643</v>
+        <v>638</v>
       </c>
     </row>
     <row r="315" ht="15" customHeight="1" spans="1:6">
       <c r="A315" s="1"/>
       <c r="B315" s="1">
-        <v>60004</v>
+        <v>30308</v>
       </c>
       <c r="C315" s="1" t="s">
-        <v>637</v>
+        <v>508</v>
       </c>
       <c r="D315" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E315" s="1" t="s">
-        <v>644</v>
+        <v>639</v>
       </c>
       <c r="F315" s="1" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
     </row>
     <row r="316" ht="15" customHeight="1" spans="1:6">
       <c r="A316" s="1"/>
       <c r="B316" s="1">
-        <v>60005</v>
+        <v>60001</v>
       </c>
       <c r="C316" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D316" s="1">
         <v>7</v>
       </c>
       <c r="E316" s="1" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="F316" s="1" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
     </row>
     <row r="317" ht="15" customHeight="1" spans="1:6">
       <c r="A317" s="1"/>
       <c r="B317" s="1">
-        <v>60006</v>
+        <v>60002</v>
       </c>
       <c r="C317" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D317" s="1">
         <v>7</v>
       </c>
       <c r="E317" s="1" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="F317" s="1" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
     </row>
     <row r="318" ht="15" customHeight="1" spans="1:6">
       <c r="A318" s="1"/>
       <c r="B318" s="1">
-        <v>60007</v>
+        <v>60003</v>
       </c>
       <c r="C318" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D318" s="1">
         <v>7</v>
       </c>
       <c r="E318" s="1" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="F318" s="1" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
     </row>
     <row r="319" ht="15" customHeight="1" spans="1:6">
       <c r="A319" s="1"/>
       <c r="B319" s="1">
-        <v>60008</v>
+        <v>60004</v>
       </c>
       <c r="C319" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D319" s="1">
         <v>7</v>
       </c>
       <c r="E319" s="1" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="F319" s="1" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
     </row>
     <row r="320" ht="15" customHeight="1" spans="1:6">
       <c r="A320" s="1"/>
       <c r="B320" s="1">
-        <v>60009</v>
+        <v>60005</v>
       </c>
       <c r="C320" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D320" s="1">
         <v>7</v>
       </c>
       <c r="E320" s="1" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="F320" s="1" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
     </row>
     <row r="321" ht="15" customHeight="1" spans="1:6">
       <c r="A321" s="1"/>
       <c r="B321" s="1">
-        <v>60010</v>
+        <v>60006</v>
       </c>
       <c r="C321" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D321" s="1">
         <v>7</v>
       </c>
       <c r="E321" s="1" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="F321" s="1" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
     </row>
     <row r="322" ht="15" customHeight="1" spans="1:6">
       <c r="A322" s="1"/>
       <c r="B322" s="1">
-        <v>60011</v>
+        <v>60007</v>
       </c>
       <c r="C322" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D322" s="1">
         <v>7</v>
       </c>
       <c r="E322" s="1" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="F322" s="1" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
     </row>
     <row r="323" ht="15" customHeight="1" spans="1:6">
       <c r="A323" s="1"/>
       <c r="B323" s="1">
-        <v>60012</v>
+        <v>60008</v>
       </c>
       <c r="C323" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D323" s="1">
         <v>7</v>
       </c>
       <c r="E323" s="1" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="F323" s="1" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
     </row>
     <row r="324" ht="15" customHeight="1" spans="1:6">
       <c r="A324" s="1"/>
       <c r="B324" s="1">
-        <v>60013</v>
+        <v>60009</v>
       </c>
       <c r="C324" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D324" s="1">
         <v>7</v>
       </c>
       <c r="E324" s="1" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="F324" s="1" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
     </row>
     <row r="325" ht="15" customHeight="1" spans="1:6">
       <c r="A325" s="1"/>
       <c r="B325" s="1">
-        <v>60014</v>
+        <v>60010</v>
       </c>
       <c r="C325" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D325" s="1">
         <v>7</v>
       </c>
       <c r="E325" s="1" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="F325" s="1" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
     </row>
     <row r="326" ht="15" customHeight="1" spans="1:6">
       <c r="A326" s="1"/>
       <c r="B326" s="1">
-        <v>60015</v>
+        <v>60011</v>
       </c>
       <c r="C326" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D326" s="1">
         <v>7</v>
       </c>
       <c r="E326" s="1" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="F326" s="1" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
     </row>
     <row r="327" ht="15" customHeight="1" spans="1:6">
       <c r="A327" s="1"/>
       <c r="B327" s="1">
-        <v>60016</v>
+        <v>60012</v>
       </c>
       <c r="C327" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D327" s="1">
         <v>7</v>
       </c>
       <c r="E327" s="1" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="F327" s="1" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
     </row>
     <row r="328" ht="15" customHeight="1" spans="1:6">
       <c r="A328" s="1"/>
       <c r="B328" s="1">
-        <v>60017</v>
+        <v>60013</v>
       </c>
       <c r="C328" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D328" s="1">
         <v>7</v>
       </c>
       <c r="E328" s="1" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="F328" s="1" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
     </row>
     <row r="329" ht="15" customHeight="1" spans="1:6">
       <c r="A329" s="1"/>
       <c r="B329" s="1">
-        <v>60018</v>
+        <v>60014</v>
       </c>
       <c r="C329" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D329" s="1">
         <v>7</v>
       </c>
       <c r="E329" s="1" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="F329" s="1" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
     </row>
     <row r="330" ht="15" customHeight="1" spans="1:6">
       <c r="A330" s="1"/>
       <c r="B330" s="1">
-        <v>60019</v>
+        <v>60015</v>
       </c>
       <c r="C330" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D330" s="1">
         <v>7</v>
       </c>
       <c r="E330" s="1" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="F330" s="1" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
     </row>
     <row r="331" ht="15" customHeight="1" spans="1:6">
       <c r="A331" s="1"/>
       <c r="B331" s="1">
-        <v>60020</v>
+        <v>60016</v>
       </c>
       <c r="C331" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D331" s="1">
         <v>7</v>
       </c>
       <c r="E331" s="1" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
       <c r="F331" s="1" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
     </row>
     <row r="332" ht="15" customHeight="1" spans="1:6">
       <c r="A332" s="1"/>
       <c r="B332" s="1">
-        <v>60021</v>
+        <v>60017</v>
       </c>
       <c r="C332" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D332" s="1">
         <v>7</v>
       </c>
       <c r="E332" s="1" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
       <c r="F332" s="1" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
     </row>
     <row r="333" ht="15" customHeight="1" spans="1:6">
       <c r="A333" s="1"/>
       <c r="B333" s="1">
-        <v>60022</v>
+        <v>60018</v>
       </c>
       <c r="C333" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D333" s="1">
         <v>7</v>
       </c>
       <c r="E333" s="1" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="F333" s="1" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
     </row>
     <row r="334" ht="15" customHeight="1" spans="1:6">
       <c r="A334" s="1"/>
       <c r="B334" s="1">
-        <v>60023</v>
+        <v>60019</v>
       </c>
       <c r="C334" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D334" s="1">
         <v>7</v>
       </c>
       <c r="E334" s="1" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="F334" s="1" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
     </row>
     <row r="335" ht="15" customHeight="1" spans="1:6">
       <c r="A335" s="1"/>
       <c r="B335" s="1">
-        <v>60024</v>
+        <v>60020</v>
       </c>
       <c r="C335" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D335" s="1">
         <v>7</v>
       </c>
       <c r="E335" s="1" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="F335" s="1" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
     </row>
     <row r="336" ht="15" customHeight="1" spans="1:6">
       <c r="A336" s="1"/>
       <c r="B336" s="1">
-        <v>60025</v>
+        <v>60021</v>
       </c>
       <c r="C336" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D336" s="1">
         <v>7</v>
       </c>
       <c r="E336" s="1" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="F336" s="1" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
     </row>
     <row r="337" ht="15" customHeight="1" spans="1:6">
       <c r="A337" s="1"/>
       <c r="B337" s="1">
-        <v>60026</v>
+        <v>60022</v>
       </c>
       <c r="C337" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D337" s="1">
         <v>7</v>
       </c>
       <c r="E337" s="1" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="F337" s="1" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
     </row>
     <row r="338" ht="15" customHeight="1" spans="1:6">
       <c r="A338" s="1"/>
       <c r="B338" s="1">
-        <v>60027</v>
+        <v>60023</v>
       </c>
       <c r="C338" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D338" s="1">
         <v>7</v>
       </c>
       <c r="E338" s="1" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="F338" s="1" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
     </row>
     <row r="339" ht="15" customHeight="1" spans="1:6">
       <c r="A339" s="1"/>
       <c r="B339" s="1">
-        <v>60028</v>
+        <v>60024</v>
       </c>
       <c r="C339" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D339" s="1">
         <v>7</v>
       </c>
       <c r="E339" s="1" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="F339" s="1" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
     </row>
     <row r="340" ht="15" customHeight="1" spans="1:6">
       <c r="A340" s="1"/>
       <c r="B340" s="1">
-        <v>60029</v>
+        <v>60025</v>
       </c>
       <c r="C340" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D340" s="1">
         <v>7</v>
       </c>
       <c r="E340" s="1" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="F340" s="1" t="s">
-        <v>695</v>
+        <v>691</v>
       </c>
     </row>
     <row r="341" ht="15" customHeight="1" spans="1:6">
       <c r="A341" s="1"/>
       <c r="B341" s="1">
-        <v>60030</v>
+        <v>60026</v>
       </c>
       <c r="C341" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D341" s="1">
         <v>7</v>
       </c>
       <c r="E341" s="1" t="s">
-        <v>696</v>
+        <v>692</v>
       </c>
       <c r="F341" s="1" t="s">
-        <v>697</v>
+        <v>693</v>
       </c>
     </row>
     <row r="342" ht="15" customHeight="1" spans="1:6">
       <c r="A342" s="1"/>
       <c r="B342" s="1">
-        <v>60031</v>
+        <v>60027</v>
       </c>
       <c r="C342" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D342" s="1">
         <v>7</v>
       </c>
       <c r="E342" s="1" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="F342" s="1" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
     </row>
     <row r="343" ht="15" customHeight="1" spans="1:6">
       <c r="A343" s="1"/>
       <c r="B343" s="1">
-        <v>60032</v>
+        <v>60028</v>
       </c>
       <c r="C343" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D343" s="1">
         <v>7</v>
       </c>
       <c r="E343" s="1" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="F343" s="1" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
     </row>
     <row r="344" ht="15" customHeight="1" spans="1:6">
       <c r="A344" s="1"/>
       <c r="B344" s="1">
-        <v>60033</v>
+        <v>60029</v>
       </c>
       <c r="C344" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D344" s="1">
         <v>7</v>
       </c>
       <c r="E344" s="1" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="F344" s="1" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
     </row>
     <row r="345" ht="15" customHeight="1" spans="1:6">
       <c r="A345" s="1"/>
       <c r="B345" s="1">
-        <v>60034</v>
+        <v>60030</v>
       </c>
       <c r="C345" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D345" s="1">
         <v>7</v>
       </c>
       <c r="E345" s="1" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="F345" s="1" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
     </row>
     <row r="346" ht="15" customHeight="1" spans="1:6">
       <c r="A346" s="1"/>
       <c r="B346" s="1">
-        <v>60035</v>
+        <v>60031</v>
       </c>
       <c r="C346" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D346" s="1">
         <v>7</v>
       </c>
       <c r="E346" s="1" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="F346" s="1" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="347" ht="15" customHeight="1" spans="1:6">
       <c r="A347" s="1"/>
       <c r="B347" s="1">
-        <v>60036</v>
+        <v>60032</v>
       </c>
       <c r="C347" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D347" s="1">
         <v>7</v>
       </c>
       <c r="E347" s="1" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="F347" s="1" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
     </row>
     <row r="348" ht="15" customHeight="1" spans="1:6">
       <c r="A348" s="1"/>
       <c r="B348" s="1">
-        <v>60037</v>
+        <v>60033</v>
       </c>
       <c r="C348" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D348" s="1">
         <v>7</v>
       </c>
       <c r="E348" s="1" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="F348" s="1" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
     </row>
     <row r="349" ht="15" customHeight="1" spans="1:6">
       <c r="A349" s="1"/>
       <c r="B349" s="1">
-        <v>60038</v>
+        <v>60034</v>
       </c>
       <c r="C349" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D349" s="1">
         <v>7</v>
       </c>
       <c r="E349" s="1" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="F349" s="1" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
     </row>
     <row r="350" ht="15" customHeight="1" spans="1:6">
       <c r="A350" s="1"/>
       <c r="B350" s="1">
-        <v>60039</v>
+        <v>60035</v>
       </c>
       <c r="C350" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D350" s="1">
         <v>7</v>
       </c>
       <c r="E350" s="1" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="F350" s="1" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
     </row>
     <row r="351" ht="15" customHeight="1" spans="1:6">
       <c r="A351" s="1"/>
       <c r="B351" s="1">
-        <v>60040</v>
+        <v>60036</v>
       </c>
       <c r="C351" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D351" s="1">
         <v>7</v>
       </c>
       <c r="E351" s="1" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="F351" s="1" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
     </row>
     <row r="352" ht="15" customHeight="1" spans="1:6">
       <c r="A352" s="1"/>
       <c r="B352" s="1">
-        <v>60041</v>
+        <v>60037</v>
       </c>
       <c r="C352" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D352" s="1">
         <v>7</v>
       </c>
       <c r="E352" s="1" t="s">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="F352" s="1" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
     </row>
     <row r="353" ht="15" customHeight="1" spans="1:6">
       <c r="A353" s="1"/>
       <c r="B353" s="1">
-        <v>60042</v>
+        <v>60038</v>
       </c>
       <c r="C353" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D353" s="1">
         <v>7</v>
       </c>
       <c r="E353" s="1" t="s">
-        <v>720</v>
+        <v>716</v>
       </c>
       <c r="F353" s="1" t="s">
-        <v>721</v>
+        <v>717</v>
       </c>
     </row>
     <row r="354" ht="15" customHeight="1" spans="1:6">
       <c r="A354" s="1"/>
       <c r="B354" s="1">
-        <v>60043</v>
+        <v>60039</v>
       </c>
       <c r="C354" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D354" s="1">
         <v>7</v>
       </c>
       <c r="E354" s="1" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="F354" s="1" t="s">
-        <v>723</v>
+        <v>719</v>
       </c>
     </row>
     <row r="355" ht="15" customHeight="1" spans="1:6">
       <c r="A355" s="1"/>
       <c r="B355" s="1">
-        <v>60044</v>
+        <v>60040</v>
       </c>
       <c r="C355" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D355" s="1">
         <v>7</v>
       </c>
       <c r="E355" s="1" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="F355" s="1" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
     </row>
     <row r="356" ht="15" customHeight="1" spans="1:6">
       <c r="A356" s="1"/>
       <c r="B356" s="1">
-        <v>60045</v>
+        <v>60041</v>
       </c>
       <c r="C356" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D356" s="1">
         <v>7</v>
       </c>
       <c r="E356" s="1" t="s">
-        <v>726</v>
+        <v>722</v>
       </c>
       <c r="F356" s="1" t="s">
-        <v>727</v>
+        <v>723</v>
       </c>
     </row>
     <row r="357" ht="15" customHeight="1" spans="1:6">
       <c r="A357" s="1"/>
       <c r="B357" s="1">
-        <v>60046</v>
+        <v>60042</v>
       </c>
       <c r="C357" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D357" s="1">
         <v>7</v>
       </c>
       <c r="E357" s="1" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
       <c r="F357" s="1" t="s">
-        <v>729</v>
+        <v>725</v>
       </c>
     </row>
     <row r="358" ht="15" customHeight="1" spans="1:6">
       <c r="A358" s="1"/>
       <c r="B358" s="1">
-        <v>60047</v>
+        <v>60043</v>
       </c>
       <c r="C358" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D358" s="1">
         <v>7</v>
       </c>
       <c r="E358" s="1" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="F358" s="1" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
     </row>
     <row r="359" ht="15" customHeight="1" spans="1:6">
       <c r="A359" s="1"/>
       <c r="B359" s="1">
-        <v>60048</v>
+        <v>60044</v>
       </c>
       <c r="C359" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D359" s="1">
         <v>7</v>
       </c>
       <c r="E359" s="1" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
       <c r="F359" s="1" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
     </row>
     <row r="360" ht="15" customHeight="1" spans="1:6">
       <c r="A360" s="1"/>
       <c r="B360" s="1">
-        <v>60049</v>
+        <v>60045</v>
       </c>
       <c r="C360" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D360" s="1">
         <v>7</v>
       </c>
       <c r="E360" s="1" t="s">
-        <v>734</v>
+        <v>730</v>
       </c>
       <c r="F360" s="1" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
     </row>
     <row r="361" ht="15" customHeight="1" spans="1:6">
       <c r="A361" s="1"/>
       <c r="B361" s="1">
-        <v>60050</v>
+        <v>60046</v>
       </c>
       <c r="C361" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D361" s="1">
         <v>7</v>
       </c>
       <c r="E361" s="1" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
       <c r="F361" s="1" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
     </row>
     <row r="362" ht="15" customHeight="1" spans="1:6">
       <c r="A362" s="1"/>
       <c r="B362" s="1">
-        <v>60051</v>
+        <v>60047</v>
       </c>
       <c r="C362" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D362" s="1">
         <v>7</v>
       </c>
       <c r="E362" s="1" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="F362" s="1" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
     </row>
     <row r="363" ht="15" customHeight="1" spans="1:6">
       <c r="A363" s="1"/>
       <c r="B363" s="1">
-        <v>60052</v>
+        <v>60048</v>
       </c>
       <c r="C363" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D363" s="1">
         <v>7</v>
       </c>
       <c r="E363" s="1" t="s">
-        <v>740</v>
+        <v>736</v>
       </c>
       <c r="F363" s="1" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
     </row>
     <row r="364" ht="15" customHeight="1" spans="1:6">
       <c r="A364" s="1"/>
       <c r="B364" s="1">
-        <v>60053</v>
+        <v>60049</v>
       </c>
       <c r="C364" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D364" s="1">
         <v>7</v>
       </c>
       <c r="E364" s="1" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="F364" s="1" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
     </row>
     <row r="365" ht="15" customHeight="1" spans="1:6">
       <c r="A365" s="1"/>
       <c r="B365" s="1">
-        <v>60054</v>
+        <v>60050</v>
       </c>
       <c r="C365" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D365" s="1">
         <v>7</v>
       </c>
       <c r="E365" s="1" t="s">
-        <v>744</v>
+        <v>740</v>
       </c>
       <c r="F365" s="1" t="s">
-        <v>745</v>
+        <v>741</v>
       </c>
     </row>
     <row r="366" ht="15" customHeight="1" spans="1:6">
       <c r="A366" s="1"/>
       <c r="B366" s="1">
-        <v>60055</v>
+        <v>60051</v>
       </c>
       <c r="C366" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D366" s="1">
         <v>7</v>
       </c>
       <c r="E366" s="1" t="s">
-        <v>746</v>
+        <v>742</v>
       </c>
       <c r="F366" s="1" t="s">
-        <v>747</v>
+        <v>743</v>
       </c>
     </row>
     <row r="367" ht="15" customHeight="1" spans="1:6">
       <c r="A367" s="1"/>
       <c r="B367" s="1">
-        <v>60056</v>
+        <v>60052</v>
       </c>
       <c r="C367" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D367" s="1">
         <v>7</v>
       </c>
       <c r="E367" s="1" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="F367" s="1" t="s">
-        <v>749</v>
+        <v>745</v>
       </c>
     </row>
     <row r="368" ht="15" customHeight="1" spans="1:6">
       <c r="A368" s="1"/>
       <c r="B368" s="1">
-        <v>60057</v>
+        <v>60053</v>
       </c>
       <c r="C368" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D368" s="1">
         <v>7</v>
       </c>
       <c r="E368" s="1" t="s">
-        <v>750</v>
+        <v>746</v>
       </c>
       <c r="F368" s="1" t="s">
-        <v>751</v>
+        <v>747</v>
       </c>
     </row>
     <row r="369" ht="15" customHeight="1" spans="1:6">
       <c r="A369" s="1"/>
       <c r="B369" s="1">
-        <v>60058</v>
+        <v>60054</v>
       </c>
       <c r="C369" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D369" s="1">
         <v>7</v>
       </c>
       <c r="E369" s="1" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="F369" s="1" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
     </row>
     <row r="370" ht="15" customHeight="1" spans="1:6">
       <c r="A370" s="1"/>
       <c r="B370" s="1">
-        <v>60059</v>
+        <v>60055</v>
       </c>
       <c r="C370" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D370" s="1">
         <v>7</v>
       </c>
       <c r="E370" s="1" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
       <c r="F370" s="1" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
     </row>
     <row r="371" ht="15" customHeight="1" spans="1:6">
       <c r="A371" s="1"/>
       <c r="B371" s="1">
-        <v>60060</v>
+        <v>60056</v>
       </c>
       <c r="C371" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D371" s="1">
         <v>7</v>
       </c>
       <c r="E371" s="1" t="s">
-        <v>756</v>
+        <v>752</v>
       </c>
       <c r="F371" s="1" t="s">
-        <v>757</v>
+        <v>753</v>
       </c>
     </row>
     <row r="372" ht="15" customHeight="1" spans="1:6">
       <c r="A372" s="1"/>
       <c r="B372" s="1">
-        <v>60061</v>
+        <v>60057</v>
       </c>
       <c r="C372" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D372" s="1">
         <v>7</v>
       </c>
       <c r="E372" s="1" t="s">
-        <v>758</v>
+        <v>754</v>
       </c>
       <c r="F372" s="1" t="s">
-        <v>759</v>
+        <v>755</v>
       </c>
     </row>
     <row r="373" ht="15" customHeight="1" spans="1:6">
       <c r="A373" s="1"/>
       <c r="B373" s="1">
-        <v>60062</v>
+        <v>60058</v>
       </c>
       <c r="C373" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D373" s="1">
         <v>7</v>
       </c>
       <c r="E373" s="1" t="s">
-        <v>760</v>
+        <v>756</v>
       </c>
       <c r="F373" s="1" t="s">
-        <v>761</v>
+        <v>757</v>
       </c>
     </row>
     <row r="374" ht="15" customHeight="1" spans="1:6">
       <c r="A374" s="1"/>
       <c r="B374" s="1">
-        <v>60063</v>
+        <v>60059</v>
       </c>
       <c r="C374" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D374" s="1">
         <v>7</v>
       </c>
       <c r="E374" s="1" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="F374" s="1" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
     </row>
     <row r="375" ht="15" customHeight="1" spans="1:6">
       <c r="A375" s="1"/>
       <c r="B375" s="1">
-        <v>60064</v>
+        <v>60060</v>
       </c>
       <c r="C375" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D375" s="1">
         <v>7</v>
       </c>
       <c r="E375" s="1" t="s">
-        <v>764</v>
+        <v>760</v>
       </c>
       <c r="F375" s="1" t="s">
-        <v>765</v>
+        <v>761</v>
       </c>
     </row>
     <row r="376" ht="15" customHeight="1" spans="1:6">
       <c r="A376" s="1"/>
       <c r="B376" s="1">
-        <v>60065</v>
+        <v>60061</v>
       </c>
       <c r="C376" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D376" s="1">
         <v>7</v>
       </c>
       <c r="E376" s="1" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
       <c r="F376" s="1" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
     </row>
     <row r="377" ht="15" customHeight="1" spans="1:6">
       <c r="A377" s="1"/>
       <c r="B377" s="1">
-        <v>60066</v>
+        <v>60062</v>
       </c>
       <c r="C377" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D377" s="1">
         <v>7</v>
       </c>
       <c r="E377" s="1" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="F377" s="1" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
     </row>
     <row r="378" ht="15" customHeight="1" spans="1:6">
       <c r="A378" s="1"/>
       <c r="B378" s="1">
-        <v>60067</v>
+        <v>60063</v>
       </c>
       <c r="C378" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D378" s="1">
         <v>7</v>
       </c>
       <c r="E378" s="1" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
       <c r="F378" s="1" t="s">
-        <v>771</v>
+        <v>767</v>
       </c>
     </row>
     <row r="379" ht="15" customHeight="1" spans="1:6">
       <c r="A379" s="1"/>
       <c r="B379" s="1">
-        <v>60068</v>
+        <v>60064</v>
       </c>
       <c r="C379" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D379" s="1">
         <v>7</v>
       </c>
       <c r="E379" s="1" t="s">
-        <v>772</v>
+        <v>768</v>
       </c>
       <c r="F379" s="1" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
     </row>
     <row r="380" ht="15" customHeight="1" spans="1:6">
       <c r="A380" s="1"/>
       <c r="B380" s="1">
-        <v>60069</v>
+        <v>60065</v>
       </c>
       <c r="C380" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D380" s="1">
         <v>7</v>
       </c>
       <c r="E380" s="1" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="F380" s="1" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
     </row>
     <row r="381" ht="15" customHeight="1" spans="1:6">
       <c r="A381" s="1"/>
       <c r="B381" s="1">
-        <v>60070</v>
+        <v>60066</v>
       </c>
       <c r="C381" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D381" s="1">
         <v>7</v>
       </c>
       <c r="E381" s="1" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="F381" s="1" t="s">
-        <v>777</v>
+        <v>773</v>
       </c>
     </row>
     <row r="382" ht="15" customHeight="1" spans="1:6">
       <c r="A382" s="1"/>
       <c r="B382" s="1">
-        <v>60071</v>
+        <v>60067</v>
       </c>
       <c r="C382" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D382" s="1">
         <v>7</v>
       </c>
       <c r="E382" s="1" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
       <c r="F382" s="1" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
     </row>
     <row r="383" ht="15" customHeight="1" spans="1:6">
       <c r="A383" s="1"/>
       <c r="B383" s="1">
-        <v>60072</v>
+        <v>60068</v>
       </c>
       <c r="C383" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D383" s="1">
         <v>7</v>
       </c>
       <c r="E383" s="1" t="s">
-        <v>780</v>
+        <v>776</v>
       </c>
       <c r="F383" s="1" t="s">
-        <v>781</v>
+        <v>777</v>
       </c>
     </row>
     <row r="384" ht="15" customHeight="1" spans="1:6">
       <c r="A384" s="1"/>
       <c r="B384" s="1">
-        <v>60073</v>
+        <v>60069</v>
       </c>
       <c r="C384" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D384" s="1">
         <v>7</v>
       </c>
       <c r="E384" s="1" t="s">
-        <v>782</v>
+        <v>778</v>
       </c>
       <c r="F384" s="1" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
     </row>
     <row r="385" ht="15" customHeight="1" spans="1:6">
       <c r="A385" s="1"/>
       <c r="B385" s="1">
-        <v>60074</v>
+        <v>60070</v>
       </c>
       <c r="C385" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D385" s="1">
         <v>7</v>
       </c>
       <c r="E385" s="1" t="s">
-        <v>784</v>
+        <v>780</v>
       </c>
       <c r="F385" s="1" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
     </row>
     <row r="386" ht="15" customHeight="1" spans="1:6">
       <c r="A386" s="1"/>
       <c r="B386" s="1">
-        <v>60075</v>
+        <v>60071</v>
       </c>
       <c r="C386" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D386" s="1">
         <v>7</v>
       </c>
       <c r="E386" s="1" t="s">
-        <v>786</v>
+        <v>782</v>
       </c>
       <c r="F386" s="1" t="s">
-        <v>787</v>
+        <v>783</v>
       </c>
     </row>
     <row r="387" ht="15" customHeight="1" spans="1:6">
       <c r="A387" s="1"/>
       <c r="B387" s="1">
-        <v>60076</v>
+        <v>60072</v>
       </c>
       <c r="C387" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D387" s="1">
         <v>7</v>
       </c>
       <c r="E387" s="1" t="s">
-        <v>788</v>
+        <v>784</v>
       </c>
       <c r="F387" s="1" t="s">
-        <v>789</v>
+        <v>785</v>
       </c>
     </row>
     <row r="388" ht="15" customHeight="1" spans="1:6">
       <c r="A388" s="1"/>
       <c r="B388" s="1">
-        <v>60077</v>
+        <v>60073</v>
       </c>
       <c r="C388" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D388" s="1">
         <v>7</v>
       </c>
       <c r="E388" s="1" t="s">
-        <v>790</v>
+        <v>786</v>
       </c>
       <c r="F388" s="1" t="s">
-        <v>791</v>
+        <v>787</v>
       </c>
     </row>
     <row r="389" ht="15" customHeight="1" spans="1:6">
       <c r="A389" s="1"/>
       <c r="B389" s="1">
-        <v>60078</v>
+        <v>60074</v>
       </c>
       <c r="C389" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D389" s="1">
         <v>7</v>
       </c>
       <c r="E389" s="1" t="s">
-        <v>792</v>
+        <v>788</v>
       </c>
       <c r="F389" s="1" t="s">
-        <v>793</v>
+        <v>789</v>
       </c>
     </row>
     <row r="390" ht="15" customHeight="1" spans="1:6">
       <c r="A390" s="1"/>
       <c r="B390" s="1">
-        <v>60079</v>
+        <v>60075</v>
       </c>
       <c r="C390" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D390" s="1">
         <v>7</v>
       </c>
       <c r="E390" s="1" t="s">
-        <v>794</v>
+        <v>790</v>
       </c>
       <c r="F390" s="1" t="s">
-        <v>795</v>
+        <v>791</v>
       </c>
     </row>
     <row r="391" ht="15" customHeight="1" spans="1:6">
       <c r="A391" s="1"/>
       <c r="B391" s="1">
-        <v>60080</v>
+        <v>60076</v>
       </c>
       <c r="C391" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D391" s="1">
         <v>7</v>
       </c>
       <c r="E391" s="1" t="s">
-        <v>796</v>
+        <v>792</v>
       </c>
       <c r="F391" s="1" t="s">
-        <v>797</v>
+        <v>793</v>
       </c>
     </row>
     <row r="392" ht="15" customHeight="1" spans="1:6">
       <c r="A392" s="1"/>
       <c r="B392" s="1">
-        <v>60081</v>
+        <v>60077</v>
       </c>
       <c r="C392" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D392" s="1">
         <v>7</v>
       </c>
       <c r="E392" s="1" t="s">
-        <v>798</v>
+        <v>794</v>
       </c>
       <c r="F392" s="1" t="s">
-        <v>799</v>
+        <v>795</v>
       </c>
     </row>
     <row r="393" ht="15" customHeight="1" spans="1:6">
       <c r="A393" s="1"/>
       <c r="B393" s="1">
-        <v>60082</v>
+        <v>60078</v>
       </c>
       <c r="C393" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D393" s="1">
         <v>7</v>
       </c>
       <c r="E393" s="1" t="s">
-        <v>800</v>
+        <v>796</v>
       </c>
       <c r="F393" s="1" t="s">
-        <v>801</v>
+        <v>797</v>
       </c>
     </row>
     <row r="394" ht="15" customHeight="1" spans="1:6">
       <c r="A394" s="1"/>
       <c r="B394" s="1">
-        <v>60083</v>
+        <v>60079</v>
       </c>
       <c r="C394" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D394" s="1">
         <v>7</v>
       </c>
       <c r="E394" s="1" t="s">
+        <v>798</v>
+      </c>
+      <c r="F394" s="1" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="395" ht="15" customHeight="1" spans="1:6">
+      <c r="A395" s="1"/>
+      <c r="B395" s="1">
+        <v>60080</v>
+      </c>
+      <c r="C395" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="D395" s="1">
+        <v>7</v>
+      </c>
+      <c r="E395" s="1" t="s">
+        <v>800</v>
+      </c>
+      <c r="F395" s="1" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="396" ht="15" customHeight="1" spans="1:6">
+      <c r="A396" s="1"/>
+      <c r="B396" s="1">
+        <v>60081</v>
+      </c>
+      <c r="C396" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="D396" s="1">
+        <v>7</v>
+      </c>
+      <c r="E396" s="1" t="s">
         <v>802</v>
       </c>
-      <c r="F394" s="1" t="s">
+      <c r="F396" s="1" t="s">
         <v>803</v>
+      </c>
+    </row>
+    <row r="397" ht="15" customHeight="1" spans="1:6">
+      <c r="A397" s="1"/>
+      <c r="B397" s="1">
+        <v>60082</v>
+      </c>
+      <c r="C397" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="D397" s="1">
+        <v>7</v>
+      </c>
+      <c r="E397" s="1" t="s">
+        <v>804</v>
+      </c>
+      <c r="F397" s="1" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="398" ht="15" customHeight="1" spans="1:6">
+      <c r="A398" s="1"/>
+      <c r="B398" s="1">
+        <v>60083</v>
+      </c>
+      <c r="C398" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="D398" s="1">
+        <v>7</v>
+      </c>
+      <c r="E398" s="1" t="s">
+        <v>806</v>
+      </c>
+      <c r="F398" s="1" t="s">
+        <v>807</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/DataTables/ResourceConfigTable.xlsx
+++ b/AAAGameData/DataTables/ResourceConfigTable.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1013" uniqueCount="808">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1011" uniqueCount="806">
   <si>
     <t>#</t>
   </si>
@@ -369,12 +369,6 @@
   </si>
   <si>
     <t>棋子-恶魂图标</t>
-  </si>
-  <si>
-    <t>Chess/靶子.png</t>
-  </si>
-  <si>
-    <t>棋子-靶子图标</t>
   </si>
   <si>
     <t>Buff/1.png</t>
@@ -3415,7 +3409,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F398"/>
+  <dimension ref="A1:F397"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -4300,7 +4294,7 @@
     <row r="55" ht="15" customHeight="1" spans="1:6">
       <c r="A55" s="1"/>
       <c r="B55" s="1">
-        <v>1399</v>
+        <v>1401</v>
       </c>
       <c r="C55" s="1"/>
       <c r="D55" s="1">
@@ -4316,7 +4310,7 @@
     <row r="56" ht="15" customHeight="1" spans="1:6">
       <c r="A56" s="1"/>
       <c r="B56" s="1">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="C56" s="1"/>
       <c r="D56" s="1">
@@ -4332,7 +4326,7 @@
     <row r="57" ht="15" customHeight="1" spans="1:6">
       <c r="A57" s="1"/>
       <c r="B57" s="1">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="C57" s="1"/>
       <c r="D57" s="1">
@@ -4348,7 +4342,7 @@
     <row r="58" ht="15" customHeight="1" spans="1:6">
       <c r="A58" s="1"/>
       <c r="B58" s="1">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="C58" s="1"/>
       <c r="D58" s="1">
@@ -4364,7 +4358,7 @@
     <row r="59" ht="15" customHeight="1" spans="1:6">
       <c r="A59" s="1"/>
       <c r="B59" s="1">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="C59" s="1"/>
       <c r="D59" s="1">
@@ -4380,7 +4374,7 @@
     <row r="60" ht="15" customHeight="1" spans="1:6">
       <c r="A60" s="1"/>
       <c r="B60" s="1">
-        <v>1405</v>
+        <v>1406</v>
       </c>
       <c r="C60" s="1"/>
       <c r="D60" s="1">
@@ -4396,26 +4390,28 @@
     <row r="61" ht="15" customHeight="1" spans="1:6">
       <c r="A61" s="1"/>
       <c r="B61" s="1">
-        <v>1406</v>
-      </c>
-      <c r="C61" s="1"/>
+        <v>1407</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>126</v>
+      </c>
       <c r="D61" s="1">
         <v>1</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="62" ht="15" customHeight="1" spans="1:6">
       <c r="A62" s="1"/>
       <c r="B62" s="1">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D62" s="1">
         <v>1</v>
@@ -4430,10 +4426,10 @@
     <row r="63" ht="15" customHeight="1" spans="1:6">
       <c r="A63" s="1"/>
       <c r="B63" s="1">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D63" s="1">
         <v>1</v>
@@ -4448,10 +4444,10 @@
     <row r="64" ht="15" customHeight="1" spans="1:6">
       <c r="A64" s="1"/>
       <c r="B64" s="1">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D64" s="1">
         <v>1</v>
@@ -4466,10 +4462,10 @@
     <row r="65" ht="15" customHeight="1" spans="1:6">
       <c r="A65" s="1"/>
       <c r="B65" s="1">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D65" s="1">
         <v>1</v>
@@ -4484,11 +4480,9 @@
     <row r="66" ht="15" customHeight="1" spans="1:6">
       <c r="A66" s="1"/>
       <c r="B66" s="1">
-        <v>1411</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>128</v>
-      </c>
+        <v>1501</v>
+      </c>
+      <c r="C66" s="1"/>
       <c r="D66" s="1">
         <v>1</v>
       </c>
@@ -4502,7 +4496,7 @@
     <row r="67" ht="15" customHeight="1" spans="1:6">
       <c r="A67" s="1"/>
       <c r="B67" s="1">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="C67" s="1"/>
       <c r="D67" s="1">
@@ -4518,7 +4512,7 @@
     <row r="68" ht="15" customHeight="1" spans="1:6">
       <c r="A68" s="1"/>
       <c r="B68" s="1">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="C68" s="1"/>
       <c r="D68" s="1">
@@ -4534,7 +4528,7 @@
     <row r="69" ht="15" customHeight="1" spans="1:6">
       <c r="A69" s="1"/>
       <c r="B69" s="1">
-        <v>1503</v>
+        <v>1601</v>
       </c>
       <c r="C69" s="1"/>
       <c r="D69" s="1">
@@ -4550,7 +4544,7 @@
     <row r="70" ht="15" customHeight="1" spans="1:6">
       <c r="A70" s="1"/>
       <c r="B70" s="1">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="C70" s="1"/>
       <c r="D70" s="1">
@@ -4566,7 +4560,7 @@
     <row r="71" ht="15" customHeight="1" spans="1:6">
       <c r="A71" s="1"/>
       <c r="B71" s="1">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="C71" s="1"/>
       <c r="D71" s="1">
@@ -4582,7 +4576,7 @@
     <row r="72" ht="15" customHeight="1" spans="1:6">
       <c r="A72" s="1"/>
       <c r="B72" s="1">
-        <v>1603</v>
+        <v>1701</v>
       </c>
       <c r="C72" s="1"/>
       <c r="D72" s="1">
@@ -4598,7 +4592,7 @@
     <row r="73" ht="15" customHeight="1" spans="1:6">
       <c r="A73" s="1"/>
       <c r="B73" s="1">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="C73" s="1"/>
       <c r="D73" s="1">
@@ -4614,7 +4608,7 @@
     <row r="74" ht="15" customHeight="1" spans="1:6">
       <c r="A74" s="1"/>
       <c r="B74" s="1">
-        <v>1702</v>
+        <v>1703</v>
       </c>
       <c r="C74" s="1"/>
       <c r="D74" s="1">
@@ -4630,7 +4624,7 @@
     <row r="75" ht="15" customHeight="1" spans="1:6">
       <c r="A75" s="1"/>
       <c r="B75" s="1">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="C75" s="1"/>
       <c r="D75" s="1">
@@ -4646,7 +4640,7 @@
     <row r="76" ht="15" customHeight="1" spans="1:6">
       <c r="A76" s="1"/>
       <c r="B76" s="1">
-        <v>1704</v>
+        <v>1705</v>
       </c>
       <c r="C76" s="1"/>
       <c r="D76" s="1">
@@ -4662,7 +4656,7 @@
     <row r="77" ht="15" customHeight="1" spans="1:6">
       <c r="A77" s="1"/>
       <c r="B77" s="1">
-        <v>1705</v>
+        <v>1706</v>
       </c>
       <c r="C77" s="1"/>
       <c r="D77" s="1">
@@ -4678,7 +4672,7 @@
     <row r="78" ht="15" customHeight="1" spans="1:6">
       <c r="A78" s="1"/>
       <c r="B78" s="1">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="C78" s="1"/>
       <c r="D78" s="1">
@@ -4694,7 +4688,7 @@
     <row r="79" ht="15" customHeight="1" spans="1:6">
       <c r="A79" s="1"/>
       <c r="B79" s="1">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="C79" s="1"/>
       <c r="D79" s="1">
@@ -4710,7 +4704,7 @@
     <row r="80" ht="15" customHeight="1" spans="1:6">
       <c r="A80" s="1"/>
       <c r="B80" s="1">
-        <v>1708</v>
+        <v>1711</v>
       </c>
       <c r="C80" s="1"/>
       <c r="D80" s="1">
@@ -4726,7 +4720,7 @@
     <row r="81" ht="15" customHeight="1" spans="1:6">
       <c r="A81" s="1"/>
       <c r="B81" s="1">
-        <v>1711</v>
+        <v>1712</v>
       </c>
       <c r="C81" s="1"/>
       <c r="D81" s="1">
@@ -4742,26 +4736,28 @@
     <row r="82" ht="15" customHeight="1" spans="1:6">
       <c r="A82" s="1"/>
       <c r="B82" s="1">
-        <v>1712</v>
-      </c>
-      <c r="C82" s="1"/>
+        <v>1801</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>169</v>
+      </c>
       <c r="D82" s="1">
         <v>1</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1" spans="1:6">
       <c r="A83" s="1"/>
       <c r="B83" s="1">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D83" s="1">
         <v>1</v>
@@ -4776,10 +4772,10 @@
     <row r="84" ht="15" customHeight="1" spans="1:6">
       <c r="A84" s="1"/>
       <c r="B84" s="1">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D84" s="1">
         <v>1</v>
@@ -4794,10 +4790,10 @@
     <row r="85" ht="15" customHeight="1" spans="1:6">
       <c r="A85" s="1"/>
       <c r="B85" s="1">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D85" s="1">
         <v>1</v>
@@ -4812,10 +4808,10 @@
     <row r="86" ht="15" customHeight="1" spans="1:6">
       <c r="A86" s="1"/>
       <c r="B86" s="1">
-        <v>1804</v>
+        <v>1805</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D86" s="1">
         <v>1</v>
@@ -4830,10 +4826,10 @@
     <row r="87" ht="15" customHeight="1" spans="1:6">
       <c r="A87" s="1"/>
       <c r="B87" s="1">
-        <v>1805</v>
+        <v>1806</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D87" s="1">
         <v>1</v>
@@ -4848,10 +4844,10 @@
     <row r="88" ht="15" customHeight="1" spans="1:6">
       <c r="A88" s="1"/>
       <c r="B88" s="1">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D88" s="1">
         <v>1</v>
@@ -4866,10 +4862,10 @@
     <row r="89" ht="15" customHeight="1" spans="1:6">
       <c r="A89" s="1"/>
       <c r="B89" s="1">
-        <v>1807</v>
+        <v>1808</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D89" s="1">
         <v>1</v>
@@ -4884,10 +4880,10 @@
     <row r="90" ht="15" customHeight="1" spans="1:6">
       <c r="A90" s="1"/>
       <c r="B90" s="1">
-        <v>1808</v>
+        <v>1831</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D90" s="1">
         <v>1</v>
@@ -4902,10 +4898,10 @@
     <row r="91" ht="15" customHeight="1" spans="1:6">
       <c r="A91" s="1"/>
       <c r="B91" s="1">
-        <v>1831</v>
+        <v>1832</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D91" s="1">
         <v>1</v>
@@ -4920,10 +4916,10 @@
     <row r="92" ht="15" customHeight="1" spans="1:6">
       <c r="A92" s="1"/>
       <c r="B92" s="1">
-        <v>1832</v>
+        <v>1833</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D92" s="1">
         <v>1</v>
@@ -4938,10 +4934,10 @@
     <row r="93" ht="15" customHeight="1" spans="1:6">
       <c r="A93" s="1"/>
       <c r="B93" s="1">
-        <v>1833</v>
+        <v>1834</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D93" s="1">
         <v>1</v>
@@ -4956,10 +4952,10 @@
     <row r="94" ht="15" customHeight="1" spans="1:6">
       <c r="A94" s="1"/>
       <c r="B94" s="1">
-        <v>1834</v>
+        <v>1841</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D94" s="1">
         <v>1</v>
@@ -4974,10 +4970,10 @@
     <row r="95" ht="15" customHeight="1" spans="1:6">
       <c r="A95" s="1"/>
       <c r="B95" s="1">
-        <v>1841</v>
+        <v>1842</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D95" s="1">
         <v>1</v>
@@ -4992,10 +4988,10 @@
     <row r="96" ht="15" customHeight="1" spans="1:6">
       <c r="A96" s="1"/>
       <c r="B96" s="1">
-        <v>1842</v>
+        <v>1843</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D96" s="1">
         <v>1</v>
@@ -5010,10 +5006,10 @@
     <row r="97" ht="15" customHeight="1" spans="1:6">
       <c r="A97" s="1"/>
       <c r="B97" s="1">
-        <v>1843</v>
+        <v>1844</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D97" s="1">
         <v>1</v>
@@ -5028,10 +5024,10 @@
     <row r="98" ht="15" customHeight="1" spans="1:6">
       <c r="A98" s="1"/>
       <c r="B98" s="1">
-        <v>1844</v>
+        <v>1845</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D98" s="1">
         <v>1</v>
@@ -5046,10 +5042,10 @@
     <row r="99" ht="15" customHeight="1" spans="1:6">
       <c r="A99" s="1"/>
       <c r="B99" s="1">
-        <v>1845</v>
+        <v>1846</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D99" s="1">
         <v>1</v>
@@ -5064,10 +5060,10 @@
     <row r="100" ht="15" customHeight="1" spans="1:6">
       <c r="A100" s="1"/>
       <c r="B100" s="1">
-        <v>1846</v>
+        <v>1847</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D100" s="1">
         <v>1</v>
@@ -5082,10 +5078,10 @@
     <row r="101" ht="15" customHeight="1" spans="1:6">
       <c r="A101" s="1"/>
       <c r="B101" s="1">
-        <v>1847</v>
+        <v>1848</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D101" s="1">
         <v>1</v>
@@ -5100,10 +5096,10 @@
     <row r="102" ht="15" customHeight="1" spans="1:6">
       <c r="A102" s="1"/>
       <c r="B102" s="1">
-        <v>1848</v>
+        <v>1849</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D102" s="1">
         <v>1</v>
@@ -5118,10 +5114,10 @@
     <row r="103" ht="15" customHeight="1" spans="1:6">
       <c r="A103" s="1"/>
       <c r="B103" s="1">
-        <v>1849</v>
+        <v>1850</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D103" s="1">
         <v>1</v>
@@ -5136,11 +5132,9 @@
     <row r="104" ht="15" customHeight="1" spans="1:6">
       <c r="A104" s="1"/>
       <c r="B104" s="1">
-        <v>1850</v>
-      </c>
-      <c r="C104" s="1" t="s">
-        <v>171</v>
-      </c>
+        <v>1901</v>
+      </c>
+      <c r="C104" s="1"/>
       <c r="D104" s="1">
         <v>1</v>
       </c>
@@ -5154,7 +5148,7 @@
     <row r="105" ht="15" customHeight="1" spans="1:6">
       <c r="A105" s="1"/>
       <c r="B105" s="1">
-        <v>1901</v>
+        <v>1902</v>
       </c>
       <c r="C105" s="1"/>
       <c r="D105" s="1">
@@ -5170,7 +5164,7 @@
     <row r="106" ht="15" customHeight="1" spans="1:6">
       <c r="A106" s="1"/>
       <c r="B106" s="1">
-        <v>1902</v>
+        <v>1903</v>
       </c>
       <c r="C106" s="1"/>
       <c r="D106" s="1">
@@ -5186,7 +5180,7 @@
     <row r="107" ht="15" customHeight="1" spans="1:6">
       <c r="A107" s="1"/>
       <c r="B107" s="1">
-        <v>1903</v>
+        <v>1904</v>
       </c>
       <c r="C107" s="1"/>
       <c r="D107" s="1">
@@ -5202,7 +5196,7 @@
     <row r="108" ht="15" customHeight="1" spans="1:6">
       <c r="A108" s="1"/>
       <c r="B108" s="1">
-        <v>1904</v>
+        <v>1905</v>
       </c>
       <c r="C108" s="1"/>
       <c r="D108" s="1">
@@ -5218,7 +5212,7 @@
     <row r="109" ht="15" customHeight="1" spans="1:6">
       <c r="A109" s="1"/>
       <c r="B109" s="1">
-        <v>1905</v>
+        <v>1906</v>
       </c>
       <c r="C109" s="1"/>
       <c r="D109" s="1">
@@ -5234,7 +5228,7 @@
     <row r="110" ht="15" customHeight="1" spans="1:6">
       <c r="A110" s="1"/>
       <c r="B110" s="1">
-        <v>1906</v>
+        <v>1907</v>
       </c>
       <c r="C110" s="1"/>
       <c r="D110" s="1">
@@ -5250,7 +5244,7 @@
     <row r="111" ht="15" customHeight="1" spans="1:6">
       <c r="A111" s="1"/>
       <c r="B111" s="1">
-        <v>1907</v>
+        <v>1908</v>
       </c>
       <c r="C111" s="1"/>
       <c r="D111" s="1">
@@ -5266,7 +5260,7 @@
     <row r="112" ht="15" customHeight="1" spans="1:6">
       <c r="A112" s="1"/>
       <c r="B112" s="1">
-        <v>1908</v>
+        <v>1909</v>
       </c>
       <c r="C112" s="1"/>
       <c r="D112" s="1">
@@ -5282,7 +5276,7 @@
     <row r="113" ht="15" customHeight="1" spans="1:6">
       <c r="A113" s="1"/>
       <c r="B113" s="1">
-        <v>1909</v>
+        <v>1910</v>
       </c>
       <c r="C113" s="1"/>
       <c r="D113" s="1">
@@ -5298,7 +5292,7 @@
     <row r="114" ht="15" customHeight="1" spans="1:6">
       <c r="A114" s="1"/>
       <c r="B114" s="1">
-        <v>1910</v>
+        <v>1911</v>
       </c>
       <c r="C114" s="1"/>
       <c r="D114" s="1">
@@ -5314,7 +5308,7 @@
     <row r="115" ht="15" customHeight="1" spans="1:6">
       <c r="A115" s="1"/>
       <c r="B115" s="1">
-        <v>1911</v>
+        <v>1912</v>
       </c>
       <c r="C115" s="1"/>
       <c r="D115" s="1">
@@ -5330,7 +5324,7 @@
     <row r="116" ht="15" customHeight="1" spans="1:6">
       <c r="A116" s="1"/>
       <c r="B116" s="1">
-        <v>1912</v>
+        <v>1913</v>
       </c>
       <c r="C116" s="1"/>
       <c r="D116" s="1">
@@ -5346,7 +5340,7 @@
     <row r="117" ht="15" customHeight="1" spans="1:6">
       <c r="A117" s="1"/>
       <c r="B117" s="1">
-        <v>1913</v>
+        <v>1914</v>
       </c>
       <c r="C117" s="1"/>
       <c r="D117" s="1">
@@ -5362,7 +5356,7 @@
     <row r="118" ht="15" customHeight="1" spans="1:6">
       <c r="A118" s="1"/>
       <c r="B118" s="1">
-        <v>1914</v>
+        <v>1915</v>
       </c>
       <c r="C118" s="1"/>
       <c r="D118" s="1">
@@ -5378,7 +5372,7 @@
     <row r="119" ht="15" customHeight="1" spans="1:6">
       <c r="A119" s="1"/>
       <c r="B119" s="1">
-        <v>1915</v>
+        <v>1916</v>
       </c>
       <c r="C119" s="1"/>
       <c r="D119" s="1">
@@ -5394,7 +5388,7 @@
     <row r="120" ht="15" customHeight="1" spans="1:6">
       <c r="A120" s="1"/>
       <c r="B120" s="1">
-        <v>1916</v>
+        <v>1917</v>
       </c>
       <c r="C120" s="1"/>
       <c r="D120" s="1">
@@ -5410,7 +5404,7 @@
     <row r="121" ht="15" customHeight="1" spans="1:6">
       <c r="A121" s="1"/>
       <c r="B121" s="1">
-        <v>1917</v>
+        <v>1918</v>
       </c>
       <c r="C121" s="1"/>
       <c r="D121" s="1">
@@ -5426,7 +5420,7 @@
     <row r="122" ht="15" customHeight="1" spans="1:6">
       <c r="A122" s="1"/>
       <c r="B122" s="1">
-        <v>1918</v>
+        <v>1919</v>
       </c>
       <c r="C122" s="1"/>
       <c r="D122" s="1">
@@ -5442,7 +5436,7 @@
     <row r="123" ht="15" customHeight="1" spans="1:6">
       <c r="A123" s="1"/>
       <c r="B123" s="1">
-        <v>1919</v>
+        <v>1920</v>
       </c>
       <c r="C123" s="1"/>
       <c r="D123" s="1">
@@ -5458,7 +5452,7 @@
     <row r="124" ht="15" customHeight="1" spans="1:6">
       <c r="A124" s="1"/>
       <c r="B124" s="1">
-        <v>1920</v>
+        <v>1921</v>
       </c>
       <c r="C124" s="1"/>
       <c r="D124" s="1">
@@ -5474,7 +5468,7 @@
     <row r="125" ht="15" customHeight="1" spans="1:6">
       <c r="A125" s="1"/>
       <c r="B125" s="1">
-        <v>1921</v>
+        <v>1922</v>
       </c>
       <c r="C125" s="1"/>
       <c r="D125" s="1">
@@ -5490,7 +5484,7 @@
     <row r="126" ht="15" customHeight="1" spans="1:6">
       <c r="A126" s="1"/>
       <c r="B126" s="1">
-        <v>1922</v>
+        <v>1923</v>
       </c>
       <c r="C126" s="1"/>
       <c r="D126" s="1">
@@ -5506,7 +5500,7 @@
     <row r="127" ht="15" customHeight="1" spans="1:6">
       <c r="A127" s="1"/>
       <c r="B127" s="1">
-        <v>1923</v>
+        <v>1924</v>
       </c>
       <c r="C127" s="1"/>
       <c r="D127" s="1">
@@ -5522,7 +5516,7 @@
     <row r="128" ht="15" customHeight="1" spans="1:6">
       <c r="A128" s="1"/>
       <c r="B128" s="1">
-        <v>1924</v>
+        <v>1925</v>
       </c>
       <c r="C128" s="1"/>
       <c r="D128" s="1">
@@ -5538,7 +5532,7 @@
     <row r="129" ht="15" customHeight="1" spans="1:6">
       <c r="A129" s="1"/>
       <c r="B129" s="1">
-        <v>1925</v>
+        <v>1926</v>
       </c>
       <c r="C129" s="1"/>
       <c r="D129" s="1">
@@ -5554,7 +5548,7 @@
     <row r="130" ht="15" customHeight="1" spans="1:6">
       <c r="A130" s="1"/>
       <c r="B130" s="1">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="C130" s="1"/>
       <c r="D130" s="1">
@@ -5570,7 +5564,7 @@
     <row r="131" ht="15" customHeight="1" spans="1:6">
       <c r="A131" s="1"/>
       <c r="B131" s="1">
-        <v>1927</v>
+        <v>1928</v>
       </c>
       <c r="C131" s="1"/>
       <c r="D131" s="1">
@@ -5586,7 +5580,7 @@
     <row r="132" ht="15" customHeight="1" spans="1:6">
       <c r="A132" s="1"/>
       <c r="B132" s="1">
-        <v>1928</v>
+        <v>1929</v>
       </c>
       <c r="C132" s="1"/>
       <c r="D132" s="1">
@@ -5602,7 +5596,7 @@
     <row r="133" ht="15" customHeight="1" spans="1:6">
       <c r="A133" s="1"/>
       <c r="B133" s="1">
-        <v>1929</v>
+        <v>1930</v>
       </c>
       <c r="C133" s="1"/>
       <c r="D133" s="1">
@@ -5618,7 +5612,7 @@
     <row r="134" ht="15" customHeight="1" spans="1:6">
       <c r="A134" s="1"/>
       <c r="B134" s="1">
-        <v>1930</v>
+        <v>1931</v>
       </c>
       <c r="C134" s="1"/>
       <c r="D134" s="1">
@@ -5634,7 +5628,7 @@
     <row r="135" ht="15" customHeight="1" spans="1:6">
       <c r="A135" s="1"/>
       <c r="B135" s="1">
-        <v>1931</v>
+        <v>1932</v>
       </c>
       <c r="C135" s="1"/>
       <c r="D135" s="1">
@@ -5650,7 +5644,7 @@
     <row r="136" ht="15" customHeight="1" spans="1:6">
       <c r="A136" s="1"/>
       <c r="B136" s="1">
-        <v>1932</v>
+        <v>1933</v>
       </c>
       <c r="C136" s="1"/>
       <c r="D136" s="1">
@@ -5666,7 +5660,7 @@
     <row r="137" ht="15" customHeight="1" spans="1:6">
       <c r="A137" s="1"/>
       <c r="B137" s="1">
-        <v>1933</v>
+        <v>1934</v>
       </c>
       <c r="C137" s="1"/>
       <c r="D137" s="1">
@@ -5682,7 +5676,7 @@
     <row r="138" ht="15" customHeight="1" spans="1:6">
       <c r="A138" s="1"/>
       <c r="B138" s="1">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="C138" s="1"/>
       <c r="D138" s="1">
@@ -5698,7 +5692,7 @@
     <row r="139" ht="15" customHeight="1" spans="1:6">
       <c r="A139" s="1"/>
       <c r="B139" s="1">
-        <v>1935</v>
+        <v>1936</v>
       </c>
       <c r="C139" s="1"/>
       <c r="D139" s="1">
@@ -5714,7 +5708,7 @@
     <row r="140" ht="15" customHeight="1" spans="1:6">
       <c r="A140" s="1"/>
       <c r="B140" s="1">
-        <v>1936</v>
+        <v>1937</v>
       </c>
       <c r="C140" s="1"/>
       <c r="D140" s="1">
@@ -5730,7 +5724,7 @@
     <row r="141" ht="15" customHeight="1" spans="1:6">
       <c r="A141" s="1"/>
       <c r="B141" s="1">
-        <v>1937</v>
+        <v>1938</v>
       </c>
       <c r="C141" s="1"/>
       <c r="D141" s="1">
@@ -5746,7 +5740,7 @@
     <row r="142" ht="15" customHeight="1" spans="1:6">
       <c r="A142" s="1"/>
       <c r="B142" s="1">
-        <v>1938</v>
+        <v>1939</v>
       </c>
       <c r="C142" s="1"/>
       <c r="D142" s="1">
@@ -5762,7 +5756,7 @@
     <row r="143" ht="15" customHeight="1" spans="1:6">
       <c r="A143" s="1"/>
       <c r="B143" s="1">
-        <v>1939</v>
+        <v>1940</v>
       </c>
       <c r="C143" s="1"/>
       <c r="D143" s="1">
@@ -5778,7 +5772,7 @@
     <row r="144" ht="15" customHeight="1" spans="1:6">
       <c r="A144" s="1"/>
       <c r="B144" s="1">
-        <v>1940</v>
+        <v>1941</v>
       </c>
       <c r="C144" s="1"/>
       <c r="D144" s="1">
@@ -5794,7 +5788,7 @@
     <row r="145" ht="15" customHeight="1" spans="1:6">
       <c r="A145" s="1"/>
       <c r="B145" s="1">
-        <v>1941</v>
+        <v>1942</v>
       </c>
       <c r="C145" s="1"/>
       <c r="D145" s="1">
@@ -5810,7 +5804,7 @@
     <row r="146" ht="15" customHeight="1" spans="1:6">
       <c r="A146" s="1"/>
       <c r="B146" s="1">
-        <v>1942</v>
+        <v>1943</v>
       </c>
       <c r="C146" s="1"/>
       <c r="D146" s="1">
@@ -5826,7 +5820,7 @@
     <row r="147" ht="15" customHeight="1" spans="1:6">
       <c r="A147" s="1"/>
       <c r="B147" s="1">
-        <v>1943</v>
+        <v>1944</v>
       </c>
       <c r="C147" s="1"/>
       <c r="D147" s="1">
@@ -5842,7 +5836,7 @@
     <row r="148" ht="15" customHeight="1" spans="1:6">
       <c r="A148" s="1"/>
       <c r="B148" s="1">
-        <v>1944</v>
+        <v>1945</v>
       </c>
       <c r="C148" s="1"/>
       <c r="D148" s="1">
@@ -5858,7 +5852,7 @@
     <row r="149" ht="15" customHeight="1" spans="1:6">
       <c r="A149" s="1"/>
       <c r="B149" s="1">
-        <v>1945</v>
+        <v>1946</v>
       </c>
       <c r="C149" s="1"/>
       <c r="D149" s="1">
@@ -5874,7 +5868,7 @@
     <row r="150" ht="15" customHeight="1" spans="1:6">
       <c r="A150" s="1"/>
       <c r="B150" s="1">
-        <v>1946</v>
+        <v>1947</v>
       </c>
       <c r="C150" s="1"/>
       <c r="D150" s="1">
@@ -5890,7 +5884,7 @@
     <row r="151" ht="15" customHeight="1" spans="1:6">
       <c r="A151" s="1"/>
       <c r="B151" s="1">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="C151" s="1"/>
       <c r="D151" s="1">
@@ -5906,11 +5900,11 @@
     <row r="152" ht="15" customHeight="1" spans="1:6">
       <c r="A152" s="1"/>
       <c r="B152" s="1">
-        <v>1948</v>
+        <v>2001</v>
       </c>
       <c r="C152" s="1"/>
       <c r="D152" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E152" s="1" t="s">
         <v>310</v>
@@ -5922,7 +5916,7 @@
     <row r="153" ht="15" customHeight="1" spans="1:6">
       <c r="A153" s="1"/>
       <c r="B153" s="1">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="C153" s="1"/>
       <c r="D153" s="1">
@@ -5938,7 +5932,7 @@
     <row r="154" ht="15" customHeight="1" spans="1:6">
       <c r="A154" s="1"/>
       <c r="B154" s="1">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="C154" s="1"/>
       <c r="D154" s="1">
@@ -5954,7 +5948,7 @@
     <row r="155" ht="15" customHeight="1" spans="1:6">
       <c r="A155" s="1"/>
       <c r="B155" s="1">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="C155" s="1"/>
       <c r="D155" s="1">
@@ -5970,7 +5964,7 @@
     <row r="156" ht="15" customHeight="1" spans="1:6">
       <c r="A156" s="1"/>
       <c r="B156" s="1">
-        <v>2004</v>
+        <v>2101</v>
       </c>
       <c r="C156" s="1"/>
       <c r="D156" s="1">
@@ -5986,68 +5980,68 @@
     <row r="157" ht="15" customHeight="1" spans="1:6">
       <c r="A157" s="1"/>
       <c r="B157" s="1">
-        <v>2101</v>
-      </c>
-      <c r="C157" s="1"/>
+        <v>2102</v>
+      </c>
+      <c r="C157" s="1" t="s">
+        <v>320</v>
+      </c>
       <c r="D157" s="1">
         <v>2</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="158" ht="15" customHeight="1" spans="1:6">
       <c r="A158" s="1"/>
       <c r="B158" s="1">
-        <v>2102</v>
+        <v>2103</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D158" s="1">
         <v>2</v>
       </c>
       <c r="E158" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="F158" s="1" t="s">
         <v>323</v>
-      </c>
-      <c r="F158" s="1" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="159" ht="15" customHeight="1" spans="1:6">
       <c r="A159" s="1"/>
       <c r="B159" s="1">
-        <v>2103</v>
+        <v>2104</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D159" s="1">
         <v>2</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="160" ht="15" customHeight="1" spans="1:6">
       <c r="A160" s="1"/>
       <c r="B160" s="1">
-        <v>2104</v>
-      </c>
-      <c r="C160" s="1" t="s">
-        <v>322</v>
-      </c>
+        <v>2201</v>
+      </c>
+      <c r="C160" s="1"/>
       <c r="D160" s="1">
         <v>2</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>326</v>
@@ -6056,7 +6050,7 @@
     <row r="161" ht="15" customHeight="1" spans="1:6">
       <c r="A161" s="1"/>
       <c r="B161" s="1">
-        <v>2201</v>
+        <v>2301</v>
       </c>
       <c r="C161" s="1"/>
       <c r="D161" s="1">
@@ -6072,7 +6066,7 @@
     <row r="162" ht="15" customHeight="1" spans="1:6">
       <c r="A162" s="1"/>
       <c r="B162" s="1">
-        <v>2301</v>
+        <v>2304</v>
       </c>
       <c r="C162" s="1"/>
       <c r="D162" s="1">
@@ -6088,7 +6082,7 @@
     <row r="163" ht="15" customHeight="1" spans="1:6">
       <c r="A163" s="1"/>
       <c r="B163" s="1">
-        <v>2304</v>
+        <v>2309</v>
       </c>
       <c r="C163" s="1"/>
       <c r="D163" s="1">
@@ -6104,7 +6098,7 @@
     <row r="164" ht="15" customHeight="1" spans="1:6">
       <c r="A164" s="1"/>
       <c r="B164" s="1">
-        <v>2309</v>
+        <v>2310</v>
       </c>
       <c r="C164" s="1"/>
       <c r="D164" s="1">
@@ -6120,7 +6114,7 @@
     <row r="165" ht="15" customHeight="1" spans="1:6">
       <c r="A165" s="1"/>
       <c r="B165" s="1">
-        <v>2310</v>
+        <v>2311</v>
       </c>
       <c r="C165" s="1"/>
       <c r="D165" s="1">
@@ -6136,7 +6130,7 @@
     <row r="166" ht="15" customHeight="1" spans="1:6">
       <c r="A166" s="1"/>
       <c r="B166" s="1">
-        <v>2311</v>
+        <v>2312</v>
       </c>
       <c r="C166" s="1"/>
       <c r="D166" s="1">
@@ -6152,9 +6146,11 @@
     <row r="167" ht="15" customHeight="1" spans="1:6">
       <c r="A167" s="1"/>
       <c r="B167" s="1">
-        <v>2312</v>
-      </c>
-      <c r="C167" s="1"/>
+        <v>2313</v>
+      </c>
+      <c r="C167" s="1" t="s">
+        <v>109</v>
+      </c>
       <c r="D167" s="1">
         <v>2</v>
       </c>
@@ -6168,11 +6164,9 @@
     <row r="168" ht="15" customHeight="1" spans="1:6">
       <c r="A168" s="1"/>
       <c r="B168" s="1">
-        <v>2313</v>
-      </c>
-      <c r="C168" s="1" t="s">
-        <v>109</v>
-      </c>
+        <v>2399</v>
+      </c>
+      <c r="C168" s="1"/>
       <c r="D168" s="1">
         <v>2</v>
       </c>
@@ -6186,11 +6180,11 @@
     <row r="169" ht="15" customHeight="1" spans="1:6">
       <c r="A169" s="1"/>
       <c r="B169" s="1">
-        <v>2399</v>
+        <v>2401</v>
       </c>
       <c r="C169" s="1"/>
       <c r="D169" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E169" s="1" t="s">
         <v>343</v>
@@ -6202,7 +6196,7 @@
     <row r="170" ht="15" customHeight="1" spans="1:6">
       <c r="A170" s="1"/>
       <c r="B170" s="1">
-        <v>2401</v>
+        <v>2402</v>
       </c>
       <c r="C170" s="1"/>
       <c r="D170" s="1">
@@ -6218,11 +6212,11 @@
     <row r="171" ht="15" customHeight="1" spans="1:6">
       <c r="A171" s="1"/>
       <c r="B171" s="1">
-        <v>2402</v>
+        <v>2501</v>
       </c>
       <c r="C171" s="1"/>
       <c r="D171" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E171" s="1" t="s">
         <v>347</v>
@@ -6234,7 +6228,7 @@
     <row r="172" ht="15" customHeight="1" spans="1:6">
       <c r="A172" s="1"/>
       <c r="B172" s="1">
-        <v>2501</v>
+        <v>2502</v>
       </c>
       <c r="C172" s="1"/>
       <c r="D172" s="1">
@@ -6250,7 +6244,7 @@
     <row r="173" ht="15" customHeight="1" spans="1:6">
       <c r="A173" s="1"/>
       <c r="B173" s="1">
-        <v>2502</v>
+        <v>2503</v>
       </c>
       <c r="C173" s="1"/>
       <c r="D173" s="1">
@@ -6266,7 +6260,7 @@
     <row r="174" ht="15" customHeight="1" spans="1:6">
       <c r="A174" s="1"/>
       <c r="B174" s="1">
-        <v>2503</v>
+        <v>2504</v>
       </c>
       <c r="C174" s="1"/>
       <c r="D174" s="1">
@@ -6282,7 +6276,7 @@
     <row r="175" ht="15" customHeight="1" spans="1:6">
       <c r="A175" s="1"/>
       <c r="B175" s="1">
-        <v>2504</v>
+        <v>2600</v>
       </c>
       <c r="C175" s="1"/>
       <c r="D175" s="1">
@@ -6298,7 +6292,7 @@
     <row r="176" ht="15" customHeight="1" spans="1:6">
       <c r="A176" s="1"/>
       <c r="B176" s="1">
-        <v>2600</v>
+        <v>2601</v>
       </c>
       <c r="C176" s="1"/>
       <c r="D176" s="1">
@@ -6314,7 +6308,7 @@
     <row r="177" ht="15" customHeight="1" spans="1:6">
       <c r="A177" s="1"/>
       <c r="B177" s="1">
-        <v>2601</v>
+        <v>2901</v>
       </c>
       <c r="C177" s="1"/>
       <c r="D177" s="1">
@@ -6330,11 +6324,11 @@
     <row r="178" ht="15" customHeight="1" spans="1:6">
       <c r="A178" s="1"/>
       <c r="B178" s="1">
-        <v>2901</v>
+        <v>3001</v>
       </c>
       <c r="C178" s="1"/>
       <c r="D178" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E178" s="1" t="s">
         <v>361</v>
@@ -6346,7 +6340,7 @@
     <row r="179" ht="15" customHeight="1" spans="1:6">
       <c r="A179" s="1"/>
       <c r="B179" s="1">
-        <v>3001</v>
+        <v>3002</v>
       </c>
       <c r="C179" s="1"/>
       <c r="D179" s="1">
@@ -6362,7 +6356,7 @@
     <row r="180" ht="15" customHeight="1" spans="1:6">
       <c r="A180" s="1"/>
       <c r="B180" s="1">
-        <v>3002</v>
+        <v>3003</v>
       </c>
       <c r="C180" s="1"/>
       <c r="D180" s="1">
@@ -6378,7 +6372,7 @@
     <row r="181" ht="15" customHeight="1" spans="1:6">
       <c r="A181" s="1"/>
       <c r="B181" s="1">
-        <v>3003</v>
+        <v>3004</v>
       </c>
       <c r="C181" s="1"/>
       <c r="D181" s="1">
@@ -6394,7 +6388,7 @@
     <row r="182" ht="15" customHeight="1" spans="1:6">
       <c r="A182" s="1"/>
       <c r="B182" s="1">
-        <v>3004</v>
+        <v>3005</v>
       </c>
       <c r="C182" s="1"/>
       <c r="D182" s="1">
@@ -6410,7 +6404,7 @@
     <row r="183" ht="15" customHeight="1" spans="1:6">
       <c r="A183" s="1"/>
       <c r="B183" s="1">
-        <v>3005</v>
+        <v>3006</v>
       </c>
       <c r="C183" s="1"/>
       <c r="D183" s="1">
@@ -6426,7 +6420,7 @@
     <row r="184" ht="15" customHeight="1" spans="1:6">
       <c r="A184" s="1"/>
       <c r="B184" s="1">
-        <v>3006</v>
+        <v>3007</v>
       </c>
       <c r="C184" s="1"/>
       <c r="D184" s="1">
@@ -6442,7 +6436,7 @@
     <row r="185" ht="15" customHeight="1" spans="1:6">
       <c r="A185" s="1"/>
       <c r="B185" s="1">
-        <v>3007</v>
+        <v>3008</v>
       </c>
       <c r="C185" s="1"/>
       <c r="D185" s="1">
@@ -6458,7 +6452,7 @@
     <row r="186" ht="15" customHeight="1" spans="1:6">
       <c r="A186" s="1"/>
       <c r="B186" s="1">
-        <v>3008</v>
+        <v>3009</v>
       </c>
       <c r="C186" s="1"/>
       <c r="D186" s="1">
@@ -6474,9 +6468,11 @@
     <row r="187" ht="15" customHeight="1" spans="1:6">
       <c r="A187" s="1"/>
       <c r="B187" s="1">
-        <v>3009</v>
-      </c>
-      <c r="C187" s="1"/>
+        <v>3010</v>
+      </c>
+      <c r="C187" s="1" t="s">
+        <v>169</v>
+      </c>
       <c r="D187" s="1">
         <v>3</v>
       </c>
@@ -6490,28 +6486,28 @@
     <row r="188" ht="15" customHeight="1" spans="1:6">
       <c r="A188" s="1"/>
       <c r="B188" s="1">
-        <v>3010</v>
+        <v>3011</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>171</v>
+        <v>381</v>
       </c>
       <c r="D188" s="1">
         <v>3</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="189" ht="15" customHeight="1" spans="1:6">
       <c r="A189" s="1"/>
       <c r="B189" s="1">
-        <v>3011</v>
+        <v>3012</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D189" s="1">
         <v>3</v>
@@ -6526,10 +6522,10 @@
     <row r="190" ht="15" customHeight="1" spans="1:6">
       <c r="A190" s="1"/>
       <c r="B190" s="1">
-        <v>3012</v>
+        <v>3013</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D190" s="1">
         <v>3</v>
@@ -6544,10 +6540,10 @@
     <row r="191" ht="15" customHeight="1" spans="1:6">
       <c r="A191" s="1"/>
       <c r="B191" s="1">
-        <v>3013</v>
+        <v>3014</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D191" s="1">
         <v>3</v>
@@ -6562,10 +6558,10 @@
     <row r="192" ht="15" customHeight="1" spans="1:6">
       <c r="A192" s="1"/>
       <c r="B192" s="1">
-        <v>3014</v>
+        <v>3015</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D192" s="1">
         <v>3</v>
@@ -6580,10 +6576,10 @@
     <row r="193" ht="15" customHeight="1" spans="1:6">
       <c r="A193" s="1"/>
       <c r="B193" s="1">
-        <v>3015</v>
+        <v>3016</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D193" s="1">
         <v>3</v>
@@ -6598,10 +6594,10 @@
     <row r="194" ht="15" customHeight="1" spans="1:6">
       <c r="A194" s="1"/>
       <c r="B194" s="1">
-        <v>3016</v>
+        <v>3017</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D194" s="1">
         <v>3</v>
@@ -6616,10 +6612,10 @@
     <row r="195" ht="15" customHeight="1" spans="1:6">
       <c r="A195" s="1"/>
       <c r="B195" s="1">
-        <v>3017</v>
+        <v>3018</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D195" s="1">
         <v>3</v>
@@ -6634,10 +6630,10 @@
     <row r="196" ht="15" customHeight="1" spans="1:6">
       <c r="A196" s="1"/>
       <c r="B196" s="1">
-        <v>3018</v>
+        <v>3019</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D196" s="1">
         <v>3</v>
@@ -6652,31 +6648,29 @@
     <row r="197" ht="15" customHeight="1" spans="1:6">
       <c r="A197" s="1"/>
       <c r="B197" s="1">
-        <v>3019</v>
+        <v>6001</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>383</v>
+        <v>400</v>
       </c>
       <c r="D197" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="198" ht="15" customHeight="1" spans="1:6">
       <c r="A198" s="1"/>
       <c r="B198" s="1">
-        <v>6001</v>
-      </c>
-      <c r="C198" s="1" t="s">
-        <v>402</v>
-      </c>
+        <v>10001</v>
+      </c>
+      <c r="C198" s="1"/>
       <c r="D198" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E198" s="1" t="s">
         <v>403</v>
@@ -6688,7 +6682,7 @@
     <row r="199" ht="15" customHeight="1" spans="1:6">
       <c r="A199" s="1"/>
       <c r="B199" s="1">
-        <v>10001</v>
+        <v>10002</v>
       </c>
       <c r="C199" s="1"/>
       <c r="D199" s="1">
@@ -6704,7 +6698,7 @@
     <row r="200" ht="15" customHeight="1" spans="1:6">
       <c r="A200" s="1"/>
       <c r="B200" s="1">
-        <v>10002</v>
+        <v>10003</v>
       </c>
       <c r="C200" s="1"/>
       <c r="D200" s="1">
@@ -6720,7 +6714,7 @@
     <row r="201" ht="15" customHeight="1" spans="1:6">
       <c r="A201" s="1"/>
       <c r="B201" s="1">
-        <v>10003</v>
+        <v>10004</v>
       </c>
       <c r="C201" s="1"/>
       <c r="D201" s="1">
@@ -6736,7 +6730,7 @@
     <row r="202" ht="15" customHeight="1" spans="1:6">
       <c r="A202" s="1"/>
       <c r="B202" s="1">
-        <v>10004</v>
+        <v>10101</v>
       </c>
       <c r="C202" s="1"/>
       <c r="D202" s="1">
@@ -6752,7 +6746,7 @@
     <row r="203" ht="15" customHeight="1" spans="1:6">
       <c r="A203" s="1"/>
       <c r="B203" s="1">
-        <v>10101</v>
+        <v>10102</v>
       </c>
       <c r="C203" s="1"/>
       <c r="D203" s="1">
@@ -6768,7 +6762,7 @@
     <row r="204" ht="15" customHeight="1" spans="1:6">
       <c r="A204" s="1"/>
       <c r="B204" s="1">
-        <v>10102</v>
+        <v>10103</v>
       </c>
       <c r="C204" s="1"/>
       <c r="D204" s="1">
@@ -6784,7 +6778,7 @@
     <row r="205" ht="15" customHeight="1" spans="1:6">
       <c r="A205" s="1"/>
       <c r="B205" s="1">
-        <v>10103</v>
+        <v>10201</v>
       </c>
       <c r="C205" s="1"/>
       <c r="D205" s="1">
@@ -6800,7 +6794,7 @@
     <row r="206" ht="15" customHeight="1" spans="1:6">
       <c r="A206" s="1"/>
       <c r="B206" s="1">
-        <v>10201</v>
+        <v>10202</v>
       </c>
       <c r="C206" s="1"/>
       <c r="D206" s="1">
@@ -6816,7 +6810,7 @@
     <row r="207" ht="15" customHeight="1" spans="1:6">
       <c r="A207" s="1"/>
       <c r="B207" s="1">
-        <v>10202</v>
+        <v>10203</v>
       </c>
       <c r="C207" s="1"/>
       <c r="D207" s="1">
@@ -6832,27 +6826,27 @@
     <row r="208" ht="15" customHeight="1" spans="1:6">
       <c r="A208" s="1"/>
       <c r="B208" s="1">
-        <v>10203</v>
-      </c>
-      <c r="C208" s="1"/>
+        <v>11001</v>
+      </c>
+      <c r="C208" s="1" t="s">
+        <v>423</v>
+      </c>
       <c r="D208" s="1">
         <v>1</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="F208" s="1" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="209" ht="15" customHeight="1" spans="1:6">
       <c r="A209" s="1"/>
       <c r="B209" s="1">
-        <v>11001</v>
-      </c>
-      <c r="C209" s="1" t="s">
-        <v>425</v>
-      </c>
+        <v>13001</v>
+      </c>
+      <c r="C209" s="1"/>
       <c r="D209" s="1">
         <v>1</v>
       </c>
@@ -6866,7 +6860,7 @@
     <row r="210" ht="15" customHeight="1" spans="1:6">
       <c r="A210" s="1"/>
       <c r="B210" s="1">
-        <v>13001</v>
+        <v>13004</v>
       </c>
       <c r="C210" s="1"/>
       <c r="D210" s="1">
@@ -6882,23 +6876,25 @@
     <row r="211" ht="15" customHeight="1" spans="1:6">
       <c r="A211" s="1"/>
       <c r="B211" s="1">
-        <v>13004</v>
-      </c>
-      <c r="C211" s="1"/>
+        <v>13010</v>
+      </c>
+      <c r="C211" s="1" t="s">
+        <v>109</v>
+      </c>
       <c r="D211" s="1">
         <v>1</v>
       </c>
       <c r="E211" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="F211" s="1" t="s">
         <v>430</v>
-      </c>
-      <c r="F211" s="1" t="s">
-        <v>431</v>
       </c>
     </row>
     <row r="212" ht="15" customHeight="1" spans="1:6">
       <c r="A212" s="1"/>
       <c r="B212" s="1">
-        <v>13010</v>
+        <v>13011</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>109</v>
@@ -6910,13 +6906,13 @@
         <v>145</v>
       </c>
       <c r="F212" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="213" ht="15" customHeight="1" spans="1:6">
       <c r="A213" s="1"/>
       <c r="B213" s="1">
-        <v>13011</v>
+        <v>13012</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>109</v>
@@ -6928,13 +6924,13 @@
         <v>147</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="214" ht="15" customHeight="1" spans="1:6">
       <c r="A214" s="1"/>
       <c r="B214" s="1">
-        <v>13012</v>
+        <v>13013</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>109</v>
@@ -6943,7 +6939,7 @@
         <v>1</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>149</v>
+        <v>433</v>
       </c>
       <c r="F214" s="1" t="s">
         <v>434</v>
@@ -6952,7 +6948,7 @@
     <row r="215" ht="15" customHeight="1" spans="1:6">
       <c r="A215" s="1"/>
       <c r="B215" s="1">
-        <v>13013</v>
+        <v>13999</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>109</v>
@@ -6970,11 +6966,9 @@
     <row r="216" ht="15" customHeight="1" spans="1:6">
       <c r="A216" s="1"/>
       <c r="B216" s="1">
-        <v>13999</v>
-      </c>
-      <c r="C216" s="1" t="s">
-        <v>109</v>
-      </c>
+        <v>15001</v>
+      </c>
+      <c r="C216" s="1"/>
       <c r="D216" s="1">
         <v>1</v>
       </c>
@@ -6988,27 +6982,27 @@
     <row r="217" ht="15" customHeight="1" spans="1:6">
       <c r="A217" s="1"/>
       <c r="B217" s="1">
-        <v>15001</v>
-      </c>
-      <c r="C217" s="1"/>
+        <v>15002</v>
+      </c>
+      <c r="C217" s="1" t="s">
+        <v>439</v>
+      </c>
       <c r="D217" s="1">
         <v>1</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="F217" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="218" ht="15" customHeight="1" spans="1:6">
       <c r="A218" s="1"/>
       <c r="B218" s="1">
-        <v>15002</v>
-      </c>
-      <c r="C218" s="1" t="s">
-        <v>441</v>
-      </c>
+        <v>15003</v>
+      </c>
+      <c r="C218" s="1"/>
       <c r="D218" s="1">
         <v>1</v>
       </c>
@@ -7022,7 +7016,7 @@
     <row r="219" ht="15" customHeight="1" spans="1:6">
       <c r="A219" s="1"/>
       <c r="B219" s="1">
-        <v>15003</v>
+        <v>15005</v>
       </c>
       <c r="C219" s="1"/>
       <c r="D219" s="1">
@@ -7038,7 +7032,7 @@
     <row r="220" ht="15" customHeight="1" spans="1:6">
       <c r="A220" s="1"/>
       <c r="B220" s="1">
-        <v>15005</v>
+        <v>15007</v>
       </c>
       <c r="C220" s="1"/>
       <c r="D220" s="1">
@@ -7054,7 +7048,7 @@
     <row r="221" ht="15" customHeight="1" spans="1:6">
       <c r="A221" s="1"/>
       <c r="B221" s="1">
-        <v>15007</v>
+        <v>15008</v>
       </c>
       <c r="C221" s="1"/>
       <c r="D221" s="1">
@@ -7070,7 +7064,7 @@
     <row r="222" ht="15" customHeight="1" spans="1:6">
       <c r="A222" s="1"/>
       <c r="B222" s="1">
-        <v>15008</v>
+        <v>15009</v>
       </c>
       <c r="C222" s="1"/>
       <c r="D222" s="1">
@@ -7086,7 +7080,7 @@
     <row r="223" ht="15" customHeight="1" spans="1:6">
       <c r="A223" s="1"/>
       <c r="B223" s="1">
-        <v>15009</v>
+        <v>15011</v>
       </c>
       <c r="C223" s="1"/>
       <c r="D223" s="1">
@@ -7102,7 +7096,7 @@
     <row r="224" ht="15" customHeight="1" spans="1:6">
       <c r="A224" s="1"/>
       <c r="B224" s="1">
-        <v>15011</v>
+        <v>15012</v>
       </c>
       <c r="C224" s="1"/>
       <c r="D224" s="1">
@@ -7118,7 +7112,7 @@
     <row r="225" ht="15" customHeight="1" spans="1:6">
       <c r="A225" s="1"/>
       <c r="B225" s="1">
-        <v>15012</v>
+        <v>15013</v>
       </c>
       <c r="C225" s="1"/>
       <c r="D225" s="1">
@@ -7134,7 +7128,7 @@
     <row r="226" ht="15" customHeight="1" spans="1:6">
       <c r="A226" s="1"/>
       <c r="B226" s="1">
-        <v>15013</v>
+        <v>15014</v>
       </c>
       <c r="C226" s="1"/>
       <c r="D226" s="1">
@@ -7150,7 +7144,7 @@
     <row r="227" ht="15" customHeight="1" spans="1:6">
       <c r="A227" s="1"/>
       <c r="B227" s="1">
-        <v>15014</v>
+        <v>15015</v>
       </c>
       <c r="C227" s="1"/>
       <c r="D227" s="1">
@@ -7166,7 +7160,7 @@
     <row r="228" ht="15" customHeight="1" spans="1:6">
       <c r="A228" s="1"/>
       <c r="B228" s="1">
-        <v>15015</v>
+        <v>15017</v>
       </c>
       <c r="C228" s="1"/>
       <c r="D228" s="1">
@@ -7182,7 +7176,7 @@
     <row r="229" ht="15" customHeight="1" spans="1:6">
       <c r="A229" s="1"/>
       <c r="B229" s="1">
-        <v>15017</v>
+        <v>15018</v>
       </c>
       <c r="C229" s="1"/>
       <c r="D229" s="1">
@@ -7198,7 +7192,7 @@
     <row r="230" ht="15" customHeight="1" spans="1:6">
       <c r="A230" s="1"/>
       <c r="B230" s="1">
-        <v>15018</v>
+        <v>15019</v>
       </c>
       <c r="C230" s="1"/>
       <c r="D230" s="1">
@@ -7214,7 +7208,7 @@
     <row r="231" ht="15" customHeight="1" spans="1:6">
       <c r="A231" s="1"/>
       <c r="B231" s="1">
-        <v>15019</v>
+        <v>15020</v>
       </c>
       <c r="C231" s="1"/>
       <c r="D231" s="1">
@@ -7230,7 +7224,7 @@
     <row r="232" ht="15" customHeight="1" spans="1:6">
       <c r="A232" s="1"/>
       <c r="B232" s="1">
-        <v>15020</v>
+        <v>15021</v>
       </c>
       <c r="C232" s="1"/>
       <c r="D232" s="1">
@@ -7246,44 +7240,46 @@
     <row r="233" ht="15" customHeight="1" spans="1:6">
       <c r="A233" s="1"/>
       <c r="B233" s="1">
-        <v>15021</v>
-      </c>
-      <c r="C233" s="1"/>
+        <v>15022</v>
+      </c>
+      <c r="C233" s="1" t="s">
+        <v>472</v>
+      </c>
       <c r="D233" s="1">
         <v>1</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="F233" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="234" ht="15" customHeight="1" spans="1:6">
       <c r="A234" s="1"/>
       <c r="B234" s="1">
-        <v>15022</v>
+        <v>16001</v>
       </c>
       <c r="C234" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D234" s="1">
         <v>1</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F234" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="235" ht="15" customHeight="1" spans="1:6">
       <c r="A235" s="1"/>
       <c r="B235" s="1">
-        <v>16001</v>
+        <v>16002</v>
       </c>
       <c r="C235" s="1" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D235" s="1">
         <v>1</v>
@@ -7298,10 +7294,10 @@
     <row r="236" ht="15" customHeight="1" spans="1:6">
       <c r="A236" s="1"/>
       <c r="B236" s="1">
-        <v>16002</v>
+        <v>16003</v>
       </c>
       <c r="C236" s="1" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D236" s="1">
         <v>1</v>
@@ -7316,10 +7312,10 @@
     <row r="237" ht="15" customHeight="1" spans="1:6">
       <c r="A237" s="1"/>
       <c r="B237" s="1">
-        <v>16003</v>
+        <v>16004</v>
       </c>
       <c r="C237" s="1" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D237" s="1">
         <v>1</v>
@@ -7334,10 +7330,10 @@
     <row r="238" ht="15" customHeight="1" spans="1:6">
       <c r="A238" s="1"/>
       <c r="B238" s="1">
-        <v>16004</v>
+        <v>16005</v>
       </c>
       <c r="C238" s="1" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D238" s="1">
         <v>1</v>
@@ -7352,10 +7348,10 @@
     <row r="239" ht="15" customHeight="1" spans="1:6">
       <c r="A239" s="1"/>
       <c r="B239" s="1">
-        <v>16005</v>
+        <v>16006</v>
       </c>
       <c r="C239" s="1" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D239" s="1">
         <v>1</v>
@@ -7370,11 +7366,9 @@
     <row r="240" ht="15" customHeight="1" spans="1:6">
       <c r="A240" s="1"/>
       <c r="B240" s="1">
-        <v>16006</v>
-      </c>
-      <c r="C240" s="1" t="s">
-        <v>477</v>
-      </c>
+        <v>19002</v>
+      </c>
+      <c r="C240" s="1"/>
       <c r="D240" s="1">
         <v>1</v>
       </c>
@@ -7388,7 +7382,7 @@
     <row r="241" ht="15" customHeight="1" spans="1:6">
       <c r="A241" s="1"/>
       <c r="B241" s="1">
-        <v>19002</v>
+        <v>19003</v>
       </c>
       <c r="C241" s="1"/>
       <c r="D241" s="1">
@@ -7404,7 +7398,7 @@
     <row r="242" ht="15" customHeight="1" spans="1:6">
       <c r="A242" s="1"/>
       <c r="B242" s="1">
-        <v>19003</v>
+        <v>19004</v>
       </c>
       <c r="C242" s="1"/>
       <c r="D242" s="1">
@@ -7420,7 +7414,7 @@
     <row r="243" ht="15" customHeight="1" spans="1:6">
       <c r="A243" s="1"/>
       <c r="B243" s="1">
-        <v>19004</v>
+        <v>19012</v>
       </c>
       <c r="C243" s="1"/>
       <c r="D243" s="1">
@@ -7436,7 +7430,7 @@
     <row r="244" ht="15" customHeight="1" spans="1:6">
       <c r="A244" s="1"/>
       <c r="B244" s="1">
-        <v>19012</v>
+        <v>19013</v>
       </c>
       <c r="C244" s="1"/>
       <c r="D244" s="1">
@@ -7452,7 +7446,7 @@
     <row r="245" ht="15" customHeight="1" spans="1:6">
       <c r="A245" s="1"/>
       <c r="B245" s="1">
-        <v>19013</v>
+        <v>19014</v>
       </c>
       <c r="C245" s="1"/>
       <c r="D245" s="1">
@@ -7468,7 +7462,7 @@
     <row r="246" ht="15" customHeight="1" spans="1:6">
       <c r="A246" s="1"/>
       <c r="B246" s="1">
-        <v>19014</v>
+        <v>19022</v>
       </c>
       <c r="C246" s="1"/>
       <c r="D246" s="1">
@@ -7484,7 +7478,7 @@
     <row r="247" ht="15" customHeight="1" spans="1:6">
       <c r="A247" s="1"/>
       <c r="B247" s="1">
-        <v>19022</v>
+        <v>19023</v>
       </c>
       <c r="C247" s="1"/>
       <c r="D247" s="1">
@@ -7500,7 +7494,7 @@
     <row r="248" ht="15" customHeight="1" spans="1:6">
       <c r="A248" s="1"/>
       <c r="B248" s="1">
-        <v>19023</v>
+        <v>19024</v>
       </c>
       <c r="C248" s="1"/>
       <c r="D248" s="1">
@@ -7516,26 +7510,28 @@
     <row r="249" ht="15" customHeight="1" spans="1:6">
       <c r="A249" s="1"/>
       <c r="B249" s="1">
-        <v>19024</v>
-      </c>
-      <c r="C249" s="1"/>
+        <v>20101</v>
+      </c>
+      <c r="C249" s="1" t="s">
+        <v>506</v>
+      </c>
       <c r="D249" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F249" s="1" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="250" ht="15" customHeight="1" spans="1:6">
       <c r="A250" s="1"/>
       <c r="B250" s="1">
-        <v>20101</v>
+        <v>20102</v>
       </c>
       <c r="C250" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D250" s="1">
         <v>2</v>
@@ -7550,10 +7546,10 @@
     <row r="251" ht="15" customHeight="1" spans="1:6">
       <c r="A251" s="1"/>
       <c r="B251" s="1">
-        <v>20102</v>
+        <v>20103</v>
       </c>
       <c r="C251" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D251" s="1">
         <v>2</v>
@@ -7568,10 +7564,10 @@
     <row r="252" ht="15" customHeight="1" spans="1:6">
       <c r="A252" s="1"/>
       <c r="B252" s="1">
-        <v>20103</v>
+        <v>20104</v>
       </c>
       <c r="C252" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D252" s="1">
         <v>2</v>
@@ -7586,10 +7582,10 @@
     <row r="253" ht="15" customHeight="1" spans="1:6">
       <c r="A253" s="1"/>
       <c r="B253" s="1">
-        <v>20104</v>
+        <v>20105</v>
       </c>
       <c r="C253" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D253" s="1">
         <v>2</v>
@@ -7604,10 +7600,10 @@
     <row r="254" ht="15" customHeight="1" spans="1:6">
       <c r="A254" s="1"/>
       <c r="B254" s="1">
-        <v>20105</v>
+        <v>20106</v>
       </c>
       <c r="C254" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D254" s="1">
         <v>2</v>
@@ -7622,10 +7618,10 @@
     <row r="255" ht="15" customHeight="1" spans="1:6">
       <c r="A255" s="1"/>
       <c r="B255" s="1">
-        <v>20106</v>
+        <v>20107</v>
       </c>
       <c r="C255" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D255" s="1">
         <v>2</v>
@@ -7640,10 +7636,10 @@
     <row r="256" ht="15" customHeight="1" spans="1:6">
       <c r="A256" s="1"/>
       <c r="B256" s="1">
-        <v>20107</v>
+        <v>20108</v>
       </c>
       <c r="C256" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D256" s="1">
         <v>2</v>
@@ -7658,10 +7654,10 @@
     <row r="257" ht="15" customHeight="1" spans="1:6">
       <c r="A257" s="1"/>
       <c r="B257" s="1">
-        <v>20108</v>
+        <v>20109</v>
       </c>
       <c r="C257" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D257" s="1">
         <v>2</v>
@@ -7676,10 +7672,10 @@
     <row r="258" ht="15" customHeight="1" spans="1:6">
       <c r="A258" s="1"/>
       <c r="B258" s="1">
-        <v>20109</v>
+        <v>20110</v>
       </c>
       <c r="C258" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D258" s="1">
         <v>2</v>
@@ -7694,10 +7690,10 @@
     <row r="259" ht="15" customHeight="1" spans="1:6">
       <c r="A259" s="1"/>
       <c r="B259" s="1">
-        <v>20110</v>
+        <v>20111</v>
       </c>
       <c r="C259" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D259" s="1">
         <v>2</v>
@@ -7712,10 +7708,10 @@
     <row r="260" ht="15" customHeight="1" spans="1:6">
       <c r="A260" s="1"/>
       <c r="B260" s="1">
-        <v>20111</v>
+        <v>20112</v>
       </c>
       <c r="C260" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D260" s="1">
         <v>2</v>
@@ -7730,10 +7726,10 @@
     <row r="261" ht="15" customHeight="1" spans="1:6">
       <c r="A261" s="1"/>
       <c r="B261" s="1">
-        <v>20112</v>
+        <v>20113</v>
       </c>
       <c r="C261" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D261" s="1">
         <v>2</v>
@@ -7748,10 +7744,10 @@
     <row r="262" ht="15" customHeight="1" spans="1:6">
       <c r="A262" s="1"/>
       <c r="B262" s="1">
-        <v>20113</v>
+        <v>20114</v>
       </c>
       <c r="C262" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D262" s="1">
         <v>2</v>
@@ -7766,10 +7762,10 @@
     <row r="263" ht="15" customHeight="1" spans="1:6">
       <c r="A263" s="1"/>
       <c r="B263" s="1">
-        <v>20114</v>
+        <v>20115</v>
       </c>
       <c r="C263" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D263" s="1">
         <v>2</v>
@@ -7784,10 +7780,10 @@
     <row r="264" ht="15" customHeight="1" spans="1:6">
       <c r="A264" s="1"/>
       <c r="B264" s="1">
-        <v>20115</v>
+        <v>20116</v>
       </c>
       <c r="C264" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D264" s="1">
         <v>2</v>
@@ -7802,10 +7798,10 @@
     <row r="265" ht="15" customHeight="1" spans="1:6">
       <c r="A265" s="1"/>
       <c r="B265" s="1">
-        <v>20116</v>
+        <v>20117</v>
       </c>
       <c r="C265" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D265" s="1">
         <v>2</v>
@@ -7820,10 +7816,10 @@
     <row r="266" ht="15" customHeight="1" spans="1:6">
       <c r="A266" s="1"/>
       <c r="B266" s="1">
-        <v>20117</v>
+        <v>20118</v>
       </c>
       <c r="C266" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D266" s="1">
         <v>2</v>
@@ -7838,10 +7834,10 @@
     <row r="267" ht="15" customHeight="1" spans="1:6">
       <c r="A267" s="1"/>
       <c r="B267" s="1">
-        <v>20118</v>
+        <v>20119</v>
       </c>
       <c r="C267" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D267" s="1">
         <v>2</v>
@@ -7856,10 +7852,10 @@
     <row r="268" ht="15" customHeight="1" spans="1:6">
       <c r="A268" s="1"/>
       <c r="B268" s="1">
-        <v>20119</v>
+        <v>20120</v>
       </c>
       <c r="C268" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D268" s="1">
         <v>2</v>
@@ -7874,10 +7870,10 @@
     <row r="269" ht="15" customHeight="1" spans="1:6">
       <c r="A269" s="1"/>
       <c r="B269" s="1">
-        <v>20120</v>
+        <v>20121</v>
       </c>
       <c r="C269" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D269" s="1">
         <v>2</v>
@@ -7892,10 +7888,10 @@
     <row r="270" ht="15" customHeight="1" spans="1:6">
       <c r="A270" s="1"/>
       <c r="B270" s="1">
-        <v>20121</v>
+        <v>20122</v>
       </c>
       <c r="C270" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D270" s="1">
         <v>2</v>
@@ -7910,10 +7906,10 @@
     <row r="271" ht="15" customHeight="1" spans="1:6">
       <c r="A271" s="1"/>
       <c r="B271" s="1">
-        <v>20122</v>
+        <v>20123</v>
       </c>
       <c r="C271" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D271" s="1">
         <v>2</v>
@@ -7928,10 +7924,10 @@
     <row r="272" ht="15" customHeight="1" spans="1:6">
       <c r="A272" s="1"/>
       <c r="B272" s="1">
-        <v>20123</v>
+        <v>20124</v>
       </c>
       <c r="C272" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D272" s="1">
         <v>2</v>
@@ -7946,10 +7942,10 @@
     <row r="273" ht="15" customHeight="1" spans="1:6">
       <c r="A273" s="1"/>
       <c r="B273" s="1">
-        <v>20124</v>
+        <v>20125</v>
       </c>
       <c r="C273" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D273" s="1">
         <v>2</v>
@@ -7964,10 +7960,10 @@
     <row r="274" ht="15" customHeight="1" spans="1:6">
       <c r="A274" s="1"/>
       <c r="B274" s="1">
-        <v>20125</v>
+        <v>20126</v>
       </c>
       <c r="C274" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D274" s="1">
         <v>2</v>
@@ -7982,10 +7978,10 @@
     <row r="275" ht="15" customHeight="1" spans="1:6">
       <c r="A275" s="1"/>
       <c r="B275" s="1">
-        <v>20126</v>
+        <v>20127</v>
       </c>
       <c r="C275" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D275" s="1">
         <v>2</v>
@@ -8000,13 +7996,13 @@
     <row r="276" ht="15" customHeight="1" spans="1:6">
       <c r="A276" s="1"/>
       <c r="B276" s="1">
-        <v>20127</v>
+        <v>30101</v>
       </c>
       <c r="C276" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D276" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E276" s="1" t="s">
         <v>561</v>
@@ -8018,10 +8014,10 @@
     <row r="277" ht="15" customHeight="1" spans="1:6">
       <c r="A277" s="1"/>
       <c r="B277" s="1">
-        <v>30101</v>
+        <v>30102</v>
       </c>
       <c r="C277" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D277" s="1">
         <v>3</v>
@@ -8036,10 +8032,10 @@
     <row r="278" ht="15" customHeight="1" spans="1:6">
       <c r="A278" s="1"/>
       <c r="B278" s="1">
-        <v>30102</v>
+        <v>30103</v>
       </c>
       <c r="C278" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D278" s="1">
         <v>3</v>
@@ -8054,10 +8050,10 @@
     <row r="279" ht="15" customHeight="1" spans="1:6">
       <c r="A279" s="1"/>
       <c r="B279" s="1">
-        <v>30103</v>
+        <v>30104</v>
       </c>
       <c r="C279" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D279" s="1">
         <v>3</v>
@@ -8072,10 +8068,10 @@
     <row r="280" ht="15" customHeight="1" spans="1:6">
       <c r="A280" s="1"/>
       <c r="B280" s="1">
-        <v>30104</v>
+        <v>30105</v>
       </c>
       <c r="C280" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D280" s="1">
         <v>3</v>
@@ -8090,10 +8086,10 @@
     <row r="281" ht="15" customHeight="1" spans="1:6">
       <c r="A281" s="1"/>
       <c r="B281" s="1">
-        <v>30105</v>
+        <v>30106</v>
       </c>
       <c r="C281" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D281" s="1">
         <v>3</v>
@@ -8108,10 +8104,10 @@
     <row r="282" ht="15" customHeight="1" spans="1:6">
       <c r="A282" s="1"/>
       <c r="B282" s="1">
-        <v>30106</v>
+        <v>30107</v>
       </c>
       <c r="C282" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D282" s="1">
         <v>3</v>
@@ -8126,10 +8122,10 @@
     <row r="283" ht="15" customHeight="1" spans="1:6">
       <c r="A283" s="1"/>
       <c r="B283" s="1">
-        <v>30107</v>
+        <v>30108</v>
       </c>
       <c r="C283" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D283" s="1">
         <v>3</v>
@@ -8144,10 +8140,10 @@
     <row r="284" ht="15" customHeight="1" spans="1:6">
       <c r="A284" s="1"/>
       <c r="B284" s="1">
-        <v>30108</v>
+        <v>30109</v>
       </c>
       <c r="C284" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D284" s="1">
         <v>3</v>
@@ -8162,10 +8158,10 @@
     <row r="285" ht="15" customHeight="1" spans="1:6">
       <c r="A285" s="1"/>
       <c r="B285" s="1">
-        <v>30109</v>
+        <v>30110</v>
       </c>
       <c r="C285" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D285" s="1">
         <v>3</v>
@@ -8180,10 +8176,10 @@
     <row r="286" ht="15" customHeight="1" spans="1:6">
       <c r="A286" s="1"/>
       <c r="B286" s="1">
-        <v>30110</v>
+        <v>30111</v>
       </c>
       <c r="C286" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D286" s="1">
         <v>3</v>
@@ -8198,10 +8194,10 @@
     <row r="287" ht="15" customHeight="1" spans="1:6">
       <c r="A287" s="1"/>
       <c r="B287" s="1">
-        <v>30111</v>
+        <v>30112</v>
       </c>
       <c r="C287" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D287" s="1">
         <v>3</v>
@@ -8216,10 +8212,10 @@
     <row r="288" ht="15" customHeight="1" spans="1:6">
       <c r="A288" s="1"/>
       <c r="B288" s="1">
-        <v>30112</v>
+        <v>30113</v>
       </c>
       <c r="C288" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D288" s="1">
         <v>3</v>
@@ -8234,10 +8230,10 @@
     <row r="289" ht="15" customHeight="1" spans="1:6">
       <c r="A289" s="1"/>
       <c r="B289" s="1">
-        <v>30113</v>
+        <v>30114</v>
       </c>
       <c r="C289" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D289" s="1">
         <v>3</v>
@@ -8252,10 +8248,10 @@
     <row r="290" ht="15" customHeight="1" spans="1:6">
       <c r="A290" s="1"/>
       <c r="B290" s="1">
-        <v>30114</v>
+        <v>30115</v>
       </c>
       <c r="C290" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D290" s="1">
         <v>3</v>
@@ -8270,10 +8266,10 @@
     <row r="291" ht="15" customHeight="1" spans="1:6">
       <c r="A291" s="1"/>
       <c r="B291" s="1">
-        <v>30115</v>
+        <v>30116</v>
       </c>
       <c r="C291" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D291" s="1">
         <v>3</v>
@@ -8288,10 +8284,10 @@
     <row r="292" ht="15" customHeight="1" spans="1:6">
       <c r="A292" s="1"/>
       <c r="B292" s="1">
-        <v>30116</v>
+        <v>30117</v>
       </c>
       <c r="C292" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D292" s="1">
         <v>3</v>
@@ -8306,10 +8302,10 @@
     <row r="293" ht="15" customHeight="1" spans="1:6">
       <c r="A293" s="1"/>
       <c r="B293" s="1">
-        <v>30117</v>
+        <v>30118</v>
       </c>
       <c r="C293" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D293" s="1">
         <v>3</v>
@@ -8324,10 +8320,10 @@
     <row r="294" ht="15" customHeight="1" spans="1:6">
       <c r="A294" s="1"/>
       <c r="B294" s="1">
-        <v>30118</v>
+        <v>30119</v>
       </c>
       <c r="C294" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D294" s="1">
         <v>3</v>
@@ -8342,10 +8338,10 @@
     <row r="295" ht="15" customHeight="1" spans="1:6">
       <c r="A295" s="1"/>
       <c r="B295" s="1">
-        <v>30119</v>
+        <v>30120</v>
       </c>
       <c r="C295" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D295" s="1">
         <v>3</v>
@@ -8360,10 +8356,10 @@
     <row r="296" ht="15" customHeight="1" spans="1:6">
       <c r="A296" s="1"/>
       <c r="B296" s="1">
-        <v>30120</v>
+        <v>30121</v>
       </c>
       <c r="C296" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D296" s="1">
         <v>3</v>
@@ -8378,10 +8374,10 @@
     <row r="297" ht="15" customHeight="1" spans="1:6">
       <c r="A297" s="1"/>
       <c r="B297" s="1">
-        <v>30121</v>
+        <v>30122</v>
       </c>
       <c r="C297" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D297" s="1">
         <v>3</v>
@@ -8396,10 +8392,10 @@
     <row r="298" ht="15" customHeight="1" spans="1:6">
       <c r="A298" s="1"/>
       <c r="B298" s="1">
-        <v>30122</v>
+        <v>30123</v>
       </c>
       <c r="C298" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D298" s="1">
         <v>3</v>
@@ -8414,10 +8410,10 @@
     <row r="299" ht="15" customHeight="1" spans="1:6">
       <c r="A299" s="1"/>
       <c r="B299" s="1">
-        <v>30123</v>
+        <v>30124</v>
       </c>
       <c r="C299" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D299" s="1">
         <v>3</v>
@@ -8432,10 +8428,10 @@
     <row r="300" ht="15" customHeight="1" spans="1:6">
       <c r="A300" s="1"/>
       <c r="B300" s="1">
-        <v>30124</v>
+        <v>30125</v>
       </c>
       <c r="C300" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D300" s="1">
         <v>3</v>
@@ -8450,10 +8446,10 @@
     <row r="301" ht="15" customHeight="1" spans="1:6">
       <c r="A301" s="1"/>
       <c r="B301" s="1">
-        <v>30125</v>
+        <v>30201</v>
       </c>
       <c r="C301" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D301" s="1">
         <v>3</v>
@@ -8468,10 +8464,10 @@
     <row r="302" ht="15" customHeight="1" spans="1:6">
       <c r="A302" s="1"/>
       <c r="B302" s="1">
-        <v>30201</v>
+        <v>30202</v>
       </c>
       <c r="C302" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D302" s="1">
         <v>3</v>
@@ -8486,10 +8482,10 @@
     <row r="303" ht="15" customHeight="1" spans="1:6">
       <c r="A303" s="1"/>
       <c r="B303" s="1">
-        <v>30202</v>
+        <v>30203</v>
       </c>
       <c r="C303" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D303" s="1">
         <v>3</v>
@@ -8504,10 +8500,10 @@
     <row r="304" ht="15" customHeight="1" spans="1:6">
       <c r="A304" s="1"/>
       <c r="B304" s="1">
-        <v>30203</v>
+        <v>30204</v>
       </c>
       <c r="C304" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D304" s="1">
         <v>3</v>
@@ -8522,10 +8518,10 @@
     <row r="305" ht="15" customHeight="1" spans="1:6">
       <c r="A305" s="1"/>
       <c r="B305" s="1">
-        <v>30204</v>
+        <v>30205</v>
       </c>
       <c r="C305" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D305" s="1">
         <v>3</v>
@@ -8540,10 +8536,10 @@
     <row r="306" ht="15" customHeight="1" spans="1:6">
       <c r="A306" s="1"/>
       <c r="B306" s="1">
-        <v>30205</v>
+        <v>30206</v>
       </c>
       <c r="C306" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D306" s="1">
         <v>3</v>
@@ -8558,10 +8554,10 @@
     <row r="307" ht="15" customHeight="1" spans="1:6">
       <c r="A307" s="1"/>
       <c r="B307" s="1">
-        <v>30206</v>
+        <v>30301</v>
       </c>
       <c r="C307" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D307" s="1">
         <v>3</v>
@@ -8576,10 +8572,10 @@
     <row r="308" ht="15" customHeight="1" spans="1:6">
       <c r="A308" s="1"/>
       <c r="B308" s="1">
-        <v>30301</v>
+        <v>30302</v>
       </c>
       <c r="C308" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D308" s="1">
         <v>3</v>
@@ -8594,10 +8590,10 @@
     <row r="309" ht="15" customHeight="1" spans="1:6">
       <c r="A309" s="1"/>
       <c r="B309" s="1">
-        <v>30302</v>
+        <v>30303</v>
       </c>
       <c r="C309" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D309" s="1">
         <v>3</v>
@@ -8612,10 +8608,10 @@
     <row r="310" ht="15" customHeight="1" spans="1:6">
       <c r="A310" s="1"/>
       <c r="B310" s="1">
-        <v>30303</v>
+        <v>30304</v>
       </c>
       <c r="C310" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D310" s="1">
         <v>3</v>
@@ -8630,10 +8626,10 @@
     <row r="311" ht="15" customHeight="1" spans="1:6">
       <c r="A311" s="1"/>
       <c r="B311" s="1">
-        <v>30304</v>
+        <v>30305</v>
       </c>
       <c r="C311" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D311" s="1">
         <v>3</v>
@@ -8648,10 +8644,10 @@
     <row r="312" ht="15" customHeight="1" spans="1:6">
       <c r="A312" s="1"/>
       <c r="B312" s="1">
-        <v>30305</v>
+        <v>30306</v>
       </c>
       <c r="C312" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D312" s="1">
         <v>3</v>
@@ -8666,10 +8662,10 @@
     <row r="313" ht="15" customHeight="1" spans="1:6">
       <c r="A313" s="1"/>
       <c r="B313" s="1">
-        <v>30306</v>
+        <v>30307</v>
       </c>
       <c r="C313" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D313" s="1">
         <v>3</v>
@@ -8684,10 +8680,10 @@
     <row r="314" ht="15" customHeight="1" spans="1:6">
       <c r="A314" s="1"/>
       <c r="B314" s="1">
-        <v>30307</v>
+        <v>30308</v>
       </c>
       <c r="C314" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D314" s="1">
         <v>3</v>
@@ -8702,28 +8698,28 @@
     <row r="315" ht="15" customHeight="1" spans="1:6">
       <c r="A315" s="1"/>
       <c r="B315" s="1">
-        <v>30308</v>
+        <v>60001</v>
       </c>
       <c r="C315" s="1" t="s">
-        <v>508</v>
+        <v>639</v>
       </c>
       <c r="D315" s="1">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E315" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="F315" s="1" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="316" ht="15" customHeight="1" spans="1:6">
       <c r="A316" s="1"/>
       <c r="B316" s="1">
-        <v>60001</v>
+        <v>60002</v>
       </c>
       <c r="C316" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D316" s="1">
         <v>7</v>
@@ -8738,10 +8734,10 @@
     <row r="317" ht="15" customHeight="1" spans="1:6">
       <c r="A317" s="1"/>
       <c r="B317" s="1">
-        <v>60002</v>
+        <v>60003</v>
       </c>
       <c r="C317" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D317" s="1">
         <v>7</v>
@@ -8756,10 +8752,10 @@
     <row r="318" ht="15" customHeight="1" spans="1:6">
       <c r="A318" s="1"/>
       <c r="B318" s="1">
-        <v>60003</v>
+        <v>60004</v>
       </c>
       <c r="C318" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D318" s="1">
         <v>7</v>
@@ -8774,10 +8770,10 @@
     <row r="319" ht="15" customHeight="1" spans="1:6">
       <c r="A319" s="1"/>
       <c r="B319" s="1">
-        <v>60004</v>
+        <v>60005</v>
       </c>
       <c r="C319" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D319" s="1">
         <v>7</v>
@@ -8792,10 +8788,10 @@
     <row r="320" ht="15" customHeight="1" spans="1:6">
       <c r="A320" s="1"/>
       <c r="B320" s="1">
-        <v>60005</v>
+        <v>60006</v>
       </c>
       <c r="C320" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D320" s="1">
         <v>7</v>
@@ -8810,10 +8806,10 @@
     <row r="321" ht="15" customHeight="1" spans="1:6">
       <c r="A321" s="1"/>
       <c r="B321" s="1">
-        <v>60006</v>
+        <v>60007</v>
       </c>
       <c r="C321" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D321" s="1">
         <v>7</v>
@@ -8828,10 +8824,10 @@
     <row r="322" ht="15" customHeight="1" spans="1:6">
       <c r="A322" s="1"/>
       <c r="B322" s="1">
-        <v>60007</v>
+        <v>60008</v>
       </c>
       <c r="C322" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D322" s="1">
         <v>7</v>
@@ -8846,10 +8842,10 @@
     <row r="323" ht="15" customHeight="1" spans="1:6">
       <c r="A323" s="1"/>
       <c r="B323" s="1">
-        <v>60008</v>
+        <v>60009</v>
       </c>
       <c r="C323" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D323" s="1">
         <v>7</v>
@@ -8864,10 +8860,10 @@
     <row r="324" ht="15" customHeight="1" spans="1:6">
       <c r="A324" s="1"/>
       <c r="B324" s="1">
-        <v>60009</v>
+        <v>60010</v>
       </c>
       <c r="C324" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D324" s="1">
         <v>7</v>
@@ -8882,10 +8878,10 @@
     <row r="325" ht="15" customHeight="1" spans="1:6">
       <c r="A325" s="1"/>
       <c r="B325" s="1">
-        <v>60010</v>
+        <v>60011</v>
       </c>
       <c r="C325" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D325" s="1">
         <v>7</v>
@@ -8900,10 +8896,10 @@
     <row r="326" ht="15" customHeight="1" spans="1:6">
       <c r="A326" s="1"/>
       <c r="B326" s="1">
-        <v>60011</v>
+        <v>60012</v>
       </c>
       <c r="C326" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D326" s="1">
         <v>7</v>
@@ -8918,10 +8914,10 @@
     <row r="327" ht="15" customHeight="1" spans="1:6">
       <c r="A327" s="1"/>
       <c r="B327" s="1">
-        <v>60012</v>
+        <v>60013</v>
       </c>
       <c r="C327" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D327" s="1">
         <v>7</v>
@@ -8936,10 +8932,10 @@
     <row r="328" ht="15" customHeight="1" spans="1:6">
       <c r="A328" s="1"/>
       <c r="B328" s="1">
-        <v>60013</v>
+        <v>60014</v>
       </c>
       <c r="C328" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D328" s="1">
         <v>7</v>
@@ -8954,10 +8950,10 @@
     <row r="329" ht="15" customHeight="1" spans="1:6">
       <c r="A329" s="1"/>
       <c r="B329" s="1">
-        <v>60014</v>
+        <v>60015</v>
       </c>
       <c r="C329" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D329" s="1">
         <v>7</v>
@@ -8972,10 +8968,10 @@
     <row r="330" ht="15" customHeight="1" spans="1:6">
       <c r="A330" s="1"/>
       <c r="B330" s="1">
-        <v>60015</v>
+        <v>60016</v>
       </c>
       <c r="C330" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D330" s="1">
         <v>7</v>
@@ -8990,10 +8986,10 @@
     <row r="331" ht="15" customHeight="1" spans="1:6">
       <c r="A331" s="1"/>
       <c r="B331" s="1">
-        <v>60016</v>
+        <v>60017</v>
       </c>
       <c r="C331" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D331" s="1">
         <v>7</v>
@@ -9008,10 +9004,10 @@
     <row r="332" ht="15" customHeight="1" spans="1:6">
       <c r="A332" s="1"/>
       <c r="B332" s="1">
-        <v>60017</v>
+        <v>60018</v>
       </c>
       <c r="C332" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D332" s="1">
         <v>7</v>
@@ -9026,10 +9022,10 @@
     <row r="333" ht="15" customHeight="1" spans="1:6">
       <c r="A333" s="1"/>
       <c r="B333" s="1">
-        <v>60018</v>
+        <v>60019</v>
       </c>
       <c r="C333" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D333" s="1">
         <v>7</v>
@@ -9044,10 +9040,10 @@
     <row r="334" ht="15" customHeight="1" spans="1:6">
       <c r="A334" s="1"/>
       <c r="B334" s="1">
-        <v>60019</v>
+        <v>60020</v>
       </c>
       <c r="C334" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D334" s="1">
         <v>7</v>
@@ -9062,10 +9058,10 @@
     <row r="335" ht="15" customHeight="1" spans="1:6">
       <c r="A335" s="1"/>
       <c r="B335" s="1">
-        <v>60020</v>
+        <v>60021</v>
       </c>
       <c r="C335" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D335" s="1">
         <v>7</v>
@@ -9080,10 +9076,10 @@
     <row r="336" ht="15" customHeight="1" spans="1:6">
       <c r="A336" s="1"/>
       <c r="B336" s="1">
-        <v>60021</v>
+        <v>60022</v>
       </c>
       <c r="C336" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D336" s="1">
         <v>7</v>
@@ -9098,10 +9094,10 @@
     <row r="337" ht="15" customHeight="1" spans="1:6">
       <c r="A337" s="1"/>
       <c r="B337" s="1">
-        <v>60022</v>
+        <v>60023</v>
       </c>
       <c r="C337" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D337" s="1">
         <v>7</v>
@@ -9116,10 +9112,10 @@
     <row r="338" ht="15" customHeight="1" spans="1:6">
       <c r="A338" s="1"/>
       <c r="B338" s="1">
-        <v>60023</v>
+        <v>60024</v>
       </c>
       <c r="C338" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D338" s="1">
         <v>7</v>
@@ -9134,10 +9130,10 @@
     <row r="339" ht="15" customHeight="1" spans="1:6">
       <c r="A339" s="1"/>
       <c r="B339" s="1">
-        <v>60024</v>
+        <v>60025</v>
       </c>
       <c r="C339" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D339" s="1">
         <v>7</v>
@@ -9152,10 +9148,10 @@
     <row r="340" ht="15" customHeight="1" spans="1:6">
       <c r="A340" s="1"/>
       <c r="B340" s="1">
-        <v>60025</v>
+        <v>60026</v>
       </c>
       <c r="C340" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D340" s="1">
         <v>7</v>
@@ -9170,10 +9166,10 @@
     <row r="341" ht="15" customHeight="1" spans="1:6">
       <c r="A341" s="1"/>
       <c r="B341" s="1">
-        <v>60026</v>
+        <v>60027</v>
       </c>
       <c r="C341" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D341" s="1">
         <v>7</v>
@@ -9188,10 +9184,10 @@
     <row r="342" ht="15" customHeight="1" spans="1:6">
       <c r="A342" s="1"/>
       <c r="B342" s="1">
-        <v>60027</v>
+        <v>60028</v>
       </c>
       <c r="C342" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D342" s="1">
         <v>7</v>
@@ -9206,10 +9202,10 @@
     <row r="343" ht="15" customHeight="1" spans="1:6">
       <c r="A343" s="1"/>
       <c r="B343" s="1">
-        <v>60028</v>
+        <v>60029</v>
       </c>
       <c r="C343" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D343" s="1">
         <v>7</v>
@@ -9224,10 +9220,10 @@
     <row r="344" ht="15" customHeight="1" spans="1:6">
       <c r="A344" s="1"/>
       <c r="B344" s="1">
-        <v>60029</v>
+        <v>60030</v>
       </c>
       <c r="C344" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D344" s="1">
         <v>7</v>
@@ -9242,10 +9238,10 @@
     <row r="345" ht="15" customHeight="1" spans="1:6">
       <c r="A345" s="1"/>
       <c r="B345" s="1">
-        <v>60030</v>
+        <v>60031</v>
       </c>
       <c r="C345" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D345" s="1">
         <v>7</v>
@@ -9260,10 +9256,10 @@
     <row r="346" ht="15" customHeight="1" spans="1:6">
       <c r="A346" s="1"/>
       <c r="B346" s="1">
-        <v>60031</v>
+        <v>60032</v>
       </c>
       <c r="C346" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D346" s="1">
         <v>7</v>
@@ -9278,10 +9274,10 @@
     <row r="347" ht="15" customHeight="1" spans="1:6">
       <c r="A347" s="1"/>
       <c r="B347" s="1">
-        <v>60032</v>
+        <v>60033</v>
       </c>
       <c r="C347" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D347" s="1">
         <v>7</v>
@@ -9296,10 +9292,10 @@
     <row r="348" ht="15" customHeight="1" spans="1:6">
       <c r="A348" s="1"/>
       <c r="B348" s="1">
-        <v>60033</v>
+        <v>60034</v>
       </c>
       <c r="C348" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D348" s="1">
         <v>7</v>
@@ -9314,10 +9310,10 @@
     <row r="349" ht="15" customHeight="1" spans="1:6">
       <c r="A349" s="1"/>
       <c r="B349" s="1">
-        <v>60034</v>
+        <v>60035</v>
       </c>
       <c r="C349" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D349" s="1">
         <v>7</v>
@@ -9332,10 +9328,10 @@
     <row r="350" ht="15" customHeight="1" spans="1:6">
       <c r="A350" s="1"/>
       <c r="B350" s="1">
-        <v>60035</v>
+        <v>60036</v>
       </c>
       <c r="C350" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D350" s="1">
         <v>7</v>
@@ -9350,10 +9346,10 @@
     <row r="351" ht="15" customHeight="1" spans="1:6">
       <c r="A351" s="1"/>
       <c r="B351" s="1">
-        <v>60036</v>
+        <v>60037</v>
       </c>
       <c r="C351" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D351" s="1">
         <v>7</v>
@@ -9368,10 +9364,10 @@
     <row r="352" ht="15" customHeight="1" spans="1:6">
       <c r="A352" s="1"/>
       <c r="B352" s="1">
-        <v>60037</v>
+        <v>60038</v>
       </c>
       <c r="C352" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D352" s="1">
         <v>7</v>
@@ -9386,10 +9382,10 @@
     <row r="353" ht="15" customHeight="1" spans="1:6">
       <c r="A353" s="1"/>
       <c r="B353" s="1">
-        <v>60038</v>
+        <v>60039</v>
       </c>
       <c r="C353" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D353" s="1">
         <v>7</v>
@@ -9404,10 +9400,10 @@
     <row r="354" ht="15" customHeight="1" spans="1:6">
       <c r="A354" s="1"/>
       <c r="B354" s="1">
-        <v>60039</v>
+        <v>60040</v>
       </c>
       <c r="C354" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D354" s="1">
         <v>7</v>
@@ -9422,10 +9418,10 @@
     <row r="355" ht="15" customHeight="1" spans="1:6">
       <c r="A355" s="1"/>
       <c r="B355" s="1">
-        <v>60040</v>
+        <v>60041</v>
       </c>
       <c r="C355" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D355" s="1">
         <v>7</v>
@@ -9440,10 +9436,10 @@
     <row r="356" ht="15" customHeight="1" spans="1:6">
       <c r="A356" s="1"/>
       <c r="B356" s="1">
-        <v>60041</v>
+        <v>60042</v>
       </c>
       <c r="C356" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D356" s="1">
         <v>7</v>
@@ -9458,10 +9454,10 @@
     <row r="357" ht="15" customHeight="1" spans="1:6">
       <c r="A357" s="1"/>
       <c r="B357" s="1">
-        <v>60042</v>
+        <v>60043</v>
       </c>
       <c r="C357" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D357" s="1">
         <v>7</v>
@@ -9476,10 +9472,10 @@
     <row r="358" ht="15" customHeight="1" spans="1:6">
       <c r="A358" s="1"/>
       <c r="B358" s="1">
-        <v>60043</v>
+        <v>60044</v>
       </c>
       <c r="C358" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D358" s="1">
         <v>7</v>
@@ -9494,10 +9490,10 @@
     <row r="359" ht="15" customHeight="1" spans="1:6">
       <c r="A359" s="1"/>
       <c r="B359" s="1">
-        <v>60044</v>
+        <v>60045</v>
       </c>
       <c r="C359" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D359" s="1">
         <v>7</v>
@@ -9512,10 +9508,10 @@
     <row r="360" ht="15" customHeight="1" spans="1:6">
       <c r="A360" s="1"/>
       <c r="B360" s="1">
-        <v>60045</v>
+        <v>60046</v>
       </c>
       <c r="C360" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D360" s="1">
         <v>7</v>
@@ -9530,10 +9526,10 @@
     <row r="361" ht="15" customHeight="1" spans="1:6">
       <c r="A361" s="1"/>
       <c r="B361" s="1">
-        <v>60046</v>
+        <v>60047</v>
       </c>
       <c r="C361" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D361" s="1">
         <v>7</v>
@@ -9548,10 +9544,10 @@
     <row r="362" ht="15" customHeight="1" spans="1:6">
       <c r="A362" s="1"/>
       <c r="B362" s="1">
-        <v>60047</v>
+        <v>60048</v>
       </c>
       <c r="C362" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D362" s="1">
         <v>7</v>
@@ -9566,10 +9562,10 @@
     <row r="363" ht="15" customHeight="1" spans="1:6">
       <c r="A363" s="1"/>
       <c r="B363" s="1">
-        <v>60048</v>
+        <v>60049</v>
       </c>
       <c r="C363" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D363" s="1">
         <v>7</v>
@@ -9584,10 +9580,10 @@
     <row r="364" ht="15" customHeight="1" spans="1:6">
       <c r="A364" s="1"/>
       <c r="B364" s="1">
-        <v>60049</v>
+        <v>60050</v>
       </c>
       <c r="C364" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D364" s="1">
         <v>7</v>
@@ -9602,10 +9598,10 @@
     <row r="365" ht="15" customHeight="1" spans="1:6">
       <c r="A365" s="1"/>
       <c r="B365" s="1">
-        <v>60050</v>
+        <v>60051</v>
       </c>
       <c r="C365" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D365" s="1">
         <v>7</v>
@@ -9620,10 +9616,10 @@
     <row r="366" ht="15" customHeight="1" spans="1:6">
       <c r="A366" s="1"/>
       <c r="B366" s="1">
-        <v>60051</v>
+        <v>60052</v>
       </c>
       <c r="C366" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D366" s="1">
         <v>7</v>
@@ -9638,10 +9634,10 @@
     <row r="367" ht="15" customHeight="1" spans="1:6">
       <c r="A367" s="1"/>
       <c r="B367" s="1">
-        <v>60052</v>
+        <v>60053</v>
       </c>
       <c r="C367" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D367" s="1">
         <v>7</v>
@@ -9656,10 +9652,10 @@
     <row r="368" ht="15" customHeight="1" spans="1:6">
       <c r="A368" s="1"/>
       <c r="B368" s="1">
-        <v>60053</v>
+        <v>60054</v>
       </c>
       <c r="C368" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D368" s="1">
         <v>7</v>
@@ -9674,10 +9670,10 @@
     <row r="369" ht="15" customHeight="1" spans="1:6">
       <c r="A369" s="1"/>
       <c r="B369" s="1">
-        <v>60054</v>
+        <v>60055</v>
       </c>
       <c r="C369" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D369" s="1">
         <v>7</v>
@@ -9692,10 +9688,10 @@
     <row r="370" ht="15" customHeight="1" spans="1:6">
       <c r="A370" s="1"/>
       <c r="B370" s="1">
-        <v>60055</v>
+        <v>60056</v>
       </c>
       <c r="C370" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D370" s="1">
         <v>7</v>
@@ -9710,10 +9706,10 @@
     <row r="371" ht="15" customHeight="1" spans="1:6">
       <c r="A371" s="1"/>
       <c r="B371" s="1">
-        <v>60056</v>
+        <v>60057</v>
       </c>
       <c r="C371" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D371" s="1">
         <v>7</v>
@@ -9728,10 +9724,10 @@
     <row r="372" ht="15" customHeight="1" spans="1:6">
       <c r="A372" s="1"/>
       <c r="B372" s="1">
-        <v>60057</v>
+        <v>60058</v>
       </c>
       <c r="C372" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D372" s="1">
         <v>7</v>
@@ -9746,10 +9742,10 @@
     <row r="373" ht="15" customHeight="1" spans="1:6">
       <c r="A373" s="1"/>
       <c r="B373" s="1">
-        <v>60058</v>
+        <v>60059</v>
       </c>
       <c r="C373" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D373" s="1">
         <v>7</v>
@@ -9764,10 +9760,10 @@
     <row r="374" ht="15" customHeight="1" spans="1:6">
       <c r="A374" s="1"/>
       <c r="B374" s="1">
-        <v>60059</v>
+        <v>60060</v>
       </c>
       <c r="C374" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D374" s="1">
         <v>7</v>
@@ -9782,10 +9778,10 @@
     <row r="375" ht="15" customHeight="1" spans="1:6">
       <c r="A375" s="1"/>
       <c r="B375" s="1">
-        <v>60060</v>
+        <v>60061</v>
       </c>
       <c r="C375" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D375" s="1">
         <v>7</v>
@@ -9800,10 +9796,10 @@
     <row r="376" ht="15" customHeight="1" spans="1:6">
       <c r="A376" s="1"/>
       <c r="B376" s="1">
-        <v>60061</v>
+        <v>60062</v>
       </c>
       <c r="C376" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D376" s="1">
         <v>7</v>
@@ -9818,10 +9814,10 @@
     <row r="377" ht="15" customHeight="1" spans="1:6">
       <c r="A377" s="1"/>
       <c r="B377" s="1">
-        <v>60062</v>
+        <v>60063</v>
       </c>
       <c r="C377" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D377" s="1">
         <v>7</v>
@@ -9836,10 +9832,10 @@
     <row r="378" ht="15" customHeight="1" spans="1:6">
       <c r="A378" s="1"/>
       <c r="B378" s="1">
-        <v>60063</v>
+        <v>60064</v>
       </c>
       <c r="C378" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D378" s="1">
         <v>7</v>
@@ -9854,10 +9850,10 @@
     <row r="379" ht="15" customHeight="1" spans="1:6">
       <c r="A379" s="1"/>
       <c r="B379" s="1">
-        <v>60064</v>
+        <v>60065</v>
       </c>
       <c r="C379" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D379" s="1">
         <v>7</v>
@@ -9872,10 +9868,10 @@
     <row r="380" ht="15" customHeight="1" spans="1:6">
       <c r="A380" s="1"/>
       <c r="B380" s="1">
-        <v>60065</v>
+        <v>60066</v>
       </c>
       <c r="C380" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D380" s="1">
         <v>7</v>
@@ -9890,10 +9886,10 @@
     <row r="381" ht="15" customHeight="1" spans="1:6">
       <c r="A381" s="1"/>
       <c r="B381" s="1">
-        <v>60066</v>
+        <v>60067</v>
       </c>
       <c r="C381" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D381" s="1">
         <v>7</v>
@@ -9908,10 +9904,10 @@
     <row r="382" ht="15" customHeight="1" spans="1:6">
       <c r="A382" s="1"/>
       <c r="B382" s="1">
-        <v>60067</v>
+        <v>60068</v>
       </c>
       <c r="C382" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D382" s="1">
         <v>7</v>
@@ -9926,10 +9922,10 @@
     <row r="383" ht="15" customHeight="1" spans="1:6">
       <c r="A383" s="1"/>
       <c r="B383" s="1">
-        <v>60068</v>
+        <v>60069</v>
       </c>
       <c r="C383" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D383" s="1">
         <v>7</v>
@@ -9944,10 +9940,10 @@
     <row r="384" ht="15" customHeight="1" spans="1:6">
       <c r="A384" s="1"/>
       <c r="B384" s="1">
-        <v>60069</v>
+        <v>60070</v>
       </c>
       <c r="C384" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D384" s="1">
         <v>7</v>
@@ -9962,10 +9958,10 @@
     <row r="385" ht="15" customHeight="1" spans="1:6">
       <c r="A385" s="1"/>
       <c r="B385" s="1">
-        <v>60070</v>
+        <v>60071</v>
       </c>
       <c r="C385" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D385" s="1">
         <v>7</v>
@@ -9980,10 +9976,10 @@
     <row r="386" ht="15" customHeight="1" spans="1:6">
       <c r="A386" s="1"/>
       <c r="B386" s="1">
-        <v>60071</v>
+        <v>60072</v>
       </c>
       <c r="C386" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D386" s="1">
         <v>7</v>
@@ -9998,10 +9994,10 @@
     <row r="387" ht="15" customHeight="1" spans="1:6">
       <c r="A387" s="1"/>
       <c r="B387" s="1">
-        <v>60072</v>
+        <v>60073</v>
       </c>
       <c r="C387" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D387" s="1">
         <v>7</v>
@@ -10016,10 +10012,10 @@
     <row r="388" ht="15" customHeight="1" spans="1:6">
       <c r="A388" s="1"/>
       <c r="B388" s="1">
-        <v>60073</v>
+        <v>60074</v>
       </c>
       <c r="C388" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D388" s="1">
         <v>7</v>
@@ -10034,10 +10030,10 @@
     <row r="389" ht="15" customHeight="1" spans="1:6">
       <c r="A389" s="1"/>
       <c r="B389" s="1">
-        <v>60074</v>
+        <v>60075</v>
       </c>
       <c r="C389" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D389" s="1">
         <v>7</v>
@@ -10052,10 +10048,10 @@
     <row r="390" ht="15" customHeight="1" spans="1:6">
       <c r="A390" s="1"/>
       <c r="B390" s="1">
-        <v>60075</v>
+        <v>60076</v>
       </c>
       <c r="C390" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D390" s="1">
         <v>7</v>
@@ -10070,10 +10066,10 @@
     <row r="391" ht="15" customHeight="1" spans="1:6">
       <c r="A391" s="1"/>
       <c r="B391" s="1">
-        <v>60076</v>
+        <v>60077</v>
       </c>
       <c r="C391" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D391" s="1">
         <v>7</v>
@@ -10088,10 +10084,10 @@
     <row r="392" ht="15" customHeight="1" spans="1:6">
       <c r="A392" s="1"/>
       <c r="B392" s="1">
-        <v>60077</v>
+        <v>60078</v>
       </c>
       <c r="C392" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D392" s="1">
         <v>7</v>
@@ -10106,10 +10102,10 @@
     <row r="393" ht="15" customHeight="1" spans="1:6">
       <c r="A393" s="1"/>
       <c r="B393" s="1">
-        <v>60078</v>
+        <v>60079</v>
       </c>
       <c r="C393" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D393" s="1">
         <v>7</v>
@@ -10124,10 +10120,10 @@
     <row r="394" ht="15" customHeight="1" spans="1:6">
       <c r="A394" s="1"/>
       <c r="B394" s="1">
-        <v>60079</v>
+        <v>60080</v>
       </c>
       <c r="C394" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D394" s="1">
         <v>7</v>
@@ -10142,10 +10138,10 @@
     <row r="395" ht="15" customHeight="1" spans="1:6">
       <c r="A395" s="1"/>
       <c r="B395" s="1">
-        <v>60080</v>
+        <v>60081</v>
       </c>
       <c r="C395" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D395" s="1">
         <v>7</v>
@@ -10160,10 +10156,10 @@
     <row r="396" ht="15" customHeight="1" spans="1:6">
       <c r="A396" s="1"/>
       <c r="B396" s="1">
-        <v>60081</v>
+        <v>60082</v>
       </c>
       <c r="C396" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D396" s="1">
         <v>7</v>
@@ -10178,10 +10174,10 @@
     <row r="397" ht="15" customHeight="1" spans="1:6">
       <c r="A397" s="1"/>
       <c r="B397" s="1">
-        <v>60082</v>
+        <v>60083</v>
       </c>
       <c r="C397" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D397" s="1">
         <v>7</v>
@@ -10191,24 +10187,6 @@
       </c>
       <c r="F397" s="1" t="s">
         <v>805</v>
-      </c>
-    </row>
-    <row r="398" ht="15" customHeight="1" spans="1:6">
-      <c r="A398" s="1"/>
-      <c r="B398" s="1">
-        <v>60083</v>
-      </c>
-      <c r="C398" s="1" t="s">
-        <v>641</v>
-      </c>
-      <c r="D398" s="1">
-        <v>7</v>
-      </c>
-      <c r="E398" s="1" t="s">
-        <v>806</v>
-      </c>
-      <c r="F398" s="1" t="s">
-        <v>807</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/DataTables/ResourceConfigTable.xlsx
+++ b/AAAGameData/DataTables/ResourceConfigTable.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1011" uniqueCount="806">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1027" uniqueCount="820">
   <si>
     <t>#</t>
   </si>
@@ -1227,6 +1227,48 @@
   </si>
   <si>
     <t>免疫提示-飘字音效</t>
+  </si>
+  <si>
+    <t>UIEffect/CommonRarity</t>
+  </si>
+  <si>
+    <t>物品稀有度特效-普通</t>
+  </si>
+  <si>
+    <t>UIEffect/UncommonRarity</t>
+  </si>
+  <si>
+    <t>物品稀有度特效-优秀</t>
+  </si>
+  <si>
+    <t>UIEffect/RareRarity</t>
+  </si>
+  <si>
+    <t>物品稀有度特效-稀有</t>
+  </si>
+  <si>
+    <t>UIEffect/EpicRarity</t>
+  </si>
+  <si>
+    <t>物品稀有度特效-史诗</t>
+  </si>
+  <si>
+    <t>UIEffect/LegendaryRarity</t>
+  </si>
+  <si>
+    <t>物品稀有度特效-传说</t>
+  </si>
+  <si>
+    <t>护盾特效</t>
+  </si>
+  <si>
+    <t>StateEffect/Shield</t>
+  </si>
+  <si>
+    <t>护盾受击特效</t>
+  </si>
+  <si>
+    <t>StateEffect/ShieldHit</t>
   </si>
   <si>
     <t>EquipmentTable使用|资源暂不存在</t>
@@ -3409,7 +3451,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F397"/>
+  <dimension ref="A1:F404"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -6648,125 +6690,129 @@
     <row r="197" ht="15" customHeight="1" spans="1:6">
       <c r="A197" s="1"/>
       <c r="B197" s="1">
-        <v>6001</v>
-      </c>
-      <c r="C197" s="1" t="s">
+        <v>3101</v>
+      </c>
+      <c r="C197" s="1"/>
+      <c r="D197" s="1">
+        <v>3</v>
+      </c>
+      <c r="E197" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="D197" s="1">
-        <v>6</v>
-      </c>
-      <c r="E197" s="1" t="s">
+      <c r="F197" s="1" t="s">
         <v>401</v>
-      </c>
-      <c r="F197" s="1" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="198" ht="15" customHeight="1" spans="1:6">
       <c r="A198" s="1"/>
       <c r="B198" s="1">
-        <v>10001</v>
+        <v>3102</v>
       </c>
       <c r="C198" s="1"/>
       <c r="D198" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E198" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="F198" s="1" t="s">
         <v>403</v>
-      </c>
-      <c r="F198" s="1" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="199" ht="15" customHeight="1" spans="1:6">
       <c r="A199" s="1"/>
       <c r="B199" s="1">
-        <v>10002</v>
+        <v>3103</v>
       </c>
       <c r="C199" s="1"/>
       <c r="D199" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E199" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="F199" s="1" t="s">
         <v>405</v>
-      </c>
-      <c r="F199" s="1" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="200" ht="15" customHeight="1" spans="1:6">
       <c r="A200" s="1"/>
       <c r="B200" s="1">
-        <v>10003</v>
+        <v>3104</v>
       </c>
       <c r="C200" s="1"/>
       <c r="D200" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E200" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="F200" s="1" t="s">
         <v>407</v>
-      </c>
-      <c r="F200" s="1" t="s">
-        <v>408</v>
       </c>
     </row>
     <row r="201" ht="15" customHeight="1" spans="1:6">
       <c r="A201" s="1"/>
       <c r="B201" s="1">
-        <v>10004</v>
+        <v>3105</v>
       </c>
       <c r="C201" s="1"/>
       <c r="D201" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E201" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="F201" s="1" t="s">
         <v>409</v>
-      </c>
-      <c r="F201" s="1" t="s">
-        <v>410</v>
       </c>
     </row>
     <row r="202" ht="15" customHeight="1" spans="1:6">
       <c r="A202" s="1"/>
       <c r="B202" s="1">
-        <v>10101</v>
-      </c>
-      <c r="C202" s="1"/>
+        <v>3201</v>
+      </c>
+      <c r="C202" s="1" t="s">
+        <v>410</v>
+      </c>
       <c r="D202" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E202" s="1" t="s">
         <v>411</v>
       </c>
       <c r="F202" s="1" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="203" ht="15" customHeight="1" spans="1:6">
       <c r="A203" s="1"/>
       <c r="B203" s="1">
-        <v>10102</v>
-      </c>
-      <c r="C203" s="1"/>
+        <v>3202</v>
+      </c>
+      <c r="C203" s="1" t="s">
+        <v>412</v>
+      </c>
       <c r="D203" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E203" s="1" t="s">
         <v>413</v>
       </c>
       <c r="F203" s="1" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="204" ht="15" customHeight="1" spans="1:6">
       <c r="A204" s="1"/>
       <c r="B204" s="1">
-        <v>10103</v>
-      </c>
-      <c r="C204" s="1"/>
+        <v>6001</v>
+      </c>
+      <c r="C204" s="1" t="s">
+        <v>414</v>
+      </c>
       <c r="D204" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E204" s="1" t="s">
         <v>415</v>
@@ -6778,7 +6824,7 @@
     <row r="205" ht="15" customHeight="1" spans="1:6">
       <c r="A205" s="1"/>
       <c r="B205" s="1">
-        <v>10201</v>
+        <v>10001</v>
       </c>
       <c r="C205" s="1"/>
       <c r="D205" s="1">
@@ -6794,7 +6840,7 @@
     <row r="206" ht="15" customHeight="1" spans="1:6">
       <c r="A206" s="1"/>
       <c r="B206" s="1">
-        <v>10202</v>
+        <v>10002</v>
       </c>
       <c r="C206" s="1"/>
       <c r="D206" s="1">
@@ -6810,7 +6856,7 @@
     <row r="207" ht="15" customHeight="1" spans="1:6">
       <c r="A207" s="1"/>
       <c r="B207" s="1">
-        <v>10203</v>
+        <v>10003</v>
       </c>
       <c r="C207" s="1"/>
       <c r="D207" s="1">
@@ -6826,66 +6872,62 @@
     <row r="208" ht="15" customHeight="1" spans="1:6">
       <c r="A208" s="1"/>
       <c r="B208" s="1">
-        <v>11001</v>
-      </c>
-      <c r="C208" s="1" t="s">
+        <v>10004</v>
+      </c>
+      <c r="C208" s="1"/>
+      <c r="D208" s="1">
+        <v>1</v>
+      </c>
+      <c r="E208" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="D208" s="1">
-        <v>1</v>
-      </c>
-      <c r="E208" s="1" t="s">
+      <c r="F208" s="1" t="s">
         <v>424</v>
-      </c>
-      <c r="F208" s="1" t="s">
-        <v>425</v>
       </c>
     </row>
     <row r="209" ht="15" customHeight="1" spans="1:6">
       <c r="A209" s="1"/>
       <c r="B209" s="1">
-        <v>13001</v>
+        <v>10101</v>
       </c>
       <c r="C209" s="1"/>
       <c r="D209" s="1">
         <v>1</v>
       </c>
       <c r="E209" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="F209" s="1" t="s">
         <v>426</v>
-      </c>
-      <c r="F209" s="1" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="210" ht="15" customHeight="1" spans="1:6">
       <c r="A210" s="1"/>
       <c r="B210" s="1">
-        <v>13004</v>
+        <v>10102</v>
       </c>
       <c r="C210" s="1"/>
       <c r="D210" s="1">
         <v>1</v>
       </c>
       <c r="E210" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="F210" s="1" t="s">
         <v>428</v>
-      </c>
-      <c r="F210" s="1" t="s">
-        <v>429</v>
       </c>
     </row>
     <row r="211" ht="15" customHeight="1" spans="1:6">
       <c r="A211" s="1"/>
       <c r="B211" s="1">
-        <v>13010</v>
-      </c>
-      <c r="C211" s="1" t="s">
-        <v>109</v>
-      </c>
+        <v>10103</v>
+      </c>
+      <c r="C211" s="1"/>
       <c r="D211" s="1">
         <v>1</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>143</v>
+        <v>429</v>
       </c>
       <c r="F211" s="1" t="s">
         <v>430</v>
@@ -6894,136 +6936,132 @@
     <row r="212" ht="15" customHeight="1" spans="1:6">
       <c r="A212" s="1"/>
       <c r="B212" s="1">
-        <v>13011</v>
-      </c>
-      <c r="C212" s="1" t="s">
-        <v>109</v>
-      </c>
+        <v>10201</v>
+      </c>
+      <c r="C212" s="1"/>
       <c r="D212" s="1">
         <v>1</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>145</v>
+        <v>431</v>
       </c>
       <c r="F212" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="213" ht="15" customHeight="1" spans="1:6">
       <c r="A213" s="1"/>
       <c r="B213" s="1">
-        <v>13012</v>
-      </c>
-      <c r="C213" s="1" t="s">
-        <v>109</v>
-      </c>
+        <v>10202</v>
+      </c>
+      <c r="C213" s="1"/>
       <c r="D213" s="1">
         <v>1</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>147</v>
+        <v>433</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="214" ht="15" customHeight="1" spans="1:6">
       <c r="A214" s="1"/>
       <c r="B214" s="1">
-        <v>13013</v>
-      </c>
-      <c r="C214" s="1" t="s">
-        <v>109</v>
-      </c>
+        <v>10203</v>
+      </c>
+      <c r="C214" s="1"/>
       <c r="D214" s="1">
         <v>1</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="F214" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="215" ht="15" customHeight="1" spans="1:6">
       <c r="A215" s="1"/>
       <c r="B215" s="1">
-        <v>13999</v>
+        <v>11001</v>
       </c>
       <c r="C215" s="1" t="s">
-        <v>109</v>
+        <v>437</v>
       </c>
       <c r="D215" s="1">
         <v>1</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="F215" s="1" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="216" ht="15" customHeight="1" spans="1:6">
       <c r="A216" s="1"/>
       <c r="B216" s="1">
-        <v>15001</v>
+        <v>13001</v>
       </c>
       <c r="C216" s="1"/>
       <c r="D216" s="1">
         <v>1</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="F216" s="1" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="217" ht="15" customHeight="1" spans="1:6">
       <c r="A217" s="1"/>
       <c r="B217" s="1">
-        <v>15002</v>
-      </c>
-      <c r="C217" s="1" t="s">
-        <v>439</v>
-      </c>
+        <v>13004</v>
+      </c>
+      <c r="C217" s="1"/>
       <c r="D217" s="1">
         <v>1</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="F217" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="218" ht="15" customHeight="1" spans="1:6">
       <c r="A218" s="1"/>
       <c r="B218" s="1">
-        <v>15003</v>
-      </c>
-      <c r="C218" s="1"/>
+        <v>13010</v>
+      </c>
+      <c r="C218" s="1" t="s">
+        <v>109</v>
+      </c>
       <c r="D218" s="1">
         <v>1</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>442</v>
+        <v>143</v>
       </c>
       <c r="F218" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="219" ht="15" customHeight="1" spans="1:6">
       <c r="A219" s="1"/>
       <c r="B219" s="1">
-        <v>15005</v>
-      </c>
-      <c r="C219" s="1"/>
+        <v>13011</v>
+      </c>
+      <c r="C219" s="1" t="s">
+        <v>109</v>
+      </c>
       <c r="D219" s="1">
         <v>1</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>444</v>
+        <v>145</v>
       </c>
       <c r="F219" s="1" t="s">
         <v>445</v>
@@ -7032,73 +7070,81 @@
     <row r="220" ht="15" customHeight="1" spans="1:6">
       <c r="A220" s="1"/>
       <c r="B220" s="1">
-        <v>15007</v>
-      </c>
-      <c r="C220" s="1"/>
+        <v>13012</v>
+      </c>
+      <c r="C220" s="1" t="s">
+        <v>109</v>
+      </c>
       <c r="D220" s="1">
         <v>1</v>
       </c>
       <c r="E220" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="F220" s="1" t="s">
         <v>446</v>
-      </c>
-      <c r="F220" s="1" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="221" ht="15" customHeight="1" spans="1:6">
       <c r="A221" s="1"/>
       <c r="B221" s="1">
-        <v>15008</v>
-      </c>
-      <c r="C221" s="1"/>
+        <v>13013</v>
+      </c>
+      <c r="C221" s="1" t="s">
+        <v>109</v>
+      </c>
       <c r="D221" s="1">
         <v>1</v>
       </c>
       <c r="E221" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="F221" s="1" t="s">
         <v>448</v>
-      </c>
-      <c r="F221" s="1" t="s">
-        <v>449</v>
       </c>
     </row>
     <row r="222" ht="15" customHeight="1" spans="1:6">
       <c r="A222" s="1"/>
       <c r="B222" s="1">
-        <v>15009</v>
-      </c>
-      <c r="C222" s="1"/>
+        <v>13999</v>
+      </c>
+      <c r="C222" s="1" t="s">
+        <v>109</v>
+      </c>
       <c r="D222" s="1">
         <v>1</v>
       </c>
       <c r="E222" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="F222" s="1" t="s">
         <v>450</v>
-      </c>
-      <c r="F222" s="1" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="223" ht="15" customHeight="1" spans="1:6">
       <c r="A223" s="1"/>
       <c r="B223" s="1">
-        <v>15011</v>
+        <v>15001</v>
       </c>
       <c r="C223" s="1"/>
       <c r="D223" s="1">
         <v>1</v>
       </c>
       <c r="E223" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="F223" s="1" t="s">
         <v>452</v>
-      </c>
-      <c r="F223" s="1" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="224" ht="15" customHeight="1" spans="1:6">
       <c r="A224" s="1"/>
       <c r="B224" s="1">
-        <v>15012</v>
-      </c>
-      <c r="C224" s="1"/>
+        <v>15002</v>
+      </c>
+      <c r="C224" s="1" t="s">
+        <v>453</v>
+      </c>
       <c r="D224" s="1">
         <v>1</v>
       </c>
@@ -7112,7 +7158,7 @@
     <row r="225" ht="15" customHeight="1" spans="1:6">
       <c r="A225" s="1"/>
       <c r="B225" s="1">
-        <v>15013</v>
+        <v>15003</v>
       </c>
       <c r="C225" s="1"/>
       <c r="D225" s="1">
@@ -7128,7 +7174,7 @@
     <row r="226" ht="15" customHeight="1" spans="1:6">
       <c r="A226" s="1"/>
       <c r="B226" s="1">
-        <v>15014</v>
+        <v>15005</v>
       </c>
       <c r="C226" s="1"/>
       <c r="D226" s="1">
@@ -7144,7 +7190,7 @@
     <row r="227" ht="15" customHeight="1" spans="1:6">
       <c r="A227" s="1"/>
       <c r="B227" s="1">
-        <v>15015</v>
+        <v>15007</v>
       </c>
       <c r="C227" s="1"/>
       <c r="D227" s="1">
@@ -7160,7 +7206,7 @@
     <row r="228" ht="15" customHeight="1" spans="1:6">
       <c r="A228" s="1"/>
       <c r="B228" s="1">
-        <v>15017</v>
+        <v>15008</v>
       </c>
       <c r="C228" s="1"/>
       <c r="D228" s="1">
@@ -7176,7 +7222,7 @@
     <row r="229" ht="15" customHeight="1" spans="1:6">
       <c r="A229" s="1"/>
       <c r="B229" s="1">
-        <v>15018</v>
+        <v>15009</v>
       </c>
       <c r="C229" s="1"/>
       <c r="D229" s="1">
@@ -7192,7 +7238,7 @@
     <row r="230" ht="15" customHeight="1" spans="1:6">
       <c r="A230" s="1"/>
       <c r="B230" s="1">
-        <v>15019</v>
+        <v>15011</v>
       </c>
       <c r="C230" s="1"/>
       <c r="D230" s="1">
@@ -7208,7 +7254,7 @@
     <row r="231" ht="15" customHeight="1" spans="1:6">
       <c r="A231" s="1"/>
       <c r="B231" s="1">
-        <v>15020</v>
+        <v>15012</v>
       </c>
       <c r="C231" s="1"/>
       <c r="D231" s="1">
@@ -7224,7 +7270,7 @@
     <row r="232" ht="15" customHeight="1" spans="1:6">
       <c r="A232" s="1"/>
       <c r="B232" s="1">
-        <v>15021</v>
+        <v>15013</v>
       </c>
       <c r="C232" s="1"/>
       <c r="D232" s="1">
@@ -7240,151 +7286,141 @@
     <row r="233" ht="15" customHeight="1" spans="1:6">
       <c r="A233" s="1"/>
       <c r="B233" s="1">
-        <v>15022</v>
-      </c>
-      <c r="C233" s="1" t="s">
+        <v>15014</v>
+      </c>
+      <c r="C233" s="1"/>
+      <c r="D233" s="1">
+        <v>1</v>
+      </c>
+      <c r="E233" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="D233" s="1">
-        <v>1</v>
-      </c>
-      <c r="E233" s="1" t="s">
+      <c r="F233" s="1" t="s">
         <v>473</v>
-      </c>
-      <c r="F233" s="1" t="s">
-        <v>474</v>
       </c>
     </row>
     <row r="234" ht="15" customHeight="1" spans="1:6">
       <c r="A234" s="1"/>
       <c r="B234" s="1">
-        <v>16001</v>
-      </c>
-      <c r="C234" s="1" t="s">
+        <v>15015</v>
+      </c>
+      <c r="C234" s="1"/>
+      <c r="D234" s="1">
+        <v>1</v>
+      </c>
+      <c r="E234" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="F234" s="1" t="s">
         <v>475</v>
-      </c>
-      <c r="D234" s="1">
-        <v>1</v>
-      </c>
-      <c r="E234" s="1" t="s">
-        <v>476</v>
-      </c>
-      <c r="F234" s="1" t="s">
-        <v>477</v>
       </c>
     </row>
     <row r="235" ht="15" customHeight="1" spans="1:6">
       <c r="A235" s="1"/>
       <c r="B235" s="1">
-        <v>16002</v>
-      </c>
-      <c r="C235" s="1" t="s">
-        <v>475</v>
-      </c>
+        <v>15017</v>
+      </c>
+      <c r="C235" s="1"/>
       <c r="D235" s="1">
         <v>1</v>
       </c>
       <c r="E235" s="1" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="F235" s="1" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
     </row>
     <row r="236" ht="15" customHeight="1" spans="1:6">
       <c r="A236" s="1"/>
       <c r="B236" s="1">
-        <v>16003</v>
-      </c>
-      <c r="C236" s="1" t="s">
-        <v>475</v>
-      </c>
+        <v>15018</v>
+      </c>
+      <c r="C236" s="1"/>
       <c r="D236" s="1">
         <v>1</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="F236" s="1" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="237" ht="15" customHeight="1" spans="1:6">
       <c r="A237" s="1"/>
       <c r="B237" s="1">
-        <v>16004</v>
-      </c>
-      <c r="C237" s="1" t="s">
-        <v>475</v>
-      </c>
+        <v>15019</v>
+      </c>
+      <c r="C237" s="1"/>
       <c r="D237" s="1">
         <v>1</v>
       </c>
       <c r="E237" s="1" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="F237" s="1" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
     </row>
     <row r="238" ht="15" customHeight="1" spans="1:6">
       <c r="A238" s="1"/>
       <c r="B238" s="1">
-        <v>16005</v>
-      </c>
-      <c r="C238" s="1" t="s">
-        <v>475</v>
-      </c>
+        <v>15020</v>
+      </c>
+      <c r="C238" s="1"/>
       <c r="D238" s="1">
         <v>1</v>
       </c>
       <c r="E238" s="1" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="F238" s="1" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="239" ht="15" customHeight="1" spans="1:6">
       <c r="A239" s="1"/>
       <c r="B239" s="1">
-        <v>16006</v>
-      </c>
-      <c r="C239" s="1" t="s">
-        <v>475</v>
-      </c>
+        <v>15021</v>
+      </c>
+      <c r="C239" s="1"/>
       <c r="D239" s="1">
         <v>1</v>
       </c>
       <c r="E239" s="1" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="F239" s="1" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="240" ht="15" customHeight="1" spans="1:6">
       <c r="A240" s="1"/>
       <c r="B240" s="1">
-        <v>19002</v>
-      </c>
-      <c r="C240" s="1"/>
+        <v>15022</v>
+      </c>
+      <c r="C240" s="1" t="s">
+        <v>486</v>
+      </c>
       <c r="D240" s="1">
         <v>1</v>
       </c>
       <c r="E240" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="F240" s="1" t="s">
         <v>488</v>
-      </c>
-      <c r="F240" s="1" t="s">
-        <v>489</v>
       </c>
     </row>
     <row r="241" ht="15" customHeight="1" spans="1:6">
       <c r="A241" s="1"/>
       <c r="B241" s="1">
-        <v>19003</v>
-      </c>
-      <c r="C241" s="1"/>
+        <v>16001</v>
+      </c>
+      <c r="C241" s="1" t="s">
+        <v>489</v>
+      </c>
       <c r="D241" s="1">
         <v>1</v>
       </c>
@@ -7398,9 +7434,11 @@
     <row r="242" ht="15" customHeight="1" spans="1:6">
       <c r="A242" s="1"/>
       <c r="B242" s="1">
-        <v>19004</v>
-      </c>
-      <c r="C242" s="1"/>
+        <v>16002</v>
+      </c>
+      <c r="C242" s="1" t="s">
+        <v>489</v>
+      </c>
       <c r="D242" s="1">
         <v>1</v>
       </c>
@@ -7414,9 +7452,11 @@
     <row r="243" ht="15" customHeight="1" spans="1:6">
       <c r="A243" s="1"/>
       <c r="B243" s="1">
-        <v>19012</v>
-      </c>
-      <c r="C243" s="1"/>
+        <v>16003</v>
+      </c>
+      <c r="C243" s="1" t="s">
+        <v>489</v>
+      </c>
       <c r="D243" s="1">
         <v>1</v>
       </c>
@@ -7430,9 +7470,11 @@
     <row r="244" ht="15" customHeight="1" spans="1:6">
       <c r="A244" s="1"/>
       <c r="B244" s="1">
-        <v>19013</v>
-      </c>
-      <c r="C244" s="1"/>
+        <v>16004</v>
+      </c>
+      <c r="C244" s="1" t="s">
+        <v>489</v>
+      </c>
       <c r="D244" s="1">
         <v>1</v>
       </c>
@@ -7446,9 +7488,11 @@
     <row r="245" ht="15" customHeight="1" spans="1:6">
       <c r="A245" s="1"/>
       <c r="B245" s="1">
-        <v>19014</v>
-      </c>
-      <c r="C245" s="1"/>
+        <v>16005</v>
+      </c>
+      <c r="C245" s="1" t="s">
+        <v>489</v>
+      </c>
       <c r="D245" s="1">
         <v>1</v>
       </c>
@@ -7462,9 +7506,11 @@
     <row r="246" ht="15" customHeight="1" spans="1:6">
       <c r="A246" s="1"/>
       <c r="B246" s="1">
-        <v>19022</v>
-      </c>
-      <c r="C246" s="1"/>
+        <v>16006</v>
+      </c>
+      <c r="C246" s="1" t="s">
+        <v>489</v>
+      </c>
       <c r="D246" s="1">
         <v>1</v>
       </c>
@@ -7478,7 +7524,7 @@
     <row r="247" ht="15" customHeight="1" spans="1:6">
       <c r="A247" s="1"/>
       <c r="B247" s="1">
-        <v>19023</v>
+        <v>19002</v>
       </c>
       <c r="C247" s="1"/>
       <c r="D247" s="1">
@@ -7494,7 +7540,7 @@
     <row r="248" ht="15" customHeight="1" spans="1:6">
       <c r="A248" s="1"/>
       <c r="B248" s="1">
-        <v>19024</v>
+        <v>19003</v>
       </c>
       <c r="C248" s="1"/>
       <c r="D248" s="1">
@@ -7510,136 +7556,122 @@
     <row r="249" ht="15" customHeight="1" spans="1:6">
       <c r="A249" s="1"/>
       <c r="B249" s="1">
-        <v>20101</v>
-      </c>
-      <c r="C249" s="1" t="s">
+        <v>19004</v>
+      </c>
+      <c r="C249" s="1"/>
+      <c r="D249" s="1">
+        <v>1</v>
+      </c>
+      <c r="E249" s="1" t="s">
         <v>506</v>
       </c>
-      <c r="D249" s="1">
-        <v>2</v>
-      </c>
-      <c r="E249" s="1" t="s">
+      <c r="F249" s="1" t="s">
         <v>507</v>
-      </c>
-      <c r="F249" s="1" t="s">
-        <v>508</v>
       </c>
     </row>
     <row r="250" ht="15" customHeight="1" spans="1:6">
       <c r="A250" s="1"/>
       <c r="B250" s="1">
-        <v>20102</v>
-      </c>
-      <c r="C250" s="1" t="s">
-        <v>506</v>
-      </c>
+        <v>19012</v>
+      </c>
+      <c r="C250" s="1"/>
       <c r="D250" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E250" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="F250" s="1" t="s">
         <v>509</v>
-      </c>
-      <c r="F250" s="1" t="s">
-        <v>510</v>
       </c>
     </row>
     <row r="251" ht="15" customHeight="1" spans="1:6">
       <c r="A251" s="1"/>
       <c r="B251" s="1">
-        <v>20103</v>
-      </c>
-      <c r="C251" s="1" t="s">
-        <v>506</v>
-      </c>
+        <v>19013</v>
+      </c>
+      <c r="C251" s="1"/>
       <c r="D251" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E251" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="F251" s="1" t="s">
         <v>511</v>
-      </c>
-      <c r="F251" s="1" t="s">
-        <v>512</v>
       </c>
     </row>
     <row r="252" ht="15" customHeight="1" spans="1:6">
       <c r="A252" s="1"/>
       <c r="B252" s="1">
-        <v>20104</v>
-      </c>
-      <c r="C252" s="1" t="s">
-        <v>506</v>
-      </c>
+        <v>19014</v>
+      </c>
+      <c r="C252" s="1"/>
       <c r="D252" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E252" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="F252" s="1" t="s">
         <v>513</v>
-      </c>
-      <c r="F252" s="1" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="253" ht="15" customHeight="1" spans="1:6">
       <c r="A253" s="1"/>
       <c r="B253" s="1">
-        <v>20105</v>
-      </c>
-      <c r="C253" s="1" t="s">
-        <v>506</v>
-      </c>
+        <v>19022</v>
+      </c>
+      <c r="C253" s="1"/>
       <c r="D253" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E253" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="F253" s="1" t="s">
         <v>515</v>
-      </c>
-      <c r="F253" s="1" t="s">
-        <v>516</v>
       </c>
     </row>
     <row r="254" ht="15" customHeight="1" spans="1:6">
       <c r="A254" s="1"/>
       <c r="B254" s="1">
-        <v>20106</v>
-      </c>
-      <c r="C254" s="1" t="s">
-        <v>506</v>
-      </c>
+        <v>19023</v>
+      </c>
+      <c r="C254" s="1"/>
       <c r="D254" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E254" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="F254" s="1" t="s">
         <v>517</v>
-      </c>
-      <c r="F254" s="1" t="s">
-        <v>518</v>
       </c>
     </row>
     <row r="255" ht="15" customHeight="1" spans="1:6">
       <c r="A255" s="1"/>
       <c r="B255" s="1">
-        <v>20107</v>
-      </c>
-      <c r="C255" s="1" t="s">
-        <v>506</v>
-      </c>
+        <v>19024</v>
+      </c>
+      <c r="C255" s="1"/>
       <c r="D255" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E255" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="F255" s="1" t="s">
         <v>519</v>
-      </c>
-      <c r="F255" s="1" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="256" ht="15" customHeight="1" spans="1:6">
       <c r="A256" s="1"/>
       <c r="B256" s="1">
-        <v>20108</v>
+        <v>20101</v>
       </c>
       <c r="C256" s="1" t="s">
-        <v>506</v>
+        <v>520</v>
       </c>
       <c r="D256" s="1">
         <v>2</v>
@@ -7654,10 +7686,10 @@
     <row r="257" ht="15" customHeight="1" spans="1:6">
       <c r="A257" s="1"/>
       <c r="B257" s="1">
-        <v>20109</v>
+        <v>20102</v>
       </c>
       <c r="C257" s="1" t="s">
-        <v>506</v>
+        <v>520</v>
       </c>
       <c r="D257" s="1">
         <v>2</v>
@@ -7672,10 +7704,10 @@
     <row r="258" ht="15" customHeight="1" spans="1:6">
       <c r="A258" s="1"/>
       <c r="B258" s="1">
-        <v>20110</v>
+        <v>20103</v>
       </c>
       <c r="C258" s="1" t="s">
-        <v>506</v>
+        <v>520</v>
       </c>
       <c r="D258" s="1">
         <v>2</v>
@@ -7690,10 +7722,10 @@
     <row r="259" ht="15" customHeight="1" spans="1:6">
       <c r="A259" s="1"/>
       <c r="B259" s="1">
-        <v>20111</v>
+        <v>20104</v>
       </c>
       <c r="C259" s="1" t="s">
-        <v>506</v>
+        <v>520</v>
       </c>
       <c r="D259" s="1">
         <v>2</v>
@@ -7708,10 +7740,10 @@
     <row r="260" ht="15" customHeight="1" spans="1:6">
       <c r="A260" s="1"/>
       <c r="B260" s="1">
-        <v>20112</v>
+        <v>20105</v>
       </c>
       <c r="C260" s="1" t="s">
-        <v>506</v>
+        <v>520</v>
       </c>
       <c r="D260" s="1">
         <v>2</v>
@@ -7726,10 +7758,10 @@
     <row r="261" ht="15" customHeight="1" spans="1:6">
       <c r="A261" s="1"/>
       <c r="B261" s="1">
-        <v>20113</v>
+        <v>20106</v>
       </c>
       <c r="C261" s="1" t="s">
-        <v>506</v>
+        <v>520</v>
       </c>
       <c r="D261" s="1">
         <v>2</v>
@@ -7744,10 +7776,10 @@
     <row r="262" ht="15" customHeight="1" spans="1:6">
       <c r="A262" s="1"/>
       <c r="B262" s="1">
-        <v>20114</v>
+        <v>20107</v>
       </c>
       <c r="C262" s="1" t="s">
-        <v>506</v>
+        <v>520</v>
       </c>
       <c r="D262" s="1">
         <v>2</v>
@@ -7762,10 +7794,10 @@
     <row r="263" ht="15" customHeight="1" spans="1:6">
       <c r="A263" s="1"/>
       <c r="B263" s="1">
-        <v>20115</v>
+        <v>20108</v>
       </c>
       <c r="C263" s="1" t="s">
-        <v>506</v>
+        <v>520</v>
       </c>
       <c r="D263" s="1">
         <v>2</v>
@@ -7780,10 +7812,10 @@
     <row r="264" ht="15" customHeight="1" spans="1:6">
       <c r="A264" s="1"/>
       <c r="B264" s="1">
-        <v>20116</v>
+        <v>20109</v>
       </c>
       <c r="C264" s="1" t="s">
-        <v>506</v>
+        <v>520</v>
       </c>
       <c r="D264" s="1">
         <v>2</v>
@@ -7798,10 +7830,10 @@
     <row r="265" ht="15" customHeight="1" spans="1:6">
       <c r="A265" s="1"/>
       <c r="B265" s="1">
-        <v>20117</v>
+        <v>20110</v>
       </c>
       <c r="C265" s="1" t="s">
-        <v>506</v>
+        <v>520</v>
       </c>
       <c r="D265" s="1">
         <v>2</v>
@@ -7816,10 +7848,10 @@
     <row r="266" ht="15" customHeight="1" spans="1:6">
       <c r="A266" s="1"/>
       <c r="B266" s="1">
-        <v>20118</v>
+        <v>20111</v>
       </c>
       <c r="C266" s="1" t="s">
-        <v>506</v>
+        <v>520</v>
       </c>
       <c r="D266" s="1">
         <v>2</v>
@@ -7834,10 +7866,10 @@
     <row r="267" ht="15" customHeight="1" spans="1:6">
       <c r="A267" s="1"/>
       <c r="B267" s="1">
-        <v>20119</v>
+        <v>20112</v>
       </c>
       <c r="C267" s="1" t="s">
-        <v>506</v>
+        <v>520</v>
       </c>
       <c r="D267" s="1">
         <v>2</v>
@@ -7852,10 +7884,10 @@
     <row r="268" ht="15" customHeight="1" spans="1:6">
       <c r="A268" s="1"/>
       <c r="B268" s="1">
-        <v>20120</v>
+        <v>20113</v>
       </c>
       <c r="C268" s="1" t="s">
-        <v>506</v>
+        <v>520</v>
       </c>
       <c r="D268" s="1">
         <v>2</v>
@@ -7870,10 +7902,10 @@
     <row r="269" ht="15" customHeight="1" spans="1:6">
       <c r="A269" s="1"/>
       <c r="B269" s="1">
-        <v>20121</v>
+        <v>20114</v>
       </c>
       <c r="C269" s="1" t="s">
-        <v>506</v>
+        <v>520</v>
       </c>
       <c r="D269" s="1">
         <v>2</v>
@@ -7888,10 +7920,10 @@
     <row r="270" ht="15" customHeight="1" spans="1:6">
       <c r="A270" s="1"/>
       <c r="B270" s="1">
-        <v>20122</v>
+        <v>20115</v>
       </c>
       <c r="C270" s="1" t="s">
-        <v>506</v>
+        <v>520</v>
       </c>
       <c r="D270" s="1">
         <v>2</v>
@@ -7906,10 +7938,10 @@
     <row r="271" ht="15" customHeight="1" spans="1:6">
       <c r="A271" s="1"/>
       <c r="B271" s="1">
-        <v>20123</v>
+        <v>20116</v>
       </c>
       <c r="C271" s="1" t="s">
-        <v>506</v>
+        <v>520</v>
       </c>
       <c r="D271" s="1">
         <v>2</v>
@@ -7924,10 +7956,10 @@
     <row r="272" ht="15" customHeight="1" spans="1:6">
       <c r="A272" s="1"/>
       <c r="B272" s="1">
-        <v>20124</v>
+        <v>20117</v>
       </c>
       <c r="C272" s="1" t="s">
-        <v>506</v>
+        <v>520</v>
       </c>
       <c r="D272" s="1">
         <v>2</v>
@@ -7942,10 +7974,10 @@
     <row r="273" ht="15" customHeight="1" spans="1:6">
       <c r="A273" s="1"/>
       <c r="B273" s="1">
-        <v>20125</v>
+        <v>20118</v>
       </c>
       <c r="C273" s="1" t="s">
-        <v>506</v>
+        <v>520</v>
       </c>
       <c r="D273" s="1">
         <v>2</v>
@@ -7960,10 +7992,10 @@
     <row r="274" ht="15" customHeight="1" spans="1:6">
       <c r="A274" s="1"/>
       <c r="B274" s="1">
-        <v>20126</v>
+        <v>20119</v>
       </c>
       <c r="C274" s="1" t="s">
-        <v>506</v>
+        <v>520</v>
       </c>
       <c r="D274" s="1">
         <v>2</v>
@@ -7978,10 +8010,10 @@
     <row r="275" ht="15" customHeight="1" spans="1:6">
       <c r="A275" s="1"/>
       <c r="B275" s="1">
-        <v>20127</v>
+        <v>20120</v>
       </c>
       <c r="C275" s="1" t="s">
-        <v>506</v>
+        <v>520</v>
       </c>
       <c r="D275" s="1">
         <v>2</v>
@@ -7996,13 +8028,13 @@
     <row r="276" ht="15" customHeight="1" spans="1:6">
       <c r="A276" s="1"/>
       <c r="B276" s="1">
-        <v>30101</v>
+        <v>20121</v>
       </c>
       <c r="C276" s="1" t="s">
-        <v>506</v>
+        <v>520</v>
       </c>
       <c r="D276" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E276" s="1" t="s">
         <v>561</v>
@@ -8014,13 +8046,13 @@
     <row r="277" ht="15" customHeight="1" spans="1:6">
       <c r="A277" s="1"/>
       <c r="B277" s="1">
-        <v>30102</v>
+        <v>20122</v>
       </c>
       <c r="C277" s="1" t="s">
-        <v>506</v>
+        <v>520</v>
       </c>
       <c r="D277" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E277" s="1" t="s">
         <v>563</v>
@@ -8032,13 +8064,13 @@
     <row r="278" ht="15" customHeight="1" spans="1:6">
       <c r="A278" s="1"/>
       <c r="B278" s="1">
-        <v>30103</v>
+        <v>20123</v>
       </c>
       <c r="C278" s="1" t="s">
-        <v>506</v>
+        <v>520</v>
       </c>
       <c r="D278" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E278" s="1" t="s">
         <v>565</v>
@@ -8050,13 +8082,13 @@
     <row r="279" ht="15" customHeight="1" spans="1:6">
       <c r="A279" s="1"/>
       <c r="B279" s="1">
-        <v>30104</v>
+        <v>20124</v>
       </c>
       <c r="C279" s="1" t="s">
-        <v>506</v>
+        <v>520</v>
       </c>
       <c r="D279" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E279" s="1" t="s">
         <v>567</v>
@@ -8068,13 +8100,13 @@
     <row r="280" ht="15" customHeight="1" spans="1:6">
       <c r="A280" s="1"/>
       <c r="B280" s="1">
-        <v>30105</v>
+        <v>20125</v>
       </c>
       <c r="C280" s="1" t="s">
-        <v>506</v>
+        <v>520</v>
       </c>
       <c r="D280" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E280" s="1" t="s">
         <v>569</v>
@@ -8086,13 +8118,13 @@
     <row r="281" ht="15" customHeight="1" spans="1:6">
       <c r="A281" s="1"/>
       <c r="B281" s="1">
-        <v>30106</v>
+        <v>20126</v>
       </c>
       <c r="C281" s="1" t="s">
-        <v>506</v>
+        <v>520</v>
       </c>
       <c r="D281" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E281" s="1" t="s">
         <v>571</v>
@@ -8104,13 +8136,13 @@
     <row r="282" ht="15" customHeight="1" spans="1:6">
       <c r="A282" s="1"/>
       <c r="B282" s="1">
-        <v>30107</v>
+        <v>20127</v>
       </c>
       <c r="C282" s="1" t="s">
-        <v>506</v>
+        <v>520</v>
       </c>
       <c r="D282" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E282" s="1" t="s">
         <v>573</v>
@@ -8122,10 +8154,10 @@
     <row r="283" ht="15" customHeight="1" spans="1:6">
       <c r="A283" s="1"/>
       <c r="B283" s="1">
-        <v>30108</v>
+        <v>30101</v>
       </c>
       <c r="C283" s="1" t="s">
-        <v>506</v>
+        <v>520</v>
       </c>
       <c r="D283" s="1">
         <v>3</v>
@@ -8140,10 +8172,10 @@
     <row r="284" ht="15" customHeight="1" spans="1:6">
       <c r="A284" s="1"/>
       <c r="B284" s="1">
-        <v>30109</v>
+        <v>30102</v>
       </c>
       <c r="C284" s="1" t="s">
-        <v>506</v>
+        <v>520</v>
       </c>
       <c r="D284" s="1">
         <v>3</v>
@@ -8158,10 +8190,10 @@
     <row r="285" ht="15" customHeight="1" spans="1:6">
       <c r="A285" s="1"/>
       <c r="B285" s="1">
-        <v>30110</v>
+        <v>30103</v>
       </c>
       <c r="C285" s="1" t="s">
-        <v>506</v>
+        <v>520</v>
       </c>
       <c r="D285" s="1">
         <v>3</v>
@@ -8176,10 +8208,10 @@
     <row r="286" ht="15" customHeight="1" spans="1:6">
       <c r="A286" s="1"/>
       <c r="B286" s="1">
-        <v>30111</v>
+        <v>30104</v>
       </c>
       <c r="C286" s="1" t="s">
-        <v>506</v>
+        <v>520</v>
       </c>
       <c r="D286" s="1">
         <v>3</v>
@@ -8194,10 +8226,10 @@
     <row r="287" ht="15" customHeight="1" spans="1:6">
       <c r="A287" s="1"/>
       <c r="B287" s="1">
-        <v>30112</v>
+        <v>30105</v>
       </c>
       <c r="C287" s="1" t="s">
-        <v>506</v>
+        <v>520</v>
       </c>
       <c r="D287" s="1">
         <v>3</v>
@@ -8212,10 +8244,10 @@
     <row r="288" ht="15" customHeight="1" spans="1:6">
       <c r="A288" s="1"/>
       <c r="B288" s="1">
-        <v>30113</v>
+        <v>30106</v>
       </c>
       <c r="C288" s="1" t="s">
-        <v>506</v>
+        <v>520</v>
       </c>
       <c r="D288" s="1">
         <v>3</v>
@@ -8230,10 +8262,10 @@
     <row r="289" ht="15" customHeight="1" spans="1:6">
       <c r="A289" s="1"/>
       <c r="B289" s="1">
-        <v>30114</v>
+        <v>30107</v>
       </c>
       <c r="C289" s="1" t="s">
-        <v>506</v>
+        <v>520</v>
       </c>
       <c r="D289" s="1">
         <v>3</v>
@@ -8248,10 +8280,10 @@
     <row r="290" ht="15" customHeight="1" spans="1:6">
       <c r="A290" s="1"/>
       <c r="B290" s="1">
-        <v>30115</v>
+        <v>30108</v>
       </c>
       <c r="C290" s="1" t="s">
-        <v>506</v>
+        <v>520</v>
       </c>
       <c r="D290" s="1">
         <v>3</v>
@@ -8266,10 +8298,10 @@
     <row r="291" ht="15" customHeight="1" spans="1:6">
       <c r="A291" s="1"/>
       <c r="B291" s="1">
-        <v>30116</v>
+        <v>30109</v>
       </c>
       <c r="C291" s="1" t="s">
-        <v>506</v>
+        <v>520</v>
       </c>
       <c r="D291" s="1">
         <v>3</v>
@@ -8284,10 +8316,10 @@
     <row r="292" ht="15" customHeight="1" spans="1:6">
       <c r="A292" s="1"/>
       <c r="B292" s="1">
-        <v>30117</v>
+        <v>30110</v>
       </c>
       <c r="C292" s="1" t="s">
-        <v>506</v>
+        <v>520</v>
       </c>
       <c r="D292" s="1">
         <v>3</v>
@@ -8302,10 +8334,10 @@
     <row r="293" ht="15" customHeight="1" spans="1:6">
       <c r="A293" s="1"/>
       <c r="B293" s="1">
-        <v>30118</v>
+        <v>30111</v>
       </c>
       <c r="C293" s="1" t="s">
-        <v>506</v>
+        <v>520</v>
       </c>
       <c r="D293" s="1">
         <v>3</v>
@@ -8320,10 +8352,10 @@
     <row r="294" ht="15" customHeight="1" spans="1:6">
       <c r="A294" s="1"/>
       <c r="B294" s="1">
-        <v>30119</v>
+        <v>30112</v>
       </c>
       <c r="C294" s="1" t="s">
-        <v>506</v>
+        <v>520</v>
       </c>
       <c r="D294" s="1">
         <v>3</v>
@@ -8338,10 +8370,10 @@
     <row r="295" ht="15" customHeight="1" spans="1:6">
       <c r="A295" s="1"/>
       <c r="B295" s="1">
-        <v>30120</v>
+        <v>30113</v>
       </c>
       <c r="C295" s="1" t="s">
-        <v>506</v>
+        <v>520</v>
       </c>
       <c r="D295" s="1">
         <v>3</v>
@@ -8356,10 +8388,10 @@
     <row r="296" ht="15" customHeight="1" spans="1:6">
       <c r="A296" s="1"/>
       <c r="B296" s="1">
-        <v>30121</v>
+        <v>30114</v>
       </c>
       <c r="C296" s="1" t="s">
-        <v>506</v>
+        <v>520</v>
       </c>
       <c r="D296" s="1">
         <v>3</v>
@@ -8374,10 +8406,10 @@
     <row r="297" ht="15" customHeight="1" spans="1:6">
       <c r="A297" s="1"/>
       <c r="B297" s="1">
-        <v>30122</v>
+        <v>30115</v>
       </c>
       <c r="C297" s="1" t="s">
-        <v>506</v>
+        <v>520</v>
       </c>
       <c r="D297" s="1">
         <v>3</v>
@@ -8392,10 +8424,10 @@
     <row r="298" ht="15" customHeight="1" spans="1:6">
       <c r="A298" s="1"/>
       <c r="B298" s="1">
-        <v>30123</v>
+        <v>30116</v>
       </c>
       <c r="C298" s="1" t="s">
-        <v>506</v>
+        <v>520</v>
       </c>
       <c r="D298" s="1">
         <v>3</v>
@@ -8410,10 +8442,10 @@
     <row r="299" ht="15" customHeight="1" spans="1:6">
       <c r="A299" s="1"/>
       <c r="B299" s="1">
-        <v>30124</v>
+        <v>30117</v>
       </c>
       <c r="C299" s="1" t="s">
-        <v>506</v>
+        <v>520</v>
       </c>
       <c r="D299" s="1">
         <v>3</v>
@@ -8428,10 +8460,10 @@
     <row r="300" ht="15" customHeight="1" spans="1:6">
       <c r="A300" s="1"/>
       <c r="B300" s="1">
-        <v>30125</v>
+        <v>30118</v>
       </c>
       <c r="C300" s="1" t="s">
-        <v>506</v>
+        <v>520</v>
       </c>
       <c r="D300" s="1">
         <v>3</v>
@@ -8446,10 +8478,10 @@
     <row r="301" ht="15" customHeight="1" spans="1:6">
       <c r="A301" s="1"/>
       <c r="B301" s="1">
-        <v>30201</v>
+        <v>30119</v>
       </c>
       <c r="C301" s="1" t="s">
-        <v>506</v>
+        <v>520</v>
       </c>
       <c r="D301" s="1">
         <v>3</v>
@@ -8464,10 +8496,10 @@
     <row r="302" ht="15" customHeight="1" spans="1:6">
       <c r="A302" s="1"/>
       <c r="B302" s="1">
-        <v>30202</v>
+        <v>30120</v>
       </c>
       <c r="C302" s="1" t="s">
-        <v>506</v>
+        <v>520</v>
       </c>
       <c r="D302" s="1">
         <v>3</v>
@@ -8482,10 +8514,10 @@
     <row r="303" ht="15" customHeight="1" spans="1:6">
       <c r="A303" s="1"/>
       <c r="B303" s="1">
-        <v>30203</v>
+        <v>30121</v>
       </c>
       <c r="C303" s="1" t="s">
-        <v>506</v>
+        <v>520</v>
       </c>
       <c r="D303" s="1">
         <v>3</v>
@@ -8500,10 +8532,10 @@
     <row r="304" ht="15" customHeight="1" spans="1:6">
       <c r="A304" s="1"/>
       <c r="B304" s="1">
-        <v>30204</v>
+        <v>30122</v>
       </c>
       <c r="C304" s="1" t="s">
-        <v>506</v>
+        <v>520</v>
       </c>
       <c r="D304" s="1">
         <v>3</v>
@@ -8518,10 +8550,10 @@
     <row r="305" ht="15" customHeight="1" spans="1:6">
       <c r="A305" s="1"/>
       <c r="B305" s="1">
-        <v>30205</v>
+        <v>30123</v>
       </c>
       <c r="C305" s="1" t="s">
-        <v>506</v>
+        <v>520</v>
       </c>
       <c r="D305" s="1">
         <v>3</v>
@@ -8536,10 +8568,10 @@
     <row r="306" ht="15" customHeight="1" spans="1:6">
       <c r="A306" s="1"/>
       <c r="B306" s="1">
-        <v>30206</v>
+        <v>30124</v>
       </c>
       <c r="C306" s="1" t="s">
-        <v>506</v>
+        <v>520</v>
       </c>
       <c r="D306" s="1">
         <v>3</v>
@@ -8554,10 +8586,10 @@
     <row r="307" ht="15" customHeight="1" spans="1:6">
       <c r="A307" s="1"/>
       <c r="B307" s="1">
-        <v>30301</v>
+        <v>30125</v>
       </c>
       <c r="C307" s="1" t="s">
-        <v>506</v>
+        <v>520</v>
       </c>
       <c r="D307" s="1">
         <v>3</v>
@@ -8572,10 +8604,10 @@
     <row r="308" ht="15" customHeight="1" spans="1:6">
       <c r="A308" s="1"/>
       <c r="B308" s="1">
-        <v>30302</v>
+        <v>30201</v>
       </c>
       <c r="C308" s="1" t="s">
-        <v>506</v>
+        <v>520</v>
       </c>
       <c r="D308" s="1">
         <v>3</v>
@@ -8590,10 +8622,10 @@
     <row r="309" ht="15" customHeight="1" spans="1:6">
       <c r="A309" s="1"/>
       <c r="B309" s="1">
-        <v>30303</v>
+        <v>30202</v>
       </c>
       <c r="C309" s="1" t="s">
-        <v>506</v>
+        <v>520</v>
       </c>
       <c r="D309" s="1">
         <v>3</v>
@@ -8608,10 +8640,10 @@
     <row r="310" ht="15" customHeight="1" spans="1:6">
       <c r="A310" s="1"/>
       <c r="B310" s="1">
-        <v>30304</v>
+        <v>30203</v>
       </c>
       <c r="C310" s="1" t="s">
-        <v>506</v>
+        <v>520</v>
       </c>
       <c r="D310" s="1">
         <v>3</v>
@@ -8626,10 +8658,10 @@
     <row r="311" ht="15" customHeight="1" spans="1:6">
       <c r="A311" s="1"/>
       <c r="B311" s="1">
-        <v>30305</v>
+        <v>30204</v>
       </c>
       <c r="C311" s="1" t="s">
-        <v>506</v>
+        <v>520</v>
       </c>
       <c r="D311" s="1">
         <v>3</v>
@@ -8644,10 +8676,10 @@
     <row r="312" ht="15" customHeight="1" spans="1:6">
       <c r="A312" s="1"/>
       <c r="B312" s="1">
-        <v>30306</v>
+        <v>30205</v>
       </c>
       <c r="C312" s="1" t="s">
-        <v>506</v>
+        <v>520</v>
       </c>
       <c r="D312" s="1">
         <v>3</v>
@@ -8662,10 +8694,10 @@
     <row r="313" ht="15" customHeight="1" spans="1:6">
       <c r="A313" s="1"/>
       <c r="B313" s="1">
-        <v>30307</v>
+        <v>30206</v>
       </c>
       <c r="C313" s="1" t="s">
-        <v>506</v>
+        <v>520</v>
       </c>
       <c r="D313" s="1">
         <v>3</v>
@@ -8680,10 +8712,10 @@
     <row r="314" ht="15" customHeight="1" spans="1:6">
       <c r="A314" s="1"/>
       <c r="B314" s="1">
-        <v>30308</v>
+        <v>30301</v>
       </c>
       <c r="C314" s="1" t="s">
-        <v>506</v>
+        <v>520</v>
       </c>
       <c r="D314" s="1">
         <v>3</v>
@@ -8698,136 +8730,136 @@
     <row r="315" ht="15" customHeight="1" spans="1:6">
       <c r="A315" s="1"/>
       <c r="B315" s="1">
-        <v>60001</v>
+        <v>30302</v>
       </c>
       <c r="C315" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="D315" s="1">
+        <v>3</v>
+      </c>
+      <c r="E315" s="1" t="s">
         <v>639</v>
       </c>
-      <c r="D315" s="1">
-        <v>7</v>
-      </c>
-      <c r="E315" s="1" t="s">
+      <c r="F315" s="1" t="s">
         <v>640</v>
-      </c>
-      <c r="F315" s="1" t="s">
-        <v>641</v>
       </c>
     </row>
     <row r="316" ht="15" customHeight="1" spans="1:6">
       <c r="A316" s="1"/>
       <c r="B316" s="1">
-        <v>60002</v>
+        <v>30303</v>
       </c>
       <c r="C316" s="1" t="s">
-        <v>639</v>
+        <v>520</v>
       </c>
       <c r="D316" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E316" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="F316" s="1" t="s">
         <v>642</v>
-      </c>
-      <c r="F316" s="1" t="s">
-        <v>643</v>
       </c>
     </row>
     <row r="317" ht="15" customHeight="1" spans="1:6">
       <c r="A317" s="1"/>
       <c r="B317" s="1">
-        <v>60003</v>
+        <v>30304</v>
       </c>
       <c r="C317" s="1" t="s">
-        <v>639</v>
+        <v>520</v>
       </c>
       <c r="D317" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E317" s="1" t="s">
+        <v>643</v>
+      </c>
+      <c r="F317" s="1" t="s">
         <v>644</v>
-      </c>
-      <c r="F317" s="1" t="s">
-        <v>645</v>
       </c>
     </row>
     <row r="318" ht="15" customHeight="1" spans="1:6">
       <c r="A318" s="1"/>
       <c r="B318" s="1">
-        <v>60004</v>
+        <v>30305</v>
       </c>
       <c r="C318" s="1" t="s">
-        <v>639</v>
+        <v>520</v>
       </c>
       <c r="D318" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E318" s="1" t="s">
+        <v>645</v>
+      </c>
+      <c r="F318" s="1" t="s">
         <v>646</v>
-      </c>
-      <c r="F318" s="1" t="s">
-        <v>647</v>
       </c>
     </row>
     <row r="319" ht="15" customHeight="1" spans="1:6">
       <c r="A319" s="1"/>
       <c r="B319" s="1">
-        <v>60005</v>
+        <v>30306</v>
       </c>
       <c r="C319" s="1" t="s">
-        <v>639</v>
+        <v>520</v>
       </c>
       <c r="D319" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E319" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="F319" s="1" t="s">
         <v>648</v>
-      </c>
-      <c r="F319" s="1" t="s">
-        <v>649</v>
       </c>
     </row>
     <row r="320" ht="15" customHeight="1" spans="1:6">
       <c r="A320" s="1"/>
       <c r="B320" s="1">
-        <v>60006</v>
+        <v>30307</v>
       </c>
       <c r="C320" s="1" t="s">
-        <v>639</v>
+        <v>520</v>
       </c>
       <c r="D320" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E320" s="1" t="s">
+        <v>649</v>
+      </c>
+      <c r="F320" s="1" t="s">
         <v>650</v>
-      </c>
-      <c r="F320" s="1" t="s">
-        <v>651</v>
       </c>
     </row>
     <row r="321" ht="15" customHeight="1" spans="1:6">
       <c r="A321" s="1"/>
       <c r="B321" s="1">
-        <v>60007</v>
+        <v>30308</v>
       </c>
       <c r="C321" s="1" t="s">
-        <v>639</v>
+        <v>520</v>
       </c>
       <c r="D321" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E321" s="1" t="s">
+        <v>651</v>
+      </c>
+      <c r="F321" s="1" t="s">
         <v>652</v>
-      </c>
-      <c r="F321" s="1" t="s">
-        <v>653</v>
       </c>
     </row>
     <row r="322" ht="15" customHeight="1" spans="1:6">
       <c r="A322" s="1"/>
       <c r="B322" s="1">
-        <v>60008</v>
+        <v>60001</v>
       </c>
       <c r="C322" s="1" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="D322" s="1">
         <v>7</v>
@@ -8842,10 +8874,10 @@
     <row r="323" ht="15" customHeight="1" spans="1:6">
       <c r="A323" s="1"/>
       <c r="B323" s="1">
-        <v>60009</v>
+        <v>60002</v>
       </c>
       <c r="C323" s="1" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="D323" s="1">
         <v>7</v>
@@ -8860,10 +8892,10 @@
     <row r="324" ht="15" customHeight="1" spans="1:6">
       <c r="A324" s="1"/>
       <c r="B324" s="1">
-        <v>60010</v>
+        <v>60003</v>
       </c>
       <c r="C324" s="1" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="D324" s="1">
         <v>7</v>
@@ -8878,10 +8910,10 @@
     <row r="325" ht="15" customHeight="1" spans="1:6">
       <c r="A325" s="1"/>
       <c r="B325" s="1">
-        <v>60011</v>
+        <v>60004</v>
       </c>
       <c r="C325" s="1" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="D325" s="1">
         <v>7</v>
@@ -8896,10 +8928,10 @@
     <row r="326" ht="15" customHeight="1" spans="1:6">
       <c r="A326" s="1"/>
       <c r="B326" s="1">
-        <v>60012</v>
+        <v>60005</v>
       </c>
       <c r="C326" s="1" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="D326" s="1">
         <v>7</v>
@@ -8914,10 +8946,10 @@
     <row r="327" ht="15" customHeight="1" spans="1:6">
       <c r="A327" s="1"/>
       <c r="B327" s="1">
-        <v>60013</v>
+        <v>60006</v>
       </c>
       <c r="C327" s="1" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="D327" s="1">
         <v>7</v>
@@ -8932,10 +8964,10 @@
     <row r="328" ht="15" customHeight="1" spans="1:6">
       <c r="A328" s="1"/>
       <c r="B328" s="1">
-        <v>60014</v>
+        <v>60007</v>
       </c>
       <c r="C328" s="1" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="D328" s="1">
         <v>7</v>
@@ -8950,10 +8982,10 @@
     <row r="329" ht="15" customHeight="1" spans="1:6">
       <c r="A329" s="1"/>
       <c r="B329" s="1">
-        <v>60015</v>
+        <v>60008</v>
       </c>
       <c r="C329" s="1" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="D329" s="1">
         <v>7</v>
@@ -8968,10 +9000,10 @@
     <row r="330" ht="15" customHeight="1" spans="1:6">
       <c r="A330" s="1"/>
       <c r="B330" s="1">
-        <v>60016</v>
+        <v>60009</v>
       </c>
       <c r="C330" s="1" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="D330" s="1">
         <v>7</v>
@@ -8986,10 +9018,10 @@
     <row r="331" ht="15" customHeight="1" spans="1:6">
       <c r="A331" s="1"/>
       <c r="B331" s="1">
-        <v>60017</v>
+        <v>60010</v>
       </c>
       <c r="C331" s="1" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="D331" s="1">
         <v>7</v>
@@ -9004,10 +9036,10 @@
     <row r="332" ht="15" customHeight="1" spans="1:6">
       <c r="A332" s="1"/>
       <c r="B332" s="1">
-        <v>60018</v>
+        <v>60011</v>
       </c>
       <c r="C332" s="1" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="D332" s="1">
         <v>7</v>
@@ -9022,10 +9054,10 @@
     <row r="333" ht="15" customHeight="1" spans="1:6">
       <c r="A333" s="1"/>
       <c r="B333" s="1">
-        <v>60019</v>
+        <v>60012</v>
       </c>
       <c r="C333" s="1" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="D333" s="1">
         <v>7</v>
@@ -9040,10 +9072,10 @@
     <row r="334" ht="15" customHeight="1" spans="1:6">
       <c r="A334" s="1"/>
       <c r="B334" s="1">
-        <v>60020</v>
+        <v>60013</v>
       </c>
       <c r="C334" s="1" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="D334" s="1">
         <v>7</v>
@@ -9058,10 +9090,10 @@
     <row r="335" ht="15" customHeight="1" spans="1:6">
       <c r="A335" s="1"/>
       <c r="B335" s="1">
-        <v>60021</v>
+        <v>60014</v>
       </c>
       <c r="C335" s="1" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="D335" s="1">
         <v>7</v>
@@ -9076,10 +9108,10 @@
     <row r="336" ht="15" customHeight="1" spans="1:6">
       <c r="A336" s="1"/>
       <c r="B336" s="1">
-        <v>60022</v>
+        <v>60015</v>
       </c>
       <c r="C336" s="1" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="D336" s="1">
         <v>7</v>
@@ -9094,10 +9126,10 @@
     <row r="337" ht="15" customHeight="1" spans="1:6">
       <c r="A337" s="1"/>
       <c r="B337" s="1">
-        <v>60023</v>
+        <v>60016</v>
       </c>
       <c r="C337" s="1" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="D337" s="1">
         <v>7</v>
@@ -9112,10 +9144,10 @@
     <row r="338" ht="15" customHeight="1" spans="1:6">
       <c r="A338" s="1"/>
       <c r="B338" s="1">
-        <v>60024</v>
+        <v>60017</v>
       </c>
       <c r="C338" s="1" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="D338" s="1">
         <v>7</v>
@@ -9130,10 +9162,10 @@
     <row r="339" ht="15" customHeight="1" spans="1:6">
       <c r="A339" s="1"/>
       <c r="B339" s="1">
-        <v>60025</v>
+        <v>60018</v>
       </c>
       <c r="C339" s="1" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="D339" s="1">
         <v>7</v>
@@ -9148,10 +9180,10 @@
     <row r="340" ht="15" customHeight="1" spans="1:6">
       <c r="A340" s="1"/>
       <c r="B340" s="1">
-        <v>60026</v>
+        <v>60019</v>
       </c>
       <c r="C340" s="1" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="D340" s="1">
         <v>7</v>
@@ -9166,10 +9198,10 @@
     <row r="341" ht="15" customHeight="1" spans="1:6">
       <c r="A341" s="1"/>
       <c r="B341" s="1">
-        <v>60027</v>
+        <v>60020</v>
       </c>
       <c r="C341" s="1" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="D341" s="1">
         <v>7</v>
@@ -9184,10 +9216,10 @@
     <row r="342" ht="15" customHeight="1" spans="1:6">
       <c r="A342" s="1"/>
       <c r="B342" s="1">
-        <v>60028</v>
+        <v>60021</v>
       </c>
       <c r="C342" s="1" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="D342" s="1">
         <v>7</v>
@@ -9202,10 +9234,10 @@
     <row r="343" ht="15" customHeight="1" spans="1:6">
       <c r="A343" s="1"/>
       <c r="B343" s="1">
-        <v>60029</v>
+        <v>60022</v>
       </c>
       <c r="C343" s="1" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="D343" s="1">
         <v>7</v>
@@ -9220,10 +9252,10 @@
     <row r="344" ht="15" customHeight="1" spans="1:6">
       <c r="A344" s="1"/>
       <c r="B344" s="1">
-        <v>60030</v>
+        <v>60023</v>
       </c>
       <c r="C344" s="1" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="D344" s="1">
         <v>7</v>
@@ -9238,10 +9270,10 @@
     <row r="345" ht="15" customHeight="1" spans="1:6">
       <c r="A345" s="1"/>
       <c r="B345" s="1">
-        <v>60031</v>
+        <v>60024</v>
       </c>
       <c r="C345" s="1" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="D345" s="1">
         <v>7</v>
@@ -9256,10 +9288,10 @@
     <row r="346" ht="15" customHeight="1" spans="1:6">
       <c r="A346" s="1"/>
       <c r="B346" s="1">
-        <v>60032</v>
+        <v>60025</v>
       </c>
       <c r="C346" s="1" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="D346" s="1">
         <v>7</v>
@@ -9274,10 +9306,10 @@
     <row r="347" ht="15" customHeight="1" spans="1:6">
       <c r="A347" s="1"/>
       <c r="B347" s="1">
-        <v>60033</v>
+        <v>60026</v>
       </c>
       <c r="C347" s="1" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="D347" s="1">
         <v>7</v>
@@ -9292,10 +9324,10 @@
     <row r="348" ht="15" customHeight="1" spans="1:6">
       <c r="A348" s="1"/>
       <c r="B348" s="1">
-        <v>60034</v>
+        <v>60027</v>
       </c>
       <c r="C348" s="1" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="D348" s="1">
         <v>7</v>
@@ -9310,10 +9342,10 @@
     <row r="349" ht="15" customHeight="1" spans="1:6">
       <c r="A349" s="1"/>
       <c r="B349" s="1">
-        <v>60035</v>
+        <v>60028</v>
       </c>
       <c r="C349" s="1" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="D349" s="1">
         <v>7</v>
@@ -9328,10 +9360,10 @@
     <row r="350" ht="15" customHeight="1" spans="1:6">
       <c r="A350" s="1"/>
       <c r="B350" s="1">
-        <v>60036</v>
+        <v>60029</v>
       </c>
       <c r="C350" s="1" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="D350" s="1">
         <v>7</v>
@@ -9346,10 +9378,10 @@
     <row r="351" ht="15" customHeight="1" spans="1:6">
       <c r="A351" s="1"/>
       <c r="B351" s="1">
-        <v>60037</v>
+        <v>60030</v>
       </c>
       <c r="C351" s="1" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="D351" s="1">
         <v>7</v>
@@ -9364,10 +9396,10 @@
     <row r="352" ht="15" customHeight="1" spans="1:6">
       <c r="A352" s="1"/>
       <c r="B352" s="1">
-        <v>60038</v>
+        <v>60031</v>
       </c>
       <c r="C352" s="1" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="D352" s="1">
         <v>7</v>
@@ -9382,10 +9414,10 @@
     <row r="353" ht="15" customHeight="1" spans="1:6">
       <c r="A353" s="1"/>
       <c r="B353" s="1">
-        <v>60039</v>
+        <v>60032</v>
       </c>
       <c r="C353" s="1" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="D353" s="1">
         <v>7</v>
@@ -9400,10 +9432,10 @@
     <row r="354" ht="15" customHeight="1" spans="1:6">
       <c r="A354" s="1"/>
       <c r="B354" s="1">
-        <v>60040</v>
+        <v>60033</v>
       </c>
       <c r="C354" s="1" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="D354" s="1">
         <v>7</v>
@@ -9418,10 +9450,10 @@
     <row r="355" ht="15" customHeight="1" spans="1:6">
       <c r="A355" s="1"/>
       <c r="B355" s="1">
-        <v>60041</v>
+        <v>60034</v>
       </c>
       <c r="C355" s="1" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="D355" s="1">
         <v>7</v>
@@ -9436,10 +9468,10 @@
     <row r="356" ht="15" customHeight="1" spans="1:6">
       <c r="A356" s="1"/>
       <c r="B356" s="1">
-        <v>60042</v>
+        <v>60035</v>
       </c>
       <c r="C356" s="1" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="D356" s="1">
         <v>7</v>
@@ -9454,10 +9486,10 @@
     <row r="357" ht="15" customHeight="1" spans="1:6">
       <c r="A357" s="1"/>
       <c r="B357" s="1">
-        <v>60043</v>
+        <v>60036</v>
       </c>
       <c r="C357" s="1" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="D357" s="1">
         <v>7</v>
@@ -9472,10 +9504,10 @@
     <row r="358" ht="15" customHeight="1" spans="1:6">
       <c r="A358" s="1"/>
       <c r="B358" s="1">
-        <v>60044</v>
+        <v>60037</v>
       </c>
       <c r="C358" s="1" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="D358" s="1">
         <v>7</v>
@@ -9490,10 +9522,10 @@
     <row r="359" ht="15" customHeight="1" spans="1:6">
       <c r="A359" s="1"/>
       <c r="B359" s="1">
-        <v>60045</v>
+        <v>60038</v>
       </c>
       <c r="C359" s="1" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="D359" s="1">
         <v>7</v>
@@ -9508,10 +9540,10 @@
     <row r="360" ht="15" customHeight="1" spans="1:6">
       <c r="A360" s="1"/>
       <c r="B360" s="1">
-        <v>60046</v>
+        <v>60039</v>
       </c>
       <c r="C360" s="1" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="D360" s="1">
         <v>7</v>
@@ -9526,10 +9558,10 @@
     <row r="361" ht="15" customHeight="1" spans="1:6">
       <c r="A361" s="1"/>
       <c r="B361" s="1">
-        <v>60047</v>
+        <v>60040</v>
       </c>
       <c r="C361" s="1" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="D361" s="1">
         <v>7</v>
@@ -9544,10 +9576,10 @@
     <row r="362" ht="15" customHeight="1" spans="1:6">
       <c r="A362" s="1"/>
       <c r="B362" s="1">
-        <v>60048</v>
+        <v>60041</v>
       </c>
       <c r="C362" s="1" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="D362" s="1">
         <v>7</v>
@@ -9562,10 +9594,10 @@
     <row r="363" ht="15" customHeight="1" spans="1:6">
       <c r="A363" s="1"/>
       <c r="B363" s="1">
-        <v>60049</v>
+        <v>60042</v>
       </c>
       <c r="C363" s="1" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="D363" s="1">
         <v>7</v>
@@ -9580,10 +9612,10 @@
     <row r="364" ht="15" customHeight="1" spans="1:6">
       <c r="A364" s="1"/>
       <c r="B364" s="1">
-        <v>60050</v>
+        <v>60043</v>
       </c>
       <c r="C364" s="1" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="D364" s="1">
         <v>7</v>
@@ -9598,10 +9630,10 @@
     <row r="365" ht="15" customHeight="1" spans="1:6">
       <c r="A365" s="1"/>
       <c r="B365" s="1">
-        <v>60051</v>
+        <v>60044</v>
       </c>
       <c r="C365" s="1" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="D365" s="1">
         <v>7</v>
@@ -9616,10 +9648,10 @@
     <row r="366" ht="15" customHeight="1" spans="1:6">
       <c r="A366" s="1"/>
       <c r="B366" s="1">
-        <v>60052</v>
+        <v>60045</v>
       </c>
       <c r="C366" s="1" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="D366" s="1">
         <v>7</v>
@@ -9634,10 +9666,10 @@
     <row r="367" ht="15" customHeight="1" spans="1:6">
       <c r="A367" s="1"/>
       <c r="B367" s="1">
-        <v>60053</v>
+        <v>60046</v>
       </c>
       <c r="C367" s="1" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="D367" s="1">
         <v>7</v>
@@ -9652,10 +9684,10 @@
     <row r="368" ht="15" customHeight="1" spans="1:6">
       <c r="A368" s="1"/>
       <c r="B368" s="1">
-        <v>60054</v>
+        <v>60047</v>
       </c>
       <c r="C368" s="1" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="D368" s="1">
         <v>7</v>
@@ -9670,10 +9702,10 @@
     <row r="369" ht="15" customHeight="1" spans="1:6">
       <c r="A369" s="1"/>
       <c r="B369" s="1">
-        <v>60055</v>
+        <v>60048</v>
       </c>
       <c r="C369" s="1" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="D369" s="1">
         <v>7</v>
@@ -9688,10 +9720,10 @@
     <row r="370" ht="15" customHeight="1" spans="1:6">
       <c r="A370" s="1"/>
       <c r="B370" s="1">
-        <v>60056</v>
+        <v>60049</v>
       </c>
       <c r="C370" s="1" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="D370" s="1">
         <v>7</v>
@@ -9706,10 +9738,10 @@
     <row r="371" ht="15" customHeight="1" spans="1:6">
       <c r="A371" s="1"/>
       <c r="B371" s="1">
-        <v>60057</v>
+        <v>60050</v>
       </c>
       <c r="C371" s="1" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="D371" s="1">
         <v>7</v>
@@ -9724,10 +9756,10 @@
     <row r="372" ht="15" customHeight="1" spans="1:6">
       <c r="A372" s="1"/>
       <c r="B372" s="1">
-        <v>60058</v>
+        <v>60051</v>
       </c>
       <c r="C372" s="1" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="D372" s="1">
         <v>7</v>
@@ -9742,10 +9774,10 @@
     <row r="373" ht="15" customHeight="1" spans="1:6">
       <c r="A373" s="1"/>
       <c r="B373" s="1">
-        <v>60059</v>
+        <v>60052</v>
       </c>
       <c r="C373" s="1" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="D373" s="1">
         <v>7</v>
@@ -9760,10 +9792,10 @@
     <row r="374" ht="15" customHeight="1" spans="1:6">
       <c r="A374" s="1"/>
       <c r="B374" s="1">
-        <v>60060</v>
+        <v>60053</v>
       </c>
       <c r="C374" s="1" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="D374" s="1">
         <v>7</v>
@@ -9778,10 +9810,10 @@
     <row r="375" ht="15" customHeight="1" spans="1:6">
       <c r="A375" s="1"/>
       <c r="B375" s="1">
-        <v>60061</v>
+        <v>60054</v>
       </c>
       <c r="C375" s="1" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="D375" s="1">
         <v>7</v>
@@ -9796,10 +9828,10 @@
     <row r="376" ht="15" customHeight="1" spans="1:6">
       <c r="A376" s="1"/>
       <c r="B376" s="1">
-        <v>60062</v>
+        <v>60055</v>
       </c>
       <c r="C376" s="1" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="D376" s="1">
         <v>7</v>
@@ -9814,10 +9846,10 @@
     <row r="377" ht="15" customHeight="1" spans="1:6">
       <c r="A377" s="1"/>
       <c r="B377" s="1">
-        <v>60063</v>
+        <v>60056</v>
       </c>
       <c r="C377" s="1" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="D377" s="1">
         <v>7</v>
@@ -9832,10 +9864,10 @@
     <row r="378" ht="15" customHeight="1" spans="1:6">
       <c r="A378" s="1"/>
       <c r="B378" s="1">
-        <v>60064</v>
+        <v>60057</v>
       </c>
       <c r="C378" s="1" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="D378" s="1">
         <v>7</v>
@@ -9850,10 +9882,10 @@
     <row r="379" ht="15" customHeight="1" spans="1:6">
       <c r="A379" s="1"/>
       <c r="B379" s="1">
-        <v>60065</v>
+        <v>60058</v>
       </c>
       <c r="C379" s="1" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="D379" s="1">
         <v>7</v>
@@ -9868,10 +9900,10 @@
     <row r="380" ht="15" customHeight="1" spans="1:6">
       <c r="A380" s="1"/>
       <c r="B380" s="1">
-        <v>60066</v>
+        <v>60059</v>
       </c>
       <c r="C380" s="1" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="D380" s="1">
         <v>7</v>
@@ -9886,10 +9918,10 @@
     <row r="381" ht="15" customHeight="1" spans="1:6">
       <c r="A381" s="1"/>
       <c r="B381" s="1">
-        <v>60067</v>
+        <v>60060</v>
       </c>
       <c r="C381" s="1" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="D381" s="1">
         <v>7</v>
@@ -9904,10 +9936,10 @@
     <row r="382" ht="15" customHeight="1" spans="1:6">
       <c r="A382" s="1"/>
       <c r="B382" s="1">
-        <v>60068</v>
+        <v>60061</v>
       </c>
       <c r="C382" s="1" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="D382" s="1">
         <v>7</v>
@@ -9922,10 +9954,10 @@
     <row r="383" ht="15" customHeight="1" spans="1:6">
       <c r="A383" s="1"/>
       <c r="B383" s="1">
-        <v>60069</v>
+        <v>60062</v>
       </c>
       <c r="C383" s="1" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="D383" s="1">
         <v>7</v>
@@ -9940,10 +9972,10 @@
     <row r="384" ht="15" customHeight="1" spans="1:6">
       <c r="A384" s="1"/>
       <c r="B384" s="1">
-        <v>60070</v>
+        <v>60063</v>
       </c>
       <c r="C384" s="1" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="D384" s="1">
         <v>7</v>
@@ -9958,10 +9990,10 @@
     <row r="385" ht="15" customHeight="1" spans="1:6">
       <c r="A385" s="1"/>
       <c r="B385" s="1">
-        <v>60071</v>
+        <v>60064</v>
       </c>
       <c r="C385" s="1" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="D385" s="1">
         <v>7</v>
@@ -9976,10 +10008,10 @@
     <row r="386" ht="15" customHeight="1" spans="1:6">
       <c r="A386" s="1"/>
       <c r="B386" s="1">
-        <v>60072</v>
+        <v>60065</v>
       </c>
       <c r="C386" s="1" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="D386" s="1">
         <v>7</v>
@@ -9994,10 +10026,10 @@
     <row r="387" ht="15" customHeight="1" spans="1:6">
       <c r="A387" s="1"/>
       <c r="B387" s="1">
-        <v>60073</v>
+        <v>60066</v>
       </c>
       <c r="C387" s="1" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="D387" s="1">
         <v>7</v>
@@ -10012,10 +10044,10 @@
     <row r="388" ht="15" customHeight="1" spans="1:6">
       <c r="A388" s="1"/>
       <c r="B388" s="1">
-        <v>60074</v>
+        <v>60067</v>
       </c>
       <c r="C388" s="1" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="D388" s="1">
         <v>7</v>
@@ -10030,10 +10062,10 @@
     <row r="389" ht="15" customHeight="1" spans="1:6">
       <c r="A389" s="1"/>
       <c r="B389" s="1">
-        <v>60075</v>
+        <v>60068</v>
       </c>
       <c r="C389" s="1" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="D389" s="1">
         <v>7</v>
@@ -10048,10 +10080,10 @@
     <row r="390" ht="15" customHeight="1" spans="1:6">
       <c r="A390" s="1"/>
       <c r="B390" s="1">
-        <v>60076</v>
+        <v>60069</v>
       </c>
       <c r="C390" s="1" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="D390" s="1">
         <v>7</v>
@@ -10066,10 +10098,10 @@
     <row r="391" ht="15" customHeight="1" spans="1:6">
       <c r="A391" s="1"/>
       <c r="B391" s="1">
-        <v>60077</v>
+        <v>60070</v>
       </c>
       <c r="C391" s="1" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="D391" s="1">
         <v>7</v>
@@ -10084,10 +10116,10 @@
     <row r="392" ht="15" customHeight="1" spans="1:6">
       <c r="A392" s="1"/>
       <c r="B392" s="1">
-        <v>60078</v>
+        <v>60071</v>
       </c>
       <c r="C392" s="1" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="D392" s="1">
         <v>7</v>
@@ -10102,10 +10134,10 @@
     <row r="393" ht="15" customHeight="1" spans="1:6">
       <c r="A393" s="1"/>
       <c r="B393" s="1">
-        <v>60079</v>
+        <v>60072</v>
       </c>
       <c r="C393" s="1" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="D393" s="1">
         <v>7</v>
@@ -10120,10 +10152,10 @@
     <row r="394" ht="15" customHeight="1" spans="1:6">
       <c r="A394" s="1"/>
       <c r="B394" s="1">
-        <v>60080</v>
+        <v>60073</v>
       </c>
       <c r="C394" s="1" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="D394" s="1">
         <v>7</v>
@@ -10138,10 +10170,10 @@
     <row r="395" ht="15" customHeight="1" spans="1:6">
       <c r="A395" s="1"/>
       <c r="B395" s="1">
-        <v>60081</v>
+        <v>60074</v>
       </c>
       <c r="C395" s="1" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="D395" s="1">
         <v>7</v>
@@ -10156,10 +10188,10 @@
     <row r="396" ht="15" customHeight="1" spans="1:6">
       <c r="A396" s="1"/>
       <c r="B396" s="1">
-        <v>60082</v>
+        <v>60075</v>
       </c>
       <c r="C396" s="1" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="D396" s="1">
         <v>7</v>
@@ -10174,10 +10206,10 @@
     <row r="397" ht="15" customHeight="1" spans="1:6">
       <c r="A397" s="1"/>
       <c r="B397" s="1">
-        <v>60083</v>
+        <v>60076</v>
       </c>
       <c r="C397" s="1" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="D397" s="1">
         <v>7</v>
@@ -10187,6 +10219,132 @@
       </c>
       <c r="F397" s="1" t="s">
         <v>805</v>
+      </c>
+    </row>
+    <row r="398" ht="15" customHeight="1" spans="1:6">
+      <c r="A398" s="1"/>
+      <c r="B398" s="1">
+        <v>60077</v>
+      </c>
+      <c r="C398" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D398" s="1">
+        <v>7</v>
+      </c>
+      <c r="E398" s="1" t="s">
+        <v>806</v>
+      </c>
+      <c r="F398" s="1" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="399" ht="15" customHeight="1" spans="1:6">
+      <c r="A399" s="1"/>
+      <c r="B399" s="1">
+        <v>60078</v>
+      </c>
+      <c r="C399" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D399" s="1">
+        <v>7</v>
+      </c>
+      <c r="E399" s="1" t="s">
+        <v>808</v>
+      </c>
+      <c r="F399" s="1" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="400" ht="15" customHeight="1" spans="1:6">
+      <c r="A400" s="1"/>
+      <c r="B400" s="1">
+        <v>60079</v>
+      </c>
+      <c r="C400" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D400" s="1">
+        <v>7</v>
+      </c>
+      <c r="E400" s="1" t="s">
+        <v>810</v>
+      </c>
+      <c r="F400" s="1" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="401" ht="15" customHeight="1" spans="1:6">
+      <c r="A401" s="1"/>
+      <c r="B401" s="1">
+        <v>60080</v>
+      </c>
+      <c r="C401" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D401" s="1">
+        <v>7</v>
+      </c>
+      <c r="E401" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="F401" s="1" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="402" ht="15" customHeight="1" spans="1:6">
+      <c r="A402" s="1"/>
+      <c r="B402" s="1">
+        <v>60081</v>
+      </c>
+      <c r="C402" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D402" s="1">
+        <v>7</v>
+      </c>
+      <c r="E402" s="1" t="s">
+        <v>814</v>
+      </c>
+      <c r="F402" s="1" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="403" ht="15" customHeight="1" spans="1:6">
+      <c r="A403" s="1"/>
+      <c r="B403" s="1">
+        <v>60082</v>
+      </c>
+      <c r="C403" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D403" s="1">
+        <v>7</v>
+      </c>
+      <c r="E403" s="1" t="s">
+        <v>816</v>
+      </c>
+      <c r="F403" s="1" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="404" ht="15" customHeight="1" spans="1:6">
+      <c r="A404" s="1"/>
+      <c r="B404" s="1">
+        <v>60083</v>
+      </c>
+      <c r="C404" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="D404" s="1">
+        <v>7</v>
+      </c>
+      <c r="E404" s="1" t="s">
+        <v>818</v>
+      </c>
+      <c r="F404" s="1" t="s">
+        <v>819</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/DataTables/ResourceConfigTable.xlsx
+++ b/AAAGameData/DataTables/ResourceConfigTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11925"/>
+    <workbookView windowWidth="29868" windowHeight="14855"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1027" uniqueCount="820">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1038" uniqueCount="837">
   <si>
     <t>#</t>
   </si>
@@ -122,6 +122,18 @@
     <t>探索阶段-遭遇战图标</t>
   </si>
   <si>
+    <t>UI/CharacterBagUI/Lebal_0.png</t>
+  </si>
+  <si>
+    <t>角色界面，标签未选中背景</t>
+  </si>
+  <si>
+    <t>UI/CharacterBagUI/Lebal_1.png</t>
+  </si>
+  <si>
+    <t>角色界面，标签选中背景</t>
+  </si>
+  <si>
     <t>UI/Items/Gold.png</t>
   </si>
   <si>
@@ -356,1017 +368,1038 @@
     <t>棋子-嫦娥图标</t>
   </si>
   <si>
+    <t>Chess/邪灵/立绘.png</t>
+  </si>
+  <si>
+    <t>棋子-邪灵图标</t>
+  </si>
+  <si>
+    <t>Chess/恶魂/立绘.png</t>
+  </si>
+  <si>
+    <t>棋子-恶魂图标</t>
+  </si>
+  <si>
+    <t>Chess/黑暗杨戬/立绘.png</t>
+  </si>
+  <si>
+    <t>棋子-黑暗杨戬图标</t>
+  </si>
+  <si>
+    <t>Chess/黑暗哮天犬/立绘.png</t>
+  </si>
+  <si>
+    <t>棋子-黑暗哮天犬图标</t>
+  </si>
+  <si>
+    <t>Buff/1.png</t>
+  </si>
+  <si>
+    <t>灼烧Buff图标</t>
+  </si>
+  <si>
+    <t>Buff/2.png</t>
+  </si>
+  <si>
+    <t>寒霜Buff图标</t>
+  </si>
+  <si>
+    <t>Buff/3.png</t>
+  </si>
+  <si>
+    <t>融化Buff图标</t>
+  </si>
+  <si>
+    <t>Buff/4.png</t>
+  </si>
+  <si>
+    <t>神力增益Buff图标</t>
+  </si>
+  <si>
+    <t>Buff/5.png</t>
+  </si>
+  <si>
+    <t>日落长弓Buff图标</t>
+  </si>
+  <si>
+    <t>Buff/6.png</t>
+  </si>
+  <si>
+    <t>九天玄冰（对敌）Buff图标</t>
+  </si>
+  <si>
+    <t>BuffTable使用|资源暂不存在</t>
+  </si>
+  <si>
+    <t>Buff/7.png</t>
+  </si>
+  <si>
+    <t>腐蚀Buff图标</t>
+  </si>
+  <si>
+    <t>Buff/8.png</t>
+  </si>
+  <si>
+    <t>黑暗狂暴Buff图标</t>
+  </si>
+  <si>
+    <t>Buff/9.png</t>
+  </si>
+  <si>
+    <t>恐惧Buff图标</t>
+  </si>
+  <si>
+    <t>Buff/10.png</t>
+  </si>
+  <si>
+    <t>虚无之躯Buff图标</t>
+  </si>
+  <si>
+    <t>Buff/28.png</t>
+  </si>
+  <si>
+    <t>九天玄冰（自身）Buff图标</t>
+  </si>
+  <si>
+    <t>UI/Icons/Skill_Dash.png</t>
+  </si>
+  <si>
+    <t>飞雷神-角色技能图标</t>
+  </si>
+  <si>
+    <t>UI/Icons/Skill_Heal.png</t>
+  </si>
+  <si>
+    <t>治疗术-角色技能图标</t>
+  </si>
+  <si>
+    <t>UI/Icons/Skill_Bomb.png</t>
+  </si>
+  <si>
+    <t>爆裂弹-角色技能图标</t>
+  </si>
+  <si>
+    <t>棋子海报</t>
+  </si>
+  <si>
+    <t>Chess/后羿/海报.png</t>
+  </si>
+  <si>
+    <t>后羿海报</t>
+  </si>
+  <si>
+    <t>Chess/嫦娥/海报.png</t>
+  </si>
+  <si>
+    <t>嫦娥海报</t>
+  </si>
+  <si>
+    <t>Chess/邪灵/海报.png</t>
+  </si>
+  <si>
+    <t>邪灵海报</t>
+  </si>
+  <si>
+    <t>Chess/恶魂/海报.png</t>
+  </si>
+  <si>
+    <t>恶魂海报</t>
+  </si>
+  <si>
+    <t>Chess/黑暗杨戬/海报.png</t>
+  </si>
+  <si>
+    <t>黑暗杨戬海报</t>
+  </si>
+  <si>
+    <t>Summoner/Skill/战意激昂技能.png</t>
+  </si>
+  <si>
+    <t>战意激昂-召唤师技能图标</t>
+  </si>
+  <si>
+    <t>Summoner/Skill/王者号令技能.png</t>
+  </si>
+  <si>
+    <t>王者号令-召唤师技能图标</t>
+  </si>
+  <si>
+    <t>Summoner/Skill/钢铁洪流技能.png</t>
+  </si>
+  <si>
+    <t>钢铁洪流-召唤师技能图标</t>
+  </si>
+  <si>
+    <t>Summoner/Skill/天灾降临技能.png</t>
+  </si>
+  <si>
+    <t>天灾降临-召唤师技能图标</t>
+  </si>
+  <si>
+    <t>Summoner/Skill/寂灭斩技能.png</t>
+  </si>
+  <si>
+    <t>寂灭斩-召唤师技能图标</t>
+  </si>
+  <si>
+    <t>Summoner/Skill/孤影技能.png</t>
+  </si>
+  <si>
+    <t>孤影-召唤师技能图标</t>
+  </si>
+  <si>
+    <t>Summoner/Skill/裁决之刻技能.png</t>
+  </si>
+  <si>
+    <t>裁决之刻-召唤师技能图标</t>
+  </si>
+  <si>
+    <t>Summoner/Skill/暗影咒体技能.png</t>
+  </si>
+  <si>
+    <t>暗影咒体-召唤师技能图标</t>
+  </si>
+  <si>
+    <t>Summoner/Skill/生命虹吸技能.png</t>
+  </si>
+  <si>
+    <t>生命虹吸-召唤师技能图标</t>
+  </si>
+  <si>
+    <t>SummonChessSkillTable使用|资源暂不存在</t>
+  </si>
+  <si>
+    <t>Skill/1.png</t>
+  </si>
+  <si>
+    <t>日落长弓-后羿技能图标</t>
+  </si>
+  <si>
+    <t>Skill/2.png</t>
+  </si>
+  <si>
+    <t>后羿普攻-后羿技能图标</t>
+  </si>
+  <si>
+    <t>Skill/3.png</t>
+  </si>
+  <si>
+    <t>神力-后羿技能图标</t>
+  </si>
+  <si>
+    <t>Skill/4.png</t>
+  </si>
+  <si>
+    <t>日陨-后羿技能图标</t>
+  </si>
+  <si>
+    <t>Skill/5.png</t>
+  </si>
+  <si>
+    <t>九天玄冰-嫦娥技能图标</t>
+  </si>
+  <si>
+    <t>Skill/6.png</t>
+  </si>
+  <si>
+    <t>嫦娥普攻-嫦娥技能图标</t>
+  </si>
+  <si>
+    <t>Skill/7.png</t>
+  </si>
+  <si>
+    <t>朔月飞轮-嫦娥技能图标</t>
+  </si>
+  <si>
+    <t>Skill/8.png</t>
+  </si>
+  <si>
+    <t>月华天倾-嫦娥技能图标</t>
+  </si>
+  <si>
+    <t>Skill/31.png</t>
+  </si>
+  <si>
+    <t>黑暗侵染-邪灵技能图标</t>
+  </si>
+  <si>
+    <t>Skill/32.png</t>
+  </si>
+  <si>
+    <t>邪灵普攻-邪灵技能图标</t>
+  </si>
+  <si>
+    <t>Skill/33.png</t>
+  </si>
+  <si>
+    <t>污染斩击-邪灵技能图标</t>
+  </si>
+  <si>
+    <t>Skill/34.png</t>
+  </si>
+  <si>
+    <t>腐蚀法阵-邪灵技能图标</t>
+  </si>
+  <si>
+    <t>Skill/41.png</t>
+  </si>
+  <si>
+    <t>虚无之躯-恶魂技能图标</t>
+  </si>
+  <si>
+    <t>Skill/42.png</t>
+  </si>
+  <si>
+    <t>恶魂普攻-恶魂技能图标</t>
+  </si>
+  <si>
+    <t>Skill/43.png</t>
+  </si>
+  <si>
+    <t>心灵扭曲-恶魂技能图标</t>
+  </si>
+  <si>
+    <t>Skill/44.png</t>
+  </si>
+  <si>
+    <t>邪念潮涌-恶魂技能图标</t>
+  </si>
+  <si>
+    <t>Skill/51.png</t>
+  </si>
+  <si>
+    <t>黑暗神力-黑暗杨戬技能图标</t>
+  </si>
+  <si>
+    <t>Skill/52.png</t>
+  </si>
+  <si>
+    <t>暗戟横扫-黑暗杨戬技能图标</t>
+  </si>
+  <si>
+    <t>Skill/53.png</t>
+  </si>
+  <si>
+    <t>天威圣戟·黑暗-黑暗杨戬技能图标</t>
+  </si>
+  <si>
+    <t>Skill/54.png</t>
+  </si>
+  <si>
+    <t>三眼天火-黑暗杨戬技能图标</t>
+  </si>
+  <si>
+    <t>Skill/55.png</t>
+  </si>
+  <si>
+    <t>堕落劈山-黑暗杨戬技能图标</t>
+  </si>
+  <si>
+    <t>Skill/56.png</t>
+  </si>
+  <si>
+    <t>撕咬-黑暗哮天犬技能图标</t>
+  </si>
+  <si>
+    <t>Items/1.png</t>
+  </si>
+  <si>
+    <t>钱包图标</t>
+  </si>
+  <si>
+    <t>Items/2.png</t>
+  </si>
+  <si>
+    <t>生命药水图标</t>
+  </si>
+  <si>
+    <t>Items/3.png</t>
+  </si>
+  <si>
+    <t>魔法药水图标</t>
+  </si>
+  <si>
+    <t>Items/4.png</t>
+  </si>
+  <si>
+    <t>经验宝石图标</t>
+  </si>
+  <si>
+    <t>Items/5.png</t>
+  </si>
+  <si>
+    <t>神秘钥匙图标</t>
+  </si>
+  <si>
+    <t>Items/6.png</t>
+  </si>
+  <si>
+    <t>古老卷轴图标</t>
+  </si>
+  <si>
+    <t>Items/7.png</t>
+  </si>
+  <si>
+    <t>八尺琼勾玉图标</t>
+  </si>
+  <si>
+    <t>Items/8.png</t>
+  </si>
+  <si>
+    <t>天丛云剑图标</t>
+  </si>
+  <si>
+    <t>Items/9.png</t>
+  </si>
+  <si>
+    <t>八咫镜图标</t>
+  </si>
+  <si>
+    <t>Items/10.png</t>
+  </si>
+  <si>
+    <t>石中剑图标</t>
+  </si>
+  <si>
+    <t>Items/11.png</t>
+  </si>
+  <si>
+    <t>龙鳞铠甲图标</t>
+  </si>
+  <si>
+    <t>Items/12.png</t>
+  </si>
+  <si>
+    <t>精灵之戒图标</t>
+  </si>
+  <si>
+    <t>Items/13.png</t>
+  </si>
+  <si>
+    <t>月华玉璧图标</t>
+  </si>
+  <si>
+    <t>Items/14.png</t>
+  </si>
+  <si>
+    <t>太阴弦月弓图标</t>
+  </si>
+  <si>
+    <t>Items/15.png</t>
+  </si>
+  <si>
+    <t>月轮镜图标</t>
+  </si>
+  <si>
+    <t>Items/16.png</t>
+  </si>
+  <si>
+    <t>炎魔之心图标</t>
+  </si>
+  <si>
+    <t>Items/17.png</t>
+  </si>
+  <si>
+    <t>炎魔之冠图标</t>
+  </si>
+  <si>
+    <t>Items/18.png</t>
+  </si>
+  <si>
+    <t>炎魔之剑图标</t>
+  </si>
+  <si>
+    <t>Items/19.png</t>
+  </si>
+  <si>
+    <t>古剑·樱花落图标</t>
+  </si>
+  <si>
+    <t>Items/20.png</t>
+  </si>
+  <si>
+    <t>暗影斗篷图标</t>
+  </si>
+  <si>
+    <t>Items/21.png</t>
+  </si>
+  <si>
+    <t>圣光铠甲图标</t>
+  </si>
+  <si>
+    <t>Items/22.png</t>
+  </si>
+  <si>
+    <t>古墓盗贼手套图标</t>
+  </si>
+  <si>
+    <t>Items/23.png</t>
+  </si>
+  <si>
+    <t>冰晶靴图标</t>
+  </si>
+  <si>
+    <t>Items/24.png</t>
+  </si>
+  <si>
+    <t>风暴法杖图标</t>
+  </si>
+  <si>
+    <t>Items/100.png</t>
+  </si>
+  <si>
+    <t>卡牌-神圣庇护解锁物图标</t>
+  </si>
+  <si>
+    <t>Items/101.png</t>
+  </si>
+  <si>
+    <t>卡牌-烈焰风暴解锁物图标</t>
+  </si>
+  <si>
+    <t>Items/102.png</t>
+  </si>
+  <si>
+    <t>卡牌-时间回溯解锁物图标</t>
+  </si>
+  <si>
+    <t>Items/103.png</t>
+  </si>
+  <si>
+    <t>卡牌-战争号角解锁物图标</t>
+  </si>
+  <si>
+    <t>Items/104.png</t>
+  </si>
+  <si>
+    <t>卡牌-暗影突袭解锁物图标</t>
+  </si>
+  <si>
+    <t>Items/105.png</t>
+  </si>
+  <si>
+    <t>卡牌-生命汲取解锁物图标</t>
+  </si>
+  <si>
+    <t>Items/106.png</t>
+  </si>
+  <si>
+    <t>卡牌-冰霜新星解锁物图标</t>
+  </si>
+  <si>
+    <t>Items/107.png</t>
+  </si>
+  <si>
+    <t>卡牌-狂暴解锁物图标</t>
+  </si>
+  <si>
+    <t>Items/108.png</t>
+  </si>
+  <si>
+    <t>卡牌-群体治疗解锁物图标</t>
+  </si>
+  <si>
+    <t>Items/109.png</t>
+  </si>
+  <si>
+    <t>卡牌-雷霆一击解锁物图标</t>
+  </si>
+  <si>
+    <t>Items/110.png</t>
+  </si>
+  <si>
+    <t>卡牌-混乱诅咒解锁物图标</t>
+  </si>
+  <si>
+    <t>Items/111.png</t>
+  </si>
+  <si>
+    <t>卡牌-不屈意志解锁物图标</t>
+  </si>
+  <si>
+    <t>Items/112.png</t>
+  </si>
+  <si>
+    <t>卡牌-反伤之盾解锁物图标</t>
+  </si>
+  <si>
+    <t>Items/113.png</t>
+  </si>
+  <si>
+    <t>卡牌-圣域防线解锁物图标</t>
+  </si>
+  <si>
+    <t>Items/114.png</t>
+  </si>
+  <si>
+    <t>卡牌-护盾再生解锁物图标</t>
+  </si>
+  <si>
+    <t>Items/115.png</t>
+  </si>
+  <si>
+    <t>卡牌-救赎之光解锁物图标</t>
+  </si>
+  <si>
+    <t>Items/116.png</t>
+  </si>
+  <si>
+    <t>卡牌-血源强化解锁物图标</t>
+  </si>
+  <si>
+    <t>Items/117.png</t>
+  </si>
+  <si>
+    <t>卡牌-吸血之刃解锁物图标</t>
+  </si>
+  <si>
+    <t>Items/118.png</t>
+  </si>
+  <si>
+    <t>卡牌-灾厄之雷解锁物图标</t>
+  </si>
+  <si>
+    <t>Items/119.png</t>
+  </si>
+  <si>
+    <t>卡牌-护甲破碎解锁物图标</t>
+  </si>
+  <si>
+    <t>Items/120.png</t>
+  </si>
+  <si>
+    <t>卡牌-虚弱诅咒解锁物图标</t>
+  </si>
+  <si>
+    <t>Items/121.png</t>
+  </si>
+  <si>
+    <t>卡牌-沉默之符解锁物图标</t>
+  </si>
+  <si>
+    <t>Items/122.png</t>
+  </si>
+  <si>
+    <t>卡牌-嘲讽之声解锁物图标</t>
+  </si>
+  <si>
+    <t>Items/123.png</t>
+  </si>
+  <si>
+    <t>卡牌-剧毒之雾解锁物图标</t>
+  </si>
+  <si>
+    <t>UI/CloudInfo/PlayerInfo</t>
+  </si>
+  <si>
+    <t>角色信息预制体</t>
+  </si>
+  <si>
+    <t>UI/CloudInfo/ItemsInfo</t>
+  </si>
+  <si>
+    <t>仓库信息预制体</t>
+  </si>
+  <si>
+    <t>UI/CloudInfo/TimeInfo</t>
+  </si>
+  <si>
+    <t>存档时间预制体</t>
+  </si>
+  <si>
+    <t>UI/Items/SummonChessStateUI</t>
+  </si>
+  <si>
+    <t>棋子状态UI预制体</t>
+  </si>
+  <si>
+    <t>角色/召唤师/狂战士/狂战士_End</t>
+  </si>
+  <si>
+    <t>狂战士</t>
+  </si>
+  <si>
+    <t>SummonerTable使用|资源暂不存在</t>
+  </si>
+  <si>
+    <t>角色/NPC/勇士End</t>
+  </si>
+  <si>
+    <t>术士</t>
+  </si>
+  <si>
+    <t>混沌</t>
+  </si>
+  <si>
+    <t>德鲁伊</t>
+  </si>
+  <si>
+    <t>Items/DashItem</t>
+  </si>
+  <si>
+    <t>飞雷神道具预制体</t>
+  </si>
+  <si>
+    <t>角色/友方神话角色/后羿</t>
+  </si>
+  <si>
+    <t>棋子-后羿预制体</t>
+  </si>
+  <si>
+    <t>角色/友方神话角色/嫦娥</t>
+  </si>
+  <si>
+    <t>棋子-嫦娥预制体</t>
+  </si>
+  <si>
+    <t>角色/友方神话角色/敌人测试</t>
+  </si>
+  <si>
+    <t>棋子-敌人测试预制体</t>
+  </si>
+  <si>
+    <t>角色/敌方神话生物/邪灵</t>
+  </si>
+  <si>
+    <t>棋子-邪灵预制体</t>
+  </si>
+  <si>
+    <t>角色/敌方神话生物/恶魂</t>
+  </si>
+  <si>
+    <t>棋子-恶魂预制体</t>
+  </si>
+  <si>
+    <t>角色/敌方神话生物/黑暗杨戬</t>
+  </si>
+  <si>
+    <t>棋子-黑暗杨戬预制体</t>
+  </si>
+  <si>
     <t>SummonChessTable使用|资源暂不存在</t>
   </si>
   <si>
-    <t>Chess/邪灵/立绘.png</t>
-  </si>
-  <si>
-    <t>棋子-邪灵图标</t>
-  </si>
-  <si>
-    <t>Chess/恶魂/立绘.png</t>
-  </si>
-  <si>
-    <t>棋子-恶魂图标</t>
-  </si>
-  <si>
-    <t>Buff/1.png</t>
-  </si>
-  <si>
-    <t>灼烧Buff图标</t>
-  </si>
-  <si>
-    <t>Buff/2.png</t>
-  </si>
-  <si>
-    <t>寒霜Buff图标</t>
-  </si>
-  <si>
-    <t>Buff/3.png</t>
-  </si>
-  <si>
-    <t>融化Buff图标</t>
-  </si>
-  <si>
-    <t>Buff/4.png</t>
-  </si>
-  <si>
-    <t>神力增益Buff图标</t>
-  </si>
-  <si>
-    <t>Buff/5.png</t>
-  </si>
-  <si>
-    <t>日落长弓Buff图标</t>
-  </si>
-  <si>
-    <t>Buff/6.png</t>
-  </si>
-  <si>
-    <t>九天玄冰（对敌）Buff图标</t>
-  </si>
-  <si>
-    <t>BuffTable使用|资源暂不存在</t>
-  </si>
-  <si>
-    <t>Buff/7.png</t>
-  </si>
-  <si>
-    <t>腐蚀Buff图标</t>
-  </si>
-  <si>
-    <t>Buff/8.png</t>
-  </si>
-  <si>
-    <t>黑暗狂暴Buff图标</t>
-  </si>
-  <si>
-    <t>Buff/9.png</t>
-  </si>
-  <si>
-    <t>恐惧Buff图标</t>
-  </si>
-  <si>
-    <t>Buff/10.png</t>
-  </si>
-  <si>
-    <t>虚无之躯Buff图标</t>
-  </si>
-  <si>
-    <t>Buff/28.png</t>
-  </si>
-  <si>
-    <t>九天玄冰（自身）Buff图标</t>
-  </si>
-  <si>
-    <t>UI/Icons/Skill_Dash.png</t>
-  </si>
-  <si>
-    <t>飞雷神-角色技能图标</t>
-  </si>
-  <si>
-    <t>UI/Icons/Skill_Heal.png</t>
-  </si>
-  <si>
-    <t>治疗术-角色技能图标</t>
-  </si>
-  <si>
-    <t>UI/Icons/Skill_Bomb.png</t>
-  </si>
-  <si>
-    <t>爆裂弹-角色技能图标</t>
+    <t>角色/敌方神话生物/黑暗哮天犬</t>
+  </si>
+  <si>
+    <t>棋子-黑暗哮天犬预制体</t>
+  </si>
+  <si>
+    <t>角色/测试/靶子</t>
+  </si>
+  <si>
+    <t>棋子-靶子预制体</t>
+  </si>
+  <si>
+    <t>DamagePopup</t>
+  </si>
+  <si>
+    <t>伤害飘字预制体</t>
+  </si>
+  <si>
+    <t>InteractTip</t>
+  </si>
+  <si>
+    <t>交互提示预制体</t>
+  </si>
+  <si>
+    <t>Game/Interact/破损的宝箱</t>
+  </si>
+  <si>
+    <t>破损的宝箱</t>
+  </si>
+  <si>
+    <t>Game/Interact/精致的宝箱</t>
+  </si>
+  <si>
+    <t>精致的宝箱</t>
+  </si>
+  <si>
+    <t>Game/Interact/华丽的宝箱</t>
+  </si>
+  <si>
+    <t>华丽的宝箱</t>
+  </si>
+  <si>
+    <t>Game/Interact/神秘的宝箱</t>
+  </si>
+  <si>
+    <t>神秘的宝箱</t>
+  </si>
+  <si>
+    <t>Enemy/后羿(敌人测试)</t>
+  </si>
+  <si>
+    <t>敌人-测试预制体</t>
+  </si>
+  <si>
+    <t>Enemy/邪灵</t>
+  </si>
+  <si>
+    <t>敌人-邪灵预制体</t>
+  </si>
+  <si>
+    <t>Combat/BattleArena</t>
+  </si>
+  <si>
+    <t>战斗场景预制体</t>
+  </si>
+  <si>
+    <t>SummonChessEffect/HouYi_Skill1</t>
+  </si>
+  <si>
+    <t>后羿技能1特效</t>
+  </si>
+  <si>
+    <t>SummonChessEffect/Projectile_HouYi_Attack</t>
+  </si>
+  <si>
+    <t>后羿普攻子弹</t>
+  </si>
+  <si>
+    <t>SummonChessEffect/Projectile_HouYi_Skill2</t>
+  </si>
+  <si>
+    <t>后羿大招子弹</t>
+  </si>
+  <si>
+    <t>SummonChessEffect/Projectile_ChangE_Attack</t>
+  </si>
+  <si>
+    <t>嫦娥普攻子弹</t>
+  </si>
+  <si>
+    <t>SummonChessEffect/Change_Skill1</t>
+  </si>
+  <si>
+    <t>嫦娥技能一子弹</t>
+  </si>
+  <si>
+    <t>SummonChessEffect/Change_Skill2</t>
+  </si>
+  <si>
+    <t>嫦娥大招法阵预制体</t>
+  </si>
+  <si>
+    <t>SummonChessEffect/Change_Skill2_Projectile</t>
+  </si>
+  <si>
+    <t>嫦娥大招法阵生成的投射物</t>
+  </si>
+  <si>
+    <t>SummonChessEffect/XieLing_Skill1_Effect</t>
+  </si>
+  <si>
+    <t>邪灵技能1特效</t>
+  </si>
+  <si>
+    <t>SummonChessEffect/XieLing_Skill2</t>
+  </si>
+  <si>
+    <t>邪灵技能2法阵预制体</t>
+  </si>
+  <si>
+    <t>SummonChessEffect/Projectile_EvilSpirit_Attack</t>
+  </si>
+  <si>
+    <t>恶魂普攻子弹</t>
+  </si>
+  <si>
+    <t>DamageFloatingTextTable使用|资源暂不存在</t>
+  </si>
+  <si>
+    <t>SummonChessEffect/EvilSpirit_Skill1</t>
+  </si>
+  <si>
+    <t>恶魂技能1特效</t>
+  </si>
+  <si>
+    <t>SummonChessEffect/EvilSpirit_Skill2</t>
+  </si>
+  <si>
+    <t>恶魂大招特效</t>
+  </si>
+  <si>
+    <t>Effect/DamageText/技能伤害</t>
+  </si>
+  <si>
+    <t>技能伤害-飘字音效</t>
+  </si>
+  <si>
+    <t>Effect/DamageText/连击伤害</t>
+  </si>
+  <si>
+    <t>连击伤害-飘字音效</t>
+  </si>
+  <si>
+    <t>Effect/DamageText/反弹伤害</t>
+  </si>
+  <si>
+    <t>反弹伤害-飘字音效</t>
+  </si>
+  <si>
+    <t>Effect/DamageText/吸血效果</t>
+  </si>
+  <si>
+    <t>吸血效果-飘字音效</t>
+  </si>
+  <si>
+    <t>Effect/DamageText/法力消耗</t>
+  </si>
+  <si>
+    <t>法力消耗-飘字音效</t>
+  </si>
+  <si>
+    <t>Effect/DamageText/法力恢复</t>
+  </si>
+  <si>
+    <t>法力恢复-飘字音效</t>
+  </si>
+  <si>
+    <t>Effect/DamageText/免疫提示</t>
+  </si>
+  <si>
+    <t>免疫提示-飘字音效</t>
+  </si>
+  <si>
+    <t>UIEffect/CommonRarity</t>
+  </si>
+  <si>
+    <t>物品稀有度特效-普通</t>
+  </si>
+  <si>
+    <t>UIEffect/UncommonRarity</t>
+  </si>
+  <si>
+    <t>物品稀有度特效-优秀</t>
+  </si>
+  <si>
+    <t>UIEffect/RareRarity</t>
+  </si>
+  <si>
+    <t>物品稀有度特效-稀有</t>
+  </si>
+  <si>
+    <t>UIEffect/EpicRarity</t>
+  </si>
+  <si>
+    <t>物品稀有度特效-史诗</t>
+  </si>
+  <si>
+    <t>UIEffect/LegendaryRarity</t>
+  </si>
+  <si>
+    <t>物品稀有度特效-传说</t>
+  </si>
+  <si>
+    <t>护盾特效</t>
+  </si>
+  <si>
+    <t>StateEffect/Shield</t>
+  </si>
+  <si>
+    <t>护盾受击特效</t>
+  </si>
+  <si>
+    <t>StateEffect/ShieldHit</t>
+  </si>
+  <si>
+    <t>EquipmentTable使用|资源暂不存在</t>
+  </si>
+  <si>
+    <t>Skills/SkillParamRegistry</t>
+  </si>
+  <si>
+    <t>技能参数注册表</t>
+  </si>
+  <si>
+    <t>Buff/2001.png</t>
+  </si>
+  <si>
+    <t>先手·速度爆发图标</t>
+  </si>
+  <si>
+    <t>Buff/2002.png</t>
+  </si>
+  <si>
+    <t>先手·攻击强化图标</t>
+  </si>
+  <si>
+    <t>Buff/2003.png</t>
+  </si>
+  <si>
+    <t>先手·伤害减免图标</t>
+  </si>
+  <si>
+    <t>Buff/2004.png</t>
+  </si>
+  <si>
+    <t>先手·防御加强图标</t>
+  </si>
+  <si>
+    <t>Buff/3001.png</t>
+  </si>
+  <si>
+    <t>偷袭·防御破阵图标</t>
+  </si>
+  <si>
+    <t>Buff/3002.png</t>
+  </si>
+  <si>
+    <t>偷袭·致命眩晕图标</t>
+  </si>
+  <si>
+    <t>Buff/3003.png</t>
+  </si>
+  <si>
+    <t>偷袭·致命流血图标</t>
+  </si>
+  <si>
+    <t>Buff/4001.png</t>
+  </si>
+  <si>
+    <t>战意激昂Buff图标</t>
+  </si>
+  <si>
+    <t>Buff/4002.png</t>
+  </si>
+  <si>
+    <t>狂怒之心Buff图标</t>
+  </si>
+  <si>
+    <t>Buff/4003.png</t>
+  </si>
+  <si>
+    <t>暗影咒体Buff图标</t>
+  </si>
+  <si>
+    <t>Chess/后羿/后羿头像.png</t>
+  </si>
+  <si>
+    <t>棋子后羿头像</t>
+  </si>
+  <si>
+    <t>Chess/嫦娥/嫦娥头像.png</t>
+  </si>
+  <si>
+    <t>棋子嫦娥头像</t>
   </si>
   <si>
     <t>Chess/邪灵/邪灵头像.png</t>
   </si>
   <si>
-    <t>邪灵-敌人头像</t>
+    <t>棋子邪灵头像</t>
   </si>
   <si>
     <t>Chess/恶魂/恶魂头像.png</t>
   </si>
   <si>
-    <t>恶魂-敌人头像</t>
+    <t>棋子恶魂头像</t>
   </si>
   <si>
     <t>Chess/黑暗杨戬/黑暗杨戬头像.png</t>
   </si>
   <si>
-    <t>黑暗杨戬-敌人头像</t>
-  </si>
-  <si>
-    <t>Summoner/Skill/狂怒之心技能.png</t>
-  </si>
-  <si>
-    <t>狂怒之心-召唤师技能图标</t>
-  </si>
-  <si>
-    <t>Summoner/Skill/战意激昂技能.png</t>
-  </si>
-  <si>
-    <t>战意激昂-召唤师技能图标</t>
-  </si>
-  <si>
-    <t>Summoner/Skill/王者号令技能.png</t>
-  </si>
-  <si>
-    <t>王者号令-召唤师技能图标</t>
-  </si>
-  <si>
-    <t>Summoner/Skill/钢铁洪流技能.png</t>
-  </si>
-  <si>
-    <t>钢铁洪流-召唤师技能图标</t>
-  </si>
-  <si>
-    <t>Summoner/Skill/天灾降临技能.png</t>
-  </si>
-  <si>
-    <t>天灾降临-召唤师技能图标</t>
-  </si>
-  <si>
-    <t>Summoner/Skill/寂灭斩技能.png</t>
-  </si>
-  <si>
-    <t>寂灭斩-召唤师技能图标</t>
-  </si>
-  <si>
-    <t>Summoner/Skill/孤影技能.png</t>
-  </si>
-  <si>
-    <t>孤影-召唤师技能图标</t>
-  </si>
-  <si>
-    <t>Summoner/Skill/裁决之刻技能.png</t>
-  </si>
-  <si>
-    <t>裁决之刻-召唤师技能图标</t>
-  </si>
-  <si>
-    <t>Summoner/Skill/暗影咒体技能.png</t>
-  </si>
-  <si>
-    <t>暗影咒体-召唤师技能图标</t>
-  </si>
-  <si>
-    <t>Summoner/Skill/生命虹吸技能.png</t>
-  </si>
-  <si>
-    <t>生命虹吸-召唤师技能图标</t>
-  </si>
-  <si>
-    <t>SummonChessSkillTable使用|资源暂不存在</t>
-  </si>
-  <si>
-    <t>Skill/1.png</t>
-  </si>
-  <si>
-    <t>日落长弓-后羿技能图标</t>
-  </si>
-  <si>
-    <t>Skill/2.png</t>
-  </si>
-  <si>
-    <t>后羿普攻-后羿技能图标</t>
-  </si>
-  <si>
-    <t>Skill/3.png</t>
-  </si>
-  <si>
-    <t>神力-后羿技能图标</t>
-  </si>
-  <si>
-    <t>Skill/4.png</t>
-  </si>
-  <si>
-    <t>日陨-后羿技能图标</t>
-  </si>
-  <si>
-    <t>Skill/5.png</t>
-  </si>
-  <si>
-    <t>九天玄冰-嫦娥技能图标</t>
-  </si>
-  <si>
-    <t>Skill/6.png</t>
-  </si>
-  <si>
-    <t>嫦娥普攻-嫦娥技能图标</t>
-  </si>
-  <si>
-    <t>Skill/7.png</t>
-  </si>
-  <si>
-    <t>朔月飞轮-嫦娥技能图标</t>
-  </si>
-  <si>
-    <t>Skill/8.png</t>
-  </si>
-  <si>
-    <t>月华天倾-嫦娥技能图标</t>
-  </si>
-  <si>
-    <t>Skill/31.png</t>
-  </si>
-  <si>
-    <t>黑暗侵染-邪灵技能图标</t>
-  </si>
-  <si>
-    <t>Skill/32.png</t>
-  </si>
-  <si>
-    <t>邪灵普攻-邪灵技能图标</t>
-  </si>
-  <si>
-    <t>Skill/33.png</t>
-  </si>
-  <si>
-    <t>污染斩击-邪灵技能图标</t>
-  </si>
-  <si>
-    <t>Skill/34.png</t>
-  </si>
-  <si>
-    <t>腐蚀法阵-邪灵技能图标</t>
-  </si>
-  <si>
-    <t>Skill/41.png</t>
-  </si>
-  <si>
-    <t>虚无之躯-恶魂技能图标</t>
-  </si>
-  <si>
-    <t>Skill/42.png</t>
-  </si>
-  <si>
-    <t>恶魂普攻-恶魂技能图标</t>
-  </si>
-  <si>
-    <t>Skill/43.png</t>
-  </si>
-  <si>
-    <t>心灵扭曲-恶魂技能图标</t>
-  </si>
-  <si>
-    <t>Skill/44.png</t>
-  </si>
-  <si>
-    <t>邪念潮涌-恶魂技能图标</t>
-  </si>
-  <si>
-    <t>Skill/51.png</t>
-  </si>
-  <si>
-    <t>黑暗神力-黑暗杨戬技能图标</t>
-  </si>
-  <si>
-    <t>Skill/52.png</t>
-  </si>
-  <si>
-    <t>暗戟横扫-黑暗杨戬技能图标</t>
-  </si>
-  <si>
-    <t>Skill/53.png</t>
-  </si>
-  <si>
-    <t>天威圣戟·黑暗-黑暗杨戬技能图标</t>
-  </si>
-  <si>
-    <t>Skill/54.png</t>
-  </si>
-  <si>
-    <t>三眼天火-黑暗杨戬技能图标</t>
-  </si>
-  <si>
-    <t>Skill/55.png</t>
-  </si>
-  <si>
-    <t>堕落劈山-黑暗杨戬技能图标</t>
-  </si>
-  <si>
-    <t>Skill/56.png</t>
-  </si>
-  <si>
-    <t>撕咬-黑暗哮天犬技能图标</t>
-  </si>
-  <si>
-    <t>Items/1.png</t>
-  </si>
-  <si>
-    <t>钱包图标</t>
-  </si>
-  <si>
-    <t>Items/2.png</t>
-  </si>
-  <si>
-    <t>生命药水图标</t>
-  </si>
-  <si>
-    <t>Items/3.png</t>
-  </si>
-  <si>
-    <t>魔法药水图标</t>
-  </si>
-  <si>
-    <t>Items/4.png</t>
-  </si>
-  <si>
-    <t>经验宝石图标</t>
-  </si>
-  <si>
-    <t>Items/5.png</t>
-  </si>
-  <si>
-    <t>神秘钥匙图标</t>
-  </si>
-  <si>
-    <t>Items/6.png</t>
-  </si>
-  <si>
-    <t>古老卷轴图标</t>
-  </si>
-  <si>
-    <t>Items/7.png</t>
-  </si>
-  <si>
-    <t>八尺琼勾玉图标</t>
-  </si>
-  <si>
-    <t>Items/8.png</t>
-  </si>
-  <si>
-    <t>天丛云剑图标</t>
-  </si>
-  <si>
-    <t>Items/9.png</t>
-  </si>
-  <si>
-    <t>八咫镜图标</t>
-  </si>
-  <si>
-    <t>Items/10.png</t>
-  </si>
-  <si>
-    <t>石中剑图标</t>
-  </si>
-  <si>
-    <t>Items/11.png</t>
-  </si>
-  <si>
-    <t>龙鳞铠甲图标</t>
-  </si>
-  <si>
-    <t>Items/12.png</t>
-  </si>
-  <si>
-    <t>精灵之戒图标</t>
-  </si>
-  <si>
-    <t>Items/13.png</t>
-  </si>
-  <si>
-    <t>月华玉璧图标</t>
-  </si>
-  <si>
-    <t>Items/14.png</t>
-  </si>
-  <si>
-    <t>太阴弦月弓图标</t>
-  </si>
-  <si>
-    <t>Items/15.png</t>
-  </si>
-  <si>
-    <t>月轮镜图标</t>
-  </si>
-  <si>
-    <t>Items/16.png</t>
-  </si>
-  <si>
-    <t>炎魔之心图标</t>
-  </si>
-  <si>
-    <t>Items/17.png</t>
-  </si>
-  <si>
-    <t>炎魔之冠图标</t>
-  </si>
-  <si>
-    <t>Items/18.png</t>
-  </si>
-  <si>
-    <t>炎魔之剑图标</t>
-  </si>
-  <si>
-    <t>Items/19.png</t>
-  </si>
-  <si>
-    <t>古剑·樱花落图标</t>
-  </si>
-  <si>
-    <t>Items/20.png</t>
-  </si>
-  <si>
-    <t>暗影斗篷图标</t>
-  </si>
-  <si>
-    <t>Items/21.png</t>
-  </si>
-  <si>
-    <t>圣光铠甲图标</t>
-  </si>
-  <si>
-    <t>Items/22.png</t>
-  </si>
-  <si>
-    <t>古墓盗贼手套图标</t>
-  </si>
-  <si>
-    <t>Items/23.png</t>
-  </si>
-  <si>
-    <t>冰晶靴图标</t>
-  </si>
-  <si>
-    <t>Items/24.png</t>
-  </si>
-  <si>
-    <t>风暴法杖图标</t>
-  </si>
-  <si>
-    <t>Items/100.png</t>
-  </si>
-  <si>
-    <t>卡牌-神圣庇护解锁物图标</t>
-  </si>
-  <si>
-    <t>Items/101.png</t>
-  </si>
-  <si>
-    <t>卡牌-烈焰风暴解锁物图标</t>
-  </si>
-  <si>
-    <t>Items/102.png</t>
-  </si>
-  <si>
-    <t>卡牌-时间回溯解锁物图标</t>
-  </si>
-  <si>
-    <t>Items/103.png</t>
-  </si>
-  <si>
-    <t>卡牌-战争号角解锁物图标</t>
-  </si>
-  <si>
-    <t>Items/104.png</t>
-  </si>
-  <si>
-    <t>卡牌-暗影突袭解锁物图标</t>
-  </si>
-  <si>
-    <t>Items/105.png</t>
-  </si>
-  <si>
-    <t>卡牌-生命汲取解锁物图标</t>
-  </si>
-  <si>
-    <t>Items/106.png</t>
-  </si>
-  <si>
-    <t>卡牌-冰霜新星解锁物图标</t>
-  </si>
-  <si>
-    <t>Items/107.png</t>
-  </si>
-  <si>
-    <t>卡牌-狂暴解锁物图标</t>
-  </si>
-  <si>
-    <t>Items/108.png</t>
-  </si>
-  <si>
-    <t>卡牌-群体治疗解锁物图标</t>
-  </si>
-  <si>
-    <t>Items/109.png</t>
-  </si>
-  <si>
-    <t>卡牌-雷霆一击解锁物图标</t>
-  </si>
-  <si>
-    <t>Items/110.png</t>
-  </si>
-  <si>
-    <t>卡牌-混乱诅咒解锁物图标</t>
-  </si>
-  <si>
-    <t>Items/111.png</t>
-  </si>
-  <si>
-    <t>卡牌-不屈意志解锁物图标</t>
-  </si>
-  <si>
-    <t>Items/112.png</t>
-  </si>
-  <si>
-    <t>卡牌-反伤之盾解锁物图标</t>
-  </si>
-  <si>
-    <t>Items/113.png</t>
-  </si>
-  <si>
-    <t>卡牌-圣域防线解锁物图标</t>
-  </si>
-  <si>
-    <t>Items/114.png</t>
-  </si>
-  <si>
-    <t>卡牌-护盾再生解锁物图标</t>
-  </si>
-  <si>
-    <t>Items/115.png</t>
-  </si>
-  <si>
-    <t>卡牌-救赎之光解锁物图标</t>
-  </si>
-  <si>
-    <t>Items/116.png</t>
-  </si>
-  <si>
-    <t>卡牌-血源强化解锁物图标</t>
-  </si>
-  <si>
-    <t>Items/117.png</t>
-  </si>
-  <si>
-    <t>卡牌-吸血之刃解锁物图标</t>
-  </si>
-  <si>
-    <t>Items/118.png</t>
-  </si>
-  <si>
-    <t>卡牌-灾厄之雷解锁物图标</t>
-  </si>
-  <si>
-    <t>Items/119.png</t>
-  </si>
-  <si>
-    <t>卡牌-护甲破碎解锁物图标</t>
-  </si>
-  <si>
-    <t>Items/120.png</t>
-  </si>
-  <si>
-    <t>卡牌-虚弱诅咒解锁物图标</t>
-  </si>
-  <si>
-    <t>Items/121.png</t>
-  </si>
-  <si>
-    <t>卡牌-沉默之符解锁物图标</t>
-  </si>
-  <si>
-    <t>Items/122.png</t>
-  </si>
-  <si>
-    <t>卡牌-嘲讽之声解锁物图标</t>
-  </si>
-  <si>
-    <t>Items/123.png</t>
-  </si>
-  <si>
-    <t>卡牌-剧毒之雾解锁物图标</t>
-  </si>
-  <si>
-    <t>UI/CloudInfo/PlayerInfo</t>
-  </si>
-  <si>
-    <t>角色信息预制体</t>
-  </si>
-  <si>
-    <t>UI/CloudInfo/ItemsInfo</t>
-  </si>
-  <si>
-    <t>仓库信息预制体</t>
-  </si>
-  <si>
-    <t>UI/CloudInfo/TimeInfo</t>
-  </si>
-  <si>
-    <t>存档时间预制体</t>
-  </si>
-  <si>
-    <t>UI/Items/SummonChessStateUI</t>
-  </si>
-  <si>
-    <t>棋子状态UI预制体</t>
-  </si>
-  <si>
-    <t>角色/召唤师/狂战士/狂战士_End</t>
-  </si>
-  <si>
-    <t>狂战士</t>
-  </si>
-  <si>
-    <t>SummonerTable使用|资源暂不存在</t>
-  </si>
-  <si>
-    <t>角色/NPC/勇士End</t>
-  </si>
-  <si>
-    <t>术士</t>
-  </si>
-  <si>
-    <t>混沌</t>
-  </si>
-  <si>
-    <t>德鲁伊</t>
-  </si>
-  <si>
-    <t>Items/DashItem</t>
-  </si>
-  <si>
-    <t>飞雷神道具预制体</t>
-  </si>
-  <si>
-    <t>角色/友方神话角色/后羿</t>
-  </si>
-  <si>
-    <t>棋子-后羿预制体</t>
-  </si>
-  <si>
-    <t>角色/友方神话角色/嫦娥</t>
-  </si>
-  <si>
-    <t>棋子-嫦娥预制体</t>
-  </si>
-  <si>
-    <t>角色/友方神话角色/敌人测试</t>
-  </si>
-  <si>
-    <t>棋子-敌人测试预制体</t>
-  </si>
-  <si>
-    <t>角色/敌方神话生物/邪灵</t>
-  </si>
-  <si>
-    <t>棋子-邪灵预制体</t>
-  </si>
-  <si>
-    <t>角色/敌方神话生物/恶魂</t>
-  </si>
-  <si>
-    <t>棋子-恶魂预制体</t>
-  </si>
-  <si>
-    <t>角色/敌方神话生物/黑暗杨戬</t>
-  </si>
-  <si>
-    <t>棋子-黑暗杨戬预制体</t>
-  </si>
-  <si>
-    <t>角色/敌方神话生物/黑暗哮天犬</t>
-  </si>
-  <si>
-    <t>棋子-黑暗哮天犬预制体</t>
-  </si>
-  <si>
-    <t>角色/测试/靶子</t>
-  </si>
-  <si>
-    <t>棋子-靶子预制体</t>
-  </si>
-  <si>
-    <t>DamagePopup</t>
-  </si>
-  <si>
-    <t>伤害飘字预制体</t>
-  </si>
-  <si>
-    <t>InteractTip</t>
-  </si>
-  <si>
-    <t>交互提示预制体</t>
-  </si>
-  <si>
-    <t>Game/Interact/破损的宝箱</t>
-  </si>
-  <si>
-    <t>破损的宝箱</t>
-  </si>
-  <si>
-    <t>Game/Interact/精致的宝箱</t>
-  </si>
-  <si>
-    <t>精致的宝箱</t>
-  </si>
-  <si>
-    <t>Game/Interact/华丽的宝箱</t>
-  </si>
-  <si>
-    <t>华丽的宝箱</t>
-  </si>
-  <si>
-    <t>Game/Interact/神秘的宝箱</t>
-  </si>
-  <si>
-    <t>神秘的宝箱</t>
-  </si>
-  <si>
-    <t>Enemy/后羿(敌人测试)</t>
-  </si>
-  <si>
-    <t>敌人-测试预制体</t>
-  </si>
-  <si>
-    <t>Enemy/邪灵</t>
-  </si>
-  <si>
-    <t>敌人-邪灵预制体</t>
-  </si>
-  <si>
-    <t>Combat/BattleArena</t>
-  </si>
-  <si>
-    <t>战斗场景预制体</t>
-  </si>
-  <si>
-    <t>SummonChessEffect/HouYi_Skill1</t>
-  </si>
-  <si>
-    <t>后羿技能1特效</t>
-  </si>
-  <si>
-    <t>SummonChessEffect/Projectile_HouYi_Attack</t>
-  </si>
-  <si>
-    <t>后羿普攻子弹</t>
-  </si>
-  <si>
-    <t>SummonChessEffect/Projectile_HouYi_Skill2</t>
-  </si>
-  <si>
-    <t>后羿大招子弹</t>
-  </si>
-  <si>
-    <t>SummonChessEffect/Projectile_ChangE_Attack</t>
-  </si>
-  <si>
-    <t>嫦娥普攻子弹</t>
-  </si>
-  <si>
-    <t>SummonChessEffect/Change_Skill1</t>
-  </si>
-  <si>
-    <t>嫦娥技能一子弹</t>
-  </si>
-  <si>
-    <t>SummonChessEffect/Change_Skill2</t>
-  </si>
-  <si>
-    <t>嫦娥大招法阵预制体</t>
-  </si>
-  <si>
-    <t>SummonChessEffect/Change_Skill2_Projectile</t>
-  </si>
-  <si>
-    <t>嫦娥大招法阵生成的投射物</t>
-  </si>
-  <si>
-    <t>SummonChessEffect/XieLing_Skill1_Effect</t>
-  </si>
-  <si>
-    <t>邪灵技能1特效</t>
-  </si>
-  <si>
-    <t>SummonChessEffect/XieLing_Skill2</t>
-  </si>
-  <si>
-    <t>邪灵技能2法阵预制体</t>
-  </si>
-  <si>
-    <t>SummonChessEffect/Projectile_EvilSpirit_Attack</t>
-  </si>
-  <si>
-    <t>恶魂普攻子弹</t>
-  </si>
-  <si>
-    <t>DamageFloatingTextTable使用|资源暂不存在</t>
-  </si>
-  <si>
-    <t>SummonChessEffect/EvilSpirit_Skill1</t>
-  </si>
-  <si>
-    <t>恶魂技能1特效</t>
-  </si>
-  <si>
-    <t>SummonChessEffect/EvilSpirit_Skill2</t>
-  </si>
-  <si>
-    <t>恶魂大招特效</t>
-  </si>
-  <si>
-    <t>Effect/DamageText/技能伤害</t>
-  </si>
-  <si>
-    <t>技能伤害-飘字音效</t>
-  </si>
-  <si>
-    <t>Effect/DamageText/连击伤害</t>
-  </si>
-  <si>
-    <t>连击伤害-飘字音效</t>
-  </si>
-  <si>
-    <t>Effect/DamageText/反弹伤害</t>
-  </si>
-  <si>
-    <t>反弹伤害-飘字音效</t>
-  </si>
-  <si>
-    <t>Effect/DamageText/吸血效果</t>
-  </si>
-  <si>
-    <t>吸血效果-飘字音效</t>
-  </si>
-  <si>
-    <t>Effect/DamageText/法力消耗</t>
-  </si>
-  <si>
-    <t>法力消耗-飘字音效</t>
-  </si>
-  <si>
-    <t>Effect/DamageText/法力恢复</t>
-  </si>
-  <si>
-    <t>法力恢复-飘字音效</t>
-  </si>
-  <si>
-    <t>Effect/DamageText/免疫提示</t>
-  </si>
-  <si>
-    <t>免疫提示-飘字音效</t>
-  </si>
-  <si>
-    <t>UIEffect/CommonRarity</t>
-  </si>
-  <si>
-    <t>物品稀有度特效-普通</t>
-  </si>
-  <si>
-    <t>UIEffect/UncommonRarity</t>
-  </si>
-  <si>
-    <t>物品稀有度特效-优秀</t>
-  </si>
-  <si>
-    <t>UIEffect/RareRarity</t>
-  </si>
-  <si>
-    <t>物品稀有度特效-稀有</t>
-  </si>
-  <si>
-    <t>UIEffect/EpicRarity</t>
-  </si>
-  <si>
-    <t>物品稀有度特效-史诗</t>
-  </si>
-  <si>
-    <t>UIEffect/LegendaryRarity</t>
-  </si>
-  <si>
-    <t>物品稀有度特效-传说</t>
-  </si>
-  <si>
-    <t>护盾特效</t>
-  </si>
-  <si>
-    <t>StateEffect/Shield</t>
-  </si>
-  <si>
-    <t>护盾受击特效</t>
-  </si>
-  <si>
-    <t>StateEffect/ShieldHit</t>
-  </si>
-  <si>
-    <t>EquipmentTable使用|资源暂不存在</t>
-  </si>
-  <si>
-    <t>Skills/SkillParamRegistry</t>
-  </si>
-  <si>
-    <t>技能参数注册表</t>
-  </si>
-  <si>
-    <t>Buff/2001.png</t>
-  </si>
-  <si>
-    <t>先手·速度爆发图标</t>
-  </si>
-  <si>
-    <t>Buff/2002.png</t>
-  </si>
-  <si>
-    <t>先手·攻击强化图标</t>
-  </si>
-  <si>
-    <t>Buff/2003.png</t>
-  </si>
-  <si>
-    <t>先手·伤害减免图标</t>
-  </si>
-  <si>
-    <t>Buff/2004.png</t>
-  </si>
-  <si>
-    <t>先手·防御加强图标</t>
-  </si>
-  <si>
-    <t>Buff/3001.png</t>
-  </si>
-  <si>
-    <t>偷袭·防御破阵图标</t>
-  </si>
-  <si>
-    <t>Buff/3002.png</t>
-  </si>
-  <si>
-    <t>偷袭·致命眩晕图标</t>
-  </si>
-  <si>
-    <t>Buff/3003.png</t>
-  </si>
-  <si>
-    <t>偷袭·致命流血图标</t>
-  </si>
-  <si>
-    <t>Buff/4001.png</t>
-  </si>
-  <si>
-    <t>战意激昂Buff图标</t>
-  </si>
-  <si>
-    <t>Buff/4002.png</t>
-  </si>
-  <si>
-    <t>狂怒之心Buff图标</t>
-  </si>
-  <si>
-    <t>Buff/4003.png</t>
-  </si>
-  <si>
-    <t>暗影咒体Buff图标</t>
-  </si>
-  <si>
-    <t>EnemyEntityTable使用|资源暂不存在</t>
-  </si>
-  <si>
-    <t>Enemy/默认.png</t>
-  </si>
-  <si>
-    <t>敌人图标</t>
-  </si>
-  <si>
-    <t>Chess/后羿/后羿头像.png</t>
-  </si>
-  <si>
-    <t>棋子后羿头像</t>
-  </si>
-  <si>
-    <t>Chess/嫦娥/嫦娥头像.png</t>
-  </si>
-  <si>
-    <t>棋子嫦娥头像</t>
-  </si>
-  <si>
-    <t>棋子邪灵头像</t>
-  </si>
-  <si>
-    <t>棋子恶魂头像</t>
-  </si>
-  <si>
     <t>棋子黑暗杨戬头像</t>
   </si>
   <si>
@@ -1535,6 +1568,12 @@
     <t>战士-职业羁绊图标</t>
   </si>
   <si>
+    <t>Card/Component/1.png</t>
+  </si>
+  <si>
+    <t>卡牌框-稀有度1</t>
+  </si>
+  <si>
     <t>Card/Component/2.png</t>
   </si>
   <si>
@@ -1553,6 +1592,12 @@
     <t>卡牌框-稀有度4</t>
   </si>
   <si>
+    <t>Card/Component/Bg-1.png</t>
+  </si>
+  <si>
+    <t>卡片背景-稀有度1</t>
+  </si>
+  <si>
     <t>Card/Component/Bg-2.png</t>
   </si>
   <si>
@@ -1571,22 +1616,28 @@
     <t>卡片背景-稀有度4</t>
   </si>
   <si>
-    <t>Card/Component/Mask/Mask2.png</t>
-  </si>
-  <si>
-    <t>名字背景-稀有度2</t>
-  </si>
-  <si>
-    <t>Card/Component/Mask/Mask3.png</t>
-  </si>
-  <si>
-    <t>名字背景-稀有度3</t>
-  </si>
-  <si>
-    <t>Card/Component/Mask/Mask4.png</t>
-  </si>
-  <si>
-    <t>名字背景-稀有度4</t>
+    <t>Card/Component/装饰/宝石_稀有.png</t>
+  </si>
+  <si>
+    <t>宝石装饰-稀有</t>
+  </si>
+  <si>
+    <t>Card/Component/装饰/宝石_史诗.png</t>
+  </si>
+  <si>
+    <t>宝石装饰-史诗</t>
+  </si>
+  <si>
+    <t>Card/Component/装饰/宝石_传奇.png</t>
+  </si>
+  <si>
+    <t>宝石装饰-传奇</t>
+  </si>
+  <si>
+    <t>Card/Component/装饰/宝石_神话.png</t>
+  </si>
+  <si>
+    <t>宝石装饰-神话</t>
   </si>
   <si>
     <t>CardTable使用|资源暂不存在</t>
@@ -3451,8 +3502,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F404"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <dimension ref="A1:F411"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="21" customWidth="1"/>
@@ -3509,7 +3560,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" ht="81" spans="1:6">
+    <row r="4" ht="86.4" spans="1:6">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -3676,7 +3727,7 @@
     <row r="14" ht="15" customHeight="1" spans="1:6">
       <c r="A14" s="1"/>
       <c r="B14" s="1">
-        <v>1101</v>
+        <v>1010</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1">
@@ -3692,7 +3743,7 @@
     <row r="15" ht="15" customHeight="1" spans="1:6">
       <c r="A15" s="1"/>
       <c r="B15" s="1">
-        <v>1102</v>
+        <v>1011</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1">
@@ -3708,7 +3759,7 @@
     <row r="16" ht="15" customHeight="1" spans="1:6">
       <c r="A16" s="1"/>
       <c r="B16" s="1">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1">
@@ -3724,7 +3775,7 @@
     <row r="17" ht="15" customHeight="1" spans="1:6">
       <c r="A17" s="1"/>
       <c r="B17" s="1">
-        <v>1104</v>
+        <v>1102</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="1">
@@ -3740,7 +3791,7 @@
     <row r="18" ht="15" customHeight="1" spans="1:6">
       <c r="A18" s="1"/>
       <c r="B18" s="1">
-        <v>1105</v>
+        <v>1103</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="1">
@@ -3756,7 +3807,7 @@
     <row r="19" ht="15" customHeight="1" spans="1:6">
       <c r="A19" s="1"/>
       <c r="B19" s="1">
-        <v>1106</v>
+        <v>1104</v>
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="1">
@@ -3772,7 +3823,7 @@
     <row r="20" ht="15" customHeight="1" spans="1:6">
       <c r="A20" s="1"/>
       <c r="B20" s="1">
-        <v>1107</v>
+        <v>1105</v>
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="1">
@@ -3788,7 +3839,7 @@
     <row r="21" ht="15" customHeight="1" spans="1:6">
       <c r="A21" s="1"/>
       <c r="B21" s="1">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="1">
@@ -3804,7 +3855,7 @@
     <row r="22" ht="15" customHeight="1" spans="1:6">
       <c r="A22" s="1"/>
       <c r="B22" s="1">
-        <v>1155</v>
+        <v>1107</v>
       </c>
       <c r="C22" s="1"/>
       <c r="D22" s="1">
@@ -3820,7 +3871,7 @@
     <row r="23" ht="15" customHeight="1" spans="1:6">
       <c r="A23" s="1"/>
       <c r="B23" s="1">
-        <v>1156</v>
+        <v>1108</v>
       </c>
       <c r="C23" s="1"/>
       <c r="D23" s="1">
@@ -3836,7 +3887,7 @@
     <row r="24" ht="15" customHeight="1" spans="1:6">
       <c r="A24" s="1"/>
       <c r="B24" s="1">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="C24" s="1"/>
       <c r="D24" s="1">
@@ -3852,7 +3903,7 @@
     <row r="25" ht="15" customHeight="1" spans="1:6">
       <c r="A25" s="1"/>
       <c r="B25" s="1">
-        <v>1158</v>
+        <v>1156</v>
       </c>
       <c r="C25" s="1"/>
       <c r="D25" s="1">
@@ -3868,7 +3919,7 @@
     <row r="26" ht="15" customHeight="1" spans="1:6">
       <c r="A26" s="1"/>
       <c r="B26" s="1">
-        <v>1201</v>
+        <v>1157</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="1">
@@ -3884,7 +3935,7 @@
     <row r="27" ht="15" customHeight="1" spans="1:6">
       <c r="A27" s="1"/>
       <c r="B27" s="1">
-        <v>1202</v>
+        <v>1158</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="1">
@@ -3900,7 +3951,7 @@
     <row r="28" ht="15" customHeight="1" spans="1:6">
       <c r="A28" s="1"/>
       <c r="B28" s="1">
-        <v>1203</v>
+        <v>1201</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="1">
@@ -3916,7 +3967,7 @@
     <row r="29" ht="15" customHeight="1" spans="1:6">
       <c r="A29" s="1"/>
       <c r="B29" s="1">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="1">
@@ -3932,7 +3983,7 @@
     <row r="30" ht="15" customHeight="1" spans="1:6">
       <c r="A30" s="1"/>
       <c r="B30" s="1">
-        <v>1205</v>
+        <v>1203</v>
       </c>
       <c r="C30" s="1"/>
       <c r="D30" s="1">
@@ -3948,7 +3999,7 @@
     <row r="31" ht="15" customHeight="1" spans="1:6">
       <c r="A31" s="1"/>
       <c r="B31" s="1">
-        <v>1206</v>
+        <v>1204</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="1">
@@ -3964,7 +4015,7 @@
     <row r="32" ht="15" customHeight="1" spans="1:6">
       <c r="A32" s="1"/>
       <c r="B32" s="1">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="C32" s="1"/>
       <c r="D32" s="1">
@@ -3980,7 +4031,7 @@
     <row r="33" ht="15" customHeight="1" spans="1:6">
       <c r="A33" s="1"/>
       <c r="B33" s="1">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="1">
@@ -3996,7 +4047,7 @@
     <row r="34" ht="15" customHeight="1" spans="1:6">
       <c r="A34" s="1"/>
       <c r="B34" s="1">
-        <v>1209</v>
+        <v>1207</v>
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="1">
@@ -4012,7 +4063,7 @@
     <row r="35" ht="15" customHeight="1" spans="1:6">
       <c r="A35" s="1"/>
       <c r="B35" s="1">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="C35" s="1"/>
       <c r="D35" s="1">
@@ -4028,7 +4079,7 @@
     <row r="36" ht="15" customHeight="1" spans="1:6">
       <c r="A36" s="1"/>
       <c r="B36" s="1">
-        <v>1211</v>
+        <v>1209</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1">
@@ -4044,7 +4095,7 @@
     <row r="37" ht="15" customHeight="1" spans="1:6">
       <c r="A37" s="1"/>
       <c r="B37" s="1">
-        <v>1212</v>
+        <v>1210</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1">
@@ -4060,7 +4111,7 @@
     <row r="38" ht="15" customHeight="1" spans="1:6">
       <c r="A38" s="1"/>
       <c r="B38" s="1">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1">
@@ -4076,7 +4127,7 @@
     <row r="39" ht="15" customHeight="1" spans="1:6">
       <c r="A39" s="1"/>
       <c r="B39" s="1">
-        <v>1214</v>
+        <v>1212</v>
       </c>
       <c r="C39" s="1"/>
       <c r="D39" s="1">
@@ -4092,7 +4143,7 @@
     <row r="40" ht="15" customHeight="1" spans="1:6">
       <c r="A40" s="1"/>
       <c r="B40" s="1">
-        <v>1215</v>
+        <v>1213</v>
       </c>
       <c r="C40" s="1"/>
       <c r="D40" s="1">
@@ -4108,7 +4159,7 @@
     <row r="41" ht="15" customHeight="1" spans="1:6">
       <c r="A41" s="1"/>
       <c r="B41" s="1">
-        <v>1216</v>
+        <v>1214</v>
       </c>
       <c r="C41" s="1"/>
       <c r="D41" s="1">
@@ -4124,7 +4175,7 @@
     <row r="42" ht="15" customHeight="1" spans="1:6">
       <c r="A42" s="1"/>
       <c r="B42" s="1">
-        <v>1217</v>
+        <v>1215</v>
       </c>
       <c r="C42" s="1"/>
       <c r="D42" s="1">
@@ -4140,7 +4191,7 @@
     <row r="43" ht="15" customHeight="1" spans="1:6">
       <c r="A43" s="1"/>
       <c r="B43" s="1">
-        <v>1218</v>
+        <v>1216</v>
       </c>
       <c r="C43" s="1"/>
       <c r="D43" s="1">
@@ -4156,7 +4207,7 @@
     <row r="44" ht="15" customHeight="1" spans="1:6">
       <c r="A44" s="1"/>
       <c r="B44" s="1">
-        <v>1219</v>
+        <v>1217</v>
       </c>
       <c r="C44" s="1"/>
       <c r="D44" s="1">
@@ -4172,7 +4223,7 @@
     <row r="45" ht="15" customHeight="1" spans="1:6">
       <c r="A45" s="1"/>
       <c r="B45" s="1">
-        <v>1220</v>
+        <v>1218</v>
       </c>
       <c r="C45" s="1"/>
       <c r="D45" s="1">
@@ -4188,7 +4239,7 @@
     <row r="46" ht="15" customHeight="1" spans="1:6">
       <c r="A46" s="1"/>
       <c r="B46" s="1">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="C46" s="1"/>
       <c r="D46" s="1">
@@ -4204,7 +4255,7 @@
     <row r="47" ht="15" customHeight="1" spans="1:6">
       <c r="A47" s="1"/>
       <c r="B47" s="1">
-        <v>1222</v>
+        <v>1220</v>
       </c>
       <c r="C47" s="1"/>
       <c r="D47" s="1">
@@ -4220,7 +4271,7 @@
     <row r="48" ht="15" customHeight="1" spans="1:6">
       <c r="A48" s="1"/>
       <c r="B48" s="1">
-        <v>1223</v>
+        <v>1221</v>
       </c>
       <c r="C48" s="1"/>
       <c r="D48" s="1">
@@ -4236,7 +4287,7 @@
     <row r="49" ht="15" customHeight="1" spans="1:6">
       <c r="A49" s="1"/>
       <c r="B49" s="1">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="C49" s="1"/>
       <c r="D49" s="1">
@@ -4252,7 +4303,7 @@
     <row r="50" ht="15" customHeight="1" spans="1:6">
       <c r="A50" s="1"/>
       <c r="B50" s="1">
-        <v>1225</v>
+        <v>1223</v>
       </c>
       <c r="C50" s="1"/>
       <c r="D50" s="1">
@@ -4268,7 +4319,7 @@
     <row r="51" ht="15" customHeight="1" spans="1:6">
       <c r="A51" s="1"/>
       <c r="B51" s="1">
-        <v>1301</v>
+        <v>1224</v>
       </c>
       <c r="C51" s="1"/>
       <c r="D51" s="1">
@@ -4284,7 +4335,7 @@
     <row r="52" ht="15" customHeight="1" spans="1:6">
       <c r="A52" s="1"/>
       <c r="B52" s="1">
-        <v>1304</v>
+        <v>1225</v>
       </c>
       <c r="C52" s="1"/>
       <c r="D52" s="1">
@@ -4300,343 +4351,341 @@
     <row r="53" ht="15" customHeight="1" spans="1:6">
       <c r="A53" s="1"/>
       <c r="B53" s="1">
-        <v>1310</v>
-      </c>
-      <c r="C53" s="1" t="s">
+        <v>1301</v>
+      </c>
+      <c r="C53" s="1"/>
+      <c r="D53" s="1">
+        <v>1</v>
+      </c>
+      <c r="E53" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="D53" s="1">
-        <v>1</v>
-      </c>
-      <c r="E53" s="1" t="s">
+      <c r="F53" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="F53" s="1" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="54" ht="15" customHeight="1" spans="1:6">
       <c r="A54" s="1"/>
       <c r="B54" s="1">
-        <v>1311</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>109</v>
-      </c>
+        <v>1304</v>
+      </c>
+      <c r="C54" s="1"/>
       <c r="D54" s="1">
         <v>1</v>
       </c>
       <c r="E54" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F54" s="1" t="s">
         <v>112</v>
-      </c>
-      <c r="F54" s="1" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="55" ht="15" customHeight="1" spans="1:6">
       <c r="A55" s="1"/>
       <c r="B55" s="1">
-        <v>1401</v>
+        <v>1310</v>
       </c>
       <c r="C55" s="1"/>
       <c r="D55" s="1">
         <v>1</v>
       </c>
       <c r="E55" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="F55" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="F55" s="1" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="56" ht="15" customHeight="1" spans="1:6">
       <c r="A56" s="1"/>
       <c r="B56" s="1">
-        <v>1402</v>
+        <v>1311</v>
       </c>
       <c r="C56" s="1"/>
       <c r="D56" s="1">
         <v>1</v>
       </c>
       <c r="E56" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F56" s="1" t="s">
         <v>116</v>
-      </c>
-      <c r="F56" s="1" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="57" ht="15" customHeight="1" spans="1:6">
       <c r="A57" s="1"/>
       <c r="B57" s="1">
-        <v>1403</v>
+        <v>1312</v>
       </c>
       <c r="C57" s="1"/>
       <c r="D57" s="1">
         <v>1</v>
       </c>
       <c r="E57" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="F57" s="1" t="s">
         <v>118</v>
-      </c>
-      <c r="F57" s="1" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="58" ht="15" customHeight="1" spans="1:6">
       <c r="A58" s="1"/>
       <c r="B58" s="1">
-        <v>1404</v>
+        <v>1313</v>
       </c>
       <c r="C58" s="1"/>
       <c r="D58" s="1">
         <v>1</v>
       </c>
       <c r="E58" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F58" s="1" t="s">
         <v>120</v>
-      </c>
-      <c r="F58" s="1" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="59" ht="15" customHeight="1" spans="1:6">
       <c r="A59" s="1"/>
       <c r="B59" s="1">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="C59" s="1"/>
       <c r="D59" s="1">
         <v>1</v>
       </c>
       <c r="E59" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="F59" s="1" t="s">
         <v>122</v>
-      </c>
-      <c r="F59" s="1" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="60" ht="15" customHeight="1" spans="1:6">
       <c r="A60" s="1"/>
       <c r="B60" s="1">
-        <v>1406</v>
+        <v>1402</v>
       </c>
       <c r="C60" s="1"/>
       <c r="D60" s="1">
         <v>1</v>
       </c>
       <c r="E60" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="F60" s="1" t="s">
         <v>124</v>
-      </c>
-      <c r="F60" s="1" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="61" ht="15" customHeight="1" spans="1:6">
       <c r="A61" s="1"/>
       <c r="B61" s="1">
-        <v>1407</v>
-      </c>
-      <c r="C61" s="1" t="s">
+        <v>1403</v>
+      </c>
+      <c r="C61" s="1"/>
+      <c r="D61" s="1">
+        <v>1</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="F61" s="1" t="s">
         <v>126</v>
-      </c>
-      <c r="D61" s="1">
-        <v>1</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="F61" s="1" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="62" ht="15" customHeight="1" spans="1:6">
       <c r="A62" s="1"/>
       <c r="B62" s="1">
-        <v>1408</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>126</v>
-      </c>
+        <v>1404</v>
+      </c>
+      <c r="C62" s="1"/>
       <c r="D62" s="1">
         <v>1</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="63" ht="15" customHeight="1" spans="1:6">
       <c r="A63" s="1"/>
       <c r="B63" s="1">
-        <v>1409</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>126</v>
-      </c>
+        <v>1405</v>
+      </c>
+      <c r="C63" s="1"/>
       <c r="D63" s="1">
         <v>1</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="64" ht="15" customHeight="1" spans="1:6">
       <c r="A64" s="1"/>
       <c r="B64" s="1">
-        <v>1410</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>126</v>
-      </c>
+        <v>1406</v>
+      </c>
+      <c r="C64" s="1"/>
       <c r="D64" s="1">
         <v>1</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="65" ht="15" customHeight="1" spans="1:6">
       <c r="A65" s="1"/>
       <c r="B65" s="1">
-        <v>1411</v>
+        <v>1407</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="D65" s="1">
         <v>1</v>
       </c>
       <c r="E65" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="F65" s="1" t="s">
         <v>135</v>
-      </c>
-      <c r="F65" s="1" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="66" ht="15" customHeight="1" spans="1:6">
       <c r="A66" s="1"/>
       <c r="B66" s="1">
-        <v>1501</v>
-      </c>
-      <c r="C66" s="1"/>
+        <v>1408</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>133</v>
+      </c>
       <c r="D66" s="1">
         <v>1</v>
       </c>
       <c r="E66" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="F66" s="1" t="s">
         <v>137</v>
-      </c>
-      <c r="F66" s="1" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1" spans="1:6">
       <c r="A67" s="1"/>
       <c r="B67" s="1">
-        <v>1502</v>
-      </c>
-      <c r="C67" s="1"/>
+        <v>1409</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>133</v>
+      </c>
       <c r="D67" s="1">
         <v>1</v>
       </c>
       <c r="E67" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="F67" s="1" t="s">
         <v>139</v>
-      </c>
-      <c r="F67" s="1" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="68" ht="15" customHeight="1" spans="1:6">
       <c r="A68" s="1"/>
       <c r="B68" s="1">
-        <v>1503</v>
-      </c>
-      <c r="C68" s="1"/>
+        <v>1410</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>133</v>
+      </c>
       <c r="D68" s="1">
         <v>1</v>
       </c>
       <c r="E68" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="F68" s="1" t="s">
         <v>141</v>
-      </c>
-      <c r="F68" s="1" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" spans="1:6">
       <c r="A69" s="1"/>
       <c r="B69" s="1">
-        <v>1601</v>
-      </c>
-      <c r="C69" s="1"/>
+        <v>1411</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>133</v>
+      </c>
       <c r="D69" s="1">
         <v>1</v>
       </c>
       <c r="E69" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="F69" s="1" t="s">
         <v>143</v>
-      </c>
-      <c r="F69" s="1" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1" spans="1:6">
       <c r="A70" s="1"/>
       <c r="B70" s="1">
-        <v>1602</v>
+        <v>1501</v>
       </c>
       <c r="C70" s="1"/>
       <c r="D70" s="1">
         <v>1</v>
       </c>
       <c r="E70" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="F70" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="F70" s="1" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="71" ht="15" customHeight="1" spans="1:6">
+    </row>
+    <row r="71" spans="1:6">
       <c r="A71" s="1"/>
       <c r="B71" s="1">
-        <v>1603</v>
+        <v>1502</v>
       </c>
       <c r="C71" s="1"/>
       <c r="D71" s="1">
         <v>1</v>
       </c>
       <c r="E71" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="F71" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="F71" s="1" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="72" ht="15" customHeight="1" spans="1:6">
+    </row>
+    <row r="72" ht="13" customHeight="1" spans="1:6">
       <c r="A72" s="1"/>
       <c r="B72" s="1">
-        <v>1701</v>
+        <v>1503</v>
       </c>
       <c r="C72" s="1"/>
       <c r="D72" s="1">
         <v>1</v>
       </c>
       <c r="E72" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="F72" s="1" t="s">
         <v>149</v>
-      </c>
-      <c r="F72" s="1" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1" spans="1:6">
       <c r="A73" s="1"/>
       <c r="B73" s="1">
-        <v>1702</v>
-      </c>
-      <c r="C73" s="1"/>
+        <v>1511</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>150</v>
+      </c>
       <c r="D73" s="1">
         <v>1</v>
       </c>
@@ -4650,9 +4699,11 @@
     <row r="74" ht="15" customHeight="1" spans="1:6">
       <c r="A74" s="1"/>
       <c r="B74" s="1">
-        <v>1703</v>
-      </c>
-      <c r="C74" s="1"/>
+        <v>1512</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>150</v>
+      </c>
       <c r="D74" s="1">
         <v>1</v>
       </c>
@@ -4666,9 +4717,11 @@
     <row r="75" ht="15" customHeight="1" spans="1:6">
       <c r="A75" s="1"/>
       <c r="B75" s="1">
-        <v>1704</v>
-      </c>
-      <c r="C75" s="1"/>
+        <v>1513</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>150</v>
+      </c>
       <c r="D75" s="1">
         <v>1</v>
       </c>
@@ -4682,9 +4735,11 @@
     <row r="76" ht="15" customHeight="1" spans="1:6">
       <c r="A76" s="1"/>
       <c r="B76" s="1">
-        <v>1705</v>
-      </c>
-      <c r="C76" s="1"/>
+        <v>1514</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>150</v>
+      </c>
       <c r="D76" s="1">
         <v>1</v>
       </c>
@@ -4698,9 +4753,11 @@
     <row r="77" ht="15" customHeight="1" spans="1:6">
       <c r="A77" s="1"/>
       <c r="B77" s="1">
-        <v>1706</v>
-      </c>
-      <c r="C77" s="1"/>
+        <v>1515</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>150</v>
+      </c>
       <c r="D77" s="1">
         <v>1</v>
       </c>
@@ -4714,7 +4771,7 @@
     <row r="78" ht="15" customHeight="1" spans="1:6">
       <c r="A78" s="1"/>
       <c r="B78" s="1">
-        <v>1707</v>
+        <v>1702</v>
       </c>
       <c r="C78" s="1"/>
       <c r="D78" s="1">
@@ -4730,7 +4787,7 @@
     <row r="79" ht="15" customHeight="1" spans="1:6">
       <c r="A79" s="1"/>
       <c r="B79" s="1">
-        <v>1708</v>
+        <v>1703</v>
       </c>
       <c r="C79" s="1"/>
       <c r="D79" s="1">
@@ -4746,7 +4803,7 @@
     <row r="80" ht="15" customHeight="1" spans="1:6">
       <c r="A80" s="1"/>
       <c r="B80" s="1">
-        <v>1711</v>
+        <v>1704</v>
       </c>
       <c r="C80" s="1"/>
       <c r="D80" s="1">
@@ -4762,7 +4819,7 @@
     <row r="81" ht="15" customHeight="1" spans="1:6">
       <c r="A81" s="1"/>
       <c r="B81" s="1">
-        <v>1712</v>
+        <v>1705</v>
       </c>
       <c r="C81" s="1"/>
       <c r="D81" s="1">
@@ -4778,100 +4835,90 @@
     <row r="82" ht="15" customHeight="1" spans="1:6">
       <c r="A82" s="1"/>
       <c r="B82" s="1">
-        <v>1801</v>
-      </c>
-      <c r="C82" s="1" t="s">
+        <v>1706</v>
+      </c>
+      <c r="C82" s="1"/>
+      <c r="D82" s="1">
+        <v>1</v>
+      </c>
+      <c r="E82" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="D82" s="1">
-        <v>1</v>
-      </c>
-      <c r="E82" s="1" t="s">
+      <c r="F82" s="1" t="s">
         <v>170</v>
-      </c>
-      <c r="F82" s="1" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1" spans="1:6">
       <c r="A83" s="1"/>
       <c r="B83" s="1">
-        <v>1802</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>169</v>
-      </c>
+        <v>1707</v>
+      </c>
+      <c r="C83" s="1"/>
       <c r="D83" s="1">
         <v>1</v>
       </c>
       <c r="E83" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="F83" s="1" t="s">
         <v>172</v>
-      </c>
-      <c r="F83" s="1" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="84" ht="15" customHeight="1" spans="1:6">
       <c r="A84" s="1"/>
       <c r="B84" s="1">
-        <v>1803</v>
-      </c>
-      <c r="C84" s="1" t="s">
-        <v>169</v>
-      </c>
+        <v>1708</v>
+      </c>
+      <c r="C84" s="1"/>
       <c r="D84" s="1">
         <v>1</v>
       </c>
       <c r="E84" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="F84" s="1" t="s">
         <v>174</v>
-      </c>
-      <c r="F84" s="1" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1" spans="1:6">
       <c r="A85" s="1"/>
       <c r="B85" s="1">
-        <v>1804</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>169</v>
-      </c>
+        <v>1711</v>
+      </c>
+      <c r="C85" s="1"/>
       <c r="D85" s="1">
         <v>1</v>
       </c>
       <c r="E85" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="F85" s="1" t="s">
         <v>176</v>
-      </c>
-      <c r="F85" s="1" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1" spans="1:6">
       <c r="A86" s="1"/>
       <c r="B86" s="1">
-        <v>1805</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>169</v>
-      </c>
+        <v>1712</v>
+      </c>
+      <c r="C86" s="1"/>
       <c r="D86" s="1">
         <v>1</v>
       </c>
       <c r="E86" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="F86" s="1" t="s">
         <v>178</v>
-      </c>
-      <c r="F86" s="1" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1" spans="1:6">
       <c r="A87" s="1"/>
       <c r="B87" s="1">
-        <v>1806</v>
+        <v>1801</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="D87" s="1">
         <v>1</v>
@@ -4886,10 +4933,10 @@
     <row r="88" ht="15" customHeight="1" spans="1:6">
       <c r="A88" s="1"/>
       <c r="B88" s="1">
-        <v>1807</v>
+        <v>1802</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="D88" s="1">
         <v>1</v>
@@ -4904,10 +4951,10 @@
     <row r="89" ht="15" customHeight="1" spans="1:6">
       <c r="A89" s="1"/>
       <c r="B89" s="1">
-        <v>1808</v>
+        <v>1803</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="D89" s="1">
         <v>1</v>
@@ -4922,10 +4969,10 @@
     <row r="90" ht="15" customHeight="1" spans="1:6">
       <c r="A90" s="1"/>
       <c r="B90" s="1">
-        <v>1831</v>
+        <v>1804</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="D90" s="1">
         <v>1</v>
@@ -4940,10 +4987,10 @@
     <row r="91" ht="15" customHeight="1" spans="1:6">
       <c r="A91" s="1"/>
       <c r="B91" s="1">
-        <v>1832</v>
+        <v>1805</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="D91" s="1">
         <v>1</v>
@@ -4958,10 +5005,10 @@
     <row r="92" ht="15" customHeight="1" spans="1:6">
       <c r="A92" s="1"/>
       <c r="B92" s="1">
-        <v>1833</v>
+        <v>1806</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="D92" s="1">
         <v>1</v>
@@ -4976,10 +5023,10 @@
     <row r="93" ht="15" customHeight="1" spans="1:6">
       <c r="A93" s="1"/>
       <c r="B93" s="1">
-        <v>1834</v>
+        <v>1807</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="D93" s="1">
         <v>1</v>
@@ -4994,10 +5041,10 @@
     <row r="94" ht="15" customHeight="1" spans="1:6">
       <c r="A94" s="1"/>
       <c r="B94" s="1">
-        <v>1841</v>
+        <v>1808</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="D94" s="1">
         <v>1</v>
@@ -5012,10 +5059,10 @@
     <row r="95" ht="15" customHeight="1" spans="1:6">
       <c r="A95" s="1"/>
       <c r="B95" s="1">
-        <v>1842</v>
+        <v>1831</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="D95" s="1">
         <v>1</v>
@@ -5030,10 +5077,10 @@
     <row r="96" ht="15" customHeight="1" spans="1:6">
       <c r="A96" s="1"/>
       <c r="B96" s="1">
-        <v>1843</v>
+        <v>1832</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="D96" s="1">
         <v>1</v>
@@ -5048,10 +5095,10 @@
     <row r="97" ht="15" customHeight="1" spans="1:6">
       <c r="A97" s="1"/>
       <c r="B97" s="1">
-        <v>1844</v>
+        <v>1833</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="D97" s="1">
         <v>1</v>
@@ -5066,10 +5113,10 @@
     <row r="98" ht="15" customHeight="1" spans="1:6">
       <c r="A98" s="1"/>
       <c r="B98" s="1">
-        <v>1845</v>
+        <v>1834</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="D98" s="1">
         <v>1</v>
@@ -5084,10 +5131,10 @@
     <row r="99" ht="15" customHeight="1" spans="1:6">
       <c r="A99" s="1"/>
       <c r="B99" s="1">
-        <v>1846</v>
+        <v>1841</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="D99" s="1">
         <v>1</v>
@@ -5102,10 +5149,10 @@
     <row r="100" ht="15" customHeight="1" spans="1:6">
       <c r="A100" s="1"/>
       <c r="B100" s="1">
-        <v>1847</v>
+        <v>1842</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="D100" s="1">
         <v>1</v>
@@ -5120,10 +5167,10 @@
     <row r="101" ht="15" customHeight="1" spans="1:6">
       <c r="A101" s="1"/>
       <c r="B101" s="1">
-        <v>1848</v>
+        <v>1843</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="D101" s="1">
         <v>1</v>
@@ -5138,10 +5185,10 @@
     <row r="102" ht="15" customHeight="1" spans="1:6">
       <c r="A102" s="1"/>
       <c r="B102" s="1">
-        <v>1849</v>
+        <v>1844</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="D102" s="1">
         <v>1</v>
@@ -5156,10 +5203,10 @@
     <row r="103" ht="15" customHeight="1" spans="1:6">
       <c r="A103" s="1"/>
       <c r="B103" s="1">
-        <v>1850</v>
+        <v>1845</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="D103" s="1">
         <v>1</v>
@@ -5174,9 +5221,11 @@
     <row r="104" ht="15" customHeight="1" spans="1:6">
       <c r="A104" s="1"/>
       <c r="B104" s="1">
-        <v>1901</v>
-      </c>
-      <c r="C104" s="1"/>
+        <v>1846</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>179</v>
+      </c>
       <c r="D104" s="1">
         <v>1</v>
       </c>
@@ -5190,9 +5239,11 @@
     <row r="105" ht="15" customHeight="1" spans="1:6">
       <c r="A105" s="1"/>
       <c r="B105" s="1">
-        <v>1902</v>
-      </c>
-      <c r="C105" s="1"/>
+        <v>1847</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>179</v>
+      </c>
       <c r="D105" s="1">
         <v>1</v>
       </c>
@@ -5206,9 +5257,11 @@
     <row r="106" ht="15" customHeight="1" spans="1:6">
       <c r="A106" s="1"/>
       <c r="B106" s="1">
-        <v>1903</v>
-      </c>
-      <c r="C106" s="1"/>
+        <v>1848</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>179</v>
+      </c>
       <c r="D106" s="1">
         <v>1</v>
       </c>
@@ -5222,9 +5275,11 @@
     <row r="107" ht="15" customHeight="1" spans="1:6">
       <c r="A107" s="1"/>
       <c r="B107" s="1">
-        <v>1904</v>
-      </c>
-      <c r="C107" s="1"/>
+        <v>1849</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>179</v>
+      </c>
       <c r="D107" s="1">
         <v>1</v>
       </c>
@@ -5238,9 +5293,11 @@
     <row r="108" ht="15" customHeight="1" spans="1:6">
       <c r="A108" s="1"/>
       <c r="B108" s="1">
-        <v>1905</v>
-      </c>
-      <c r="C108" s="1"/>
+        <v>1850</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>179</v>
+      </c>
       <c r="D108" s="1">
         <v>1</v>
       </c>
@@ -5254,7 +5311,7 @@
     <row r="109" ht="15" customHeight="1" spans="1:6">
       <c r="A109" s="1"/>
       <c r="B109" s="1">
-        <v>1906</v>
+        <v>1901</v>
       </c>
       <c r="C109" s="1"/>
       <c r="D109" s="1">
@@ -5270,7 +5327,7 @@
     <row r="110" ht="15" customHeight="1" spans="1:6">
       <c r="A110" s="1"/>
       <c r="B110" s="1">
-        <v>1907</v>
+        <v>1902</v>
       </c>
       <c r="C110" s="1"/>
       <c r="D110" s="1">
@@ -5286,7 +5343,7 @@
     <row r="111" ht="15" customHeight="1" spans="1:6">
       <c r="A111" s="1"/>
       <c r="B111" s="1">
-        <v>1908</v>
+        <v>1903</v>
       </c>
       <c r="C111" s="1"/>
       <c r="D111" s="1">
@@ -5302,7 +5359,7 @@
     <row r="112" ht="15" customHeight="1" spans="1:6">
       <c r="A112" s="1"/>
       <c r="B112" s="1">
-        <v>1909</v>
+        <v>1904</v>
       </c>
       <c r="C112" s="1"/>
       <c r="D112" s="1">
@@ -5318,7 +5375,7 @@
     <row r="113" ht="15" customHeight="1" spans="1:6">
       <c r="A113" s="1"/>
       <c r="B113" s="1">
-        <v>1910</v>
+        <v>1905</v>
       </c>
       <c r="C113" s="1"/>
       <c r="D113" s="1">
@@ -5334,7 +5391,7 @@
     <row r="114" ht="15" customHeight="1" spans="1:6">
       <c r="A114" s="1"/>
       <c r="B114" s="1">
-        <v>1911</v>
+        <v>1906</v>
       </c>
       <c r="C114" s="1"/>
       <c r="D114" s="1">
@@ -5350,7 +5407,7 @@
     <row r="115" ht="15" customHeight="1" spans="1:6">
       <c r="A115" s="1"/>
       <c r="B115" s="1">
-        <v>1912</v>
+        <v>1907</v>
       </c>
       <c r="C115" s="1"/>
       <c r="D115" s="1">
@@ -5366,7 +5423,7 @@
     <row r="116" ht="15" customHeight="1" spans="1:6">
       <c r="A116" s="1"/>
       <c r="B116" s="1">
-        <v>1913</v>
+        <v>1908</v>
       </c>
       <c r="C116" s="1"/>
       <c r="D116" s="1">
@@ -5382,7 +5439,7 @@
     <row r="117" ht="15" customHeight="1" spans="1:6">
       <c r="A117" s="1"/>
       <c r="B117" s="1">
-        <v>1914</v>
+        <v>1909</v>
       </c>
       <c r="C117" s="1"/>
       <c r="D117" s="1">
@@ -5398,7 +5455,7 @@
     <row r="118" ht="15" customHeight="1" spans="1:6">
       <c r="A118" s="1"/>
       <c r="B118" s="1">
-        <v>1915</v>
+        <v>1910</v>
       </c>
       <c r="C118" s="1"/>
       <c r="D118" s="1">
@@ -5414,7 +5471,7 @@
     <row r="119" ht="15" customHeight="1" spans="1:6">
       <c r="A119" s="1"/>
       <c r="B119" s="1">
-        <v>1916</v>
+        <v>1911</v>
       </c>
       <c r="C119" s="1"/>
       <c r="D119" s="1">
@@ -5430,7 +5487,7 @@
     <row r="120" ht="15" customHeight="1" spans="1:6">
       <c r="A120" s="1"/>
       <c r="B120" s="1">
-        <v>1917</v>
+        <v>1912</v>
       </c>
       <c r="C120" s="1"/>
       <c r="D120" s="1">
@@ -5446,7 +5503,7 @@
     <row r="121" ht="15" customHeight="1" spans="1:6">
       <c r="A121" s="1"/>
       <c r="B121" s="1">
-        <v>1918</v>
+        <v>1913</v>
       </c>
       <c r="C121" s="1"/>
       <c r="D121" s="1">
@@ -5462,7 +5519,7 @@
     <row r="122" ht="15" customHeight="1" spans="1:6">
       <c r="A122" s="1"/>
       <c r="B122" s="1">
-        <v>1919</v>
+        <v>1914</v>
       </c>
       <c r="C122" s="1"/>
       <c r="D122" s="1">
@@ -5478,7 +5535,7 @@
     <row r="123" ht="15" customHeight="1" spans="1:6">
       <c r="A123" s="1"/>
       <c r="B123" s="1">
-        <v>1920</v>
+        <v>1915</v>
       </c>
       <c r="C123" s="1"/>
       <c r="D123" s="1">
@@ -5494,7 +5551,7 @@
     <row r="124" ht="15" customHeight="1" spans="1:6">
       <c r="A124" s="1"/>
       <c r="B124" s="1">
-        <v>1921</v>
+        <v>1916</v>
       </c>
       <c r="C124" s="1"/>
       <c r="D124" s="1">
@@ -5510,7 +5567,7 @@
     <row r="125" ht="15" customHeight="1" spans="1:6">
       <c r="A125" s="1"/>
       <c r="B125" s="1">
-        <v>1922</v>
+        <v>1917</v>
       </c>
       <c r="C125" s="1"/>
       <c r="D125" s="1">
@@ -5526,7 +5583,7 @@
     <row r="126" ht="15" customHeight="1" spans="1:6">
       <c r="A126" s="1"/>
       <c r="B126" s="1">
-        <v>1923</v>
+        <v>1918</v>
       </c>
       <c r="C126" s="1"/>
       <c r="D126" s="1">
@@ -5542,7 +5599,7 @@
     <row r="127" ht="15" customHeight="1" spans="1:6">
       <c r="A127" s="1"/>
       <c r="B127" s="1">
-        <v>1924</v>
+        <v>1919</v>
       </c>
       <c r="C127" s="1"/>
       <c r="D127" s="1">
@@ -5558,7 +5615,7 @@
     <row r="128" ht="15" customHeight="1" spans="1:6">
       <c r="A128" s="1"/>
       <c r="B128" s="1">
-        <v>1925</v>
+        <v>1920</v>
       </c>
       <c r="C128" s="1"/>
       <c r="D128" s="1">
@@ -5574,7 +5631,7 @@
     <row r="129" ht="15" customHeight="1" spans="1:6">
       <c r="A129" s="1"/>
       <c r="B129" s="1">
-        <v>1926</v>
+        <v>1921</v>
       </c>
       <c r="C129" s="1"/>
       <c r="D129" s="1">
@@ -5590,7 +5647,7 @@
     <row r="130" ht="15" customHeight="1" spans="1:6">
       <c r="A130" s="1"/>
       <c r="B130" s="1">
-        <v>1927</v>
+        <v>1922</v>
       </c>
       <c r="C130" s="1"/>
       <c r="D130" s="1">
@@ -5606,7 +5663,7 @@
     <row r="131" ht="15" customHeight="1" spans="1:6">
       <c r="A131" s="1"/>
       <c r="B131" s="1">
-        <v>1928</v>
+        <v>1923</v>
       </c>
       <c r="C131" s="1"/>
       <c r="D131" s="1">
@@ -5622,7 +5679,7 @@
     <row r="132" ht="15" customHeight="1" spans="1:6">
       <c r="A132" s="1"/>
       <c r="B132" s="1">
-        <v>1929</v>
+        <v>1924</v>
       </c>
       <c r="C132" s="1"/>
       <c r="D132" s="1">
@@ -5638,7 +5695,7 @@
     <row r="133" ht="15" customHeight="1" spans="1:6">
       <c r="A133" s="1"/>
       <c r="B133" s="1">
-        <v>1930</v>
+        <v>1925</v>
       </c>
       <c r="C133" s="1"/>
       <c r="D133" s="1">
@@ -5654,7 +5711,7 @@
     <row r="134" ht="15" customHeight="1" spans="1:6">
       <c r="A134" s="1"/>
       <c r="B134" s="1">
-        <v>1931</v>
+        <v>1926</v>
       </c>
       <c r="C134" s="1"/>
       <c r="D134" s="1">
@@ -5670,7 +5727,7 @@
     <row r="135" ht="15" customHeight="1" spans="1:6">
       <c r="A135" s="1"/>
       <c r="B135" s="1">
-        <v>1932</v>
+        <v>1927</v>
       </c>
       <c r="C135" s="1"/>
       <c r="D135" s="1">
@@ -5686,7 +5743,7 @@
     <row r="136" ht="15" customHeight="1" spans="1:6">
       <c r="A136" s="1"/>
       <c r="B136" s="1">
-        <v>1933</v>
+        <v>1928</v>
       </c>
       <c r="C136" s="1"/>
       <c r="D136" s="1">
@@ -5702,7 +5759,7 @@
     <row r="137" ht="15" customHeight="1" spans="1:6">
       <c r="A137" s="1"/>
       <c r="B137" s="1">
-        <v>1934</v>
+        <v>1929</v>
       </c>
       <c r="C137" s="1"/>
       <c r="D137" s="1">
@@ -5718,7 +5775,7 @@
     <row r="138" ht="15" customHeight="1" spans="1:6">
       <c r="A138" s="1"/>
       <c r="B138" s="1">
-        <v>1935</v>
+        <v>1930</v>
       </c>
       <c r="C138" s="1"/>
       <c r="D138" s="1">
@@ -5734,7 +5791,7 @@
     <row r="139" ht="15" customHeight="1" spans="1:6">
       <c r="A139" s="1"/>
       <c r="B139" s="1">
-        <v>1936</v>
+        <v>1931</v>
       </c>
       <c r="C139" s="1"/>
       <c r="D139" s="1">
@@ -5750,7 +5807,7 @@
     <row r="140" ht="15" customHeight="1" spans="1:6">
       <c r="A140" s="1"/>
       <c r="B140" s="1">
-        <v>1937</v>
+        <v>1932</v>
       </c>
       <c r="C140" s="1"/>
       <c r="D140" s="1">
@@ -5766,7 +5823,7 @@
     <row r="141" ht="15" customHeight="1" spans="1:6">
       <c r="A141" s="1"/>
       <c r="B141" s="1">
-        <v>1938</v>
+        <v>1933</v>
       </c>
       <c r="C141" s="1"/>
       <c r="D141" s="1">
@@ -5782,7 +5839,7 @@
     <row r="142" ht="15" customHeight="1" spans="1:6">
       <c r="A142" s="1"/>
       <c r="B142" s="1">
-        <v>1939</v>
+        <v>1934</v>
       </c>
       <c r="C142" s="1"/>
       <c r="D142" s="1">
@@ -5798,7 +5855,7 @@
     <row r="143" ht="15" customHeight="1" spans="1:6">
       <c r="A143" s="1"/>
       <c r="B143" s="1">
-        <v>1940</v>
+        <v>1935</v>
       </c>
       <c r="C143" s="1"/>
       <c r="D143" s="1">
@@ -5814,7 +5871,7 @@
     <row r="144" ht="15" customHeight="1" spans="1:6">
       <c r="A144" s="1"/>
       <c r="B144" s="1">
-        <v>1941</v>
+        <v>1936</v>
       </c>
       <c r="C144" s="1"/>
       <c r="D144" s="1">
@@ -5830,7 +5887,7 @@
     <row r="145" ht="15" customHeight="1" spans="1:6">
       <c r="A145" s="1"/>
       <c r="B145" s="1">
-        <v>1942</v>
+        <v>1937</v>
       </c>
       <c r="C145" s="1"/>
       <c r="D145" s="1">
@@ -5846,7 +5903,7 @@
     <row r="146" ht="15" customHeight="1" spans="1:6">
       <c r="A146" s="1"/>
       <c r="B146" s="1">
-        <v>1943</v>
+        <v>1938</v>
       </c>
       <c r="C146" s="1"/>
       <c r="D146" s="1">
@@ -5862,7 +5919,7 @@
     <row r="147" ht="15" customHeight="1" spans="1:6">
       <c r="A147" s="1"/>
       <c r="B147" s="1">
-        <v>1944</v>
+        <v>1939</v>
       </c>
       <c r="C147" s="1"/>
       <c r="D147" s="1">
@@ -5878,7 +5935,7 @@
     <row r="148" ht="15" customHeight="1" spans="1:6">
       <c r="A148" s="1"/>
       <c r="B148" s="1">
-        <v>1945</v>
+        <v>1940</v>
       </c>
       <c r="C148" s="1"/>
       <c r="D148" s="1">
@@ -5894,7 +5951,7 @@
     <row r="149" ht="15" customHeight="1" spans="1:6">
       <c r="A149" s="1"/>
       <c r="B149" s="1">
-        <v>1946</v>
+        <v>1941</v>
       </c>
       <c r="C149" s="1"/>
       <c r="D149" s="1">
@@ -5910,7 +5967,7 @@
     <row r="150" ht="15" customHeight="1" spans="1:6">
       <c r="A150" s="1"/>
       <c r="B150" s="1">
-        <v>1947</v>
+        <v>1942</v>
       </c>
       <c r="C150" s="1"/>
       <c r="D150" s="1">
@@ -5926,7 +5983,7 @@
     <row r="151" ht="15" customHeight="1" spans="1:6">
       <c r="A151" s="1"/>
       <c r="B151" s="1">
-        <v>1948</v>
+        <v>1943</v>
       </c>
       <c r="C151" s="1"/>
       <c r="D151" s="1">
@@ -5942,11 +5999,11 @@
     <row r="152" ht="15" customHeight="1" spans="1:6">
       <c r="A152" s="1"/>
       <c r="B152" s="1">
-        <v>2001</v>
+        <v>1944</v>
       </c>
       <c r="C152" s="1"/>
       <c r="D152" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E152" s="1" t="s">
         <v>310</v>
@@ -5958,11 +6015,11 @@
     <row r="153" ht="15" customHeight="1" spans="1:6">
       <c r="A153" s="1"/>
       <c r="B153" s="1">
-        <v>2002</v>
+        <v>1945</v>
       </c>
       <c r="C153" s="1"/>
       <c r="D153" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E153" s="1" t="s">
         <v>312</v>
@@ -5974,11 +6031,11 @@
     <row r="154" ht="15" customHeight="1" spans="1:6">
       <c r="A154" s="1"/>
       <c r="B154" s="1">
-        <v>2003</v>
+        <v>1946</v>
       </c>
       <c r="C154" s="1"/>
       <c r="D154" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E154" s="1" t="s">
         <v>314</v>
@@ -5990,11 +6047,11 @@
     <row r="155" ht="15" customHeight="1" spans="1:6">
       <c r="A155" s="1"/>
       <c r="B155" s="1">
-        <v>2004</v>
+        <v>1947</v>
       </c>
       <c r="C155" s="1"/>
       <c r="D155" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E155" s="1" t="s">
         <v>316</v>
@@ -6006,11 +6063,11 @@
     <row r="156" ht="15" customHeight="1" spans="1:6">
       <c r="A156" s="1"/>
       <c r="B156" s="1">
-        <v>2101</v>
+        <v>1948</v>
       </c>
       <c r="C156" s="1"/>
       <c r="D156" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E156" s="1" t="s">
         <v>318</v>
@@ -6022,34 +6079,30 @@
     <row r="157" ht="15" customHeight="1" spans="1:6">
       <c r="A157" s="1"/>
       <c r="B157" s="1">
-        <v>2102</v>
-      </c>
-      <c r="C157" s="1" t="s">
-        <v>320</v>
-      </c>
+        <v>2001</v>
+      </c>
+      <c r="C157" s="1"/>
       <c r="D157" s="1">
         <v>2</v>
       </c>
       <c r="E157" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="F157" s="1" t="s">
         <v>321</v>
-      </c>
-      <c r="F157" s="1" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="158" ht="15" customHeight="1" spans="1:6">
       <c r="A158" s="1"/>
       <c r="B158" s="1">
-        <v>2103</v>
-      </c>
-      <c r="C158" s="1" t="s">
-        <v>320</v>
-      </c>
+        <v>2002</v>
+      </c>
+      <c r="C158" s="1"/>
       <c r="D158" s="1">
         <v>2</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>323</v>
@@ -6058,75 +6111,77 @@
     <row r="159" ht="15" customHeight="1" spans="1:6">
       <c r="A159" s="1"/>
       <c r="B159" s="1">
-        <v>2104</v>
-      </c>
-      <c r="C159" s="1" t="s">
-        <v>320</v>
-      </c>
+        <v>2003</v>
+      </c>
+      <c r="C159" s="1"/>
       <c r="D159" s="1">
         <v>2</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="160" ht="15" customHeight="1" spans="1:6">
       <c r="A160" s="1"/>
       <c r="B160" s="1">
-        <v>2201</v>
+        <v>2004</v>
       </c>
       <c r="C160" s="1"/>
       <c r="D160" s="1">
         <v>2</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="161" ht="15" customHeight="1" spans="1:6">
       <c r="A161" s="1"/>
       <c r="B161" s="1">
-        <v>2301</v>
+        <v>2101</v>
       </c>
       <c r="C161" s="1"/>
       <c r="D161" s="1">
         <v>2</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="162" ht="15" customHeight="1" spans="1:6">
       <c r="A162" s="1"/>
       <c r="B162" s="1">
-        <v>2304</v>
-      </c>
-      <c r="C162" s="1"/>
+        <v>2102</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>330</v>
+      </c>
       <c r="D162" s="1">
         <v>2</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="163" ht="15" customHeight="1" spans="1:6">
       <c r="A163" s="1"/>
       <c r="B163" s="1">
-        <v>2309</v>
-      </c>
-      <c r="C163" s="1"/>
+        <v>2103</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>330</v>
+      </c>
       <c r="D163" s="1">
         <v>2</v>
       </c>
@@ -6134,20 +6189,22 @@
         <v>331</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="164" ht="15" customHeight="1" spans="1:6">
       <c r="A164" s="1"/>
       <c r="B164" s="1">
-        <v>2310</v>
-      </c>
-      <c r="C164" s="1"/>
+        <v>2104</v>
+      </c>
+      <c r="C164" s="1" t="s">
+        <v>330</v>
+      </c>
       <c r="D164" s="1">
         <v>2</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>334</v>
@@ -6156,7 +6213,7 @@
     <row r="165" ht="15" customHeight="1" spans="1:6">
       <c r="A165" s="1"/>
       <c r="B165" s="1">
-        <v>2311</v>
+        <v>2201</v>
       </c>
       <c r="C165" s="1"/>
       <c r="D165" s="1">
@@ -6172,7 +6229,7 @@
     <row r="166" ht="15" customHeight="1" spans="1:6">
       <c r="A166" s="1"/>
       <c r="B166" s="1">
-        <v>2312</v>
+        <v>2301</v>
       </c>
       <c r="C166" s="1"/>
       <c r="D166" s="1">
@@ -6188,11 +6245,9 @@
     <row r="167" ht="15" customHeight="1" spans="1:6">
       <c r="A167" s="1"/>
       <c r="B167" s="1">
-        <v>2313</v>
-      </c>
-      <c r="C167" s="1" t="s">
-        <v>109</v>
-      </c>
+        <v>2304</v>
+      </c>
+      <c r="C167" s="1"/>
       <c r="D167" s="1">
         <v>2</v>
       </c>
@@ -6206,7 +6261,7 @@
     <row r="168" ht="15" customHeight="1" spans="1:6">
       <c r="A168" s="1"/>
       <c r="B168" s="1">
-        <v>2399</v>
+        <v>2309</v>
       </c>
       <c r="C168" s="1"/>
       <c r="D168" s="1">
@@ -6222,11 +6277,11 @@
     <row r="169" ht="15" customHeight="1" spans="1:6">
       <c r="A169" s="1"/>
       <c r="B169" s="1">
-        <v>2401</v>
+        <v>2310</v>
       </c>
       <c r="C169" s="1"/>
       <c r="D169" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E169" s="1" t="s">
         <v>343</v>
@@ -6238,11 +6293,11 @@
     <row r="170" ht="15" customHeight="1" spans="1:6">
       <c r="A170" s="1"/>
       <c r="B170" s="1">
-        <v>2402</v>
+        <v>2311</v>
       </c>
       <c r="C170" s="1"/>
       <c r="D170" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E170" s="1" t="s">
         <v>345</v>
@@ -6254,7 +6309,7 @@
     <row r="171" ht="15" customHeight="1" spans="1:6">
       <c r="A171" s="1"/>
       <c r="B171" s="1">
-        <v>2501</v>
+        <v>2312</v>
       </c>
       <c r="C171" s="1"/>
       <c r="D171" s="1">
@@ -6270,269 +6325,267 @@
     <row r="172" ht="15" customHeight="1" spans="1:6">
       <c r="A172" s="1"/>
       <c r="B172" s="1">
-        <v>2502</v>
-      </c>
-      <c r="C172" s="1"/>
+        <v>2313</v>
+      </c>
+      <c r="C172" s="1" t="s">
+        <v>349</v>
+      </c>
       <c r="D172" s="1">
         <v>2</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="173" ht="15" customHeight="1" spans="1:6">
       <c r="A173" s="1"/>
       <c r="B173" s="1">
-        <v>2503</v>
+        <v>2399</v>
       </c>
       <c r="C173" s="1"/>
       <c r="D173" s="1">
         <v>2</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="174" ht="15" customHeight="1" spans="1:6">
       <c r="A174" s="1"/>
       <c r="B174" s="1">
-        <v>2504</v>
+        <v>2401</v>
       </c>
       <c r="C174" s="1"/>
       <c r="D174" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="175" ht="15" customHeight="1" spans="1:6">
       <c r="A175" s="1"/>
       <c r="B175" s="1">
-        <v>2600</v>
+        <v>2402</v>
       </c>
       <c r="C175" s="1"/>
       <c r="D175" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="176" ht="15" customHeight="1" spans="1:6">
       <c r="A176" s="1"/>
       <c r="B176" s="1">
-        <v>2601</v>
+        <v>2501</v>
       </c>
       <c r="C176" s="1"/>
       <c r="D176" s="1">
         <v>2</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="177" ht="15" customHeight="1" spans="1:6">
       <c r="A177" s="1"/>
       <c r="B177" s="1">
-        <v>2901</v>
+        <v>2502</v>
       </c>
       <c r="C177" s="1"/>
       <c r="D177" s="1">
         <v>2</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="178" ht="15" customHeight="1" spans="1:6">
       <c r="A178" s="1"/>
       <c r="B178" s="1">
-        <v>3001</v>
+        <v>2503</v>
       </c>
       <c r="C178" s="1"/>
       <c r="D178" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="179" ht="15" customHeight="1" spans="1:6">
       <c r="A179" s="1"/>
       <c r="B179" s="1">
-        <v>3002</v>
+        <v>2504</v>
       </c>
       <c r="C179" s="1"/>
       <c r="D179" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="180" ht="15" customHeight="1" spans="1:6">
       <c r="A180" s="1"/>
       <c r="B180" s="1">
-        <v>3003</v>
+        <v>2600</v>
       </c>
       <c r="C180" s="1"/>
       <c r="D180" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="181" ht="15" customHeight="1" spans="1:6">
       <c r="A181" s="1"/>
       <c r="B181" s="1">
-        <v>3004</v>
+        <v>2601</v>
       </c>
       <c r="C181" s="1"/>
       <c r="D181" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="182" ht="15" customHeight="1" spans="1:6">
       <c r="A182" s="1"/>
       <c r="B182" s="1">
-        <v>3005</v>
+        <v>2901</v>
       </c>
       <c r="C182" s="1"/>
       <c r="D182" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="183" ht="15" customHeight="1" spans="1:6">
       <c r="A183" s="1"/>
       <c r="B183" s="1">
-        <v>3006</v>
+        <v>3001</v>
       </c>
       <c r="C183" s="1"/>
       <c r="D183" s="1">
         <v>3</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="184" ht="15" customHeight="1" spans="1:6">
       <c r="A184" s="1"/>
       <c r="B184" s="1">
-        <v>3007</v>
+        <v>3002</v>
       </c>
       <c r="C184" s="1"/>
       <c r="D184" s="1">
         <v>3</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="185" ht="15" customHeight="1" spans="1:6">
       <c r="A185" s="1"/>
       <c r="B185" s="1">
-        <v>3008</v>
+        <v>3003</v>
       </c>
       <c r="C185" s="1"/>
       <c r="D185" s="1">
         <v>3</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="186" ht="15" customHeight="1" spans="1:6">
       <c r="A186" s="1"/>
       <c r="B186" s="1">
-        <v>3009</v>
+        <v>3004</v>
       </c>
       <c r="C186" s="1"/>
       <c r="D186" s="1">
         <v>3</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="187" ht="15" customHeight="1" spans="1:6">
       <c r="A187" s="1"/>
       <c r="B187" s="1">
-        <v>3010</v>
-      </c>
-      <c r="C187" s="1" t="s">
-        <v>169</v>
-      </c>
+        <v>3005</v>
+      </c>
+      <c r="C187" s="1"/>
       <c r="D187" s="1">
         <v>3</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="188" ht="15" customHeight="1" spans="1:6">
       <c r="A188" s="1"/>
       <c r="B188" s="1">
-        <v>3011</v>
-      </c>
-      <c r="C188" s="1" t="s">
-        <v>381</v>
-      </c>
+        <v>3006</v>
+      </c>
+      <c r="C188" s="1"/>
       <c r="D188" s="1">
         <v>3</v>
       </c>
@@ -6546,11 +6599,9 @@
     <row r="189" ht="15" customHeight="1" spans="1:6">
       <c r="A189" s="1"/>
       <c r="B189" s="1">
-        <v>3012</v>
-      </c>
-      <c r="C189" s="1" t="s">
-        <v>381</v>
-      </c>
+        <v>3007</v>
+      </c>
+      <c r="C189" s="1"/>
       <c r="D189" s="1">
         <v>3</v>
       </c>
@@ -6564,11 +6615,9 @@
     <row r="190" ht="15" customHeight="1" spans="1:6">
       <c r="A190" s="1"/>
       <c r="B190" s="1">
-        <v>3013</v>
-      </c>
-      <c r="C190" s="1" t="s">
-        <v>381</v>
-      </c>
+        <v>3008</v>
+      </c>
+      <c r="C190" s="1"/>
       <c r="D190" s="1">
         <v>3</v>
       </c>
@@ -6582,11 +6631,9 @@
     <row r="191" ht="15" customHeight="1" spans="1:6">
       <c r="A191" s="1"/>
       <c r="B191" s="1">
-        <v>3014</v>
-      </c>
-      <c r="C191" s="1" t="s">
-        <v>381</v>
-      </c>
+        <v>3009</v>
+      </c>
+      <c r="C191" s="1"/>
       <c r="D191" s="1">
         <v>3</v>
       </c>
@@ -6600,10 +6647,10 @@
     <row r="192" ht="15" customHeight="1" spans="1:6">
       <c r="A192" s="1"/>
       <c r="B192" s="1">
-        <v>3015</v>
+        <v>3010</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>381</v>
+        <v>179</v>
       </c>
       <c r="D192" s="1">
         <v>3</v>
@@ -6618,163 +6665,171 @@
     <row r="193" ht="15" customHeight="1" spans="1:6">
       <c r="A193" s="1"/>
       <c r="B193" s="1">
-        <v>3016</v>
+        <v>3011</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="D193" s="1">
         <v>3</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="194" ht="15" customHeight="1" spans="1:6">
       <c r="A194" s="1"/>
       <c r="B194" s="1">
-        <v>3017</v>
+        <v>3012</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="D194" s="1">
         <v>3</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="F194" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="195" ht="15" customHeight="1" spans="1:6">
       <c r="A195" s="1"/>
       <c r="B195" s="1">
-        <v>3018</v>
+        <v>3013</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="D195" s="1">
         <v>3</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="F195" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="196" ht="15" customHeight="1" spans="1:6">
       <c r="A196" s="1"/>
       <c r="B196" s="1">
-        <v>3019</v>
+        <v>3014</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="D196" s="1">
         <v>3</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="F196" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="197" ht="15" customHeight="1" spans="1:6">
       <c r="A197" s="1"/>
       <c r="B197" s="1">
-        <v>3101</v>
-      </c>
-      <c r="C197" s="1"/>
+        <v>3015</v>
+      </c>
+      <c r="C197" s="1" t="s">
+        <v>392</v>
+      </c>
       <c r="D197" s="1">
         <v>3</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="198" ht="15" customHeight="1" spans="1:6">
       <c r="A198" s="1"/>
       <c r="B198" s="1">
-        <v>3102</v>
-      </c>
-      <c r="C198" s="1"/>
+        <v>3016</v>
+      </c>
+      <c r="C198" s="1" t="s">
+        <v>392</v>
+      </c>
       <c r="D198" s="1">
         <v>3</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="F198" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="199" ht="15" customHeight="1" spans="1:6">
       <c r="A199" s="1"/>
       <c r="B199" s="1">
-        <v>3103</v>
-      </c>
-      <c r="C199" s="1"/>
+        <v>3017</v>
+      </c>
+      <c r="C199" s="1" t="s">
+        <v>392</v>
+      </c>
       <c r="D199" s="1">
         <v>3</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="F199" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="200" ht="15" customHeight="1" spans="1:6">
       <c r="A200" s="1"/>
       <c r="B200" s="1">
-        <v>3104</v>
-      </c>
-      <c r="C200" s="1"/>
+        <v>3018</v>
+      </c>
+      <c r="C200" s="1" t="s">
+        <v>392</v>
+      </c>
       <c r="D200" s="1">
         <v>3</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F200" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="201" ht="15" customHeight="1" spans="1:6">
       <c r="A201" s="1"/>
       <c r="B201" s="1">
-        <v>3105</v>
-      </c>
-      <c r="C201" s="1"/>
+        <v>3019</v>
+      </c>
+      <c r="C201" s="1" t="s">
+        <v>392</v>
+      </c>
       <c r="D201" s="1">
         <v>3</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="202" ht="15" customHeight="1" spans="1:6">
       <c r="A202" s="1"/>
       <c r="B202" s="1">
-        <v>3201</v>
-      </c>
-      <c r="C202" s="1" t="s">
-        <v>410</v>
-      </c>
+        <v>3101</v>
+      </c>
+      <c r="C202" s="1"/>
       <c r="D202" s="1">
         <v>3</v>
       </c>
@@ -6782,17 +6837,15 @@
         <v>411</v>
       </c>
       <c r="F202" s="1" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="203" ht="15" customHeight="1" spans="1:6">
       <c r="A203" s="1"/>
       <c r="B203" s="1">
-        <v>3202</v>
-      </c>
-      <c r="C203" s="1" t="s">
-        <v>412</v>
-      </c>
+        <v>3102</v>
+      </c>
+      <c r="C203" s="1"/>
       <c r="D203" s="1">
         <v>3</v>
       </c>
@@ -6800,19 +6853,17 @@
         <v>413</v>
       </c>
       <c r="F203" s="1" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="204" ht="15" customHeight="1" spans="1:6">
       <c r="A204" s="1"/>
       <c r="B204" s="1">
-        <v>6001</v>
-      </c>
-      <c r="C204" s="1" t="s">
-        <v>414</v>
-      </c>
+        <v>3103</v>
+      </c>
+      <c r="C204" s="1"/>
       <c r="D204" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E204" s="1" t="s">
         <v>415</v>
@@ -6824,11 +6875,11 @@
     <row r="205" ht="15" customHeight="1" spans="1:6">
       <c r="A205" s="1"/>
       <c r="B205" s="1">
-        <v>10001</v>
+        <v>3104</v>
       </c>
       <c r="C205" s="1"/>
       <c r="D205" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E205" s="1" t="s">
         <v>417</v>
@@ -6840,11 +6891,11 @@
     <row r="206" ht="15" customHeight="1" spans="1:6">
       <c r="A206" s="1"/>
       <c r="B206" s="1">
-        <v>10002</v>
+        <v>3105</v>
       </c>
       <c r="C206" s="1"/>
       <c r="D206" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E206" s="1" t="s">
         <v>419</v>
@@ -6856,139 +6907,143 @@
     <row r="207" ht="15" customHeight="1" spans="1:6">
       <c r="A207" s="1"/>
       <c r="B207" s="1">
-        <v>10003</v>
-      </c>
-      <c r="C207" s="1"/>
+        <v>3201</v>
+      </c>
+      <c r="C207" s="1" t="s">
+        <v>421</v>
+      </c>
       <c r="D207" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E207" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="F207" s="1" t="s">
         <v>421</v>
-      </c>
-      <c r="F207" s="1" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="208" ht="15" customHeight="1" spans="1:6">
       <c r="A208" s="1"/>
       <c r="B208" s="1">
-        <v>10004</v>
-      </c>
-      <c r="C208" s="1"/>
+        <v>3202</v>
+      </c>
+      <c r="C208" s="1" t="s">
+        <v>423</v>
+      </c>
       <c r="D208" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E208" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="F208" s="1" t="s">
         <v>423</v>
-      </c>
-      <c r="F208" s="1" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="209" ht="15" customHeight="1" spans="1:6">
       <c r="A209" s="1"/>
       <c r="B209" s="1">
-        <v>10101</v>
-      </c>
-      <c r="C209" s="1"/>
+        <v>6001</v>
+      </c>
+      <c r="C209" s="1" t="s">
+        <v>425</v>
+      </c>
       <c r="D209" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F209" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="210" ht="15" customHeight="1" spans="1:6">
       <c r="A210" s="1"/>
       <c r="B210" s="1">
-        <v>10102</v>
+        <v>10001</v>
       </c>
       <c r="C210" s="1"/>
       <c r="D210" s="1">
         <v>1</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F210" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="211" ht="15" customHeight="1" spans="1:6">
       <c r="A211" s="1"/>
       <c r="B211" s="1">
-        <v>10103</v>
+        <v>10002</v>
       </c>
       <c r="C211" s="1"/>
       <c r="D211" s="1">
         <v>1</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F211" s="1" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="212" ht="15" customHeight="1" spans="1:6">
       <c r="A212" s="1"/>
       <c r="B212" s="1">
-        <v>10201</v>
+        <v>10003</v>
       </c>
       <c r="C212" s="1"/>
       <c r="D212" s="1">
         <v>1</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F212" s="1" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="213" ht="15" customHeight="1" spans="1:6">
       <c r="A213" s="1"/>
       <c r="B213" s="1">
-        <v>10202</v>
+        <v>10004</v>
       </c>
       <c r="C213" s="1"/>
       <c r="D213" s="1">
         <v>1</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="214" ht="15" customHeight="1" spans="1:6">
       <c r="A214" s="1"/>
       <c r="B214" s="1">
-        <v>10203</v>
+        <v>10101</v>
       </c>
       <c r="C214" s="1"/>
       <c r="D214" s="1">
         <v>1</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F214" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="215" ht="15" customHeight="1" spans="1:6">
       <c r="A215" s="1"/>
       <c r="B215" s="1">
-        <v>11001</v>
-      </c>
-      <c r="C215" s="1" t="s">
-        <v>437</v>
-      </c>
+        <v>10102</v>
+      </c>
+      <c r="C215" s="1"/>
       <c r="D215" s="1">
         <v>1</v>
       </c>
@@ -7002,7 +7057,7 @@
     <row r="216" ht="15" customHeight="1" spans="1:6">
       <c r="A216" s="1"/>
       <c r="B216" s="1">
-        <v>13001</v>
+        <v>10103</v>
       </c>
       <c r="C216" s="1"/>
       <c r="D216" s="1">
@@ -7018,7 +7073,7 @@
     <row r="217" ht="15" customHeight="1" spans="1:6">
       <c r="A217" s="1"/>
       <c r="B217" s="1">
-        <v>13004</v>
+        <v>10201</v>
       </c>
       <c r="C217" s="1"/>
       <c r="D217" s="1">
@@ -7034,3317 +7089,3419 @@
     <row r="218" ht="15" customHeight="1" spans="1:6">
       <c r="A218" s="1"/>
       <c r="B218" s="1">
-        <v>13010</v>
-      </c>
-      <c r="C218" s="1" t="s">
-        <v>109</v>
-      </c>
+        <v>10202</v>
+      </c>
+      <c r="C218" s="1"/>
       <c r="D218" s="1">
         <v>1</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>143</v>
+        <v>444</v>
       </c>
       <c r="F218" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="219" ht="15" customHeight="1" spans="1:6">
       <c r="A219" s="1"/>
       <c r="B219" s="1">
-        <v>13011</v>
-      </c>
-      <c r="C219" s="1" t="s">
-        <v>109</v>
-      </c>
+        <v>10203</v>
+      </c>
+      <c r="C219" s="1"/>
       <c r="D219" s="1">
         <v>1</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>145</v>
+        <v>446</v>
       </c>
       <c r="F219" s="1" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="220" ht="15" customHeight="1" spans="1:6">
       <c r="A220" s="1"/>
       <c r="B220" s="1">
-        <v>13012</v>
-      </c>
-      <c r="C220" s="1" t="s">
-        <v>109</v>
-      </c>
+        <v>13001</v>
+      </c>
+      <c r="C220" s="1"/>
       <c r="D220" s="1">
         <v>1</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>147</v>
+        <v>448</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="221" ht="15" customHeight="1" spans="1:6">
       <c r="A221" s="1"/>
       <c r="B221" s="1">
-        <v>13013</v>
-      </c>
-      <c r="C221" s="1" t="s">
-        <v>109</v>
-      </c>
+        <v>13004</v>
+      </c>
+      <c r="C221" s="1"/>
       <c r="D221" s="1">
         <v>1</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="F221" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="222" ht="15" customHeight="1" spans="1:6">
       <c r="A222" s="1"/>
       <c r="B222" s="1">
-        <v>13999</v>
-      </c>
-      <c r="C222" s="1" t="s">
-        <v>109</v>
-      </c>
+        <v>13010</v>
+      </c>
+      <c r="C222" s="1"/>
       <c r="D222" s="1">
         <v>1</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="F222" s="1" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="223" ht="15" customHeight="1" spans="1:6">
       <c r="A223" s="1"/>
       <c r="B223" s="1">
-        <v>15001</v>
+        <v>13011</v>
       </c>
       <c r="C223" s="1"/>
       <c r="D223" s="1">
         <v>1</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="F223" s="1" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="224" ht="15" customHeight="1" spans="1:6">
       <c r="A224" s="1"/>
       <c r="B224" s="1">
-        <v>15002</v>
-      </c>
-      <c r="C224" s="1" t="s">
-        <v>453</v>
-      </c>
+        <v>13012</v>
+      </c>
+      <c r="C224" s="1"/>
       <c r="D224" s="1">
         <v>1</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="F224" s="1" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="225" ht="15" customHeight="1" spans="1:6">
       <c r="A225" s="1"/>
       <c r="B225" s="1">
-        <v>15003</v>
+        <v>13013</v>
       </c>
       <c r="C225" s="1"/>
       <c r="D225" s="1">
         <v>1</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="F225" s="1" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="226" ht="15" customHeight="1" spans="1:6">
       <c r="A226" s="1"/>
       <c r="B226" s="1">
-        <v>15005</v>
+        <v>13999</v>
       </c>
       <c r="C226" s="1"/>
       <c r="D226" s="1">
         <v>1</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="F226" s="1" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="227" ht="15" customHeight="1" spans="1:6">
       <c r="A227" s="1"/>
       <c r="B227" s="1">
-        <v>15007</v>
+        <v>15001</v>
       </c>
       <c r="C227" s="1"/>
       <c r="D227" s="1">
         <v>1</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="228" ht="15" customHeight="1" spans="1:6">
       <c r="A228" s="1"/>
       <c r="B228" s="1">
-        <v>15008</v>
-      </c>
-      <c r="C228" s="1"/>
+        <v>15002</v>
+      </c>
+      <c r="C228" s="1" t="s">
+        <v>464</v>
+      </c>
       <c r="D228" s="1">
         <v>1</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="F228" s="1" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="229" ht="15" customHeight="1" spans="1:6">
       <c r="A229" s="1"/>
       <c r="B229" s="1">
-        <v>15009</v>
+        <v>15003</v>
       </c>
       <c r="C229" s="1"/>
       <c r="D229" s="1">
         <v>1</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="F229" s="1" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="230" ht="15" customHeight="1" spans="1:6">
       <c r="A230" s="1"/>
       <c r="B230" s="1">
-        <v>15011</v>
+        <v>15005</v>
       </c>
       <c r="C230" s="1"/>
       <c r="D230" s="1">
         <v>1</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="F230" s="1" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="231" ht="15" customHeight="1" spans="1:6">
       <c r="A231" s="1"/>
       <c r="B231" s="1">
-        <v>15012</v>
+        <v>15007</v>
       </c>
       <c r="C231" s="1"/>
       <c r="D231" s="1">
         <v>1</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="F231" s="1" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="232" ht="15" customHeight="1" spans="1:6">
       <c r="A232" s="1"/>
       <c r="B232" s="1">
-        <v>15013</v>
+        <v>15008</v>
       </c>
       <c r="C232" s="1"/>
       <c r="D232" s="1">
         <v>1</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="F232" s="1" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="233" ht="15" customHeight="1" spans="1:6">
       <c r="A233" s="1"/>
       <c r="B233" s="1">
-        <v>15014</v>
+        <v>15009</v>
       </c>
       <c r="C233" s="1"/>
       <c r="D233" s="1">
         <v>1</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="F233" s="1" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="234" ht="15" customHeight="1" spans="1:6">
       <c r="A234" s="1"/>
       <c r="B234" s="1">
-        <v>15015</v>
+        <v>15011</v>
       </c>
       <c r="C234" s="1"/>
       <c r="D234" s="1">
         <v>1</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="F234" s="1" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="235" ht="15" customHeight="1" spans="1:6">
       <c r="A235" s="1"/>
       <c r="B235" s="1">
-        <v>15017</v>
+        <v>15012</v>
       </c>
       <c r="C235" s="1"/>
       <c r="D235" s="1">
         <v>1</v>
       </c>
       <c r="E235" s="1" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="F235" s="1" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="236" ht="15" customHeight="1" spans="1:6">
       <c r="A236" s="1"/>
       <c r="B236" s="1">
-        <v>15018</v>
+        <v>15013</v>
       </c>
       <c r="C236" s="1"/>
       <c r="D236" s="1">
         <v>1</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="F236" s="1" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="237" ht="15" customHeight="1" spans="1:6">
       <c r="A237" s="1"/>
       <c r="B237" s="1">
-        <v>15019</v>
+        <v>15014</v>
       </c>
       <c r="C237" s="1"/>
       <c r="D237" s="1">
         <v>1</v>
       </c>
       <c r="E237" s="1" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="F237" s="1" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="238" ht="15" customHeight="1" spans="1:6">
       <c r="A238" s="1"/>
       <c r="B238" s="1">
-        <v>15020</v>
+        <v>15015</v>
       </c>
       <c r="C238" s="1"/>
       <c r="D238" s="1">
         <v>1</v>
       </c>
       <c r="E238" s="1" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="F238" s="1" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="239" ht="15" customHeight="1" spans="1:6">
       <c r="A239" s="1"/>
       <c r="B239" s="1">
-        <v>15021</v>
+        <v>15017</v>
       </c>
       <c r="C239" s="1"/>
       <c r="D239" s="1">
         <v>1</v>
       </c>
       <c r="E239" s="1" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="F239" s="1" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="240" ht="15" customHeight="1" spans="1:6">
       <c r="A240" s="1"/>
       <c r="B240" s="1">
-        <v>15022</v>
-      </c>
-      <c r="C240" s="1" t="s">
-        <v>486</v>
-      </c>
+        <v>15018</v>
+      </c>
+      <c r="C240" s="1"/>
       <c r="D240" s="1">
         <v>1</v>
       </c>
       <c r="E240" s="1" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="F240" s="1" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="241" ht="15" customHeight="1" spans="1:6">
       <c r="A241" s="1"/>
       <c r="B241" s="1">
-        <v>16001</v>
-      </c>
-      <c r="C241" s="1" t="s">
-        <v>489</v>
-      </c>
+        <v>15019</v>
+      </c>
+      <c r="C241" s="1"/>
       <c r="D241" s="1">
         <v>1</v>
       </c>
       <c r="E241" s="1" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="F241" s="1" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="242" ht="15" customHeight="1" spans="1:6">
       <c r="A242" s="1"/>
       <c r="B242" s="1">
-        <v>16002</v>
-      </c>
-      <c r="C242" s="1" t="s">
-        <v>489</v>
-      </c>
+        <v>15020</v>
+      </c>
+      <c r="C242" s="1"/>
       <c r="D242" s="1">
         <v>1</v>
       </c>
       <c r="E242" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="F242" s="1" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="243" ht="15" customHeight="1" spans="1:6">
       <c r="A243" s="1"/>
       <c r="B243" s="1">
-        <v>16003</v>
-      </c>
-      <c r="C243" s="1" t="s">
-        <v>489</v>
-      </c>
+        <v>15021</v>
+      </c>
+      <c r="C243" s="1"/>
       <c r="D243" s="1">
         <v>1</v>
       </c>
       <c r="E243" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="F243" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="244" ht="15" customHeight="1" spans="1:6">
       <c r="A244" s="1"/>
       <c r="B244" s="1">
-        <v>16004</v>
+        <v>15022</v>
       </c>
       <c r="C244" s="1" t="s">
-        <v>489</v>
+        <v>497</v>
       </c>
       <c r="D244" s="1">
         <v>1</v>
       </c>
       <c r="E244" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="F244" s="1" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="245" ht="15" customHeight="1" spans="1:6">
       <c r="A245" s="1"/>
       <c r="B245" s="1">
-        <v>16005</v>
+        <v>16001</v>
       </c>
       <c r="C245" s="1" t="s">
-        <v>489</v>
+        <v>500</v>
       </c>
       <c r="D245" s="1">
         <v>1</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="F245" s="1" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="246" ht="15" customHeight="1" spans="1:6">
       <c r="A246" s="1"/>
       <c r="B246" s="1">
-        <v>16006</v>
+        <v>16002</v>
       </c>
       <c r="C246" s="1" t="s">
-        <v>489</v>
+        <v>500</v>
       </c>
       <c r="D246" s="1">
         <v>1</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="F246" s="1" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="247" ht="15" customHeight="1" spans="1:6">
       <c r="A247" s="1"/>
       <c r="B247" s="1">
-        <v>19002</v>
-      </c>
-      <c r="C247" s="1"/>
+        <v>16003</v>
+      </c>
+      <c r="C247" s="1" t="s">
+        <v>500</v>
+      </c>
       <c r="D247" s="1">
         <v>1</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="F247" s="1" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
     </row>
     <row r="248" ht="15" customHeight="1" spans="1:6">
       <c r="A248" s="1"/>
       <c r="B248" s="1">
-        <v>19003</v>
-      </c>
-      <c r="C248" s="1"/>
+        <v>16004</v>
+      </c>
+      <c r="C248" s="1" t="s">
+        <v>500</v>
+      </c>
       <c r="D248" s="1">
         <v>1</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="F248" s="1" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
     </row>
     <row r="249" ht="15" customHeight="1" spans="1:6">
       <c r="A249" s="1"/>
       <c r="B249" s="1">
-        <v>19004</v>
-      </c>
-      <c r="C249" s="1"/>
+        <v>16005</v>
+      </c>
+      <c r="C249" s="1" t="s">
+        <v>500</v>
+      </c>
       <c r="D249" s="1">
         <v>1</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="F249" s="1" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="250" ht="15" customHeight="1" spans="1:6">
       <c r="A250" s="1"/>
       <c r="B250" s="1">
-        <v>19012</v>
-      </c>
-      <c r="C250" s="1"/>
+        <v>16006</v>
+      </c>
+      <c r="C250" s="1" t="s">
+        <v>500</v>
+      </c>
       <c r="D250" s="1">
         <v>1</v>
       </c>
       <c r="E250" s="1" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="F250" s="1" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="251" ht="15" customHeight="1" spans="1:6">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="251" ht="14" customHeight="1" spans="1:6">
       <c r="A251" s="1"/>
       <c r="B251" s="1">
-        <v>19013</v>
+        <v>19001</v>
       </c>
       <c r="C251" s="1"/>
       <c r="D251" s="1">
         <v>1</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="F251" s="1" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="252" ht="15" customHeight="1" spans="1:6">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="252" ht="14" customHeight="1" spans="1:6">
       <c r="A252" s="1"/>
       <c r="B252" s="1">
-        <v>19014</v>
+        <v>19002</v>
       </c>
       <c r="C252" s="1"/>
       <c r="D252" s="1">
         <v>1</v>
       </c>
       <c r="E252" s="1" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="F252" s="1" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
     </row>
     <row r="253" ht="15" customHeight="1" spans="1:6">
       <c r="A253" s="1"/>
       <c r="B253" s="1">
-        <v>19022</v>
+        <v>19003</v>
       </c>
       <c r="C253" s="1"/>
       <c r="D253" s="1">
         <v>1</v>
       </c>
       <c r="E253" s="1" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="F253" s="1" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
     </row>
     <row r="254" ht="15" customHeight="1" spans="1:6">
       <c r="A254" s="1"/>
       <c r="B254" s="1">
-        <v>19023</v>
+        <v>19004</v>
       </c>
       <c r="C254" s="1"/>
       <c r="D254" s="1">
         <v>1</v>
       </c>
       <c r="E254" s="1" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="F254" s="1" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="255" ht="15" customHeight="1" spans="1:6">
       <c r="A255" s="1"/>
       <c r="B255" s="1">
-        <v>19024</v>
+        <v>19011</v>
       </c>
       <c r="C255" s="1"/>
       <c r="D255" s="1">
         <v>1</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="F255" s="1" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
     </row>
     <row r="256" ht="15" customHeight="1" spans="1:6">
       <c r="A256" s="1"/>
       <c r="B256" s="1">
-        <v>20101</v>
-      </c>
-      <c r="C256" s="1" t="s">
-        <v>520</v>
-      </c>
+        <v>19012</v>
+      </c>
+      <c r="C256" s="1"/>
       <c r="D256" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E256" s="1" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="F256" s="1" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="257" ht="15" customHeight="1" spans="1:6">
       <c r="A257" s="1"/>
       <c r="B257" s="1">
-        <v>20102</v>
-      </c>
-      <c r="C257" s="1" t="s">
-        <v>520</v>
-      </c>
+        <v>19013</v>
+      </c>
+      <c r="C257" s="1"/>
       <c r="D257" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E257" s="1" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="F257" s="1" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="258" ht="15" customHeight="1" spans="1:6">
       <c r="A258" s="1"/>
       <c r="B258" s="1">
-        <v>20103</v>
-      </c>
-      <c r="C258" s="1" t="s">
-        <v>520</v>
-      </c>
+        <v>19014</v>
+      </c>
+      <c r="C258" s="1"/>
       <c r="D258" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="F258" s="1" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="259" ht="15" customHeight="1" spans="1:6">
       <c r="A259" s="1"/>
       <c r="B259" s="1">
-        <v>20104</v>
-      </c>
-      <c r="C259" s="1" t="s">
-        <v>520</v>
-      </c>
+        <v>19021</v>
+      </c>
+      <c r="C259" s="1"/>
       <c r="D259" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="F259" s="1" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="260" ht="15" customHeight="1" spans="1:6">
       <c r="A260" s="1"/>
       <c r="B260" s="1">
-        <v>20105</v>
-      </c>
-      <c r="C260" s="1" t="s">
-        <v>520</v>
-      </c>
+        <v>19022</v>
+      </c>
+      <c r="C260" s="1"/>
       <c r="D260" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="F260" s="1" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="261" ht="15" customHeight="1" spans="1:6">
       <c r="A261" s="1"/>
       <c r="B261" s="1">
-        <v>20106</v>
-      </c>
-      <c r="C261" s="1" t="s">
-        <v>520</v>
-      </c>
+        <v>19023</v>
+      </c>
+      <c r="C261" s="1"/>
       <c r="D261" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="F261" s="1" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="262" ht="15" customHeight="1" spans="1:6">
       <c r="A262" s="1"/>
       <c r="B262" s="1">
-        <v>20107</v>
-      </c>
-      <c r="C262" s="1" t="s">
-        <v>520</v>
-      </c>
+        <v>19024</v>
+      </c>
+      <c r="C262" s="1"/>
       <c r="D262" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="F262" s="1" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="263" ht="15" customHeight="1" spans="1:6">
       <c r="A263" s="1"/>
       <c r="B263" s="1">
-        <v>20108</v>
+        <v>20101</v>
       </c>
       <c r="C263" s="1" t="s">
-        <v>520</v>
+        <v>537</v>
       </c>
       <c r="D263" s="1">
         <v>2</v>
       </c>
       <c r="E263" s="1" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="F263" s="1" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
     </row>
     <row r="264" ht="15" customHeight="1" spans="1:6">
       <c r="A264" s="1"/>
       <c r="B264" s="1">
-        <v>20109</v>
+        <v>20102</v>
       </c>
       <c r="C264" s="1" t="s">
-        <v>520</v>
+        <v>537</v>
       </c>
       <c r="D264" s="1">
         <v>2</v>
       </c>
       <c r="E264" s="1" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="F264" s="1" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
     </row>
     <row r="265" ht="15" customHeight="1" spans="1:6">
       <c r="A265" s="1"/>
       <c r="B265" s="1">
-        <v>20110</v>
+        <v>20103</v>
       </c>
       <c r="C265" s="1" t="s">
-        <v>520</v>
+        <v>537</v>
       </c>
       <c r="D265" s="1">
         <v>2</v>
       </c>
       <c r="E265" s="1" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="F265" s="1" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
     </row>
     <row r="266" ht="15" customHeight="1" spans="1:6">
       <c r="A266" s="1"/>
       <c r="B266" s="1">
-        <v>20111</v>
+        <v>20104</v>
       </c>
       <c r="C266" s="1" t="s">
-        <v>520</v>
+        <v>537</v>
       </c>
       <c r="D266" s="1">
         <v>2</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="F266" s="1" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
     </row>
     <row r="267" ht="15" customHeight="1" spans="1:6">
       <c r="A267" s="1"/>
       <c r="B267" s="1">
-        <v>20112</v>
+        <v>20105</v>
       </c>
       <c r="C267" s="1" t="s">
-        <v>520</v>
+        <v>537</v>
       </c>
       <c r="D267" s="1">
         <v>2</v>
       </c>
       <c r="E267" s="1" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="F267" s="1" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
     </row>
     <row r="268" ht="15" customHeight="1" spans="1:6">
       <c r="A268" s="1"/>
       <c r="B268" s="1">
-        <v>20113</v>
+        <v>20106</v>
       </c>
       <c r="C268" s="1" t="s">
-        <v>520</v>
+        <v>537</v>
       </c>
       <c r="D268" s="1">
         <v>2</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="F268" s="1" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
     </row>
     <row r="269" ht="15" customHeight="1" spans="1:6">
       <c r="A269" s="1"/>
       <c r="B269" s="1">
-        <v>20114</v>
+        <v>20107</v>
       </c>
       <c r="C269" s="1" t="s">
-        <v>520</v>
+        <v>537</v>
       </c>
       <c r="D269" s="1">
         <v>2</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="F269" s="1" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
     </row>
     <row r="270" ht="15" customHeight="1" spans="1:6">
       <c r="A270" s="1"/>
       <c r="B270" s="1">
-        <v>20115</v>
+        <v>20108</v>
       </c>
       <c r="C270" s="1" t="s">
-        <v>520</v>
+        <v>537</v>
       </c>
       <c r="D270" s="1">
         <v>2</v>
       </c>
       <c r="E270" s="1" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="F270" s="1" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
     </row>
     <row r="271" ht="15" customHeight="1" spans="1:6">
       <c r="A271" s="1"/>
       <c r="B271" s="1">
-        <v>20116</v>
+        <v>20109</v>
       </c>
       <c r="C271" s="1" t="s">
-        <v>520</v>
+        <v>537</v>
       </c>
       <c r="D271" s="1">
         <v>2</v>
       </c>
       <c r="E271" s="1" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="F271" s="1" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
     </row>
     <row r="272" ht="15" customHeight="1" spans="1:6">
       <c r="A272" s="1"/>
       <c r="B272" s="1">
-        <v>20117</v>
+        <v>20110</v>
       </c>
       <c r="C272" s="1" t="s">
-        <v>520</v>
+        <v>537</v>
       </c>
       <c r="D272" s="1">
         <v>2</v>
       </c>
       <c r="E272" s="1" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="F272" s="1" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
     </row>
     <row r="273" ht="15" customHeight="1" spans="1:6">
       <c r="A273" s="1"/>
       <c r="B273" s="1">
-        <v>20118</v>
+        <v>20111</v>
       </c>
       <c r="C273" s="1" t="s">
-        <v>520</v>
+        <v>537</v>
       </c>
       <c r="D273" s="1">
         <v>2</v>
       </c>
       <c r="E273" s="1" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="F273" s="1" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
     </row>
     <row r="274" ht="15" customHeight="1" spans="1:6">
       <c r="A274" s="1"/>
       <c r="B274" s="1">
-        <v>20119</v>
+        <v>20112</v>
       </c>
       <c r="C274" s="1" t="s">
-        <v>520</v>
+        <v>537</v>
       </c>
       <c r="D274" s="1">
         <v>2</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="F274" s="1" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
     </row>
     <row r="275" ht="15" customHeight="1" spans="1:6">
       <c r="A275" s="1"/>
       <c r="B275" s="1">
-        <v>20120</v>
+        <v>20113</v>
       </c>
       <c r="C275" s="1" t="s">
-        <v>520</v>
+        <v>537</v>
       </c>
       <c r="D275" s="1">
         <v>2</v>
       </c>
       <c r="E275" s="1" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="F275" s="1" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
     </row>
     <row r="276" ht="15" customHeight="1" spans="1:6">
       <c r="A276" s="1"/>
       <c r="B276" s="1">
-        <v>20121</v>
+        <v>20114</v>
       </c>
       <c r="C276" s="1" t="s">
-        <v>520</v>
+        <v>537</v>
       </c>
       <c r="D276" s="1">
         <v>2</v>
       </c>
       <c r="E276" s="1" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="F276" s="1" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
     </row>
     <row r="277" ht="15" customHeight="1" spans="1:6">
       <c r="A277" s="1"/>
       <c r="B277" s="1">
-        <v>20122</v>
+        <v>20115</v>
       </c>
       <c r="C277" s="1" t="s">
-        <v>520</v>
+        <v>537</v>
       </c>
       <c r="D277" s="1">
         <v>2</v>
       </c>
       <c r="E277" s="1" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="F277" s="1" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
     </row>
     <row r="278" ht="15" customHeight="1" spans="1:6">
       <c r="A278" s="1"/>
       <c r="B278" s="1">
-        <v>20123</v>
+        <v>20116</v>
       </c>
       <c r="C278" s="1" t="s">
-        <v>520</v>
+        <v>537</v>
       </c>
       <c r="D278" s="1">
         <v>2</v>
       </c>
       <c r="E278" s="1" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="F278" s="1" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
     </row>
     <row r="279" ht="15" customHeight="1" spans="1:6">
       <c r="A279" s="1"/>
       <c r="B279" s="1">
-        <v>20124</v>
+        <v>20117</v>
       </c>
       <c r="C279" s="1" t="s">
-        <v>520</v>
+        <v>537</v>
       </c>
       <c r="D279" s="1">
         <v>2</v>
       </c>
       <c r="E279" s="1" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="F279" s="1" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
     </row>
     <row r="280" ht="15" customHeight="1" spans="1:6">
       <c r="A280" s="1"/>
       <c r="B280" s="1">
-        <v>20125</v>
+        <v>20118</v>
       </c>
       <c r="C280" s="1" t="s">
-        <v>520</v>
+        <v>537</v>
       </c>
       <c r="D280" s="1">
         <v>2</v>
       </c>
       <c r="E280" s="1" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="F280" s="1" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
     </row>
     <row r="281" ht="15" customHeight="1" spans="1:6">
       <c r="A281" s="1"/>
       <c r="B281" s="1">
-        <v>20126</v>
+        <v>20119</v>
       </c>
       <c r="C281" s="1" t="s">
-        <v>520</v>
+        <v>537</v>
       </c>
       <c r="D281" s="1">
         <v>2</v>
       </c>
       <c r="E281" s="1" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="F281" s="1" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
     </row>
     <row r="282" ht="15" customHeight="1" spans="1:6">
       <c r="A282" s="1"/>
       <c r="B282" s="1">
-        <v>20127</v>
+        <v>20120</v>
       </c>
       <c r="C282" s="1" t="s">
-        <v>520</v>
+        <v>537</v>
       </c>
       <c r="D282" s="1">
         <v>2</v>
       </c>
       <c r="E282" s="1" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="F282" s="1" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
     </row>
     <row r="283" ht="15" customHeight="1" spans="1:6">
       <c r="A283" s="1"/>
       <c r="B283" s="1">
-        <v>30101</v>
+        <v>20121</v>
       </c>
       <c r="C283" s="1" t="s">
-        <v>520</v>
+        <v>537</v>
       </c>
       <c r="D283" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E283" s="1" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="F283" s="1" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
     </row>
     <row r="284" ht="15" customHeight="1" spans="1:6">
       <c r="A284" s="1"/>
       <c r="B284" s="1">
-        <v>30102</v>
+        <v>20122</v>
       </c>
       <c r="C284" s="1" t="s">
-        <v>520</v>
+        <v>537</v>
       </c>
       <c r="D284" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E284" s="1" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="F284" s="1" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
     </row>
     <row r="285" ht="15" customHeight="1" spans="1:6">
       <c r="A285" s="1"/>
       <c r="B285" s="1">
-        <v>30103</v>
+        <v>20123</v>
       </c>
       <c r="C285" s="1" t="s">
-        <v>520</v>
+        <v>537</v>
       </c>
       <c r="D285" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E285" s="1" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="F285" s="1" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
     </row>
     <row r="286" ht="15" customHeight="1" spans="1:6">
       <c r="A286" s="1"/>
       <c r="B286" s="1">
-        <v>30104</v>
+        <v>20124</v>
       </c>
       <c r="C286" s="1" t="s">
-        <v>520</v>
+        <v>537</v>
       </c>
       <c r="D286" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="F286" s="1" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
     </row>
     <row r="287" ht="15" customHeight="1" spans="1:6">
       <c r="A287" s="1"/>
       <c r="B287" s="1">
-        <v>30105</v>
+        <v>20125</v>
       </c>
       <c r="C287" s="1" t="s">
-        <v>520</v>
+        <v>537</v>
       </c>
       <c r="D287" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="F287" s="1" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
     </row>
     <row r="288" ht="15" customHeight="1" spans="1:6">
       <c r="A288" s="1"/>
       <c r="B288" s="1">
-        <v>30106</v>
+        <v>20126</v>
       </c>
       <c r="C288" s="1" t="s">
-        <v>520</v>
+        <v>537</v>
       </c>
       <c r="D288" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="F288" s="1" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
     </row>
     <row r="289" ht="15" customHeight="1" spans="1:6">
       <c r="A289" s="1"/>
       <c r="B289" s="1">
-        <v>30107</v>
+        <v>20127</v>
       </c>
       <c r="C289" s="1" t="s">
-        <v>520</v>
+        <v>537</v>
       </c>
       <c r="D289" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E289" s="1" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="F289" s="1" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
     </row>
     <row r="290" ht="15" customHeight="1" spans="1:6">
       <c r="A290" s="1"/>
       <c r="B290" s="1">
-        <v>30108</v>
+        <v>30101</v>
       </c>
       <c r="C290" s="1" t="s">
-        <v>520</v>
+        <v>537</v>
       </c>
       <c r="D290" s="1">
         <v>3</v>
       </c>
       <c r="E290" s="1" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="F290" s="1" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
     </row>
     <row r="291" ht="15" customHeight="1" spans="1:6">
       <c r="A291" s="1"/>
       <c r="B291" s="1">
-        <v>30109</v>
+        <v>30102</v>
       </c>
       <c r="C291" s="1" t="s">
-        <v>520</v>
+        <v>537</v>
       </c>
       <c r="D291" s="1">
         <v>3</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="F291" s="1" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
     </row>
     <row r="292" ht="15" customHeight="1" spans="1:6">
       <c r="A292" s="1"/>
       <c r="B292" s="1">
-        <v>30110</v>
+        <v>30103</v>
       </c>
       <c r="C292" s="1" t="s">
-        <v>520</v>
+        <v>537</v>
       </c>
       <c r="D292" s="1">
         <v>3</v>
       </c>
       <c r="E292" s="1" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="F292" s="1" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
     </row>
     <row r="293" ht="15" customHeight="1" spans="1:6">
       <c r="A293" s="1"/>
       <c r="B293" s="1">
-        <v>30111</v>
+        <v>30104</v>
       </c>
       <c r="C293" s="1" t="s">
-        <v>520</v>
+        <v>537</v>
       </c>
       <c r="D293" s="1">
         <v>3</v>
       </c>
       <c r="E293" s="1" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="F293" s="1" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
     </row>
     <row r="294" ht="15" customHeight="1" spans="1:6">
       <c r="A294" s="1"/>
       <c r="B294" s="1">
-        <v>30112</v>
+        <v>30105</v>
       </c>
       <c r="C294" s="1" t="s">
-        <v>520</v>
+        <v>537</v>
       </c>
       <c r="D294" s="1">
         <v>3</v>
       </c>
       <c r="E294" s="1" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="F294" s="1" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
     </row>
     <row r="295" ht="15" customHeight="1" spans="1:6">
       <c r="A295" s="1"/>
       <c r="B295" s="1">
-        <v>30113</v>
+        <v>30106</v>
       </c>
       <c r="C295" s="1" t="s">
-        <v>520</v>
+        <v>537</v>
       </c>
       <c r="D295" s="1">
         <v>3</v>
       </c>
       <c r="E295" s="1" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="F295" s="1" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
     </row>
     <row r="296" ht="15" customHeight="1" spans="1:6">
       <c r="A296" s="1"/>
       <c r="B296" s="1">
-        <v>30114</v>
+        <v>30107</v>
       </c>
       <c r="C296" s="1" t="s">
-        <v>520</v>
+        <v>537</v>
       </c>
       <c r="D296" s="1">
         <v>3</v>
       </c>
       <c r="E296" s="1" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="F296" s="1" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
     </row>
     <row r="297" ht="15" customHeight="1" spans="1:6">
       <c r="A297" s="1"/>
       <c r="B297" s="1">
-        <v>30115</v>
+        <v>30108</v>
       </c>
       <c r="C297" s="1" t="s">
-        <v>520</v>
+        <v>537</v>
       </c>
       <c r="D297" s="1">
         <v>3</v>
       </c>
       <c r="E297" s="1" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="F297" s="1" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
     </row>
     <row r="298" ht="15" customHeight="1" spans="1:6">
       <c r="A298" s="1"/>
       <c r="B298" s="1">
-        <v>30116</v>
+        <v>30109</v>
       </c>
       <c r="C298" s="1" t="s">
-        <v>520</v>
+        <v>537</v>
       </c>
       <c r="D298" s="1">
         <v>3</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="F298" s="1" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
     </row>
     <row r="299" ht="15" customHeight="1" spans="1:6">
       <c r="A299" s="1"/>
       <c r="B299" s="1">
-        <v>30117</v>
+        <v>30110</v>
       </c>
       <c r="C299" s="1" t="s">
-        <v>520</v>
+        <v>537</v>
       </c>
       <c r="D299" s="1">
         <v>3</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="F299" s="1" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
     </row>
     <row r="300" ht="15" customHeight="1" spans="1:6">
       <c r="A300" s="1"/>
       <c r="B300" s="1">
-        <v>30118</v>
+        <v>30111</v>
       </c>
       <c r="C300" s="1" t="s">
-        <v>520</v>
+        <v>537</v>
       </c>
       <c r="D300" s="1">
         <v>3</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="F300" s="1" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
     </row>
     <row r="301" ht="15" customHeight="1" spans="1:6">
       <c r="A301" s="1"/>
       <c r="B301" s="1">
-        <v>30119</v>
+        <v>30112</v>
       </c>
       <c r="C301" s="1" t="s">
-        <v>520</v>
+        <v>537</v>
       </c>
       <c r="D301" s="1">
         <v>3</v>
       </c>
       <c r="E301" s="1" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="F301" s="1" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
     </row>
     <row r="302" ht="15" customHeight="1" spans="1:6">
       <c r="A302" s="1"/>
       <c r="B302" s="1">
-        <v>30120</v>
+        <v>30113</v>
       </c>
       <c r="C302" s="1" t="s">
-        <v>520</v>
+        <v>537</v>
       </c>
       <c r="D302" s="1">
         <v>3</v>
       </c>
       <c r="E302" s="1" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="F302" s="1" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
     </row>
     <row r="303" ht="15" customHeight="1" spans="1:6">
       <c r="A303" s="1"/>
       <c r="B303" s="1">
-        <v>30121</v>
+        <v>30114</v>
       </c>
       <c r="C303" s="1" t="s">
-        <v>520</v>
+        <v>537</v>
       </c>
       <c r="D303" s="1">
         <v>3</v>
       </c>
       <c r="E303" s="1" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="F303" s="1" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
     </row>
     <row r="304" ht="15" customHeight="1" spans="1:6">
       <c r="A304" s="1"/>
       <c r="B304" s="1">
-        <v>30122</v>
+        <v>30115</v>
       </c>
       <c r="C304" s="1" t="s">
-        <v>520</v>
+        <v>537</v>
       </c>
       <c r="D304" s="1">
         <v>3</v>
       </c>
       <c r="E304" s="1" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="F304" s="1" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
     </row>
     <row r="305" ht="15" customHeight="1" spans="1:6">
       <c r="A305" s="1"/>
       <c r="B305" s="1">
-        <v>30123</v>
+        <v>30116</v>
       </c>
       <c r="C305" s="1" t="s">
-        <v>520</v>
+        <v>537</v>
       </c>
       <c r="D305" s="1">
         <v>3</v>
       </c>
       <c r="E305" s="1" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="F305" s="1" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
     </row>
     <row r="306" ht="15" customHeight="1" spans="1:6">
       <c r="A306" s="1"/>
       <c r="B306" s="1">
-        <v>30124</v>
+        <v>30117</v>
       </c>
       <c r="C306" s="1" t="s">
-        <v>520</v>
+        <v>537</v>
       </c>
       <c r="D306" s="1">
         <v>3</v>
       </c>
       <c r="E306" s="1" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="F306" s="1" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
     </row>
     <row r="307" ht="15" customHeight="1" spans="1:6">
       <c r="A307" s="1"/>
       <c r="B307" s="1">
-        <v>30125</v>
+        <v>30118</v>
       </c>
       <c r="C307" s="1" t="s">
-        <v>520</v>
+        <v>537</v>
       </c>
       <c r="D307" s="1">
         <v>3</v>
       </c>
       <c r="E307" s="1" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="F307" s="1" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
     </row>
     <row r="308" ht="15" customHeight="1" spans="1:6">
       <c r="A308" s="1"/>
       <c r="B308" s="1">
-        <v>30201</v>
+        <v>30119</v>
       </c>
       <c r="C308" s="1" t="s">
-        <v>520</v>
+        <v>537</v>
       </c>
       <c r="D308" s="1">
         <v>3</v>
       </c>
       <c r="E308" s="1" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="F308" s="1" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
     </row>
     <row r="309" ht="15" customHeight="1" spans="1:6">
       <c r="A309" s="1"/>
       <c r="B309" s="1">
-        <v>30202</v>
+        <v>30120</v>
       </c>
       <c r="C309" s="1" t="s">
-        <v>520</v>
+        <v>537</v>
       </c>
       <c r="D309" s="1">
         <v>3</v>
       </c>
       <c r="E309" s="1" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="F309" s="1" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
     </row>
     <row r="310" ht="15" customHeight="1" spans="1:6">
       <c r="A310" s="1"/>
       <c r="B310" s="1">
-        <v>30203</v>
+        <v>30121</v>
       </c>
       <c r="C310" s="1" t="s">
-        <v>520</v>
+        <v>537</v>
       </c>
       <c r="D310" s="1">
         <v>3</v>
       </c>
       <c r="E310" s="1" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="F310" s="1" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
     </row>
     <row r="311" ht="15" customHeight="1" spans="1:6">
       <c r="A311" s="1"/>
       <c r="B311" s="1">
-        <v>30204</v>
+        <v>30122</v>
       </c>
       <c r="C311" s="1" t="s">
-        <v>520</v>
+        <v>537</v>
       </c>
       <c r="D311" s="1">
         <v>3</v>
       </c>
       <c r="E311" s="1" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="F311" s="1" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
     </row>
     <row r="312" ht="15" customHeight="1" spans="1:6">
       <c r="A312" s="1"/>
       <c r="B312" s="1">
-        <v>30205</v>
+        <v>30123</v>
       </c>
       <c r="C312" s="1" t="s">
-        <v>520</v>
+        <v>537</v>
       </c>
       <c r="D312" s="1">
         <v>3</v>
       </c>
       <c r="E312" s="1" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="F312" s="1" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
     </row>
     <row r="313" ht="15" customHeight="1" spans="1:6">
       <c r="A313" s="1"/>
       <c r="B313" s="1">
-        <v>30206</v>
+        <v>30124</v>
       </c>
       <c r="C313" s="1" t="s">
-        <v>520</v>
+        <v>537</v>
       </c>
       <c r="D313" s="1">
         <v>3</v>
       </c>
       <c r="E313" s="1" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="F313" s="1" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
     </row>
     <row r="314" ht="15" customHeight="1" spans="1:6">
       <c r="A314" s="1"/>
       <c r="B314" s="1">
-        <v>30301</v>
+        <v>30125</v>
       </c>
       <c r="C314" s="1" t="s">
-        <v>520</v>
+        <v>537</v>
       </c>
       <c r="D314" s="1">
         <v>3</v>
       </c>
       <c r="E314" s="1" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="F314" s="1" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
     </row>
     <row r="315" ht="15" customHeight="1" spans="1:6">
       <c r="A315" s="1"/>
       <c r="B315" s="1">
-        <v>30302</v>
+        <v>30201</v>
       </c>
       <c r="C315" s="1" t="s">
-        <v>520</v>
+        <v>537</v>
       </c>
       <c r="D315" s="1">
         <v>3</v>
       </c>
       <c r="E315" s="1" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="F315" s="1" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
     </row>
     <row r="316" ht="15" customHeight="1" spans="1:6">
       <c r="A316" s="1"/>
       <c r="B316" s="1">
-        <v>30303</v>
+        <v>30202</v>
       </c>
       <c r="C316" s="1" t="s">
-        <v>520</v>
+        <v>537</v>
       </c>
       <c r="D316" s="1">
         <v>3</v>
       </c>
       <c r="E316" s="1" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="F316" s="1" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
     </row>
     <row r="317" ht="15" customHeight="1" spans="1:6">
       <c r="A317" s="1"/>
       <c r="B317" s="1">
-        <v>30304</v>
+        <v>30203</v>
       </c>
       <c r="C317" s="1" t="s">
-        <v>520</v>
+        <v>537</v>
       </c>
       <c r="D317" s="1">
         <v>3</v>
       </c>
       <c r="E317" s="1" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="F317" s="1" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
     </row>
     <row r="318" ht="15" customHeight="1" spans="1:6">
       <c r="A318" s="1"/>
       <c r="B318" s="1">
-        <v>30305</v>
+        <v>30204</v>
       </c>
       <c r="C318" s="1" t="s">
-        <v>520</v>
+        <v>537</v>
       </c>
       <c r="D318" s="1">
         <v>3</v>
       </c>
       <c r="E318" s="1" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="F318" s="1" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
     </row>
     <row r="319" ht="15" customHeight="1" spans="1:6">
       <c r="A319" s="1"/>
       <c r="B319" s="1">
-        <v>30306</v>
+        <v>30205</v>
       </c>
       <c r="C319" s="1" t="s">
-        <v>520</v>
+        <v>537</v>
       </c>
       <c r="D319" s="1">
         <v>3</v>
       </c>
       <c r="E319" s="1" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="F319" s="1" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
     </row>
     <row r="320" ht="15" customHeight="1" spans="1:6">
       <c r="A320" s="1"/>
       <c r="B320" s="1">
-        <v>30307</v>
+        <v>30206</v>
       </c>
       <c r="C320" s="1" t="s">
-        <v>520</v>
+        <v>537</v>
       </c>
       <c r="D320" s="1">
         <v>3</v>
       </c>
       <c r="E320" s="1" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="F320" s="1" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
     </row>
     <row r="321" ht="15" customHeight="1" spans="1:6">
       <c r="A321" s="1"/>
       <c r="B321" s="1">
-        <v>30308</v>
+        <v>30301</v>
       </c>
       <c r="C321" s="1" t="s">
-        <v>520</v>
+        <v>537</v>
       </c>
       <c r="D321" s="1">
         <v>3</v>
       </c>
       <c r="E321" s="1" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="F321" s="1" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
     </row>
     <row r="322" ht="15" customHeight="1" spans="1:6">
       <c r="A322" s="1"/>
       <c r="B322" s="1">
-        <v>60001</v>
+        <v>30302</v>
       </c>
       <c r="C322" s="1" t="s">
-        <v>653</v>
+        <v>537</v>
       </c>
       <c r="D322" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E322" s="1" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="F322" s="1" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
     </row>
     <row r="323" ht="15" customHeight="1" spans="1:6">
       <c r="A323" s="1"/>
       <c r="B323" s="1">
-        <v>60002</v>
+        <v>30303</v>
       </c>
       <c r="C323" s="1" t="s">
-        <v>653</v>
+        <v>537</v>
       </c>
       <c r="D323" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E323" s="1" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="F323" s="1" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
     </row>
     <row r="324" ht="15" customHeight="1" spans="1:6">
       <c r="A324" s="1"/>
       <c r="B324" s="1">
-        <v>60003</v>
+        <v>30304</v>
       </c>
       <c r="C324" s="1" t="s">
-        <v>653</v>
+        <v>537</v>
       </c>
       <c r="D324" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E324" s="1" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="F324" s="1" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
     </row>
     <row r="325" ht="15" customHeight="1" spans="1:6">
       <c r="A325" s="1"/>
       <c r="B325" s="1">
-        <v>60004</v>
+        <v>30305</v>
       </c>
       <c r="C325" s="1" t="s">
-        <v>653</v>
+        <v>537</v>
       </c>
       <c r="D325" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E325" s="1" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="F325" s="1" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
     </row>
     <row r="326" ht="15" customHeight="1" spans="1:6">
       <c r="A326" s="1"/>
       <c r="B326" s="1">
-        <v>60005</v>
+        <v>30306</v>
       </c>
       <c r="C326" s="1" t="s">
-        <v>653</v>
+        <v>537</v>
       </c>
       <c r="D326" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E326" s="1" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="F326" s="1" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
     </row>
     <row r="327" ht="15" customHeight="1" spans="1:6">
       <c r="A327" s="1"/>
       <c r="B327" s="1">
-        <v>60006</v>
+        <v>30307</v>
       </c>
       <c r="C327" s="1" t="s">
-        <v>653</v>
+        <v>537</v>
       </c>
       <c r="D327" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E327" s="1" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="F327" s="1" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
     </row>
     <row r="328" ht="15" customHeight="1" spans="1:6">
       <c r="A328" s="1"/>
       <c r="B328" s="1">
-        <v>60007</v>
+        <v>30308</v>
       </c>
       <c r="C328" s="1" t="s">
-        <v>653</v>
+        <v>537</v>
       </c>
       <c r="D328" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E328" s="1" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="F328" s="1" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="329" ht="15" customHeight="1" spans="1:6">
       <c r="A329" s="1"/>
       <c r="B329" s="1">
-        <v>60008</v>
+        <v>60001</v>
       </c>
       <c r="C329" s="1" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="D329" s="1">
         <v>7</v>
       </c>
       <c r="E329" s="1" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="F329" s="1" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
     </row>
     <row r="330" ht="15" customHeight="1" spans="1:6">
       <c r="A330" s="1"/>
       <c r="B330" s="1">
-        <v>60009</v>
+        <v>60002</v>
       </c>
       <c r="C330" s="1" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="D330" s="1">
         <v>7</v>
       </c>
       <c r="E330" s="1" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="F330" s="1" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
     </row>
     <row r="331" ht="15" customHeight="1" spans="1:6">
       <c r="A331" s="1"/>
       <c r="B331" s="1">
-        <v>60010</v>
+        <v>60003</v>
       </c>
       <c r="C331" s="1" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="D331" s="1">
         <v>7</v>
       </c>
       <c r="E331" s="1" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="F331" s="1" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
     </row>
     <row r="332" ht="15" customHeight="1" spans="1:6">
       <c r="A332" s="1"/>
       <c r="B332" s="1">
-        <v>60011</v>
+        <v>60004</v>
       </c>
       <c r="C332" s="1" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="D332" s="1">
         <v>7</v>
       </c>
       <c r="E332" s="1" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="F332" s="1" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
     </row>
     <row r="333" ht="15" customHeight="1" spans="1:6">
       <c r="A333" s="1"/>
       <c r="B333" s="1">
-        <v>60012</v>
+        <v>60005</v>
       </c>
       <c r="C333" s="1" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="D333" s="1">
         <v>7</v>
       </c>
       <c r="E333" s="1" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="F333" s="1" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
     </row>
     <row r="334" ht="15" customHeight="1" spans="1:6">
       <c r="A334" s="1"/>
       <c r="B334" s="1">
-        <v>60013</v>
+        <v>60006</v>
       </c>
       <c r="C334" s="1" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="D334" s="1">
         <v>7</v>
       </c>
       <c r="E334" s="1" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="F334" s="1" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
     </row>
     <row r="335" ht="15" customHeight="1" spans="1:6">
       <c r="A335" s="1"/>
       <c r="B335" s="1">
-        <v>60014</v>
+        <v>60007</v>
       </c>
       <c r="C335" s="1" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="D335" s="1">
         <v>7</v>
       </c>
       <c r="E335" s="1" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="F335" s="1" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
     </row>
     <row r="336" ht="15" customHeight="1" spans="1:6">
       <c r="A336" s="1"/>
       <c r="B336" s="1">
-        <v>60015</v>
+        <v>60008</v>
       </c>
       <c r="C336" s="1" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="D336" s="1">
         <v>7</v>
       </c>
       <c r="E336" s="1" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="F336" s="1" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
     </row>
     <row r="337" ht="15" customHeight="1" spans="1:6">
       <c r="A337" s="1"/>
       <c r="B337" s="1">
-        <v>60016</v>
+        <v>60009</v>
       </c>
       <c r="C337" s="1" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="D337" s="1">
         <v>7</v>
       </c>
       <c r="E337" s="1" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="F337" s="1" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
     </row>
     <row r="338" ht="15" customHeight="1" spans="1:6">
       <c r="A338" s="1"/>
       <c r="B338" s="1">
-        <v>60017</v>
+        <v>60010</v>
       </c>
       <c r="C338" s="1" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="D338" s="1">
         <v>7</v>
       </c>
       <c r="E338" s="1" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="F338" s="1" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
     </row>
     <row r="339" ht="15" customHeight="1" spans="1:6">
       <c r="A339" s="1"/>
       <c r="B339" s="1">
-        <v>60018</v>
+        <v>60011</v>
       </c>
       <c r="C339" s="1" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="D339" s="1">
         <v>7</v>
       </c>
       <c r="E339" s="1" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="F339" s="1" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
     </row>
     <row r="340" ht="15" customHeight="1" spans="1:6">
       <c r="A340" s="1"/>
       <c r="B340" s="1">
-        <v>60019</v>
+        <v>60012</v>
       </c>
       <c r="C340" s="1" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="D340" s="1">
         <v>7</v>
       </c>
       <c r="E340" s="1" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="F340" s="1" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
     </row>
     <row r="341" ht="15" customHeight="1" spans="1:6">
       <c r="A341" s="1"/>
       <c r="B341" s="1">
-        <v>60020</v>
+        <v>60013</v>
       </c>
       <c r="C341" s="1" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="D341" s="1">
         <v>7</v>
       </c>
       <c r="E341" s="1" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="F341" s="1" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
     </row>
     <row r="342" ht="15" customHeight="1" spans="1:6">
       <c r="A342" s="1"/>
       <c r="B342" s="1">
-        <v>60021</v>
+        <v>60014</v>
       </c>
       <c r="C342" s="1" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="D342" s="1">
         <v>7</v>
       </c>
       <c r="E342" s="1" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="F342" s="1" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
     </row>
     <row r="343" ht="15" customHeight="1" spans="1:6">
       <c r="A343" s="1"/>
       <c r="B343" s="1">
-        <v>60022</v>
+        <v>60015</v>
       </c>
       <c r="C343" s="1" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="D343" s="1">
         <v>7</v>
       </c>
       <c r="E343" s="1" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="F343" s="1" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
     </row>
     <row r="344" ht="15" customHeight="1" spans="1:6">
       <c r="A344" s="1"/>
       <c r="B344" s="1">
-        <v>60023</v>
+        <v>60016</v>
       </c>
       <c r="C344" s="1" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="D344" s="1">
         <v>7</v>
       </c>
       <c r="E344" s="1" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="F344" s="1" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
     </row>
     <row r="345" ht="15" customHeight="1" spans="1:6">
       <c r="A345" s="1"/>
       <c r="B345" s="1">
-        <v>60024</v>
+        <v>60017</v>
       </c>
       <c r="C345" s="1" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="D345" s="1">
         <v>7</v>
       </c>
       <c r="E345" s="1" t="s">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="F345" s="1" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
     </row>
     <row r="346" ht="15" customHeight="1" spans="1:6">
       <c r="A346" s="1"/>
       <c r="B346" s="1">
-        <v>60025</v>
+        <v>60018</v>
       </c>
       <c r="C346" s="1" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="D346" s="1">
         <v>7</v>
       </c>
       <c r="E346" s="1" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="F346" s="1" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
     </row>
     <row r="347" ht="15" customHeight="1" spans="1:6">
       <c r="A347" s="1"/>
       <c r="B347" s="1">
-        <v>60026</v>
+        <v>60019</v>
       </c>
       <c r="C347" s="1" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="D347" s="1">
         <v>7</v>
       </c>
       <c r="E347" s="1" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="F347" s="1" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
     </row>
     <row r="348" ht="15" customHeight="1" spans="1:6">
       <c r="A348" s="1"/>
       <c r="B348" s="1">
-        <v>60027</v>
+        <v>60020</v>
       </c>
       <c r="C348" s="1" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="D348" s="1">
         <v>7</v>
       </c>
       <c r="E348" s="1" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="F348" s="1" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
     </row>
     <row r="349" ht="15" customHeight="1" spans="1:6">
       <c r="A349" s="1"/>
       <c r="B349" s="1">
-        <v>60028</v>
+        <v>60021</v>
       </c>
       <c r="C349" s="1" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="D349" s="1">
         <v>7</v>
       </c>
       <c r="E349" s="1" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="F349" s="1" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
     </row>
     <row r="350" ht="15" customHeight="1" spans="1:6">
       <c r="A350" s="1"/>
       <c r="B350" s="1">
-        <v>60029</v>
+        <v>60022</v>
       </c>
       <c r="C350" s="1" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="D350" s="1">
         <v>7</v>
       </c>
       <c r="E350" s="1" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="F350" s="1" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
     </row>
     <row r="351" ht="15" customHeight="1" spans="1:6">
       <c r="A351" s="1"/>
       <c r="B351" s="1">
-        <v>60030</v>
+        <v>60023</v>
       </c>
       <c r="C351" s="1" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="D351" s="1">
         <v>7</v>
       </c>
       <c r="E351" s="1" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="F351" s="1" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
     </row>
     <row r="352" ht="15" customHeight="1" spans="1:6">
       <c r="A352" s="1"/>
       <c r="B352" s="1">
-        <v>60031</v>
+        <v>60024</v>
       </c>
       <c r="C352" s="1" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="D352" s="1">
         <v>7</v>
       </c>
       <c r="E352" s="1" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="F352" s="1" t="s">
-        <v>715</v>
+        <v>718</v>
       </c>
     </row>
     <row r="353" ht="15" customHeight="1" spans="1:6">
       <c r="A353" s="1"/>
       <c r="B353" s="1">
-        <v>60032</v>
+        <v>60025</v>
       </c>
       <c r="C353" s="1" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="D353" s="1">
         <v>7</v>
       </c>
       <c r="E353" s="1" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="F353" s="1" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
     </row>
     <row r="354" ht="15" customHeight="1" spans="1:6">
       <c r="A354" s="1"/>
       <c r="B354" s="1">
-        <v>60033</v>
+        <v>60026</v>
       </c>
       <c r="C354" s="1" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="D354" s="1">
         <v>7</v>
       </c>
       <c r="E354" s="1" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="F354" s="1" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
     </row>
     <row r="355" ht="15" customHeight="1" spans="1:6">
       <c r="A355" s="1"/>
       <c r="B355" s="1">
-        <v>60034</v>
+        <v>60027</v>
       </c>
       <c r="C355" s="1" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="D355" s="1">
         <v>7</v>
       </c>
       <c r="E355" s="1" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="F355" s="1" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
     </row>
     <row r="356" ht="15" customHeight="1" spans="1:6">
       <c r="A356" s="1"/>
       <c r="B356" s="1">
-        <v>60035</v>
+        <v>60028</v>
       </c>
       <c r="C356" s="1" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="D356" s="1">
         <v>7</v>
       </c>
       <c r="E356" s="1" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="F356" s="1" t="s">
-        <v>723</v>
+        <v>726</v>
       </c>
     </row>
     <row r="357" ht="15" customHeight="1" spans="1:6">
       <c r="A357" s="1"/>
       <c r="B357" s="1">
-        <v>60036</v>
+        <v>60029</v>
       </c>
       <c r="C357" s="1" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="D357" s="1">
         <v>7</v>
       </c>
       <c r="E357" s="1" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="F357" s="1" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
     </row>
     <row r="358" ht="15" customHeight="1" spans="1:6">
       <c r="A358" s="1"/>
       <c r="B358" s="1">
-        <v>60037</v>
+        <v>60030</v>
       </c>
       <c r="C358" s="1" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="D358" s="1">
         <v>7</v>
       </c>
       <c r="E358" s="1" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="F358" s="1" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
     </row>
     <row r="359" ht="15" customHeight="1" spans="1:6">
       <c r="A359" s="1"/>
       <c r="B359" s="1">
-        <v>60038</v>
+        <v>60031</v>
       </c>
       <c r="C359" s="1" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="D359" s="1">
         <v>7</v>
       </c>
       <c r="E359" s="1" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="F359" s="1" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
     </row>
     <row r="360" ht="15" customHeight="1" spans="1:6">
       <c r="A360" s="1"/>
       <c r="B360" s="1">
-        <v>60039</v>
+        <v>60032</v>
       </c>
       <c r="C360" s="1" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="D360" s="1">
         <v>7</v>
       </c>
       <c r="E360" s="1" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="F360" s="1" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
     </row>
     <row r="361" ht="15" customHeight="1" spans="1:6">
       <c r="A361" s="1"/>
       <c r="B361" s="1">
-        <v>60040</v>
+        <v>60033</v>
       </c>
       <c r="C361" s="1" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="D361" s="1">
         <v>7</v>
       </c>
       <c r="E361" s="1" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="F361" s="1" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
     </row>
     <row r="362" ht="15" customHeight="1" spans="1:6">
       <c r="A362" s="1"/>
       <c r="B362" s="1">
-        <v>60041</v>
+        <v>60034</v>
       </c>
       <c r="C362" s="1" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="D362" s="1">
         <v>7</v>
       </c>
       <c r="E362" s="1" t="s">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="F362" s="1" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
     </row>
     <row r="363" ht="15" customHeight="1" spans="1:6">
       <c r="A363" s="1"/>
       <c r="B363" s="1">
-        <v>60042</v>
+        <v>60035</v>
       </c>
       <c r="C363" s="1" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="D363" s="1">
         <v>7</v>
       </c>
       <c r="E363" s="1" t="s">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="F363" s="1" t="s">
-        <v>737</v>
+        <v>740</v>
       </c>
     </row>
     <row r="364" ht="15" customHeight="1" spans="1:6">
       <c r="A364" s="1"/>
       <c r="B364" s="1">
-        <v>60043</v>
+        <v>60036</v>
       </c>
       <c r="C364" s="1" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="D364" s="1">
         <v>7</v>
       </c>
       <c r="E364" s="1" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="F364" s="1" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
     </row>
     <row r="365" ht="15" customHeight="1" spans="1:6">
       <c r="A365" s="1"/>
       <c r="B365" s="1">
-        <v>60044</v>
+        <v>60037</v>
       </c>
       <c r="C365" s="1" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="D365" s="1">
         <v>7</v>
       </c>
       <c r="E365" s="1" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="F365" s="1" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
     </row>
     <row r="366" ht="15" customHeight="1" spans="1:6">
       <c r="A366" s="1"/>
       <c r="B366" s="1">
-        <v>60045</v>
+        <v>60038</v>
       </c>
       <c r="C366" s="1" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="D366" s="1">
         <v>7</v>
       </c>
       <c r="E366" s="1" t="s">
-        <v>742</v>
+        <v>745</v>
       </c>
       <c r="F366" s="1" t="s">
-        <v>743</v>
+        <v>746</v>
       </c>
     </row>
     <row r="367" ht="15" customHeight="1" spans="1:6">
       <c r="A367" s="1"/>
       <c r="B367" s="1">
-        <v>60046</v>
+        <v>60039</v>
       </c>
       <c r="C367" s="1" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="D367" s="1">
         <v>7</v>
       </c>
       <c r="E367" s="1" t="s">
-        <v>744</v>
+        <v>747</v>
       </c>
       <c r="F367" s="1" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
     </row>
     <row r="368" ht="15" customHeight="1" spans="1:6">
       <c r="A368" s="1"/>
       <c r="B368" s="1">
-        <v>60047</v>
+        <v>60040</v>
       </c>
       <c r="C368" s="1" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="D368" s="1">
         <v>7</v>
       </c>
       <c r="E368" s="1" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="F368" s="1" t="s">
-        <v>747</v>
+        <v>750</v>
       </c>
     </row>
     <row r="369" ht="15" customHeight="1" spans="1:6">
       <c r="A369" s="1"/>
       <c r="B369" s="1">
-        <v>60048</v>
+        <v>60041</v>
       </c>
       <c r="C369" s="1" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="D369" s="1">
         <v>7</v>
       </c>
       <c r="E369" s="1" t="s">
-        <v>748</v>
+        <v>751</v>
       </c>
       <c r="F369" s="1" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
     </row>
     <row r="370" ht="15" customHeight="1" spans="1:6">
       <c r="A370" s="1"/>
       <c r="B370" s="1">
-        <v>60049</v>
+        <v>60042</v>
       </c>
       <c r="C370" s="1" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="D370" s="1">
         <v>7</v>
       </c>
       <c r="E370" s="1" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="F370" s="1" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
     </row>
     <row r="371" ht="15" customHeight="1" spans="1:6">
       <c r="A371" s="1"/>
       <c r="B371" s="1">
-        <v>60050</v>
+        <v>60043</v>
       </c>
       <c r="C371" s="1" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="D371" s="1">
         <v>7</v>
       </c>
       <c r="E371" s="1" t="s">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="F371" s="1" t="s">
-        <v>753</v>
+        <v>756</v>
       </c>
     </row>
     <row r="372" ht="15" customHeight="1" spans="1:6">
       <c r="A372" s="1"/>
       <c r="B372" s="1">
-        <v>60051</v>
+        <v>60044</v>
       </c>
       <c r="C372" s="1" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="D372" s="1">
         <v>7</v>
       </c>
       <c r="E372" s="1" t="s">
-        <v>754</v>
+        <v>757</v>
       </c>
       <c r="F372" s="1" t="s">
-        <v>755</v>
+        <v>758</v>
       </c>
     </row>
     <row r="373" ht="15" customHeight="1" spans="1:6">
       <c r="A373" s="1"/>
       <c r="B373" s="1">
-        <v>60052</v>
+        <v>60045</v>
       </c>
       <c r="C373" s="1" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="D373" s="1">
         <v>7</v>
       </c>
       <c r="E373" s="1" t="s">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="F373" s="1" t="s">
-        <v>757</v>
+        <v>760</v>
       </c>
     </row>
     <row r="374" ht="15" customHeight="1" spans="1:6">
       <c r="A374" s="1"/>
       <c r="B374" s="1">
-        <v>60053</v>
+        <v>60046</v>
       </c>
       <c r="C374" s="1" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="D374" s="1">
         <v>7</v>
       </c>
       <c r="E374" s="1" t="s">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="F374" s="1" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
     </row>
     <row r="375" ht="15" customHeight="1" spans="1:6">
       <c r="A375" s="1"/>
       <c r="B375" s="1">
-        <v>60054</v>
+        <v>60047</v>
       </c>
       <c r="C375" s="1" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="D375" s="1">
         <v>7</v>
       </c>
       <c r="E375" s="1" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="F375" s="1" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
     </row>
     <row r="376" ht="15" customHeight="1" spans="1:6">
       <c r="A376" s="1"/>
       <c r="B376" s="1">
-        <v>60055</v>
+        <v>60048</v>
       </c>
       <c r="C376" s="1" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="D376" s="1">
         <v>7</v>
       </c>
       <c r="E376" s="1" t="s">
-        <v>762</v>
+        <v>765</v>
       </c>
       <c r="F376" s="1" t="s">
-        <v>763</v>
+        <v>766</v>
       </c>
     </row>
     <row r="377" ht="15" customHeight="1" spans="1:6">
       <c r="A377" s="1"/>
       <c r="B377" s="1">
-        <v>60056</v>
+        <v>60049</v>
       </c>
       <c r="C377" s="1" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="D377" s="1">
         <v>7</v>
       </c>
       <c r="E377" s="1" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="F377" s="1" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
     </row>
     <row r="378" ht="15" customHeight="1" spans="1:6">
       <c r="A378" s="1"/>
       <c r="B378" s="1">
-        <v>60057</v>
+        <v>60050</v>
       </c>
       <c r="C378" s="1" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="D378" s="1">
         <v>7</v>
       </c>
       <c r="E378" s="1" t="s">
-        <v>766</v>
+        <v>769</v>
       </c>
       <c r="F378" s="1" t="s">
-        <v>767</v>
+        <v>770</v>
       </c>
     </row>
     <row r="379" ht="15" customHeight="1" spans="1:6">
       <c r="A379" s="1"/>
       <c r="B379" s="1">
-        <v>60058</v>
+        <v>60051</v>
       </c>
       <c r="C379" s="1" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="D379" s="1">
         <v>7</v>
       </c>
       <c r="E379" s="1" t="s">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="F379" s="1" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
     </row>
     <row r="380" ht="15" customHeight="1" spans="1:6">
       <c r="A380" s="1"/>
       <c r="B380" s="1">
-        <v>60059</v>
+        <v>60052</v>
       </c>
       <c r="C380" s="1" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="D380" s="1">
         <v>7</v>
       </c>
       <c r="E380" s="1" t="s">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="F380" s="1" t="s">
-        <v>771</v>
+        <v>774</v>
       </c>
     </row>
     <row r="381" ht="15" customHeight="1" spans="1:6">
       <c r="A381" s="1"/>
       <c r="B381" s="1">
-        <v>60060</v>
+        <v>60053</v>
       </c>
       <c r="C381" s="1" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="D381" s="1">
         <v>7</v>
       </c>
       <c r="E381" s="1" t="s">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="F381" s="1" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
     </row>
     <row r="382" ht="15" customHeight="1" spans="1:6">
       <c r="A382" s="1"/>
       <c r="B382" s="1">
-        <v>60061</v>
+        <v>60054</v>
       </c>
       <c r="C382" s="1" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="D382" s="1">
         <v>7</v>
       </c>
       <c r="E382" s="1" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="F382" s="1" t="s">
-        <v>775</v>
+        <v>778</v>
       </c>
     </row>
     <row r="383" ht="15" customHeight="1" spans="1:6">
       <c r="A383" s="1"/>
       <c r="B383" s="1">
-        <v>60062</v>
+        <v>60055</v>
       </c>
       <c r="C383" s="1" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="D383" s="1">
         <v>7</v>
       </c>
       <c r="E383" s="1" t="s">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="F383" s="1" t="s">
-        <v>777</v>
+        <v>780</v>
       </c>
     </row>
     <row r="384" ht="15" customHeight="1" spans="1:6">
       <c r="A384" s="1"/>
       <c r="B384" s="1">
-        <v>60063</v>
+        <v>60056</v>
       </c>
       <c r="C384" s="1" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="D384" s="1">
         <v>7</v>
       </c>
       <c r="E384" s="1" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="F384" s="1" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
     </row>
     <row r="385" ht="15" customHeight="1" spans="1:6">
       <c r="A385" s="1"/>
       <c r="B385" s="1">
-        <v>60064</v>
+        <v>60057</v>
       </c>
       <c r="C385" s="1" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="D385" s="1">
         <v>7</v>
       </c>
       <c r="E385" s="1" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="F385" s="1" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
     </row>
     <row r="386" ht="15" customHeight="1" spans="1:6">
       <c r="A386" s="1"/>
       <c r="B386" s="1">
-        <v>60065</v>
+        <v>60058</v>
       </c>
       <c r="C386" s="1" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="D386" s="1">
         <v>7</v>
       </c>
       <c r="E386" s="1" t="s">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="F386" s="1" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
     </row>
     <row r="387" ht="15" customHeight="1" spans="1:6">
       <c r="A387" s="1"/>
       <c r="B387" s="1">
-        <v>60066</v>
+        <v>60059</v>
       </c>
       <c r="C387" s="1" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="D387" s="1">
         <v>7</v>
       </c>
       <c r="E387" s="1" t="s">
-        <v>784</v>
+        <v>787</v>
       </c>
       <c r="F387" s="1" t="s">
-        <v>785</v>
+        <v>788</v>
       </c>
     </row>
     <row r="388" ht="15" customHeight="1" spans="1:6">
       <c r="A388" s="1"/>
       <c r="B388" s="1">
-        <v>60067</v>
+        <v>60060</v>
       </c>
       <c r="C388" s="1" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="D388" s="1">
         <v>7</v>
       </c>
       <c r="E388" s="1" t="s">
-        <v>786</v>
+        <v>789</v>
       </c>
       <c r="F388" s="1" t="s">
-        <v>787</v>
+        <v>790</v>
       </c>
     </row>
     <row r="389" ht="15" customHeight="1" spans="1:6">
       <c r="A389" s="1"/>
       <c r="B389" s="1">
-        <v>60068</v>
+        <v>60061</v>
       </c>
       <c r="C389" s="1" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="D389" s="1">
         <v>7</v>
       </c>
       <c r="E389" s="1" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="F389" s="1" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
     </row>
     <row r="390" ht="15" customHeight="1" spans="1:6">
       <c r="A390" s="1"/>
       <c r="B390" s="1">
-        <v>60069</v>
+        <v>60062</v>
       </c>
       <c r="C390" s="1" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="D390" s="1">
         <v>7</v>
       </c>
       <c r="E390" s="1" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="F390" s="1" t="s">
-        <v>791</v>
+        <v>794</v>
       </c>
     </row>
     <row r="391" ht="15" customHeight="1" spans="1:6">
       <c r="A391" s="1"/>
       <c r="B391" s="1">
-        <v>60070</v>
+        <v>60063</v>
       </c>
       <c r="C391" s="1" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="D391" s="1">
         <v>7</v>
       </c>
       <c r="E391" s="1" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="F391" s="1" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
     </row>
     <row r="392" ht="15" customHeight="1" spans="1:6">
       <c r="A392" s="1"/>
       <c r="B392" s="1">
-        <v>60071</v>
+        <v>60064</v>
       </c>
       <c r="C392" s="1" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="D392" s="1">
         <v>7</v>
       </c>
       <c r="E392" s="1" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="F392" s="1" t="s">
-        <v>795</v>
+        <v>798</v>
       </c>
     </row>
     <row r="393" ht="15" customHeight="1" spans="1:6">
       <c r="A393" s="1"/>
       <c r="B393" s="1">
-        <v>60072</v>
+        <v>60065</v>
       </c>
       <c r="C393" s="1" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="D393" s="1">
         <v>7</v>
       </c>
       <c r="E393" s="1" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="F393" s="1" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
     </row>
     <row r="394" ht="15" customHeight="1" spans="1:6">
       <c r="A394" s="1"/>
       <c r="B394" s="1">
-        <v>60073</v>
+        <v>60066</v>
       </c>
       <c r="C394" s="1" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="D394" s="1">
         <v>7</v>
       </c>
       <c r="E394" s="1" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="F394" s="1" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
     </row>
     <row r="395" ht="15" customHeight="1" spans="1:6">
       <c r="A395" s="1"/>
       <c r="B395" s="1">
-        <v>60074</v>
+        <v>60067</v>
       </c>
       <c r="C395" s="1" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="D395" s="1">
         <v>7</v>
       </c>
       <c r="E395" s="1" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="F395" s="1" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
     </row>
     <row r="396" ht="15" customHeight="1" spans="1:6">
       <c r="A396" s="1"/>
       <c r="B396" s="1">
-        <v>60075</v>
+        <v>60068</v>
       </c>
       <c r="C396" s="1" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="D396" s="1">
         <v>7</v>
       </c>
       <c r="E396" s="1" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="F396" s="1" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
     </row>
     <row r="397" ht="15" customHeight="1" spans="1:6">
       <c r="A397" s="1"/>
       <c r="B397" s="1">
-        <v>60076</v>
+        <v>60069</v>
       </c>
       <c r="C397" s="1" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="D397" s="1">
         <v>7</v>
       </c>
       <c r="E397" s="1" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="F397" s="1" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
     </row>
     <row r="398" ht="15" customHeight="1" spans="1:6">
       <c r="A398" s="1"/>
       <c r="B398" s="1">
-        <v>60077</v>
+        <v>60070</v>
       </c>
       <c r="C398" s="1" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="D398" s="1">
         <v>7</v>
       </c>
       <c r="E398" s="1" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="F398" s="1" t="s">
-        <v>807</v>
+        <v>810</v>
       </c>
     </row>
     <row r="399" ht="15" customHeight="1" spans="1:6">
       <c r="A399" s="1"/>
       <c r="B399" s="1">
-        <v>60078</v>
+        <v>60071</v>
       </c>
       <c r="C399" s="1" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="D399" s="1">
         <v>7</v>
       </c>
       <c r="E399" s="1" t="s">
-        <v>808</v>
+        <v>811</v>
       </c>
       <c r="F399" s="1" t="s">
-        <v>809</v>
+        <v>812</v>
       </c>
     </row>
     <row r="400" ht="15" customHeight="1" spans="1:6">
       <c r="A400" s="1"/>
       <c r="B400" s="1">
-        <v>60079</v>
+        <v>60072</v>
       </c>
       <c r="C400" s="1" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="D400" s="1">
         <v>7</v>
       </c>
       <c r="E400" s="1" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="F400" s="1" t="s">
-        <v>811</v>
+        <v>814</v>
       </c>
     </row>
     <row r="401" ht="15" customHeight="1" spans="1:6">
       <c r="A401" s="1"/>
       <c r="B401" s="1">
-        <v>60080</v>
+        <v>60073</v>
       </c>
       <c r="C401" s="1" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="D401" s="1">
         <v>7</v>
       </c>
       <c r="E401" s="1" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="F401" s="1" t="s">
-        <v>813</v>
+        <v>816</v>
       </c>
     </row>
     <row r="402" ht="15" customHeight="1" spans="1:6">
       <c r="A402" s="1"/>
       <c r="B402" s="1">
-        <v>60081</v>
+        <v>60074</v>
       </c>
       <c r="C402" s="1" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="D402" s="1">
         <v>7</v>
       </c>
       <c r="E402" s="1" t="s">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="F402" s="1" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
     </row>
     <row r="403" ht="15" customHeight="1" spans="1:6">
       <c r="A403" s="1"/>
       <c r="B403" s="1">
-        <v>60082</v>
+        <v>60075</v>
       </c>
       <c r="C403" s="1" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="D403" s="1">
         <v>7</v>
       </c>
       <c r="E403" s="1" t="s">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="F403" s="1" t="s">
-        <v>817</v>
+        <v>820</v>
       </c>
     </row>
     <row r="404" ht="15" customHeight="1" spans="1:6">
       <c r="A404" s="1"/>
       <c r="B404" s="1">
-        <v>60083</v>
+        <v>60076</v>
       </c>
       <c r="C404" s="1" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
       <c r="D404" s="1">
         <v>7</v>
       </c>
       <c r="E404" s="1" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="F404" s="1" t="s">
-        <v>819</v>
+        <v>822</v>
+      </c>
+    </row>
+    <row r="405" ht="15" customHeight="1" spans="1:6">
+      <c r="A405" s="1"/>
+      <c r="B405" s="1">
+        <v>60077</v>
+      </c>
+      <c r="C405" s="1" t="s">
+        <v>670</v>
+      </c>
+      <c r="D405" s="1">
+        <v>7</v>
+      </c>
+      <c r="E405" s="1" t="s">
+        <v>823</v>
+      </c>
+      <c r="F405" s="1" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="406" ht="15" customHeight="1" spans="1:6">
+      <c r="A406" s="1"/>
+      <c r="B406" s="1">
+        <v>60078</v>
+      </c>
+      <c r="C406" s="1" t="s">
+        <v>670</v>
+      </c>
+      <c r="D406" s="1">
+        <v>7</v>
+      </c>
+      <c r="E406" s="1" t="s">
+        <v>825</v>
+      </c>
+      <c r="F406" s="1" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="407" ht="15" customHeight="1" spans="1:6">
+      <c r="A407" s="1"/>
+      <c r="B407" s="1">
+        <v>60079</v>
+      </c>
+      <c r="C407" s="1" t="s">
+        <v>670</v>
+      </c>
+      <c r="D407" s="1">
+        <v>7</v>
+      </c>
+      <c r="E407" s="1" t="s">
+        <v>827</v>
+      </c>
+      <c r="F407" s="1" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="408" ht="15" customHeight="1" spans="1:6">
+      <c r="A408" s="1"/>
+      <c r="B408" s="1">
+        <v>60080</v>
+      </c>
+      <c r="C408" s="1" t="s">
+        <v>670</v>
+      </c>
+      <c r="D408" s="1">
+        <v>7</v>
+      </c>
+      <c r="E408" s="1" t="s">
+        <v>829</v>
+      </c>
+      <c r="F408" s="1" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="409" ht="15" customHeight="1" spans="1:6">
+      <c r="A409" s="1"/>
+      <c r="B409" s="1">
+        <v>60081</v>
+      </c>
+      <c r="C409" s="1" t="s">
+        <v>670</v>
+      </c>
+      <c r="D409" s="1">
+        <v>7</v>
+      </c>
+      <c r="E409" s="1" t="s">
+        <v>831</v>
+      </c>
+      <c r="F409" s="1" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="410" ht="15" customHeight="1" spans="1:6">
+      <c r="A410" s="1"/>
+      <c r="B410" s="1">
+        <v>60082</v>
+      </c>
+      <c r="C410" s="1" t="s">
+        <v>670</v>
+      </c>
+      <c r="D410" s="1">
+        <v>7</v>
+      </c>
+      <c r="E410" s="1" t="s">
+        <v>833</v>
+      </c>
+      <c r="F410" s="1" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="411" ht="15" customHeight="1" spans="1:6">
+      <c r="A411" s="1"/>
+      <c r="B411" s="1">
+        <v>60083</v>
+      </c>
+      <c r="C411" s="1" t="s">
+        <v>670</v>
+      </c>
+      <c r="D411" s="1">
+        <v>7</v>
+      </c>
+      <c r="E411" s="1" t="s">
+        <v>835</v>
+      </c>
+      <c r="F411" s="1" t="s">
+        <v>836</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/DataTables/ResourceConfigTable.xlsx
+++ b/AAAGameData/DataTables/ResourceConfigTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="14855"/>
+    <workbookView windowWidth="27948" windowHeight="11855"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1038" uniqueCount="837">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1046" uniqueCount="845">
   <si>
     <t>#</t>
   </si>
@@ -132,6 +132,30 @@
   </si>
   <si>
     <t>角色界面，标签选中背景</t>
+  </si>
+  <si>
+    <t>UI/Common/角色Logo.png</t>
+  </si>
+  <si>
+    <t>角色图标</t>
+  </si>
+  <si>
+    <t>UI/Common/图鉴Logo.png</t>
+  </si>
+  <si>
+    <t>图鉴图标</t>
+  </si>
+  <si>
+    <t>UI/Common/仓库Logo.png</t>
+  </si>
+  <si>
+    <t>仓库图标</t>
+  </si>
+  <si>
+    <t>UI/Common/战斗预设Logo.png</t>
+  </si>
+  <si>
+    <t>出战预设图标</t>
   </si>
   <si>
     <t>UI/Items/Gold.png</t>
@@ -3502,7 +3526,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F411"/>
+  <dimension ref="A1:F415"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -3759,7 +3783,7 @@
     <row r="16" ht="15" customHeight="1" spans="1:6">
       <c r="A16" s="1"/>
       <c r="B16" s="1">
-        <v>1101</v>
+        <v>1012</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1">
@@ -3775,7 +3799,7 @@
     <row r="17" ht="15" customHeight="1" spans="1:6">
       <c r="A17" s="1"/>
       <c r="B17" s="1">
-        <v>1102</v>
+        <v>1013</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="1">
@@ -3791,7 +3815,7 @@
     <row r="18" ht="15" customHeight="1" spans="1:6">
       <c r="A18" s="1"/>
       <c r="B18" s="1">
-        <v>1103</v>
+        <v>1014</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="1">
@@ -3807,7 +3831,7 @@
     <row r="19" ht="15" customHeight="1" spans="1:6">
       <c r="A19" s="1"/>
       <c r="B19" s="1">
-        <v>1104</v>
+        <v>1015</v>
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="1">
@@ -3823,7 +3847,7 @@
     <row r="20" ht="15" customHeight="1" spans="1:6">
       <c r="A20" s="1"/>
       <c r="B20" s="1">
-        <v>1105</v>
+        <v>1101</v>
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="1">
@@ -3839,7 +3863,7 @@
     <row r="21" ht="15" customHeight="1" spans="1:6">
       <c r="A21" s="1"/>
       <c r="B21" s="1">
-        <v>1106</v>
+        <v>1102</v>
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="1">
@@ -3855,7 +3879,7 @@
     <row r="22" ht="15" customHeight="1" spans="1:6">
       <c r="A22" s="1"/>
       <c r="B22" s="1">
-        <v>1107</v>
+        <v>1103</v>
       </c>
       <c r="C22" s="1"/>
       <c r="D22" s="1">
@@ -3871,7 +3895,7 @@
     <row r="23" ht="15" customHeight="1" spans="1:6">
       <c r="A23" s="1"/>
       <c r="B23" s="1">
-        <v>1108</v>
+        <v>1104</v>
       </c>
       <c r="C23" s="1"/>
       <c r="D23" s="1">
@@ -3887,7 +3911,7 @@
     <row r="24" ht="15" customHeight="1" spans="1:6">
       <c r="A24" s="1"/>
       <c r="B24" s="1">
-        <v>1155</v>
+        <v>1105</v>
       </c>
       <c r="C24" s="1"/>
       <c r="D24" s="1">
@@ -3903,7 +3927,7 @@
     <row r="25" ht="15" customHeight="1" spans="1:6">
       <c r="A25" s="1"/>
       <c r="B25" s="1">
-        <v>1156</v>
+        <v>1106</v>
       </c>
       <c r="C25" s="1"/>
       <c r="D25" s="1">
@@ -3919,7 +3943,7 @@
     <row r="26" ht="15" customHeight="1" spans="1:6">
       <c r="A26" s="1"/>
       <c r="B26" s="1">
-        <v>1157</v>
+        <v>1107</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="1">
@@ -3935,7 +3959,7 @@
     <row r="27" ht="15" customHeight="1" spans="1:6">
       <c r="A27" s="1"/>
       <c r="B27" s="1">
-        <v>1158</v>
+        <v>1108</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="1">
@@ -3951,7 +3975,7 @@
     <row r="28" ht="15" customHeight="1" spans="1:6">
       <c r="A28" s="1"/>
       <c r="B28" s="1">
-        <v>1201</v>
+        <v>1155</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="1">
@@ -3967,7 +3991,7 @@
     <row r="29" ht="15" customHeight="1" spans="1:6">
       <c r="A29" s="1"/>
       <c r="B29" s="1">
-        <v>1202</v>
+        <v>1156</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="1">
@@ -3983,7 +4007,7 @@
     <row r="30" ht="15" customHeight="1" spans="1:6">
       <c r="A30" s="1"/>
       <c r="B30" s="1">
-        <v>1203</v>
+        <v>1157</v>
       </c>
       <c r="C30" s="1"/>
       <c r="D30" s="1">
@@ -3999,7 +4023,7 @@
     <row r="31" ht="15" customHeight="1" spans="1:6">
       <c r="A31" s="1"/>
       <c r="B31" s="1">
-        <v>1204</v>
+        <v>1158</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="1">
@@ -4015,7 +4039,7 @@
     <row r="32" ht="15" customHeight="1" spans="1:6">
       <c r="A32" s="1"/>
       <c r="B32" s="1">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="C32" s="1"/>
       <c r="D32" s="1">
@@ -4031,7 +4055,7 @@
     <row r="33" ht="15" customHeight="1" spans="1:6">
       <c r="A33" s="1"/>
       <c r="B33" s="1">
-        <v>1206</v>
+        <v>1202</v>
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="1">
@@ -4047,7 +4071,7 @@
     <row r="34" ht="15" customHeight="1" spans="1:6">
       <c r="A34" s="1"/>
       <c r="B34" s="1">
-        <v>1207</v>
+        <v>1203</v>
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="1">
@@ -4063,7 +4087,7 @@
     <row r="35" ht="15" customHeight="1" spans="1:6">
       <c r="A35" s="1"/>
       <c r="B35" s="1">
-        <v>1208</v>
+        <v>1204</v>
       </c>
       <c r="C35" s="1"/>
       <c r="D35" s="1">
@@ -4079,7 +4103,7 @@
     <row r="36" ht="15" customHeight="1" spans="1:6">
       <c r="A36" s="1"/>
       <c r="B36" s="1">
-        <v>1209</v>
+        <v>1205</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1">
@@ -4095,7 +4119,7 @@
     <row r="37" ht="15" customHeight="1" spans="1:6">
       <c r="A37" s="1"/>
       <c r="B37" s="1">
-        <v>1210</v>
+        <v>1206</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1">
@@ -4111,7 +4135,7 @@
     <row r="38" ht="15" customHeight="1" spans="1:6">
       <c r="A38" s="1"/>
       <c r="B38" s="1">
-        <v>1211</v>
+        <v>1207</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1">
@@ -4127,7 +4151,7 @@
     <row r="39" ht="15" customHeight="1" spans="1:6">
       <c r="A39" s="1"/>
       <c r="B39" s="1">
-        <v>1212</v>
+        <v>1208</v>
       </c>
       <c r="C39" s="1"/>
       <c r="D39" s="1">
@@ -4143,7 +4167,7 @@
     <row r="40" ht="15" customHeight="1" spans="1:6">
       <c r="A40" s="1"/>
       <c r="B40" s="1">
-        <v>1213</v>
+        <v>1209</v>
       </c>
       <c r="C40" s="1"/>
       <c r="D40" s="1">
@@ -4159,7 +4183,7 @@
     <row r="41" ht="15" customHeight="1" spans="1:6">
       <c r="A41" s="1"/>
       <c r="B41" s="1">
-        <v>1214</v>
+        <v>1210</v>
       </c>
       <c r="C41" s="1"/>
       <c r="D41" s="1">
@@ -4175,7 +4199,7 @@
     <row r="42" ht="15" customHeight="1" spans="1:6">
       <c r="A42" s="1"/>
       <c r="B42" s="1">
-        <v>1215</v>
+        <v>1211</v>
       </c>
       <c r="C42" s="1"/>
       <c r="D42" s="1">
@@ -4191,7 +4215,7 @@
     <row r="43" ht="15" customHeight="1" spans="1:6">
       <c r="A43" s="1"/>
       <c r="B43" s="1">
-        <v>1216</v>
+        <v>1212</v>
       </c>
       <c r="C43" s="1"/>
       <c r="D43" s="1">
@@ -4207,7 +4231,7 @@
     <row r="44" ht="15" customHeight="1" spans="1:6">
       <c r="A44" s="1"/>
       <c r="B44" s="1">
-        <v>1217</v>
+        <v>1213</v>
       </c>
       <c r="C44" s="1"/>
       <c r="D44" s="1">
@@ -4223,7 +4247,7 @@
     <row r="45" ht="15" customHeight="1" spans="1:6">
       <c r="A45" s="1"/>
       <c r="B45" s="1">
-        <v>1218</v>
+        <v>1214</v>
       </c>
       <c r="C45" s="1"/>
       <c r="D45" s="1">
@@ -4239,7 +4263,7 @@
     <row r="46" ht="15" customHeight="1" spans="1:6">
       <c r="A46" s="1"/>
       <c r="B46" s="1">
-        <v>1219</v>
+        <v>1215</v>
       </c>
       <c r="C46" s="1"/>
       <c r="D46" s="1">
@@ -4255,7 +4279,7 @@
     <row r="47" ht="15" customHeight="1" spans="1:6">
       <c r="A47" s="1"/>
       <c r="B47" s="1">
-        <v>1220</v>
+        <v>1216</v>
       </c>
       <c r="C47" s="1"/>
       <c r="D47" s="1">
@@ -4271,7 +4295,7 @@
     <row r="48" ht="15" customHeight="1" spans="1:6">
       <c r="A48" s="1"/>
       <c r="B48" s="1">
-        <v>1221</v>
+        <v>1217</v>
       </c>
       <c r="C48" s="1"/>
       <c r="D48" s="1">
@@ -4287,7 +4311,7 @@
     <row r="49" ht="15" customHeight="1" spans="1:6">
       <c r="A49" s="1"/>
       <c r="B49" s="1">
-        <v>1222</v>
+        <v>1218</v>
       </c>
       <c r="C49" s="1"/>
       <c r="D49" s="1">
@@ -4303,7 +4327,7 @@
     <row r="50" ht="15" customHeight="1" spans="1:6">
       <c r="A50" s="1"/>
       <c r="B50" s="1">
-        <v>1223</v>
+        <v>1219</v>
       </c>
       <c r="C50" s="1"/>
       <c r="D50" s="1">
@@ -4319,7 +4343,7 @@
     <row r="51" ht="15" customHeight="1" spans="1:6">
       <c r="A51" s="1"/>
       <c r="B51" s="1">
-        <v>1224</v>
+        <v>1220</v>
       </c>
       <c r="C51" s="1"/>
       <c r="D51" s="1">
@@ -4335,7 +4359,7 @@
     <row r="52" ht="15" customHeight="1" spans="1:6">
       <c r="A52" s="1"/>
       <c r="B52" s="1">
-        <v>1225</v>
+        <v>1221</v>
       </c>
       <c r="C52" s="1"/>
       <c r="D52" s="1">
@@ -4351,7 +4375,7 @@
     <row r="53" ht="15" customHeight="1" spans="1:6">
       <c r="A53" s="1"/>
       <c r="B53" s="1">
-        <v>1301</v>
+        <v>1222</v>
       </c>
       <c r="C53" s="1"/>
       <c r="D53" s="1">
@@ -4367,7 +4391,7 @@
     <row r="54" ht="15" customHeight="1" spans="1:6">
       <c r="A54" s="1"/>
       <c r="B54" s="1">
-        <v>1304</v>
+        <v>1223</v>
       </c>
       <c r="C54" s="1"/>
       <c r="D54" s="1">
@@ -4383,7 +4407,7 @@
     <row r="55" ht="15" customHeight="1" spans="1:6">
       <c r="A55" s="1"/>
       <c r="B55" s="1">
-        <v>1310</v>
+        <v>1224</v>
       </c>
       <c r="C55" s="1"/>
       <c r="D55" s="1">
@@ -4399,7 +4423,7 @@
     <row r="56" ht="15" customHeight="1" spans="1:6">
       <c r="A56" s="1"/>
       <c r="B56" s="1">
-        <v>1311</v>
+        <v>1225</v>
       </c>
       <c r="C56" s="1"/>
       <c r="D56" s="1">
@@ -4415,7 +4439,7 @@
     <row r="57" ht="15" customHeight="1" spans="1:6">
       <c r="A57" s="1"/>
       <c r="B57" s="1">
-        <v>1312</v>
+        <v>1301</v>
       </c>
       <c r="C57" s="1"/>
       <c r="D57" s="1">
@@ -4431,7 +4455,7 @@
     <row r="58" ht="15" customHeight="1" spans="1:6">
       <c r="A58" s="1"/>
       <c r="B58" s="1">
-        <v>1313</v>
+        <v>1304</v>
       </c>
       <c r="C58" s="1"/>
       <c r="D58" s="1">
@@ -4447,7 +4471,7 @@
     <row r="59" ht="15" customHeight="1" spans="1:6">
       <c r="A59" s="1"/>
       <c r="B59" s="1">
-        <v>1401</v>
+        <v>1310</v>
       </c>
       <c r="C59" s="1"/>
       <c r="D59" s="1">
@@ -4463,7 +4487,7 @@
     <row r="60" ht="15" customHeight="1" spans="1:6">
       <c r="A60" s="1"/>
       <c r="B60" s="1">
-        <v>1402</v>
+        <v>1311</v>
       </c>
       <c r="C60" s="1"/>
       <c r="D60" s="1">
@@ -4479,7 +4503,7 @@
     <row r="61" ht="15" customHeight="1" spans="1:6">
       <c r="A61" s="1"/>
       <c r="B61" s="1">
-        <v>1403</v>
+        <v>1312</v>
       </c>
       <c r="C61" s="1"/>
       <c r="D61" s="1">
@@ -4495,7 +4519,7 @@
     <row r="62" ht="15" customHeight="1" spans="1:6">
       <c r="A62" s="1"/>
       <c r="B62" s="1">
-        <v>1404</v>
+        <v>1313</v>
       </c>
       <c r="C62" s="1"/>
       <c r="D62" s="1">
@@ -4511,7 +4535,7 @@
     <row r="63" ht="15" customHeight="1" spans="1:6">
       <c r="A63" s="1"/>
       <c r="B63" s="1">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="C63" s="1"/>
       <c r="D63" s="1">
@@ -4527,7 +4551,7 @@
     <row r="64" ht="15" customHeight="1" spans="1:6">
       <c r="A64" s="1"/>
       <c r="B64" s="1">
-        <v>1406</v>
+        <v>1402</v>
       </c>
       <c r="C64" s="1"/>
       <c r="D64" s="1">
@@ -4543,82 +4567,74 @@
     <row r="65" ht="15" customHeight="1" spans="1:6">
       <c r="A65" s="1"/>
       <c r="B65" s="1">
-        <v>1407</v>
-      </c>
-      <c r="C65" s="1" t="s">
+        <v>1403</v>
+      </c>
+      <c r="C65" s="1"/>
+      <c r="D65" s="1">
+        <v>1</v>
+      </c>
+      <c r="E65" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="D65" s="1">
-        <v>1</v>
-      </c>
-      <c r="E65" s="1" t="s">
+      <c r="F65" s="1" t="s">
         <v>134</v>
-      </c>
-      <c r="F65" s="1" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="66" ht="15" customHeight="1" spans="1:6">
       <c r="A66" s="1"/>
       <c r="B66" s="1">
-        <v>1408</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>133</v>
-      </c>
+        <v>1404</v>
+      </c>
+      <c r="C66" s="1"/>
       <c r="D66" s="1">
         <v>1</v>
       </c>
       <c r="E66" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="F66" s="1" t="s">
         <v>136</v>
-      </c>
-      <c r="F66" s="1" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1" spans="1:6">
       <c r="A67" s="1"/>
       <c r="B67" s="1">
-        <v>1409</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>133</v>
-      </c>
+        <v>1405</v>
+      </c>
+      <c r="C67" s="1"/>
       <c r="D67" s="1">
         <v>1</v>
       </c>
       <c r="E67" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="F67" s="1" t="s">
         <v>138</v>
-      </c>
-      <c r="F67" s="1" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="68" ht="15" customHeight="1" spans="1:6">
       <c r="A68" s="1"/>
       <c r="B68" s="1">
-        <v>1410</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>133</v>
-      </c>
+        <v>1406</v>
+      </c>
+      <c r="C68" s="1"/>
       <c r="D68" s="1">
         <v>1</v>
       </c>
       <c r="E68" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="F68" s="1" t="s">
         <v>140</v>
-      </c>
-      <c r="F68" s="1" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" spans="1:6">
       <c r="A69" s="1"/>
       <c r="B69" s="1">
-        <v>1411</v>
+        <v>1407</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="D69" s="1">
         <v>1</v>
@@ -4633,9 +4649,11 @@
     <row r="70" ht="15" customHeight="1" spans="1:6">
       <c r="A70" s="1"/>
       <c r="B70" s="1">
-        <v>1501</v>
-      </c>
-      <c r="C70" s="1"/>
+        <v>1408</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>141</v>
+      </c>
       <c r="D70" s="1">
         <v>1</v>
       </c>
@@ -4646,12 +4664,14 @@
         <v>145</v>
       </c>
     </row>
-    <row r="71" spans="1:6">
+    <row r="71" ht="15" customHeight="1" spans="1:6">
       <c r="A71" s="1"/>
       <c r="B71" s="1">
-        <v>1502</v>
-      </c>
-      <c r="C71" s="1"/>
+        <v>1409</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>141</v>
+      </c>
       <c r="D71" s="1">
         <v>1</v>
       </c>
@@ -4662,12 +4682,14 @@
         <v>147</v>
       </c>
     </row>
-    <row r="72" ht="13" customHeight="1" spans="1:6">
+    <row r="72" ht="15" customHeight="1" spans="1:6">
       <c r="A72" s="1"/>
       <c r="B72" s="1">
-        <v>1503</v>
-      </c>
-      <c r="C72" s="1"/>
+        <v>1410</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>141</v>
+      </c>
       <c r="D72" s="1">
         <v>1</v>
       </c>
@@ -4681,82 +4703,76 @@
     <row r="73" ht="15" customHeight="1" spans="1:6">
       <c r="A73" s="1"/>
       <c r="B73" s="1">
-        <v>1511</v>
+        <v>1411</v>
       </c>
       <c r="C73" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="D73" s="1">
+        <v>1</v>
+      </c>
+      <c r="E73" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="D73" s="1">
-        <v>1</v>
-      </c>
-      <c r="E73" s="1" t="s">
+      <c r="F73" s="1" t="s">
         <v>151</v>
-      </c>
-      <c r="F73" s="1" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="74" ht="15" customHeight="1" spans="1:6">
       <c r="A74" s="1"/>
       <c r="B74" s="1">
-        <v>1512</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>150</v>
-      </c>
+        <v>1501</v>
+      </c>
+      <c r="C74" s="1"/>
       <c r="D74" s="1">
         <v>1</v>
       </c>
       <c r="E74" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="F74" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="F74" s="1" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="75" ht="15" customHeight="1" spans="1:6">
+    </row>
+    <row r="75" spans="1:6">
       <c r="A75" s="1"/>
       <c r="B75" s="1">
-        <v>1513</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>150</v>
-      </c>
+        <v>1502</v>
+      </c>
+      <c r="C75" s="1"/>
       <c r="D75" s="1">
         <v>1</v>
       </c>
       <c r="E75" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="F75" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="F75" s="1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="76" ht="15" customHeight="1" spans="1:6">
+    </row>
+    <row r="76" ht="13" customHeight="1" spans="1:6">
       <c r="A76" s="1"/>
       <c r="B76" s="1">
-        <v>1514</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>150</v>
-      </c>
+        <v>1503</v>
+      </c>
+      <c r="C76" s="1"/>
       <c r="D76" s="1">
         <v>1</v>
       </c>
       <c r="E76" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="F76" s="1" t="s">
         <v>157</v>
-      </c>
-      <c r="F76" s="1" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="77" ht="15" customHeight="1" spans="1:6">
       <c r="A77" s="1"/>
       <c r="B77" s="1">
-        <v>1515</v>
+        <v>1511</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="D77" s="1">
         <v>1</v>
@@ -4771,9 +4787,11 @@
     <row r="78" ht="15" customHeight="1" spans="1:6">
       <c r="A78" s="1"/>
       <c r="B78" s="1">
-        <v>1702</v>
-      </c>
-      <c r="C78" s="1"/>
+        <v>1512</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="D78" s="1">
         <v>1</v>
       </c>
@@ -4787,9 +4805,11 @@
     <row r="79" ht="15" customHeight="1" spans="1:6">
       <c r="A79" s="1"/>
       <c r="B79" s="1">
-        <v>1703</v>
-      </c>
-      <c r="C79" s="1"/>
+        <v>1513</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="D79" s="1">
         <v>1</v>
       </c>
@@ -4803,9 +4823,11 @@
     <row r="80" ht="15" customHeight="1" spans="1:6">
       <c r="A80" s="1"/>
       <c r="B80" s="1">
-        <v>1704</v>
-      </c>
-      <c r="C80" s="1"/>
+        <v>1514</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="D80" s="1">
         <v>1</v>
       </c>
@@ -4819,9 +4841,11 @@
     <row r="81" ht="15" customHeight="1" spans="1:6">
       <c r="A81" s="1"/>
       <c r="B81" s="1">
-        <v>1705</v>
-      </c>
-      <c r="C81" s="1"/>
+        <v>1515</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="D81" s="1">
         <v>1</v>
       </c>
@@ -4835,7 +4859,7 @@
     <row r="82" ht="15" customHeight="1" spans="1:6">
       <c r="A82" s="1"/>
       <c r="B82" s="1">
-        <v>1706</v>
+        <v>1702</v>
       </c>
       <c r="C82" s="1"/>
       <c r="D82" s="1">
@@ -4851,7 +4875,7 @@
     <row r="83" ht="15" customHeight="1" spans="1:6">
       <c r="A83" s="1"/>
       <c r="B83" s="1">
-        <v>1707</v>
+        <v>1703</v>
       </c>
       <c r="C83" s="1"/>
       <c r="D83" s="1">
@@ -4867,7 +4891,7 @@
     <row r="84" ht="15" customHeight="1" spans="1:6">
       <c r="A84" s="1"/>
       <c r="B84" s="1">
-        <v>1708</v>
+        <v>1704</v>
       </c>
       <c r="C84" s="1"/>
       <c r="D84" s="1">
@@ -4883,7 +4907,7 @@
     <row r="85" ht="15" customHeight="1" spans="1:6">
       <c r="A85" s="1"/>
       <c r="B85" s="1">
-        <v>1711</v>
+        <v>1705</v>
       </c>
       <c r="C85" s="1"/>
       <c r="D85" s="1">
@@ -4899,7 +4923,7 @@
     <row r="86" ht="15" customHeight="1" spans="1:6">
       <c r="A86" s="1"/>
       <c r="B86" s="1">
-        <v>1712</v>
+        <v>1706</v>
       </c>
       <c r="C86" s="1"/>
       <c r="D86" s="1">
@@ -4915,82 +4939,74 @@
     <row r="87" ht="15" customHeight="1" spans="1:6">
       <c r="A87" s="1"/>
       <c r="B87" s="1">
-        <v>1801</v>
-      </c>
-      <c r="C87" s="1" t="s">
+        <v>1707</v>
+      </c>
+      <c r="C87" s="1"/>
+      <c r="D87" s="1">
+        <v>1</v>
+      </c>
+      <c r="E87" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="D87" s="1">
-        <v>1</v>
-      </c>
-      <c r="E87" s="1" t="s">
+      <c r="F87" s="1" t="s">
         <v>180</v>
-      </c>
-      <c r="F87" s="1" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="88" ht="15" customHeight="1" spans="1:6">
       <c r="A88" s="1"/>
       <c r="B88" s="1">
-        <v>1802</v>
-      </c>
-      <c r="C88" s="1" t="s">
-        <v>179</v>
-      </c>
+        <v>1708</v>
+      </c>
+      <c r="C88" s="1"/>
       <c r="D88" s="1">
         <v>1</v>
       </c>
       <c r="E88" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="F88" s="1" t="s">
         <v>182</v>
-      </c>
-      <c r="F88" s="1" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="89" ht="15" customHeight="1" spans="1:6">
       <c r="A89" s="1"/>
       <c r="B89" s="1">
-        <v>1803</v>
-      </c>
-      <c r="C89" s="1" t="s">
-        <v>179</v>
-      </c>
+        <v>1711</v>
+      </c>
+      <c r="C89" s="1"/>
       <c r="D89" s="1">
         <v>1</v>
       </c>
       <c r="E89" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="F89" s="1" t="s">
         <v>184</v>
-      </c>
-      <c r="F89" s="1" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="90" ht="15" customHeight="1" spans="1:6">
       <c r="A90" s="1"/>
       <c r="B90" s="1">
-        <v>1804</v>
-      </c>
-      <c r="C90" s="1" t="s">
-        <v>179</v>
-      </c>
+        <v>1712</v>
+      </c>
+      <c r="C90" s="1"/>
       <c r="D90" s="1">
         <v>1</v>
       </c>
       <c r="E90" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="F90" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="F90" s="1" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="91" ht="15" customHeight="1" spans="1:6">
       <c r="A91" s="1"/>
       <c r="B91" s="1">
-        <v>1805</v>
+        <v>1801</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="D91" s="1">
         <v>1</v>
@@ -5005,10 +5021,10 @@
     <row r="92" ht="15" customHeight="1" spans="1:6">
       <c r="A92" s="1"/>
       <c r="B92" s="1">
-        <v>1806</v>
+        <v>1802</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="D92" s="1">
         <v>1</v>
@@ -5023,10 +5039,10 @@
     <row r="93" ht="15" customHeight="1" spans="1:6">
       <c r="A93" s="1"/>
       <c r="B93" s="1">
-        <v>1807</v>
+        <v>1803</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="D93" s="1">
         <v>1</v>
@@ -5041,10 +5057,10 @@
     <row r="94" ht="15" customHeight="1" spans="1:6">
       <c r="A94" s="1"/>
       <c r="B94" s="1">
-        <v>1808</v>
+        <v>1804</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="D94" s="1">
         <v>1</v>
@@ -5059,10 +5075,10 @@
     <row r="95" ht="15" customHeight="1" spans="1:6">
       <c r="A95" s="1"/>
       <c r="B95" s="1">
-        <v>1831</v>
+        <v>1805</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="D95" s="1">
         <v>1</v>
@@ -5077,10 +5093,10 @@
     <row r="96" ht="15" customHeight="1" spans="1:6">
       <c r="A96" s="1"/>
       <c r="B96" s="1">
-        <v>1832</v>
+        <v>1806</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="D96" s="1">
         <v>1</v>
@@ -5095,10 +5111,10 @@
     <row r="97" ht="15" customHeight="1" spans="1:6">
       <c r="A97" s="1"/>
       <c r="B97" s="1">
-        <v>1833</v>
+        <v>1807</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="D97" s="1">
         <v>1</v>
@@ -5113,10 +5129,10 @@
     <row r="98" ht="15" customHeight="1" spans="1:6">
       <c r="A98" s="1"/>
       <c r="B98" s="1">
-        <v>1834</v>
+        <v>1808</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="D98" s="1">
         <v>1</v>
@@ -5131,10 +5147,10 @@
     <row r="99" ht="15" customHeight="1" spans="1:6">
       <c r="A99" s="1"/>
       <c r="B99" s="1">
-        <v>1841</v>
+        <v>1831</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="D99" s="1">
         <v>1</v>
@@ -5149,10 +5165,10 @@
     <row r="100" ht="15" customHeight="1" spans="1:6">
       <c r="A100" s="1"/>
       <c r="B100" s="1">
-        <v>1842</v>
+        <v>1832</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="D100" s="1">
         <v>1</v>
@@ -5167,10 +5183,10 @@
     <row r="101" ht="15" customHeight="1" spans="1:6">
       <c r="A101" s="1"/>
       <c r="B101" s="1">
-        <v>1843</v>
+        <v>1833</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="D101" s="1">
         <v>1</v>
@@ -5185,10 +5201,10 @@
     <row r="102" ht="15" customHeight="1" spans="1:6">
       <c r="A102" s="1"/>
       <c r="B102" s="1">
-        <v>1844</v>
+        <v>1834</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="D102" s="1">
         <v>1</v>
@@ -5203,10 +5219,10 @@
     <row r="103" ht="15" customHeight="1" spans="1:6">
       <c r="A103" s="1"/>
       <c r="B103" s="1">
-        <v>1845</v>
+        <v>1841</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="D103" s="1">
         <v>1</v>
@@ -5221,10 +5237,10 @@
     <row r="104" ht="15" customHeight="1" spans="1:6">
       <c r="A104" s="1"/>
       <c r="B104" s="1">
-        <v>1846</v>
+        <v>1842</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="D104" s="1">
         <v>1</v>
@@ -5239,10 +5255,10 @@
     <row r="105" ht="15" customHeight="1" spans="1:6">
       <c r="A105" s="1"/>
       <c r="B105" s="1">
-        <v>1847</v>
+        <v>1843</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="D105" s="1">
         <v>1</v>
@@ -5257,10 +5273,10 @@
     <row r="106" ht="15" customHeight="1" spans="1:6">
       <c r="A106" s="1"/>
       <c r="B106" s="1">
-        <v>1848</v>
+        <v>1844</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="D106" s="1">
         <v>1</v>
@@ -5275,10 +5291,10 @@
     <row r="107" ht="15" customHeight="1" spans="1:6">
       <c r="A107" s="1"/>
       <c r="B107" s="1">
-        <v>1849</v>
+        <v>1845</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="D107" s="1">
         <v>1</v>
@@ -5293,10 +5309,10 @@
     <row r="108" ht="15" customHeight="1" spans="1:6">
       <c r="A108" s="1"/>
       <c r="B108" s="1">
-        <v>1850</v>
+        <v>1846</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="D108" s="1">
         <v>1</v>
@@ -5311,9 +5327,11 @@
     <row r="109" ht="15" customHeight="1" spans="1:6">
       <c r="A109" s="1"/>
       <c r="B109" s="1">
-        <v>1901</v>
-      </c>
-      <c r="C109" s="1"/>
+        <v>1847</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>187</v>
+      </c>
       <c r="D109" s="1">
         <v>1</v>
       </c>
@@ -5327,9 +5345,11 @@
     <row r="110" ht="15" customHeight="1" spans="1:6">
       <c r="A110" s="1"/>
       <c r="B110" s="1">
-        <v>1902</v>
-      </c>
-      <c r="C110" s="1"/>
+        <v>1848</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>187</v>
+      </c>
       <c r="D110" s="1">
         <v>1</v>
       </c>
@@ -5343,9 +5363,11 @@
     <row r="111" ht="15" customHeight="1" spans="1:6">
       <c r="A111" s="1"/>
       <c r="B111" s="1">
-        <v>1903</v>
-      </c>
-      <c r="C111" s="1"/>
+        <v>1849</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>187</v>
+      </c>
       <c r="D111" s="1">
         <v>1</v>
       </c>
@@ -5359,9 +5381,11 @@
     <row r="112" ht="15" customHeight="1" spans="1:6">
       <c r="A112" s="1"/>
       <c r="B112" s="1">
-        <v>1904</v>
-      </c>
-      <c r="C112" s="1"/>
+        <v>1850</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>187</v>
+      </c>
       <c r="D112" s="1">
         <v>1</v>
       </c>
@@ -5375,7 +5399,7 @@
     <row r="113" ht="15" customHeight="1" spans="1:6">
       <c r="A113" s="1"/>
       <c r="B113" s="1">
-        <v>1905</v>
+        <v>1901</v>
       </c>
       <c r="C113" s="1"/>
       <c r="D113" s="1">
@@ -5391,7 +5415,7 @@
     <row r="114" ht="15" customHeight="1" spans="1:6">
       <c r="A114" s="1"/>
       <c r="B114" s="1">
-        <v>1906</v>
+        <v>1902</v>
       </c>
       <c r="C114" s="1"/>
       <c r="D114" s="1">
@@ -5407,7 +5431,7 @@
     <row r="115" ht="15" customHeight="1" spans="1:6">
       <c r="A115" s="1"/>
       <c r="B115" s="1">
-        <v>1907</v>
+        <v>1903</v>
       </c>
       <c r="C115" s="1"/>
       <c r="D115" s="1">
@@ -5423,7 +5447,7 @@
     <row r="116" ht="15" customHeight="1" spans="1:6">
       <c r="A116" s="1"/>
       <c r="B116" s="1">
-        <v>1908</v>
+        <v>1904</v>
       </c>
       <c r="C116" s="1"/>
       <c r="D116" s="1">
@@ -5439,7 +5463,7 @@
     <row r="117" ht="15" customHeight="1" spans="1:6">
       <c r="A117" s="1"/>
       <c r="B117" s="1">
-        <v>1909</v>
+        <v>1905</v>
       </c>
       <c r="C117" s="1"/>
       <c r="D117" s="1">
@@ -5455,7 +5479,7 @@
     <row r="118" ht="15" customHeight="1" spans="1:6">
       <c r="A118" s="1"/>
       <c r="B118" s="1">
-        <v>1910</v>
+        <v>1906</v>
       </c>
       <c r="C118" s="1"/>
       <c r="D118" s="1">
@@ -5471,7 +5495,7 @@
     <row r="119" ht="15" customHeight="1" spans="1:6">
       <c r="A119" s="1"/>
       <c r="B119" s="1">
-        <v>1911</v>
+        <v>1907</v>
       </c>
       <c r="C119" s="1"/>
       <c r="D119" s="1">
@@ -5487,7 +5511,7 @@
     <row r="120" ht="15" customHeight="1" spans="1:6">
       <c r="A120" s="1"/>
       <c r="B120" s="1">
-        <v>1912</v>
+        <v>1908</v>
       </c>
       <c r="C120" s="1"/>
       <c r="D120" s="1">
@@ -5503,7 +5527,7 @@
     <row r="121" ht="15" customHeight="1" spans="1:6">
       <c r="A121" s="1"/>
       <c r="B121" s="1">
-        <v>1913</v>
+        <v>1909</v>
       </c>
       <c r="C121" s="1"/>
       <c r="D121" s="1">
@@ -5519,7 +5543,7 @@
     <row r="122" ht="15" customHeight="1" spans="1:6">
       <c r="A122" s="1"/>
       <c r="B122" s="1">
-        <v>1914</v>
+        <v>1910</v>
       </c>
       <c r="C122" s="1"/>
       <c r="D122" s="1">
@@ -5535,7 +5559,7 @@
     <row r="123" ht="15" customHeight="1" spans="1:6">
       <c r="A123" s="1"/>
       <c r="B123" s="1">
-        <v>1915</v>
+        <v>1911</v>
       </c>
       <c r="C123" s="1"/>
       <c r="D123" s="1">
@@ -5551,7 +5575,7 @@
     <row r="124" ht="15" customHeight="1" spans="1:6">
       <c r="A124" s="1"/>
       <c r="B124" s="1">
-        <v>1916</v>
+        <v>1912</v>
       </c>
       <c r="C124" s="1"/>
       <c r="D124" s="1">
@@ -5567,7 +5591,7 @@
     <row r="125" ht="15" customHeight="1" spans="1:6">
       <c r="A125" s="1"/>
       <c r="B125" s="1">
-        <v>1917</v>
+        <v>1913</v>
       </c>
       <c r="C125" s="1"/>
       <c r="D125" s="1">
@@ -5583,7 +5607,7 @@
     <row r="126" ht="15" customHeight="1" spans="1:6">
       <c r="A126" s="1"/>
       <c r="B126" s="1">
-        <v>1918</v>
+        <v>1914</v>
       </c>
       <c r="C126" s="1"/>
       <c r="D126" s="1">
@@ -5599,7 +5623,7 @@
     <row r="127" ht="15" customHeight="1" spans="1:6">
       <c r="A127" s="1"/>
       <c r="B127" s="1">
-        <v>1919</v>
+        <v>1915</v>
       </c>
       <c r="C127" s="1"/>
       <c r="D127" s="1">
@@ -5615,7 +5639,7 @@
     <row r="128" ht="15" customHeight="1" spans="1:6">
       <c r="A128" s="1"/>
       <c r="B128" s="1">
-        <v>1920</v>
+        <v>1916</v>
       </c>
       <c r="C128" s="1"/>
       <c r="D128" s="1">
@@ -5631,7 +5655,7 @@
     <row r="129" ht="15" customHeight="1" spans="1:6">
       <c r="A129" s="1"/>
       <c r="B129" s="1">
-        <v>1921</v>
+        <v>1917</v>
       </c>
       <c r="C129" s="1"/>
       <c r="D129" s="1">
@@ -5647,7 +5671,7 @@
     <row r="130" ht="15" customHeight="1" spans="1:6">
       <c r="A130" s="1"/>
       <c r="B130" s="1">
-        <v>1922</v>
+        <v>1918</v>
       </c>
       <c r="C130" s="1"/>
       <c r="D130" s="1">
@@ -5663,7 +5687,7 @@
     <row r="131" ht="15" customHeight="1" spans="1:6">
       <c r="A131" s="1"/>
       <c r="B131" s="1">
-        <v>1923</v>
+        <v>1919</v>
       </c>
       <c r="C131" s="1"/>
       <c r="D131" s="1">
@@ -5679,7 +5703,7 @@
     <row r="132" ht="15" customHeight="1" spans="1:6">
       <c r="A132" s="1"/>
       <c r="B132" s="1">
-        <v>1924</v>
+        <v>1920</v>
       </c>
       <c r="C132" s="1"/>
       <c r="D132" s="1">
@@ -5695,7 +5719,7 @@
     <row r="133" ht="15" customHeight="1" spans="1:6">
       <c r="A133" s="1"/>
       <c r="B133" s="1">
-        <v>1925</v>
+        <v>1921</v>
       </c>
       <c r="C133" s="1"/>
       <c r="D133" s="1">
@@ -5711,7 +5735,7 @@
     <row r="134" ht="15" customHeight="1" spans="1:6">
       <c r="A134" s="1"/>
       <c r="B134" s="1">
-        <v>1926</v>
+        <v>1922</v>
       </c>
       <c r="C134" s="1"/>
       <c r="D134" s="1">
@@ -5727,7 +5751,7 @@
     <row r="135" ht="15" customHeight="1" spans="1:6">
       <c r="A135" s="1"/>
       <c r="B135" s="1">
-        <v>1927</v>
+        <v>1923</v>
       </c>
       <c r="C135" s="1"/>
       <c r="D135" s="1">
@@ -5743,7 +5767,7 @@
     <row r="136" ht="15" customHeight="1" spans="1:6">
       <c r="A136" s="1"/>
       <c r="B136" s="1">
-        <v>1928</v>
+        <v>1924</v>
       </c>
       <c r="C136" s="1"/>
       <c r="D136" s="1">
@@ -5759,7 +5783,7 @@
     <row r="137" ht="15" customHeight="1" spans="1:6">
       <c r="A137" s="1"/>
       <c r="B137" s="1">
-        <v>1929</v>
+        <v>1925</v>
       </c>
       <c r="C137" s="1"/>
       <c r="D137" s="1">
@@ -5775,7 +5799,7 @@
     <row r="138" ht="15" customHeight="1" spans="1:6">
       <c r="A138" s="1"/>
       <c r="B138" s="1">
-        <v>1930</v>
+        <v>1926</v>
       </c>
       <c r="C138" s="1"/>
       <c r="D138" s="1">
@@ -5791,7 +5815,7 @@
     <row r="139" ht="15" customHeight="1" spans="1:6">
       <c r="A139" s="1"/>
       <c r="B139" s="1">
-        <v>1931</v>
+        <v>1927</v>
       </c>
       <c r="C139" s="1"/>
       <c r="D139" s="1">
@@ -5807,7 +5831,7 @@
     <row r="140" ht="15" customHeight="1" spans="1:6">
       <c r="A140" s="1"/>
       <c r="B140" s="1">
-        <v>1932</v>
+        <v>1928</v>
       </c>
       <c r="C140" s="1"/>
       <c r="D140" s="1">
@@ -5823,7 +5847,7 @@
     <row r="141" ht="15" customHeight="1" spans="1:6">
       <c r="A141" s="1"/>
       <c r="B141" s="1">
-        <v>1933</v>
+        <v>1929</v>
       </c>
       <c r="C141" s="1"/>
       <c r="D141" s="1">
@@ -5839,7 +5863,7 @@
     <row r="142" ht="15" customHeight="1" spans="1:6">
       <c r="A142" s="1"/>
       <c r="B142" s="1">
-        <v>1934</v>
+        <v>1930</v>
       </c>
       <c r="C142" s="1"/>
       <c r="D142" s="1">
@@ -5855,7 +5879,7 @@
     <row r="143" ht="15" customHeight="1" spans="1:6">
       <c r="A143" s="1"/>
       <c r="B143" s="1">
-        <v>1935</v>
+        <v>1931</v>
       </c>
       <c r="C143" s="1"/>
       <c r="D143" s="1">
@@ -5871,7 +5895,7 @@
     <row r="144" ht="15" customHeight="1" spans="1:6">
       <c r="A144" s="1"/>
       <c r="B144" s="1">
-        <v>1936</v>
+        <v>1932</v>
       </c>
       <c r="C144" s="1"/>
       <c r="D144" s="1">
@@ -5887,7 +5911,7 @@
     <row r="145" ht="15" customHeight="1" spans="1:6">
       <c r="A145" s="1"/>
       <c r="B145" s="1">
-        <v>1937</v>
+        <v>1933</v>
       </c>
       <c r="C145" s="1"/>
       <c r="D145" s="1">
@@ -5903,7 +5927,7 @@
     <row r="146" ht="15" customHeight="1" spans="1:6">
       <c r="A146" s="1"/>
       <c r="B146" s="1">
-        <v>1938</v>
+        <v>1934</v>
       </c>
       <c r="C146" s="1"/>
       <c r="D146" s="1">
@@ -5919,7 +5943,7 @@
     <row r="147" ht="15" customHeight="1" spans="1:6">
       <c r="A147" s="1"/>
       <c r="B147" s="1">
-        <v>1939</v>
+        <v>1935</v>
       </c>
       <c r="C147" s="1"/>
       <c r="D147" s="1">
@@ -5935,7 +5959,7 @@
     <row r="148" ht="15" customHeight="1" spans="1:6">
       <c r="A148" s="1"/>
       <c r="B148" s="1">
-        <v>1940</v>
+        <v>1936</v>
       </c>
       <c r="C148" s="1"/>
       <c r="D148" s="1">
@@ -5951,7 +5975,7 @@
     <row r="149" ht="15" customHeight="1" spans="1:6">
       <c r="A149" s="1"/>
       <c r="B149" s="1">
-        <v>1941</v>
+        <v>1937</v>
       </c>
       <c r="C149" s="1"/>
       <c r="D149" s="1">
@@ -5967,7 +5991,7 @@
     <row r="150" ht="15" customHeight="1" spans="1:6">
       <c r="A150" s="1"/>
       <c r="B150" s="1">
-        <v>1942</v>
+        <v>1938</v>
       </c>
       <c r="C150" s="1"/>
       <c r="D150" s="1">
@@ -5983,7 +6007,7 @@
     <row r="151" ht="15" customHeight="1" spans="1:6">
       <c r="A151" s="1"/>
       <c r="B151" s="1">
-        <v>1943</v>
+        <v>1939</v>
       </c>
       <c r="C151" s="1"/>
       <c r="D151" s="1">
@@ -5999,7 +6023,7 @@
     <row r="152" ht="15" customHeight="1" spans="1:6">
       <c r="A152" s="1"/>
       <c r="B152" s="1">
-        <v>1944</v>
+        <v>1940</v>
       </c>
       <c r="C152" s="1"/>
       <c r="D152" s="1">
@@ -6015,7 +6039,7 @@
     <row r="153" ht="15" customHeight="1" spans="1:6">
       <c r="A153" s="1"/>
       <c r="B153" s="1">
-        <v>1945</v>
+        <v>1941</v>
       </c>
       <c r="C153" s="1"/>
       <c r="D153" s="1">
@@ -6031,7 +6055,7 @@
     <row r="154" ht="15" customHeight="1" spans="1:6">
       <c r="A154" s="1"/>
       <c r="B154" s="1">
-        <v>1946</v>
+        <v>1942</v>
       </c>
       <c r="C154" s="1"/>
       <c r="D154" s="1">
@@ -6047,7 +6071,7 @@
     <row r="155" ht="15" customHeight="1" spans="1:6">
       <c r="A155" s="1"/>
       <c r="B155" s="1">
-        <v>1947</v>
+        <v>1943</v>
       </c>
       <c r="C155" s="1"/>
       <c r="D155" s="1">
@@ -6063,7 +6087,7 @@
     <row r="156" ht="15" customHeight="1" spans="1:6">
       <c r="A156" s="1"/>
       <c r="B156" s="1">
-        <v>1948</v>
+        <v>1944</v>
       </c>
       <c r="C156" s="1"/>
       <c r="D156" s="1">
@@ -6079,11 +6103,11 @@
     <row r="157" ht="15" customHeight="1" spans="1:6">
       <c r="A157" s="1"/>
       <c r="B157" s="1">
-        <v>2001</v>
+        <v>1945</v>
       </c>
       <c r="C157" s="1"/>
       <c r="D157" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E157" s="1" t="s">
         <v>320</v>
@@ -6095,11 +6119,11 @@
     <row r="158" ht="15" customHeight="1" spans="1:6">
       <c r="A158" s="1"/>
       <c r="B158" s="1">
-        <v>2002</v>
+        <v>1946</v>
       </c>
       <c r="C158" s="1"/>
       <c r="D158" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E158" s="1" t="s">
         <v>322</v>
@@ -6111,11 +6135,11 @@
     <row r="159" ht="15" customHeight="1" spans="1:6">
       <c r="A159" s="1"/>
       <c r="B159" s="1">
-        <v>2003</v>
+        <v>1947</v>
       </c>
       <c r="C159" s="1"/>
       <c r="D159" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E159" s="1" t="s">
         <v>324</v>
@@ -6127,11 +6151,11 @@
     <row r="160" ht="15" customHeight="1" spans="1:6">
       <c r="A160" s="1"/>
       <c r="B160" s="1">
-        <v>2004</v>
+        <v>1948</v>
       </c>
       <c r="C160" s="1"/>
       <c r="D160" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E160" s="1" t="s">
         <v>326</v>
@@ -6143,7 +6167,7 @@
     <row r="161" ht="15" customHeight="1" spans="1:6">
       <c r="A161" s="1"/>
       <c r="B161" s="1">
-        <v>2101</v>
+        <v>2001</v>
       </c>
       <c r="C161" s="1"/>
       <c r="D161" s="1">
@@ -6159,34 +6183,30 @@
     <row r="162" ht="15" customHeight="1" spans="1:6">
       <c r="A162" s="1"/>
       <c r="B162" s="1">
-        <v>2102</v>
-      </c>
-      <c r="C162" s="1" t="s">
-        <v>330</v>
-      </c>
+        <v>2002</v>
+      </c>
+      <c r="C162" s="1"/>
       <c r="D162" s="1">
         <v>2</v>
       </c>
       <c r="E162" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="F162" s="1" t="s">
         <v>331</v>
-      </c>
-      <c r="F162" s="1" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="163" ht="15" customHeight="1" spans="1:6">
       <c r="A163" s="1"/>
       <c r="B163" s="1">
-        <v>2103</v>
-      </c>
-      <c r="C163" s="1" t="s">
-        <v>330</v>
-      </c>
+        <v>2003</v>
+      </c>
+      <c r="C163" s="1"/>
       <c r="D163" s="1">
         <v>2</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F163" s="1" t="s">
         <v>333</v>
@@ -6195,59 +6215,61 @@
     <row r="164" ht="15" customHeight="1" spans="1:6">
       <c r="A164" s="1"/>
       <c r="B164" s="1">
-        <v>2104</v>
-      </c>
-      <c r="C164" s="1" t="s">
-        <v>330</v>
-      </c>
+        <v>2004</v>
+      </c>
+      <c r="C164" s="1"/>
       <c r="D164" s="1">
         <v>2</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="165" ht="15" customHeight="1" spans="1:6">
       <c r="A165" s="1"/>
       <c r="B165" s="1">
-        <v>2201</v>
+        <v>2101</v>
       </c>
       <c r="C165" s="1"/>
       <c r="D165" s="1">
         <v>2</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="166" ht="15" customHeight="1" spans="1:6">
       <c r="A166" s="1"/>
       <c r="B166" s="1">
-        <v>2301</v>
-      </c>
-      <c r="C166" s="1"/>
+        <v>2102</v>
+      </c>
+      <c r="C166" s="1" t="s">
+        <v>338</v>
+      </c>
       <c r="D166" s="1">
         <v>2</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="167" ht="15" customHeight="1" spans="1:6">
       <c r="A167" s="1"/>
       <c r="B167" s="1">
-        <v>2304</v>
-      </c>
-      <c r="C167" s="1"/>
+        <v>2103</v>
+      </c>
+      <c r="C167" s="1" t="s">
+        <v>338</v>
+      </c>
       <c r="D167" s="1">
         <v>2</v>
       </c>
@@ -6255,20 +6277,22 @@
         <v>339</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="168" ht="15" customHeight="1" spans="1:6">
       <c r="A168" s="1"/>
       <c r="B168" s="1">
-        <v>2309</v>
-      </c>
-      <c r="C168" s="1"/>
+        <v>2104</v>
+      </c>
+      <c r="C168" s="1" t="s">
+        <v>338</v>
+      </c>
       <c r="D168" s="1">
         <v>2</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>342</v>
@@ -6277,7 +6301,7 @@
     <row r="169" ht="15" customHeight="1" spans="1:6">
       <c r="A169" s="1"/>
       <c r="B169" s="1">
-        <v>2310</v>
+        <v>2201</v>
       </c>
       <c r="C169" s="1"/>
       <c r="D169" s="1">
@@ -6293,7 +6317,7 @@
     <row r="170" ht="15" customHeight="1" spans="1:6">
       <c r="A170" s="1"/>
       <c r="B170" s="1">
-        <v>2311</v>
+        <v>2301</v>
       </c>
       <c r="C170" s="1"/>
       <c r="D170" s="1">
@@ -6309,7 +6333,7 @@
     <row r="171" ht="15" customHeight="1" spans="1:6">
       <c r="A171" s="1"/>
       <c r="B171" s="1">
-        <v>2312</v>
+        <v>2304</v>
       </c>
       <c r="C171" s="1"/>
       <c r="D171" s="1">
@@ -6325,75 +6349,75 @@
     <row r="172" ht="15" customHeight="1" spans="1:6">
       <c r="A172" s="1"/>
       <c r="B172" s="1">
-        <v>2313</v>
-      </c>
-      <c r="C172" s="1" t="s">
-        <v>349</v>
-      </c>
+        <v>2309</v>
+      </c>
+      <c r="C172" s="1"/>
       <c r="D172" s="1">
         <v>2</v>
       </c>
       <c r="E172" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="F172" s="1" t="s">
         <v>350</v>
-      </c>
-      <c r="F172" s="1" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="173" ht="15" customHeight="1" spans="1:6">
       <c r="A173" s="1"/>
       <c r="B173" s="1">
-        <v>2399</v>
+        <v>2310</v>
       </c>
       <c r="C173" s="1"/>
       <c r="D173" s="1">
         <v>2</v>
       </c>
       <c r="E173" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="F173" s="1" t="s">
         <v>352</v>
-      </c>
-      <c r="F173" s="1" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="174" ht="15" customHeight="1" spans="1:6">
       <c r="A174" s="1"/>
       <c r="B174" s="1">
-        <v>2401</v>
+        <v>2311</v>
       </c>
       <c r="C174" s="1"/>
       <c r="D174" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E174" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="F174" s="1" t="s">
         <v>354</v>
-      </c>
-      <c r="F174" s="1" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="175" ht="15" customHeight="1" spans="1:6">
       <c r="A175" s="1"/>
       <c r="B175" s="1">
-        <v>2402</v>
+        <v>2312</v>
       </c>
       <c r="C175" s="1"/>
       <c r="D175" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E175" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="F175" s="1" t="s">
         <v>356</v>
-      </c>
-      <c r="F175" s="1" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="176" ht="15" customHeight="1" spans="1:6">
       <c r="A176" s="1"/>
       <c r="B176" s="1">
-        <v>2501</v>
-      </c>
-      <c r="C176" s="1"/>
+        <v>2313</v>
+      </c>
+      <c r="C176" s="1" t="s">
+        <v>357</v>
+      </c>
       <c r="D176" s="1">
         <v>2</v>
       </c>
@@ -6407,7 +6431,7 @@
     <row r="177" ht="15" customHeight="1" spans="1:6">
       <c r="A177" s="1"/>
       <c r="B177" s="1">
-        <v>2502</v>
+        <v>2399</v>
       </c>
       <c r="C177" s="1"/>
       <c r="D177" s="1">
@@ -6423,11 +6447,11 @@
     <row r="178" ht="15" customHeight="1" spans="1:6">
       <c r="A178" s="1"/>
       <c r="B178" s="1">
-        <v>2503</v>
+        <v>2401</v>
       </c>
       <c r="C178" s="1"/>
       <c r="D178" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E178" s="1" t="s">
         <v>362</v>
@@ -6439,11 +6463,11 @@
     <row r="179" ht="15" customHeight="1" spans="1:6">
       <c r="A179" s="1"/>
       <c r="B179" s="1">
-        <v>2504</v>
+        <v>2402</v>
       </c>
       <c r="C179" s="1"/>
       <c r="D179" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E179" s="1" t="s">
         <v>364</v>
@@ -6455,7 +6479,7 @@
     <row r="180" ht="15" customHeight="1" spans="1:6">
       <c r="A180" s="1"/>
       <c r="B180" s="1">
-        <v>2600</v>
+        <v>2501</v>
       </c>
       <c r="C180" s="1"/>
       <c r="D180" s="1">
@@ -6471,7 +6495,7 @@
     <row r="181" ht="15" customHeight="1" spans="1:6">
       <c r="A181" s="1"/>
       <c r="B181" s="1">
-        <v>2601</v>
+        <v>2502</v>
       </c>
       <c r="C181" s="1"/>
       <c r="D181" s="1">
@@ -6487,7 +6511,7 @@
     <row r="182" ht="15" customHeight="1" spans="1:6">
       <c r="A182" s="1"/>
       <c r="B182" s="1">
-        <v>2901</v>
+        <v>2503</v>
       </c>
       <c r="C182" s="1"/>
       <c r="D182" s="1">
@@ -6503,11 +6527,11 @@
     <row r="183" ht="15" customHeight="1" spans="1:6">
       <c r="A183" s="1"/>
       <c r="B183" s="1">
-        <v>3001</v>
+        <v>2504</v>
       </c>
       <c r="C183" s="1"/>
       <c r="D183" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E183" s="1" t="s">
         <v>372</v>
@@ -6519,11 +6543,11 @@
     <row r="184" ht="15" customHeight="1" spans="1:6">
       <c r="A184" s="1"/>
       <c r="B184" s="1">
-        <v>3002</v>
+        <v>2600</v>
       </c>
       <c r="C184" s="1"/>
       <c r="D184" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E184" s="1" t="s">
         <v>374</v>
@@ -6535,11 +6559,11 @@
     <row r="185" ht="15" customHeight="1" spans="1:6">
       <c r="A185" s="1"/>
       <c r="B185" s="1">
-        <v>3003</v>
+        <v>2601</v>
       </c>
       <c r="C185" s="1"/>
       <c r="D185" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E185" s="1" t="s">
         <v>376</v>
@@ -6551,11 +6575,11 @@
     <row r="186" ht="15" customHeight="1" spans="1:6">
       <c r="A186" s="1"/>
       <c r="B186" s="1">
-        <v>3004</v>
+        <v>2901</v>
       </c>
       <c r="C186" s="1"/>
       <c r="D186" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E186" s="1" t="s">
         <v>378</v>
@@ -6567,7 +6591,7 @@
     <row r="187" ht="15" customHeight="1" spans="1:6">
       <c r="A187" s="1"/>
       <c r="B187" s="1">
-        <v>3005</v>
+        <v>3001</v>
       </c>
       <c r="C187" s="1"/>
       <c r="D187" s="1">
@@ -6583,7 +6607,7 @@
     <row r="188" ht="15" customHeight="1" spans="1:6">
       <c r="A188" s="1"/>
       <c r="B188" s="1">
-        <v>3006</v>
+        <v>3002</v>
       </c>
       <c r="C188" s="1"/>
       <c r="D188" s="1">
@@ -6599,7 +6623,7 @@
     <row r="189" ht="15" customHeight="1" spans="1:6">
       <c r="A189" s="1"/>
       <c r="B189" s="1">
-        <v>3007</v>
+        <v>3003</v>
       </c>
       <c r="C189" s="1"/>
       <c r="D189" s="1">
@@ -6615,7 +6639,7 @@
     <row r="190" ht="15" customHeight="1" spans="1:6">
       <c r="A190" s="1"/>
       <c r="B190" s="1">
-        <v>3008</v>
+        <v>3004</v>
       </c>
       <c r="C190" s="1"/>
       <c r="D190" s="1">
@@ -6631,7 +6655,7 @@
     <row r="191" ht="15" customHeight="1" spans="1:6">
       <c r="A191" s="1"/>
       <c r="B191" s="1">
-        <v>3009</v>
+        <v>3005</v>
       </c>
       <c r="C191" s="1"/>
       <c r="D191" s="1">
@@ -6647,11 +6671,9 @@
     <row r="192" ht="15" customHeight="1" spans="1:6">
       <c r="A192" s="1"/>
       <c r="B192" s="1">
-        <v>3010</v>
-      </c>
-      <c r="C192" s="1" t="s">
-        <v>179</v>
-      </c>
+        <v>3006</v>
+      </c>
+      <c r="C192" s="1"/>
       <c r="D192" s="1">
         <v>3</v>
       </c>
@@ -6665,82 +6687,76 @@
     <row r="193" ht="15" customHeight="1" spans="1:6">
       <c r="A193" s="1"/>
       <c r="B193" s="1">
-        <v>3011</v>
-      </c>
-      <c r="C193" s="1" t="s">
-        <v>392</v>
-      </c>
+        <v>3007</v>
+      </c>
+      <c r="C193" s="1"/>
       <c r="D193" s="1">
         <v>3</v>
       </c>
       <c r="E193" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="F193" s="1" t="s">
         <v>393</v>
-      </c>
-      <c r="F193" s="1" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="194" ht="15" customHeight="1" spans="1:6">
       <c r="A194" s="1"/>
       <c r="B194" s="1">
-        <v>3012</v>
-      </c>
-      <c r="C194" s="1" t="s">
-        <v>392</v>
-      </c>
+        <v>3008</v>
+      </c>
+      <c r="C194" s="1"/>
       <c r="D194" s="1">
         <v>3</v>
       </c>
       <c r="E194" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="F194" s="1" t="s">
         <v>395</v>
-      </c>
-      <c r="F194" s="1" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="195" ht="15" customHeight="1" spans="1:6">
       <c r="A195" s="1"/>
       <c r="B195" s="1">
-        <v>3013</v>
-      </c>
-      <c r="C195" s="1" t="s">
-        <v>392</v>
-      </c>
+        <v>3009</v>
+      </c>
+      <c r="C195" s="1"/>
       <c r="D195" s="1">
         <v>3</v>
       </c>
       <c r="E195" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="F195" s="1" t="s">
         <v>397</v>
-      </c>
-      <c r="F195" s="1" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="196" ht="15" customHeight="1" spans="1:6">
       <c r="A196" s="1"/>
       <c r="B196" s="1">
-        <v>3014</v>
+        <v>3010</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>392</v>
+        <v>187</v>
       </c>
       <c r="D196" s="1">
         <v>3</v>
       </c>
       <c r="E196" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="F196" s="1" t="s">
         <v>399</v>
-      </c>
-      <c r="F196" s="1" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="197" ht="15" customHeight="1" spans="1:6">
       <c r="A197" s="1"/>
       <c r="B197" s="1">
-        <v>3015</v>
+        <v>3011</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="D197" s="1">
         <v>3</v>
@@ -6755,10 +6771,10 @@
     <row r="198" ht="15" customHeight="1" spans="1:6">
       <c r="A198" s="1"/>
       <c r="B198" s="1">
-        <v>3016</v>
+        <v>3012</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="D198" s="1">
         <v>3</v>
@@ -6773,10 +6789,10 @@
     <row r="199" ht="15" customHeight="1" spans="1:6">
       <c r="A199" s="1"/>
       <c r="B199" s="1">
-        <v>3017</v>
+        <v>3013</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="D199" s="1">
         <v>3</v>
@@ -6791,10 +6807,10 @@
     <row r="200" ht="15" customHeight="1" spans="1:6">
       <c r="A200" s="1"/>
       <c r="B200" s="1">
-        <v>3018</v>
+        <v>3014</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="D200" s="1">
         <v>3</v>
@@ -6809,10 +6825,10 @@
     <row r="201" ht="15" customHeight="1" spans="1:6">
       <c r="A201" s="1"/>
       <c r="B201" s="1">
-        <v>3019</v>
+        <v>3015</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="D201" s="1">
         <v>3</v>
@@ -6827,9 +6843,11 @@
     <row r="202" ht="15" customHeight="1" spans="1:6">
       <c r="A202" s="1"/>
       <c r="B202" s="1">
-        <v>3101</v>
-      </c>
-      <c r="C202" s="1"/>
+        <v>3016</v>
+      </c>
+      <c r="C202" s="1" t="s">
+        <v>400</v>
+      </c>
       <c r="D202" s="1">
         <v>3</v>
       </c>
@@ -6843,9 +6861,11 @@
     <row r="203" ht="15" customHeight="1" spans="1:6">
       <c r="A203" s="1"/>
       <c r="B203" s="1">
-        <v>3102</v>
-      </c>
-      <c r="C203" s="1"/>
+        <v>3017</v>
+      </c>
+      <c r="C203" s="1" t="s">
+        <v>400</v>
+      </c>
       <c r="D203" s="1">
         <v>3</v>
       </c>
@@ -6859,9 +6879,11 @@
     <row r="204" ht="15" customHeight="1" spans="1:6">
       <c r="A204" s="1"/>
       <c r="B204" s="1">
-        <v>3103</v>
-      </c>
-      <c r="C204" s="1"/>
+        <v>3018</v>
+      </c>
+      <c r="C204" s="1" t="s">
+        <v>400</v>
+      </c>
       <c r="D204" s="1">
         <v>3</v>
       </c>
@@ -6875,9 +6897,11 @@
     <row r="205" ht="15" customHeight="1" spans="1:6">
       <c r="A205" s="1"/>
       <c r="B205" s="1">
-        <v>3104</v>
-      </c>
-      <c r="C205" s="1"/>
+        <v>3019</v>
+      </c>
+      <c r="C205" s="1" t="s">
+        <v>400</v>
+      </c>
       <c r="D205" s="1">
         <v>3</v>
       </c>
@@ -6891,7 +6915,7 @@
     <row r="206" ht="15" customHeight="1" spans="1:6">
       <c r="A206" s="1"/>
       <c r="B206" s="1">
-        <v>3105</v>
+        <v>3101</v>
       </c>
       <c r="C206" s="1"/>
       <c r="D206" s="1">
@@ -6907,113 +6931,113 @@
     <row r="207" ht="15" customHeight="1" spans="1:6">
       <c r="A207" s="1"/>
       <c r="B207" s="1">
-        <v>3201</v>
-      </c>
-      <c r="C207" s="1" t="s">
-        <v>421</v>
-      </c>
+        <v>3102</v>
+      </c>
+      <c r="C207" s="1"/>
       <c r="D207" s="1">
         <v>3</v>
       </c>
       <c r="E207" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="F207" s="1" t="s">
         <v>422</v>
-      </c>
-      <c r="F207" s="1" t="s">
-        <v>421</v>
       </c>
     </row>
     <row r="208" ht="15" customHeight="1" spans="1:6">
       <c r="A208" s="1"/>
       <c r="B208" s="1">
-        <v>3202</v>
-      </c>
-      <c r="C208" s="1" t="s">
-        <v>423</v>
-      </c>
+        <v>3103</v>
+      </c>
+      <c r="C208" s="1"/>
       <c r="D208" s="1">
         <v>3</v>
       </c>
       <c r="E208" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="F208" s="1" t="s">
         <v>424</v>
-      </c>
-      <c r="F208" s="1" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="209" ht="15" customHeight="1" spans="1:6">
       <c r="A209" s="1"/>
       <c r="B209" s="1">
-        <v>6001</v>
-      </c>
-      <c r="C209" s="1" t="s">
+        <v>3104</v>
+      </c>
+      <c r="C209" s="1"/>
+      <c r="D209" s="1">
+        <v>3</v>
+      </c>
+      <c r="E209" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="D209" s="1">
-        <v>6</v>
-      </c>
-      <c r="E209" s="1" t="s">
+      <c r="F209" s="1" t="s">
         <v>426</v>
-      </c>
-      <c r="F209" s="1" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="210" ht="15" customHeight="1" spans="1:6">
       <c r="A210" s="1"/>
       <c r="B210" s="1">
-        <v>10001</v>
+        <v>3105</v>
       </c>
       <c r="C210" s="1"/>
       <c r="D210" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E210" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="F210" s="1" t="s">
         <v>428</v>
-      </c>
-      <c r="F210" s="1" t="s">
-        <v>429</v>
       </c>
     </row>
     <row r="211" ht="15" customHeight="1" spans="1:6">
       <c r="A211" s="1"/>
       <c r="B211" s="1">
-        <v>10002</v>
-      </c>
-      <c r="C211" s="1"/>
+        <v>3201</v>
+      </c>
+      <c r="C211" s="1" t="s">
+        <v>429</v>
+      </c>
       <c r="D211" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E211" s="1" t="s">
         <v>430</v>
       </c>
       <c r="F211" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="212" ht="15" customHeight="1" spans="1:6">
       <c r="A212" s="1"/>
       <c r="B212" s="1">
-        <v>10003</v>
-      </c>
-      <c r="C212" s="1"/>
+        <v>3202</v>
+      </c>
+      <c r="C212" s="1" t="s">
+        <v>431</v>
+      </c>
       <c r="D212" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E212" s="1" t="s">
         <v>432</v>
       </c>
       <c r="F212" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="213" ht="15" customHeight="1" spans="1:6">
       <c r="A213" s="1"/>
       <c r="B213" s="1">
-        <v>10004</v>
-      </c>
-      <c r="C213" s="1"/>
+        <v>6001</v>
+      </c>
+      <c r="C213" s="1" t="s">
+        <v>433</v>
+      </c>
       <c r="D213" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E213" s="1" t="s">
         <v>434</v>
@@ -7025,7 +7049,7 @@
     <row r="214" ht="15" customHeight="1" spans="1:6">
       <c r="A214" s="1"/>
       <c r="B214" s="1">
-        <v>10101</v>
+        <v>10001</v>
       </c>
       <c r="C214" s="1"/>
       <c r="D214" s="1">
@@ -7041,7 +7065,7 @@
     <row r="215" ht="15" customHeight="1" spans="1:6">
       <c r="A215" s="1"/>
       <c r="B215" s="1">
-        <v>10102</v>
+        <v>10002</v>
       </c>
       <c r="C215" s="1"/>
       <c r="D215" s="1">
@@ -7057,7 +7081,7 @@
     <row r="216" ht="15" customHeight="1" spans="1:6">
       <c r="A216" s="1"/>
       <c r="B216" s="1">
-        <v>10103</v>
+        <v>10003</v>
       </c>
       <c r="C216" s="1"/>
       <c r="D216" s="1">
@@ -7073,7 +7097,7 @@
     <row r="217" ht="15" customHeight="1" spans="1:6">
       <c r="A217" s="1"/>
       <c r="B217" s="1">
-        <v>10201</v>
+        <v>10004</v>
       </c>
       <c r="C217" s="1"/>
       <c r="D217" s="1">
@@ -7089,7 +7113,7 @@
     <row r="218" ht="15" customHeight="1" spans="1:6">
       <c r="A218" s="1"/>
       <c r="B218" s="1">
-        <v>10202</v>
+        <v>10101</v>
       </c>
       <c r="C218" s="1"/>
       <c r="D218" s="1">
@@ -7105,7 +7129,7 @@
     <row r="219" ht="15" customHeight="1" spans="1:6">
       <c r="A219" s="1"/>
       <c r="B219" s="1">
-        <v>10203</v>
+        <v>10102</v>
       </c>
       <c r="C219" s="1"/>
       <c r="D219" s="1">
@@ -7121,7 +7145,7 @@
     <row r="220" ht="15" customHeight="1" spans="1:6">
       <c r="A220" s="1"/>
       <c r="B220" s="1">
-        <v>13001</v>
+        <v>10103</v>
       </c>
       <c r="C220" s="1"/>
       <c r="D220" s="1">
@@ -7137,7 +7161,7 @@
     <row r="221" ht="15" customHeight="1" spans="1:6">
       <c r="A221" s="1"/>
       <c r="B221" s="1">
-        <v>13004</v>
+        <v>10201</v>
       </c>
       <c r="C221" s="1"/>
       <c r="D221" s="1">
@@ -7153,7 +7177,7 @@
     <row r="222" ht="15" customHeight="1" spans="1:6">
       <c r="A222" s="1"/>
       <c r="B222" s="1">
-        <v>13010</v>
+        <v>10202</v>
       </c>
       <c r="C222" s="1"/>
       <c r="D222" s="1">
@@ -7169,7 +7193,7 @@
     <row r="223" ht="15" customHeight="1" spans="1:6">
       <c r="A223" s="1"/>
       <c r="B223" s="1">
-        <v>13011</v>
+        <v>10203</v>
       </c>
       <c r="C223" s="1"/>
       <c r="D223" s="1">
@@ -7185,7 +7209,7 @@
     <row r="224" ht="15" customHeight="1" spans="1:6">
       <c r="A224" s="1"/>
       <c r="B224" s="1">
-        <v>13012</v>
+        <v>13001</v>
       </c>
       <c r="C224" s="1"/>
       <c r="D224" s="1">
@@ -7201,7 +7225,7 @@
     <row r="225" ht="15" customHeight="1" spans="1:6">
       <c r="A225" s="1"/>
       <c r="B225" s="1">
-        <v>13013</v>
+        <v>13004</v>
       </c>
       <c r="C225" s="1"/>
       <c r="D225" s="1">
@@ -7217,7 +7241,7 @@
     <row r="226" ht="15" customHeight="1" spans="1:6">
       <c r="A226" s="1"/>
       <c r="B226" s="1">
-        <v>13999</v>
+        <v>13010</v>
       </c>
       <c r="C226" s="1"/>
       <c r="D226" s="1">
@@ -7233,7 +7257,7 @@
     <row r="227" ht="15" customHeight="1" spans="1:6">
       <c r="A227" s="1"/>
       <c r="B227" s="1">
-        <v>15001</v>
+        <v>13011</v>
       </c>
       <c r="C227" s="1"/>
       <c r="D227" s="1">
@@ -7249,75 +7273,75 @@
     <row r="228" ht="15" customHeight="1" spans="1:6">
       <c r="A228" s="1"/>
       <c r="B228" s="1">
-        <v>15002</v>
-      </c>
-      <c r="C228" s="1" t="s">
+        <v>13012</v>
+      </c>
+      <c r="C228" s="1"/>
+      <c r="D228" s="1">
+        <v>1</v>
+      </c>
+      <c r="E228" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="D228" s="1">
-        <v>1</v>
-      </c>
-      <c r="E228" s="1" t="s">
+      <c r="F228" s="1" t="s">
         <v>465</v>
-      </c>
-      <c r="F228" s="1" t="s">
-        <v>466</v>
       </c>
     </row>
     <row r="229" ht="15" customHeight="1" spans="1:6">
       <c r="A229" s="1"/>
       <c r="B229" s="1">
-        <v>15003</v>
+        <v>13013</v>
       </c>
       <c r="C229" s="1"/>
       <c r="D229" s="1">
         <v>1</v>
       </c>
       <c r="E229" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="F229" s="1" t="s">
         <v>467</v>
-      </c>
-      <c r="F229" s="1" t="s">
-        <v>468</v>
       </c>
     </row>
     <row r="230" ht="15" customHeight="1" spans="1:6">
       <c r="A230" s="1"/>
       <c r="B230" s="1">
-        <v>15005</v>
+        <v>13999</v>
       </c>
       <c r="C230" s="1"/>
       <c r="D230" s="1">
         <v>1</v>
       </c>
       <c r="E230" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="F230" s="1" t="s">
         <v>469</v>
-      </c>
-      <c r="F230" s="1" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="231" ht="15" customHeight="1" spans="1:6">
       <c r="A231" s="1"/>
       <c r="B231" s="1">
-        <v>15007</v>
+        <v>15001</v>
       </c>
       <c r="C231" s="1"/>
       <c r="D231" s="1">
         <v>1</v>
       </c>
       <c r="E231" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="F231" s="1" t="s">
         <v>471</v>
-      </c>
-      <c r="F231" s="1" t="s">
-        <v>472</v>
       </c>
     </row>
     <row r="232" ht="15" customHeight="1" spans="1:6">
       <c r="A232" s="1"/>
       <c r="B232" s="1">
-        <v>15008</v>
-      </c>
-      <c r="C232" s="1"/>
+        <v>15002</v>
+      </c>
+      <c r="C232" s="1" t="s">
+        <v>472</v>
+      </c>
       <c r="D232" s="1">
         <v>1</v>
       </c>
@@ -7331,7 +7355,7 @@
     <row r="233" ht="15" customHeight="1" spans="1:6">
       <c r="A233" s="1"/>
       <c r="B233" s="1">
-        <v>15009</v>
+        <v>15003</v>
       </c>
       <c r="C233" s="1"/>
       <c r="D233" s="1">
@@ -7347,7 +7371,7 @@
     <row r="234" ht="15" customHeight="1" spans="1:6">
       <c r="A234" s="1"/>
       <c r="B234" s="1">
-        <v>15011</v>
+        <v>15005</v>
       </c>
       <c r="C234" s="1"/>
       <c r="D234" s="1">
@@ -7363,7 +7387,7 @@
     <row r="235" ht="15" customHeight="1" spans="1:6">
       <c r="A235" s="1"/>
       <c r="B235" s="1">
-        <v>15012</v>
+        <v>15007</v>
       </c>
       <c r="C235" s="1"/>
       <c r="D235" s="1">
@@ -7379,7 +7403,7 @@
     <row r="236" ht="15" customHeight="1" spans="1:6">
       <c r="A236" s="1"/>
       <c r="B236" s="1">
-        <v>15013</v>
+        <v>15008</v>
       </c>
       <c r="C236" s="1"/>
       <c r="D236" s="1">
@@ -7395,7 +7419,7 @@
     <row r="237" ht="15" customHeight="1" spans="1:6">
       <c r="A237" s="1"/>
       <c r="B237" s="1">
-        <v>15014</v>
+        <v>15009</v>
       </c>
       <c r="C237" s="1"/>
       <c r="D237" s="1">
@@ -7411,7 +7435,7 @@
     <row r="238" ht="15" customHeight="1" spans="1:6">
       <c r="A238" s="1"/>
       <c r="B238" s="1">
-        <v>15015</v>
+        <v>15011</v>
       </c>
       <c r="C238" s="1"/>
       <c r="D238" s="1">
@@ -7427,7 +7451,7 @@
     <row r="239" ht="15" customHeight="1" spans="1:6">
       <c r="A239" s="1"/>
       <c r="B239" s="1">
-        <v>15017</v>
+        <v>15012</v>
       </c>
       <c r="C239" s="1"/>
       <c r="D239" s="1">
@@ -7443,7 +7467,7 @@
     <row r="240" ht="15" customHeight="1" spans="1:6">
       <c r="A240" s="1"/>
       <c r="B240" s="1">
-        <v>15018</v>
+        <v>15013</v>
       </c>
       <c r="C240" s="1"/>
       <c r="D240" s="1">
@@ -7459,7 +7483,7 @@
     <row r="241" ht="15" customHeight="1" spans="1:6">
       <c r="A241" s="1"/>
       <c r="B241" s="1">
-        <v>15019</v>
+        <v>15014</v>
       </c>
       <c r="C241" s="1"/>
       <c r="D241" s="1">
@@ -7475,7 +7499,7 @@
     <row r="242" ht="15" customHeight="1" spans="1:6">
       <c r="A242" s="1"/>
       <c r="B242" s="1">
-        <v>15020</v>
+        <v>15015</v>
       </c>
       <c r="C242" s="1"/>
       <c r="D242" s="1">
@@ -7491,7 +7515,7 @@
     <row r="243" ht="15" customHeight="1" spans="1:6">
       <c r="A243" s="1"/>
       <c r="B243" s="1">
-        <v>15021</v>
+        <v>15017</v>
       </c>
       <c r="C243" s="1"/>
       <c r="D243" s="1">
@@ -7507,100 +7531,92 @@
     <row r="244" ht="15" customHeight="1" spans="1:6">
       <c r="A244" s="1"/>
       <c r="B244" s="1">
-        <v>15022</v>
-      </c>
-      <c r="C244" s="1" t="s">
+        <v>15018</v>
+      </c>
+      <c r="C244" s="1"/>
+      <c r="D244" s="1">
+        <v>1</v>
+      </c>
+      <c r="E244" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="D244" s="1">
-        <v>1</v>
-      </c>
-      <c r="E244" s="1" t="s">
+      <c r="F244" s="1" t="s">
         <v>498</v>
-      </c>
-      <c r="F244" s="1" t="s">
-        <v>499</v>
       </c>
     </row>
     <row r="245" ht="15" customHeight="1" spans="1:6">
       <c r="A245" s="1"/>
       <c r="B245" s="1">
-        <v>16001</v>
-      </c>
-      <c r="C245" s="1" t="s">
+        <v>15019</v>
+      </c>
+      <c r="C245" s="1"/>
+      <c r="D245" s="1">
+        <v>1</v>
+      </c>
+      <c r="E245" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="F245" s="1" t="s">
         <v>500</v>
-      </c>
-      <c r="D245" s="1">
-        <v>1</v>
-      </c>
-      <c r="E245" s="1" t="s">
-        <v>501</v>
-      </c>
-      <c r="F245" s="1" t="s">
-        <v>502</v>
       </c>
     </row>
     <row r="246" ht="15" customHeight="1" spans="1:6">
       <c r="A246" s="1"/>
       <c r="B246" s="1">
-        <v>16002</v>
-      </c>
-      <c r="C246" s="1" t="s">
-        <v>500</v>
-      </c>
+        <v>15020</v>
+      </c>
+      <c r="C246" s="1"/>
       <c r="D246" s="1">
         <v>1</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="F246" s="1" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="247" ht="15" customHeight="1" spans="1:6">
       <c r="A247" s="1"/>
       <c r="B247" s="1">
-        <v>16003</v>
-      </c>
-      <c r="C247" s="1" t="s">
-        <v>500</v>
-      </c>
+        <v>15021</v>
+      </c>
+      <c r="C247" s="1"/>
       <c r="D247" s="1">
         <v>1</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="F247" s="1" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="248" ht="15" customHeight="1" spans="1:6">
       <c r="A248" s="1"/>
       <c r="B248" s="1">
-        <v>16004</v>
+        <v>15022</v>
       </c>
       <c r="C248" s="1" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="D248" s="1">
         <v>1</v>
       </c>
       <c r="E248" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="F248" s="1" t="s">
         <v>507</v>
-      </c>
-      <c r="F248" s="1" t="s">
-        <v>508</v>
       </c>
     </row>
     <row r="249" ht="15" customHeight="1" spans="1:6">
       <c r="A249" s="1"/>
       <c r="B249" s="1">
-        <v>16005</v>
+        <v>16001</v>
       </c>
       <c r="C249" s="1" t="s">
-        <v>500</v>
+        <v>508</v>
       </c>
       <c r="D249" s="1">
         <v>1</v>
@@ -7615,10 +7631,10 @@
     <row r="250" ht="15" customHeight="1" spans="1:6">
       <c r="A250" s="1"/>
       <c r="B250" s="1">
-        <v>16006</v>
+        <v>16002</v>
       </c>
       <c r="C250" s="1" t="s">
-        <v>500</v>
+        <v>508</v>
       </c>
       <c r="D250" s="1">
         <v>1</v>
@@ -7630,12 +7646,14 @@
         <v>512</v>
       </c>
     </row>
-    <row r="251" ht="14" customHeight="1" spans="1:6">
+    <row r="251" ht="15" customHeight="1" spans="1:6">
       <c r="A251" s="1"/>
       <c r="B251" s="1">
-        <v>19001</v>
-      </c>
-      <c r="C251" s="1"/>
+        <v>16003</v>
+      </c>
+      <c r="C251" s="1" t="s">
+        <v>508</v>
+      </c>
       <c r="D251" s="1">
         <v>1</v>
       </c>
@@ -7646,12 +7664,14 @@
         <v>514</v>
       </c>
     </row>
-    <row r="252" ht="14" customHeight="1" spans="1:6">
+    <row r="252" ht="15" customHeight="1" spans="1:6">
       <c r="A252" s="1"/>
       <c r="B252" s="1">
-        <v>19002</v>
-      </c>
-      <c r="C252" s="1"/>
+        <v>16004</v>
+      </c>
+      <c r="C252" s="1" t="s">
+        <v>508</v>
+      </c>
       <c r="D252" s="1">
         <v>1</v>
       </c>
@@ -7665,9 +7685,11 @@
     <row r="253" ht="15" customHeight="1" spans="1:6">
       <c r="A253" s="1"/>
       <c r="B253" s="1">
-        <v>19003</v>
-      </c>
-      <c r="C253" s="1"/>
+        <v>16005</v>
+      </c>
+      <c r="C253" s="1" t="s">
+        <v>508</v>
+      </c>
       <c r="D253" s="1">
         <v>1</v>
       </c>
@@ -7681,9 +7703,11 @@
     <row r="254" ht="15" customHeight="1" spans="1:6">
       <c r="A254" s="1"/>
       <c r="B254" s="1">
-        <v>19004</v>
-      </c>
-      <c r="C254" s="1"/>
+        <v>16006</v>
+      </c>
+      <c r="C254" s="1" t="s">
+        <v>508</v>
+      </c>
       <c r="D254" s="1">
         <v>1</v>
       </c>
@@ -7694,10 +7718,10 @@
         <v>520</v>
       </c>
     </row>
-    <row r="255" ht="15" customHeight="1" spans="1:6">
+    <row r="255" ht="14" customHeight="1" spans="1:6">
       <c r="A255" s="1"/>
       <c r="B255" s="1">
-        <v>19011</v>
+        <v>19001</v>
       </c>
       <c r="C255" s="1"/>
       <c r="D255" s="1">
@@ -7710,10 +7734,10 @@
         <v>522</v>
       </c>
     </row>
-    <row r="256" ht="15" customHeight="1" spans="1:6">
+    <row r="256" ht="14" customHeight="1" spans="1:6">
       <c r="A256" s="1"/>
       <c r="B256" s="1">
-        <v>19012</v>
+        <v>19002</v>
       </c>
       <c r="C256" s="1"/>
       <c r="D256" s="1">
@@ -7729,7 +7753,7 @@
     <row r="257" ht="15" customHeight="1" spans="1:6">
       <c r="A257" s="1"/>
       <c r="B257" s="1">
-        <v>19013</v>
+        <v>19003</v>
       </c>
       <c r="C257" s="1"/>
       <c r="D257" s="1">
@@ -7745,7 +7769,7 @@
     <row r="258" ht="15" customHeight="1" spans="1:6">
       <c r="A258" s="1"/>
       <c r="B258" s="1">
-        <v>19014</v>
+        <v>19004</v>
       </c>
       <c r="C258" s="1"/>
       <c r="D258" s="1">
@@ -7761,7 +7785,7 @@
     <row r="259" ht="15" customHeight="1" spans="1:6">
       <c r="A259" s="1"/>
       <c r="B259" s="1">
-        <v>19021</v>
+        <v>19011</v>
       </c>
       <c r="C259" s="1"/>
       <c r="D259" s="1">
@@ -7777,7 +7801,7 @@
     <row r="260" ht="15" customHeight="1" spans="1:6">
       <c r="A260" s="1"/>
       <c r="B260" s="1">
-        <v>19022</v>
+        <v>19012</v>
       </c>
       <c r="C260" s="1"/>
       <c r="D260" s="1">
@@ -7793,7 +7817,7 @@
     <row r="261" ht="15" customHeight="1" spans="1:6">
       <c r="A261" s="1"/>
       <c r="B261" s="1">
-        <v>19023</v>
+        <v>19013</v>
       </c>
       <c r="C261" s="1"/>
       <c r="D261" s="1">
@@ -7809,7 +7833,7 @@
     <row r="262" ht="15" customHeight="1" spans="1:6">
       <c r="A262" s="1"/>
       <c r="B262" s="1">
-        <v>19024</v>
+        <v>19014</v>
       </c>
       <c r="C262" s="1"/>
       <c r="D262" s="1">
@@ -7825,82 +7849,74 @@
     <row r="263" ht="15" customHeight="1" spans="1:6">
       <c r="A263" s="1"/>
       <c r="B263" s="1">
-        <v>20101</v>
-      </c>
-      <c r="C263" s="1" t="s">
+        <v>19021</v>
+      </c>
+      <c r="C263" s="1"/>
+      <c r="D263" s="1">
+        <v>1</v>
+      </c>
+      <c r="E263" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="D263" s="1">
-        <v>2</v>
-      </c>
-      <c r="E263" s="1" t="s">
+      <c r="F263" s="1" t="s">
         <v>538</v>
-      </c>
-      <c r="F263" s="1" t="s">
-        <v>539</v>
       </c>
     </row>
     <row r="264" ht="15" customHeight="1" spans="1:6">
       <c r="A264" s="1"/>
       <c r="B264" s="1">
-        <v>20102</v>
-      </c>
-      <c r="C264" s="1" t="s">
-        <v>537</v>
-      </c>
+        <v>19022</v>
+      </c>
+      <c r="C264" s="1"/>
       <c r="D264" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E264" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="F264" s="1" t="s">
         <v>540</v>
-      </c>
-      <c r="F264" s="1" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="265" ht="15" customHeight="1" spans="1:6">
       <c r="A265" s="1"/>
       <c r="B265" s="1">
-        <v>20103</v>
-      </c>
-      <c r="C265" s="1" t="s">
-        <v>537</v>
-      </c>
+        <v>19023</v>
+      </c>
+      <c r="C265" s="1"/>
       <c r="D265" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E265" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="F265" s="1" t="s">
         <v>542</v>
-      </c>
-      <c r="F265" s="1" t="s">
-        <v>543</v>
       </c>
     </row>
     <row r="266" ht="15" customHeight="1" spans="1:6">
       <c r="A266" s="1"/>
       <c r="B266" s="1">
-        <v>20104</v>
-      </c>
-      <c r="C266" s="1" t="s">
-        <v>537</v>
-      </c>
+        <v>19024</v>
+      </c>
+      <c r="C266" s="1"/>
       <c r="D266" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E266" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="F266" s="1" t="s">
         <v>544</v>
-      </c>
-      <c r="F266" s="1" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="267" ht="15" customHeight="1" spans="1:6">
       <c r="A267" s="1"/>
       <c r="B267" s="1">
-        <v>20105</v>
+        <v>20101</v>
       </c>
       <c r="C267" s="1" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="D267" s="1">
         <v>2</v>
@@ -7915,10 +7931,10 @@
     <row r="268" ht="15" customHeight="1" spans="1:6">
       <c r="A268" s="1"/>
       <c r="B268" s="1">
-        <v>20106</v>
+        <v>20102</v>
       </c>
       <c r="C268" s="1" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="D268" s="1">
         <v>2</v>
@@ -7933,10 +7949,10 @@
     <row r="269" ht="15" customHeight="1" spans="1:6">
       <c r="A269" s="1"/>
       <c r="B269" s="1">
-        <v>20107</v>
+        <v>20103</v>
       </c>
       <c r="C269" s="1" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="D269" s="1">
         <v>2</v>
@@ -7951,10 +7967,10 @@
     <row r="270" ht="15" customHeight="1" spans="1:6">
       <c r="A270" s="1"/>
       <c r="B270" s="1">
-        <v>20108</v>
+        <v>20104</v>
       </c>
       <c r="C270" s="1" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="D270" s="1">
         <v>2</v>
@@ -7969,10 +7985,10 @@
     <row r="271" ht="15" customHeight="1" spans="1:6">
       <c r="A271" s="1"/>
       <c r="B271" s="1">
-        <v>20109</v>
+        <v>20105</v>
       </c>
       <c r="C271" s="1" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="D271" s="1">
         <v>2</v>
@@ -7987,10 +8003,10 @@
     <row r="272" ht="15" customHeight="1" spans="1:6">
       <c r="A272" s="1"/>
       <c r="B272" s="1">
-        <v>20110</v>
+        <v>20106</v>
       </c>
       <c r="C272" s="1" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="D272" s="1">
         <v>2</v>
@@ -8005,10 +8021,10 @@
     <row r="273" ht="15" customHeight="1" spans="1:6">
       <c r="A273" s="1"/>
       <c r="B273" s="1">
-        <v>20111</v>
+        <v>20107</v>
       </c>
       <c r="C273" s="1" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="D273" s="1">
         <v>2</v>
@@ -8023,10 +8039,10 @@
     <row r="274" ht="15" customHeight="1" spans="1:6">
       <c r="A274" s="1"/>
       <c r="B274" s="1">
-        <v>20112</v>
+        <v>20108</v>
       </c>
       <c r="C274" s="1" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="D274" s="1">
         <v>2</v>
@@ -8041,10 +8057,10 @@
     <row r="275" ht="15" customHeight="1" spans="1:6">
       <c r="A275" s="1"/>
       <c r="B275" s="1">
-        <v>20113</v>
+        <v>20109</v>
       </c>
       <c r="C275" s="1" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="D275" s="1">
         <v>2</v>
@@ -8059,10 +8075,10 @@
     <row r="276" ht="15" customHeight="1" spans="1:6">
       <c r="A276" s="1"/>
       <c r="B276" s="1">
-        <v>20114</v>
+        <v>20110</v>
       </c>
       <c r="C276" s="1" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="D276" s="1">
         <v>2</v>
@@ -8077,10 +8093,10 @@
     <row r="277" ht="15" customHeight="1" spans="1:6">
       <c r="A277" s="1"/>
       <c r="B277" s="1">
-        <v>20115</v>
+        <v>20111</v>
       </c>
       <c r="C277" s="1" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="D277" s="1">
         <v>2</v>
@@ -8095,10 +8111,10 @@
     <row r="278" ht="15" customHeight="1" spans="1:6">
       <c r="A278" s="1"/>
       <c r="B278" s="1">
-        <v>20116</v>
+        <v>20112</v>
       </c>
       <c r="C278" s="1" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="D278" s="1">
         <v>2</v>
@@ -8113,10 +8129,10 @@
     <row r="279" ht="15" customHeight="1" spans="1:6">
       <c r="A279" s="1"/>
       <c r="B279" s="1">
-        <v>20117</v>
+        <v>20113</v>
       </c>
       <c r="C279" s="1" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="D279" s="1">
         <v>2</v>
@@ -8131,10 +8147,10 @@
     <row r="280" ht="15" customHeight="1" spans="1:6">
       <c r="A280" s="1"/>
       <c r="B280" s="1">
-        <v>20118</v>
+        <v>20114</v>
       </c>
       <c r="C280" s="1" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="D280" s="1">
         <v>2</v>
@@ -8149,10 +8165,10 @@
     <row r="281" ht="15" customHeight="1" spans="1:6">
       <c r="A281" s="1"/>
       <c r="B281" s="1">
-        <v>20119</v>
+        <v>20115</v>
       </c>
       <c r="C281" s="1" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="D281" s="1">
         <v>2</v>
@@ -8167,10 +8183,10 @@
     <row r="282" ht="15" customHeight="1" spans="1:6">
       <c r="A282" s="1"/>
       <c r="B282" s="1">
-        <v>20120</v>
+        <v>20116</v>
       </c>
       <c r="C282" s="1" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="D282" s="1">
         <v>2</v>
@@ -8185,10 +8201,10 @@
     <row r="283" ht="15" customHeight="1" spans="1:6">
       <c r="A283" s="1"/>
       <c r="B283" s="1">
-        <v>20121</v>
+        <v>20117</v>
       </c>
       <c r="C283" s="1" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="D283" s="1">
         <v>2</v>
@@ -8203,10 +8219,10 @@
     <row r="284" ht="15" customHeight="1" spans="1:6">
       <c r="A284" s="1"/>
       <c r="B284" s="1">
-        <v>20122</v>
+        <v>20118</v>
       </c>
       <c r="C284" s="1" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="D284" s="1">
         <v>2</v>
@@ -8221,10 +8237,10 @@
     <row r="285" ht="15" customHeight="1" spans="1:6">
       <c r="A285" s="1"/>
       <c r="B285" s="1">
-        <v>20123</v>
+        <v>20119</v>
       </c>
       <c r="C285" s="1" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="D285" s="1">
         <v>2</v>
@@ -8239,10 +8255,10 @@
     <row r="286" ht="15" customHeight="1" spans="1:6">
       <c r="A286" s="1"/>
       <c r="B286" s="1">
-        <v>20124</v>
+        <v>20120</v>
       </c>
       <c r="C286" s="1" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="D286" s="1">
         <v>2</v>
@@ -8257,10 +8273,10 @@
     <row r="287" ht="15" customHeight="1" spans="1:6">
       <c r="A287" s="1"/>
       <c r="B287" s="1">
-        <v>20125</v>
+        <v>20121</v>
       </c>
       <c r="C287" s="1" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="D287" s="1">
         <v>2</v>
@@ -8275,10 +8291,10 @@
     <row r="288" ht="15" customHeight="1" spans="1:6">
       <c r="A288" s="1"/>
       <c r="B288" s="1">
-        <v>20126</v>
+        <v>20122</v>
       </c>
       <c r="C288" s="1" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="D288" s="1">
         <v>2</v>
@@ -8293,10 +8309,10 @@
     <row r="289" ht="15" customHeight="1" spans="1:6">
       <c r="A289" s="1"/>
       <c r="B289" s="1">
-        <v>20127</v>
+        <v>20123</v>
       </c>
       <c r="C289" s="1" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="D289" s="1">
         <v>2</v>
@@ -8311,13 +8327,13 @@
     <row r="290" ht="15" customHeight="1" spans="1:6">
       <c r="A290" s="1"/>
       <c r="B290" s="1">
-        <v>30101</v>
+        <v>20124</v>
       </c>
       <c r="C290" s="1" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="D290" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E290" s="1" t="s">
         <v>592</v>
@@ -8329,13 +8345,13 @@
     <row r="291" ht="15" customHeight="1" spans="1:6">
       <c r="A291" s="1"/>
       <c r="B291" s="1">
-        <v>30102</v>
+        <v>20125</v>
       </c>
       <c r="C291" s="1" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="D291" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E291" s="1" t="s">
         <v>594</v>
@@ -8347,13 +8363,13 @@
     <row r="292" ht="15" customHeight="1" spans="1:6">
       <c r="A292" s="1"/>
       <c r="B292" s="1">
-        <v>30103</v>
+        <v>20126</v>
       </c>
       <c r="C292" s="1" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="D292" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E292" s="1" t="s">
         <v>596</v>
@@ -8365,13 +8381,13 @@
     <row r="293" ht="15" customHeight="1" spans="1:6">
       <c r="A293" s="1"/>
       <c r="B293" s="1">
-        <v>30104</v>
+        <v>20127</v>
       </c>
       <c r="C293" s="1" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="D293" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E293" s="1" t="s">
         <v>598</v>
@@ -8383,10 +8399,10 @@
     <row r="294" ht="15" customHeight="1" spans="1:6">
       <c r="A294" s="1"/>
       <c r="B294" s="1">
-        <v>30105</v>
+        <v>30101</v>
       </c>
       <c r="C294" s="1" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="D294" s="1">
         <v>3</v>
@@ -8401,10 +8417,10 @@
     <row r="295" ht="15" customHeight="1" spans="1:6">
       <c r="A295" s="1"/>
       <c r="B295" s="1">
-        <v>30106</v>
+        <v>30102</v>
       </c>
       <c r="C295" s="1" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="D295" s="1">
         <v>3</v>
@@ -8419,10 +8435,10 @@
     <row r="296" ht="15" customHeight="1" spans="1:6">
       <c r="A296" s="1"/>
       <c r="B296" s="1">
-        <v>30107</v>
+        <v>30103</v>
       </c>
       <c r="C296" s="1" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="D296" s="1">
         <v>3</v>
@@ -8437,10 +8453,10 @@
     <row r="297" ht="15" customHeight="1" spans="1:6">
       <c r="A297" s="1"/>
       <c r="B297" s="1">
-        <v>30108</v>
+        <v>30104</v>
       </c>
       <c r="C297" s="1" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="D297" s="1">
         <v>3</v>
@@ -8455,10 +8471,10 @@
     <row r="298" ht="15" customHeight="1" spans="1:6">
       <c r="A298" s="1"/>
       <c r="B298" s="1">
-        <v>30109</v>
+        <v>30105</v>
       </c>
       <c r="C298" s="1" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="D298" s="1">
         <v>3</v>
@@ -8473,10 +8489,10 @@
     <row r="299" ht="15" customHeight="1" spans="1:6">
       <c r="A299" s="1"/>
       <c r="B299" s="1">
-        <v>30110</v>
+        <v>30106</v>
       </c>
       <c r="C299" s="1" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="D299" s="1">
         <v>3</v>
@@ -8491,10 +8507,10 @@
     <row r="300" ht="15" customHeight="1" spans="1:6">
       <c r="A300" s="1"/>
       <c r="B300" s="1">
-        <v>30111</v>
+        <v>30107</v>
       </c>
       <c r="C300" s="1" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="D300" s="1">
         <v>3</v>
@@ -8509,10 +8525,10 @@
     <row r="301" ht="15" customHeight="1" spans="1:6">
       <c r="A301" s="1"/>
       <c r="B301" s="1">
-        <v>30112</v>
+        <v>30108</v>
       </c>
       <c r="C301" s="1" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="D301" s="1">
         <v>3</v>
@@ -8527,10 +8543,10 @@
     <row r="302" ht="15" customHeight="1" spans="1:6">
       <c r="A302" s="1"/>
       <c r="B302" s="1">
-        <v>30113</v>
+        <v>30109</v>
       </c>
       <c r="C302" s="1" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="D302" s="1">
         <v>3</v>
@@ -8545,10 +8561,10 @@
     <row r="303" ht="15" customHeight="1" spans="1:6">
       <c r="A303" s="1"/>
       <c r="B303" s="1">
-        <v>30114</v>
+        <v>30110</v>
       </c>
       <c r="C303" s="1" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="D303" s="1">
         <v>3</v>
@@ -8563,10 +8579,10 @@
     <row r="304" ht="15" customHeight="1" spans="1:6">
       <c r="A304" s="1"/>
       <c r="B304" s="1">
-        <v>30115</v>
+        <v>30111</v>
       </c>
       <c r="C304" s="1" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="D304" s="1">
         <v>3</v>
@@ -8581,10 +8597,10 @@
     <row r="305" ht="15" customHeight="1" spans="1:6">
       <c r="A305" s="1"/>
       <c r="B305" s="1">
-        <v>30116</v>
+        <v>30112</v>
       </c>
       <c r="C305" s="1" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="D305" s="1">
         <v>3</v>
@@ -8599,10 +8615,10 @@
     <row r="306" ht="15" customHeight="1" spans="1:6">
       <c r="A306" s="1"/>
       <c r="B306" s="1">
-        <v>30117</v>
+        <v>30113</v>
       </c>
       <c r="C306" s="1" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="D306" s="1">
         <v>3</v>
@@ -8617,10 +8633,10 @@
     <row r="307" ht="15" customHeight="1" spans="1:6">
       <c r="A307" s="1"/>
       <c r="B307" s="1">
-        <v>30118</v>
+        <v>30114</v>
       </c>
       <c r="C307" s="1" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="D307" s="1">
         <v>3</v>
@@ -8635,10 +8651,10 @@
     <row r="308" ht="15" customHeight="1" spans="1:6">
       <c r="A308" s="1"/>
       <c r="B308" s="1">
-        <v>30119</v>
+        <v>30115</v>
       </c>
       <c r="C308" s="1" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="D308" s="1">
         <v>3</v>
@@ -8653,10 +8669,10 @@
     <row r="309" ht="15" customHeight="1" spans="1:6">
       <c r="A309" s="1"/>
       <c r="B309" s="1">
-        <v>30120</v>
+        <v>30116</v>
       </c>
       <c r="C309" s="1" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="D309" s="1">
         <v>3</v>
@@ -8671,10 +8687,10 @@
     <row r="310" ht="15" customHeight="1" spans="1:6">
       <c r="A310" s="1"/>
       <c r="B310" s="1">
-        <v>30121</v>
+        <v>30117</v>
       </c>
       <c r="C310" s="1" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="D310" s="1">
         <v>3</v>
@@ -8689,10 +8705,10 @@
     <row r="311" ht="15" customHeight="1" spans="1:6">
       <c r="A311" s="1"/>
       <c r="B311" s="1">
-        <v>30122</v>
+        <v>30118</v>
       </c>
       <c r="C311" s="1" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="D311" s="1">
         <v>3</v>
@@ -8707,10 +8723,10 @@
     <row r="312" ht="15" customHeight="1" spans="1:6">
       <c r="A312" s="1"/>
       <c r="B312" s="1">
-        <v>30123</v>
+        <v>30119</v>
       </c>
       <c r="C312" s="1" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="D312" s="1">
         <v>3</v>
@@ -8725,10 +8741,10 @@
     <row r="313" ht="15" customHeight="1" spans="1:6">
       <c r="A313" s="1"/>
       <c r="B313" s="1">
-        <v>30124</v>
+        <v>30120</v>
       </c>
       <c r="C313" s="1" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="D313" s="1">
         <v>3</v>
@@ -8743,10 +8759,10 @@
     <row r="314" ht="15" customHeight="1" spans="1:6">
       <c r="A314" s="1"/>
       <c r="B314" s="1">
-        <v>30125</v>
+        <v>30121</v>
       </c>
       <c r="C314" s="1" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="D314" s="1">
         <v>3</v>
@@ -8761,10 +8777,10 @@
     <row r="315" ht="15" customHeight="1" spans="1:6">
       <c r="A315" s="1"/>
       <c r="B315" s="1">
-        <v>30201</v>
+        <v>30122</v>
       </c>
       <c r="C315" s="1" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="D315" s="1">
         <v>3</v>
@@ -8779,10 +8795,10 @@
     <row r="316" ht="15" customHeight="1" spans="1:6">
       <c r="A316" s="1"/>
       <c r="B316" s="1">
-        <v>30202</v>
+        <v>30123</v>
       </c>
       <c r="C316" s="1" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="D316" s="1">
         <v>3</v>
@@ -8797,10 +8813,10 @@
     <row r="317" ht="15" customHeight="1" spans="1:6">
       <c r="A317" s="1"/>
       <c r="B317" s="1">
-        <v>30203</v>
+        <v>30124</v>
       </c>
       <c r="C317" s="1" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="D317" s="1">
         <v>3</v>
@@ -8815,10 +8831,10 @@
     <row r="318" ht="15" customHeight="1" spans="1:6">
       <c r="A318" s="1"/>
       <c r="B318" s="1">
-        <v>30204</v>
+        <v>30125</v>
       </c>
       <c r="C318" s="1" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="D318" s="1">
         <v>3</v>
@@ -8833,10 +8849,10 @@
     <row r="319" ht="15" customHeight="1" spans="1:6">
       <c r="A319" s="1"/>
       <c r="B319" s="1">
-        <v>30205</v>
+        <v>30201</v>
       </c>
       <c r="C319" s="1" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="D319" s="1">
         <v>3</v>
@@ -8851,10 +8867,10 @@
     <row r="320" ht="15" customHeight="1" spans="1:6">
       <c r="A320" s="1"/>
       <c r="B320" s="1">
-        <v>30206</v>
+        <v>30202</v>
       </c>
       <c r="C320" s="1" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="D320" s="1">
         <v>3</v>
@@ -8869,10 +8885,10 @@
     <row r="321" ht="15" customHeight="1" spans="1:6">
       <c r="A321" s="1"/>
       <c r="B321" s="1">
-        <v>30301</v>
+        <v>30203</v>
       </c>
       <c r="C321" s="1" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="D321" s="1">
         <v>3</v>
@@ -8887,10 +8903,10 @@
     <row r="322" ht="15" customHeight="1" spans="1:6">
       <c r="A322" s="1"/>
       <c r="B322" s="1">
-        <v>30302</v>
+        <v>30204</v>
       </c>
       <c r="C322" s="1" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="D322" s="1">
         <v>3</v>
@@ -8905,10 +8921,10 @@
     <row r="323" ht="15" customHeight="1" spans="1:6">
       <c r="A323" s="1"/>
       <c r="B323" s="1">
-        <v>30303</v>
+        <v>30205</v>
       </c>
       <c r="C323" s="1" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="D323" s="1">
         <v>3</v>
@@ -8923,10 +8939,10 @@
     <row r="324" ht="15" customHeight="1" spans="1:6">
       <c r="A324" s="1"/>
       <c r="B324" s="1">
-        <v>30304</v>
+        <v>30206</v>
       </c>
       <c r="C324" s="1" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="D324" s="1">
         <v>3</v>
@@ -8941,10 +8957,10 @@
     <row r="325" ht="15" customHeight="1" spans="1:6">
       <c r="A325" s="1"/>
       <c r="B325" s="1">
-        <v>30305</v>
+        <v>30301</v>
       </c>
       <c r="C325" s="1" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="D325" s="1">
         <v>3</v>
@@ -8959,10 +8975,10 @@
     <row r="326" ht="15" customHeight="1" spans="1:6">
       <c r="A326" s="1"/>
       <c r="B326" s="1">
-        <v>30306</v>
+        <v>30302</v>
       </c>
       <c r="C326" s="1" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="D326" s="1">
         <v>3</v>
@@ -8977,10 +8993,10 @@
     <row r="327" ht="15" customHeight="1" spans="1:6">
       <c r="A327" s="1"/>
       <c r="B327" s="1">
-        <v>30307</v>
+        <v>30303</v>
       </c>
       <c r="C327" s="1" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="D327" s="1">
         <v>3</v>
@@ -8995,10 +9011,10 @@
     <row r="328" ht="15" customHeight="1" spans="1:6">
       <c r="A328" s="1"/>
       <c r="B328" s="1">
-        <v>30308</v>
+        <v>30304</v>
       </c>
       <c r="C328" s="1" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="D328" s="1">
         <v>3</v>
@@ -9013,82 +9029,82 @@
     <row r="329" ht="15" customHeight="1" spans="1:6">
       <c r="A329" s="1"/>
       <c r="B329" s="1">
-        <v>60001</v>
+        <v>30305</v>
       </c>
       <c r="C329" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="D329" s="1">
+        <v>3</v>
+      </c>
+      <c r="E329" s="1" t="s">
         <v>670</v>
       </c>
-      <c r="D329" s="1">
-        <v>7</v>
-      </c>
-      <c r="E329" s="1" t="s">
+      <c r="F329" s="1" t="s">
         <v>671</v>
-      </c>
-      <c r="F329" s="1" t="s">
-        <v>672</v>
       </c>
     </row>
     <row r="330" ht="15" customHeight="1" spans="1:6">
       <c r="A330" s="1"/>
       <c r="B330" s="1">
-        <v>60002</v>
+        <v>30306</v>
       </c>
       <c r="C330" s="1" t="s">
-        <v>670</v>
+        <v>545</v>
       </c>
       <c r="D330" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E330" s="1" t="s">
+        <v>672</v>
+      </c>
+      <c r="F330" s="1" t="s">
         <v>673</v>
-      </c>
-      <c r="F330" s="1" t="s">
-        <v>674</v>
       </c>
     </row>
     <row r="331" ht="15" customHeight="1" spans="1:6">
       <c r="A331" s="1"/>
       <c r="B331" s="1">
-        <v>60003</v>
+        <v>30307</v>
       </c>
       <c r="C331" s="1" t="s">
-        <v>670</v>
+        <v>545</v>
       </c>
       <c r="D331" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E331" s="1" t="s">
+        <v>674</v>
+      </c>
+      <c r="F331" s="1" t="s">
         <v>675</v>
-      </c>
-      <c r="F331" s="1" t="s">
-        <v>676</v>
       </c>
     </row>
     <row r="332" ht="15" customHeight="1" spans="1:6">
       <c r="A332" s="1"/>
       <c r="B332" s="1">
-        <v>60004</v>
+        <v>30308</v>
       </c>
       <c r="C332" s="1" t="s">
-        <v>670</v>
+        <v>545</v>
       </c>
       <c r="D332" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E332" s="1" t="s">
+        <v>676</v>
+      </c>
+      <c r="F332" s="1" t="s">
         <v>677</v>
-      </c>
-      <c r="F332" s="1" t="s">
-        <v>678</v>
       </c>
     </row>
     <row r="333" ht="15" customHeight="1" spans="1:6">
       <c r="A333" s="1"/>
       <c r="B333" s="1">
-        <v>60005</v>
+        <v>60001</v>
       </c>
       <c r="C333" s="1" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="D333" s="1">
         <v>7</v>
@@ -9103,10 +9119,10 @@
     <row r="334" ht="15" customHeight="1" spans="1:6">
       <c r="A334" s="1"/>
       <c r="B334" s="1">
-        <v>60006</v>
+        <v>60002</v>
       </c>
       <c r="C334" s="1" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="D334" s="1">
         <v>7</v>
@@ -9121,10 +9137,10 @@
     <row r="335" ht="15" customHeight="1" spans="1:6">
       <c r="A335" s="1"/>
       <c r="B335" s="1">
-        <v>60007</v>
+        <v>60003</v>
       </c>
       <c r="C335" s="1" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="D335" s="1">
         <v>7</v>
@@ -9139,10 +9155,10 @@
     <row r="336" ht="15" customHeight="1" spans="1:6">
       <c r="A336" s="1"/>
       <c r="B336" s="1">
-        <v>60008</v>
+        <v>60004</v>
       </c>
       <c r="C336" s="1" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="D336" s="1">
         <v>7</v>
@@ -9157,10 +9173,10 @@
     <row r="337" ht="15" customHeight="1" spans="1:6">
       <c r="A337" s="1"/>
       <c r="B337" s="1">
-        <v>60009</v>
+        <v>60005</v>
       </c>
       <c r="C337" s="1" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="D337" s="1">
         <v>7</v>
@@ -9175,10 +9191,10 @@
     <row r="338" ht="15" customHeight="1" spans="1:6">
       <c r="A338" s="1"/>
       <c r="B338" s="1">
-        <v>60010</v>
+        <v>60006</v>
       </c>
       <c r="C338" s="1" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="D338" s="1">
         <v>7</v>
@@ -9193,10 +9209,10 @@
     <row r="339" ht="15" customHeight="1" spans="1:6">
       <c r="A339" s="1"/>
       <c r="B339" s="1">
-        <v>60011</v>
+        <v>60007</v>
       </c>
       <c r="C339" s="1" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="D339" s="1">
         <v>7</v>
@@ -9211,10 +9227,10 @@
     <row r="340" ht="15" customHeight="1" spans="1:6">
       <c r="A340" s="1"/>
       <c r="B340" s="1">
-        <v>60012</v>
+        <v>60008</v>
       </c>
       <c r="C340" s="1" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="D340" s="1">
         <v>7</v>
@@ -9229,10 +9245,10 @@
     <row r="341" ht="15" customHeight="1" spans="1:6">
       <c r="A341" s="1"/>
       <c r="B341" s="1">
-        <v>60013</v>
+        <v>60009</v>
       </c>
       <c r="C341" s="1" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="D341" s="1">
         <v>7</v>
@@ -9247,10 +9263,10 @@
     <row r="342" ht="15" customHeight="1" spans="1:6">
       <c r="A342" s="1"/>
       <c r="B342" s="1">
-        <v>60014</v>
+        <v>60010</v>
       </c>
       <c r="C342" s="1" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="D342" s="1">
         <v>7</v>
@@ -9265,10 +9281,10 @@
     <row r="343" ht="15" customHeight="1" spans="1:6">
       <c r="A343" s="1"/>
       <c r="B343" s="1">
-        <v>60015</v>
+        <v>60011</v>
       </c>
       <c r="C343" s="1" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="D343" s="1">
         <v>7</v>
@@ -9283,10 +9299,10 @@
     <row r="344" ht="15" customHeight="1" spans="1:6">
       <c r="A344" s="1"/>
       <c r="B344" s="1">
-        <v>60016</v>
+        <v>60012</v>
       </c>
       <c r="C344" s="1" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="D344" s="1">
         <v>7</v>
@@ -9301,10 +9317,10 @@
     <row r="345" ht="15" customHeight="1" spans="1:6">
       <c r="A345" s="1"/>
       <c r="B345" s="1">
-        <v>60017</v>
+        <v>60013</v>
       </c>
       <c r="C345" s="1" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="D345" s="1">
         <v>7</v>
@@ -9319,10 +9335,10 @@
     <row r="346" ht="15" customHeight="1" spans="1:6">
       <c r="A346" s="1"/>
       <c r="B346" s="1">
-        <v>60018</v>
+        <v>60014</v>
       </c>
       <c r="C346" s="1" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="D346" s="1">
         <v>7</v>
@@ -9337,10 +9353,10 @@
     <row r="347" ht="15" customHeight="1" spans="1:6">
       <c r="A347" s="1"/>
       <c r="B347" s="1">
-        <v>60019</v>
+        <v>60015</v>
       </c>
       <c r="C347" s="1" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="D347" s="1">
         <v>7</v>
@@ -9355,10 +9371,10 @@
     <row r="348" ht="15" customHeight="1" spans="1:6">
       <c r="A348" s="1"/>
       <c r="B348" s="1">
-        <v>60020</v>
+        <v>60016</v>
       </c>
       <c r="C348" s="1" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="D348" s="1">
         <v>7</v>
@@ -9373,10 +9389,10 @@
     <row r="349" ht="15" customHeight="1" spans="1:6">
       <c r="A349" s="1"/>
       <c r="B349" s="1">
-        <v>60021</v>
+        <v>60017</v>
       </c>
       <c r="C349" s="1" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="D349" s="1">
         <v>7</v>
@@ -9391,10 +9407,10 @@
     <row r="350" ht="15" customHeight="1" spans="1:6">
       <c r="A350" s="1"/>
       <c r="B350" s="1">
-        <v>60022</v>
+        <v>60018</v>
       </c>
       <c r="C350" s="1" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="D350" s="1">
         <v>7</v>
@@ -9409,10 +9425,10 @@
     <row r="351" ht="15" customHeight="1" spans="1:6">
       <c r="A351" s="1"/>
       <c r="B351" s="1">
-        <v>60023</v>
+        <v>60019</v>
       </c>
       <c r="C351" s="1" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="D351" s="1">
         <v>7</v>
@@ -9427,10 +9443,10 @@
     <row r="352" ht="15" customHeight="1" spans="1:6">
       <c r="A352" s="1"/>
       <c r="B352" s="1">
-        <v>60024</v>
+        <v>60020</v>
       </c>
       <c r="C352" s="1" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="D352" s="1">
         <v>7</v>
@@ -9445,10 +9461,10 @@
     <row r="353" ht="15" customHeight="1" spans="1:6">
       <c r="A353" s="1"/>
       <c r="B353" s="1">
-        <v>60025</v>
+        <v>60021</v>
       </c>
       <c r="C353" s="1" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="D353" s="1">
         <v>7</v>
@@ -9463,10 +9479,10 @@
     <row r="354" ht="15" customHeight="1" spans="1:6">
       <c r="A354" s="1"/>
       <c r="B354" s="1">
-        <v>60026</v>
+        <v>60022</v>
       </c>
       <c r="C354" s="1" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="D354" s="1">
         <v>7</v>
@@ -9481,10 +9497,10 @@
     <row r="355" ht="15" customHeight="1" spans="1:6">
       <c r="A355" s="1"/>
       <c r="B355" s="1">
-        <v>60027</v>
+        <v>60023</v>
       </c>
       <c r="C355" s="1" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="D355" s="1">
         <v>7</v>
@@ -9499,10 +9515,10 @@
     <row r="356" ht="15" customHeight="1" spans="1:6">
       <c r="A356" s="1"/>
       <c r="B356" s="1">
-        <v>60028</v>
+        <v>60024</v>
       </c>
       <c r="C356" s="1" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="D356" s="1">
         <v>7</v>
@@ -9517,10 +9533,10 @@
     <row r="357" ht="15" customHeight="1" spans="1:6">
       <c r="A357" s="1"/>
       <c r="B357" s="1">
-        <v>60029</v>
+        <v>60025</v>
       </c>
       <c r="C357" s="1" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="D357" s="1">
         <v>7</v>
@@ -9535,10 +9551,10 @@
     <row r="358" ht="15" customHeight="1" spans="1:6">
       <c r="A358" s="1"/>
       <c r="B358" s="1">
-        <v>60030</v>
+        <v>60026</v>
       </c>
       <c r="C358" s="1" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="D358" s="1">
         <v>7</v>
@@ -9553,10 +9569,10 @@
     <row r="359" ht="15" customHeight="1" spans="1:6">
       <c r="A359" s="1"/>
       <c r="B359" s="1">
-        <v>60031</v>
+        <v>60027</v>
       </c>
       <c r="C359" s="1" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="D359" s="1">
         <v>7</v>
@@ -9571,10 +9587,10 @@
     <row r="360" ht="15" customHeight="1" spans="1:6">
       <c r="A360" s="1"/>
       <c r="B360" s="1">
-        <v>60032</v>
+        <v>60028</v>
       </c>
       <c r="C360" s="1" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="D360" s="1">
         <v>7</v>
@@ -9589,10 +9605,10 @@
     <row r="361" ht="15" customHeight="1" spans="1:6">
       <c r="A361" s="1"/>
       <c r="B361" s="1">
-        <v>60033</v>
+        <v>60029</v>
       </c>
       <c r="C361" s="1" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="D361" s="1">
         <v>7</v>
@@ -9607,10 +9623,10 @@
     <row r="362" ht="15" customHeight="1" spans="1:6">
       <c r="A362" s="1"/>
       <c r="B362" s="1">
-        <v>60034</v>
+        <v>60030</v>
       </c>
       <c r="C362" s="1" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="D362" s="1">
         <v>7</v>
@@ -9625,10 +9641,10 @@
     <row r="363" ht="15" customHeight="1" spans="1:6">
       <c r="A363" s="1"/>
       <c r="B363" s="1">
-        <v>60035</v>
+        <v>60031</v>
       </c>
       <c r="C363" s="1" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="D363" s="1">
         <v>7</v>
@@ -9643,10 +9659,10 @@
     <row r="364" ht="15" customHeight="1" spans="1:6">
       <c r="A364" s="1"/>
       <c r="B364" s="1">
-        <v>60036</v>
+        <v>60032</v>
       </c>
       <c r="C364" s="1" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="D364" s="1">
         <v>7</v>
@@ -9661,10 +9677,10 @@
     <row r="365" ht="15" customHeight="1" spans="1:6">
       <c r="A365" s="1"/>
       <c r="B365" s="1">
-        <v>60037</v>
+        <v>60033</v>
       </c>
       <c r="C365" s="1" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="D365" s="1">
         <v>7</v>
@@ -9679,10 +9695,10 @@
     <row r="366" ht="15" customHeight="1" spans="1:6">
       <c r="A366" s="1"/>
       <c r="B366" s="1">
-        <v>60038</v>
+        <v>60034</v>
       </c>
       <c r="C366" s="1" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="D366" s="1">
         <v>7</v>
@@ -9697,10 +9713,10 @@
     <row r="367" ht="15" customHeight="1" spans="1:6">
       <c r="A367" s="1"/>
       <c r="B367" s="1">
-        <v>60039</v>
+        <v>60035</v>
       </c>
       <c r="C367" s="1" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="D367" s="1">
         <v>7</v>
@@ -9715,10 +9731,10 @@
     <row r="368" ht="15" customHeight="1" spans="1:6">
       <c r="A368" s="1"/>
       <c r="B368" s="1">
-        <v>60040</v>
+        <v>60036</v>
       </c>
       <c r="C368" s="1" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="D368" s="1">
         <v>7</v>
@@ -9733,10 +9749,10 @@
     <row r="369" ht="15" customHeight="1" spans="1:6">
       <c r="A369" s="1"/>
       <c r="B369" s="1">
-        <v>60041</v>
+        <v>60037</v>
       </c>
       <c r="C369" s="1" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="D369" s="1">
         <v>7</v>
@@ -9751,10 +9767,10 @@
     <row r="370" ht="15" customHeight="1" spans="1:6">
       <c r="A370" s="1"/>
       <c r="B370" s="1">
-        <v>60042</v>
+        <v>60038</v>
       </c>
       <c r="C370" s="1" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="D370" s="1">
         <v>7</v>
@@ -9769,10 +9785,10 @@
     <row r="371" ht="15" customHeight="1" spans="1:6">
       <c r="A371" s="1"/>
       <c r="B371" s="1">
-        <v>60043</v>
+        <v>60039</v>
       </c>
       <c r="C371" s="1" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="D371" s="1">
         <v>7</v>
@@ -9787,10 +9803,10 @@
     <row r="372" ht="15" customHeight="1" spans="1:6">
       <c r="A372" s="1"/>
       <c r="B372" s="1">
-        <v>60044</v>
+        <v>60040</v>
       </c>
       <c r="C372" s="1" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="D372" s="1">
         <v>7</v>
@@ -9805,10 +9821,10 @@
     <row r="373" ht="15" customHeight="1" spans="1:6">
       <c r="A373" s="1"/>
       <c r="B373" s="1">
-        <v>60045</v>
+        <v>60041</v>
       </c>
       <c r="C373" s="1" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="D373" s="1">
         <v>7</v>
@@ -9823,10 +9839,10 @@
     <row r="374" ht="15" customHeight="1" spans="1:6">
       <c r="A374" s="1"/>
       <c r="B374" s="1">
-        <v>60046</v>
+        <v>60042</v>
       </c>
       <c r="C374" s="1" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="D374" s="1">
         <v>7</v>
@@ -9841,10 +9857,10 @@
     <row r="375" ht="15" customHeight="1" spans="1:6">
       <c r="A375" s="1"/>
       <c r="B375" s="1">
-        <v>60047</v>
+        <v>60043</v>
       </c>
       <c r="C375" s="1" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="D375" s="1">
         <v>7</v>
@@ -9859,10 +9875,10 @@
     <row r="376" ht="15" customHeight="1" spans="1:6">
       <c r="A376" s="1"/>
       <c r="B376" s="1">
-        <v>60048</v>
+        <v>60044</v>
       </c>
       <c r="C376" s="1" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="D376" s="1">
         <v>7</v>
@@ -9877,10 +9893,10 @@
     <row r="377" ht="15" customHeight="1" spans="1:6">
       <c r="A377" s="1"/>
       <c r="B377" s="1">
-        <v>60049</v>
+        <v>60045</v>
       </c>
       <c r="C377" s="1" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="D377" s="1">
         <v>7</v>
@@ -9895,10 +9911,10 @@
     <row r="378" ht="15" customHeight="1" spans="1:6">
       <c r="A378" s="1"/>
       <c r="B378" s="1">
-        <v>60050</v>
+        <v>60046</v>
       </c>
       <c r="C378" s="1" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="D378" s="1">
         <v>7</v>
@@ -9913,10 +9929,10 @@
     <row r="379" ht="15" customHeight="1" spans="1:6">
       <c r="A379" s="1"/>
       <c r="B379" s="1">
-        <v>60051</v>
+        <v>60047</v>
       </c>
       <c r="C379" s="1" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="D379" s="1">
         <v>7</v>
@@ -9931,10 +9947,10 @@
     <row r="380" ht="15" customHeight="1" spans="1:6">
       <c r="A380" s="1"/>
       <c r="B380" s="1">
-        <v>60052</v>
+        <v>60048</v>
       </c>
       <c r="C380" s="1" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="D380" s="1">
         <v>7</v>
@@ -9949,10 +9965,10 @@
     <row r="381" ht="15" customHeight="1" spans="1:6">
       <c r="A381" s="1"/>
       <c r="B381" s="1">
-        <v>60053</v>
+        <v>60049</v>
       </c>
       <c r="C381" s="1" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="D381" s="1">
         <v>7</v>
@@ -9967,10 +9983,10 @@
     <row r="382" ht="15" customHeight="1" spans="1:6">
       <c r="A382" s="1"/>
       <c r="B382" s="1">
-        <v>60054</v>
+        <v>60050</v>
       </c>
       <c r="C382" s="1" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="D382" s="1">
         <v>7</v>
@@ -9985,10 +10001,10 @@
     <row r="383" ht="15" customHeight="1" spans="1:6">
       <c r="A383" s="1"/>
       <c r="B383" s="1">
-        <v>60055</v>
+        <v>60051</v>
       </c>
       <c r="C383" s="1" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="D383" s="1">
         <v>7</v>
@@ -10003,10 +10019,10 @@
     <row r="384" ht="15" customHeight="1" spans="1:6">
       <c r="A384" s="1"/>
       <c r="B384" s="1">
-        <v>60056</v>
+        <v>60052</v>
       </c>
       <c r="C384" s="1" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="D384" s="1">
         <v>7</v>
@@ -10021,10 +10037,10 @@
     <row r="385" ht="15" customHeight="1" spans="1:6">
       <c r="A385" s="1"/>
       <c r="B385" s="1">
-        <v>60057</v>
+        <v>60053</v>
       </c>
       <c r="C385" s="1" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="D385" s="1">
         <v>7</v>
@@ -10039,10 +10055,10 @@
     <row r="386" ht="15" customHeight="1" spans="1:6">
       <c r="A386" s="1"/>
       <c r="B386" s="1">
-        <v>60058</v>
+        <v>60054</v>
       </c>
       <c r="C386" s="1" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="D386" s="1">
         <v>7</v>
@@ -10057,10 +10073,10 @@
     <row r="387" ht="15" customHeight="1" spans="1:6">
       <c r="A387" s="1"/>
       <c r="B387" s="1">
-        <v>60059</v>
+        <v>60055</v>
       </c>
       <c r="C387" s="1" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="D387" s="1">
         <v>7</v>
@@ -10075,10 +10091,10 @@
     <row r="388" ht="15" customHeight="1" spans="1:6">
       <c r="A388" s="1"/>
       <c r="B388" s="1">
-        <v>60060</v>
+        <v>60056</v>
       </c>
       <c r="C388" s="1" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="D388" s="1">
         <v>7</v>
@@ -10093,10 +10109,10 @@
     <row r="389" ht="15" customHeight="1" spans="1:6">
       <c r="A389" s="1"/>
       <c r="B389" s="1">
-        <v>60061</v>
+        <v>60057</v>
       </c>
       <c r="C389" s="1" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="D389" s="1">
         <v>7</v>
@@ -10111,10 +10127,10 @@
     <row r="390" ht="15" customHeight="1" spans="1:6">
       <c r="A390" s="1"/>
       <c r="B390" s="1">
-        <v>60062</v>
+        <v>60058</v>
       </c>
       <c r="C390" s="1" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="D390" s="1">
         <v>7</v>
@@ -10129,10 +10145,10 @@
     <row r="391" ht="15" customHeight="1" spans="1:6">
       <c r="A391" s="1"/>
       <c r="B391" s="1">
-        <v>60063</v>
+        <v>60059</v>
       </c>
       <c r="C391" s="1" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="D391" s="1">
         <v>7</v>
@@ -10147,10 +10163,10 @@
     <row r="392" ht="15" customHeight="1" spans="1:6">
       <c r="A392" s="1"/>
       <c r="B392" s="1">
-        <v>60064</v>
+        <v>60060</v>
       </c>
       <c r="C392" s="1" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="D392" s="1">
         <v>7</v>
@@ -10165,10 +10181,10 @@
     <row r="393" ht="15" customHeight="1" spans="1:6">
       <c r="A393" s="1"/>
       <c r="B393" s="1">
-        <v>60065</v>
+        <v>60061</v>
       </c>
       <c r="C393" s="1" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="D393" s="1">
         <v>7</v>
@@ -10183,10 +10199,10 @@
     <row r="394" ht="15" customHeight="1" spans="1:6">
       <c r="A394" s="1"/>
       <c r="B394" s="1">
-        <v>60066</v>
+        <v>60062</v>
       </c>
       <c r="C394" s="1" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="D394" s="1">
         <v>7</v>
@@ -10201,10 +10217,10 @@
     <row r="395" ht="15" customHeight="1" spans="1:6">
       <c r="A395" s="1"/>
       <c r="B395" s="1">
-        <v>60067</v>
+        <v>60063</v>
       </c>
       <c r="C395" s="1" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="D395" s="1">
         <v>7</v>
@@ -10219,10 +10235,10 @@
     <row r="396" ht="15" customHeight="1" spans="1:6">
       <c r="A396" s="1"/>
       <c r="B396" s="1">
-        <v>60068</v>
+        <v>60064</v>
       </c>
       <c r="C396" s="1" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="D396" s="1">
         <v>7</v>
@@ -10237,10 +10253,10 @@
     <row r="397" ht="15" customHeight="1" spans="1:6">
       <c r="A397" s="1"/>
       <c r="B397" s="1">
-        <v>60069</v>
+        <v>60065</v>
       </c>
       <c r="C397" s="1" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="D397" s="1">
         <v>7</v>
@@ -10255,10 +10271,10 @@
     <row r="398" ht="15" customHeight="1" spans="1:6">
       <c r="A398" s="1"/>
       <c r="B398" s="1">
-        <v>60070</v>
+        <v>60066</v>
       </c>
       <c r="C398" s="1" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="D398" s="1">
         <v>7</v>
@@ -10273,10 +10289,10 @@
     <row r="399" ht="15" customHeight="1" spans="1:6">
       <c r="A399" s="1"/>
       <c r="B399" s="1">
-        <v>60071</v>
+        <v>60067</v>
       </c>
       <c r="C399" s="1" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="D399" s="1">
         <v>7</v>
@@ -10291,10 +10307,10 @@
     <row r="400" ht="15" customHeight="1" spans="1:6">
       <c r="A400" s="1"/>
       <c r="B400" s="1">
-        <v>60072</v>
+        <v>60068</v>
       </c>
       <c r="C400" s="1" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="D400" s="1">
         <v>7</v>
@@ -10309,10 +10325,10 @@
     <row r="401" ht="15" customHeight="1" spans="1:6">
       <c r="A401" s="1"/>
       <c r="B401" s="1">
-        <v>60073</v>
+        <v>60069</v>
       </c>
       <c r="C401" s="1" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="D401" s="1">
         <v>7</v>
@@ -10327,10 +10343,10 @@
     <row r="402" ht="15" customHeight="1" spans="1:6">
       <c r="A402" s="1"/>
       <c r="B402" s="1">
-        <v>60074</v>
+        <v>60070</v>
       </c>
       <c r="C402" s="1" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="D402" s="1">
         <v>7</v>
@@ -10345,10 +10361,10 @@
     <row r="403" ht="15" customHeight="1" spans="1:6">
       <c r="A403" s="1"/>
       <c r="B403" s="1">
-        <v>60075</v>
+        <v>60071</v>
       </c>
       <c r="C403" s="1" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="D403" s="1">
         <v>7</v>
@@ -10363,10 +10379,10 @@
     <row r="404" ht="15" customHeight="1" spans="1:6">
       <c r="A404" s="1"/>
       <c r="B404" s="1">
-        <v>60076</v>
+        <v>60072</v>
       </c>
       <c r="C404" s="1" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="D404" s="1">
         <v>7</v>
@@ -10381,10 +10397,10 @@
     <row r="405" ht="15" customHeight="1" spans="1:6">
       <c r="A405" s="1"/>
       <c r="B405" s="1">
-        <v>60077</v>
+        <v>60073</v>
       </c>
       <c r="C405" s="1" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="D405" s="1">
         <v>7</v>
@@ -10399,10 +10415,10 @@
     <row r="406" ht="15" customHeight="1" spans="1:6">
       <c r="A406" s="1"/>
       <c r="B406" s="1">
-        <v>60078</v>
+        <v>60074</v>
       </c>
       <c r="C406" s="1" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="D406" s="1">
         <v>7</v>
@@ -10417,10 +10433,10 @@
     <row r="407" ht="15" customHeight="1" spans="1:6">
       <c r="A407" s="1"/>
       <c r="B407" s="1">
-        <v>60079</v>
+        <v>60075</v>
       </c>
       <c r="C407" s="1" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="D407" s="1">
         <v>7</v>
@@ -10435,10 +10451,10 @@
     <row r="408" ht="15" customHeight="1" spans="1:6">
       <c r="A408" s="1"/>
       <c r="B408" s="1">
-        <v>60080</v>
+        <v>60076</v>
       </c>
       <c r="C408" s="1" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="D408" s="1">
         <v>7</v>
@@ -10453,10 +10469,10 @@
     <row r="409" ht="15" customHeight="1" spans="1:6">
       <c r="A409" s="1"/>
       <c r="B409" s="1">
-        <v>60081</v>
+        <v>60077</v>
       </c>
       <c r="C409" s="1" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="D409" s="1">
         <v>7</v>
@@ -10471,10 +10487,10 @@
     <row r="410" ht="15" customHeight="1" spans="1:6">
       <c r="A410" s="1"/>
       <c r="B410" s="1">
-        <v>60082</v>
+        <v>60078</v>
       </c>
       <c r="C410" s="1" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="D410" s="1">
         <v>7</v>
@@ -10489,10 +10505,10 @@
     <row r="411" ht="15" customHeight="1" spans="1:6">
       <c r="A411" s="1"/>
       <c r="B411" s="1">
-        <v>60083</v>
+        <v>60079</v>
       </c>
       <c r="C411" s="1" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="D411" s="1">
         <v>7</v>
@@ -10502,6 +10518,78 @@
       </c>
       <c r="F411" s="1" t="s">
         <v>836</v>
+      </c>
+    </row>
+    <row r="412" ht="15" customHeight="1" spans="1:6">
+      <c r="A412" s="1"/>
+      <c r="B412" s="1">
+        <v>60080</v>
+      </c>
+      <c r="C412" s="1" t="s">
+        <v>678</v>
+      </c>
+      <c r="D412" s="1">
+        <v>7</v>
+      </c>
+      <c r="E412" s="1" t="s">
+        <v>837</v>
+      </c>
+      <c r="F412" s="1" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="413" ht="15" customHeight="1" spans="1:6">
+      <c r="A413" s="1"/>
+      <c r="B413" s="1">
+        <v>60081</v>
+      </c>
+      <c r="C413" s="1" t="s">
+        <v>678</v>
+      </c>
+      <c r="D413" s="1">
+        <v>7</v>
+      </c>
+      <c r="E413" s="1" t="s">
+        <v>839</v>
+      </c>
+      <c r="F413" s="1" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="414" ht="15" customHeight="1" spans="1:6">
+      <c r="A414" s="1"/>
+      <c r="B414" s="1">
+        <v>60082</v>
+      </c>
+      <c r="C414" s="1" t="s">
+        <v>678</v>
+      </c>
+      <c r="D414" s="1">
+        <v>7</v>
+      </c>
+      <c r="E414" s="1" t="s">
+        <v>841</v>
+      </c>
+      <c r="F414" s="1" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="415" ht="15" customHeight="1" spans="1:6">
+      <c r="A415" s="1"/>
+      <c r="B415" s="1">
+        <v>60083</v>
+      </c>
+      <c r="C415" s="1" t="s">
+        <v>678</v>
+      </c>
+      <c r="D415" s="1">
+        <v>7</v>
+      </c>
+      <c r="E415" s="1" t="s">
+        <v>843</v>
+      </c>
+      <c r="F415" s="1" t="s">
+        <v>844</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/DataTables/ResourceConfigTable.xlsx
+++ b/AAAGameData/DataTables/ResourceConfigTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27948" windowHeight="11855"/>
+    <workbookView windowWidth="29868" windowHeight="14855"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1046" uniqueCount="845">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1044" uniqueCount="843">
   <si>
     <t>#</t>
   </si>
@@ -1433,12 +1433,6 @@
     <t>棋子黑暗哮天犬头像</t>
   </si>
   <si>
-    <t>Chess/稻草人/稻草人头像.png</t>
-  </si>
-  <si>
-    <t>稻草人头像</t>
-  </si>
-  <si>
     <t>Buff/5001.png</t>
   </si>
   <si>
@@ -1640,25 +1634,25 @@
     <t>卡片背景-稀有度4</t>
   </si>
   <si>
-    <t>Card/Component/装饰/宝石_稀有.png</t>
+    <t>Card/Component/装饰/1.png</t>
   </si>
   <si>
     <t>宝石装饰-稀有</t>
   </si>
   <si>
-    <t>Card/Component/装饰/宝石_史诗.png</t>
+    <t>Card/Component/装饰/2.png</t>
   </si>
   <si>
     <t>宝石装饰-史诗</t>
   </si>
   <si>
-    <t>Card/Component/装饰/宝石_传奇.png</t>
+    <t>Card/Component/装饰/3.png</t>
   </si>
   <si>
     <t>宝石装饰-传奇</t>
   </si>
   <si>
-    <t>Card/Component/装饰/宝石_神话.png</t>
+    <t>Card/Component/装饰/4.png</t>
   </si>
   <si>
     <t>宝石装饰-神话</t>
@@ -3526,7 +3520,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F415"/>
+  <dimension ref="A1:F414"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -7305,7 +7299,7 @@
     <row r="230" ht="15" customHeight="1" spans="1:6">
       <c r="A230" s="1"/>
       <c r="B230" s="1">
-        <v>13999</v>
+        <v>15001</v>
       </c>
       <c r="C230" s="1"/>
       <c r="D230" s="1">
@@ -7321,27 +7315,27 @@
     <row r="231" ht="15" customHeight="1" spans="1:6">
       <c r="A231" s="1"/>
       <c r="B231" s="1">
-        <v>15001</v>
-      </c>
-      <c r="C231" s="1"/>
+        <v>15002</v>
+      </c>
+      <c r="C231" s="1" t="s">
+        <v>470</v>
+      </c>
       <c r="D231" s="1">
         <v>1</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F231" s="1" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="232" ht="15" customHeight="1" spans="1:6">
       <c r="A232" s="1"/>
       <c r="B232" s="1">
-        <v>15002</v>
-      </c>
-      <c r="C232" s="1" t="s">
-        <v>472</v>
-      </c>
+        <v>15003</v>
+      </c>
+      <c r="C232" s="1"/>
       <c r="D232" s="1">
         <v>1</v>
       </c>
@@ -7355,7 +7349,7 @@
     <row r="233" ht="15" customHeight="1" spans="1:6">
       <c r="A233" s="1"/>
       <c r="B233" s="1">
-        <v>15003</v>
+        <v>15005</v>
       </c>
       <c r="C233" s="1"/>
       <c r="D233" s="1">
@@ -7371,7 +7365,7 @@
     <row r="234" ht="15" customHeight="1" spans="1:6">
       <c r="A234" s="1"/>
       <c r="B234" s="1">
-        <v>15005</v>
+        <v>15007</v>
       </c>
       <c r="C234" s="1"/>
       <c r="D234" s="1">
@@ -7387,7 +7381,7 @@
     <row r="235" ht="15" customHeight="1" spans="1:6">
       <c r="A235" s="1"/>
       <c r="B235" s="1">
-        <v>15007</v>
+        <v>15008</v>
       </c>
       <c r="C235" s="1"/>
       <c r="D235" s="1">
@@ -7403,7 +7397,7 @@
     <row r="236" ht="15" customHeight="1" spans="1:6">
       <c r="A236" s="1"/>
       <c r="B236" s="1">
-        <v>15008</v>
+        <v>15009</v>
       </c>
       <c r="C236" s="1"/>
       <c r="D236" s="1">
@@ -7419,7 +7413,7 @@
     <row r="237" ht="15" customHeight="1" spans="1:6">
       <c r="A237" s="1"/>
       <c r="B237" s="1">
-        <v>15009</v>
+        <v>15011</v>
       </c>
       <c r="C237" s="1"/>
       <c r="D237" s="1">
@@ -7435,7 +7429,7 @@
     <row r="238" ht="15" customHeight="1" spans="1:6">
       <c r="A238" s="1"/>
       <c r="B238" s="1">
-        <v>15011</v>
+        <v>15012</v>
       </c>
       <c r="C238" s="1"/>
       <c r="D238" s="1">
@@ -7451,7 +7445,7 @@
     <row r="239" ht="15" customHeight="1" spans="1:6">
       <c r="A239" s="1"/>
       <c r="B239" s="1">
-        <v>15012</v>
+        <v>15013</v>
       </c>
       <c r="C239" s="1"/>
       <c r="D239" s="1">
@@ -7467,7 +7461,7 @@
     <row r="240" ht="15" customHeight="1" spans="1:6">
       <c r="A240" s="1"/>
       <c r="B240" s="1">
-        <v>15013</v>
+        <v>15014</v>
       </c>
       <c r="C240" s="1"/>
       <c r="D240" s="1">
@@ -7483,7 +7477,7 @@
     <row r="241" ht="15" customHeight="1" spans="1:6">
       <c r="A241" s="1"/>
       <c r="B241" s="1">
-        <v>15014</v>
+        <v>15015</v>
       </c>
       <c r="C241" s="1"/>
       <c r="D241" s="1">
@@ -7499,7 +7493,7 @@
     <row r="242" ht="15" customHeight="1" spans="1:6">
       <c r="A242" s="1"/>
       <c r="B242" s="1">
-        <v>15015</v>
+        <v>15017</v>
       </c>
       <c r="C242" s="1"/>
       <c r="D242" s="1">
@@ -7515,7 +7509,7 @@
     <row r="243" ht="15" customHeight="1" spans="1:6">
       <c r="A243" s="1"/>
       <c r="B243" s="1">
-        <v>15017</v>
+        <v>15018</v>
       </c>
       <c r="C243" s="1"/>
       <c r="D243" s="1">
@@ -7531,7 +7525,7 @@
     <row r="244" ht="15" customHeight="1" spans="1:6">
       <c r="A244" s="1"/>
       <c r="B244" s="1">
-        <v>15018</v>
+        <v>15019</v>
       </c>
       <c r="C244" s="1"/>
       <c r="D244" s="1">
@@ -7547,7 +7541,7 @@
     <row r="245" ht="15" customHeight="1" spans="1:6">
       <c r="A245" s="1"/>
       <c r="B245" s="1">
-        <v>15019</v>
+        <v>15020</v>
       </c>
       <c r="C245" s="1"/>
       <c r="D245" s="1">
@@ -7563,7 +7557,7 @@
     <row r="246" ht="15" customHeight="1" spans="1:6">
       <c r="A246" s="1"/>
       <c r="B246" s="1">
-        <v>15020</v>
+        <v>15021</v>
       </c>
       <c r="C246" s="1"/>
       <c r="D246" s="1">
@@ -7579,44 +7573,46 @@
     <row r="247" ht="15" customHeight="1" spans="1:6">
       <c r="A247" s="1"/>
       <c r="B247" s="1">
-        <v>15021</v>
-      </c>
-      <c r="C247" s="1"/>
+        <v>15022</v>
+      </c>
+      <c r="C247" s="1" t="s">
+        <v>503</v>
+      </c>
       <c r="D247" s="1">
         <v>1</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="F247" s="1" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="248" ht="15" customHeight="1" spans="1:6">
       <c r="A248" s="1"/>
       <c r="B248" s="1">
-        <v>15022</v>
+        <v>16001</v>
       </c>
       <c r="C248" s="1" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D248" s="1">
         <v>1</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F248" s="1" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="249" ht="15" customHeight="1" spans="1:6">
       <c r="A249" s="1"/>
       <c r="B249" s="1">
-        <v>16001</v>
+        <v>16002</v>
       </c>
       <c r="C249" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D249" s="1">
         <v>1</v>
@@ -7631,10 +7627,10 @@
     <row r="250" ht="15" customHeight="1" spans="1:6">
       <c r="A250" s="1"/>
       <c r="B250" s="1">
-        <v>16002</v>
+        <v>16003</v>
       </c>
       <c r="C250" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D250" s="1">
         <v>1</v>
@@ -7649,10 +7645,10 @@
     <row r="251" ht="15" customHeight="1" spans="1:6">
       <c r="A251" s="1"/>
       <c r="B251" s="1">
-        <v>16003</v>
+        <v>16004</v>
       </c>
       <c r="C251" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D251" s="1">
         <v>1</v>
@@ -7667,10 +7663,10 @@
     <row r="252" ht="15" customHeight="1" spans="1:6">
       <c r="A252" s="1"/>
       <c r="B252" s="1">
-        <v>16004</v>
+        <v>16005</v>
       </c>
       <c r="C252" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D252" s="1">
         <v>1</v>
@@ -7685,10 +7681,10 @@
     <row r="253" ht="15" customHeight="1" spans="1:6">
       <c r="A253" s="1"/>
       <c r="B253" s="1">
-        <v>16005</v>
+        <v>16006</v>
       </c>
       <c r="C253" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D253" s="1">
         <v>1</v>
@@ -7700,14 +7696,12 @@
         <v>518</v>
       </c>
     </row>
-    <row r="254" ht="15" customHeight="1" spans="1:6">
+    <row r="254" ht="14" customHeight="1" spans="1:6">
       <c r="A254" s="1"/>
       <c r="B254" s="1">
-        <v>16006</v>
-      </c>
-      <c r="C254" s="1" t="s">
-        <v>508</v>
-      </c>
+        <v>19001</v>
+      </c>
+      <c r="C254" s="1"/>
       <c r="D254" s="1">
         <v>1</v>
       </c>
@@ -7721,7 +7715,7 @@
     <row r="255" ht="14" customHeight="1" spans="1:6">
       <c r="A255" s="1"/>
       <c r="B255" s="1">
-        <v>19001</v>
+        <v>19002</v>
       </c>
       <c r="C255" s="1"/>
       <c r="D255" s="1">
@@ -7734,10 +7728,10 @@
         <v>522</v>
       </c>
     </row>
-    <row r="256" ht="14" customHeight="1" spans="1:6">
+    <row r="256" ht="15" customHeight="1" spans="1:6">
       <c r="A256" s="1"/>
       <c r="B256" s="1">
-        <v>19002</v>
+        <v>19003</v>
       </c>
       <c r="C256" s="1"/>
       <c r="D256" s="1">
@@ -7753,7 +7747,7 @@
     <row r="257" ht="15" customHeight="1" spans="1:6">
       <c r="A257" s="1"/>
       <c r="B257" s="1">
-        <v>19003</v>
+        <v>19004</v>
       </c>
       <c r="C257" s="1"/>
       <c r="D257" s="1">
@@ -7769,7 +7763,7 @@
     <row r="258" ht="15" customHeight="1" spans="1:6">
       <c r="A258" s="1"/>
       <c r="B258" s="1">
-        <v>19004</v>
+        <v>19011</v>
       </c>
       <c r="C258" s="1"/>
       <c r="D258" s="1">
@@ -7785,7 +7779,7 @@
     <row r="259" ht="15" customHeight="1" spans="1:6">
       <c r="A259" s="1"/>
       <c r="B259" s="1">
-        <v>19011</v>
+        <v>19012</v>
       </c>
       <c r="C259" s="1"/>
       <c r="D259" s="1">
@@ -7801,7 +7795,7 @@
     <row r="260" ht="15" customHeight="1" spans="1:6">
       <c r="A260" s="1"/>
       <c r="B260" s="1">
-        <v>19012</v>
+        <v>19013</v>
       </c>
       <c r="C260" s="1"/>
       <c r="D260" s="1">
@@ -7817,7 +7811,7 @@
     <row r="261" ht="15" customHeight="1" spans="1:6">
       <c r="A261" s="1"/>
       <c r="B261" s="1">
-        <v>19013</v>
+        <v>19014</v>
       </c>
       <c r="C261" s="1"/>
       <c r="D261" s="1">
@@ -7833,7 +7827,7 @@
     <row r="262" ht="15" customHeight="1" spans="1:6">
       <c r="A262" s="1"/>
       <c r="B262" s="1">
-        <v>19014</v>
+        <v>19021</v>
       </c>
       <c r="C262" s="1"/>
       <c r="D262" s="1">
@@ -7849,7 +7843,7 @@
     <row r="263" ht="15" customHeight="1" spans="1:6">
       <c r="A263" s="1"/>
       <c r="B263" s="1">
-        <v>19021</v>
+        <v>19022</v>
       </c>
       <c r="C263" s="1"/>
       <c r="D263" s="1">
@@ -7865,7 +7859,7 @@
     <row r="264" ht="15" customHeight="1" spans="1:6">
       <c r="A264" s="1"/>
       <c r="B264" s="1">
-        <v>19022</v>
+        <v>19023</v>
       </c>
       <c r="C264" s="1"/>
       <c r="D264" s="1">
@@ -7881,7 +7875,7 @@
     <row r="265" ht="15" customHeight="1" spans="1:6">
       <c r="A265" s="1"/>
       <c r="B265" s="1">
-        <v>19023</v>
+        <v>19024</v>
       </c>
       <c r="C265" s="1"/>
       <c r="D265" s="1">
@@ -7897,26 +7891,28 @@
     <row r="266" ht="15" customHeight="1" spans="1:6">
       <c r="A266" s="1"/>
       <c r="B266" s="1">
-        <v>19024</v>
-      </c>
-      <c r="C266" s="1"/>
+        <v>20101</v>
+      </c>
+      <c r="C266" s="1" t="s">
+        <v>543</v>
+      </c>
       <c r="D266" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="F266" s="1" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="267" ht="15" customHeight="1" spans="1:6">
       <c r="A267" s="1"/>
       <c r="B267" s="1">
-        <v>20101</v>
+        <v>20102</v>
       </c>
       <c r="C267" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D267" s="1">
         <v>2</v>
@@ -7931,10 +7927,10 @@
     <row r="268" ht="15" customHeight="1" spans="1:6">
       <c r="A268" s="1"/>
       <c r="B268" s="1">
-        <v>20102</v>
+        <v>20103</v>
       </c>
       <c r="C268" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D268" s="1">
         <v>2</v>
@@ -7949,10 +7945,10 @@
     <row r="269" ht="15" customHeight="1" spans="1:6">
       <c r="A269" s="1"/>
       <c r="B269" s="1">
-        <v>20103</v>
+        <v>20104</v>
       </c>
       <c r="C269" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D269" s="1">
         <v>2</v>
@@ -7967,10 +7963,10 @@
     <row r="270" ht="15" customHeight="1" spans="1:6">
       <c r="A270" s="1"/>
       <c r="B270" s="1">
-        <v>20104</v>
+        <v>20105</v>
       </c>
       <c r="C270" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D270" s="1">
         <v>2</v>
@@ -7985,10 +7981,10 @@
     <row r="271" ht="15" customHeight="1" spans="1:6">
       <c r="A271" s="1"/>
       <c r="B271" s="1">
-        <v>20105</v>
+        <v>20106</v>
       </c>
       <c r="C271" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D271" s="1">
         <v>2</v>
@@ -8003,10 +7999,10 @@
     <row r="272" ht="15" customHeight="1" spans="1:6">
       <c r="A272" s="1"/>
       <c r="B272" s="1">
-        <v>20106</v>
+        <v>20107</v>
       </c>
       <c r="C272" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D272" s="1">
         <v>2</v>
@@ -8021,10 +8017,10 @@
     <row r="273" ht="15" customHeight="1" spans="1:6">
       <c r="A273" s="1"/>
       <c r="B273" s="1">
-        <v>20107</v>
+        <v>20108</v>
       </c>
       <c r="C273" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D273" s="1">
         <v>2</v>
@@ -8039,10 +8035,10 @@
     <row r="274" ht="15" customHeight="1" spans="1:6">
       <c r="A274" s="1"/>
       <c r="B274" s="1">
-        <v>20108</v>
+        <v>20109</v>
       </c>
       <c r="C274" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D274" s="1">
         <v>2</v>
@@ -8057,10 +8053,10 @@
     <row r="275" ht="15" customHeight="1" spans="1:6">
       <c r="A275" s="1"/>
       <c r="B275" s="1">
-        <v>20109</v>
+        <v>20110</v>
       </c>
       <c r="C275" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D275" s="1">
         <v>2</v>
@@ -8075,10 +8071,10 @@
     <row r="276" ht="15" customHeight="1" spans="1:6">
       <c r="A276" s="1"/>
       <c r="B276" s="1">
-        <v>20110</v>
+        <v>20111</v>
       </c>
       <c r="C276" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D276" s="1">
         <v>2</v>
@@ -8093,10 +8089,10 @@
     <row r="277" ht="15" customHeight="1" spans="1:6">
       <c r="A277" s="1"/>
       <c r="B277" s="1">
-        <v>20111</v>
+        <v>20112</v>
       </c>
       <c r="C277" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D277" s="1">
         <v>2</v>
@@ -8111,10 +8107,10 @@
     <row r="278" ht="15" customHeight="1" spans="1:6">
       <c r="A278" s="1"/>
       <c r="B278" s="1">
-        <v>20112</v>
+        <v>20113</v>
       </c>
       <c r="C278" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D278" s="1">
         <v>2</v>
@@ -8129,10 +8125,10 @@
     <row r="279" ht="15" customHeight="1" spans="1:6">
       <c r="A279" s="1"/>
       <c r="B279" s="1">
-        <v>20113</v>
+        <v>20114</v>
       </c>
       <c r="C279" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D279" s="1">
         <v>2</v>
@@ -8147,10 +8143,10 @@
     <row r="280" ht="15" customHeight="1" spans="1:6">
       <c r="A280" s="1"/>
       <c r="B280" s="1">
-        <v>20114</v>
+        <v>20115</v>
       </c>
       <c r="C280" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D280" s="1">
         <v>2</v>
@@ -8165,10 +8161,10 @@
     <row r="281" ht="15" customHeight="1" spans="1:6">
       <c r="A281" s="1"/>
       <c r="B281" s="1">
-        <v>20115</v>
+        <v>20116</v>
       </c>
       <c r="C281" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D281" s="1">
         <v>2</v>
@@ -8183,10 +8179,10 @@
     <row r="282" ht="15" customHeight="1" spans="1:6">
       <c r="A282" s="1"/>
       <c r="B282" s="1">
-        <v>20116</v>
+        <v>20117</v>
       </c>
       <c r="C282" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D282" s="1">
         <v>2</v>
@@ -8201,10 +8197,10 @@
     <row r="283" ht="15" customHeight="1" spans="1:6">
       <c r="A283" s="1"/>
       <c r="B283" s="1">
-        <v>20117</v>
+        <v>20118</v>
       </c>
       <c r="C283" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D283" s="1">
         <v>2</v>
@@ -8219,10 +8215,10 @@
     <row r="284" ht="15" customHeight="1" spans="1:6">
       <c r="A284" s="1"/>
       <c r="B284" s="1">
-        <v>20118</v>
+        <v>20119</v>
       </c>
       <c r="C284" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D284" s="1">
         <v>2</v>
@@ -8237,10 +8233,10 @@
     <row r="285" ht="15" customHeight="1" spans="1:6">
       <c r="A285" s="1"/>
       <c r="B285" s="1">
-        <v>20119</v>
+        <v>20120</v>
       </c>
       <c r="C285" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D285" s="1">
         <v>2</v>
@@ -8255,10 +8251,10 @@
     <row r="286" ht="15" customHeight="1" spans="1:6">
       <c r="A286" s="1"/>
       <c r="B286" s="1">
-        <v>20120</v>
+        <v>20121</v>
       </c>
       <c r="C286" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D286" s="1">
         <v>2</v>
@@ -8273,10 +8269,10 @@
     <row r="287" ht="15" customHeight="1" spans="1:6">
       <c r="A287" s="1"/>
       <c r="B287" s="1">
-        <v>20121</v>
+        <v>20122</v>
       </c>
       <c r="C287" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D287" s="1">
         <v>2</v>
@@ -8291,10 +8287,10 @@
     <row r="288" ht="15" customHeight="1" spans="1:6">
       <c r="A288" s="1"/>
       <c r="B288" s="1">
-        <v>20122</v>
+        <v>20123</v>
       </c>
       <c r="C288" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D288" s="1">
         <v>2</v>
@@ -8309,10 +8305,10 @@
     <row r="289" ht="15" customHeight="1" spans="1:6">
       <c r="A289" s="1"/>
       <c r="B289" s="1">
-        <v>20123</v>
+        <v>20124</v>
       </c>
       <c r="C289" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D289" s="1">
         <v>2</v>
@@ -8327,10 +8323,10 @@
     <row r="290" ht="15" customHeight="1" spans="1:6">
       <c r="A290" s="1"/>
       <c r="B290" s="1">
-        <v>20124</v>
+        <v>20125</v>
       </c>
       <c r="C290" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D290" s="1">
         <v>2</v>
@@ -8345,10 +8341,10 @@
     <row r="291" ht="15" customHeight="1" spans="1:6">
       <c r="A291" s="1"/>
       <c r="B291" s="1">
-        <v>20125</v>
+        <v>20126</v>
       </c>
       <c r="C291" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D291" s="1">
         <v>2</v>
@@ -8363,10 +8359,10 @@
     <row r="292" ht="15" customHeight="1" spans="1:6">
       <c r="A292" s="1"/>
       <c r="B292" s="1">
-        <v>20126</v>
+        <v>20127</v>
       </c>
       <c r="C292" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D292" s="1">
         <v>2</v>
@@ -8381,13 +8377,13 @@
     <row r="293" ht="15" customHeight="1" spans="1:6">
       <c r="A293" s="1"/>
       <c r="B293" s="1">
-        <v>20127</v>
+        <v>30101</v>
       </c>
       <c r="C293" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D293" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E293" s="1" t="s">
         <v>598</v>
@@ -8399,10 +8395,10 @@
     <row r="294" ht="15" customHeight="1" spans="1:6">
       <c r="A294" s="1"/>
       <c r="B294" s="1">
-        <v>30101</v>
+        <v>30102</v>
       </c>
       <c r="C294" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D294" s="1">
         <v>3</v>
@@ -8417,10 +8413,10 @@
     <row r="295" ht="15" customHeight="1" spans="1:6">
       <c r="A295" s="1"/>
       <c r="B295" s="1">
-        <v>30102</v>
+        <v>30103</v>
       </c>
       <c r="C295" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D295" s="1">
         <v>3</v>
@@ -8435,10 +8431,10 @@
     <row r="296" ht="15" customHeight="1" spans="1:6">
       <c r="A296" s="1"/>
       <c r="B296" s="1">
-        <v>30103</v>
+        <v>30104</v>
       </c>
       <c r="C296" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D296" s="1">
         <v>3</v>
@@ -8453,10 +8449,10 @@
     <row r="297" ht="15" customHeight="1" spans="1:6">
       <c r="A297" s="1"/>
       <c r="B297" s="1">
-        <v>30104</v>
+        <v>30105</v>
       </c>
       <c r="C297" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D297" s="1">
         <v>3</v>
@@ -8471,10 +8467,10 @@
     <row r="298" ht="15" customHeight="1" spans="1:6">
       <c r="A298" s="1"/>
       <c r="B298" s="1">
-        <v>30105</v>
+        <v>30106</v>
       </c>
       <c r="C298" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D298" s="1">
         <v>3</v>
@@ -8489,10 +8485,10 @@
     <row r="299" ht="15" customHeight="1" spans="1:6">
       <c r="A299" s="1"/>
       <c r="B299" s="1">
-        <v>30106</v>
+        <v>30107</v>
       </c>
       <c r="C299" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D299" s="1">
         <v>3</v>
@@ -8507,10 +8503,10 @@
     <row r="300" ht="15" customHeight="1" spans="1:6">
       <c r="A300" s="1"/>
       <c r="B300" s="1">
-        <v>30107</v>
+        <v>30108</v>
       </c>
       <c r="C300" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D300" s="1">
         <v>3</v>
@@ -8525,10 +8521,10 @@
     <row r="301" ht="15" customHeight="1" spans="1:6">
       <c r="A301" s="1"/>
       <c r="B301" s="1">
-        <v>30108</v>
+        <v>30109</v>
       </c>
       <c r="C301" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D301" s="1">
         <v>3</v>
@@ -8543,10 +8539,10 @@
     <row r="302" ht="15" customHeight="1" spans="1:6">
       <c r="A302" s="1"/>
       <c r="B302" s="1">
-        <v>30109</v>
+        <v>30110</v>
       </c>
       <c r="C302" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D302" s="1">
         <v>3</v>
@@ -8561,10 +8557,10 @@
     <row r="303" ht="15" customHeight="1" spans="1:6">
       <c r="A303" s="1"/>
       <c r="B303" s="1">
-        <v>30110</v>
+        <v>30111</v>
       </c>
       <c r="C303" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D303" s="1">
         <v>3</v>
@@ -8579,10 +8575,10 @@
     <row r="304" ht="15" customHeight="1" spans="1:6">
       <c r="A304" s="1"/>
       <c r="B304" s="1">
-        <v>30111</v>
+        <v>30112</v>
       </c>
       <c r="C304" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D304" s="1">
         <v>3</v>
@@ -8597,10 +8593,10 @@
     <row r="305" ht="15" customHeight="1" spans="1:6">
       <c r="A305" s="1"/>
       <c r="B305" s="1">
-        <v>30112</v>
+        <v>30113</v>
       </c>
       <c r="C305" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D305" s="1">
         <v>3</v>
@@ -8615,10 +8611,10 @@
     <row r="306" ht="15" customHeight="1" spans="1:6">
       <c r="A306" s="1"/>
       <c r="B306" s="1">
-        <v>30113</v>
+        <v>30114</v>
       </c>
       <c r="C306" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D306" s="1">
         <v>3</v>
@@ -8633,10 +8629,10 @@
     <row r="307" ht="15" customHeight="1" spans="1:6">
       <c r="A307" s="1"/>
       <c r="B307" s="1">
-        <v>30114</v>
+        <v>30115</v>
       </c>
       <c r="C307" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D307" s="1">
         <v>3</v>
@@ -8651,10 +8647,10 @@
     <row r="308" ht="15" customHeight="1" spans="1:6">
       <c r="A308" s="1"/>
       <c r="B308" s="1">
-        <v>30115</v>
+        <v>30116</v>
       </c>
       <c r="C308" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D308" s="1">
         <v>3</v>
@@ -8669,10 +8665,10 @@
     <row r="309" ht="15" customHeight="1" spans="1:6">
       <c r="A309" s="1"/>
       <c r="B309" s="1">
-        <v>30116</v>
+        <v>30117</v>
       </c>
       <c r="C309" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D309" s="1">
         <v>3</v>
@@ -8687,10 +8683,10 @@
     <row r="310" ht="15" customHeight="1" spans="1:6">
       <c r="A310" s="1"/>
       <c r="B310" s="1">
-        <v>30117</v>
+        <v>30118</v>
       </c>
       <c r="C310" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D310" s="1">
         <v>3</v>
@@ -8705,10 +8701,10 @@
     <row r="311" ht="15" customHeight="1" spans="1:6">
       <c r="A311" s="1"/>
       <c r="B311" s="1">
-        <v>30118</v>
+        <v>30119</v>
       </c>
       <c r="C311" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D311" s="1">
         <v>3</v>
@@ -8723,10 +8719,10 @@
     <row r="312" ht="15" customHeight="1" spans="1:6">
       <c r="A312" s="1"/>
       <c r="B312" s="1">
-        <v>30119</v>
+        <v>30120</v>
       </c>
       <c r="C312" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D312" s="1">
         <v>3</v>
@@ -8741,10 +8737,10 @@
     <row r="313" ht="15" customHeight="1" spans="1:6">
       <c r="A313" s="1"/>
       <c r="B313" s="1">
-        <v>30120</v>
+        <v>30121</v>
       </c>
       <c r="C313" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D313" s="1">
         <v>3</v>
@@ -8759,10 +8755,10 @@
     <row r="314" ht="15" customHeight="1" spans="1:6">
       <c r="A314" s="1"/>
       <c r="B314" s="1">
-        <v>30121</v>
+        <v>30122</v>
       </c>
       <c r="C314" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D314" s="1">
         <v>3</v>
@@ -8777,10 +8773,10 @@
     <row r="315" ht="15" customHeight="1" spans="1:6">
       <c r="A315" s="1"/>
       <c r="B315" s="1">
-        <v>30122</v>
+        <v>30123</v>
       </c>
       <c r="C315" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D315" s="1">
         <v>3</v>
@@ -8795,10 +8791,10 @@
     <row r="316" ht="15" customHeight="1" spans="1:6">
       <c r="A316" s="1"/>
       <c r="B316" s="1">
-        <v>30123</v>
+        <v>30124</v>
       </c>
       <c r="C316" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D316" s="1">
         <v>3</v>
@@ -8813,10 +8809,10 @@
     <row r="317" ht="15" customHeight="1" spans="1:6">
       <c r="A317" s="1"/>
       <c r="B317" s="1">
-        <v>30124</v>
+        <v>30125</v>
       </c>
       <c r="C317" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D317" s="1">
         <v>3</v>
@@ -8831,10 +8827,10 @@
     <row r="318" ht="15" customHeight="1" spans="1:6">
       <c r="A318" s="1"/>
       <c r="B318" s="1">
-        <v>30125</v>
+        <v>30201</v>
       </c>
       <c r="C318" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D318" s="1">
         <v>3</v>
@@ -8849,10 +8845,10 @@
     <row r="319" ht="15" customHeight="1" spans="1:6">
       <c r="A319" s="1"/>
       <c r="B319" s="1">
-        <v>30201</v>
+        <v>30202</v>
       </c>
       <c r="C319" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D319" s="1">
         <v>3</v>
@@ -8867,10 +8863,10 @@
     <row r="320" ht="15" customHeight="1" spans="1:6">
       <c r="A320" s="1"/>
       <c r="B320" s="1">
-        <v>30202</v>
+        <v>30203</v>
       </c>
       <c r="C320" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D320" s="1">
         <v>3</v>
@@ -8885,10 +8881,10 @@
     <row r="321" ht="15" customHeight="1" spans="1:6">
       <c r="A321" s="1"/>
       <c r="B321" s="1">
-        <v>30203</v>
+        <v>30204</v>
       </c>
       <c r="C321" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D321" s="1">
         <v>3</v>
@@ -8903,10 +8899,10 @@
     <row r="322" ht="15" customHeight="1" spans="1:6">
       <c r="A322" s="1"/>
       <c r="B322" s="1">
-        <v>30204</v>
+        <v>30205</v>
       </c>
       <c r="C322" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D322" s="1">
         <v>3</v>
@@ -8921,10 +8917,10 @@
     <row r="323" ht="15" customHeight="1" spans="1:6">
       <c r="A323" s="1"/>
       <c r="B323" s="1">
-        <v>30205</v>
+        <v>30206</v>
       </c>
       <c r="C323" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D323" s="1">
         <v>3</v>
@@ -8939,10 +8935,10 @@
     <row r="324" ht="15" customHeight="1" spans="1:6">
       <c r="A324" s="1"/>
       <c r="B324" s="1">
-        <v>30206</v>
+        <v>30301</v>
       </c>
       <c r="C324" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D324" s="1">
         <v>3</v>
@@ -8957,10 +8953,10 @@
     <row r="325" ht="15" customHeight="1" spans="1:6">
       <c r="A325" s="1"/>
       <c r="B325" s="1">
-        <v>30301</v>
+        <v>30302</v>
       </c>
       <c r="C325" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D325" s="1">
         <v>3</v>
@@ -8975,10 +8971,10 @@
     <row r="326" ht="15" customHeight="1" spans="1:6">
       <c r="A326" s="1"/>
       <c r="B326" s="1">
-        <v>30302</v>
+        <v>30303</v>
       </c>
       <c r="C326" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D326" s="1">
         <v>3</v>
@@ -8993,10 +8989,10 @@
     <row r="327" ht="15" customHeight="1" spans="1:6">
       <c r="A327" s="1"/>
       <c r="B327" s="1">
-        <v>30303</v>
+        <v>30304</v>
       </c>
       <c r="C327" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D327" s="1">
         <v>3</v>
@@ -9011,10 +9007,10 @@
     <row r="328" ht="15" customHeight="1" spans="1:6">
       <c r="A328" s="1"/>
       <c r="B328" s="1">
-        <v>30304</v>
+        <v>30305</v>
       </c>
       <c r="C328" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D328" s="1">
         <v>3</v>
@@ -9029,10 +9025,10 @@
     <row r="329" ht="15" customHeight="1" spans="1:6">
       <c r="A329" s="1"/>
       <c r="B329" s="1">
-        <v>30305</v>
+        <v>30306</v>
       </c>
       <c r="C329" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D329" s="1">
         <v>3</v>
@@ -9047,10 +9043,10 @@
     <row r="330" ht="15" customHeight="1" spans="1:6">
       <c r="A330" s="1"/>
       <c r="B330" s="1">
-        <v>30306</v>
+        <v>30307</v>
       </c>
       <c r="C330" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D330" s="1">
         <v>3</v>
@@ -9065,10 +9061,10 @@
     <row r="331" ht="15" customHeight="1" spans="1:6">
       <c r="A331" s="1"/>
       <c r="B331" s="1">
-        <v>30307</v>
+        <v>30308</v>
       </c>
       <c r="C331" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D331" s="1">
         <v>3</v>
@@ -9083,28 +9079,28 @@
     <row r="332" ht="15" customHeight="1" spans="1:6">
       <c r="A332" s="1"/>
       <c r="B332" s="1">
-        <v>30308</v>
+        <v>60001</v>
       </c>
       <c r="C332" s="1" t="s">
-        <v>545</v>
+        <v>676</v>
       </c>
       <c r="D332" s="1">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E332" s="1" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="F332" s="1" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="333" ht="15" customHeight="1" spans="1:6">
       <c r="A333" s="1"/>
       <c r="B333" s="1">
-        <v>60001</v>
+        <v>60002</v>
       </c>
       <c r="C333" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D333" s="1">
         <v>7</v>
@@ -9119,10 +9115,10 @@
     <row r="334" ht="15" customHeight="1" spans="1:6">
       <c r="A334" s="1"/>
       <c r="B334" s="1">
-        <v>60002</v>
+        <v>60003</v>
       </c>
       <c r="C334" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D334" s="1">
         <v>7</v>
@@ -9137,10 +9133,10 @@
     <row r="335" ht="15" customHeight="1" spans="1:6">
       <c r="A335" s="1"/>
       <c r="B335" s="1">
-        <v>60003</v>
+        <v>60004</v>
       </c>
       <c r="C335" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D335" s="1">
         <v>7</v>
@@ -9155,10 +9151,10 @@
     <row r="336" ht="15" customHeight="1" spans="1:6">
       <c r="A336" s="1"/>
       <c r="B336" s="1">
-        <v>60004</v>
+        <v>60005</v>
       </c>
       <c r="C336" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D336" s="1">
         <v>7</v>
@@ -9173,10 +9169,10 @@
     <row r="337" ht="15" customHeight="1" spans="1:6">
       <c r="A337" s="1"/>
       <c r="B337" s="1">
-        <v>60005</v>
+        <v>60006</v>
       </c>
       <c r="C337" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D337" s="1">
         <v>7</v>
@@ -9191,10 +9187,10 @@
     <row r="338" ht="15" customHeight="1" spans="1:6">
       <c r="A338" s="1"/>
       <c r="B338" s="1">
-        <v>60006</v>
+        <v>60007</v>
       </c>
       <c r="C338" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D338" s="1">
         <v>7</v>
@@ -9209,10 +9205,10 @@
     <row r="339" ht="15" customHeight="1" spans="1:6">
       <c r="A339" s="1"/>
       <c r="B339" s="1">
-        <v>60007</v>
+        <v>60008</v>
       </c>
       <c r="C339" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D339" s="1">
         <v>7</v>
@@ -9227,10 +9223,10 @@
     <row r="340" ht="15" customHeight="1" spans="1:6">
       <c r="A340" s="1"/>
       <c r="B340" s="1">
-        <v>60008</v>
+        <v>60009</v>
       </c>
       <c r="C340" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D340" s="1">
         <v>7</v>
@@ -9245,10 +9241,10 @@
     <row r="341" ht="15" customHeight="1" spans="1:6">
       <c r="A341" s="1"/>
       <c r="B341" s="1">
-        <v>60009</v>
+        <v>60010</v>
       </c>
       <c r="C341" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D341" s="1">
         <v>7</v>
@@ -9263,10 +9259,10 @@
     <row r="342" ht="15" customHeight="1" spans="1:6">
       <c r="A342" s="1"/>
       <c r="B342" s="1">
-        <v>60010</v>
+        <v>60011</v>
       </c>
       <c r="C342" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D342" s="1">
         <v>7</v>
@@ -9281,10 +9277,10 @@
     <row r="343" ht="15" customHeight="1" spans="1:6">
       <c r="A343" s="1"/>
       <c r="B343" s="1">
-        <v>60011</v>
+        <v>60012</v>
       </c>
       <c r="C343" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D343" s="1">
         <v>7</v>
@@ -9299,10 +9295,10 @@
     <row r="344" ht="15" customHeight="1" spans="1:6">
       <c r="A344" s="1"/>
       <c r="B344" s="1">
-        <v>60012</v>
+        <v>60013</v>
       </c>
       <c r="C344" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D344" s="1">
         <v>7</v>
@@ -9317,10 +9313,10 @@
     <row r="345" ht="15" customHeight="1" spans="1:6">
       <c r="A345" s="1"/>
       <c r="B345" s="1">
-        <v>60013</v>
+        <v>60014</v>
       </c>
       <c r="C345" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D345" s="1">
         <v>7</v>
@@ -9335,10 +9331,10 @@
     <row r="346" ht="15" customHeight="1" spans="1:6">
       <c r="A346" s="1"/>
       <c r="B346" s="1">
-        <v>60014</v>
+        <v>60015</v>
       </c>
       <c r="C346" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D346" s="1">
         <v>7</v>
@@ -9353,10 +9349,10 @@
     <row r="347" ht="15" customHeight="1" spans="1:6">
       <c r="A347" s="1"/>
       <c r="B347" s="1">
-        <v>60015</v>
+        <v>60016</v>
       </c>
       <c r="C347" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D347" s="1">
         <v>7</v>
@@ -9371,10 +9367,10 @@
     <row r="348" ht="15" customHeight="1" spans="1:6">
       <c r="A348" s="1"/>
       <c r="B348" s="1">
-        <v>60016</v>
+        <v>60017</v>
       </c>
       <c r="C348" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D348" s="1">
         <v>7</v>
@@ -9389,10 +9385,10 @@
     <row r="349" ht="15" customHeight="1" spans="1:6">
       <c r="A349" s="1"/>
       <c r="B349" s="1">
-        <v>60017</v>
+        <v>60018</v>
       </c>
       <c r="C349" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D349" s="1">
         <v>7</v>
@@ -9407,10 +9403,10 @@
     <row r="350" ht="15" customHeight="1" spans="1:6">
       <c r="A350" s="1"/>
       <c r="B350" s="1">
-        <v>60018</v>
+        <v>60019</v>
       </c>
       <c r="C350" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D350" s="1">
         <v>7</v>
@@ -9425,10 +9421,10 @@
     <row r="351" ht="15" customHeight="1" spans="1:6">
       <c r="A351" s="1"/>
       <c r="B351" s="1">
-        <v>60019</v>
+        <v>60020</v>
       </c>
       <c r="C351" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D351" s="1">
         <v>7</v>
@@ -9443,10 +9439,10 @@
     <row r="352" ht="15" customHeight="1" spans="1:6">
       <c r="A352" s="1"/>
       <c r="B352" s="1">
-        <v>60020</v>
+        <v>60021</v>
       </c>
       <c r="C352" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D352" s="1">
         <v>7</v>
@@ -9461,10 +9457,10 @@
     <row r="353" ht="15" customHeight="1" spans="1:6">
       <c r="A353" s="1"/>
       <c r="B353" s="1">
-        <v>60021</v>
+        <v>60022</v>
       </c>
       <c r="C353" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D353" s="1">
         <v>7</v>
@@ -9479,10 +9475,10 @@
     <row r="354" ht="15" customHeight="1" spans="1:6">
       <c r="A354" s="1"/>
       <c r="B354" s="1">
-        <v>60022</v>
+        <v>60023</v>
       </c>
       <c r="C354" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D354" s="1">
         <v>7</v>
@@ -9497,10 +9493,10 @@
     <row r="355" ht="15" customHeight="1" spans="1:6">
       <c r="A355" s="1"/>
       <c r="B355" s="1">
-        <v>60023</v>
+        <v>60024</v>
       </c>
       <c r="C355" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D355" s="1">
         <v>7</v>
@@ -9515,10 +9511,10 @@
     <row r="356" ht="15" customHeight="1" spans="1:6">
       <c r="A356" s="1"/>
       <c r="B356" s="1">
-        <v>60024</v>
+        <v>60025</v>
       </c>
       <c r="C356" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D356" s="1">
         <v>7</v>
@@ -9533,10 +9529,10 @@
     <row r="357" ht="15" customHeight="1" spans="1:6">
       <c r="A357" s="1"/>
       <c r="B357" s="1">
-        <v>60025</v>
+        <v>60026</v>
       </c>
       <c r="C357" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D357" s="1">
         <v>7</v>
@@ -9551,10 +9547,10 @@
     <row r="358" ht="15" customHeight="1" spans="1:6">
       <c r="A358" s="1"/>
       <c r="B358" s="1">
-        <v>60026</v>
+        <v>60027</v>
       </c>
       <c r="C358" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D358" s="1">
         <v>7</v>
@@ -9569,10 +9565,10 @@
     <row r="359" ht="15" customHeight="1" spans="1:6">
       <c r="A359" s="1"/>
       <c r="B359" s="1">
-        <v>60027</v>
+        <v>60028</v>
       </c>
       <c r="C359" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D359" s="1">
         <v>7</v>
@@ -9587,10 +9583,10 @@
     <row r="360" ht="15" customHeight="1" spans="1:6">
       <c r="A360" s="1"/>
       <c r="B360" s="1">
-        <v>60028</v>
+        <v>60029</v>
       </c>
       <c r="C360" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D360" s="1">
         <v>7</v>
@@ -9605,10 +9601,10 @@
     <row r="361" ht="15" customHeight="1" spans="1:6">
       <c r="A361" s="1"/>
       <c r="B361" s="1">
-        <v>60029</v>
+        <v>60030</v>
       </c>
       <c r="C361" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D361" s="1">
         <v>7</v>
@@ -9623,10 +9619,10 @@
     <row r="362" ht="15" customHeight="1" spans="1:6">
       <c r="A362" s="1"/>
       <c r="B362" s="1">
-        <v>60030</v>
+        <v>60031</v>
       </c>
       <c r="C362" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D362" s="1">
         <v>7</v>
@@ -9641,10 +9637,10 @@
     <row r="363" ht="15" customHeight="1" spans="1:6">
       <c r="A363" s="1"/>
       <c r="B363" s="1">
-        <v>60031</v>
+        <v>60032</v>
       </c>
       <c r="C363" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D363" s="1">
         <v>7</v>
@@ -9659,10 +9655,10 @@
     <row r="364" ht="15" customHeight="1" spans="1:6">
       <c r="A364" s="1"/>
       <c r="B364" s="1">
-        <v>60032</v>
+        <v>60033</v>
       </c>
       <c r="C364" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D364" s="1">
         <v>7</v>
@@ -9677,10 +9673,10 @@
     <row r="365" ht="15" customHeight="1" spans="1:6">
       <c r="A365" s="1"/>
       <c r="B365" s="1">
-        <v>60033</v>
+        <v>60034</v>
       </c>
       <c r="C365" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D365" s="1">
         <v>7</v>
@@ -9695,10 +9691,10 @@
     <row r="366" ht="15" customHeight="1" spans="1:6">
       <c r="A366" s="1"/>
       <c r="B366" s="1">
-        <v>60034</v>
+        <v>60035</v>
       </c>
       <c r="C366" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D366" s="1">
         <v>7</v>
@@ -9713,10 +9709,10 @@
     <row r="367" ht="15" customHeight="1" spans="1:6">
       <c r="A367" s="1"/>
       <c r="B367" s="1">
-        <v>60035</v>
+        <v>60036</v>
       </c>
       <c r="C367" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D367" s="1">
         <v>7</v>
@@ -9731,10 +9727,10 @@
     <row r="368" ht="15" customHeight="1" spans="1:6">
       <c r="A368" s="1"/>
       <c r="B368" s="1">
-        <v>60036</v>
+        <v>60037</v>
       </c>
       <c r="C368" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D368" s="1">
         <v>7</v>
@@ -9749,10 +9745,10 @@
     <row r="369" ht="15" customHeight="1" spans="1:6">
       <c r="A369" s="1"/>
       <c r="B369" s="1">
-        <v>60037</v>
+        <v>60038</v>
       </c>
       <c r="C369" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D369" s="1">
         <v>7</v>
@@ -9767,10 +9763,10 @@
     <row r="370" ht="15" customHeight="1" spans="1:6">
       <c r="A370" s="1"/>
       <c r="B370" s="1">
-        <v>60038</v>
+        <v>60039</v>
       </c>
       <c r="C370" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D370" s="1">
         <v>7</v>
@@ -9785,10 +9781,10 @@
     <row r="371" ht="15" customHeight="1" spans="1:6">
       <c r="A371" s="1"/>
       <c r="B371" s="1">
-        <v>60039</v>
+        <v>60040</v>
       </c>
       <c r="C371" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D371" s="1">
         <v>7</v>
@@ -9803,10 +9799,10 @@
     <row r="372" ht="15" customHeight="1" spans="1:6">
       <c r="A372" s="1"/>
       <c r="B372" s="1">
-        <v>60040</v>
+        <v>60041</v>
       </c>
       <c r="C372" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D372" s="1">
         <v>7</v>
@@ -9821,10 +9817,10 @@
     <row r="373" ht="15" customHeight="1" spans="1:6">
       <c r="A373" s="1"/>
       <c r="B373" s="1">
-        <v>60041</v>
+        <v>60042</v>
       </c>
       <c r="C373" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D373" s="1">
         <v>7</v>
@@ -9839,10 +9835,10 @@
     <row r="374" ht="15" customHeight="1" spans="1:6">
       <c r="A374" s="1"/>
       <c r="B374" s="1">
-        <v>60042</v>
+        <v>60043</v>
       </c>
       <c r="C374" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D374" s="1">
         <v>7</v>
@@ -9857,10 +9853,10 @@
     <row r="375" ht="15" customHeight="1" spans="1:6">
       <c r="A375" s="1"/>
       <c r="B375" s="1">
-        <v>60043</v>
+        <v>60044</v>
       </c>
       <c r="C375" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D375" s="1">
         <v>7</v>
@@ -9875,10 +9871,10 @@
     <row r="376" ht="15" customHeight="1" spans="1:6">
       <c r="A376" s="1"/>
       <c r="B376" s="1">
-        <v>60044</v>
+        <v>60045</v>
       </c>
       <c r="C376" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D376" s="1">
         <v>7</v>
@@ -9893,10 +9889,10 @@
     <row r="377" ht="15" customHeight="1" spans="1:6">
       <c r="A377" s="1"/>
       <c r="B377" s="1">
-        <v>60045</v>
+        <v>60046</v>
       </c>
       <c r="C377" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D377" s="1">
         <v>7</v>
@@ -9911,10 +9907,10 @@
     <row r="378" ht="15" customHeight="1" spans="1:6">
       <c r="A378" s="1"/>
       <c r="B378" s="1">
-        <v>60046</v>
+        <v>60047</v>
       </c>
       <c r="C378" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D378" s="1">
         <v>7</v>
@@ -9929,10 +9925,10 @@
     <row r="379" ht="15" customHeight="1" spans="1:6">
       <c r="A379" s="1"/>
       <c r="B379" s="1">
-        <v>60047</v>
+        <v>60048</v>
       </c>
       <c r="C379" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D379" s="1">
         <v>7</v>
@@ -9947,10 +9943,10 @@
     <row r="380" ht="15" customHeight="1" spans="1:6">
       <c r="A380" s="1"/>
       <c r="B380" s="1">
-        <v>60048</v>
+        <v>60049</v>
       </c>
       <c r="C380" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D380" s="1">
         <v>7</v>
@@ -9965,10 +9961,10 @@
     <row r="381" ht="15" customHeight="1" spans="1:6">
       <c r="A381" s="1"/>
       <c r="B381" s="1">
-        <v>60049</v>
+        <v>60050</v>
       </c>
       <c r="C381" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D381" s="1">
         <v>7</v>
@@ -9983,10 +9979,10 @@
     <row r="382" ht="15" customHeight="1" spans="1:6">
       <c r="A382" s="1"/>
       <c r="B382" s="1">
-        <v>60050</v>
+        <v>60051</v>
       </c>
       <c r="C382" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D382" s="1">
         <v>7</v>
@@ -10001,10 +9997,10 @@
     <row r="383" ht="15" customHeight="1" spans="1:6">
       <c r="A383" s="1"/>
       <c r="B383" s="1">
-        <v>60051</v>
+        <v>60052</v>
       </c>
       <c r="C383" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D383" s="1">
         <v>7</v>
@@ -10019,10 +10015,10 @@
     <row r="384" ht="15" customHeight="1" spans="1:6">
       <c r="A384" s="1"/>
       <c r="B384" s="1">
-        <v>60052</v>
+        <v>60053</v>
       </c>
       <c r="C384" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D384" s="1">
         <v>7</v>
@@ -10037,10 +10033,10 @@
     <row r="385" ht="15" customHeight="1" spans="1:6">
       <c r="A385" s="1"/>
       <c r="B385" s="1">
-        <v>60053</v>
+        <v>60054</v>
       </c>
       <c r="C385" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D385" s="1">
         <v>7</v>
@@ -10055,10 +10051,10 @@
     <row r="386" ht="15" customHeight="1" spans="1:6">
       <c r="A386" s="1"/>
       <c r="B386" s="1">
-        <v>60054</v>
+        <v>60055</v>
       </c>
       <c r="C386" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D386" s="1">
         <v>7</v>
@@ -10073,10 +10069,10 @@
     <row r="387" ht="15" customHeight="1" spans="1:6">
       <c r="A387" s="1"/>
       <c r="B387" s="1">
-        <v>60055</v>
+        <v>60056</v>
       </c>
       <c r="C387" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D387" s="1">
         <v>7</v>
@@ -10091,10 +10087,10 @@
     <row r="388" ht="15" customHeight="1" spans="1:6">
       <c r="A388" s="1"/>
       <c r="B388" s="1">
-        <v>60056</v>
+        <v>60057</v>
       </c>
       <c r="C388" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D388" s="1">
         <v>7</v>
@@ -10109,10 +10105,10 @@
     <row r="389" ht="15" customHeight="1" spans="1:6">
       <c r="A389" s="1"/>
       <c r="B389" s="1">
-        <v>60057</v>
+        <v>60058</v>
       </c>
       <c r="C389" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D389" s="1">
         <v>7</v>
@@ -10127,10 +10123,10 @@
     <row r="390" ht="15" customHeight="1" spans="1:6">
       <c r="A390" s="1"/>
       <c r="B390" s="1">
-        <v>60058</v>
+        <v>60059</v>
       </c>
       <c r="C390" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D390" s="1">
         <v>7</v>
@@ -10145,10 +10141,10 @@
     <row r="391" ht="15" customHeight="1" spans="1:6">
       <c r="A391" s="1"/>
       <c r="B391" s="1">
-        <v>60059</v>
+        <v>60060</v>
       </c>
       <c r="C391" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D391" s="1">
         <v>7</v>
@@ -10163,10 +10159,10 @@
     <row r="392" ht="15" customHeight="1" spans="1:6">
       <c r="A392" s="1"/>
       <c r="B392" s="1">
-        <v>60060</v>
+        <v>60061</v>
       </c>
       <c r="C392" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D392" s="1">
         <v>7</v>
@@ -10181,10 +10177,10 @@
     <row r="393" ht="15" customHeight="1" spans="1:6">
       <c r="A393" s="1"/>
       <c r="B393" s="1">
-        <v>60061</v>
+        <v>60062</v>
       </c>
       <c r="C393" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D393" s="1">
         <v>7</v>
@@ -10199,10 +10195,10 @@
     <row r="394" ht="15" customHeight="1" spans="1:6">
       <c r="A394" s="1"/>
       <c r="B394" s="1">
-        <v>60062</v>
+        <v>60063</v>
       </c>
       <c r="C394" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D394" s="1">
         <v>7</v>
@@ -10217,10 +10213,10 @@
     <row r="395" ht="15" customHeight="1" spans="1:6">
       <c r="A395" s="1"/>
       <c r="B395" s="1">
-        <v>60063</v>
+        <v>60064</v>
       </c>
       <c r="C395" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D395" s="1">
         <v>7</v>
@@ -10235,10 +10231,10 @@
     <row r="396" ht="15" customHeight="1" spans="1:6">
       <c r="A396" s="1"/>
       <c r="B396" s="1">
-        <v>60064</v>
+        <v>60065</v>
       </c>
       <c r="C396" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D396" s="1">
         <v>7</v>
@@ -10253,10 +10249,10 @@
     <row r="397" ht="15" customHeight="1" spans="1:6">
       <c r="A397" s="1"/>
       <c r="B397" s="1">
-        <v>60065</v>
+        <v>60066</v>
       </c>
       <c r="C397" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D397" s="1">
         <v>7</v>
@@ -10271,10 +10267,10 @@
     <row r="398" ht="15" customHeight="1" spans="1:6">
       <c r="A398" s="1"/>
       <c r="B398" s="1">
-        <v>60066</v>
+        <v>60067</v>
       </c>
       <c r="C398" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D398" s="1">
         <v>7</v>
@@ -10289,10 +10285,10 @@
     <row r="399" ht="15" customHeight="1" spans="1:6">
       <c r="A399" s="1"/>
       <c r="B399" s="1">
-        <v>60067</v>
+        <v>60068</v>
       </c>
       <c r="C399" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D399" s="1">
         <v>7</v>
@@ -10307,10 +10303,10 @@
     <row r="400" ht="15" customHeight="1" spans="1:6">
       <c r="A400" s="1"/>
       <c r="B400" s="1">
-        <v>60068</v>
+        <v>60069</v>
       </c>
       <c r="C400" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D400" s="1">
         <v>7</v>
@@ -10325,10 +10321,10 @@
     <row r="401" ht="15" customHeight="1" spans="1:6">
       <c r="A401" s="1"/>
       <c r="B401" s="1">
-        <v>60069</v>
+        <v>60070</v>
       </c>
       <c r="C401" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D401" s="1">
         <v>7</v>
@@ -10343,10 +10339,10 @@
     <row r="402" ht="15" customHeight="1" spans="1:6">
       <c r="A402" s="1"/>
       <c r="B402" s="1">
-        <v>60070</v>
+        <v>60071</v>
       </c>
       <c r="C402" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D402" s="1">
         <v>7</v>
@@ -10361,10 +10357,10 @@
     <row r="403" ht="15" customHeight="1" spans="1:6">
       <c r="A403" s="1"/>
       <c r="B403" s="1">
-        <v>60071</v>
+        <v>60072</v>
       </c>
       <c r="C403" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D403" s="1">
         <v>7</v>
@@ -10379,10 +10375,10 @@
     <row r="404" ht="15" customHeight="1" spans="1:6">
       <c r="A404" s="1"/>
       <c r="B404" s="1">
-        <v>60072</v>
+        <v>60073</v>
       </c>
       <c r="C404" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D404" s="1">
         <v>7</v>
@@ -10397,10 +10393,10 @@
     <row r="405" ht="15" customHeight="1" spans="1:6">
       <c r="A405" s="1"/>
       <c r="B405" s="1">
-        <v>60073</v>
+        <v>60074</v>
       </c>
       <c r="C405" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D405" s="1">
         <v>7</v>
@@ -10415,10 +10411,10 @@
     <row r="406" ht="15" customHeight="1" spans="1:6">
       <c r="A406" s="1"/>
       <c r="B406" s="1">
-        <v>60074</v>
+        <v>60075</v>
       </c>
       <c r="C406" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D406" s="1">
         <v>7</v>
@@ -10433,10 +10429,10 @@
     <row r="407" ht="15" customHeight="1" spans="1:6">
       <c r="A407" s="1"/>
       <c r="B407" s="1">
-        <v>60075</v>
+        <v>60076</v>
       </c>
       <c r="C407" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D407" s="1">
         <v>7</v>
@@ -10451,10 +10447,10 @@
     <row r="408" ht="15" customHeight="1" spans="1:6">
       <c r="A408" s="1"/>
       <c r="B408" s="1">
-        <v>60076</v>
+        <v>60077</v>
       </c>
       <c r="C408" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D408" s="1">
         <v>7</v>
@@ -10469,10 +10465,10 @@
     <row r="409" ht="15" customHeight="1" spans="1:6">
       <c r="A409" s="1"/>
       <c r="B409" s="1">
-        <v>60077</v>
+        <v>60078</v>
       </c>
       <c r="C409" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D409" s="1">
         <v>7</v>
@@ -10487,10 +10483,10 @@
     <row r="410" ht="15" customHeight="1" spans="1:6">
       <c r="A410" s="1"/>
       <c r="B410" s="1">
-        <v>60078</v>
+        <v>60079</v>
       </c>
       <c r="C410" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D410" s="1">
         <v>7</v>
@@ -10505,10 +10501,10 @@
     <row r="411" ht="15" customHeight="1" spans="1:6">
       <c r="A411" s="1"/>
       <c r="B411" s="1">
-        <v>60079</v>
+        <v>60080</v>
       </c>
       <c r="C411" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D411" s="1">
         <v>7</v>
@@ -10523,10 +10519,10 @@
     <row r="412" ht="15" customHeight="1" spans="1:6">
       <c r="A412" s="1"/>
       <c r="B412" s="1">
-        <v>60080</v>
+        <v>60081</v>
       </c>
       <c r="C412" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D412" s="1">
         <v>7</v>
@@ -10541,10 +10537,10 @@
     <row r="413" ht="15" customHeight="1" spans="1:6">
       <c r="A413" s="1"/>
       <c r="B413" s="1">
-        <v>60081</v>
+        <v>60082</v>
       </c>
       <c r="C413" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D413" s="1">
         <v>7</v>
@@ -10559,10 +10555,10 @@
     <row r="414" ht="15" customHeight="1" spans="1:6">
       <c r="A414" s="1"/>
       <c r="B414" s="1">
-        <v>60082</v>
+        <v>60083</v>
       </c>
       <c r="C414" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D414" s="1">
         <v>7</v>
@@ -10572,24 +10568,6 @@
       </c>
       <c r="F414" s="1" t="s">
         <v>842</v>
-      </c>
-    </row>
-    <row r="415" ht="15" customHeight="1" spans="1:6">
-      <c r="A415" s="1"/>
-      <c r="B415" s="1">
-        <v>60083</v>
-      </c>
-      <c r="C415" s="1" t="s">
-        <v>678</v>
-      </c>
-      <c r="D415" s="1">
-        <v>7</v>
-      </c>
-      <c r="E415" s="1" t="s">
-        <v>843</v>
-      </c>
-      <c r="F415" s="1" t="s">
-        <v>844</v>
       </c>
     </row>
   </sheetData>
